--- a/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
+++ b/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$390</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$392</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J390"/>
+  <dimension ref="A1:J392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11894,7 +11894,7 @@
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>OUR-15</t>
+          <t>OUR-120</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -11909,17 +11909,17 @@
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Leave a list, then start a new one WITHOUT deleting the old</t>
+          <t>Waiting-with-no-code says so, and the re-mint is a real button</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>Leave a shared list. On the closed screen, start a new shared list with someone else.</t>
+          <t>Mint a code, leave Ours entirely (back to Today), then come back to Ours before anyone joins.</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>Starting a new list is offered on the closed screen itself and works. The old list is NOT deleted and is still readable. At no point is destroying it the only way forward.</t>
+          <t>The screen is titled 'Waiting for your person', NOT 'Read this to your person' over an empty space (the code renders exactly once; the server keeps only a hash, so it can never be re-shown). 'Get a new code' is a full primary button in this state, not a quiet text link (the 2026-09-13 field report walked right past the link: 'no easy way to... regenerate the code'). While the code IS still on screen, the title and the quiet link stay as they were.</t>
         </is>
       </c>
       <c r="G280" s="7" t="inlineStr">
@@ -11934,7 +11934,7 @@
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>OUR-16</t>
+          <t>OUR-121</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>A failed read never offers to start a list you already have</t>
+          <t>Whose email, and which code goes where</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, turn the network off and open Ours.</t>
+          <t>Signed out: read the Menu's Ours line, open Ours, read the signed-out screen, tap Sign in and read the field. Then, on the sign-in code step, paste an Ours-style code (letters in it). Separately, signed in, open Ours 'I have a code' and type a 6-digit emailed sign-in code.</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>A calm connection line. The screen never says you have no shared list and never offers to start one. Turning the network back on recovers without a restart.</t>
+          <t>The Menu's Ours line reads 'A list kept with one person. Sign in first.' (the old 'Needs your email, no password' invited typing the PARTNER'S email; a real user did exactly that on 2026-09-13 and it became their account). The Ours signed-out screen opens with the plain fact 'You're not signed in on this phone.' The sign-in email field is labelled 'Your own email', and the subtitle says sharing happens later, in Ours, with a code, never by typing the partner's email here. Letters in the 6-digit code field draw the calm hint that it will be an Ours invite code (a hint, never an auto-redirect or a cleared field). Six bare digits failing in the Ours join field add one line naming the emailed sign-in code as the likely mix-up, alongside the unchanged honest failure.</t>
         </is>
       </c>
       <c r="G281" s="7" t="inlineStr">
@@ -11974,7 +11974,7 @@
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>OUR-17</t>
+          <t>OUR-15</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -11982,24 +11982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C282" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C282" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>A list nobody joined can be left</t>
+          <t>Leave a list, then start a new one WITHOUT deleting the old</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>Create a list, get a code, give it to nobody. Return to Ours.</t>
+          <t>Leave a shared list. On the closed screen, start a new shared list with someone else.</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>There is a way out on the waiting screen, and its wording does not claim it closes for two people. After leaving, you can start or join a list again.</t>
+          <t>Starting a new list is offered on the closed screen itself and works. The old list is NOT deleted and is still readable. At no point is destroying it the only way forward.</t>
         </is>
       </c>
       <c r="G282" s="7" t="inlineStr">
@@ -12014,7 +12014,7 @@
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>OUR-18</t>
+          <t>OUR-16</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
@@ -12022,24 +12022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C283" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C283" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>The arrival announces once and stays announced</t>
+          <t>A failed read never offers to start a list you already have</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>Sit on the waiting screen while the other account joins. Background the app and return.</t>
+          <t>With a live shared list, turn the network off and open Ours.</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>The name appears once and does not flicker back to waiting and re-announce. The way out beside it ('that wasn't who I meant') never appears on a list you did not just gain a person on.</t>
+          <t>A calm connection line. The screen never says you have no shared list and never offers to start one. Turning the network back on recovers without a restart.</t>
         </is>
       </c>
       <c r="G283" s="7" t="inlineStr">
@@ -12054,7 +12054,7 @@
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>OUR-19</t>
+          <t>OUR-17</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -12069,17 +12069,17 @@
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>A repeat the app cannot read is SHOWN, never hidden</t>
+          <t>A list nobody joined can be left</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>Requires two app versions. On the newer one, set a shared task to a cadence the older build does not have. Open the list on the older build.</t>
+          <t>Create a list, get a code, give it to nobody. Return to Ours.</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>The task is visible on both, with whatever cadence line the newer app left. It is never silently absent from one person's list, and the older app does not erase the schedule when it syncs.</t>
+          <t>There is a way out on the waiting screen, and its wording does not claim it closes for two people. After leaving, you can start or join a list again.</t>
         </is>
       </c>
       <c r="G284" s="7" t="inlineStr">
@@ -12094,7 +12094,7 @@
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>OUR-20</t>
+          <t>OUR-18</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
@@ -12102,24 +12102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C285" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C285" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>The room opens from Today and from the Menu</t>
+          <t>The arrival announces once and stays announced</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, tap the 'Ours · {name}' row on Today. Then go back and reach it through Menu › Ours.</t>
+          <t>Sit on the waiting screen while the other account joins. Background the app and return.</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>Both land on the shared list itself, not the pairing screen. The header line reads 'Kept with {their name}' and tapping it goes to the pairing/management screen.</t>
+          <t>The name appears once and does not flicker back to waiting and re-announce. The way out beside it ('that wasn't who I meant') never appears on a list you did not just gain a person on.</t>
         </is>
       </c>
       <c r="G285" s="7" t="inlineStr">
@@ -12134,7 +12134,7 @@
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>OUR-21</t>
+          <t>OUR-19</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -12142,24 +12142,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C286" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C286" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>Add, tick and UN-tick on the shared list</t>
+          <t>A repeat the app cannot read is SHOWN, never hidden</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>Add a task in the room. Tick it. Un-tick it. Watch the other account (reload or wait ~15s).</t>
+          <t>Requires two app versions. On the newer one, set a shared task to a cadence the older build does not have. Open the list on the older build.</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>Every step appears on both. Un-ticking works as easily as ticking, on both sides. No affirmation or celebration fires on Ours.</t>
+          <t>The task is visible on both, with whatever cadence line the newer app left. It is never silently absent from one person's list, and the older app does not erase the schedule when it syncs.</t>
         </is>
       </c>
       <c r="G286" s="7" t="inlineStr">
@@ -12174,7 +12174,7 @@
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>OUR-22</t>
+          <t>OUR-20</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -12189,17 +12189,17 @@
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Un-tick a one-off the DAY AFTER it was ticked</t>
+          <t>The room opens from Today and from the Menu</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>Tick a shared one-off. Change the device date to tomorrow (or wait a day), reopen the room, tap it again.</t>
+          <t>With a live shared list, tap the 'Ours · {name}' row on Today. Then go back and reach it through Menu › Ours.</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>It un-ticks. (The pre-fix build could never un-tick it again, on any device, forever.)</t>
+          <t>Both land on the shared list itself, not the pairing screen. The header line reads 'Kept with {their name}' and tapping it goes to the pairing/management screen.</t>
         </is>
       </c>
       <c r="G287" s="7" t="inlineStr">
@@ -12214,7 +12214,7 @@
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>OUR-23</t>
+          <t>OUR-21</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -12229,17 +12229,17 @@
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Bring to my Today makes a COPY, and marks only yours</t>
+          <t>Add, tick and UN-tick on the shared list</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>Hold a shared row, tap 'Bring to my Today'. Look at your Today, then at the shared list on BOTH accounts.</t>
+          <t>Add a task in the room. Tick it. Un-tick it. Watch the other account (reload or wait ~15s).</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>Your Today shows the task with a faint '· Ours'. The shared row is completely unchanged on both sides, with no marker of any kind. The held card now reads 'Already on your Today' and cannot make a second copy.</t>
+          <t>Every step appears on both. Un-ticking works as easily as ticking, on both sides. No affirmation or celebration fires on Ours.</t>
         </is>
       </c>
       <c r="G288" s="7" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>OUR-24</t>
+          <t>OUR-22</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -12269,17 +12269,17 @@
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Your tick on the copy closes both</t>
+          <t>Un-tick a one-off the DAY AFTER it was ticked</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>Tick the brought copy on your Today. Check the shared list on the other account.</t>
+          <t>Tick a shared one-off. Change the device date to tomorrow (or wait a day), reopen the room, tap it again.</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>The shared row is done. It enters YOUR Lookback. Nothing on the other side says who did it.</t>
+          <t>It un-ticks. (The pre-fix build could never un-tick it again, on any device, forever.)</t>
         </is>
       </c>
       <c r="G289" s="7" t="inlineStr">
@@ -12294,7 +12294,7 @@
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>OUR-25</t>
+          <t>OUR-23</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -12309,17 +12309,17 @@
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>Ticking a brought copy on a device that has NEVER opened the room</t>
+          <t>Bring to my Today makes a COPY, and marks only yours</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>Bring a task over on phone A. Sign in on a second device (or clear its local data) and go straight to Today WITHOUT opening Ours. Tick the copy there.</t>
+          <t>Hold a shared row, tap 'Bring to my Today'. Look at your Today, then at the shared list on BOTH accounts.</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>The shared row closes. (The pre-fix build silently discarded the tick with no error.)</t>
+          <t>Your Today shows the task with a faint '· Ours'. The shared row is completely unchanged on both sides, with no marker of any kind. The held card now reads 'Already on your Today' and cannot make a second copy.</t>
         </is>
       </c>
       <c r="G290" s="7" t="inlineStr">
@@ -12334,7 +12334,7 @@
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>OUR-26</t>
+          <t>OUR-24</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
@@ -12349,17 +12349,17 @@
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Their tick leaves a rest-note, never a strike-through</t>
+          <t>Your tick on the copy closes both</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>Bring a task over. On the OTHER account, tick the shared row. Return to your Today.</t>
+          <t>Tick the brought copy on your Today. Check the shared list on the other account.</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>Your copy is gone from the day, replaced by a dashed sage line: 'Handled on Ours. It's off your day.' It is NOT struck through and does NOT appear in your Lookback. Leaving Today and coming back clears the note.</t>
+          <t>The shared row is done. It enters YOUR Lookback. Nothing on the other side says who did it.</t>
         </is>
       </c>
       <c r="G291" s="7" t="inlineStr">
@@ -12374,7 +12374,7 @@
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>OUR-27</t>
+          <t>OUR-25</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -12382,24 +12382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C292" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C292" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>Share to Ours warns about the length BEFORE it copies</t>
+          <t>Ticking a brought copy on a device that has NEVER opened the room</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>Hold one of your own Today tasks with a very long title (500+ chars), open More, tap 'Share to Ours'.</t>
+          <t>Bring a task over on phone A. Sign in on a second device (or clear its local data) and go straight to Today WITHOUT opening Ours. Tick the copy there.</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>A line says Ours keeps titles shorter and this one will be trimmed, BEFORE the copy is made. The copy appears on the shared list. 'Share to Ours' is absent entirely when there is no live list.</t>
+          <t>The shared row closes. (The pre-fix build silently discarded the tick with no error.)</t>
         </is>
       </c>
       <c r="G292" s="7" t="inlineStr">
@@ -12414,7 +12414,7 @@
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>OUR-28</t>
+          <t>OUR-26</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
@@ -12429,17 +12429,17 @@
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>A repeat set on Ours uses the SAME cadence sheet as home</t>
+          <t>Their tick leaves a rest-note, never a strike-through</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>Hold a shared row, tap 'Repeat…'. Compare with Menu › Repeating › Edit on a personal task.</t>
+          <t>Bring a task over. On the OTHER account, tick the shared row. Return to your Today.</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>Identical controls. The commit button NAMES the cadence ('Every day', 'Every 2 days'), on both. The Ours sheet adds one line: 'You'll both see it on its day.' It appears on its days for both people.</t>
+          <t>Your copy is gone from the day, replaced by a dashed sage line: 'Handled on Ours. It's off your day.' It is NOT struck through and does NOT appear in your Lookback. Leaving Today and coming back clears the note.</t>
         </is>
       </c>
       <c r="G293" s="7" t="inlineStr">
@@ -12454,7 +12454,7 @@
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>OUR-29</t>
+          <t>OUR-27</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -12462,24 +12462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C294" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C294" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>A cadence this build cannot read is inert, and says why</t>
+          <t>Share to Ours warns about the length BEFORE it copies</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>Get a shared row carrying a recurrence this build does not understand (a newer build, or hand-write one via the API).</t>
+          <t>Hold one of your own Today tasks with a very long title (500+ chars), open More, tap 'Share to Ours'.</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>The row is SHOWN, never hidden. Tapping it does nothing and a line explains it is safe and will appear on its days after an update. 'Repeat…' is withheld. It never marks itself done.</t>
+          <t>A line says Ours keeps titles shorter and this one will be trimmed, BEFORE the copy is made. The copy appears on the shared list. 'Share to Ours' is absent entirely when there is no live list.</t>
         </is>
       </c>
       <c r="G294" s="7" t="inlineStr">
@@ -12494,7 +12494,7 @@
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>OUR-30</t>
+          <t>OUR-28</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
@@ -12502,24 +12502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C295" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C295" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash marks what changed, and never your own edits</t>
+          <t>A repeat set on Ours uses the SAME cadence sheet as home</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>Have the other account add and change a few rows. Open the room. Then tick something yourself and reopen.</t>
+          <t>Hold a shared row, tap 'Repeat…'. Compare with Menu › Repeating › Edit on a personal task.</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>Their changed rows carry a tint and a firmer border on arrival; a screen reader says 'changed since you last looked'. Your OWN edits are never washed. Leaving and returning clears it.</t>
+          <t>Identical controls. The commit button NAMES the cadence ('Every day', 'Every 2 days'), on both. The Ours sheet adds one line: 'You'll both see it on its day.' It appears on its days for both people.</t>
         </is>
       </c>
       <c r="G295" s="7" t="inlineStr">
@@ -12534,7 +12534,7 @@
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>OUR-31</t>
+          <t>OUR-29</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -12542,24 +12542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C296" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C296" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>Recently removed puts a task back</t>
+          <t>A cadence this build cannot read is inert, and says why</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>Remove a shared row. Scroll to the foot of the list.</t>
+          <t>Get a shared row carrying a recurrence this build does not understand (a newer build, or hand-write one via the API).</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>It sits under 'Recently removed', dimmed, with 'Put it back'. Restoring returns it for both people. Nothing anywhere says which of you removed it.</t>
+          <t>The row is SHOWN, never hidden. Tapping it does nothing and a line explains it is safe and will appear on its days after an update. 'Repeat…' is withheld. It never marks itself done.</t>
         </is>
       </c>
       <c r="G296" s="7" t="inlineStr">
@@ -12574,7 +12574,7 @@
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>OUR-32</t>
+          <t>OUR-30</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -12589,17 +12589,17 @@
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>Removing a shared REPEAT does not pretend to be 'Skip today'</t>
+          <t>The quiet wash marks what changed, and never your own edits</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>Hold a repeating shared row and look at the shelf.</t>
+          <t>Have the other account add and change a few rows. Open the room. Then tick something yourself and reopen.</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>It reads 'Remove', not 'Skip today', and the spoken label names removing the repeat. (The shared list has no per-day skip; the pre-fix build promised one and deleted the series for both people.)</t>
+          <t>Their changed rows carry a tint and a firmer border on arrival; a screen reader says 'changed since you last looked'. Your OWN edits are never washed. Leaving and returning clears it.</t>
         </is>
       </c>
       <c r="G297" s="7" t="inlineStr">
@@ -12614,7 +12614,7 @@
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>OUR-33</t>
+          <t>OUR-31</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -12622,24 +12622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C298" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C298" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>A closed list is still readable, and read-only</t>
+          <t>Recently removed puts a task back</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>Leave a list. Open it from the archive on the pairing screen.</t>
+          <t>Remove a shared row. Scroll to the foot of the list.</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>Every row is readable. The capture bar is GONE. Ticking, renaming, removing and re-cadencing all do nothing, and each row says why. Each row still offers taking a copy for yourself.</t>
+          <t>It sits under 'Recently removed', dimmed, with 'Put it back'. Restoring returns it for both people. Nothing anywhere says which of you removed it.</t>
         </is>
       </c>
       <c r="G298" s="7" t="inlineStr">
@@ -12654,7 +12654,7 @@
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>OUR-34</t>
+          <t>OUR-32</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
@@ -12669,17 +12669,17 @@
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>The archive lists closed lists, and puts them away</t>
+          <t>Removing a shared REPEAT does not pretend to be 'Skip today'</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>With at least one closed list, look under 'Lists you have kept' on the pairing screen.</t>
+          <t>Hold a repeating shared row and look at the shelf.</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>Purpose and closed MONTH only, no counts of any kind. 'Put it away' hides it from the default view; 'Show the ones put away' brings it back. Nothing is deleted.</t>
+          <t>It reads 'Remove', not 'Skip today', and the spoken label names removing the repeat. (The shared list has no per-day skip; the pre-fix build promised one and deleted the series for both people.)</t>
         </is>
       </c>
       <c r="G299" s="7" t="inlineStr">
@@ -12694,7 +12694,7 @@
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>OUR-35</t>
+          <t>OUR-33</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
@@ -12709,17 +12709,17 @@
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>Reopening together is a handshake, never unilateral</t>
+          <t>A closed list is still readable, and read-only</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Reopen together…'. Read the code to the second account and enter it in the ordinary join field.</t>
+          <t>Leave a list. Open it from the archive on the pairing screen.</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>The offering side gets a code and nothing reopens yet. Entering it in the SAME field used for a new list reopens the list for both, with everything as it was. It is never asked which kind of code it is.</t>
+          <t>Every row is readable. The capture bar is GONE. Ticking, renaming, removing and re-cadencing all do nothing, and each row says why. Each row still offers taking a copy for yourself.</t>
         </is>
       </c>
       <c r="G300" s="7" t="inlineStr">
@@ -12734,7 +12734,7 @@
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>OUR-36</t>
+          <t>OUR-34</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -12742,24 +12742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C301" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C301" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>Delete for good commits when the screen closes, not on a timer</t>
+          <t>The archive lists closed lists, and puts them away</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
+          <t>With at least one closed list, look under 'Lists you have kept' on the pairing screen.</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
+          <t>Purpose and closed MONTH only, no counts of any kind. 'Put it away' hides it from the default view; 'Show the ones put away' brings it back. Nothing is deleted.</t>
         </is>
       </c>
       <c r="G301" s="7" t="inlineStr">
@@ -12774,7 +12774,7 @@
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
         <is>
-          <t>OUR-37</t>
+          <t>OUR-35</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
@@ -12782,24 +12782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C302" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C302" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>Rename yourself, and only yourself</t>
+          <t>Reopening together is a handshake, never unilateral</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
+          <t>On a closed list, tap 'Reopen together…'. Read the code to the second account and enter it in the ordinary join field.</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
+          <t>The offering side gets a code and nothing reopens yet. Entering it in the SAME field used for a new list reopens the list for both, with everything as it was. It is never asked which kind of code it is.</t>
         </is>
       </c>
       <c r="G302" s="7" t="inlineStr">
@@ -12814,7 +12814,7 @@
     <row r="303">
       <c r="A303" s="6" t="inlineStr">
         <is>
-          <t>OUR-38</t>
+          <t>OUR-36</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
@@ -12822,24 +12822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C303" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C303" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>A dropped signal never throws you out of the room</t>
+          <t>Delete for good commits when the screen closes, not on a timer</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
+          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
+          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
         </is>
       </c>
       <c r="G303" s="7" t="inlineStr">
@@ -12854,7 +12854,7 @@
     <row r="304">
       <c r="A304" s="6" t="inlineStr">
         <is>
-          <t>OUR-39</t>
+          <t>OUR-37</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -12862,24 +12862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C304" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C304" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>Report this list reaches us and tells nobody else</t>
+          <t>Rename yourself, and only yourself</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
+          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
+          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
         </is>
       </c>
       <c r="G304" s="7" t="inlineStr">
@@ -12894,7 +12894,7 @@
     <row r="305">
       <c r="A305" s="6" t="inlineStr">
         <is>
-          <t>OUR-40</t>
+          <t>OUR-38</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -12902,24 +12902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C305" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C305" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
+          <t>A dropped signal never throws you out of the room</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
+          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
+          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
         </is>
       </c>
       <c r="G305" s="7" t="inlineStr">
@@ -12934,7 +12934,7 @@
     <row r="306">
       <c r="A306" s="6" t="inlineStr">
         <is>
-          <t>OUR-41</t>
+          <t>OUR-39</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -12942,24 +12942,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C306" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C306" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>Leaving is the block, and needs no reason</t>
+          <t>Report this list reaches us and tells nobody else</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap 'Leave this list'.</t>
+          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
+          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
         </is>
       </c>
       <c r="G306" s="7" t="inlineStr">
@@ -12974,32 +12974,32 @@
     <row r="307">
       <c r="A307" s="6" t="inlineStr">
         <is>
-          <t>LEG-05</t>
+          <t>OUR-40</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
         <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="C307" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="C307" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>The shared-list clauses are in both copies of both documents</t>
+          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
+          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
+          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
         </is>
       </c>
       <c r="G307" s="7" t="inlineStr">
@@ -13014,7 +13014,7 @@
     <row r="308">
       <c r="A308" s="6" t="inlineStr">
         <is>
-          <t>OUR-42</t>
+          <t>OUR-41</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
@@ -13022,24 +13022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C308" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C308" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>A change on one phone appears on the other WITHOUT touching it</t>
+          <t>Leaving is the block, and needs no reason</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
+          <t>On a live list, tap 'Leave this list'.</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
+          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
         </is>
       </c>
       <c r="G308" s="7" t="inlineStr">
@@ -13054,32 +13054,32 @@
     <row r="309">
       <c r="A309" s="6" t="inlineStr">
         <is>
-          <t>OUR-43</t>
+          <t>LEG-05</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C309" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C309" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>Opening your own list does not bounce you back</t>
+          <t>The shared-list clauses are in both copies of both documents</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
+          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
+          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
         </is>
       </c>
       <c r="G309" s="7" t="inlineStr">
@@ -13094,7 +13094,7 @@
     <row r="310">
       <c r="A310" s="6" t="inlineStr">
         <is>
-          <t>OUR-44</t>
+          <t>OUR-42</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -13102,24 +13102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C310" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C310" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>The pairing screen offers a way INTO the list</t>
+          <t>A change on one phone appears on the other WITHOUT touching it</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>Finish pairing, then look at the pairing screen.</t>
+          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
+          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
         </is>
       </c>
       <c r="G310" s="7" t="inlineStr">
@@ -13134,7 +13134,7 @@
     <row r="311">
       <c r="A311" s="6" t="inlineStr">
         <is>
-          <t>OUR-45</t>
+          <t>OUR-43</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -13142,24 +13142,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C311" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C311" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash appears and then takes itself away</t>
+          <t>Opening your own list does not bounce you back</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
+          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
+          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
         </is>
       </c>
       <c r="G311" s="7" t="inlineStr">
@@ -13174,7 +13174,7 @@
     <row r="312">
       <c r="A312" s="6" t="inlineStr">
         <is>
-          <t>OUR-47</t>
+          <t>OUR-44</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -13189,17 +13189,17 @@
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>The Ours door on Today is findable</t>
+          <t>The pairing screen offers a way INTO the list</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>With a live list, look at Today.</t>
+          <t>Finish pairing, then look at the pairing screen.</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>A tinted, accented card carrying the list's name, not a hairline footnote. Absent entirely when there is no live list.</t>
+          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
         </is>
       </c>
       <c r="G312" s="7" t="inlineStr">
@@ -13214,7 +13214,7 @@
     <row r="313">
       <c r="A313" s="6" t="inlineStr">
         <is>
-          <t>OUR-48</t>
+          <t>OUR-45</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -13222,24 +13222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C313" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C313" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>Their tick marks your copy DONE and leaves it on your day</t>
+          <t>The quiet wash appears and then takes itself away</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
+          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
+          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
         </is>
       </c>
       <c r="G313" s="7" t="inlineStr">
@@ -13254,7 +13254,7 @@
     <row r="314">
       <c r="A314" s="6" t="inlineStr">
         <is>
-          <t>OUR-49</t>
+          <t>OUR-47</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -13262,24 +13262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C314" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C314" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>A settled copy carries a completion DATE, not just a done flag</t>
+          <t>The Ours door on Today is findable</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
+          <t>With a live list, look at Today.</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
+          <t>A tinted, accented card carrying the list's name, not a hairline footnote. Absent entirely when there is no live list.</t>
         </is>
       </c>
       <c r="G314" s="7" t="inlineStr">
@@ -13294,7 +13294,7 @@
     <row r="315">
       <c r="A315" s="6" t="inlineStr">
         <is>
-          <t>OUR-50</t>
+          <t>OUR-48</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -13302,24 +13302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C315" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C315" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>A finished copy can be brought over again</t>
+          <t>Their tick marks your copy DONE and leaves it on your day</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, hold that row in Ours.</t>
+          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
+          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
         </is>
       </c>
       <c r="G315" s="7" t="inlineStr">
@@ -13334,7 +13334,7 @@
     <row r="316">
       <c r="A316" s="6" t="inlineStr">
         <is>
-          <t>OUR-51</t>
+          <t>OUR-49</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -13349,17 +13349,17 @@
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>Your own edit never highlights; their later edit always does</t>
+          <t>A settled copy carries a completion DATE, not just a done flag</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
+          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
+          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
         </is>
       </c>
       <c r="G316" s="7" t="inlineStr">
@@ -13374,7 +13374,7 @@
     <row r="317">
       <c r="A317" s="6" t="inlineStr">
         <is>
-          <t>OUR-52</t>
+          <t>OUR-50</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -13389,17 +13389,17 @@
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>The highlight arrives at once and fades away</t>
+          <t>A finished copy can be brought over again</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>Have B change a row while A is on the list.</t>
+          <t>After OUR-48, hold that row in Ours.</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
+          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
         </is>
       </c>
       <c r="G317" s="7" t="inlineStr">
@@ -13414,7 +13414,7 @@
     <row r="318">
       <c r="A318" s="6" t="inlineStr">
         <is>
-          <t>OUR-53</t>
+          <t>OUR-51</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -13422,24 +13422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C318" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C318" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>Two devices share ONE clock</t>
+          <t>Your own edit never highlights; their later edit always does</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
+          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
+          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
         </is>
       </c>
       <c r="G318" s="7" t="inlineStr">
@@ -13454,7 +13454,7 @@
     <row r="319">
       <c r="A319" s="6" t="inlineStr">
         <is>
-          <t>OUR-54</t>
+          <t>OUR-52</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -13462,24 +13462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C319" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C319" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>The debug panel is opt-in and carries no task text</t>
+          <t>The highlight arrives at once and fades away</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
+          <t>Have B change a row while A is on the list.</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
+          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
         </is>
       </c>
       <c r="G319" s="7" t="inlineStr">
@@ -13494,7 +13494,7 @@
     <row r="320">
       <c r="A320" s="6" t="inlineStr">
         <is>
-          <t>OUR-55</t>
+          <t>OUR-53</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -13502,24 +13502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C320" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C320" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>Capture on Ours IS Today's capture</t>
+          <t>Two devices share ONE clock</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>Open a shared list and tap the launcher at the foot of the screen.</t>
+          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>The same panel Today opens: the same input, the same Speak button (web), the same door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
+          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
         </is>
       </c>
       <c r="G320" s="7" t="inlineStr">
@@ -13534,7 +13534,7 @@
     <row r="321">
       <c r="A321" s="6" t="inlineStr">
         <is>
-          <t>OUR-56</t>
+          <t>OUR-54</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -13542,24 +13542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C321" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C321" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Repeating can be set AT capture, without knowing a gesture</t>
+          <t>The debug panel is opt-in and carries no task text</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
+          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
+          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
         </is>
       </c>
       <c r="G321" s="7" t="inlineStr">
@@ -13574,7 +13574,7 @@
     <row r="322">
       <c r="A322" s="6" t="inlineStr">
         <is>
-          <t>OUR-57</t>
+          <t>OUR-55</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -13582,24 +13582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C322" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C322" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>A dump becomes several shared rows, in the order typed</t>
+          <t>Capture on Ours IS Today's capture</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>Type three lines into the Ours capture and Add.</t>
+          <t>Open a shared list and tap the launcher at the foot of the screen.</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
+          <t>The same panel Today opens: the same input, the same Speak button (web), the same door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
         </is>
       </c>
       <c r="G322" s="7" t="inlineStr">
@@ -13614,7 +13614,7 @@
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
         <is>
-          <t>OUR-58</t>
+          <t>OUR-56</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -13629,17 +13629,17 @@
       </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
-          <t>The shared door offers When and Repeating, never Steps</t>
+          <t>Repeating can be set AT capture, without knowing a gesture</t>
         </is>
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>Open the door on Ours and compare it with the door on Today.</t>
+          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
         </is>
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
+          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
         </is>
       </c>
       <c r="G323" s="7" t="inlineStr">
@@ -13654,7 +13654,7 @@
     <row r="324">
       <c r="A324" s="6" t="inlineStr">
         <is>
-          <t>OUR-59</t>
+          <t>OUR-57</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -13669,17 +13669,17 @@
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>Typed text survives closing the panel</t>
+          <t>A dump becomes several shared rows, in the order typed</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>Type half a sentence into the Ours capture, tap Close, tick something, then reopen the panel.</t>
+          <t>Type three lines into the Ours capture and Add.</t>
         </is>
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>The half sentence is still there. The panel is hidden, never unmounted. The door resets to no-repeat, the words never reset.</t>
+          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
         </is>
       </c>
       <c r="G324" s="7" t="inlineStr">
@@ -13694,7 +13694,7 @@
     <row r="325">
       <c r="A325" s="6" t="inlineStr">
         <is>
-          <t>OUR-60</t>
+          <t>OUR-58</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -13702,29 +13702,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C325" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C325" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>The Ours capture rides above the keyboard</t>
+          <t>The shared door offers When and Repeating, never Steps</t>
         </is>
       </c>
       <c r="E325" s="9" t="inlineStr">
         <is>
-          <t>On a real Android device, open the Ours capture and start typing.</t>
+          <t>Open the door on Ours and compare it with the door on Today.</t>
         </is>
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>The panel and its Add button stay visible above the keyboard. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
+          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
         </is>
       </c>
       <c r="G325" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H325" s="7" t="inlineStr"/>
@@ -13734,7 +13734,7 @@
     <row r="326">
       <c r="A326" s="6" t="inlineStr">
         <is>
-          <t>OUR-61</t>
+          <t>OUR-59</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -13742,24 +13742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C326" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C326" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
-          <t>No AI on the shared capture</t>
+          <t>Typed text survives closing the panel</t>
         </is>
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>Open the Ours capture with AI enabled in Settings.</t>
+          <t>Type half a sentence into the Ours capture, tap Close, tick something, then reopen the panel.</t>
         </is>
       </c>
       <c r="F326" s="9" t="inlineStr">
         <is>
-          <t>No 'Break it down' and no 'Sort for me': steps a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
+          <t>The half sentence is still there. The panel is hidden, never unmounted. The door resets to no-repeat, the words never reset.</t>
         </is>
       </c>
       <c r="G326" s="7" t="inlineStr">
@@ -13774,7 +13774,7 @@
     <row r="327">
       <c r="A327" s="6" t="inlineStr">
         <is>
-          <t>OUR-62</t>
+          <t>OUR-60</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -13782,24 +13782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C327" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C327" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>Scan (premium) reaches the shared capture</t>
+          <t>The Ours capture rides above the keyboard</t>
         </is>
       </c>
       <c r="E327" s="9" t="inlineStr">
         <is>
-          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
+          <t>On a real Android device, open the Ours capture and start typing.</t>
         </is>
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>The words land IN the capture box, not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
+          <t>The panel and its Add button stay visible above the keyboard. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
         </is>
       </c>
       <c r="G327" s="7" t="inlineStr">
@@ -13814,7 +13814,7 @@
     <row r="328">
       <c r="A328" s="6" t="inlineStr">
         <is>
-          <t>OUR-63</t>
+          <t>OUR-61</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -13822,24 +13822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C328" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C328" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
+          <t>No AI on the shared capture</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
+          <t>Open the Ours capture with AI enabled in Settings.</t>
         </is>
       </c>
       <c r="F328" s="9" t="inlineStr">
         <is>
-          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
+          <t>No 'Break it down' and no 'Sort for me': steps a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
         </is>
       </c>
       <c r="G328" s="7" t="inlineStr">
@@ -13854,7 +13854,7 @@
     <row r="329">
       <c r="A329" s="6" t="inlineStr">
         <is>
-          <t>OUR-64</t>
+          <t>OUR-62</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -13862,29 +13862,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C329" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C329" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>The photo never reaches the shared list</t>
+          <t>Scan (premium) reaches the shared capture</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>Scan something into Ours and Add it. Check the other device.</t>
+          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
         </is>
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
+          <t>The words land IN the capture box, not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
         </is>
       </c>
       <c r="G329" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H329" s="7" t="inlineStr"/>
@@ -13894,7 +13894,7 @@
     <row r="330">
       <c r="A330" s="6" t="inlineStr">
         <is>
-          <t>OUR-65</t>
+          <t>OUR-63</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -13902,24 +13902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C330" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C330" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>Scan is absent when AI is off</t>
+          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>Turn AI off in Settings, then open the Ours capture.</t>
+          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
         </is>
       </c>
       <c r="F330" s="9" t="inlineStr">
         <is>
-          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
+          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
         </is>
       </c>
       <c r="G330" s="7" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="331">
       <c r="A331" s="6" t="inlineStr">
         <is>
-          <t>OUR-66</t>
+          <t>OUR-64</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -13942,24 +13942,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C331" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C331" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D331" s="9" t="inlineStr">
         <is>
-          <t>A repeating shared row appears on BOTH Todays on its day</t>
+          <t>The photo never reaches the shared list</t>
         </is>
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
+          <t>Scan something into Ours and Add it. Check the other device.</t>
         </is>
       </c>
       <c r="F331" s="9" t="inlineStr">
         <is>
-          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
+          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
         </is>
       </c>
       <c r="G331" s="7" t="inlineStr">
@@ -13974,7 +13974,7 @@
     <row r="332">
       <c r="A332" s="6" t="inlineStr">
         <is>
-          <t>OUR-67</t>
+          <t>OUR-65</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -13982,24 +13982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C332" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C332" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D332" s="9" t="inlineStr">
         <is>
-          <t>An UNDATED shared row never reaches Today</t>
+          <t>Scan is absent when AI is off</t>
         </is>
       </c>
       <c r="E332" s="9" t="inlineStr">
         <is>
-          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
+          <t>Turn AI off in Settings, then open the Ours capture.</t>
         </is>
       </c>
       <c r="F332" s="9" t="inlineStr">
         <is>
-          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
+          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
         </is>
       </c>
       <c r="G332" s="7" t="inlineStr">
@@ -14014,7 +14014,7 @@
     <row r="333">
       <c r="A333" s="6" t="inlineStr">
         <is>
-          <t>OUR-68</t>
+          <t>OUR-66</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -14029,17 +14029,17 @@
       </c>
       <c r="D333" s="9" t="inlineStr">
         <is>
-          <t>Shared rows never make the day look heavier</t>
+          <t>A repeating shared row appears on BOTH Todays on its day</t>
         </is>
       </c>
       <c r="E333" s="9" t="inlineStr">
         <is>
-          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
+          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
         </is>
       </c>
       <c r="F333" s="9" t="inlineStr">
         <is>
-          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
+          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
         </is>
       </c>
       <c r="G333" s="7" t="inlineStr">
@@ -14054,7 +14054,7 @@
     <row r="334">
       <c r="A334" s="6" t="inlineStr">
         <is>
-          <t>OUR-69</t>
+          <t>OUR-67</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -14069,17 +14069,17 @@
       </c>
       <c r="D334" s="9" t="inlineStr">
         <is>
-          <t>Ticking a shared row from Today closes it for both</t>
+          <t>An UNDATED shared row never reaches Today</t>
         </is>
       </c>
       <c r="E334" s="9" t="inlineStr">
         <is>
-          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
+          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
         </is>
       </c>
       <c r="F334" s="9" t="inlineStr">
         <is>
-          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
+          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
         </is>
       </c>
       <c r="G334" s="7" t="inlineStr">
@@ -14094,7 +14094,7 @@
     <row r="335">
       <c r="A335" s="6" t="inlineStr">
         <is>
-          <t>OUR-70</t>
+          <t>OUR-68</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -14102,24 +14102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C335" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C335" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D335" s="9" t="inlineStr">
         <is>
-          <t>A dated shared row shows from its day onward, never before</t>
+          <t>Shared rows never make the day look heavier</t>
         </is>
       </c>
       <c r="E335" s="9" t="inlineStr">
         <is>
-          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
+          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
         </is>
       </c>
       <c r="F335" s="9" t="inlineStr">
         <is>
-          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
+          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
         </is>
       </c>
       <c r="G335" s="7" t="inlineStr">
@@ -14134,7 +14134,7 @@
     <row r="336">
       <c r="A336" s="6" t="inlineStr">
         <is>
-          <t>OUR-71</t>
+          <t>OUR-69</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -14149,17 +14149,17 @@
       </c>
       <c r="D336" s="9" t="inlineStr">
         <is>
-          <t>The shared capture rests on Anytime</t>
+          <t>Ticking a shared row from Today closes it for both</t>
         </is>
       </c>
       <c r="E336" s="9" t="inlineStr">
         <is>
-          <t>Open the Ours capture and open the door.</t>
+          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
         </is>
       </c>
       <c r="F336" s="9" t="inlineStr">
         <is>
-          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected. The Add button says just 'Add'. Choosing Today makes it read 'Add . Today', because that is the notable case: it will appear on both your days.</t>
+          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
         </is>
       </c>
       <c r="G336" s="7" t="inlineStr">
@@ -14174,7 +14174,7 @@
     <row r="337">
       <c r="A337" s="6" t="inlineStr">
         <is>
-          <t>OUR-112</t>
+          <t>OUR-70</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -14182,24 +14182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C337" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C337" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D337" s="9" t="inlineStr">
         <is>
-          <t>A shared row's WHEN can be changed, and cleared</t>
+          <t>A dated shared row shows from its day onward, never before</t>
         </is>
       </c>
       <c r="E337" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
+          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
         </is>
       </c>
       <c r="F337" s="9" t="inlineStr">
         <is>
-          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
+          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
         </is>
       </c>
       <c r="G337" s="7" t="inlineStr">
@@ -14214,7 +14214,7 @@
     <row r="338">
       <c r="A338" s="6" t="inlineStr">
         <is>
-          <t>OUR-113</t>
+          <t>OUR-71</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -14229,17 +14229,17 @@
       </c>
       <c r="D338" s="9" t="inlineStr">
         <is>
-          <t>Ending a rhythm does NOT mark the row done for both people</t>
+          <t>The shared capture rests on Anytime</t>
         </is>
       </c>
       <c r="E338" s="9" t="inlineStr">
         <is>
-          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
+          <t>Open the Ours capture and open the door.</t>
         </is>
       </c>
       <c r="F338" s="9" t="inlineStr">
         <is>
-          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
+          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected. The Add button says just 'Add'. Choosing Today makes it read 'Add . Today', because that is the notable case: it will appear on both your days.</t>
         </is>
       </c>
       <c r="G338" s="7" t="inlineStr">
@@ -14254,7 +14254,7 @@
     <row r="339">
       <c r="A339" s="6" t="inlineStr">
         <is>
-          <t>OUR-114</t>
+          <t>OUR-112</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -14262,24 +14262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C339" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C339" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D339" s="9" t="inlineStr">
         <is>
-          <t>The day zone changes its question when a rhythm is alive</t>
+          <t>A shared row's WHEN can be changed, and cleared</t>
         </is>
       </c>
       <c r="E339" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
+          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
         </is>
       </c>
       <c r="F339" s="9" t="inlineStr">
         <is>
-          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
+          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
         </is>
       </c>
       <c r="G339" s="7" t="inlineStr">
@@ -14294,7 +14294,7 @@
     <row r="340">
       <c r="A340" s="6" t="inlineStr">
         <is>
-          <t>OUR-115</t>
+          <t>OUR-113</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -14302,24 +14302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C340" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C340" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D340" s="9" t="inlineStr">
         <is>
-          <t>Setting a shared row to Today actually reaches both Todays</t>
+          <t>Ending a rhythm does NOT mark the row done for both people</t>
         </is>
       </c>
       <c r="E340" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
+          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
         </is>
       </c>
       <c r="F340" s="9" t="inlineStr">
         <is>
-          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
+          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
         </is>
       </c>
       <c r="G340" s="7" t="inlineStr">
@@ -14334,7 +14334,7 @@
     <row r="341">
       <c r="A341" s="6" t="inlineStr">
         <is>
-          <t>OUR-116</t>
+          <t>OUR-114</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -14342,24 +14342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C341" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C341" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D341" s="9" t="inlineStr">
         <is>
-          <t>An idle Set does not wash the row on the other device</t>
+          <t>The day zone changes its question when a rhythm is alive</t>
         </is>
       </c>
       <c r="E341" s="9" t="inlineStr">
         <is>
-          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
+          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
         </is>
       </c>
       <c r="F341" s="9" t="inlineStr">
         <is>
-          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
+          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
         </is>
       </c>
       <c r="G341" s="7" t="inlineStr">
@@ -14374,7 +14374,7 @@
     <row r="342">
       <c r="A342" s="6" t="inlineStr">
         <is>
-          <t>OUR-118</t>
+          <t>OUR-115</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -14382,24 +14382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C342" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C342" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>A repeat you have already done today keeps its held card</t>
+          <t>Setting a shared row to Today actually reaches both Todays</t>
         </is>
       </c>
       <c r="E342" s="9" t="inlineStr">
         <is>
-          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
+          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
         </is>
       </c>
       <c r="F342" s="9" t="inlineStr">
         <is>
-          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
+          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
         </is>
       </c>
       <c r="G342" s="7" t="inlineStr">
@@ -14414,7 +14414,7 @@
     <row r="343">
       <c r="A343" s="6" t="inlineStr">
         <is>
-          <t>OUR-117</t>
+          <t>OUR-116</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -14422,24 +14422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C343" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C343" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D343" s="9" t="inlineStr">
         <is>
-          <t>The Repeating drawer is untouched by the When editor</t>
+          <t>An idle Set does not wash the row on the other device</t>
         </is>
       </c>
       <c r="E343" s="9" t="inlineStr">
         <is>
-          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
+          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
         </is>
       </c>
       <c r="F343" s="9" t="inlineStr">
         <is>
-          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the drawer.</t>
+          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
         </is>
       </c>
       <c r="G343" s="7" t="inlineStr">
@@ -14454,7 +14454,7 @@
     <row r="344">
       <c r="A344" s="6" t="inlineStr">
         <is>
-          <t>OUR-119</t>
+          <t>OUR-118</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -14462,24 +14462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C344" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C344" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D344" s="9" t="inlineStr">
         <is>
-          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
+          <t>A repeat you have already done today keeps its held card</t>
         </is>
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
+          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
         </is>
       </c>
       <c r="F344" s="9" t="inlineStr">
         <is>
-          <t>Monthly is the fourth rhythm chip here too, from the same sheet the personal drawer uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
+          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
         </is>
       </c>
       <c r="G344" s="7" t="inlineStr">
@@ -14494,7 +14494,7 @@
     <row r="345">
       <c r="A345" s="6" t="inlineStr">
         <is>
-          <t>OUR-111</t>
+          <t>OUR-117</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -14502,24 +14502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C345" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C345" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D345" s="9" t="inlineStr">
         <is>
-          <t>A finished dated shared row leaves both Todays the next day</t>
+          <t>The Repeating drawer is untouched by the When editor</t>
         </is>
       </c>
       <c r="E345" s="9" t="inlineStr">
         <is>
-          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
+          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
         </is>
       </c>
       <c r="F345" s="9" t="inlineStr">
         <is>
-          <t>Today: still there on BOTH, struck through, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
+          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the drawer.</t>
         </is>
       </c>
       <c r="G345" s="7" t="inlineStr">
@@ -14534,7 +14534,7 @@
     <row r="346">
       <c r="A346" s="6" t="inlineStr">
         <is>
-          <t>OUR-72</t>
+          <t>OUR-119</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -14549,17 +14549,17 @@
       </c>
       <c r="D346" s="9" t="inlineStr">
         <is>
-          <t>A repeat supersedes the day rather than joining it</t>
+          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
         </is>
       </c>
       <c r="E346" s="9" t="inlineStr">
         <is>
-          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
+          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
         </is>
       </c>
       <c r="F346" s="9" t="inlineStr">
         <is>
-          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
+          <t>Monthly is the fourth rhythm chip here too, from the same sheet the personal drawer uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
         </is>
       </c>
       <c r="G346" s="7" t="inlineStr">
@@ -14574,7 +14574,7 @@
     <row r="347">
       <c r="A347" s="6" t="inlineStr">
         <is>
-          <t>OUR-73</t>
+          <t>OUR-111</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -14582,24 +14582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C347" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C347" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D347" s="9" t="inlineStr">
         <is>
-          <t>An unreadable cadence is never placed on a day</t>
+          <t>A finished dated shared row leaves both Todays the next day</t>
         </is>
       </c>
       <c r="E347" s="9" t="inlineStr">
         <is>
-          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
+          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
         </is>
       </c>
       <c r="F347" s="9" t="inlineStr">
         <is>
-          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
+          <t>Today: still there on BOTH, struck through, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
         </is>
       </c>
       <c r="G347" s="7" t="inlineStr">
@@ -14614,7 +14614,7 @@
     <row r="348">
       <c r="A348" s="6" t="inlineStr">
         <is>
-          <t>OUR-74</t>
+          <t>OUR-72</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -14622,24 +14622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C348" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C348" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D348" s="9" t="inlineStr">
         <is>
-          <t>The door says what changed since you looked, and clears when you look</t>
+          <t>A repeat supersedes the day rather than joining it</t>
         </is>
       </c>
       <c r="E348" s="9" t="inlineStr">
         <is>
-          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap through to Ours and come back.</t>
+          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
         </is>
       </c>
       <c r="F348" s="9" t="inlineStr">
         <is>
-          <t>The Ours door reads '1 since you looked'. After visiting, it is gone. The number is bounded by your own attention, not by the list's length, so it can never sit there climbing at you.</t>
+          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
         </is>
       </c>
       <c r="G348" s="7" t="inlineStr">
@@ -14654,7 +14654,7 @@
     <row r="349">
       <c r="A349" s="6" t="inlineStr">
         <is>
-          <t>OUR-75</t>
+          <t>OUR-73</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -14662,24 +14662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C349" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C349" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D349" s="9" t="inlineStr">
         <is>
-          <t>Your OWN changes never appear in that count</t>
+          <t>An unreadable cadence is never placed on a day</t>
         </is>
       </c>
       <c r="E349" s="9" t="inlineStr">
         <is>
-          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
+          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
         </is>
       </c>
       <c r="F349" s="9" t="inlineStr">
         <is>
-          <t>No count on the door. It uses the room's own wash arithmetic, so the door and the room always agree about whose change it was.</t>
+          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
         </is>
       </c>
       <c r="G349" s="7" t="inlineStr">
@@ -14694,7 +14694,7 @@
     <row r="350">
       <c r="A350" s="6" t="inlineStr">
         <is>
-          <t>OUR-76</t>
+          <t>OUR-74</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -14702,24 +14702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C350" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C350" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D350" s="9" t="inlineStr">
         <is>
-          <t>A first-ever visit counts nothing</t>
+          <t>The door says what changed since you looked, and clears when you look</t>
         </is>
       </c>
       <c r="E350" s="9" t="inlineStr">
         <is>
-          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
+          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap through to Ours and come back.</t>
         </is>
       </c>
       <c r="F350" s="9" t="inlineStr">
         <is>
-          <t>No count. There is no 'last looked' to measure against, and inventing one would open the app with a number already on it.</t>
+          <t>The Ours door reads '1 since you looked'. After visiting, it is gone. The number is bounded by your own attention, not by the list's length, so it can never sit there climbing at you.</t>
         </is>
       </c>
       <c r="G350" s="7" t="inlineStr">
@@ -14734,7 +14734,7 @@
     <row r="351">
       <c r="A351" s="6" t="inlineStr">
         <is>
-          <t>OUR-77</t>
+          <t>OUR-75</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -14742,24 +14742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C351" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C351" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D351" s="9" t="inlineStr">
         <is>
-          <t>The capture's AI note names only what that surface HAS</t>
+          <t>Your OWN changes never appear in that count</t>
         </is>
       </c>
       <c r="E351" s="9" t="inlineStr">
         <is>
-          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
+          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
         </is>
       </c>
       <c r="F351" s="9" t="inlineStr">
         <is>
-          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
+          <t>No count on the door. It uses the room's own wash arithmetic, so the door and the room always agree about whose change it was.</t>
         </is>
       </c>
       <c r="G351" s="7" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="352">
       <c r="A352" s="6" t="inlineStr">
         <is>
-          <t>OUR-78</t>
+          <t>OUR-76</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -14782,24 +14782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C352" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C352" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D352" s="9" t="inlineStr">
         <is>
-          <t>Scan discloses on every path that can reach a camera</t>
+          <t>A first-ever visit counts nothing</t>
         </is>
       </c>
       <c r="E352" s="9" t="inlineStr">
         <is>
-          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
+          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
         </is>
       </c>
       <c r="F352" s="9" t="inlineStr">
         <is>
-          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
+          <t>No count. There is no 'last looked' to measure against, and inventing one would open the app with a number already on it.</t>
         </is>
       </c>
       <c r="G352" s="7" t="inlineStr">
@@ -14814,7 +14814,7 @@
     <row r="353">
       <c r="A353" s="6" t="inlineStr">
         <is>
-          <t>OUR-79</t>
+          <t>OUR-77</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -14829,17 +14829,17 @@
       </c>
       <c r="D353" s="9" t="inlineStr">
         <is>
-          <t>Press and hold a From Ours row on Today</t>
+          <t>The capture's AI note names only what that surface HAS</t>
         </is>
       </c>
       <c r="E353" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Ours strip.</t>
+          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
         </is>
       </c>
       <c r="F353" s="9" t="inlineStr">
         <is>
-          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
+          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
         </is>
       </c>
       <c r="G353" s="7" t="inlineStr">
@@ -14854,7 +14854,7 @@
     <row r="354">
       <c r="A354" s="6" t="inlineStr">
         <is>
-          <t>OUR-80</t>
+          <t>OUR-78</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -14869,17 +14869,17 @@
       </c>
       <c r="D354" s="9" t="inlineStr">
         <is>
-          <t>Pin and Move-to never rearrange the other person's day</t>
+          <t>Scan discloses on every path that can reach a camera</t>
         </is>
       </c>
       <c r="E354" s="9" t="inlineStr">
         <is>
-          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
+          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
         </is>
       </c>
       <c r="F354" s="9" t="inlineStr">
         <is>
-          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
+          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
         </is>
       </c>
       <c r="G354" s="7" t="inlineStr">
@@ -14894,7 +14894,7 @@
     <row r="355">
       <c r="A355" s="6" t="inlineStr">
         <is>
-          <t>OUR-81</t>
+          <t>OUR-79</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -14902,24 +14902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C355" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C355" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D355" s="9" t="inlineStr">
         <is>
-          <t>A taken-on row is never on screen twice</t>
+          <t>Press and hold a From Ours row on Today</t>
         </is>
       </c>
       <c r="E355" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
+          <t>Hold a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F355" s="9" t="inlineStr">
         <is>
-          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
+          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
         </is>
       </c>
       <c r="G355" s="7" t="inlineStr">
@@ -14934,7 +14934,7 @@
     <row r="356">
       <c r="A356" s="6" t="inlineStr">
         <is>
-          <t>OUR-82</t>
+          <t>OUR-80</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -14942,24 +14942,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C356" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C356" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D356" s="9" t="inlineStr">
         <is>
-          <t>Move-to is not offered on a repeating shared row</t>
+          <t>Pin and Move-to never rearrange the other person's day</t>
         </is>
       </c>
       <c r="E356" s="9" t="inlineStr">
         <is>
-          <t>Hold a repeating row in the From Ours strip.</t>
+          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
         </is>
       </c>
       <c r="F356" s="9" t="inlineStr">
         <is>
-          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
+          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
         </is>
       </c>
       <c r="G356" s="7" t="inlineStr">
@@ -14974,7 +14974,7 @@
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
         <is>
-          <t>OUR-83</t>
+          <t>OUR-81</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -14982,24 +14982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C357" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C357" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D357" s="9" t="inlineStr">
         <is>
-          <t>One shared row, one route onto your day</t>
+          <t>A taken-on row is never on screen twice</t>
         </is>
       </c>
       <c r="E357" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
+          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
         </is>
       </c>
       <c r="F357" s="9" t="inlineStr">
         <is>
-          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
+          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
         </is>
       </c>
       <c r="G357" s="7" t="inlineStr">
@@ -15014,7 +15014,7 @@
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
         <is>
-          <t>OUR-84</t>
+          <t>OUR-82</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -15022,24 +15022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C358" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C358" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D358" s="9" t="inlineStr">
         <is>
-          <t>Take a From Ours row on, and it becomes an ordinary task</t>
+          <t>Move-to is not offered on a repeating shared row</t>
         </is>
       </c>
       <c r="E358" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
+          <t>Hold a repeating row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F358" s="9" t="inlineStr">
         <is>
-          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
+          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
         </is>
       </c>
       <c r="G358" s="7" t="inlineStr">
@@ -15054,7 +15054,7 @@
     <row r="359">
       <c r="A359" s="6" t="inlineStr">
         <is>
-          <t>OUR-85</t>
+          <t>OUR-83</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -15062,24 +15062,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C359" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C359" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D359" s="9" t="inlineStr">
         <is>
-          <t>Break it down works once taken on, and never touches the shared list</t>
+          <t>One shared row, one route onto your day</t>
         </is>
       </c>
       <c r="E359" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on, then Break it down.</t>
+          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
         </is>
       </c>
       <c r="F359" s="9" t="inlineStr">
         <is>
-          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
+          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
         </is>
       </c>
       <c r="G359" s="7" t="inlineStr">
@@ -15094,7 +15094,7 @@
     <row r="360">
       <c r="A360" s="6" t="inlineStr">
         <is>
-          <t>OUR-86</t>
+          <t>OUR-84</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -15109,17 +15109,17 @@
       </c>
       <c r="D360" s="9" t="inlineStr">
         <is>
-          <t>Select several rows in the room and tick them together</t>
+          <t>Take a From Ours row on, and it becomes an ordinary task</t>
         </is>
       </c>
       <c r="E360" s="9" t="inlineStr">
         <is>
-          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
+          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
         </is>
       </c>
       <c r="F360" s="9" t="inlineStr">
         <is>
-          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
+          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
         </is>
       </c>
       <c r="G360" s="7" t="inlineStr">
@@ -15134,7 +15134,7 @@
     <row r="361">
       <c r="A361" s="6" t="inlineStr">
         <is>
-          <t>OUR-87</t>
+          <t>OUR-85</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -15142,24 +15142,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C361" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C361" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D361" s="9" t="inlineStr">
         <is>
-          <t>Bulk tick never UN-ticks</t>
+          <t>Break it down works once taken on, and never touches the shared list</t>
         </is>
       </c>
       <c r="E361" s="9" t="inlineStr">
         <is>
-          <t>Select a mix of done and not-done rows and tap Done.</t>
+          <t>Take a shared row on, then Break it down.</t>
         </is>
       </c>
       <c r="F361" s="9" t="inlineStr">
         <is>
-          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
+          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
         </is>
       </c>
       <c r="G361" s="7" t="inlineStr">
@@ -15174,7 +15174,7 @@
     <row r="362">
       <c r="A362" s="6" t="inlineStr">
         <is>
-          <t>OUR-88</t>
+          <t>OUR-86</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -15189,17 +15189,17 @@
       </c>
       <c r="D362" s="9" t="inlineStr">
         <is>
-          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
+          <t>Select several rows in the room and tick them together</t>
         </is>
       </c>
       <c r="E362" s="9" t="inlineStr">
         <is>
-          <t>Select a repeating row along with others. Read the shelf.</t>
+          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
         </is>
       </c>
       <c r="F362" s="9" t="inlineStr">
         <is>
-          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
+          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
         </is>
       </c>
       <c r="G362" s="7" t="inlineStr">
@@ -15214,7 +15214,7 @@
     <row r="363">
       <c r="A363" s="6" t="inlineStr">
         <is>
-          <t>OUR-89</t>
+          <t>OUR-87</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -15222,24 +15222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C363" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C363" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D363" s="9" t="inlineStr">
         <is>
-          <t>The select shelf takes the capture bar's seat</t>
+          <t>Bulk tick never UN-ticks</t>
         </is>
       </c>
       <c r="E363" s="9" t="inlineStr">
         <is>
-          <t>Enter select mode in the room.</t>
+          <t>Select a mix of done and not-done rows and tap Done.</t>
         </is>
       </c>
       <c r="F363" s="9" t="inlineStr">
         <is>
-          <t>The capture bar is gone while selecting, and back when you cancel. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
+          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
         </is>
       </c>
       <c r="G363" s="7" t="inlineStr">
@@ -15254,7 +15254,7 @@
     <row r="364">
       <c r="A364" s="6" t="inlineStr">
         <is>
-          <t>OUR-90</t>
+          <t>OUR-88</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -15262,24 +15262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C364" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C364" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D364" s="9" t="inlineStr">
         <is>
-          <t>No select mode on a closed list</t>
+          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
         </is>
       </c>
       <c r="E364" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list and hold a row.</t>
+          <t>Select a repeating row along with others. Read the shelf.</t>
         </is>
       </c>
       <c r="F364" s="9" t="inlineStr">
         <is>
-          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
+          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
         </is>
       </c>
       <c r="G364" s="7" t="inlineStr">
@@ -15294,7 +15294,7 @@
     <row r="365">
       <c r="A365" s="6" t="inlineStr">
         <is>
-          <t>OUR-91</t>
+          <t>OUR-89</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -15302,24 +15302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C365" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C365" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D365" s="9" t="inlineStr">
         <is>
-          <t>A copy says when its shared row was taken off the list</t>
+          <t>The select shelf takes the capture bar's seat</t>
         </is>
       </c>
       <c r="E365" s="9" t="inlineStr">
         <is>
-          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
+          <t>Enter select mode in the room.</t>
         </is>
       </c>
       <c r="F365" s="9" t="inlineStr">
         <is>
-          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
+          <t>The capture bar is gone while selecting, and back when you cancel. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
         </is>
       </c>
       <c r="G365" s="7" t="inlineStr">
@@ -15334,7 +15334,7 @@
     <row r="366">
       <c r="A366" s="6" t="inlineStr">
         <is>
-          <t>OUR-92</t>
+          <t>OUR-90</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -15342,24 +15342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C366" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C366" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D366" s="9" t="inlineStr">
         <is>
-          <t>That line never says who, and never says why</t>
+          <t>No select mode on a closed list</t>
         </is>
       </c>
       <c r="E366" s="9" t="inlineStr">
         <is>
-          <t>Read the line closely.</t>
+          <t>Open an archived list and hold a row.</t>
         </is>
       </c>
       <c r="F366" s="9" t="inlineStr">
         <is>
-          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
+          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
         </is>
       </c>
       <c r="G366" s="7" t="inlineStr">
@@ -15374,7 +15374,7 @@
     <row r="367">
       <c r="A367" s="6" t="inlineStr">
         <is>
-          <t>OUR-93</t>
+          <t>OUR-91</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -15382,24 +15382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C367" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C367" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D367" s="9" t="inlineStr">
         <is>
-          <t>No line on a copy you already finished or removed</t>
+          <t>A copy says when its shared row was taken off the list</t>
         </is>
       </c>
       <c r="E367" s="9" t="inlineStr">
         <is>
-          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
+          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
         </is>
       </c>
       <c r="F367" s="9" t="inlineStr">
         <is>
-          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
+          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
         </is>
       </c>
       <c r="G367" s="7" t="inlineStr">
@@ -15414,7 +15414,7 @@
     <row r="368">
       <c r="A368" s="6" t="inlineStr">
         <is>
-          <t>OUR-94</t>
+          <t>OUR-92</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -15422,24 +15422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C368" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C368" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D368" s="9" t="inlineStr">
         <is>
-          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
+          <t>That line never says who, and never says why</t>
         </is>
       </c>
       <c r="E368" s="9" t="inlineStr">
         <is>
-          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
+          <t>Read the line closely.</t>
         </is>
       </c>
       <c r="F368" s="9" t="inlineStr">
         <is>
-          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
+          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
         </is>
       </c>
       <c r="G368" s="7" t="inlineStr">
@@ -15454,7 +15454,7 @@
     <row r="369">
       <c r="A369" s="6" t="inlineStr">
         <is>
-          <t>OUR-95</t>
+          <t>OUR-93</t>
         </is>
       </c>
       <c r="B369" s="7" t="inlineStr">
@@ -15462,24 +15462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C369" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C369" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D369" s="9" t="inlineStr">
         <is>
-          <t>A row's note is VISIBLE, not only spoken</t>
+          <t>No line on a copy you already finished or removed</t>
         </is>
       </c>
       <c r="E369" s="9" t="inlineStr">
         <is>
-          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
+          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
         </is>
       </c>
       <c r="F369" s="9" t="inlineStr">
         <is>
-          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
+          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
         </is>
       </c>
       <c r="G369" s="7" t="inlineStr">
@@ -15494,7 +15494,7 @@
     <row r="370">
       <c r="A370" s="6" t="inlineStr">
         <is>
-          <t>OUR-96</t>
+          <t>OUR-94</t>
         </is>
       </c>
       <c r="B370" s="7" t="inlineStr">
@@ -15502,24 +15502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C370" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C370" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D370" s="9" t="inlineStr">
         <is>
-          <t>Rows WITHOUT a note are unchanged</t>
+          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
         </is>
       </c>
       <c r="E370" s="9" t="inlineStr">
         <is>
-          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
+          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
         </is>
       </c>
       <c r="F370" s="9" t="inlineStr">
         <is>
-          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
+          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
         </is>
       </c>
       <c r="G370" s="7" t="inlineStr">
@@ -15534,7 +15534,7 @@
     <row r="371">
       <c r="A371" s="6" t="inlineStr">
         <is>
-          <t>OUR-97</t>
+          <t>OUR-95</t>
         </is>
       </c>
       <c r="B371" s="7" t="inlineStr">
@@ -15549,17 +15549,17 @@
       </c>
       <c r="D371" s="9" t="inlineStr">
         <is>
-          <t>A tick after midnight lands on the RIGHT day</t>
+          <t>A row's note is VISIBLE, not only spoken</t>
         </is>
       </c>
       <c r="E371" s="9" t="inlineStr">
         <is>
-          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
+          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
         </is>
       </c>
       <c r="F371" s="9" t="inlineStr">
         <is>
-          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
+          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
         </is>
       </c>
       <c r="G371" s="7" t="inlineStr">
@@ -15574,7 +15574,7 @@
     <row r="372">
       <c r="A372" s="6" t="inlineStr">
         <is>
-          <t>OUR-98</t>
+          <t>OUR-96</t>
         </is>
       </c>
       <c r="B372" s="7" t="inlineStr">
@@ -15582,24 +15582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C372" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C372" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D372" s="9" t="inlineStr">
         <is>
-          <t>A tick made during a background sync is not undone</t>
+          <t>Rows WITHOUT a note are unchanged</t>
         </is>
       </c>
       <c r="E372" s="9" t="inlineStr">
         <is>
-          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
+          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
         </is>
       </c>
       <c r="F372" s="9" t="inlineStr">
         <is>
-          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
+          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
         </is>
       </c>
       <c r="G372" s="7" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="373">
       <c r="A373" s="6" t="inlineStr">
         <is>
-          <t>OUR-99</t>
+          <t>OUR-97</t>
         </is>
       </c>
       <c r="B373" s="7" t="inlineStr">
@@ -15629,17 +15629,17 @@
       </c>
       <c r="D373" s="9" t="inlineStr">
         <is>
-          <t>A tick survives a device that has never opened the room</t>
+          <t>A tick after midnight lands on the RIGHT day</t>
         </is>
       </c>
       <c r="E373" s="9" t="inlineStr">
         <is>
-          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
+          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
         </is>
       </c>
       <c r="F373" s="9" t="inlineStr">
         <is>
-          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
+          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
         </is>
       </c>
       <c r="G373" s="7" t="inlineStr">
@@ -15654,7 +15654,7 @@
     <row r="374">
       <c r="A374" s="6" t="inlineStr">
         <is>
-          <t>OUR-100</t>
+          <t>OUR-98</t>
         </is>
       </c>
       <c r="B374" s="7" t="inlineStr">
@@ -15669,17 +15669,17 @@
       </c>
       <c r="D374" s="9" t="inlineStr">
         <is>
-          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
+          <t>A tick made during a background sync is not undone</t>
         </is>
       </c>
       <c r="E374" s="9" t="inlineStr">
         <is>
-          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
+          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F374" s="9" t="inlineStr">
         <is>
-          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
+          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
         </is>
       </c>
       <c r="G374" s="7" t="inlineStr">
@@ -15694,7 +15694,7 @@
     <row r="375">
       <c r="A375" s="6" t="inlineStr">
         <is>
-          <t>OUR-101</t>
+          <t>OUR-99</t>
         </is>
       </c>
       <c r="B375" s="7" t="inlineStr">
@@ -15702,24 +15702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C375" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C375" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D375" s="9" t="inlineStr">
         <is>
-          <t>A closed list stops promising it keeps trying</t>
+          <t>A tick survives a device that has never opened the room</t>
         </is>
       </c>
       <c r="E375" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list that has unpushed local changes.</t>
+          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
         </is>
       </c>
       <c r="F375" s="9" t="inlineStr">
         <is>
-          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
+          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
         </is>
       </c>
       <c r="G375" s="7" t="inlineStr">
@@ -15734,7 +15734,7 @@
     <row r="376">
       <c r="A376" s="6" t="inlineStr">
         <is>
-          <t>OUR-102</t>
+          <t>OUR-100</t>
         </is>
       </c>
       <c r="B376" s="7" t="inlineStr">
@@ -15742,24 +15742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C376" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C376" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D376" s="9" t="inlineStr">
         <is>
-          <t>Setting a rhythm clears any date the row was carrying</t>
+          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
         </is>
       </c>
       <c r="E376" s="9" t="inlineStr">
         <is>
-          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
+          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
         </is>
       </c>
       <c r="F376" s="9" t="inlineStr">
         <is>
-          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
+          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
         </is>
       </c>
       <c r="G376" s="7" t="inlineStr">
@@ -15774,7 +15774,7 @@
     <row r="377">
       <c r="A377" s="6" t="inlineStr">
         <is>
-          <t>OUR-103</t>
+          <t>OUR-101</t>
         </is>
       </c>
       <c r="B377" s="7" t="inlineStr">
@@ -15789,17 +15789,17 @@
       </c>
       <c r="D377" s="9" t="inlineStr">
         <is>
-          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
+          <t>A closed list stops promising it keeps trying</t>
         </is>
       </c>
       <c r="E377" s="9" t="inlineStr">
         <is>
-          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
+          <t>Open an archived list that has unpushed local changes.</t>
         </is>
       </c>
       <c r="F377" s="9" t="inlineStr">
         <is>
-          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
+          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
         </is>
       </c>
       <c r="G377" s="7" t="inlineStr">
@@ -15814,7 +15814,7 @@
     <row r="378">
       <c r="A378" s="6" t="inlineStr">
         <is>
-          <t>OUR-104</t>
+          <t>OUR-102</t>
         </is>
       </c>
       <c r="B378" s="7" t="inlineStr">
@@ -15822,24 +15822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C378" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C378" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D378" s="9" t="inlineStr">
         <is>
-          <t>No dead reorder rail on shared rows</t>
+          <t>Setting a rhythm clears any date the row was carrying</t>
         </is>
       </c>
       <c r="E378" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the room and in the From Ours strip.</t>
+          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
         </is>
       </c>
       <c r="F378" s="9" t="inlineStr">
         <is>
-          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
+          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
         </is>
       </c>
       <c r="G378" s="7" t="inlineStr">
@@ -15854,7 +15854,7 @@
     <row r="379">
       <c r="A379" s="6" t="inlineStr">
         <is>
-          <t>OUR-105</t>
+          <t>OUR-103</t>
         </is>
       </c>
       <c r="B379" s="7" t="inlineStr">
@@ -15862,24 +15862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C379" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C379" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D379" s="9" t="inlineStr">
         <is>
-          <t>First run introduces the shared list</t>
+          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
         </is>
       </c>
       <c r="E379" s="9" t="inlineStr">
         <is>
-          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
+          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
         </is>
       </c>
       <c r="F379" s="9" t="inlineStr">
         <is>
-          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
+          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
         </is>
       </c>
       <c r="G379" s="7" t="inlineStr">
@@ -15894,7 +15894,7 @@
     <row r="380">
       <c r="A380" s="6" t="inlineStr">
         <is>
-          <t>OUR-106</t>
+          <t>OUR-104</t>
         </is>
       </c>
       <c r="B380" s="7" t="inlineStr">
@@ -15902,24 +15902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C380" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C380" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D380" s="9" t="inlineStr">
         <is>
-          <t>Anyone can start a shared list, not just an allowlisted address</t>
+          <t>No dead reorder rail on shared rows</t>
         </is>
       </c>
       <c r="E380" s="9" t="inlineStr">
         <is>
-          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
+          <t>Hold a row in the room and in the From Ours strip.</t>
         </is>
       </c>
       <c r="F380" s="9" t="inlineStr">
         <is>
-          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
+          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
         </is>
       </c>
       <c r="G380" s="7" t="inlineStr">
@@ -15934,7 +15934,7 @@
     <row r="381">
       <c r="A381" s="6" t="inlineStr">
         <is>
-          <t>OUR-107</t>
+          <t>OUR-105</t>
         </is>
       </c>
       <c r="B381" s="7" t="inlineStr">
@@ -15949,17 +15949,17 @@
       </c>
       <c r="D381" s="9" t="inlineStr">
         <is>
-          <t>The shared-list onboarding step can actually be REACHED</t>
+          <t>First run introduces the shared list</t>
         </is>
       </c>
       <c r="E381" s="9" t="inlineStr">
         <is>
-          <t>Replay the first run and press the primary button through every step without skipping.</t>
+          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
         </is>
       </c>
       <c r="F381" s="9" t="inlineStr">
         <is>
-          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
+          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
         </is>
       </c>
       <c r="G381" s="7" t="inlineStr">
@@ -15974,7 +15974,7 @@
     <row r="382">
       <c r="A382" s="6" t="inlineStr">
         <is>
-          <t>OUR-108</t>
+          <t>OUR-106</t>
         </is>
       </c>
       <c r="B382" s="7" t="inlineStr">
@@ -15982,24 +15982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C382" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C382" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D382" s="9" t="inlineStr">
         <is>
-          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
+          <t>Anyone can start a shared list, not just an allowlisted address</t>
         </is>
       </c>
       <c r="E382" s="9" t="inlineStr">
         <is>
-          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
+          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
         </is>
       </c>
       <c r="F382" s="9" t="inlineStr">
         <is>
-          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
+          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
         </is>
       </c>
       <c r="G382" s="7" t="inlineStr">
@@ -16014,7 +16014,7 @@
     <row r="383">
       <c r="A383" s="6" t="inlineStr">
         <is>
-          <t>OUR-109</t>
+          <t>OUR-107</t>
         </is>
       </c>
       <c r="B383" s="7" t="inlineStr">
@@ -16029,17 +16029,17 @@
       </c>
       <c r="D383" s="9" t="inlineStr">
         <is>
-          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
+          <t>The shared-list onboarding step can actually be REACHED</t>
         </is>
       </c>
       <c r="E383" s="9" t="inlineStr">
         <is>
-          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
+          <t>Replay the first run and press the primary button through every step without skipping.</t>
         </is>
       </c>
       <c r="F383" s="9" t="inlineStr">
         <is>
-          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
+          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
         </is>
       </c>
       <c r="G383" s="7" t="inlineStr">
@@ -16054,7 +16054,7 @@
     <row r="384">
       <c r="A384" s="6" t="inlineStr">
         <is>
-          <t>OUR-110</t>
+          <t>OUR-108</t>
         </is>
       </c>
       <c r="B384" s="7" t="inlineStr">
@@ -16062,24 +16062,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C384" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C384" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D384" s="9" t="inlineStr">
         <is>
-          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
+          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
         </is>
       </c>
       <c r="E384" s="9" t="inlineStr">
         <is>
-          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
+          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
         </is>
       </c>
       <c r="F384" s="9" t="inlineStr">
         <is>
-          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
+          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
         </is>
       </c>
       <c r="G384" s="7" t="inlineStr">
@@ -16094,12 +16094,12 @@
     <row r="385">
       <c r="A385" s="6" t="inlineStr">
         <is>
-          <t>UPD-01</t>
+          <t>OUR-109</t>
         </is>
       </c>
       <c r="B385" s="7" t="inlineStr">
         <is>
-          <t>Updates</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C385" s="8" t="inlineStr">
@@ -16109,17 +16109,17 @@
       </c>
       <c r="D385" s="9" t="inlineStr">
         <is>
-          <t>Settings states the version, and up-to-date is a fact</t>
+          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
         </is>
       </c>
       <c r="E385" s="9" t="inlineStr">
         <is>
-          <t>Open Settings and scroll to the foot.</t>
+          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
         </is>
       </c>
       <c r="F385" s="9" t="inlineStr">
         <is>
-          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
+          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
         </is>
       </c>
       <c r="G385" s="7" t="inlineStr">
@@ -16134,12 +16134,12 @@
     <row r="386">
       <c r="A386" s="6" t="inlineStr">
         <is>
-          <t>UPD-02</t>
+          <t>OUR-110</t>
         </is>
       </c>
       <c r="B386" s="7" t="inlineStr">
         <is>
-          <t>Updates</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C386" s="8" t="inlineStr">
@@ -16149,22 +16149,22 @@
       </c>
       <c r="D386" s="9" t="inlineStr">
         <is>
-          <t>Web offers a reload, and says drafts are kept</t>
+          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
         </is>
       </c>
       <c r="E386" s="9" t="inlineStr">
         <is>
-          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
+          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
         </is>
       </c>
       <c r="F386" s="9" t="inlineStr">
         <is>
-          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
+          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
         </is>
       </c>
       <c r="G386" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H386" s="7" t="inlineStr"/>
@@ -16174,7 +16174,7 @@
     <row r="387">
       <c r="A387" s="6" t="inlineStr">
         <is>
-          <t>UPD-03</t>
+          <t>UPD-01</t>
         </is>
       </c>
       <c r="B387" s="7" t="inlineStr">
@@ -16189,22 +16189,22 @@
       </c>
       <c r="D387" s="9" t="inlineStr">
         <is>
-          <t>Native points at the store, and says lists are untouched</t>
+          <t>Settings states the version, and up-to-date is a fact</t>
         </is>
       </c>
       <c r="E387" s="9" t="inlineStr">
         <is>
-          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
+          <t>Open Settings and scroll to the foot.</t>
         </is>
       </c>
       <c r="F387" s="9" t="inlineStr">
         <is>
-          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
+          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
         </is>
       </c>
       <c r="G387" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H387" s="7" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
     <row r="388">
       <c r="A388" s="6" t="inlineStr">
         <is>
-          <t>UPD-04</t>
+          <t>UPD-02</t>
         </is>
       </c>
       <c r="B388" s="7" t="inlineStr">
@@ -16222,29 +16222,29 @@
           <t>Updates</t>
         </is>
       </c>
-      <c r="C388" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C388" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D388" s="9" t="inlineStr">
         <is>
-          <t>Unreachable server says NOTHING, never 'up to date'</t>
+          <t>Web offers a reload, and says drafts are kept</t>
         </is>
       </c>
       <c r="E388" s="9" t="inlineStr">
         <is>
-          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
+          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
         </is>
       </c>
       <c r="F388" s="9" t="inlineStr">
         <is>
-          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
+          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
         </is>
       </c>
       <c r="G388" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H388" s="7" t="inlineStr"/>
@@ -16254,7 +16254,7 @@
     <row r="389">
       <c r="A389" s="6" t="inlineStr">
         <is>
-          <t>UPD-05</t>
+          <t>UPD-03</t>
         </is>
       </c>
       <c r="B389" s="7" t="inlineStr">
@@ -16262,29 +16262,29 @@
           <t>Updates</t>
         </is>
       </c>
-      <c r="C389" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C389" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D389" s="9" t="inlineStr">
         <is>
-          <t>The goodnight mention is rare, and framed for the other person</t>
+          <t>Native points at the store, and says lists are untouched</t>
         </is>
       </c>
       <c r="E389" s="9" t="inlineStr">
         <is>
-          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
+          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
         </is>
       </c>
       <c r="F389" s="9" t="inlineStr">
         <is>
-          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
+          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
         </is>
       </c>
       <c r="G389" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H389" s="7" t="inlineStr"/>
@@ -16294,32 +16294,32 @@
     <row r="390">
       <c r="A390" s="6" t="inlineStr">
         <is>
-          <t>OUR-12</t>
+          <t>UPD-04</t>
         </is>
       </c>
       <c r="B390" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C390" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="C390" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D390" s="9" t="inlineStr">
         <is>
-          <t>Unnamed lists read in each person's language</t>
+          <t>Unreachable server says NOTHING, never 'up to date'</t>
         </is>
       </c>
       <c r="E390" s="9" t="inlineStr">
         <is>
-          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
         </is>
       </c>
       <c r="F390" s="9" t="inlineStr">
         <is>
-          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
         </is>
       </c>
       <c r="G390" s="7" t="inlineStr">
@@ -16331,9 +16331,89 @@
       <c r="I390" s="9" t="inlineStr"/>
       <c r="J390" s="7" t="inlineStr"/>
     </row>
+    <row r="391">
+      <c r="A391" s="6" t="inlineStr">
+        <is>
+          <t>UPD-05</t>
+        </is>
+      </c>
+      <c r="B391" s="7" t="inlineStr">
+        <is>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="C391" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D391" s="9" t="inlineStr">
+        <is>
+          <t>The goodnight mention is rare, and framed for the other person</t>
+        </is>
+      </c>
+      <c r="E391" s="9" t="inlineStr">
+        <is>
+          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
+        </is>
+      </c>
+      <c r="F391" s="9" t="inlineStr">
+        <is>
+          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
+        </is>
+      </c>
+      <c r="G391" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H391" s="7" t="inlineStr"/>
+      <c r="I391" s="9" t="inlineStr"/>
+      <c r="J391" s="7" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="6" t="inlineStr">
+        <is>
+          <t>OUR-12</t>
+        </is>
+      </c>
+      <c r="B392" s="7" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="C392" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D392" s="9" t="inlineStr">
+        <is>
+          <t>Unnamed lists read in each person's language</t>
+        </is>
+      </c>
+      <c r="E392" s="9" t="inlineStr">
+        <is>
+          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+        </is>
+      </c>
+      <c r="F392" s="9" t="inlineStr">
+        <is>
+          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+        </is>
+      </c>
+      <c r="G392" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H392" s="7" t="inlineStr"/>
+      <c r="I392" s="9" t="inlineStr"/>
+      <c r="J392" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J390"/>
-  <conditionalFormatting sqref="H2:H390">
+  <autoFilter ref="A1:J392"/>
+  <conditionalFormatting sqref="H2:H392">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -16345,7 +16425,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H390" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
+    <dataValidation sqref="H2:H392" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
       <formula1>"Pass,Fail,Blocked,Not run"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16381,7 +16461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>391</t>
         </is>
       </c>
     </row>
@@ -16392,7 +16472,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF('Test Suite'!$H$2:$H$390,"Pass")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$392,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -16403,7 +16483,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF('Test Suite'!$H$2:$H$390,"Fail")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$392,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -16414,7 +16494,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Suite'!$H$2:$H$390,"Blocked")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$392,"Blocked")</f>
         <v/>
       </c>
     </row>
@@ -16425,7 +16505,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Suite'!$H$2:$H$390,"Not run")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$392,"Not run")</f>
         <v/>
       </c>
     </row>
@@ -16436,7 +16516,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>389-COUNTA('Test Suite'!$H$2:$H$390)</f>
+        <f>391-COUNTA('Test Suite'!$H$2:$H$392)</f>
         <v/>
       </c>
     </row>
@@ -16447,7 +16527,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF('Test Suite'!$C$2:$C$390,"P1")</f>
+        <f>COUNTIF('Test Suite'!$C$2:$C$392,"P1")</f>
         <v/>
       </c>
     </row>
@@ -16458,7 +16538,7 @@
         </is>
       </c>
       <c r="B10">
-        <f>COUNTIFS('Test Suite'!$C$2:$C$390,"P1",'Test Suite'!$H$2:$H$390,"Pass")</f>
+        <f>COUNTIFS('Test Suite'!$C$2:$C$392,"P1",'Test Suite'!$H$2:$H$392,"Pass")</f>
         <v/>
       </c>
     </row>

--- a/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
+++ b/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
@@ -11909,17 +11909,17 @@
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Waiting-with-no-code says so, and the re-mint is a real button</t>
+          <t>Waiting-with-no-code is reachable, says so, and the re-mint is a real button</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>Mint a code, leave Ours entirely (back to Today), then come back to Ours before anyone joins.</t>
+          <t>Mint a code, leave Ours entirely (back to Today), then come back via the MENU's Ours row before anyone joins.</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>The screen is titled 'Waiting for your person', NOT 'Read this to your person' over an empty space (the code renders exactly once; the server keeps only a hash, so it can never be re-shown). 'Get a new code' is a full primary button in this state, not a quiet text link (the 2026-09-13 field report walked right past the link: 'no easy way to... regenerate the code'). While the code IS still on screen, the title and the quiet link stay as they were.</t>
+          <t>The Menu lands on the shared LIST (usable solo while waiting), and the list's header line reads 'Waiting for your person - Get a new code' where 'Kept with {name}' will later sit; tapping it opens the pairing screen (both Melroy's C6 check and the field report hit this as a dead end before 2026-09-20). That screen is titled 'Waiting for your person', NOT 'Read this to your person' over an empty space (the code renders exactly once; the server keeps only a hash, so it can never be re-shown), and 'Get a new code' is a full primary button there, not a quiet text link. While the code IS still on screen, the old title and quiet link stay as they were.</t>
         </is>
       </c>
       <c r="G280" s="7" t="inlineStr">

--- a/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
+++ b/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
@@ -13034,12 +13034,12 @@
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Reopen together…'. Read the code to the second account and enter it in the ordinary join field.</t>
+          <t>On a closed list, tap 'Reopen together…' on ONE side only. Read the code to the second account. On that side, tap 'Got a code from them? Enter it to reopen.' (under the reopen hint on the closed-list screen) and enter it. Repeat with the closed list being the ONLY closed list on both accounts.</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>The offering side gets a code and nothing reopens yet. Entering it in the SAME field used for a new list reopens the list for both, with everything as it was. It is never asked which kind of code it is.</t>
+          <t>The offering side gets a code and nothing reopens yet. The other side has a named door to the join field and entering the code there reopens the list for both, with everything as it was. It is never asked which kind of code it is, and it works when the closed list on screen is the only one (the D2 'handshake purgatory', 2026-09-22).</t>
         </is>
       </c>
       <c r="G308" s="7" t="inlineStr">

--- a/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
+++ b/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$398</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$399</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J398"/>
+  <dimension ref="A1:J399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -13034,12 +13034,12 @@
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Reopen together…' on ONE side only. Read the code to the second account. On that side, tap 'Got a code from them? Enter it to reopen.' (under the reopen hint on the closed-list screen) and enter it. Repeat with the closed list being the ONLY closed list on both accounts.</t>
+          <t>On a closed list, tap 'Reopen together…' on ONE side only and STAY on that screen, hands off. Read the code to the second account. On that side, tap 'Got a code from them? Enter it to reopen.' (under the reopen hint on the closed-list screen) and enter it. Repeat with the closed list being the ONLY closed list on both accounts.</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>The offering side gets a code and nothing reopens yet. The other side has a named door to the join field and entering the code there reopens the list for both, with everything as it was. It is never asked which kind of code it is, and it works when the closed list on screen is the only one (the D2 'handshake purgatory', 2026-09-22).</t>
+          <t>The offering side gets a code and nothing reopens yet. The other side has a named door to the join field and entering the code there reopens the list for both, with everything as it was. It is never asked which kind of code it is, and it works when the closed list on screen is the only one (the D2 'handshake purgatory', 2026-09-22). Within about ten seconds, with nothing touched, the offering side's screen changes on its own: the code is gone and the live list shows 'They used the code. The list is open again…'.</t>
         </is>
       </c>
       <c r="G308" s="7" t="inlineStr">
@@ -13054,7 +13054,7 @@
     <row r="309">
       <c r="A309" s="6" t="inlineStr">
         <is>
-          <t>OUR-36</t>
+          <t>OUR-122</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
@@ -13062,24 +13062,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C309" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C309" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>Delete for good commits when the screen closes, not on a timer</t>
+          <t>Waiting screens look on their own, and 'Check now' is there for the impatient</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
+          <t>A: mint a pairing code and stay on that screen, hands off. B: join. Watch A. Then, on a closed list: A taps 'Reopen together…' and stays; B redeems. Watch A. Then, on either waiting screen, tap 'Check now'.</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
+          <t>Both times A's screen changes on its own within about ten seconds: the pairing wait becomes '{name} joined.', and the closed list becomes the live list with the 'They used the code' line and the spent code gone. 'Check now' sits under the waiting text and under a minted reopen code, and does the same immediately. Once A has opened the list, the pairing screen underneath stops looking (nothing to see by eye; the rule is focus AND foreground AND under 30 minutes).</t>
         </is>
       </c>
       <c r="G309" s="7" t="inlineStr">
@@ -13094,7 +13094,7 @@
     <row r="310">
       <c r="A310" s="6" t="inlineStr">
         <is>
-          <t>OUR-37</t>
+          <t>OUR-36</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -13102,24 +13102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C310" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C310" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>Rename yourself, and only yourself</t>
+          <t>Delete for good commits when the screen closes, not on a timer</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
+          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
+          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
         </is>
       </c>
       <c r="G310" s="7" t="inlineStr">
@@ -13134,7 +13134,7 @@
     <row r="311">
       <c r="A311" s="6" t="inlineStr">
         <is>
-          <t>OUR-38</t>
+          <t>OUR-37</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -13149,17 +13149,17 @@
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>A dropped signal never throws you out of the room</t>
+          <t>Rename yourself, and only yourself</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
+          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
+          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
         </is>
       </c>
       <c r="G311" s="7" t="inlineStr">
@@ -13174,7 +13174,7 @@
     <row r="312">
       <c r="A312" s="6" t="inlineStr">
         <is>
-          <t>OUR-39</t>
+          <t>OUR-38</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -13182,24 +13182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C312" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C312" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>Report this list reaches us and tells nobody else</t>
+          <t>A dropped signal never throws you out of the room</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
+          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
+          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
         </is>
       </c>
       <c r="G312" s="7" t="inlineStr">
@@ -13214,7 +13214,7 @@
     <row r="313">
       <c r="A313" s="6" t="inlineStr">
         <is>
-          <t>OUR-40</t>
+          <t>OUR-39</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -13229,17 +13229,17 @@
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
+          <t>Report this list reaches us and tells nobody else</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
+          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
+          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
         </is>
       </c>
       <c r="G313" s="7" t="inlineStr">
@@ -13254,7 +13254,7 @@
     <row r="314">
       <c r="A314" s="6" t="inlineStr">
         <is>
-          <t>OUR-41</t>
+          <t>OUR-40</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -13262,24 +13262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C314" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C314" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>Leaving is the block, and needs no reason</t>
+          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap 'Leave this list'.</t>
+          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
+          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
         </is>
       </c>
       <c r="G314" s="7" t="inlineStr">
@@ -13294,12 +13294,12 @@
     <row r="315">
       <c r="A315" s="6" t="inlineStr">
         <is>
-          <t>LEG-05</t>
+          <t>OUR-41</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C315" s="10" t="inlineStr">
@@ -13309,17 +13309,17 @@
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>The shared-list clauses are in both copies of both documents</t>
+          <t>Leaving is the block, and needs no reason</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
+          <t>On a live list, tap 'Leave this list'.</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
+          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
         </is>
       </c>
       <c r="G315" s="7" t="inlineStr">
@@ -13334,32 +13334,32 @@
     <row r="316">
       <c r="A316" s="6" t="inlineStr">
         <is>
-          <t>OUR-42</t>
+          <t>LEG-05</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C316" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C316" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>A change on one phone appears on the other WITHOUT touching it</t>
+          <t>The shared-list clauses are in both copies of both documents</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
+          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
+          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
         </is>
       </c>
       <c r="G316" s="7" t="inlineStr">
@@ -13374,7 +13374,7 @@
     <row r="317">
       <c r="A317" s="6" t="inlineStr">
         <is>
-          <t>OUR-43</t>
+          <t>OUR-42</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -13389,17 +13389,17 @@
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>Opening your own list does not bounce you back</t>
+          <t>A change on one phone appears on the other WITHOUT touching it</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
+          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
+          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
         </is>
       </c>
       <c r="G317" s="7" t="inlineStr">
@@ -13414,7 +13414,7 @@
     <row r="318">
       <c r="A318" s="6" t="inlineStr">
         <is>
-          <t>OUR-44</t>
+          <t>OUR-43</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -13422,24 +13422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C318" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C318" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>The pairing screen offers a way INTO the list</t>
+          <t>Opening your own list does not bounce you back</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>Finish pairing, then look at the pairing screen.</t>
+          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
+          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
         </is>
       </c>
       <c r="G318" s="7" t="inlineStr">
@@ -13454,7 +13454,7 @@
     <row r="319">
       <c r="A319" s="6" t="inlineStr">
         <is>
-          <t>OUR-45</t>
+          <t>OUR-44</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -13469,17 +13469,17 @@
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash appears and then takes itself away</t>
+          <t>The pairing screen offers a way INTO the list</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
+          <t>Finish pairing, then look at the pairing screen.</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
+          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
         </is>
       </c>
       <c r="G319" s="7" t="inlineStr">
@@ -13494,7 +13494,7 @@
     <row r="320">
       <c r="A320" s="6" t="inlineStr">
         <is>
-          <t>OUR-47</t>
+          <t>OUR-45</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -13509,17 +13509,17 @@
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>The Ours door on Today is findable</t>
+          <t>The quiet wash appears and then takes itself away</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>With a live list, look at Today.</t>
+          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>A tinted, accented card carrying the list's name, not a hairline footnote. Absent entirely when there is no live list.</t>
+          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
         </is>
       </c>
       <c r="G320" s="7" t="inlineStr">
@@ -13534,7 +13534,7 @@
     <row r="321">
       <c r="A321" s="6" t="inlineStr">
         <is>
-          <t>OUR-48</t>
+          <t>OUR-47</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -13542,24 +13542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C321" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C321" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Their tick marks your copy DONE and leaves it on your day</t>
+          <t>The Ours door on Today is findable</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
+          <t>With a live list, look at Today.</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
+          <t>A tinted, accented card carrying the list's name, not a hairline footnote. Absent entirely when there is no live list.</t>
         </is>
       </c>
       <c r="G321" s="7" t="inlineStr">
@@ -13574,7 +13574,7 @@
     <row r="322">
       <c r="A322" s="6" t="inlineStr">
         <is>
-          <t>OUR-49</t>
+          <t>OUR-48</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -13589,17 +13589,17 @@
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>A settled copy carries a completion DATE, not just a done flag</t>
+          <t>Their tick marks your copy DONE and leaves it on your day</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
+          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
+          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
         </is>
       </c>
       <c r="G322" s="7" t="inlineStr">
@@ -13614,7 +13614,7 @@
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
         <is>
-          <t>OUR-50</t>
+          <t>OUR-49</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -13622,24 +13622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C323" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C323" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
-          <t>A finished copy can be brought over again</t>
+          <t>A settled copy carries a completion DATE, not just a done flag</t>
         </is>
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, hold that row in Ours.</t>
+          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
         </is>
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
+          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
         </is>
       </c>
       <c r="G323" s="7" t="inlineStr">
@@ -13654,7 +13654,7 @@
     <row r="324">
       <c r="A324" s="6" t="inlineStr">
         <is>
-          <t>OUR-51</t>
+          <t>OUR-50</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -13662,24 +13662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C324" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C324" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>Your own edit never highlights; their later edit always does</t>
+          <t>A finished copy can be brought over again</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
+          <t>After OUR-48, hold that row in Ours.</t>
         </is>
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
+          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
         </is>
       </c>
       <c r="G324" s="7" t="inlineStr">
@@ -13694,7 +13694,7 @@
     <row r="325">
       <c r="A325" s="6" t="inlineStr">
         <is>
-          <t>OUR-52</t>
+          <t>OUR-51</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -13702,24 +13702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C325" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C325" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>The highlight arrives at once and fades away</t>
+          <t>Your own edit never highlights; their later edit always does</t>
         </is>
       </c>
       <c r="E325" s="9" t="inlineStr">
         <is>
-          <t>Have B change a row while A is on the list.</t>
+          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
         </is>
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
+          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
         </is>
       </c>
       <c r="G325" s="7" t="inlineStr">
@@ -13734,7 +13734,7 @@
     <row r="326">
       <c r="A326" s="6" t="inlineStr">
         <is>
-          <t>OUR-53</t>
+          <t>OUR-52</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -13749,17 +13749,17 @@
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
-          <t>Two devices share ONE clock</t>
+          <t>The highlight arrives at once and fades away</t>
         </is>
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
+          <t>Have B change a row while A is on the list.</t>
         </is>
       </c>
       <c r="F326" s="9" t="inlineStr">
         <is>
-          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
+          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
         </is>
       </c>
       <c r="G326" s="7" t="inlineStr">
@@ -13774,7 +13774,7 @@
     <row r="327">
       <c r="A327" s="6" t="inlineStr">
         <is>
-          <t>OUR-54</t>
+          <t>OUR-53</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -13782,24 +13782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C327" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C327" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>The debug panel is opt-in and carries no task text</t>
+          <t>Two devices share ONE clock</t>
         </is>
       </c>
       <c r="E327" s="9" t="inlineStr">
         <is>
-          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
+          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
         </is>
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
+          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
         </is>
       </c>
       <c r="G327" s="7" t="inlineStr">
@@ -13814,7 +13814,7 @@
     <row r="328">
       <c r="A328" s="6" t="inlineStr">
         <is>
-          <t>OUR-55</t>
+          <t>OUR-54</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -13822,24 +13822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C328" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C328" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>Capture on Ours IS Today's capture</t>
+          <t>The debug panel is opt-in and carries no task text</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>Open a shared list and tap the launcher at the foot of the screen.</t>
+          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
         </is>
       </c>
       <c r="F328" s="9" t="inlineStr">
         <is>
-          <t>The same panel Today opens: the same input, the same Speak button (web), the same door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
+          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
         </is>
       </c>
       <c r="G328" s="7" t="inlineStr">
@@ -13854,7 +13854,7 @@
     <row r="329">
       <c r="A329" s="6" t="inlineStr">
         <is>
-          <t>OUR-56</t>
+          <t>OUR-55</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -13869,17 +13869,17 @@
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>Repeating can be set AT capture, without knowing a gesture</t>
+          <t>Capture on Ours IS Today's capture</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
+          <t>Open a shared list and tap the launcher at the foot of the screen.</t>
         </is>
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
+          <t>The same panel Today opens: the same input, the same Speak button (web), the same door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
         </is>
       </c>
       <c r="G329" s="7" t="inlineStr">
@@ -13894,7 +13894,7 @@
     <row r="330">
       <c r="A330" s="6" t="inlineStr">
         <is>
-          <t>OUR-57</t>
+          <t>OUR-56</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -13902,24 +13902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C330" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C330" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>A dump becomes several shared rows, in the order typed</t>
+          <t>Repeating can be set AT capture, without knowing a gesture</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>Type three lines into the Ours capture and Add.</t>
+          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
         </is>
       </c>
       <c r="F330" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
+          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
         </is>
       </c>
       <c r="G330" s="7" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="331">
       <c r="A331" s="6" t="inlineStr">
         <is>
-          <t>OUR-58</t>
+          <t>OUR-57</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -13942,24 +13942,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C331" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C331" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D331" s="9" t="inlineStr">
         <is>
-          <t>The shared door offers When and Repeating, never Steps</t>
+          <t>A dump becomes several shared rows, in the order typed</t>
         </is>
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>Open the door on Ours and compare it with the door on Today.</t>
+          <t>Type three lines into the Ours capture and Add.</t>
         </is>
       </c>
       <c r="F331" s="9" t="inlineStr">
         <is>
-          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
+          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
         </is>
       </c>
       <c r="G331" s="7" t="inlineStr">
@@ -13974,7 +13974,7 @@
     <row r="332">
       <c r="A332" s="6" t="inlineStr">
         <is>
-          <t>OUR-59</t>
+          <t>OUR-58</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -13982,24 +13982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C332" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C332" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D332" s="9" t="inlineStr">
         <is>
-          <t>Typed text survives closing the panel</t>
+          <t>The shared door offers When and Repeating, never Steps</t>
         </is>
       </c>
       <c r="E332" s="9" t="inlineStr">
         <is>
-          <t>Type half a sentence into the Ours capture, tap Close, tick something, then reopen the panel.</t>
+          <t>Open the door on Ours and compare it with the door on Today.</t>
         </is>
       </c>
       <c r="F332" s="9" t="inlineStr">
         <is>
-          <t>The half sentence is still there. The panel is hidden, never unmounted. The door resets to no-repeat, the words never reset.</t>
+          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
         </is>
       </c>
       <c r="G332" s="7" t="inlineStr">
@@ -14014,7 +14014,7 @@
     <row r="333">
       <c r="A333" s="6" t="inlineStr">
         <is>
-          <t>OUR-60</t>
+          <t>OUR-59</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -14029,22 +14029,22 @@
       </c>
       <c r="D333" s="9" t="inlineStr">
         <is>
-          <t>The Ours capture rides above the keyboard</t>
+          <t>Typed text survives closing the panel</t>
         </is>
       </c>
       <c r="E333" s="9" t="inlineStr">
         <is>
-          <t>On a real Android device, open the Ours capture and start typing.</t>
+          <t>Type half a sentence into the Ours capture, tap Close, tick something, then reopen the panel.</t>
         </is>
       </c>
       <c r="F333" s="9" t="inlineStr">
         <is>
-          <t>The panel and its Add button stay visible above the keyboard. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
+          <t>The half sentence is still there. The panel is hidden, never unmounted. The door resets to no-repeat, the words never reset.</t>
         </is>
       </c>
       <c r="G333" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H333" s="7" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
     <row r="334">
       <c r="A334" s="6" t="inlineStr">
         <is>
-          <t>OUR-61</t>
+          <t>OUR-60</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -14062,29 +14062,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C334" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C334" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D334" s="9" t="inlineStr">
         <is>
-          <t>No AI on the shared capture</t>
+          <t>The Ours capture rides above the keyboard</t>
         </is>
       </c>
       <c r="E334" s="9" t="inlineStr">
         <is>
-          <t>Open the Ours capture with AI enabled in Settings.</t>
+          <t>On a real Android device, open the Ours capture and start typing.</t>
         </is>
       </c>
       <c r="F334" s="9" t="inlineStr">
         <is>
-          <t>No 'Break it down' and no 'Sort for me': steps a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
+          <t>The panel and its Add button stay visible above the keyboard. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
         </is>
       </c>
       <c r="G334" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H334" s="7" t="inlineStr"/>
@@ -14094,7 +14094,7 @@
     <row r="335">
       <c r="A335" s="6" t="inlineStr">
         <is>
-          <t>OUR-62</t>
+          <t>OUR-61</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -14102,29 +14102,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C335" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C335" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D335" s="9" t="inlineStr">
         <is>
-          <t>Scan (premium) reaches the shared capture</t>
+          <t>No AI on the shared capture</t>
         </is>
       </c>
       <c r="E335" s="9" t="inlineStr">
         <is>
-          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
+          <t>Open the Ours capture with AI enabled in Settings.</t>
         </is>
       </c>
       <c r="F335" s="9" t="inlineStr">
         <is>
-          <t>The words land IN the capture box, not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
+          <t>No 'Break it down' and no 'Sort for me': steps a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
         </is>
       </c>
       <c r="G335" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H335" s="7" t="inlineStr"/>
@@ -14134,7 +14134,7 @@
     <row r="336">
       <c r="A336" s="6" t="inlineStr">
         <is>
-          <t>OUR-63</t>
+          <t>OUR-62</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="D336" s="9" t="inlineStr">
         <is>
-          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
+          <t>Scan (premium) reaches the shared capture</t>
         </is>
       </c>
       <c r="E336" s="9" t="inlineStr">
         <is>
-          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
+          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
         </is>
       </c>
       <c r="F336" s="9" t="inlineStr">
         <is>
-          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
+          <t>The words land IN the capture box, not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
         </is>
       </c>
       <c r="G336" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H336" s="7" t="inlineStr"/>
@@ -14174,7 +14174,7 @@
     <row r="337">
       <c r="A337" s="6" t="inlineStr">
         <is>
-          <t>OUR-64</t>
+          <t>OUR-63</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -14182,24 +14182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C337" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C337" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D337" s="9" t="inlineStr">
         <is>
-          <t>The photo never reaches the shared list</t>
+          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
         </is>
       </c>
       <c r="E337" s="9" t="inlineStr">
         <is>
-          <t>Scan something into Ours and Add it. Check the other device.</t>
+          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
         </is>
       </c>
       <c r="F337" s="9" t="inlineStr">
         <is>
-          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
+          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
         </is>
       </c>
       <c r="G337" s="7" t="inlineStr">
@@ -14214,7 +14214,7 @@
     <row r="338">
       <c r="A338" s="6" t="inlineStr">
         <is>
-          <t>OUR-65</t>
+          <t>OUR-64</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -14222,24 +14222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C338" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C338" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D338" s="9" t="inlineStr">
         <is>
-          <t>Scan is absent when AI is off</t>
+          <t>The photo never reaches the shared list</t>
         </is>
       </c>
       <c r="E338" s="9" t="inlineStr">
         <is>
-          <t>Turn AI off in Settings, then open the Ours capture.</t>
+          <t>Scan something into Ours and Add it. Check the other device.</t>
         </is>
       </c>
       <c r="F338" s="9" t="inlineStr">
         <is>
-          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
+          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
         </is>
       </c>
       <c r="G338" s="7" t="inlineStr">
@@ -14254,7 +14254,7 @@
     <row r="339">
       <c r="A339" s="6" t="inlineStr">
         <is>
-          <t>OUR-66</t>
+          <t>OUR-65</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -14262,24 +14262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C339" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C339" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D339" s="9" t="inlineStr">
         <is>
-          <t>A repeating shared row appears on BOTH Todays on its day</t>
+          <t>Scan is absent when AI is off</t>
         </is>
       </c>
       <c r="E339" s="9" t="inlineStr">
         <is>
-          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
+          <t>Turn AI off in Settings, then open the Ours capture.</t>
         </is>
       </c>
       <c r="F339" s="9" t="inlineStr">
         <is>
-          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
+          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
         </is>
       </c>
       <c r="G339" s="7" t="inlineStr">
@@ -14294,7 +14294,7 @@
     <row r="340">
       <c r="A340" s="6" t="inlineStr">
         <is>
-          <t>OUR-67</t>
+          <t>OUR-66</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -14309,17 +14309,17 @@
       </c>
       <c r="D340" s="9" t="inlineStr">
         <is>
-          <t>An UNDATED shared row never reaches Today</t>
+          <t>A repeating shared row appears on BOTH Todays on its day</t>
         </is>
       </c>
       <c r="E340" s="9" t="inlineStr">
         <is>
-          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
+          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
         </is>
       </c>
       <c r="F340" s="9" t="inlineStr">
         <is>
-          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
+          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
         </is>
       </c>
       <c r="G340" s="7" t="inlineStr">
@@ -14334,7 +14334,7 @@
     <row r="341">
       <c r="A341" s="6" t="inlineStr">
         <is>
-          <t>OUR-68</t>
+          <t>OUR-67</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -14349,17 +14349,17 @@
       </c>
       <c r="D341" s="9" t="inlineStr">
         <is>
-          <t>Shared rows never make the day look heavier</t>
+          <t>An UNDATED shared row never reaches Today</t>
         </is>
       </c>
       <c r="E341" s="9" t="inlineStr">
         <is>
-          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
+          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
         </is>
       </c>
       <c r="F341" s="9" t="inlineStr">
         <is>
-          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
+          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
         </is>
       </c>
       <c r="G341" s="7" t="inlineStr">
@@ -14374,7 +14374,7 @@
     <row r="342">
       <c r="A342" s="6" t="inlineStr">
         <is>
-          <t>OUR-69</t>
+          <t>OUR-68</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -14389,17 +14389,17 @@
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>Ticking a shared row from Today closes it for both</t>
+          <t>Shared rows never make the day look heavier</t>
         </is>
       </c>
       <c r="E342" s="9" t="inlineStr">
         <is>
-          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
+          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
         </is>
       </c>
       <c r="F342" s="9" t="inlineStr">
         <is>
-          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
+          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
         </is>
       </c>
       <c r="G342" s="7" t="inlineStr">
@@ -14414,7 +14414,7 @@
     <row r="343">
       <c r="A343" s="6" t="inlineStr">
         <is>
-          <t>OUR-70</t>
+          <t>OUR-69</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -14422,24 +14422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C343" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C343" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D343" s="9" t="inlineStr">
         <is>
-          <t>A dated shared row shows from its day onward, never before</t>
+          <t>Ticking a shared row from Today closes it for both</t>
         </is>
       </c>
       <c r="E343" s="9" t="inlineStr">
         <is>
-          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
+          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
         </is>
       </c>
       <c r="F343" s="9" t="inlineStr">
         <is>
-          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
+          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
         </is>
       </c>
       <c r="G343" s="7" t="inlineStr">
@@ -14454,7 +14454,7 @@
     <row r="344">
       <c r="A344" s="6" t="inlineStr">
         <is>
-          <t>OUR-71</t>
+          <t>OUR-70</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -14462,24 +14462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C344" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C344" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D344" s="9" t="inlineStr">
         <is>
-          <t>The shared capture rests on Anytime</t>
+          <t>A dated shared row shows from its day onward, never before</t>
         </is>
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>Open the Ours capture and open the door.</t>
+          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
         </is>
       </c>
       <c r="F344" s="9" t="inlineStr">
         <is>
-          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected. The Add button says just 'Add'. Choosing Today makes it read 'Add . Today', because that is the notable case: it will appear on both your days.</t>
+          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
         </is>
       </c>
       <c r="G344" s="7" t="inlineStr">
@@ -14494,7 +14494,7 @@
     <row r="345">
       <c r="A345" s="6" t="inlineStr">
         <is>
-          <t>OUR-112</t>
+          <t>OUR-71</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -14509,17 +14509,17 @@
       </c>
       <c r="D345" s="9" t="inlineStr">
         <is>
-          <t>A shared row's WHEN can be changed, and cleared</t>
+          <t>The shared capture rests on Anytime</t>
         </is>
       </c>
       <c r="E345" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
+          <t>Open the Ours capture and open the door.</t>
         </is>
       </c>
       <c r="F345" s="9" t="inlineStr">
         <is>
-          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
+          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected. The Add button says just 'Add'. Choosing Today makes it read 'Add . Today', because that is the notable case: it will appear on both your days.</t>
         </is>
       </c>
       <c r="G345" s="7" t="inlineStr">
@@ -14534,7 +14534,7 @@
     <row r="346">
       <c r="A346" s="6" t="inlineStr">
         <is>
-          <t>OUR-113</t>
+          <t>OUR-112</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -14549,17 +14549,17 @@
       </c>
       <c r="D346" s="9" t="inlineStr">
         <is>
-          <t>Ending a rhythm does NOT mark the row done for both people</t>
+          <t>A shared row's WHEN can be changed, and cleared</t>
         </is>
       </c>
       <c r="E346" s="9" t="inlineStr">
         <is>
-          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
+          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
         </is>
       </c>
       <c r="F346" s="9" t="inlineStr">
         <is>
-          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
+          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
         </is>
       </c>
       <c r="G346" s="7" t="inlineStr">
@@ -14574,7 +14574,7 @@
     <row r="347">
       <c r="A347" s="6" t="inlineStr">
         <is>
-          <t>OUR-114</t>
+          <t>OUR-113</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -14582,24 +14582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C347" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C347" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D347" s="9" t="inlineStr">
         <is>
-          <t>The day zone changes its question when a rhythm is alive</t>
+          <t>Ending a rhythm does NOT mark the row done for both people</t>
         </is>
       </c>
       <c r="E347" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
+          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
         </is>
       </c>
       <c r="F347" s="9" t="inlineStr">
         <is>
-          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
+          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
         </is>
       </c>
       <c r="G347" s="7" t="inlineStr">
@@ -14614,7 +14614,7 @@
     <row r="348">
       <c r="A348" s="6" t="inlineStr">
         <is>
-          <t>OUR-115</t>
+          <t>OUR-114</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -14629,17 +14629,17 @@
       </c>
       <c r="D348" s="9" t="inlineStr">
         <is>
-          <t>Setting a shared row to Today actually reaches both Todays</t>
+          <t>The day zone changes its question when a rhythm is alive</t>
         </is>
       </c>
       <c r="E348" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
+          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
         </is>
       </c>
       <c r="F348" s="9" t="inlineStr">
         <is>
-          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
+          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
         </is>
       </c>
       <c r="G348" s="7" t="inlineStr">
@@ -14654,7 +14654,7 @@
     <row r="349">
       <c r="A349" s="6" t="inlineStr">
         <is>
-          <t>OUR-116</t>
+          <t>OUR-115</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -14662,24 +14662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C349" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C349" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D349" s="9" t="inlineStr">
         <is>
-          <t>An idle Set does not wash the row on the other device</t>
+          <t>Setting a shared row to Today actually reaches both Todays</t>
         </is>
       </c>
       <c r="E349" s="9" t="inlineStr">
         <is>
-          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
+          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
         </is>
       </c>
       <c r="F349" s="9" t="inlineStr">
         <is>
-          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
+          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
         </is>
       </c>
       <c r="G349" s="7" t="inlineStr">
@@ -14694,7 +14694,7 @@
     <row r="350">
       <c r="A350" s="6" t="inlineStr">
         <is>
-          <t>OUR-118</t>
+          <t>OUR-116</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -14702,24 +14702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C350" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C350" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D350" s="9" t="inlineStr">
         <is>
-          <t>A repeat you have already done today keeps its held card</t>
+          <t>An idle Set does not wash the row on the other device</t>
         </is>
       </c>
       <c r="E350" s="9" t="inlineStr">
         <is>
-          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
+          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
         </is>
       </c>
       <c r="F350" s="9" t="inlineStr">
         <is>
-          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
+          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
         </is>
       </c>
       <c r="G350" s="7" t="inlineStr">
@@ -14734,7 +14734,7 @@
     <row r="351">
       <c r="A351" s="6" t="inlineStr">
         <is>
-          <t>OUR-117</t>
+          <t>OUR-118</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -14742,24 +14742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C351" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C351" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D351" s="9" t="inlineStr">
         <is>
-          <t>The Repeating drawer is untouched by the When editor</t>
+          <t>A repeat you have already done today keeps its held card</t>
         </is>
       </c>
       <c r="E351" s="9" t="inlineStr">
         <is>
-          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
+          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
         </is>
       </c>
       <c r="F351" s="9" t="inlineStr">
         <is>
-          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the drawer.</t>
+          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
         </is>
       </c>
       <c r="G351" s="7" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="352">
       <c r="A352" s="6" t="inlineStr">
         <is>
-          <t>OUR-119</t>
+          <t>OUR-117</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -14789,17 +14789,17 @@
       </c>
       <c r="D352" s="9" t="inlineStr">
         <is>
-          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
+          <t>The Repeating drawer is untouched by the When editor</t>
         </is>
       </c>
       <c r="E352" s="9" t="inlineStr">
         <is>
-          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
+          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
         </is>
       </c>
       <c r="F352" s="9" t="inlineStr">
         <is>
-          <t>Monthly is the fourth rhythm chip here too, from the same sheet the personal drawer uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
+          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the drawer.</t>
         </is>
       </c>
       <c r="G352" s="7" t="inlineStr">
@@ -14814,7 +14814,7 @@
     <row r="353">
       <c r="A353" s="6" t="inlineStr">
         <is>
-          <t>OUR-111</t>
+          <t>OUR-119</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -14822,24 +14822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C353" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C353" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D353" s="9" t="inlineStr">
         <is>
-          <t>A finished dated shared row leaves both Todays the next day</t>
+          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
         </is>
       </c>
       <c r="E353" s="9" t="inlineStr">
         <is>
-          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
+          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
         </is>
       </c>
       <c r="F353" s="9" t="inlineStr">
         <is>
-          <t>Today: still there on BOTH, struck through, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
+          <t>Monthly is the fourth rhythm chip here too, from the same sheet the personal drawer uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
         </is>
       </c>
       <c r="G353" s="7" t="inlineStr">
@@ -14854,7 +14854,7 @@
     <row r="354">
       <c r="A354" s="6" t="inlineStr">
         <is>
-          <t>OUR-72</t>
+          <t>OUR-111</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -14862,24 +14862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C354" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C354" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D354" s="9" t="inlineStr">
         <is>
-          <t>A repeat supersedes the day rather than joining it</t>
+          <t>A finished dated shared row leaves both Todays the next day</t>
         </is>
       </c>
       <c r="E354" s="9" t="inlineStr">
         <is>
-          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
+          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
         </is>
       </c>
       <c r="F354" s="9" t="inlineStr">
         <is>
-          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
+          <t>Today: still there on BOTH, struck through, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
         </is>
       </c>
       <c r="G354" s="7" t="inlineStr">
@@ -14894,7 +14894,7 @@
     <row r="355">
       <c r="A355" s="6" t="inlineStr">
         <is>
-          <t>OUR-73</t>
+          <t>OUR-72</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -14902,24 +14902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C355" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C355" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D355" s="9" t="inlineStr">
         <is>
-          <t>An unreadable cadence is never placed on a day</t>
+          <t>A repeat supersedes the day rather than joining it</t>
         </is>
       </c>
       <c r="E355" s="9" t="inlineStr">
         <is>
-          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
+          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
         </is>
       </c>
       <c r="F355" s="9" t="inlineStr">
         <is>
-          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
+          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
         </is>
       </c>
       <c r="G355" s="7" t="inlineStr">
@@ -14934,7 +14934,7 @@
     <row r="356">
       <c r="A356" s="6" t="inlineStr">
         <is>
-          <t>OUR-74</t>
+          <t>OUR-73</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -14942,24 +14942,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C356" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C356" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D356" s="9" t="inlineStr">
         <is>
-          <t>The door says what changed since you looked, and clears when you look</t>
+          <t>An unreadable cadence is never placed on a day</t>
         </is>
       </c>
       <c r="E356" s="9" t="inlineStr">
         <is>
-          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap through to Ours and come back.</t>
+          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
         </is>
       </c>
       <c r="F356" s="9" t="inlineStr">
         <is>
-          <t>The Ours door reads '1 since you looked'. After visiting, it is gone. The number is bounded by your own attention, not by the list's length, so it can never sit there climbing at you.</t>
+          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
         </is>
       </c>
       <c r="G356" s="7" t="inlineStr">
@@ -14974,7 +14974,7 @@
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
         <is>
-          <t>OUR-75</t>
+          <t>OUR-74</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -14982,24 +14982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C357" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C357" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D357" s="9" t="inlineStr">
         <is>
-          <t>Your OWN changes never appear in that count</t>
+          <t>The door says what changed since you looked, and clears when you look</t>
         </is>
       </c>
       <c r="E357" s="9" t="inlineStr">
         <is>
-          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
+          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap through to Ours and come back.</t>
         </is>
       </c>
       <c r="F357" s="9" t="inlineStr">
         <is>
-          <t>No count on the door. It uses the room's own wash arithmetic, so the door and the room always agree about whose change it was.</t>
+          <t>The Ours door reads '1 since you looked'. After visiting, it is gone. The number is bounded by your own attention, not by the list's length, so it can never sit there climbing at you.</t>
         </is>
       </c>
       <c r="G357" s="7" t="inlineStr">
@@ -15014,7 +15014,7 @@
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
         <is>
-          <t>OUR-76</t>
+          <t>OUR-75</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -15029,17 +15029,17 @@
       </c>
       <c r="D358" s="9" t="inlineStr">
         <is>
-          <t>A first-ever visit counts nothing</t>
+          <t>Your OWN changes never appear in that count</t>
         </is>
       </c>
       <c r="E358" s="9" t="inlineStr">
         <is>
-          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
+          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
         </is>
       </c>
       <c r="F358" s="9" t="inlineStr">
         <is>
-          <t>No count. There is no 'last looked' to measure against, and inventing one would open the app with a number already on it.</t>
+          <t>No count on the door. It uses the room's own wash arithmetic, so the door and the room always agree about whose change it was.</t>
         </is>
       </c>
       <c r="G358" s="7" t="inlineStr">
@@ -15054,7 +15054,7 @@
     <row r="359">
       <c r="A359" s="6" t="inlineStr">
         <is>
-          <t>OUR-77</t>
+          <t>OUR-76</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -15062,24 +15062,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C359" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C359" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D359" s="9" t="inlineStr">
         <is>
-          <t>The capture's AI note names only what that surface HAS</t>
+          <t>A first-ever visit counts nothing</t>
         </is>
       </c>
       <c r="E359" s="9" t="inlineStr">
         <is>
-          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
+          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
         </is>
       </c>
       <c r="F359" s="9" t="inlineStr">
         <is>
-          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
+          <t>No count. There is no 'last looked' to measure against, and inventing one would open the app with a number already on it.</t>
         </is>
       </c>
       <c r="G359" s="7" t="inlineStr">
@@ -15094,7 +15094,7 @@
     <row r="360">
       <c r="A360" s="6" t="inlineStr">
         <is>
-          <t>OUR-78</t>
+          <t>OUR-77</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -15109,17 +15109,17 @@
       </c>
       <c r="D360" s="9" t="inlineStr">
         <is>
-          <t>Scan discloses on every path that can reach a camera</t>
+          <t>The capture's AI note names only what that surface HAS</t>
         </is>
       </c>
       <c r="E360" s="9" t="inlineStr">
         <is>
-          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
+          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
         </is>
       </c>
       <c r="F360" s="9" t="inlineStr">
         <is>
-          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
+          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
         </is>
       </c>
       <c r="G360" s="7" t="inlineStr">
@@ -15134,7 +15134,7 @@
     <row r="361">
       <c r="A361" s="6" t="inlineStr">
         <is>
-          <t>OUR-79</t>
+          <t>OUR-78</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -15149,17 +15149,17 @@
       </c>
       <c r="D361" s="9" t="inlineStr">
         <is>
-          <t>Press and hold a From Ours row on Today</t>
+          <t>Scan discloses on every path that can reach a camera</t>
         </is>
       </c>
       <c r="E361" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Ours strip.</t>
+          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
         </is>
       </c>
       <c r="F361" s="9" t="inlineStr">
         <is>
-          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
+          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
         </is>
       </c>
       <c r="G361" s="7" t="inlineStr">
@@ -15174,7 +15174,7 @@
     <row r="362">
       <c r="A362" s="6" t="inlineStr">
         <is>
-          <t>OUR-80</t>
+          <t>OUR-79</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -15189,17 +15189,17 @@
       </c>
       <c r="D362" s="9" t="inlineStr">
         <is>
-          <t>Pin and Move-to never rearrange the other person's day</t>
+          <t>Press and hold a From Ours row on Today</t>
         </is>
       </c>
       <c r="E362" s="9" t="inlineStr">
         <is>
-          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
+          <t>Hold a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F362" s="9" t="inlineStr">
         <is>
-          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
+          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
         </is>
       </c>
       <c r="G362" s="7" t="inlineStr">
@@ -15214,7 +15214,7 @@
     <row r="363">
       <c r="A363" s="6" t="inlineStr">
         <is>
-          <t>OUR-81</t>
+          <t>OUR-80</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -15222,24 +15222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C363" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C363" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D363" s="9" t="inlineStr">
         <is>
-          <t>A taken-on row is never on screen twice</t>
+          <t>Pin and Move-to never rearrange the other person's day</t>
         </is>
       </c>
       <c r="E363" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
+          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
         </is>
       </c>
       <c r="F363" s="9" t="inlineStr">
         <is>
-          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
+          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
         </is>
       </c>
       <c r="G363" s="7" t="inlineStr">
@@ -15254,7 +15254,7 @@
     <row r="364">
       <c r="A364" s="6" t="inlineStr">
         <is>
-          <t>OUR-82</t>
+          <t>OUR-81</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -15269,17 +15269,17 @@
       </c>
       <c r="D364" s="9" t="inlineStr">
         <is>
-          <t>Move-to is not offered on a repeating shared row</t>
+          <t>A taken-on row is never on screen twice</t>
         </is>
       </c>
       <c r="E364" s="9" t="inlineStr">
         <is>
-          <t>Hold a repeating row in the From Ours strip.</t>
+          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
         </is>
       </c>
       <c r="F364" s="9" t="inlineStr">
         <is>
-          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
+          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
         </is>
       </c>
       <c r="G364" s="7" t="inlineStr">
@@ -15294,7 +15294,7 @@
     <row r="365">
       <c r="A365" s="6" t="inlineStr">
         <is>
-          <t>OUR-83</t>
+          <t>OUR-82</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -15302,24 +15302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C365" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C365" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D365" s="9" t="inlineStr">
         <is>
-          <t>One shared row, one route onto your day</t>
+          <t>Move-to is not offered on a repeating shared row</t>
         </is>
       </c>
       <c r="E365" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
+          <t>Hold a repeating row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F365" s="9" t="inlineStr">
         <is>
-          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
+          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
         </is>
       </c>
       <c r="G365" s="7" t="inlineStr">
@@ -15334,7 +15334,7 @@
     <row r="366">
       <c r="A366" s="6" t="inlineStr">
         <is>
-          <t>OUR-84</t>
+          <t>OUR-83</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -15349,17 +15349,17 @@
       </c>
       <c r="D366" s="9" t="inlineStr">
         <is>
-          <t>Take a From Ours row on, and it becomes an ordinary task</t>
+          <t>One shared row, one route onto your day</t>
         </is>
       </c>
       <c r="E366" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
+          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
         </is>
       </c>
       <c r="F366" s="9" t="inlineStr">
         <is>
-          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
+          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
         </is>
       </c>
       <c r="G366" s="7" t="inlineStr">
@@ -15374,7 +15374,7 @@
     <row r="367">
       <c r="A367" s="6" t="inlineStr">
         <is>
-          <t>OUR-85</t>
+          <t>OUR-84</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -15382,24 +15382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C367" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C367" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D367" s="9" t="inlineStr">
         <is>
-          <t>Break it down works once taken on, and never touches the shared list</t>
+          <t>Take a From Ours row on, and it becomes an ordinary task</t>
         </is>
       </c>
       <c r="E367" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on, then Break it down.</t>
+          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
         </is>
       </c>
       <c r="F367" s="9" t="inlineStr">
         <is>
-          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
+          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
         </is>
       </c>
       <c r="G367" s="7" t="inlineStr">
@@ -15414,7 +15414,7 @@
     <row r="368">
       <c r="A368" s="6" t="inlineStr">
         <is>
-          <t>OUR-86</t>
+          <t>OUR-85</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -15422,24 +15422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C368" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C368" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D368" s="9" t="inlineStr">
         <is>
-          <t>Select several rows in the room and tick them together</t>
+          <t>Break it down works once taken on, and never touches the shared list</t>
         </is>
       </c>
       <c r="E368" s="9" t="inlineStr">
         <is>
-          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
+          <t>Take a shared row on, then Break it down.</t>
         </is>
       </c>
       <c r="F368" s="9" t="inlineStr">
         <is>
-          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
+          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
         </is>
       </c>
       <c r="G368" s="7" t="inlineStr">
@@ -15454,7 +15454,7 @@
     <row r="369">
       <c r="A369" s="6" t="inlineStr">
         <is>
-          <t>OUR-87</t>
+          <t>OUR-86</t>
         </is>
       </c>
       <c r="B369" s="7" t="inlineStr">
@@ -15469,17 +15469,17 @@
       </c>
       <c r="D369" s="9" t="inlineStr">
         <is>
-          <t>Bulk tick never UN-ticks</t>
+          <t>Select several rows in the room and tick them together</t>
         </is>
       </c>
       <c r="E369" s="9" t="inlineStr">
         <is>
-          <t>Select a mix of done and not-done rows and tap Done.</t>
+          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
         </is>
       </c>
       <c r="F369" s="9" t="inlineStr">
         <is>
-          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
+          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
         </is>
       </c>
       <c r="G369" s="7" t="inlineStr">
@@ -15494,7 +15494,7 @@
     <row r="370">
       <c r="A370" s="6" t="inlineStr">
         <is>
-          <t>OUR-88</t>
+          <t>OUR-87</t>
         </is>
       </c>
       <c r="B370" s="7" t="inlineStr">
@@ -15509,17 +15509,17 @@
       </c>
       <c r="D370" s="9" t="inlineStr">
         <is>
-          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
+          <t>Bulk tick never UN-ticks</t>
         </is>
       </c>
       <c r="E370" s="9" t="inlineStr">
         <is>
-          <t>Select a repeating row along with others. Read the shelf.</t>
+          <t>Select a mix of done and not-done rows and tap Done.</t>
         </is>
       </c>
       <c r="F370" s="9" t="inlineStr">
         <is>
-          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
+          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
         </is>
       </c>
       <c r="G370" s="7" t="inlineStr">
@@ -15534,7 +15534,7 @@
     <row r="371">
       <c r="A371" s="6" t="inlineStr">
         <is>
-          <t>OUR-89</t>
+          <t>OUR-88</t>
         </is>
       </c>
       <c r="B371" s="7" t="inlineStr">
@@ -15542,24 +15542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C371" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C371" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D371" s="9" t="inlineStr">
         <is>
-          <t>The select shelf takes the capture bar's seat</t>
+          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
         </is>
       </c>
       <c r="E371" s="9" t="inlineStr">
         <is>
-          <t>Enter select mode in the room.</t>
+          <t>Select a repeating row along with others. Read the shelf.</t>
         </is>
       </c>
       <c r="F371" s="9" t="inlineStr">
         <is>
-          <t>The capture bar is gone while selecting, and back when you cancel. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
+          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
         </is>
       </c>
       <c r="G371" s="7" t="inlineStr">
@@ -15574,7 +15574,7 @@
     <row r="372">
       <c r="A372" s="6" t="inlineStr">
         <is>
-          <t>OUR-90</t>
+          <t>OUR-89</t>
         </is>
       </c>
       <c r="B372" s="7" t="inlineStr">
@@ -15582,24 +15582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C372" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C372" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D372" s="9" t="inlineStr">
         <is>
-          <t>No select mode on a closed list</t>
+          <t>The select shelf takes the capture bar's seat</t>
         </is>
       </c>
       <c r="E372" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list and hold a row.</t>
+          <t>Enter select mode in the room.</t>
         </is>
       </c>
       <c r="F372" s="9" t="inlineStr">
         <is>
-          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
+          <t>The capture bar is gone while selecting, and back when you cancel. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
         </is>
       </c>
       <c r="G372" s="7" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="373">
       <c r="A373" s="6" t="inlineStr">
         <is>
-          <t>OUR-91</t>
+          <t>OUR-90</t>
         </is>
       </c>
       <c r="B373" s="7" t="inlineStr">
@@ -15622,24 +15622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C373" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C373" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D373" s="9" t="inlineStr">
         <is>
-          <t>A copy says when its shared row was taken off the list</t>
+          <t>No select mode on a closed list</t>
         </is>
       </c>
       <c r="E373" s="9" t="inlineStr">
         <is>
-          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
+          <t>Open an archived list and hold a row.</t>
         </is>
       </c>
       <c r="F373" s="9" t="inlineStr">
         <is>
-          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
+          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
         </is>
       </c>
       <c r="G373" s="7" t="inlineStr">
@@ -15654,7 +15654,7 @@
     <row r="374">
       <c r="A374" s="6" t="inlineStr">
         <is>
-          <t>OUR-92</t>
+          <t>OUR-91</t>
         </is>
       </c>
       <c r="B374" s="7" t="inlineStr">
@@ -15669,17 +15669,17 @@
       </c>
       <c r="D374" s="9" t="inlineStr">
         <is>
-          <t>That line never says who, and never says why</t>
+          <t>A copy says when its shared row was taken off the list</t>
         </is>
       </c>
       <c r="E374" s="9" t="inlineStr">
         <is>
-          <t>Read the line closely.</t>
+          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
         </is>
       </c>
       <c r="F374" s="9" t="inlineStr">
         <is>
-          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
+          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
         </is>
       </c>
       <c r="G374" s="7" t="inlineStr">
@@ -15694,7 +15694,7 @@
     <row r="375">
       <c r="A375" s="6" t="inlineStr">
         <is>
-          <t>OUR-93</t>
+          <t>OUR-92</t>
         </is>
       </c>
       <c r="B375" s="7" t="inlineStr">
@@ -15702,24 +15702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C375" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C375" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D375" s="9" t="inlineStr">
         <is>
-          <t>No line on a copy you already finished or removed</t>
+          <t>That line never says who, and never says why</t>
         </is>
       </c>
       <c r="E375" s="9" t="inlineStr">
         <is>
-          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
+          <t>Read the line closely.</t>
         </is>
       </c>
       <c r="F375" s="9" t="inlineStr">
         <is>
-          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
+          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
         </is>
       </c>
       <c r="G375" s="7" t="inlineStr">
@@ -15734,7 +15734,7 @@
     <row r="376">
       <c r="A376" s="6" t="inlineStr">
         <is>
-          <t>OUR-94</t>
+          <t>OUR-93</t>
         </is>
       </c>
       <c r="B376" s="7" t="inlineStr">
@@ -15742,24 +15742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C376" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C376" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D376" s="9" t="inlineStr">
         <is>
-          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
+          <t>No line on a copy you already finished or removed</t>
         </is>
       </c>
       <c r="E376" s="9" t="inlineStr">
         <is>
-          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
+          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
         </is>
       </c>
       <c r="F376" s="9" t="inlineStr">
         <is>
-          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
+          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
         </is>
       </c>
       <c r="G376" s="7" t="inlineStr">
@@ -15774,7 +15774,7 @@
     <row r="377">
       <c r="A377" s="6" t="inlineStr">
         <is>
-          <t>OUR-95</t>
+          <t>OUR-94</t>
         </is>
       </c>
       <c r="B377" s="7" t="inlineStr">
@@ -15782,24 +15782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C377" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C377" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D377" s="9" t="inlineStr">
         <is>
-          <t>A row's note is VISIBLE, not only spoken</t>
+          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
         </is>
       </c>
       <c r="E377" s="9" t="inlineStr">
         <is>
-          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
+          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
         </is>
       </c>
       <c r="F377" s="9" t="inlineStr">
         <is>
-          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
+          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
         </is>
       </c>
       <c r="G377" s="7" t="inlineStr">
@@ -15814,7 +15814,7 @@
     <row r="378">
       <c r="A378" s="6" t="inlineStr">
         <is>
-          <t>OUR-96</t>
+          <t>OUR-95</t>
         </is>
       </c>
       <c r="B378" s="7" t="inlineStr">
@@ -15822,24 +15822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C378" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C378" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D378" s="9" t="inlineStr">
         <is>
-          <t>Rows WITHOUT a note are unchanged</t>
+          <t>A row's note is VISIBLE, not only spoken</t>
         </is>
       </c>
       <c r="E378" s="9" t="inlineStr">
         <is>
-          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
+          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
         </is>
       </c>
       <c r="F378" s="9" t="inlineStr">
         <is>
-          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
+          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
         </is>
       </c>
       <c r="G378" s="7" t="inlineStr">
@@ -15854,7 +15854,7 @@
     <row r="379">
       <c r="A379" s="6" t="inlineStr">
         <is>
-          <t>OUR-97</t>
+          <t>OUR-96</t>
         </is>
       </c>
       <c r="B379" s="7" t="inlineStr">
@@ -15862,24 +15862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C379" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C379" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D379" s="9" t="inlineStr">
         <is>
-          <t>A tick after midnight lands on the RIGHT day</t>
+          <t>Rows WITHOUT a note are unchanged</t>
         </is>
       </c>
       <c r="E379" s="9" t="inlineStr">
         <is>
-          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
+          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
         </is>
       </c>
       <c r="F379" s="9" t="inlineStr">
         <is>
-          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
+          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
         </is>
       </c>
       <c r="G379" s="7" t="inlineStr">
@@ -15894,7 +15894,7 @@
     <row r="380">
       <c r="A380" s="6" t="inlineStr">
         <is>
-          <t>OUR-98</t>
+          <t>OUR-97</t>
         </is>
       </c>
       <c r="B380" s="7" t="inlineStr">
@@ -15909,17 +15909,17 @@
       </c>
       <c r="D380" s="9" t="inlineStr">
         <is>
-          <t>A tick made during a background sync is not undone</t>
+          <t>A tick after midnight lands on the RIGHT day</t>
         </is>
       </c>
       <c r="E380" s="9" t="inlineStr">
         <is>
-          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
+          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
         </is>
       </c>
       <c r="F380" s="9" t="inlineStr">
         <is>
-          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
+          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
         </is>
       </c>
       <c r="G380" s="7" t="inlineStr">
@@ -15934,7 +15934,7 @@
     <row r="381">
       <c r="A381" s="6" t="inlineStr">
         <is>
-          <t>OUR-99</t>
+          <t>OUR-98</t>
         </is>
       </c>
       <c r="B381" s="7" t="inlineStr">
@@ -15949,17 +15949,17 @@
       </c>
       <c r="D381" s="9" t="inlineStr">
         <is>
-          <t>A tick survives a device that has never opened the room</t>
+          <t>A tick made during a background sync is not undone</t>
         </is>
       </c>
       <c r="E381" s="9" t="inlineStr">
         <is>
-          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
+          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F381" s="9" t="inlineStr">
         <is>
-          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
+          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
         </is>
       </c>
       <c r="G381" s="7" t="inlineStr">
@@ -15974,7 +15974,7 @@
     <row r="382">
       <c r="A382" s="6" t="inlineStr">
         <is>
-          <t>OUR-100</t>
+          <t>OUR-99</t>
         </is>
       </c>
       <c r="B382" s="7" t="inlineStr">
@@ -15989,17 +15989,17 @@
       </c>
       <c r="D382" s="9" t="inlineStr">
         <is>
-          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
+          <t>A tick survives a device that has never opened the room</t>
         </is>
       </c>
       <c r="E382" s="9" t="inlineStr">
         <is>
-          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
+          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
         </is>
       </c>
       <c r="F382" s="9" t="inlineStr">
         <is>
-          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
+          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
         </is>
       </c>
       <c r="G382" s="7" t="inlineStr">
@@ -16014,7 +16014,7 @@
     <row r="383">
       <c r="A383" s="6" t="inlineStr">
         <is>
-          <t>OUR-101</t>
+          <t>OUR-100</t>
         </is>
       </c>
       <c r="B383" s="7" t="inlineStr">
@@ -16022,24 +16022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C383" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C383" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D383" s="9" t="inlineStr">
         <is>
-          <t>A closed list stops promising it keeps trying</t>
+          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
         </is>
       </c>
       <c r="E383" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list that has unpushed local changes.</t>
+          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
         </is>
       </c>
       <c r="F383" s="9" t="inlineStr">
         <is>
-          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
+          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
         </is>
       </c>
       <c r="G383" s="7" t="inlineStr">
@@ -16054,7 +16054,7 @@
     <row r="384">
       <c r="A384" s="6" t="inlineStr">
         <is>
-          <t>OUR-102</t>
+          <t>OUR-101</t>
         </is>
       </c>
       <c r="B384" s="7" t="inlineStr">
@@ -16069,17 +16069,17 @@
       </c>
       <c r="D384" s="9" t="inlineStr">
         <is>
-          <t>Setting a rhythm clears any date the row was carrying</t>
+          <t>A closed list stops promising it keeps trying</t>
         </is>
       </c>
       <c r="E384" s="9" t="inlineStr">
         <is>
-          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
+          <t>Open an archived list that has unpushed local changes.</t>
         </is>
       </c>
       <c r="F384" s="9" t="inlineStr">
         <is>
-          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
+          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
         </is>
       </c>
       <c r="G384" s="7" t="inlineStr">
@@ -16094,7 +16094,7 @@
     <row r="385">
       <c r="A385" s="6" t="inlineStr">
         <is>
-          <t>OUR-103</t>
+          <t>OUR-102</t>
         </is>
       </c>
       <c r="B385" s="7" t="inlineStr">
@@ -16109,17 +16109,17 @@
       </c>
       <c r="D385" s="9" t="inlineStr">
         <is>
-          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
+          <t>Setting a rhythm clears any date the row was carrying</t>
         </is>
       </c>
       <c r="E385" s="9" t="inlineStr">
         <is>
-          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
+          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
         </is>
       </c>
       <c r="F385" s="9" t="inlineStr">
         <is>
-          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
+          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
         </is>
       </c>
       <c r="G385" s="7" t="inlineStr">
@@ -16134,7 +16134,7 @@
     <row r="386">
       <c r="A386" s="6" t="inlineStr">
         <is>
-          <t>OUR-104</t>
+          <t>OUR-103</t>
         </is>
       </c>
       <c r="B386" s="7" t="inlineStr">
@@ -16142,24 +16142,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C386" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C386" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D386" s="9" t="inlineStr">
         <is>
-          <t>No dead reorder rail on shared rows</t>
+          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
         </is>
       </c>
       <c r="E386" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the room and in the From Ours strip.</t>
+          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
         </is>
       </c>
       <c r="F386" s="9" t="inlineStr">
         <is>
-          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
+          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
         </is>
       </c>
       <c r="G386" s="7" t="inlineStr">
@@ -16174,7 +16174,7 @@
     <row r="387">
       <c r="A387" s="6" t="inlineStr">
         <is>
-          <t>OUR-105</t>
+          <t>OUR-104</t>
         </is>
       </c>
       <c r="B387" s="7" t="inlineStr">
@@ -16182,24 +16182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C387" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C387" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D387" s="9" t="inlineStr">
         <is>
-          <t>First run introduces the shared list</t>
+          <t>No dead reorder rail on shared rows</t>
         </is>
       </c>
       <c r="E387" s="9" t="inlineStr">
         <is>
-          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
+          <t>Hold a row in the room and in the From Ours strip.</t>
         </is>
       </c>
       <c r="F387" s="9" t="inlineStr">
         <is>
-          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
+          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
         </is>
       </c>
       <c r="G387" s="7" t="inlineStr">
@@ -16214,7 +16214,7 @@
     <row r="388">
       <c r="A388" s="6" t="inlineStr">
         <is>
-          <t>OUR-106</t>
+          <t>OUR-105</t>
         </is>
       </c>
       <c r="B388" s="7" t="inlineStr">
@@ -16229,17 +16229,17 @@
       </c>
       <c r="D388" s="9" t="inlineStr">
         <is>
-          <t>Anyone can start a shared list, not just an allowlisted address</t>
+          <t>First run introduces the shared list</t>
         </is>
       </c>
       <c r="E388" s="9" t="inlineStr">
         <is>
-          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
+          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
         </is>
       </c>
       <c r="F388" s="9" t="inlineStr">
         <is>
-          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
+          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
         </is>
       </c>
       <c r="G388" s="7" t="inlineStr">
@@ -16254,7 +16254,7 @@
     <row r="389">
       <c r="A389" s="6" t="inlineStr">
         <is>
-          <t>OUR-107</t>
+          <t>OUR-106</t>
         </is>
       </c>
       <c r="B389" s="7" t="inlineStr">
@@ -16269,17 +16269,17 @@
       </c>
       <c r="D389" s="9" t="inlineStr">
         <is>
-          <t>The shared-list onboarding step can actually be REACHED</t>
+          <t>Anyone can start a shared list, not just an allowlisted address</t>
         </is>
       </c>
       <c r="E389" s="9" t="inlineStr">
         <is>
-          <t>Replay the first run and press the primary button through every step without skipping.</t>
+          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
         </is>
       </c>
       <c r="F389" s="9" t="inlineStr">
         <is>
-          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
+          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
         </is>
       </c>
       <c r="G389" s="7" t="inlineStr">
@@ -16294,7 +16294,7 @@
     <row r="390">
       <c r="A390" s="6" t="inlineStr">
         <is>
-          <t>OUR-108</t>
+          <t>OUR-107</t>
         </is>
       </c>
       <c r="B390" s="7" t="inlineStr">
@@ -16302,24 +16302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C390" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C390" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D390" s="9" t="inlineStr">
         <is>
-          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
+          <t>The shared-list onboarding step can actually be REACHED</t>
         </is>
       </c>
       <c r="E390" s="9" t="inlineStr">
         <is>
-          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
+          <t>Replay the first run and press the primary button through every step without skipping.</t>
         </is>
       </c>
       <c r="F390" s="9" t="inlineStr">
         <is>
-          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
+          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
         </is>
       </c>
       <c r="G390" s="7" t="inlineStr">
@@ -16334,7 +16334,7 @@
     <row r="391">
       <c r="A391" s="6" t="inlineStr">
         <is>
-          <t>OUR-109</t>
+          <t>OUR-108</t>
         </is>
       </c>
       <c r="B391" s="7" t="inlineStr">
@@ -16342,24 +16342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C391" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C391" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D391" s="9" t="inlineStr">
         <is>
-          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
+          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
         </is>
       </c>
       <c r="E391" s="9" t="inlineStr">
         <is>
-          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
+          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
         </is>
       </c>
       <c r="F391" s="9" t="inlineStr">
         <is>
-          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
+          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
         </is>
       </c>
       <c r="G391" s="7" t="inlineStr">
@@ -16374,7 +16374,7 @@
     <row r="392">
       <c r="A392" s="6" t="inlineStr">
         <is>
-          <t>OUR-110</t>
+          <t>OUR-109</t>
         </is>
       </c>
       <c r="B392" s="7" t="inlineStr">
@@ -16389,17 +16389,17 @@
       </c>
       <c r="D392" s="9" t="inlineStr">
         <is>
-          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
+          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
         </is>
       </c>
       <c r="E392" s="9" t="inlineStr">
         <is>
-          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
+          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
         </is>
       </c>
       <c r="F392" s="9" t="inlineStr">
         <is>
-          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
+          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
         </is>
       </c>
       <c r="G392" s="7" t="inlineStr">
@@ -16414,12 +16414,12 @@
     <row r="393">
       <c r="A393" s="6" t="inlineStr">
         <is>
-          <t>UPD-01</t>
+          <t>OUR-110</t>
         </is>
       </c>
       <c r="B393" s="7" t="inlineStr">
         <is>
-          <t>Updates</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C393" s="8" t="inlineStr">
@@ -16429,17 +16429,17 @@
       </c>
       <c r="D393" s="9" t="inlineStr">
         <is>
-          <t>Settings states the version, and up-to-date is a fact</t>
+          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
         </is>
       </c>
       <c r="E393" s="9" t="inlineStr">
         <is>
-          <t>Open Settings and scroll to the foot.</t>
+          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
         </is>
       </c>
       <c r="F393" s="9" t="inlineStr">
         <is>
-          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
+          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
         </is>
       </c>
       <c r="G393" s="7" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="394">
       <c r="A394" s="6" t="inlineStr">
         <is>
-          <t>UPD-02</t>
+          <t>UPD-01</t>
         </is>
       </c>
       <c r="B394" s="7" t="inlineStr">
@@ -16469,22 +16469,22 @@
       </c>
       <c r="D394" s="9" t="inlineStr">
         <is>
-          <t>Web offers a reload, and says drafts are kept</t>
+          <t>Settings states the version, and up-to-date is a fact</t>
         </is>
       </c>
       <c r="E394" s="9" t="inlineStr">
         <is>
-          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
+          <t>Open Settings and scroll to the foot.</t>
         </is>
       </c>
       <c r="F394" s="9" t="inlineStr">
         <is>
-          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
+          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
         </is>
       </c>
       <c r="G394" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H394" s="7" t="inlineStr"/>
@@ -16494,7 +16494,7 @@
     <row r="395">
       <c r="A395" s="6" t="inlineStr">
         <is>
-          <t>UPD-03</t>
+          <t>UPD-02</t>
         </is>
       </c>
       <c r="B395" s="7" t="inlineStr">
@@ -16509,22 +16509,22 @@
       </c>
       <c r="D395" s="9" t="inlineStr">
         <is>
-          <t>Native points at the store, and says lists are untouched</t>
+          <t>Web offers a reload, and says drafts are kept</t>
         </is>
       </c>
       <c r="E395" s="9" t="inlineStr">
         <is>
-          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
+          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
         </is>
       </c>
       <c r="F395" s="9" t="inlineStr">
         <is>
-          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
+          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
         </is>
       </c>
       <c r="G395" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H395" s="7" t="inlineStr"/>
@@ -16534,7 +16534,7 @@
     <row r="396">
       <c r="A396" s="6" t="inlineStr">
         <is>
-          <t>UPD-04</t>
+          <t>UPD-03</t>
         </is>
       </c>
       <c r="B396" s="7" t="inlineStr">
@@ -16542,29 +16542,29 @@
           <t>Updates</t>
         </is>
       </c>
-      <c r="C396" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C396" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D396" s="9" t="inlineStr">
         <is>
-          <t>Unreachable server says NOTHING, never 'up to date'</t>
+          <t>Native points at the store, and says lists are untouched</t>
         </is>
       </c>
       <c r="E396" s="9" t="inlineStr">
         <is>
-          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
+          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
         </is>
       </c>
       <c r="F396" s="9" t="inlineStr">
         <is>
-          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
+          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
         </is>
       </c>
       <c r="G396" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H396" s="7" t="inlineStr"/>
@@ -16574,7 +16574,7 @@
     <row r="397">
       <c r="A397" s="6" t="inlineStr">
         <is>
-          <t>UPD-05</t>
+          <t>UPD-04</t>
         </is>
       </c>
       <c r="B397" s="7" t="inlineStr">
@@ -16589,17 +16589,17 @@
       </c>
       <c r="D397" s="9" t="inlineStr">
         <is>
-          <t>The goodnight mention is rare, and framed for the other person</t>
+          <t>Unreachable server says NOTHING, never 'up to date'</t>
         </is>
       </c>
       <c r="E397" s="9" t="inlineStr">
         <is>
-          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
+          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
         </is>
       </c>
       <c r="F397" s="9" t="inlineStr">
         <is>
-          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
+          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
         </is>
       </c>
       <c r="G397" s="7" t="inlineStr">
@@ -16614,32 +16614,32 @@
     <row r="398">
       <c r="A398" s="6" t="inlineStr">
         <is>
-          <t>OUR-12</t>
+          <t>UPD-05</t>
         </is>
       </c>
       <c r="B398" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C398" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="C398" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D398" s="9" t="inlineStr">
         <is>
-          <t>Unnamed lists read in each person's language</t>
+          <t>The goodnight mention is rare, and framed for the other person</t>
         </is>
       </c>
       <c r="E398" s="9" t="inlineStr">
         <is>
-          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
         </is>
       </c>
       <c r="F398" s="9" t="inlineStr">
         <is>
-          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
         </is>
       </c>
       <c r="G398" s="7" t="inlineStr">
@@ -16651,9 +16651,49 @@
       <c r="I398" s="9" t="inlineStr"/>
       <c r="J398" s="7" t="inlineStr"/>
     </row>
+    <row r="399">
+      <c r="A399" s="6" t="inlineStr">
+        <is>
+          <t>OUR-12</t>
+        </is>
+      </c>
+      <c r="B399" s="7" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="C399" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D399" s="9" t="inlineStr">
+        <is>
+          <t>Unnamed lists read in each person's language</t>
+        </is>
+      </c>
+      <c r="E399" s="9" t="inlineStr">
+        <is>
+          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+        </is>
+      </c>
+      <c r="F399" s="9" t="inlineStr">
+        <is>
+          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+        </is>
+      </c>
+      <c r="G399" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H399" s="7" t="inlineStr"/>
+      <c r="I399" s="9" t="inlineStr"/>
+      <c r="J399" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J398"/>
-  <conditionalFormatting sqref="H2:H398">
+  <autoFilter ref="A1:J399"/>
+  <conditionalFormatting sqref="H2:H399">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -16665,7 +16705,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H398" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
+    <dataValidation sqref="H2:H399" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
       <formula1>"Pass,Fail,Blocked,Not run"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16701,7 +16741,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>398</t>
         </is>
       </c>
     </row>
@@ -16712,7 +16752,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF('Test Suite'!$H$2:$H$398,"Pass")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$399,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -16723,7 +16763,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF('Test Suite'!$H$2:$H$398,"Fail")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$399,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -16734,7 +16774,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Suite'!$H$2:$H$398,"Blocked")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$399,"Blocked")</f>
         <v/>
       </c>
     </row>
@@ -16745,7 +16785,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Suite'!$H$2:$H$398,"Not run")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$399,"Not run")</f>
         <v/>
       </c>
     </row>
@@ -16756,7 +16796,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>397-COUNTA('Test Suite'!$H$2:$H$398)</f>
+        <f>398-COUNTA('Test Suite'!$H$2:$H$399)</f>
         <v/>
       </c>
     </row>
@@ -16767,7 +16807,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF('Test Suite'!$C$2:$C$398,"P1")</f>
+        <f>COUNTIF('Test Suite'!$C$2:$C$399,"P1")</f>
         <v/>
       </c>
     </row>
@@ -16778,7 +16818,7 @@
         </is>
       </c>
       <c r="B10">
-        <f>COUNTIFS('Test Suite'!$C$2:$C$398,"P1",'Test Suite'!$H$2:$H$398,"Pass")</f>
+        <f>COUNTIFS('Test Suite'!$C$2:$C$399,"P1",'Test Suite'!$H$2:$H$399,"Pass")</f>
         <v/>
       </c>
     </row>

--- a/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
+++ b/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$400</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$402</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J400"/>
+  <dimension ref="A1:J402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="F145" s="9" t="inlineStr">
         <is>
-          <t>Returns your open tasks, each with an id. Repeating tasks due today appear once and drop after you tick or skip them.</t>
+          <t>Returns your open tasks, each with an id. A repeating task due today appears once, marked (repeats), and drops after you tick or skip it. Today here is the UTC calendar day, so before about 10am AEST it can still be yesterday's (known; a timezone option is planned).</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
@@ -6561,17 +6561,17 @@
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>complete_task</t>
+          <t>complete_task on a one-off</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>Ask the agent to complete one of the listed tasks by id.</t>
+          <t>Ask the agent to complete one of the listed ONE-OFF tasks by id.</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>Marked done; reflects in the app after sync.</t>
+          <t>'Marked it done. Nice.'; it reads as done in the app after the next sync (cold open).</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
@@ -6586,7 +6586,7 @@
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>MCP-10</t>
+          <t>MCP-18</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>add_task with a future due date</t>
+          <t>complete_task on a REPEATING task ticks one day, never closes it</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>Ask the agent: add 'call the plumber' for next Tuesday. PREREQ: MCP-01.</t>
+          <t>With a daily repeat on Today (it shows as (repeats) in list_today): ask the agent to complete it. Ask again. Then open the app (cold), check Today, the Repeating drawer and the Lookback. Then ask the agent to complete it for today's LOCAL date (say the date).</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr">
         <is>
-          <t>The task is created dated (not on Today). It surfaces on that day, and appears in list_upcoming. Confirmation names the date. Sending both a due date and a repeat is refused calmly.</t>
+          <t>First: 'Ticked for &lt;date&gt;. It repeats, so it will be back on its next day.' Second: 'Already ticked for &lt;date&gt;...'. In the app the task is still in the Repeating drawer, comes back on its next day, and the tick shows on &lt;date&gt; in the Lookback. Before about 10am AEST &lt;date&gt; is YESTERDAY's (the UTC day, named in the answer, known); the agent passing `day` with the local date lands it on today. It never ends the series: the repeat is still there tomorrow.</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>MCP-11</t>
+          <t>MCP-19</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
@@ -6634,24 +6634,24 @@
           <t>MCP</t>
         </is>
       </c>
-      <c r="C148" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>add_task repeating</t>
+          <t>update_task done:false un-ticks on the server only</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>Ask the agent: add 'water the plants' every 2 days (and separately, 'standup' every weekday). PREREQ: MCP-01.</t>
+          <t>After MCP-18, on a phone that has already synced the tick: ask the agent to un-tick the repeat (update_task done: false). Then open the phone.</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>A repeating task is created (interval / weekly). It appears on the right days in the app and in list_today when due. A malformed repeat (e.g. weekly with no weekdays) returns a calm error, never a crash.</t>
+          <t>The agent's answer says it un-ticked &lt;date&gt; on the server AND that a device that already synced the tick will bring it back. The phone does exactly that on its next open (ticks are kept on purpose). Nothing is lost, nothing shames.</t>
         </is>
       </c>
       <c r="G148" s="7" t="inlineStr">
@@ -6666,7 +6666,7 @@
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>MCP-12</t>
+          <t>MCP-10</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
@@ -6681,17 +6681,17 @@
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>list_upcoming look-ahead</t>
+          <t>add_task with a future due date</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>Ask the agent: what's coming up this week? Then: next 14 days. PREREQ: at least one future-dated and one repeating task.</t>
+          <t>Ask the agent: add 'call the plumber' for next Tuesday. PREREQ: MCP-01.</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr">
         <is>
-          <t>Lists future one-offs by date AND each repeat's next occurrence, in date order, each with an id. Window clamps to 1..30 days (default 7). A repeat already done for its next hit shows the following occurrence.</t>
+          <t>The task is created dated (not on Today). It surfaces on that day, and appears in list_upcoming. Confirmation names the date. Sending both a due date and a repeat is refused calmly.</t>
         </is>
       </c>
       <c r="G149" s="7" t="inlineStr">
@@ -6706,7 +6706,7 @@
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>MCP-13</t>
+          <t>MCP-11</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
@@ -6721,17 +6721,17 @@
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>update_task edits</t>
+          <t>add_task repeating</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>Ask the agent to rename a task, then to move its due date, then to make it repeat daily. PREREQ: MCP-01.</t>
+          <t>Ask the agent: add 'water the plants' every 2 days (and separately, 'standup' every weekday). PREREQ: MCP-01.</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>Each change reflects in the app after sync. Setting a due date clears any repeat and vice versa. An update with nothing to change is refused calmly. Editing a missing id says so.</t>
+          <t>A repeating task is created (interval / weekly). It appears on the right days in the app and in list_today when due. A malformed repeat (e.g. weekly with no weekdays) returns a calm error, never a crash.</t>
         </is>
       </c>
       <c r="G150" s="7" t="inlineStr">
@@ -6746,7 +6746,7 @@
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>MCP-14</t>
+          <t>MCP-12</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
@@ -6761,17 +6761,17 @@
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>delete_task is a recoverable tombstone</t>
+          <t>list_upcoming look-ahead</t>
         </is>
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>Ask the agent to remove a task by id. PREREQ: MCP-01.</t>
+          <t>Ask the agent: what's coming up this week? Then: next 14 days. PREREQ: at least one future-dated and one repeating task.</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr">
         <is>
-          <t>The task disappears from the app (hidden), confirmed 'Removed.' It is soft-deleted (deleted_at set), never hard-deleted; the tombstone syncs across devices.</t>
+          <t>Lists future one-offs by date AND each repeat's next occurrence, in date order, each with an id. Window clamps to 1..30 days (default 7). A repeat already done for its next hit shows the following occurrence.</t>
         </is>
       </c>
       <c r="G151" s="7" t="inlineStr">
@@ -6786,7 +6786,7 @@
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>MCP-15</t>
+          <t>MCP-13</t>
         </is>
       </c>
       <c r="B152" s="7" t="inlineStr">
@@ -6801,17 +6801,17 @@
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>break_down proposes, never adds (propose-then-accept)</t>
+          <t>update_task edits</t>
         </is>
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>Ask the agent to break down a dreaded task (e.g. 'do my tax'). Read the steps. Then say 'yes, add them'. PREREQ: MCP-01.</t>
+          <t>Ask the agent to rename a task, then to move its due date, then to make it repeat daily. PREREQ: MCP-01.</t>
         </is>
       </c>
       <c r="F152" s="9" t="inlineStr">
         <is>
-          <t>break_down returns small, ordered, time-boxed steps and adds NOTHING (it reminds you nothing was added yet). Only after you agree does the agent call add_task per step and they appear in the app. Steps read calm, no shame, no exclamation marks.</t>
+          <t>Each change reflects in the app after sync. Setting a due date clears any repeat and vice versa. An update with nothing to change is refused calmly. Editing a missing id says so.</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr">
@@ -6826,7 +6826,7 @@
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>MCP-16</t>
+          <t>MCP-14</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
@@ -6834,24 +6834,24 @@
           <t>MCP</t>
         </is>
       </c>
-      <c r="C153" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>break_down per-user hourly cap</t>
+          <t>delete_task is a recoverable tombstone</t>
         </is>
       </c>
       <c r="E153" s="9" t="inlineStr">
         <is>
-          <t>In a loop, ask the agent to break down tasks more than ~20 times within an hour. PREREQ: MCP-01.</t>
+          <t>Ask the agent to remove a task by id. PREREQ: MCP-01.</t>
         </is>
       </c>
       <c r="F153" s="9" t="inlineStr">
         <is>
-          <t>After the cap, break_down returns a calm 'Let's pause breaking things down for a bit' with NO AI spend, and recovers on its own the next hour. Other tools keep working throughout.</t>
+          <t>The task disappears from the app (hidden), confirmed 'Removed.' It is soft-deleted (deleted_at set), never hard-deleted; the tombstone syncs across devices.</t>
         </is>
       </c>
       <c r="G153" s="7" t="inlineStr">
@@ -6866,7 +6866,7 @@
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>MCP-17</t>
+          <t>MCP-15</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
@@ -6874,29 +6874,29 @@
           <t>MCP</t>
         </is>
       </c>
-      <c r="C154" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C154" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>ChatGPT Deep Research (search + fetch)</t>
+          <t>break_down proposes, never adds (propose-then-accept)</t>
         </is>
       </c>
       <c r="E154" s="9" t="inlineStr">
         <is>
-          <t>Connect the DoubleDone connector to ChatGPT Deep Research (OAuth, MCP-07). Run a research prompt that references your tasks, e.g. 'summarise what's open in my DoubleDone about the move'.</t>
+          <t>Ask the agent to break down a dreaded task (e.g. 'do my tax'). Read the steps. Then say 'yes, add them'. PREREQ: MCP-01.</t>
         </is>
       </c>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>Deep Research calls search then fetch under the hood. search returns matching open tasks (by keyword, case-insensitive); fetch returns one task's detail. Results are read-only (nothing changes) and cite doubledone.app.</t>
+          <t>break_down returns small, ordered, time-boxed steps and adds NOTHING (it reminds you nothing was added yet). Only after you agree does the agent call add_task per step and they appear in the app. Steps read calm, no shame, no exclamation marks.</t>
         </is>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>OAuth</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="H154" s="7" t="inlineStr"/>
@@ -6906,12 +6906,12 @@
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>API-01</t>
+          <t>MCP-16</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>REST API</t>
+          <t>MCP</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
@@ -6921,22 +6921,22 @@
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>Create a repeating task via POST /tasks</t>
+          <t>break_down per-user hourly cap</t>
         </is>
       </c>
       <c r="E155" s="9" t="inlineStr">
         <is>
-          <t>In the Swagger UI (/api/v1/docs) or curl, POST /tasks with { title, repeat: { kind: 'weekly', weekdays: [1,3,5] } } and a bearer token.</t>
+          <t>In a loop, ask the agent to break down tasks more than ~20 times within an hour. PREREQ: MCP-01.</t>
         </is>
       </c>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>201 with the task carrying a normalised recurrence object + a 'repeats' summary ('Mon, Wed, Fri'), no due. Sending both due and repeat returns a calm 400, never a 500. An app-made and API-made repeat behave identically (shared cadence engine).</t>
+          <t>After the cap, break_down returns a calm 'Let's pause breaking things down for a bit' with NO AI spend, and recovers on its own the next hour. Other tools keep working throughout.</t>
         </is>
       </c>
       <c r="G155" s="7" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="H155" s="7" t="inlineStr"/>
@@ -6946,12 +6946,12 @@
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>API-02</t>
+          <t>MCP-17</t>
         </is>
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t>REST API</t>
+          <t>MCP</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
@@ -6961,22 +6961,22 @@
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>Search and look-ahead query modes on GET /tasks</t>
+          <t>ChatGPT Deep Research (search + fetch)</t>
         </is>
       </c>
       <c r="E156" s="9" t="inlineStr">
         <is>
-          <t>GET /tasks?q=dentist (substring search) and GET /tasks?upcoming=7 (next 7 days), with a bearer token.</t>
+          <t>Connect the DoubleDone connector to ChatGPT Deep Research (OAuth, MCP-07). Run a research prompt that references your tasks, e.g. 'summarise what's open in my DoubleDone about the move'.</t>
         </is>
       </c>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>?q returns open tasks whose title matches (case-insensitive, open tasks only). ?upcoming returns future one-offs plus each repeat's next occurrence within the window (future only; today is /tasks?today). Precedence q &gt; upcoming &gt; today.</t>
+          <t>Deep Research calls search then fetch under the hood. search returns matching open tasks (by keyword, case-insensitive); fetch returns one task's detail. Results are read-only (nothing changes) and cite doubledone.app.</t>
         </is>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>OAuth</t>
         </is>
       </c>
       <c r="H156" s="7" t="inlineStr"/>
@@ -6986,7 +6986,7 @@
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>API-03</t>
+          <t>API-01</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
@@ -7001,17 +7001,17 @@
       </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
-          <t>OpenAPI spec + Swagger UI current at 1.1.0</t>
+          <t>Create a repeating task via POST /tasks</t>
         </is>
       </c>
       <c r="E157" s="9" t="inlineStr">
         <is>
-          <t>Open https://api.doubledone.app/api/v1/docs and GET /api/v1/openapi.json.</t>
+          <t>In the Swagger UI (/api/v1/docs) or curl, POST /tasks with { title, repeat: { kind: 'weekly', weekdays: [1,3,5] } } and a bearer token.</t>
         </is>
       </c>
       <c r="F157" s="9" t="inlineStr">
         <is>
-          <t>Swagger UI loads; the spec is version 1.1.0 and documents recurrence in the task shape, the Repeat input, and the ?q/?upcoming/?today query params.</t>
+          <t>201 with the task carrying a normalised recurrence object + a 'repeats' summary ('Mon, Wed, Fri'), no due. Sending both due and repeat returns a calm 400, never a 500. An app-made and API-made repeat behave identically (shared cadence engine).</t>
         </is>
       </c>
       <c r="G157" s="7" t="inlineStr">
@@ -7026,37 +7026,37 @@
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>MCP-07</t>
+          <t>API-02</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>MCP</t>
-        </is>
-      </c>
-      <c r="C158" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>REST API</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>Connect by URL (OAuth) from claude.ai / ChatGPT</t>
+          <t>Search and look-ahead query modes on GET /tasks</t>
         </is>
       </c>
       <c r="E158" s="9" t="inlineStr">
         <is>
-          <t>In claude.ai/Cowork: Settings -&gt; Connectors -&gt; Add custom connector, URL https://api.doubledone.app/mcp. In ChatGPT: Developer mode -&gt; add connector, same URL, OAuth. Complete the DoubleDone sign-in: email -&gt; 6-digit code -&gt; Allow. Then ask the agent to add and list tasks.</t>
+          <t>GET /tasks?q=dentist (substring search) and GET /tasks?upcoming=7 (next 7 days), with a bearer token.</t>
         </is>
       </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>A DoubleDone sign-in page appears (warm paper, brand). Existing accounts only (an unknown email never receives a code). The consent screen names what the connector may do AND the host access is sent to. After Allow, add_task/list_today/complete_task work against your rows; the connection persists without re-pasting a token.</t>
+          <t>?q returns open tasks whose title matches (case-insensitive, open tasks only). ?upcoming returns future one-offs plus each repeat's next occurrence within the window (future only; today is /tasks?today). Precedence q &gt; upcoming &gt; today.</t>
         </is>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>OAuth</t>
+          <t>API</t>
         </is>
       </c>
       <c r="H158" s="7" t="inlineStr"/>
@@ -7066,37 +7066,37 @@
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>MCP-08</t>
+          <t>API-03</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>MCP</t>
-        </is>
-      </c>
-      <c r="C159" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>REST API</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>Disconnect AI connectors (immediate kill switch)</t>
+          <t>OpenAPI spec + Swagger UI current at 1.1.0</t>
         </is>
       </c>
       <c r="E159" s="9" t="inlineStr">
         <is>
-          <t>With a URL-connected agent active, in the app go Settings -&gt; AI agent access (MCP) -&gt; Disconnect AI connectors. Then have the agent try a tool.</t>
+          <t>Open https://api.doubledone.app/api/v1/docs and GET /api/v1/openapi.json.</t>
         </is>
       </c>
       <c r="F159" s="9" t="inlineStr">
         <is>
-          <t>The app confirms 'Disconnected. Any connected agent must sign in again.' The very next tool call from the connector fails (must re-authorise); no ~1h lag. The pasted-token path is unaffected (it expires on its own).</t>
+          <t>Swagger UI loads; the spec is version 1.1.0 and documents recurrence in the task shape, the Repeat input, and the ?q/?upcoming/?today query params.</t>
         </is>
       </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>OAuth</t>
+          <t>API</t>
         </is>
       </c>
       <c r="H159" s="7" t="inlineStr"/>
@@ -7106,7 +7106,7 @@
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>MCP-09</t>
+          <t>MCP-07</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
@@ -7114,24 +7114,24 @@
           <t>MCP</t>
         </is>
       </c>
-      <c r="C160" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C160" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>PKCE is required (OAuth 2.1)</t>
+          <t>Connect by URL (OAuth) from claude.ai / ChatGPT</t>
         </is>
       </c>
       <c r="E160" s="9" t="inlineStr">
         <is>
-          <t>Drive /authorize with a registered client but WITHOUT a code_challenge (or with method=plain), e.g. via a crafted URL or the MCP Inspector.</t>
+          <t>In claude.ai/Cowork: Settings -&gt; Connectors -&gt; Add custom connector, URL https://api.doubledone.app/mcp. In ChatGPT: Developer mode -&gt; add connector, same URL, OAuth. Complete the DoubleDone sign-in: email -&gt; 6-digit code -&gt; Allow. Then ask the agent to add and list tasks.</t>
         </is>
       </c>
       <c r="F160" s="9" t="inlineStr">
         <is>
-          <t>The request is rejected (invalid_request) before any sign-in UI or session is minted. Only S256 PKCE flows proceed. No grant is created.</t>
+          <t>A DoubleDone sign-in page appears (warm paper, brand). Existing accounts only (an unknown email never receives a code). The consent screen names what the connector may do AND the host access is sent to. After Allow, add_task/list_today/complete_task work against your rows; the connection persists without re-pasting a token.</t>
         </is>
       </c>
       <c r="G160" s="7" t="inlineStr">
@@ -7146,7 +7146,7 @@
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>MCP-05</t>
+          <t>MCP-08</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
@@ -7154,29 +7154,29 @@
           <t>MCP</t>
         </is>
       </c>
-      <c r="C161" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>No-token gate</t>
+          <t>Disconnect AI connectors (immediate kill switch)</t>
         </is>
       </c>
       <c r="E161" s="9" t="inlineStr">
         <is>
-          <t>In the MCP Inspector, call a tool WITHOUT the Authorization header.</t>
+          <t>With a URL-connected agent active, in the app go Settings -&gt; AI agent access (MCP) -&gt; Disconnect AI connectors. Then have the agent try a tool.</t>
         </is>
       </c>
       <c r="F161" s="9" t="inlineStr">
         <is>
-          <t>Calm 'Not connected' result (isError). Nothing in your account changes.</t>
+          <t>The app confirms 'Disconnected. Any connected agent must sign in again.' The very next tool call from the connector fails (must re-authorise); no ~1h lag. The pasted-token path is unaffected (it expires on its own).</t>
         </is>
       </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>Inspector</t>
+          <t>OAuth</t>
         </is>
       </c>
       <c r="H161" s="7" t="inlineStr"/>
@@ -7186,7 +7186,7 @@
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>MCP-06</t>
+          <t>MCP-09</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
@@ -7201,22 +7201,22 @@
       </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>Expired token re-copy</t>
+          <t>PKCE is required (OAuth 2.1)</t>
         </is>
       </c>
       <c r="E162" s="9" t="inlineStr">
         <is>
-          <t>Use a token older than ~1 hour, then re-copy a fresh one.</t>
+          <t>Drive /authorize with a registered client but WITHOUT a code_challenge (or with method=plain), e.g. via a crafted URL or the MCP Inspector.</t>
         </is>
       </c>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>Stale token fails cleanly; fresh token works. No data exposed.</t>
+          <t>The request is rejected (invalid_request) before any sign-in UI or session is minted. Only S256 PKCE flows proceed. No grant is created.</t>
         </is>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>OAuth</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr"/>
@@ -7226,37 +7226,37 @@
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>SET-01</t>
+          <t>MCP-05</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="C163" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>Theme light / dark / system</t>
+          <t>No-token gate</t>
         </is>
       </c>
       <c r="E163" s="9" t="inlineStr">
         <is>
-          <t>Switch theme between Light, Dark, and System.</t>
+          <t>In the MCP Inspector, call a tool WITHOUT the Authorization header.</t>
         </is>
       </c>
       <c r="F163" s="9" t="inlineStr">
         <is>
-          <t>Applies immediately. Dusk palette correct in both; System follows the OS.</t>
+          <t>Calm 'Not connected' result (isError). Nothing in your account changes.</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Inspector</t>
         </is>
       </c>
       <c r="H163" s="7" t="inlineStr"/>
@@ -7266,12 +7266,12 @@
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>SET-02</t>
+          <t>MCP-06</t>
         </is>
       </c>
       <c r="B164" s="7" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>MCP</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
@@ -7281,22 +7281,22 @@
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>Text size small / default / large</t>
+          <t>Expired token re-copy</t>
         </is>
       </c>
       <c r="E164" s="9" t="inlineStr">
         <is>
-          <t>Change text size across all three.</t>
+          <t>Use a token older than ~1 hour, then re-copy a fresh one.</t>
         </is>
       </c>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>App scales. No clipping or broken layout at large.</t>
+          <t>Stale token fails cleanly; fresh token works. No data exposed.</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="H164" s="7" t="inlineStr"/>
@@ -7306,7 +7306,7 @@
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>SET-03</t>
+          <t>SET-01</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
@@ -7314,24 +7314,24 @@
           <t>Settings</t>
         </is>
       </c>
-      <c r="C165" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
-          <t>Motion -&gt; Reduce</t>
+          <t>Theme light / dark / system</t>
         </is>
       </c>
       <c r="E165" s="9" t="inlineStr">
         <is>
-          <t>Set Motion to Reduce.</t>
+          <t>Switch theme between Light, Dark, and System.</t>
         </is>
       </c>
       <c r="F165" s="9" t="inlineStr">
         <is>
-          <t>Gentle fades and scrolling titles stop.</t>
+          <t>Applies immediately. Dusk palette correct in both; System follows the OS.</t>
         </is>
       </c>
       <c r="G165" s="7" t="inlineStr">
@@ -7346,7 +7346,7 @@
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>SET-04</t>
+          <t>SET-02</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
@@ -7361,17 +7361,17 @@
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>Privacy &amp; data link</t>
+          <t>Text size small / default / large</t>
         </is>
       </c>
       <c r="E166" s="9" t="inlineStr">
         <is>
-          <t>Tap 'Privacy &amp; data' in Settings.</t>
+          <t>Change text size across all three.</t>
         </is>
       </c>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>Opens the privacy screen.</t>
+          <t>App scales. No clipping or broken layout at large.</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
@@ -7386,7 +7386,7 @@
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>SET-05</t>
+          <t>SET-03</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
@@ -7401,17 +7401,17 @@
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>Export your data</t>
+          <t>Motion -&gt; Reduce</t>
         </is>
       </c>
       <c r="E167" s="9" t="inlineStr">
         <is>
-          <t>In Settings -&gt; Your data, tap 'Export your data' (works with no account).</t>
+          <t>Set Motion to Reduce.</t>
         </is>
       </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>Web downloads a doubledone-export-&lt;date&gt;.json with your tasks + completions; native opens the share sheet. Tombstones excluded, completion data kept.</t>
+          <t>Gentle fades and scrolling titles stop.</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr">
@@ -7426,7 +7426,7 @@
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>SET-06</t>
+          <t>SET-04</t>
         </is>
       </c>
       <c r="B168" s="7" t="inlineStr">
@@ -7441,17 +7441,17 @@
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>Send feedback in-app</t>
+          <t>Privacy &amp; data link</t>
         </is>
       </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
-          <t>In Settings, tap 'Send feedback', type a note, tap Send.</t>
+          <t>Tap 'Privacy &amp; data' in Settings.</t>
         </is>
       </c>
       <c r="F168" s="9" t="inlineStr">
         <is>
-          <t>An inline box opens (no mail client, no leaving the app). Send shows 'Sending...' then a calm 'Thank you. It is on its way.', and the note arrives at the support inbox. On failure it shows a calm retry with the typed text kept. Needs the Worker deployed with /feedback + the FEEDBACK_TO secret set.</t>
+          <t>Opens the privacy screen.</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
@@ -7466,7 +7466,7 @@
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>SET-07</t>
+          <t>SET-05</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>Daily reminder explains why it can't turn on</t>
+          <t>Export your data</t>
         </is>
       </c>
       <c r="E169" s="9" t="inlineStr">
         <is>
-          <t>In Settings, set 'Daily reminder' to On in a context where it can't be granted: deny the browser notification prompt on web, or have notifications blocked.</t>
+          <t>In Settings -&gt; Your data, tap 'Export your data' (works with no account).</t>
         </is>
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>The toggle returns to Off and a calm one-line reason appears under it (e.g. 'Notifications are off for DoubleDone. Turn them on in your settings, then try again.'), never a silent failure and never a raw error. Granting permission and retrying turns it On.</t>
+          <t>Web downloads a doubledone-export-&lt;date&gt;.json with your tasks + completions; native opens the share sheet. Tombstones excluded, completion data kept.</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
@@ -7506,7 +7506,7 @@
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>SET-08</t>
+          <t>SET-06</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
@@ -7521,17 +7521,17 @@
       </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>Daily reminder time picker</t>
+          <t>Send feedback in-app</t>
         </is>
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>Turn 'Daily reminder' On, then use the - / + stepper that appears under it to change the time. Step down toward 12:00 AM and up toward 11:00 PM (the ends disable). Reload and re-open Settings; also turn the reminder on from the Today footer and confirm it uses the chosen time.</t>
+          <t>In Settings, tap 'Send feedback', type a note, tap Send.</t>
         </is>
       </c>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>A '- TIME +' stepper shows ONLY while the reminder is On, with a calm 12-hour label (e.g. '9:00 AM'). Each tap moves the hour by one and the label updates instantly; the minus disables at 12:00 AM, the plus at 11:00 PM. The chosen time survives reload and the daily nudge fires at that hour (not a fixed 9am), consistently wherever the reminder is switched on. Free for everyone, no upsell.</t>
+          <t>An inline box opens (no mail client, no leaving the app). Send shows 'Sending...' then a calm 'Thank you. It is on its way.', and the note arrives at the support inbox. On failure it shows a calm retry with the typed text kept. Needs the Worker deployed with /feedback + the FEEDBACK_TO secret set.</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
@@ -7546,7 +7546,7 @@
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>SET-09</t>
+          <t>SET-07</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
@@ -7554,24 +7554,24 @@
           <t>Settings</t>
         </is>
       </c>
-      <c r="C171" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>Turn AI off, the app whole without it</t>
+          <t>Daily reminder explains why it can't turn on</t>
         </is>
       </c>
       <c r="E171" s="9" t="inlineStr">
         <is>
-          <t>In Settings under 'AI', tap 'Turn AI off'. Then move through the app: capture, Today (long-press a task), the Menu, Calendar.</t>
+          <t>In Settings, set 'Daily reminder' to On in a context where it can't be granted: deny the browser notification prompt on web, or have notifications blocked.</t>
         </is>
       </c>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>Turning off is instant with a warm line ('AI is off. Everything stays on your device.'). Every AI affordance then disappears: Sort for me / Tidy this / Scan in capture; Break it down / Make it tiny / Combine / Plan my day on Today, including the per-task Break-down and Make-tiny; the 'Chart a course' menu entry (and the screen redirects away); and Calendar's scrapbook + weekly reflection. On-device Speak stays. Nothing calls the AI backend and the calm to-do loop still works fully.</t>
+          <t>The toggle returns to Off and a calm one-line reason appears under it (e.g. 'Notifications are off for DoubleDone. Turn them on in your settings, then try again.'), never a silent failure and never a raw error. Granting permission and retrying turns it On.</t>
         </is>
       </c>
       <c r="G171" s="7" t="inlineStr">
@@ -7586,7 +7586,7 @@
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>SET-10</t>
+          <t>SET-08</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
@@ -7601,17 +7601,17 @@
       </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>Turn AI back on (informed consent)</t>
+          <t>Daily reminder time picker</t>
         </is>
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>With AI off, in Settings tap 'Turn AI on', read the card, and tap 'Turn on AI' (also try 'Not now').</t>
+          <t>Turn 'Daily reminder' On, then use the - / + stepper that appears under it to change the time. Step down toward 12:00 AM and up toward 11:00 PM (the ends disable). Reload and re-open Settings; also turn the reminder on from the Today footer and confirm it uses the chosen time.</t>
         </is>
       </c>
       <c r="F172" s="9" t="inlineStr">
         <is>
-          <t>Turning ON asks first: a card naming exactly what is sent and to whom ('sends the text you choose... to Anthropic's Claude... Nothing else ever leaves your device.'). 'Not now' cancels with no change. 'Turn on AI' restores every AI affordance across the app. The asymmetry is deliberate: off is one instant tap, on is a clear informed tap.</t>
+          <t>A '- TIME +' stepper shows ONLY while the reminder is On, with a calm 12-hour label (e.g. '9:00 AM'). Each tap moves the hour by one and the label updates instantly; the minus disables at 12:00 AM, the plus at 11:00 PM. The chosen time survives reload and the daily nudge fires at that hour (not a fixed 9am), consistently wherever the reminder is switched on. Free for everyone, no upsell.</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr">
@@ -7626,7 +7626,7 @@
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>SET-11</t>
+          <t>SET-09</t>
         </is>
       </c>
       <c r="B173" s="7" t="inlineStr">
@@ -7634,24 +7634,24 @@
           <t>Settings</t>
         </is>
       </c>
-      <c r="C173" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>The installed version shows at the foot of Settings</t>
+          <t>Turn AI off, the app whole without it</t>
         </is>
       </c>
       <c r="E173" s="9" t="inlineStr">
         <is>
-          <t>Scroll to the very bottom of Settings on Android and on web.</t>
+          <t>In Settings under 'AI', tap 'Turn AI off'. Then move through the app: capture, Today (long-press a task), the Menu, Calendar.</t>
         </is>
       </c>
       <c r="F173" s="9" t="inlineStr">
         <is>
-          <t>One quiet line shows the installed version: 'v1.0.0 (20)' on Android (the number in brackets is the versionCode, the thing Play never shows a user), 'v1.0.0 (web)' on web. Exists because every store build shares the version NAME, so during the v19/v20 keyboard-fix confusion a tester had no way to say which build they held. When triaging any report, ask for this line first.</t>
+          <t>Turning off is instant with a warm line ('AI is off. Everything stays on your device.'). Every AI affordance then disappears: Sort for me / Tidy this / Scan in capture; Break it down / Make it tiny / Combine / Plan my day on Today, including the per-task Break-down and Make-tiny; the 'Chart a course' menu entry (and the screen redirects away); and Calendar's scrapbook + weekly reflection. On-device Speak stays. Nothing calls the AI backend and the calm to-do loop still works fully.</t>
         </is>
       </c>
       <c r="G173" s="7" t="inlineStr">
@@ -7666,12 +7666,12 @@
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>I18N-01</t>
+          <t>SET-10</t>
         </is>
       </c>
       <c r="B174" s="7" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
@@ -7681,17 +7681,17 @@
       </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>App follows the device language (Italian / Spanish / French)</t>
+          <t>Turn AI back on (informed consent)</t>
         </is>
       </c>
       <c r="E174" s="9" t="inlineStr">
         <is>
-          <t>Set the device (or browser) language to Italian, Spanish, or French and open DoubleDone fresh. Walk Today, the introduction, Settings, Calendar, capture, and close-the-day.</t>
+          <t>With AI off, in Settings tap 'Turn AI on', read the card, and tap 'Turn on AI' (also try 'Not now').</t>
         </is>
       </c>
       <c r="F174" s="9" t="inlineStr">
         <is>
-          <t>The whole UI renders in that language: screens, buttons, hints, errors, notification copy, and screen-reader labels. Dates and times follow the region's convention (24-hour clock and day-month order where the locale uses them). Task titles the user typed stay exactly as typed (user data never translates), the brand stays 'DoubleDone', and legal pages stay English. Any missing string falls back to English, never a blank. An English device sees the app unchanged.</t>
+          <t>Turning ON asks first: a card naming exactly what is sent and to whom ('sends the text you choose... to Anthropic's Claude... Nothing else ever leaves your device.'). 'Not now' cancels with no change. 'Turn on AI' restores every AI affordance across the app. The asymmetry is deliberate: off is one instant tap, on is a clear informed tap.</t>
         </is>
       </c>
       <c r="G174" s="7" t="inlineStr">
@@ -7706,37 +7706,37 @@
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>A11Y-01</t>
+          <t>SET-11</t>
         </is>
       </c>
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="C175" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C175" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>Screen reader (TalkBack)</t>
+          <t>The installed version shows at the foot of Settings</t>
         </is>
       </c>
       <c r="E175" s="9" t="inlineStr">
         <is>
-          <t>Enable TalkBack, navigate Today and capture.</t>
+          <t>Scroll to the very bottom of Settings on Android and on web.</t>
         </is>
       </c>
       <c r="F175" s="9" t="inlineStr">
         <is>
-          <t>Controls are labelled. Dates read in a friendly way.</t>
+          <t>One quiet line shows the installed version: 'v1.0.0 (20)' on Android (the number in brackets is the versionCode, the thing Play never shows a user), 'v1.0.0 (web)' on web. Exists because every store build shares the version NAME, so during the v19/v20 keyboard-fix confusion a tester had no way to say which build they held. When triaging any report, ask for this line first.</t>
         </is>
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H175" s="7" t="inlineStr"/>
@@ -7746,12 +7746,12 @@
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>A11Y-02</t>
+          <t>I18N-01</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
@@ -7761,17 +7761,17 @@
       </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>Touch targets</t>
+          <t>App follows the device language (Italian / Spanish / French)</t>
         </is>
       </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
-          <t>Tap the small controls (done, chips, actions) with a thumb.</t>
+          <t>Set the device (or browser) language to Italian, Spanish, or French and open DoubleDone fresh. Walk Today, the introduction, Settings, Calendar, capture, and close-the-day.</t>
         </is>
       </c>
       <c r="F176" s="9" t="inlineStr">
         <is>
-          <t>Comfortable to hit. No fiddly mis-taps (hitSlop adequate).</t>
+          <t>The whole UI renders in that language: screens, buttons, hints, errors, notification copy, and screen-reader labels. Dates and times follow the region's convention (24-hour clock and day-month order where the locale uses them). Task titles the user typed stay exactly as typed (user data never translates), the brand stays 'DoubleDone', and legal pages stay English. Any missing string falls back to English, never a blank. An English device sees the app unchanged.</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
@@ -7786,7 +7786,7 @@
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>A11Y-03</t>
+          <t>A11Y-01</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
@@ -7794,29 +7794,29 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="C177" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C177" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>Large text does not clip</t>
+          <t>Screen reader (TalkBack)</t>
         </is>
       </c>
       <c r="E177" s="9" t="inlineStr">
         <is>
-          <t>Set text size Large and walk every screen.</t>
+          <t>Enable TalkBack, navigate Today and capture.</t>
         </is>
       </c>
       <c r="F177" s="9" t="inlineStr">
         <is>
-          <t>Nothing important truncated or overlapping.</t>
+          <t>Controls are labelled. Dates read in a friendly way.</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H177" s="7" t="inlineStr"/>
@@ -7826,37 +7826,37 @@
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>VIS-01</t>
+          <t>A11Y-02</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>Visual</t>
-        </is>
-      </c>
-      <c r="C178" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C178" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D178" s="9" t="inlineStr">
         <is>
-          <t>Native fonts render</t>
+          <t>Touch targets</t>
         </is>
       </c>
       <c r="E178" s="9" t="inlineStr">
         <is>
-          <t>On the Android build, look at headers and body text.</t>
+          <t>Tap the small controls (done, chips, actions) with a thumb.</t>
         </is>
       </c>
       <c r="F178" s="9" t="inlineStr">
         <is>
-          <t>Serif (Newsreader) headers, Atkinson body, correct bold weights.</t>
+          <t>Comfortable to hit. No fiddly mis-taps (hitSlop adequate).</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H178" s="7" t="inlineStr"/>
@@ -7866,37 +7866,37 @@
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>VIS-02</t>
+          <t>A11Y-03</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
-          <t>Visual</t>
-        </is>
-      </c>
-      <c r="C179" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C179" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>Dark palette on device</t>
+          <t>Large text does not clip</t>
         </is>
       </c>
       <c r="E179" s="9" t="inlineStr">
         <is>
-          <t>Switch to Dark on the Android build.</t>
+          <t>Set text size Large and walk every screen.</t>
         </is>
       </c>
       <c r="F179" s="9" t="inlineStr">
         <is>
-          <t>Dusk dark, comfortable contrast, no harsh pure-black/white.</t>
+          <t>Nothing important truncated or overlapping.</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H179" s="7" t="inlineStr"/>
@@ -7906,7 +7906,7 @@
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>VIS-03</t>
+          <t>VIS-01</t>
         </is>
       </c>
       <c r="B180" s="7" t="inlineStr">
@@ -7914,24 +7914,24 @@
           <t>Visual</t>
         </is>
       </c>
-      <c r="C180" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C180" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D180" s="9" t="inlineStr">
         <is>
-          <t>Bold body text renders</t>
+          <t>Native fonts render</t>
         </is>
       </c>
       <c r="E180" s="9" t="inlineStr">
         <is>
-          <t>Find bold body text (e.g. emphasised labels) on Android.</t>
+          <t>On the Android build, look at headers and body text.</t>
         </is>
       </c>
       <c r="F180" s="9" t="inlineStr">
         <is>
-          <t>Bold reads as truly bold (the bodyBold fix), not faux/again-regular.</t>
+          <t>Serif (Newsreader) headers, Atkinson body, correct bold weights.</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr">
@@ -7946,32 +7946,32 @@
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>REM-01</t>
+          <t>VIS-02</t>
         </is>
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>Reminders</t>
-        </is>
-      </c>
-      <c r="C181" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C181" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>Daily reminder fires</t>
+          <t>Dark palette on device</t>
         </is>
       </c>
       <c r="E181" s="9" t="inlineStr">
         <is>
-          <t>Turn the daily reminder on (Settings &gt; Daily reminder, or the Today footer), grant permission, and leave it on until the daily hour.</t>
+          <t>Switch to Dark on the Android build.</t>
         </is>
       </c>
       <c r="F181" s="9" t="inlineStr">
         <is>
-          <t>A calm 'Your today is here when you are ready.' notification arrives at the scheduled hour (verified firing on a real Samsung device). Toggling it off cancels it.</t>
+          <t>Dusk dark, comfortable contrast, no harsh pure-black/white.</t>
         </is>
       </c>
       <c r="G181" s="7" t="inlineStr">
@@ -7986,12 +7986,12 @@
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>REM-02</t>
+          <t>VIS-03</t>
         </is>
       </c>
       <c r="B182" s="7" t="inlineStr">
         <is>
-          <t>Reminders</t>
+          <t>Visual</t>
         </is>
       </c>
       <c r="C182" s="10" t="inlineStr">
@@ -8001,17 +8001,17 @@
       </c>
       <c r="D182" s="9" t="inlineStr">
         <is>
-          <t>Reminder channel present</t>
+          <t>Bold body text renders</t>
         </is>
       </c>
       <c r="E182" s="9" t="inlineStr">
         <is>
-          <t>Android Settings -&gt; Apps -&gt; DoubleDone -&gt; Notifications.</t>
+          <t>Find bold body text (e.g. emphasised labels) on Android.</t>
         </is>
       </c>
       <c r="F182" s="9" t="inlineStr">
         <is>
-          <t>A DoubleDone reminder channel exists and is controllable.</t>
+          <t>Bold reads as truly bold (the bodyBold fix), not faux/again-regular.</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr">
@@ -8026,12 +8026,12 @@
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>PRV-01</t>
+          <t>REM-01</t>
         </is>
       </c>
       <c r="B183" s="7" t="inlineStr">
         <is>
-          <t>Privacy</t>
+          <t>Reminders</t>
         </is>
       </c>
       <c r="C183" s="8" t="inlineStr">
@@ -8041,22 +8041,22 @@
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>Privacy policy reachable</t>
+          <t>Daily reminder fires</t>
         </is>
       </c>
       <c r="E183" s="9" t="inlineStr">
         <is>
-          <t>Visit doubledone.app/privacy (and via Settings).</t>
+          <t>Turn the daily reminder on (Settings &gt; Daily reminder, or the Today footer), grant permission, and leave it on until the daily hour.</t>
         </is>
       </c>
       <c r="F183" s="9" t="inlineStr">
         <is>
-          <t>Loads, plain-English, matches the privacy posture.</t>
+          <t>A calm 'Your today is here when you are ready.' notification arrives at the scheduled hour (verified firing on a real Samsung device). Toggling it off cancels it.</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H183" s="7" t="inlineStr"/>
@@ -8066,37 +8066,37 @@
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>DEP-01</t>
+          <t>REM-02</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
         <is>
-          <t>Deploy</t>
-        </is>
-      </c>
-      <c r="C184" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Reminders</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>Web loads + deep links</t>
+          <t>Reminder channel present</t>
         </is>
       </c>
       <c r="E184" s="9" t="inlineStr">
         <is>
-          <t>Open doubledone.app, then hard-load /privacy and /sign-in directly.</t>
+          <t>Android Settings -&gt; Apps -&gt; DoubleDone -&gt; Notifications.</t>
         </is>
       </c>
       <c r="F184" s="9" t="inlineStr">
         <is>
-          <t>App loads; deep links resolve (SPA fallback), no 404.</t>
+          <t>A DoubleDone reminder channel exists and is controllable.</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H184" s="7" t="inlineStr"/>
@@ -8106,12 +8106,12 @@
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>DEP-02</t>
+          <t>PRV-01</t>
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr">
         <is>
-          <t>Deploy</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
@@ -8121,22 +8121,22 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>Android APK installs + launches</t>
+          <t>Privacy policy reachable</t>
         </is>
       </c>
       <c r="E185" s="9" t="inlineStr">
         <is>
-          <t>Sideload the latest APK and open it.</t>
+          <t>Visit doubledone.app/privacy (and via Settings).</t>
         </is>
       </c>
       <c r="F185" s="9" t="inlineStr">
         <is>
-          <t>Installs and runs. Core loop works.</t>
+          <t>Loads, plain-English, matches the privacy posture.</t>
         </is>
       </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H185" s="7" t="inlineStr"/>
@@ -8146,7 +8146,7 @@
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>DEP-03</t>
+          <t>DEP-01</t>
         </is>
       </c>
       <c r="B186" s="7" t="inlineStr">
@@ -8154,29 +8154,29 @@
           <t>Deploy</t>
         </is>
       </c>
-      <c r="C186" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C186" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D186" s="9" t="inlineStr">
         <is>
-          <t>Local-first offline</t>
+          <t>Web loads + deep links</t>
         </is>
       </c>
       <c r="E186" s="9" t="inlineStr">
         <is>
-          <t>Use core features (add/complete) with no network.</t>
+          <t>Open doubledone.app, then hard-load /privacy and /sign-in directly.</t>
         </is>
       </c>
       <c r="F186" s="9" t="inlineStr">
         <is>
-          <t>Works offline; syncs later when signed in.</t>
+          <t>App loads; deep links resolve (SPA fallback), no 404.</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H186" s="7" t="inlineStr"/>
@@ -8186,12 +8186,12 @@
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>PREM-00</t>
+          <t>DEP-02</t>
         </is>
       </c>
       <c r="B187" s="7" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Deploy</t>
         </is>
       </c>
       <c r="C187" s="8" t="inlineStr">
@@ -8201,22 +8201,22 @@
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>PREREQ: Stripe test keys + webhook</t>
+          <t>Android APK installs + launches</t>
         </is>
       </c>
       <c r="E187" s="9" t="inlineStr">
         <is>
-          <t>Set STRIPE_SECRET_KEY + STRIPE_WEBHOOK_SECRET as Worker secrets; register the /stripe-webhook URL in the Stripe sandbox.</t>
+          <t>Sideload the latest APK and open it.</t>
         </is>
       </c>
       <c r="F187" s="9" t="inlineStr">
         <is>
-          <t>Worker deployed with the keys; webhook endpoint registered and reachable.</t>
+          <t>Installs and runs. Core loop works.</t>
         </is>
       </c>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H187" s="7" t="inlineStr"/>
@@ -8226,32 +8226,32 @@
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>PREM-01</t>
+          <t>DEP-03</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
         <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="C188" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Deploy</t>
+        </is>
+      </c>
+      <c r="C188" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D188" s="9" t="inlineStr">
         <is>
-          <t>Paywall renders</t>
+          <t>Local-first offline</t>
         </is>
       </c>
       <c r="E188" s="9" t="inlineStr">
         <is>
-          <t>Open Settings -&gt; DoubleDone Premium.</t>
+          <t>Use core features (add/complete) with no network.</t>
         </is>
       </c>
       <c r="F188" s="9" t="inlineStr">
         <is>
-          <t>The calm 'Keep every week' pitch, the A$5/mo price, the 1 -&gt; 2 -&gt; 4 tenure tiers. The feature list includes the personalisation pair (Quiet, the borderless look, and the seven colour themes) alongside Scan, Pin and the AI suite, so a user sent here from the Interface gate can see the thing they tapped.</t>
+          <t>Works offline; syncs later when signed in.</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr">
@@ -8266,7 +8266,7 @@
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>PREM-02</t>
+          <t>PREM-00</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
@@ -8281,22 +8281,22 @@
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>Free monthly gate routes to the paywall</t>
+          <t>PREREQ: Stripe test keys + webhook</t>
         </is>
       </c>
       <c r="E189" s="9" t="inlineStr">
         <is>
-          <t>As a free user who already made a scrapbook this month, tap 'Make a scrapbook'.</t>
+          <t>Set STRIPE_SECRET_KEY + STRIPE_WEBHOOK_SECRET as Worker secrets; register the /stripe-webhook URL in the Stripe sandbox.</t>
         </is>
       </c>
       <c r="F189" s="9" t="inlineStr">
         <is>
-          <t>Routed to the Premium paywall, calm, never a shaming message.</t>
+          <t>Worker deployed with the keys; webhook endpoint registered and reachable.</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr"/>
@@ -8306,7 +8306,7 @@
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>PREM-03</t>
+          <t>PREM-01</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
@@ -8321,22 +8321,22 @@
       </c>
       <c r="D190" s="9" t="inlineStr">
         <is>
-          <t>Checkout with a test card</t>
+          <t>Paywall renders</t>
         </is>
       </c>
       <c r="E190" s="9" t="inlineStr">
         <is>
-          <t>Signed in, tap Go Premium, pay with Stripe test card 4242 4242 4242 4242 (any future expiry, any CVC).</t>
+          <t>Open Settings -&gt; DoubleDone Premium.</t>
         </is>
       </c>
       <c r="F190" s="9" t="inlineStr">
         <is>
-          <t>Stripe Checkout opens, payment succeeds, returns to /premium?status=success.</t>
+          <t>The calm 'Keep every week' pitch, the A$5/mo price, the 1 -&gt; 2 -&gt; 4 tenure tiers. The feature list includes the personalisation pair (Quiet, the borderless look, and the seven colour themes) alongside Scan, Pin and the AI suite, so a user sent here from the Interface gate can see the thing they tapped.</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H190" s="7" t="inlineStr"/>
@@ -8346,7 +8346,7 @@
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>PREM-04</t>
+          <t>PREM-02</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
@@ -8361,17 +8361,17 @@
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>Entitlement flips to premium</t>
+          <t>Free monthly gate routes to the paywall</t>
         </is>
       </c>
       <c r="E191" s="9" t="inlineStr">
         <is>
-          <t>After the test checkout, reopen Premium and the Calendar.</t>
+          <t>As a free user who already made a scrapbook this month, tap 'Make a scrapbook'.</t>
         </is>
       </c>
       <c r="F191" s="9" t="inlineStr">
         <is>
-          <t>Premium shows active; the scrapbook is no longer monthly-gated (now weekly).</t>
+          <t>Routed to the Premium paywall, calm, never a shaming message.</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
@@ -8386,7 +8386,7 @@
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>PREM-05</t>
+          <t>PREM-03</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
@@ -8394,29 +8394,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C192" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D192" s="9" t="inlineStr">
         <is>
-          <t>Premium weekly wait stays calm</t>
+          <t>Checkout with a test card</t>
         </is>
       </c>
       <c r="E192" s="9" t="inlineStr">
         <is>
-          <t>As premium, make this week's allowance of scrapbooks, then try one more.</t>
+          <t>Signed in, tap Go Premium, pay with Stripe test card 4242 4242 4242 4242 (any future expiry, any CVC).</t>
         </is>
       </c>
       <c r="F192" s="9" t="inlineStr">
         <is>
-          <t>A calm 'next ready in N days' message, never a paywall.</t>
+          <t>Stripe Checkout opens, payment succeeds, returns to /premium?status=success.</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H192" s="7" t="inlineStr"/>
@@ -8426,7 +8426,7 @@
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>PREM-06</t>
+          <t>PREM-04</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
@@ -8434,29 +8434,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C193" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C193" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>Webhook rejects a bad signature</t>
+          <t>Entitlement flips to premium</t>
         </is>
       </c>
       <c r="E193" s="9" t="inlineStr">
         <is>
-          <t>POST a forged event to /stripe-webhook with no valid Stripe-Signature.</t>
+          <t>After the test checkout, reopen Premium and the Calendar.</t>
         </is>
       </c>
       <c r="F193" s="9" t="inlineStr">
         <is>
-          <t>400 bad signature; no entitlement change.</t>
+          <t>Premium shows active; the scrapbook is no longer monthly-gated (now weekly).</t>
         </is>
       </c>
       <c r="G193" s="7" t="inlineStr">
         <is>
-          <t>Worker</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H193" s="7" t="inlineStr"/>
@@ -8466,7 +8466,7 @@
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>PREM-07</t>
+          <t>PREM-05</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
@@ -8474,29 +8474,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C194" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C194" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D194" s="9" t="inlineStr">
         <is>
-          <t>Webhook delivery succeeds (Stripe side)</t>
+          <t>Premium weekly wait stays calm</t>
         </is>
       </c>
       <c r="E194" s="9" t="inlineStr">
         <is>
-          <t>After the test checkout, open the Stripe event destination's delivery log.</t>
+          <t>As premium, make this week's allowance of scrapbooks, then try one more.</t>
         </is>
       </c>
       <c r="F194" s="9" t="inlineStr">
         <is>
-          <t>The checkout/subscription events show 'delivered' with a 200 from the Worker.</t>
+          <t>A calm 'next ready in N days' message, never a paywall.</t>
         </is>
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H194" s="7" t="inlineStr"/>
@@ -8506,7 +8506,7 @@
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>PREM-08</t>
+          <t>PREM-06</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
@@ -8514,29 +8514,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C195" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C195" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D195" s="9" t="inlineStr">
         <is>
-          <t>Manage subscription opens the billing portal</t>
+          <t>Webhook rejects a bad signature</t>
         </is>
       </c>
       <c r="E195" s="9" t="inlineStr">
         <is>
-          <t>As premium: /premium -&gt; Manage subscription.</t>
+          <t>POST a forged event to /stripe-webhook with no valid Stripe-Signature.</t>
         </is>
       </c>
       <c r="F195" s="9" t="inlineStr">
         <is>
-          <t>Redirects to the Stripe Billing Portal (cancel / update card / invoices).</t>
+          <t>400 bad signature; no entitlement change.</t>
         </is>
       </c>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Worker</t>
         </is>
       </c>
       <c r="H195" s="7" t="inlineStr"/>
@@ -8546,7 +8546,7 @@
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>PREM-09</t>
+          <t>PREM-07</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
@@ -8561,17 +8561,17 @@
       </c>
       <c r="D196" s="9" t="inlineStr">
         <is>
-          <t>Cancel reverts to free</t>
+          <t>Webhook delivery succeeds (Stripe side)</t>
         </is>
       </c>
       <c r="E196" s="9" t="inlineStr">
         <is>
-          <t>In the portal, cancel immediately, then return to the app.</t>
+          <t>After the test checkout, open the Stripe event destination's delivery log.</t>
         </is>
       </c>
       <c r="F196" s="9" t="inlineStr">
         <is>
-          <t>Entitlement flips to free; the scrapbook is monthly-gated again; tenure (started_at) is preserved.</t>
+          <t>The checkout/subscription events show 'delivered' with a 200 from the Worker.</t>
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
@@ -8586,7 +8586,7 @@
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>PREM-10</t>
+          <t>PREM-08</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
@@ -8594,24 +8594,24 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C197" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C197" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>Premium screen shows the renew / cancel date</t>
+          <t>Manage subscription opens the billing portal</t>
         </is>
       </c>
       <c r="E197" s="9" t="inlineStr">
         <is>
-          <t>As premium, open /premium; then schedule a cancel-at-period-end in the portal and reopen.</t>
+          <t>As premium: /premium -&gt; Manage subscription.</t>
         </is>
       </c>
       <c r="F197" s="9" t="inlineStr">
         <is>
-          <t>Reads 'Renews &lt;date&gt;' when active, and 'Premium until &lt;date&gt;, then free' when a cancel is scheduled.</t>
+          <t>Redirects to the Stripe Billing Portal (cancel / update card / invoices).</t>
         </is>
       </c>
       <c r="G197" s="7" t="inlineStr">
@@ -8626,7 +8626,7 @@
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>PREM-11</t>
+          <t>PREM-09</t>
         </is>
       </c>
       <c r="B198" s="7" t="inlineStr">
@@ -8634,29 +8634,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C198" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C198" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D198" s="9" t="inlineStr">
         <is>
-          <t>Comp allowlist: the owner email is always premium</t>
+          <t>Cancel reverts to free</t>
         </is>
       </c>
       <c r="E198" s="9" t="inlineStr">
         <is>
-          <t>Sign in with the comp email (the owner account listed in server/src/comp.ts), without ever paying.</t>
+          <t>In the portal, cancel immediately, then return to the app.</t>
         </is>
       </c>
       <c r="F198" s="9" t="inlineStr">
         <is>
-          <t>Premium is active immediately: Settings and the Calendar show the scrapbook unlocked and Scan works, with no Stripe charge. A non-allowlisted free account stays free. The allowlist is checked against a cryptographically verified token on the costed gate, so a forged token cannot claim premium compute. REGRESSION CHECK (found on-device 2026-07-19): on /premium the panel reads 'You're Premium' and, because a comp has no Stripe customer, shows a calm 'nothing to manage here' line IN PLACE of a Manage button. It must never show 'Could not open the billing portal. Please try again.' (retrying a portal that does not exist). POST /portal answers such accounts 404 and the app reads that as nothing-to-manage, not a failure.</t>
+          <t>Entitlement flips to free; the scrapbook is monthly-gated again; tenure (started_at) is preserved.</t>
         </is>
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H198" s="7" t="inlineStr"/>
@@ -8666,7 +8666,7 @@
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>PREM-12</t>
+          <t>PREM-10</t>
         </is>
       </c>
       <c r="B199" s="7" t="inlineStr">
@@ -8674,29 +8674,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C199" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C199" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D199" s="9" t="inlineStr">
         <is>
-          <t>Calendar insights: the premium 'Your patterns' card</t>
+          <t>Premium screen shows the renew / cancel date</t>
         </is>
       </c>
       <c r="E199" s="9" t="inlineStr">
         <is>
-          <t>As premium (or with the dev Premium override on), finish a few tasks across a couple of days this week including one big/dreaded one, then open the Calendar and scroll below the Scrapbook. Tap 'Reflect on this week'.</t>
+          <t>As premium, open /premium; then schedule a cancel-at-period-end in the portal and reopen.</t>
         </is>
       </c>
       <c r="F199" s="9" t="inlineStr">
         <is>
-          <t>A calm 'Your patterns' card shows warm counts (finished this week, 'on N days', reclaimed old tasks named) with NO streak, score, percent, or 'missed' wording. 'Reflect on this week' returns one warm paragraph that only celebrates what was done (never a performance review) and changes nothing about your tasks. A 'lookback.summary.made' event is logged.</t>
+          <t>Reads 'Renews &lt;date&gt;' when active, and 'Premium until &lt;date&gt;, then free' when a cancel is scheduled.</t>
         </is>
       </c>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H199" s="7" t="inlineStr"/>
@@ -8706,7 +8706,7 @@
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>PREM-13</t>
+          <t>PREM-11</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
@@ -8714,24 +8714,24 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C200" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C200" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D200" s="9" t="inlineStr">
         <is>
-          <t>Calendar insights: free sees a calm upsell, not a wall</t>
+          <t>Comp allowlist: the owner email is always premium</t>
         </is>
       </c>
       <c r="E200" s="9" t="inlineStr">
         <is>
-          <t>As a free user, open the Calendar and scroll below the Scrapbook, then tap the 'Your patterns' card.</t>
+          <t>Sign in with the comp email (the owner account listed in server/src/comp.ts), without ever paying.</t>
         </is>
       </c>
       <c r="F200" s="9" t="inlineStr">
         <is>
-          <t>A calm one-line invite ('See what your weeks and months add up to'), never a teased count and never a wall. Tapping routes to /premium and logs 'premium.gate_hit' with reason 'insights'. The free user's calendar and their one monthly scrapbook are completely untouched.</t>
+          <t>Premium is active immediately: Settings and the Calendar show the scrapbook unlocked and Scan works, with no Stripe charge. A non-allowlisted free account stays free. The allowlist is checked against a cryptographically verified token on the costed gate, so a forged token cannot claim premium compute. REGRESSION CHECK (found on-device 2026-07-19): on /premium the panel reads 'You're Premium' and, because a comp has no Stripe customer, shows a calm 'nothing to manage here' line IN PLACE of a Manage button. It must never show 'Could not open the billing portal. Please try again.' (retrying a portal that does not exist). POST /portal answers such accounts 404 and the app reads that as nothing-to-manage, not a failure.</t>
         </is>
       </c>
       <c r="G200" s="7" t="inlineStr">
@@ -8746,7 +8746,7 @@
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>PREM-14</t>
+          <t>PREM-12</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
@@ -8754,24 +8754,24 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C201" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C201" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D201" s="9" t="inlineStr">
         <is>
-          <t>Premium: custom colour theme</t>
+          <t>Calendar insights: the premium 'Your patterns' card</t>
         </is>
       </c>
       <c r="E201" s="9" t="inlineStr">
         <is>
-          <t>As premium (or with the dev Premium override on), open Settings -&gt; Comfort -&gt; 'Colour theme' and tap each of Dusk / Sage / Slate / Heather / Fog / Honey / Rose, reloading after choosing one, in BOTH light and dark mode. Then as a FREE user, tap a preset.</t>
+          <t>As premium (or with the dev Premium override on), finish a few tasks across a couple of days this week including one big/dreaded one, then open the Calendar and scroll below the Scrapbook. Tap 'Reflect on this week'.</t>
         </is>
       </c>
       <c r="F201" s="9" t="inlineStr">
         <is>
-          <t>Premium: tapping a preset repaints the WHOLE app in that palette (background, cards, accent, the brand) and the choice survives reload; the chosen preset is ringed; Dusk is the default and looks identical to the pre-themes app. Each preset has a tuned light and dark variant. Honey's buttons keep DARK labels (a calm gold can't carry white text). Free: the block shows a 'Premium' tag and tapping any preset routes to the paywall with no change applied. A lapsed subscriber keeps the preset they chose.</t>
+          <t>A calm 'Your patterns' card shows warm counts (finished this week, 'on N days', reclaimed old tasks named) with NO streak, score, percent, or 'missed' wording. 'Reflect on this week' returns one warm paragraph that only celebrates what was done (never a performance review) and changes nothing about your tasks. A 'lookback.summary.made' event is logged.</t>
         </is>
       </c>
       <c r="G201" s="7" t="inlineStr">
@@ -8786,7 +8786,7 @@
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>PREM-15</t>
+          <t>PREM-13</t>
         </is>
       </c>
       <c r="B202" s="7" t="inlineStr">
@@ -8794,24 +8794,24 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C202" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C202" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D202" s="9" t="inlineStr">
         <is>
-          <t>Post-payment 'taking a while' recovery</t>
+          <t>Calendar insights: free sees a calm upsell, not a wall</t>
         </is>
       </c>
       <c r="E202" s="9" t="inlineStr">
         <is>
-          <t>Complete a test checkout, then on the return /premium success screen simulate the entitlement being slow (e.g. the webhook delayed) so polling does not flip within ~10 tries.</t>
+          <t>As a free user, open the Calendar and scroll below the Scrapbook, then tap the 'Your patterns' card.</t>
         </is>
       </c>
       <c r="F202" s="9" t="inlineStr">
         <is>
-          <t>Instead of spinning forever it shows a calm message ('This is taking longer than usual. Your payment went through, give it a minute, then tap Refresh.') with a Refresh button and a pointer to send a note from Settings if it persists. Tapping Refresh re-checks and flips to premium once the entitlement lands. It never says the payment failed.</t>
+          <t>A calm one-line invite ('See what your weeks and months add up to'), never a teased count and never a wall. Tapping routes to /premium and logs 'premium.gate_hit' with reason 'insights'. The free user's calendar and their one monthly scrapbook are completely untouched.</t>
         </is>
       </c>
       <c r="G202" s="7" t="inlineStr">
@@ -8826,7 +8826,7 @@
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>PREM-16</t>
+          <t>PREM-14</t>
         </is>
       </c>
       <c r="B203" s="7" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>Card-free 'Try Premium' one-month trial</t>
+          <t>Premium: custom colour theme</t>
         </is>
       </c>
       <c r="E203" s="9" t="inlineStr">
         <is>
-          <t>Signed in, on /premium tap 'Try Premium free for a month'. Confirm Premium unlocks. Tap it again on the SAME account. Advance the clock past 30 days (or inspect the trials row) and re-check entitlement. Also open the trial link signed OUT.</t>
+          <t>As premium (or with the dev Premium override on), open Settings -&gt; Comfort -&gt; 'Colour theme' and tap each of Dusk / Sage / Slate / Heather / Fog / Honey / Rose, reloading after choosing one, in BOTH light and dark mode. Then as a FREE user, tap a preset.</t>
         </is>
       </c>
       <c r="F203" s="9" t="inlineStr">
         <is>
-          <t>First tap: a calm confirm, Premium turns on with NO card and NO Stripe (status 'trial'); the page shows 'Your free month', 'Free until &lt;date&gt;', and on web/Android the convert area shows the SAME monthly/annual toggle as the free paywall with the chosen price, and 'Go Premium to keep it' opens Stripe checkout for THAT plan (a trial member could only ever convert to monthly until 2026-08-01, when one asked to buy the year and could not; never 'Manage': a trial has no portal, so a Manage button here could only 404). On iOS the same trial copy shows with NO mid-trial CTA at all (StoreKit refuses a second purchase while premium and the trial never auto-charges; the 'Free until' line carries it), and never a Manage button. Second tap, same account: a gentle 'You've already had your free month' (never shame), no second trial granted. After expiry it reverts to free on its own, no charge ever. Signed out: an account is required (one trial per account), so the link routes to sign-in rather than granting. NOTE: this exact expected text was specified from the start, but the screen read the URL ?status= param instead of the entitlement status, so every trial user actually saw 'You're Premium' plus a dead Manage button until 2026-07-19. If this case regresses, that is the bug that came back.</t>
+          <t>Premium: tapping a preset repaints the WHOLE app in that palette (background, cards, accent, the brand) and the choice survives reload; the chosen preset is ringed; Dusk is the default and looks identical to the pre-themes app. Each preset has a tuned light and dark variant. Honey's buttons keep DARK labels (a calm gold can't carry white text). Free: the block shows a 'Premium' tag and tapping any preset routes to the paywall with no change applied. A lapsed subscriber keeps the preset they chose.</t>
         </is>
       </c>
       <c r="G203" s="7" t="inlineStr">
@@ -8866,7 +8866,7 @@
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>PREM-17</t>
+          <t>PREM-15</t>
         </is>
       </c>
       <c r="B204" s="7" t="inlineStr">
@@ -8881,17 +8881,17 @@
       </c>
       <c r="D204" s="9" t="inlineStr">
         <is>
-          <t>Annual vs monthly plan checkout</t>
+          <t>Post-payment 'taking a while' recovery</t>
         </is>
       </c>
       <c r="E204" s="9" t="inlineStr">
         <is>
-          <t>On /premium use the Monthly / Annual toggle, then Subscribe. Confirm the Stripe Checkout reflects the chosen plan. Complete a test annual checkout. Then, as an already-subscribed user, hit Subscribe again.</t>
+          <t>Complete a test checkout, then on the return /premium success screen simulate the entitlement being slow (e.g. the webhook delayed) so polling does not flip within ~10 tries.</t>
         </is>
       </c>
       <c r="F204" s="9" t="inlineStr">
         <is>
-          <t>The toggle shows 'A$50/year, about two months free' for annual; Checkout opens the YEARLY price for Annual and the monthly price for Monthly, and the success path grants Premium either way. An already-subscribed user is refused a second Checkout (the server 409s and the app says 'You're already on Premium', never a double charge). Prerequisite: the Worker deployed with STRIPE_PRICE_ID_ANNUAL and that price live in Stripe.</t>
+          <t>Instead of spinning forever it shows a calm message ('This is taking longer than usual. Your payment went through, give it a minute, then tap Refresh.') with a Refresh button and a pointer to send a note from Settings if it persists. Tapping Refresh re-checks and flips to premium once the entitlement lands. It never says the payment failed.</t>
         </is>
       </c>
       <c r="G204" s="7" t="inlineStr">
@@ -8906,7 +8906,7 @@
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>PREM-18</t>
+          <t>PREM-16</t>
         </is>
       </c>
       <c r="B205" s="7" t="inlineStr">
@@ -8914,29 +8914,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C205" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C205" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
-          <t>iOS paywall carries everything Apple requires</t>
+          <t>Card-free 'Try Premium' one-month trial</t>
         </is>
       </c>
       <c r="E205" s="9" t="inlineStr">
         <is>
-          <t>On the iPhone (TestFlight), open Premium while signed out. Read the whole paywall.</t>
+          <t>Signed in, on /premium tap 'Try Premium free for a month'. Confirm Premium unlocks. Tap it again on the SAME account. Advance the clock past 30 days (or inspect the trials row) and re-check entitlement. Also open the trial link signed OUT.</t>
         </is>
       </c>
       <c r="F205" s="9" t="inlineStr">
         <is>
-          <t>The paywall shows: the title 'DoubleDone Premium', BOTH prices from the store in the device's currency (A$5.00 / A$50.00 on an Australian storefront; StoreKit renders the viewer's own storefront price, so other regions see their converted price), the renewal line ('It renews on its own until you cancel it...'), a tappable Terms of use and Privacy policy, and a visible 'Restore a purchase'. There is NO mention of Stripe anywhere on the screen. The prices come from StoreKit, so if they read blank the offering is misconfigured (App Store Connect), not a code bug.</t>
+          <t>First tap: a calm confirm, Premium turns on with NO card and NO Stripe (status 'trial'); the page shows 'Your free month', 'Free until &lt;date&gt;', and on web/Android the convert area shows the SAME monthly/annual toggle as the free paywall with the chosen price, and 'Go Premium to keep it' opens Stripe checkout for THAT plan (a trial member could only ever convert to monthly until 2026-08-01, when one asked to buy the year and could not; never 'Manage': a trial has no portal, so a Manage button here could only 404). On iOS the same trial copy shows with NO mid-trial CTA at all (StoreKit refuses a second purchase while premium and the trial never auto-charges; the 'Free until' line carries it), and never a Manage button. Second tap, same account: a gentle 'You've already had your free month' (never shame), no second trial granted. After expiry it reverts to free on its own, no charge ever. Signed out: an account is required (one trial per account), so the link routes to sign-in rather than granting. NOTE: this exact expected text was specified from the start, but the screen read the URL ?status= param instead of the entitlement status, so every trial user actually saw 'You're Premium' plus a dead Manage button until 2026-07-19. If this case regresses, that is the bug that came back.</t>
         </is>
       </c>
       <c r="G205" s="7" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H205" s="7" t="inlineStr"/>
@@ -8946,7 +8946,7 @@
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>PREM-19</t>
+          <t>PREM-17</t>
         </is>
       </c>
       <c r="B206" s="7" t="inlineStr">
@@ -8954,29 +8954,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C206" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C206" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D206" s="9" t="inlineStr">
         <is>
-          <t>Anonymous Go Premium opens the purchase sheet (registration is OPTIONAL, App Review 5.1.1)</t>
+          <t>Annual vs monthly plan checkout</t>
         </is>
       </c>
       <c r="E206" s="9" t="inlineStr">
         <is>
-          <t>Signed out on the iPhone (no account at all), open Premium, read the line under the button, then tap 'Go Premium' and complete a sandbox purchase. Kill and relaunch the app. THEN sign in with a fresh email + OTP.</t>
+          <t>On /premium use the Monthly / Annual toggle, then Subscribe. Confirm the Stripe Checkout reflects the chosen plan. Complete a test annual checkout. Then, as an already-subscribed user, hit Subscribe again.</t>
         </is>
       </c>
       <c r="F206" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Go Premium' while anonymous and opens the StoreKit sheet directly, no sign-in wall anywhere (the wall was rejected under 5.1.1(v), 2026-07-28). The line under it explains, calmly: no account needed, Premium lives with the Apple ID, signing in any time brings it to other devices, and an existing web subscriber should sign in first. After the purchase Premium is ON while still anonymous, and SURVIVES a relaunch (the device's own RevenueCat entitlement is the source, no server row exists yet). Signing in later aliases the purchase onto the account (the webhook then writes D1), so it appears on the user's other devices: Apple's exact suggested flow.</t>
+          <t>The toggle shows 'A$50/year, about two months free' for annual; Checkout opens the YEARLY price for Annual and the monthly price for Monthly, and the success path grants Premium either way. An already-subscribed user is refused a second Checkout (the server 409s and the app says 'You're already on Premium', never a double charge). Prerequisite: the Worker deployed with STRIPE_PRICE_ID_ANNUAL and that price live in Stripe.</t>
         </is>
       </c>
       <c r="G206" s="7" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H206" s="7" t="inlineStr"/>
@@ -8986,7 +8986,7 @@
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>PREM-20</t>
+          <t>PREM-18</t>
         </is>
       </c>
       <c r="B207" s="7" t="inlineStr">
@@ -9001,17 +9001,17 @@
       </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
-          <t>Sandbox purchase unlocks Premium via the webhook</t>
+          <t>iOS paywall carries everything Apple requires</t>
         </is>
       </c>
       <c r="E207" s="9" t="inlineStr">
         <is>
-          <t>Signed in with a sandbox Apple ID, tap Go Premium, complete the StoreKit sheet.</t>
+          <t>On the iPhone (TestFlight), open Premium while signed out. Read the whole paywall.</t>
         </is>
       </c>
       <c r="F207" s="9" t="inlineStr">
         <is>
-          <t>The StoreKit sheet appears, the sandbox payment succeeds, the calm 'setting up' beat shows, then Premium flips on within ~20s (the RevenueCat webhook writes D1, the success-poll picks it up). Apple's accelerated sandbox clock then renews it several times and expires it, exercising the whole INITIAL_PURCHASE -&gt; RENEWAL -&gt; EXPIRATION chain against the real Worker. Prerequisite: the Worker deployed with RC_WEBHOOK_AUTH and the RevenueCat dashboard webhook set to the same secret.</t>
+          <t>The paywall shows: the title 'DoubleDone Premium', BOTH prices from the store in the device's currency (A$5.00 / A$50.00 on an Australian storefront; StoreKit renders the viewer's own storefront price, so other regions see their converted price), the renewal line ('It renews on its own until you cancel it...'), a tappable Terms of use and Privacy policy, and a visible 'Restore a purchase'. There is NO mention of Stripe anywhere on the screen. The prices come from StoreKit, so if they read blank the offering is misconfigured (App Store Connect), not a code bug.</t>
         </is>
       </c>
       <c r="G207" s="7" t="inlineStr">
@@ -9026,7 +9026,7 @@
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>PREM-21</t>
+          <t>PREM-19</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="D208" s="9" t="inlineStr">
         <is>
-          <t>A Stripe web subscriber is NEVER charged again on iOS</t>
+          <t>Anonymous Go Premium opens the purchase sheet (registration is OPTIONAL, App Review 5.1.1)</t>
         </is>
       </c>
       <c r="E208" s="9" t="inlineStr">
         <is>
-          <t>As a user who already subscribed to Premium on the website (Stripe), install on iPhone, open Premium, and sign in with that same account.</t>
+          <t>Signed out on the iPhone (no account at all), open Premium, read the line under the button, then tap 'Go Premium' and complete a sandbox purchase. Kill and relaunch the app. THEN sign in with a fresh email + OTP.</t>
         </is>
       </c>
       <c r="F208" s="9" t="inlineStr">
         <is>
-          <t>The screen shows the Premium (active) panel with NO buy button, so a second charge is impossible. Even if the buy button were reachable mid-load, the fresh entitlement read before buy() bails to the active panel. This is the double-charge guard, and the single most important iOS case.</t>
+          <t>The button reads 'Go Premium' while anonymous and opens the StoreKit sheet directly, no sign-in wall anywhere (the wall was rejected under 5.1.1(v), 2026-07-28). The line under it explains, calmly: no account needed, Premium lives with the Apple ID, signing in any time brings it to other devices, and an existing web subscriber should sign in first. After the purchase Premium is ON while still anonymous, and SURVIVES a relaunch (the device's own RevenueCat entitlement is the source, no server row exists yet). Signing in later aliases the purchase onto the account (the webhook then writes D1), so it appears on the user's other devices: Apple's exact suggested flow.</t>
         </is>
       </c>
       <c r="G208" s="7" t="inlineStr">
@@ -9066,7 +9066,7 @@
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>PREM-22</t>
+          <t>PREM-20</t>
         </is>
       </c>
       <c r="B209" s="7" t="inlineStr">
@@ -9081,17 +9081,17 @@
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>Cancelling the StoreKit sheet shows nothing</t>
+          <t>Sandbox purchase unlocks Premium via the webhook</t>
         </is>
       </c>
       <c r="E209" s="9" t="inlineStr">
         <is>
-          <t>Tap Go Premium, then cancel/dismiss the Apple payment sheet.</t>
+          <t>Signed in with a sandbox Apple ID, tap Go Premium, complete the StoreKit sheet.</t>
         </is>
       </c>
       <c r="F209" s="9" t="inlineStr">
         <is>
-          <t>The app shows nothing at all: no error, no message, no toast. The user simply backed out. (Every OTHER failure does show a calm specific line: pending, already-owned, not-allowed, store-down.)</t>
+          <t>The StoreKit sheet appears, the sandbox payment succeeds, the calm 'setting up' beat shows, then Premium flips on within ~20s (the RevenueCat webhook writes D1, the success-poll picks it up). Apple's accelerated sandbox clock then renews it several times and expires it, exercising the whole INITIAL_PURCHASE -&gt; RENEWAL -&gt; EXPIRATION chain against the real Worker. Prerequisite: the Worker deployed with RC_WEBHOOK_AUTH and the RevenueCat dashboard webhook set to the same secret.</t>
         </is>
       </c>
       <c r="G209" s="7" t="inlineStr">
@@ -9106,7 +9106,7 @@
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>PREM-23</t>
+          <t>PREM-21</t>
         </is>
       </c>
       <c r="B210" s="7" t="inlineStr">
@@ -9121,17 +9121,17 @@
       </c>
       <c r="D210" s="9" t="inlineStr">
         <is>
-          <t>Restore works with no account at all, and always answers honestly</t>
+          <t>A Stripe web subscriber is NEVER charged again on iOS</t>
         </is>
       </c>
       <c r="E210" s="9" t="inlineStr">
         <is>
-          <t>Tap 'Restore a purchase' while signed out, on an Apple ID WITH a prior purchase. Then signed out on an Apple ID with NO purchase. Then repeat signed in.</t>
+          <t>As a user who already subscribed to Premium on the website (Stripe), install on iPhone, open Premium, and sign in with that same account.</t>
         </is>
       </c>
       <c r="F210" s="9" t="inlineStr">
         <is>
-          <t>No sign-in is ever required (5.1.1: the receipt lives with the Apple ID, and the device's own entitlement now unlocks Premium locally). With a purchase -&gt; 'Restored. Premium is back on.' and Premium turns on, account or not. With nothing -&gt; 'Nothing to restore on this Apple ID...' It is NEVER a silent no-op (Apple rejects a restore that appears to do nothing).</t>
+          <t>The screen shows the Premium (active) panel with NO buy button, so a second charge is impossible. Even if the buy button were reachable mid-load, the fresh entitlement read before buy() bails to the active panel. This is the double-charge guard, and the single most important iOS case.</t>
         </is>
       </c>
       <c r="G210" s="7" t="inlineStr">
@@ -9146,7 +9146,7 @@
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>PREM-24</t>
+          <t>PREM-22</t>
         </is>
       </c>
       <c r="B211" s="7" t="inlineStr">
@@ -9154,24 +9154,24 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C211" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
-          <t>Manage subscription opens Apple's sheet, not a browser</t>
+          <t>Cancelling the StoreKit sheet shows nothing</t>
         </is>
       </c>
       <c r="E211" s="9" t="inlineStr">
         <is>
-          <t>As an Apple subscriber on the iPhone, open Premium and tap Manage subscription.</t>
+          <t>Tap Go Premium, then cancel/dismiss the Apple payment sheet.</t>
         </is>
       </c>
       <c r="F211" s="9" t="inlineStr">
         <is>
-          <t>Apple's own Manage Subscriptions sheet opens in-app. It never opens a browser or the Stripe portal.</t>
+          <t>The app shows nothing at all: no error, no message, no toast. The user simply backed out. (Every OTHER failure does show a calm specific line: pending, already-owned, not-allowed, store-down.)</t>
         </is>
       </c>
       <c r="G211" s="7" t="inlineStr">
@@ -9186,7 +9186,7 @@
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>PREM-25</t>
+          <t>PREM-23</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
@@ -9194,29 +9194,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C212" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C212" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D212" s="9" t="inlineStr">
         <is>
-          <t>An Apple subscriber on the web sees 'Apple handles it', not a portal error</t>
+          <t>Restore works with no account at all, and always answers honestly</t>
         </is>
       </c>
       <c r="E212" s="9" t="inlineStr">
         <is>
-          <t>As a user whose Premium was bought on iPhone, open the web app, go to Premium, tap Manage subscription.</t>
+          <t>Tap 'Restore a purchase' while signed out, on an Apple ID WITH a prior purchase. Then signed out on an Apple ID with NO purchase. Then repeat signed in.</t>
         </is>
       </c>
       <c r="F212" s="9" t="inlineStr">
         <is>
-          <t>The app says the subscription is managed in Apple's settings on the device it was bought on. It does NOT 404 the Stripe billing portal or show 'Could not open the billing portal' (the bug the entitlement source column exists to fix).</t>
+          <t>No sign-in is ever required (5.1.1: the receipt lives with the Apple ID, and the device's own entitlement now unlocks Premium locally). With a purchase -&gt; 'Restored. Premium is back on.' and Premium turns on, account or not. With nothing -&gt; 'Nothing to restore on this Apple ID...' It is NEVER a silent no-op (Apple rejects a restore that appears to do nothing).</t>
         </is>
       </c>
       <c r="G212" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="H212" s="7" t="inlineStr"/>
@@ -9226,37 +9226,37 @@
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>SETL-01</t>
+          <t>PREM-24</t>
         </is>
       </c>
       <c r="B213" s="7" t="inlineStr">
         <is>
-          <t>Settle</t>
-        </is>
-      </c>
-      <c r="C213" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="C213" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>The breathing room: rhythm, words, and the never-rules</t>
+          <t>Manage subscription opens Apple's sheet, not a browser</t>
         </is>
       </c>
       <c r="E213" s="9" t="inlineStr">
         <is>
-          <t>Open the day tools and tap Settle. Sit with it for a full minute. Toggle the guide pill off and wait ~90 seconds. Leave. Re-enter.</t>
+          <t>As an Apple subscriber on the iPhone, open Premium and tap Manage subscription.</t>
         </is>
       </c>
       <c r="F213" s="9" t="inlineStr">
         <is>
-          <t>The room holds ONLY: Leave (top-left), the breathing blob, one word slot, and the guide pill (reads 'Breathing guide · on/off'). NO title, NO timer or duration anywhere, NO stats, NO paywall or lock (free, unlimited, forever). The blob swells ~4s, holds ~1.5s, settles ~6.5s, on a loop, BRIGHTENING as it fills (an inner glow blooms at the top of the in-breath) and dimming as it empties; guide ON fades the three literal words in and out in phase ('in, gently…' / 'rest here' / 'slowly out…'), each breath wearing the next Dusk accent like Today's inscription, never a hard swap. Guide OFF: words stop, and at most one affirmation appears every 30-60s (seven lines rotating in order), fading in over ~3s and gone within 12, never stacking, never praising, its colour FROZEN for its whole display (never flipping when the breath advances the accent cycle). The toggle is REMEMBERED across visits. Leaving fades out on the out-breath (≤800ms) with 'Today is where you left it.', then Today exactly as left: no summary, no toast.</t>
+          <t>Apple's own Manage Subscriptions sheet opens in-app. It never opens a browser or the Stripe portal.</t>
         </is>
       </c>
       <c r="G213" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="H213" s="7" t="inlineStr"/>
@@ -9266,32 +9266,32 @@
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
         <is>
-          <t>SETL-02</t>
+          <t>PREM-25</t>
         </is>
       </c>
       <c r="B214" s="7" t="inlineStr">
         <is>
-          <t>Settle</t>
-        </is>
-      </c>
-      <c r="C214" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="C214" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D214" s="9" t="inlineStr">
         <is>
-          <t>Settle's two doors: the tools panel and the wind-down evening line</t>
+          <t>An Apple subscriber on the web sees 'Apple handles it', not a portal error</t>
         </is>
       </c>
       <c r="E214" s="9" t="inlineStr">
         <is>
-          <t>Open the day-tools caret at any hour and read the order. Then after ~19:00, look under the wind-down line. Also check with AI off.</t>
+          <t>As a user whose Premium was bought on iPhone, open the web app, go to Premium, tap Manage subscription.</t>
         </is>
       </c>
       <c r="F214" s="9" t="inlineStr">
         <is>
-          <t>The panel order is fixed forever: Plan my day, Focus on one thing, Lighten today, Settle, Close the day (AI off: Focus, Settle, Close). Settle renders as plainly as its neighbours, is NEVER the 'Right now' occupant at any hour, is never gated or locked, and the app NEVER opens it by itself. In the evening one soft italic line sits under the wind-down text ('If today is still loud, there's room to settle first.') and opens the room.</t>
+          <t>The app says the subscription is managed in Apple's settings on the device it was bought on. It does NOT 404 the Stripe billing portal or show 'Could not open the billing portal' (the bug the entitlement source column exists to fix).</t>
         </is>
       </c>
       <c r="G214" s="7" t="inlineStr">
@@ -9306,7 +9306,7 @@
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>SETL-03</t>
+          <t>SETL-01</t>
         </is>
       </c>
       <c r="B215" s="7" t="inlineStr">
@@ -9314,24 +9314,24 @@
           <t>Settle</t>
         </is>
       </c>
-      <c r="C215" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C215" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>The haptic breath and the reduce-motion room (device only)</t>
+          <t>The breathing room: rhythm, words, and the never-rules</t>
         </is>
       </c>
       <c r="E215" s="9" t="inlineStr">
         <is>
-          <t>On a phone, enter Settle and hold the phone: feel for one light tap at the swell and two tiny taps ~300ms apart at the settle, nothing during the still. Turn the phone face-down and keep feeling. Then enable OS reduce-motion and re-enter.</t>
+          <t>Open the day tools and tap Settle. Sit with it for a full minute. Toggle the guide pill off and wait ~90 seconds. Leave. Re-enter.</t>
         </is>
       </c>
       <c r="F215" s="9" t="inlineStr">
         <is>
-          <t>The haptic breath marks the phases and keeps working face-down and after the screen dims (no keep-awake, deliberately). Under reduce-motion the blob's GEOMETRY holds still and only its warmth breathes (or the room sits fully still), while the haptics and guide words carry the whole rhythm: the reduce-motion room is a designed variant, not a broken one. This is the ONE surface whose haptics do not silence under reduce-motion, by design.</t>
+          <t>The room holds ONLY: Leave (top-left), the breathing blob, one word slot, and the guide pill (reads 'Breathing guide · on/off'). NO title, NO timer or duration anywhere, NO stats, NO paywall or lock (free, unlimited, forever). The blob swells ~4s, holds ~1.5s, settles ~6.5s, on a loop, BRIGHTENING as it fills (an inner glow blooms at the top of the in-breath) and dimming as it empties; guide ON fades the three literal words in and out in phase ('in, gently…' / 'rest here' / 'slowly out…'), each breath wearing the next Dusk accent like Today's inscription, never a hard swap. Guide OFF: words stop, and at most one affirmation appears every 30-60s (seven lines rotating in order), fading in over ~3s and gone within 12, never stacking, never praising, its colour FROZEN for its whole display (never flipping when the breath advances the accent cycle). The toggle is REMEMBERED across visits. Leaving fades out on the out-breath (≤800ms) with 'Today is where you left it.', then Today exactly as left: no summary, no toast.</t>
         </is>
       </c>
       <c r="G215" s="7" t="inlineStr">
@@ -9346,32 +9346,32 @@
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
         <is>
-          <t>WN-01</t>
+          <t>SETL-02</t>
         </is>
       </c>
       <c r="B216" s="7" t="inlineStr">
         <is>
-          <t>What's new</t>
-        </is>
-      </c>
-      <c r="C216" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Settle</t>
+        </is>
+      </c>
+      <c r="C216" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D216" s="9" t="inlineStr">
         <is>
-          <t>The What's new card appears once, and is dismissible</t>
+          <t>Settle's two doors: the tools panel and the wind-down evening line</t>
         </is>
       </c>
       <c r="E216" s="9" t="inlineStr">
         <is>
-          <t>Open Today after a version whose WHATS_NEW id has bumped.</t>
+          <t>Open the day-tools caret at any hour and read the order. Then after ~19:00, look under the wind-down line. Also check with AI off.</t>
         </is>
       </c>
       <c r="F216" s="9" t="inlineStr">
         <is>
-          <t>A calm card at the top of Today, never a modal. The Ours entry runs to FOUR lines where earlier ones took two, which is the difference between a change and a surface: what it is, why it cannot become a scoreboard, why it cannot make your day heavier, and where to find it. One tap on Got it retires it forever.</t>
+          <t>The panel order is fixed forever: Plan my day, Focus on one thing, Lighten today, Settle, Close the day (AI off: Focus, Settle, Close). Settle renders as plainly as its neighbours, is NEVER the 'Right now' occupant at any hour, is never gated or locked, and the app NEVER opens it by itself. In the evening one soft italic line sits under the wind-down text ('If today is still loud, there's room to settle first.') and opens the room.</t>
         </is>
       </c>
       <c r="G216" s="7" t="inlineStr">
@@ -9386,12 +9386,12 @@
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>WEB-02</t>
+          <t>SETL-03</t>
         </is>
       </c>
       <c r="B217" s="7" t="inlineStr">
         <is>
-          <t>Web landing</t>
+          <t>Settle</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
@@ -9401,22 +9401,22 @@
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>The landing page carries both store badges, web only</t>
+          <t>The haptic breath and the reduce-motion room (device only)</t>
         </is>
       </c>
       <c r="E217" s="9" t="inlineStr">
         <is>
-          <t>As a fresh (not-onboarded) web visitor open doubledone.app and scroll to the closing section. Tap each badge. Also open the app on Android and iOS and confirm the landing never appears there.</t>
+          <t>On a phone, enter Settle and hold the phone: feel for one light tap at the swell and two tiny taps ~300ms apart at the settle, nothing during the still. Turn the phone face-down and keep feeling. Then enable OS reduce-motion and re-enter.</t>
         </is>
       </c>
       <c r="F217" s="9" t="inlineStr">
         <is>
-          <t>Official 'Download on the App Store' and 'Get it on Google Play' badges sit under the Begin button, visually equal in the row, with the Google-required trademark line in small print beneath. Each opens the correct store listing (country-less links, so every visitor lands on their own storefront in their own language). On native the landing redirects to Today before rendering, so the Play badge can never appear inside the iOS app (App Review would reject it). Screen readers hear the localised badge labels.</t>
+          <t>The haptic breath marks the phases and keeps working face-down and after the screen dims (no keep-awake, deliberately). Under reduce-motion the blob's GEOMETRY holds still and only its warmth breathes (or the room sits fully still), while the haptics and guide words carry the whole rhythm: the reduce-motion room is a designed variant, not a broken one. This is the ONE surface whose haptics do not silence under reduce-motion, by design.</t>
         </is>
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H217" s="7" t="inlineStr"/>
@@ -9426,12 +9426,12 @@
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>ANA-01</t>
+          <t>WN-01</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>What's new</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
@@ -9441,18 +9441,22 @@
       </c>
       <c r="D218" s="9" t="inlineStr">
         <is>
-          <t>The Analytics Centre is token-gated, read-only, and answers the four questions</t>
-        </is>
-      </c>
-      <c r="E218" s="9" t="inlineStr"/>
+          <t>The What's new card appears once, and is dismissible</t>
+        </is>
+      </c>
+      <c r="E218" s="9" t="inlineStr">
+        <is>
+          <t>Open Today after a version whose WHATS_NEW id has bumped.</t>
+        </is>
+      </c>
       <c r="F218" s="9" t="inlineStr">
         <is>
-          <t>GET /admin/analytics with no token -&gt; 401 (or 503 if ANALYTICS_TOKEN is unset: an undeployed secret is never an open page). With ?token=&lt;secret&gt; -&gt; a server-rendered Dusk page showing: premium counts by store and status plus active trials (Money), month-to-date AI spend with the month-end projection against the cap (AI spend), decompositions offered vs came-back-with-a-finished-step plus the median days to the first step (The moat), and keepsakes made in 28 days (Scrapbooks). No JavaScript, cache-control no-store, x-robots-tag noindex. Covered by analytics.test.ts; re-confirm once on the deployed Worker.</t>
+          <t>A calm card at the top of Today, never a modal. The Ours entry runs to FOUR lines where earlier ones took two, which is the difference between a change and a surface: what it is, why it cannot become a scoreboard, why it cannot make your day heavier, and where to find it. One tap on Got it retires it forever.</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>Worker</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H218" s="7" t="inlineStr"/>
@@ -9462,33 +9466,37 @@
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>PREM-26</t>
+          <t>WEB-02</t>
         </is>
       </c>
       <c r="B219" s="7" t="inlineStr">
         <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="C219" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Web landing</t>
+        </is>
+      </c>
+      <c r="C219" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>RevenueCat webhook rejects a wrong Authorization header</t>
-        </is>
-      </c>
-      <c r="E219" s="9" t="inlineStr"/>
+          <t>The landing page carries both store badges, web only</t>
+        </is>
+      </c>
+      <c r="E219" s="9" t="inlineStr">
+        <is>
+          <t>As a fresh (not-onboarded) web visitor open doubledone.app and scroll to the closing section. Tap each badge. Also open the app on Android and iOS and confirm the landing never appears there.</t>
+        </is>
+      </c>
       <c r="F219" s="9" t="inlineStr">
         <is>
-          <t>POST /rc-webhook with a wrong Authorization header returns 401 and writes nothing to D1. With no RC_WEBHOOK_AUTH configured it returns 503. (Covered by revenuecat.test.ts; re-confirm on the deployed Worker.)</t>
+          <t>Official 'Download on the App Store' and 'Get it on Google Play' badges sit under the Begin button, visually equal in the row, with the Google-required trademark line in small print beneath. Each opens the correct store listing (country-less links, so every visitor lands on their own storefront in their own language). On native the landing redirects to Today before rendering, so the Play badge can never appear inside the iOS app (App Review would reject it). Screen readers hear the localised badge labels.</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
-          <t>Worker</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H219" s="7" t="inlineStr"/>
@@ -9498,32 +9506,28 @@
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>PREM-27</t>
+          <t>ANA-01</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
         <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="C220" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="C220" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D220" s="9" t="inlineStr">
         <is>
-          <t>CANCELLATION keeps Premium on; EXPIRATION ends it</t>
-        </is>
-      </c>
-      <c r="E220" s="9" t="inlineStr">
-        <is>
-          <t>Trigger (or replay) a RevenueCat CANCELLATION event for a subscriber, then an EXPIRATION.</t>
-        </is>
-      </c>
+          <t>The Analytics Centre is token-gated, read-only, and answers the four questions</t>
+        </is>
+      </c>
+      <c r="E220" s="9" t="inlineStr"/>
       <c r="F220" s="9" t="inlineStr">
         <is>
-          <t>CANCELLATION leaves premium ON and the app reads 'Premium until {date}' (auto-renew off, access to period end), NOT an immediate revoke. A later EXPIRATION (with its date in the past) flips it to free and preserves the tenure start. A CUSTOMER_SUPPORT cancellation (a refund) DOES revoke immediately. (Locked by revenuecat.test.ts.)</t>
+          <t>GET /admin/analytics with no token -&gt; 401 (or 503 if ANALYTICS_TOKEN is unset: an undeployed secret is never an open page). With ?token=&lt;secret&gt; -&gt; a server-rendered Dusk page showing: premium counts by store and status plus active trials (Money), month-to-date AI spend with the month-end projection against the cap (AI spend), decompositions offered vs came-back-with-a-finished-step plus the median days to the first step (The moat), and keepsakes made in 28 days (Scrapbooks). No JavaScript, cache-control no-store, x-robots-tag noindex. Covered by analytics.test.ts; re-confirm once on the deployed Worker.</t>
         </is>
       </c>
       <c r="G220" s="7" t="inlineStr">
@@ -9538,7 +9542,7 @@
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>PREM-28</t>
+          <t>PREM-26</t>
         </is>
       </c>
       <c r="B221" s="7" t="inlineStr">
@@ -9546,24 +9550,20 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C221" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C221" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>A redelivered RevenueCat event is a no-op</t>
-        </is>
-      </c>
-      <c r="E221" s="9" t="inlineStr">
-        <is>
-          <t>Deliver the same RevenueCat event id twice.</t>
-        </is>
-      </c>
+          <t>RevenueCat webhook rejects a wrong Authorization header</t>
+        </is>
+      </c>
+      <c r="E221" s="9" t="inlineStr"/>
       <c r="F221" s="9" t="inlineStr">
         <is>
-          <t>The second delivery changes nothing (idempotent on the rc: namespaced event id, so it can never collide with a Stripe evt_ id). A dedup-store hiccup still writes (fail open), because the entitlement write is an idempotent upsert.</t>
+          <t>POST /rc-webhook with a wrong Authorization header returns 401 and writes nothing to D1. With no RC_WEBHOOK_AUTH configured it returns 503. (Covered by revenuecat.test.ts; re-confirm on the deployed Worker.)</t>
         </is>
       </c>
       <c r="G221" s="7" t="inlineStr">
@@ -9578,7 +9578,7 @@
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
         <is>
-          <t>PREM-35</t>
+          <t>PREM-27</t>
         </is>
       </c>
       <c r="B222" s="7" t="inlineStr">
@@ -9593,22 +9593,22 @@
       </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
-          <t>Every RevenueCat delivery lands in the rc_events audit log</t>
+          <t>CANCELLATION keeps Premium on; EXPIRATION ends it</t>
         </is>
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>After a Worker deploy, make any Apple subscription change (or replay an event from the RevenueCat dashboard). Then run the three queries in docs/operations.md against the rc_events table.</t>
+          <t>Trigger (or replay) a RevenueCat CANCELLATION event for a subscriber, then an EXPIRATION.</t>
         </is>
       </c>
       <c r="F222" s="9" t="inlineStr">
         <is>
-          <t>Every delivery is logged, including the ones the webhook deliberately ignores, each with an `outcome` saying why: applied, duplicate, transfer, unresolved-user, other-entitlement, stale-expiration, sandbox, no-op. `period_type` and `environment` are both captured, which is the whole point: 'was that a trial or a real charge, and was it even production' must be answerable from our own database in one query, without opening RevenueCat or App Store Connect. An ANONYMOUS purchase (no Supabase id) writes no entitlement row, as before, but now leaves a row here with user_id NULL, so a paying customer can never again be invisible to us. Breaking the table (or deploying before it exists) must NOT break the webhook: premium still gets granted, because the log fails silently by design.</t>
+          <t>CANCELLATION leaves premium ON and the app reads 'Premium until {date}' (auto-renew off, access to period end), NOT an immediate revoke. A later EXPIRATION (with its date in the past) flips it to free and preserves the tenure start. A CUSTOMER_SUPPORT cancellation (a refund) DOES revoke immediately. (Locked by revenuecat.test.ts.)</t>
         </is>
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Worker</t>
         </is>
       </c>
       <c r="H222" s="7" t="inlineStr"/>
@@ -9618,7 +9618,7 @@
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>PREM-36</t>
+          <t>PREM-28</t>
         </is>
       </c>
       <c r="B223" s="7" t="inlineStr">
@@ -9626,29 +9626,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C223" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C223" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>A TestFlight (sandbox) purchase never grants server-side Premium</t>
+          <t>A redelivered RevenueCat event is a no-op</t>
         </is>
       </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>On a TestFlight build, buy Premium with a sandbox Apple ID. Then check the D1 entitlements table for that user, and the rc_events log. Also confirm what the app itself shows on that device.</t>
+          <t>Deliver the same RevenueCat event id twice.</t>
         </is>
       </c>
       <c r="F223" s="9" t="inlineStr">
         <is>
-          <t>The webhook answers 200 with {received:true, sandbox:true} and writes NO entitlements row: sandbox money is not money, and before this guard a TestFlight build could grant itself real Premium. The delivery IS logged in rc_events with outcome 'sandbox', so testing stays visible rather than becoming a blind spot. The tester still SEES Premium on their device, because RevenueCat grants the entitlement locally and the client merges that over the server's answer, so testing the paid surface still works. A real PRODUCTION purchase is unaffected. And a sandbox event for someone who is already a genuine paying subscriber must leave them exactly as they were: ignoring, rather than writing premium=0, is what makes that true.</t>
+          <t>The second delivery changes nothing (idempotent on the rc: namespaced event id, so it can never collide with a Stripe evt_ id). A dedup-store hiccup still writes (fail open), because the entitlement write is an idempotent upsert.</t>
         </is>
       </c>
       <c r="G223" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Worker</t>
         </is>
       </c>
       <c r="H223" s="7" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>PREM-37</t>
+          <t>PREM-35</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
@@ -9673,22 +9673,22 @@
       </c>
       <c r="D224" s="9" t="inlineStr">
         <is>
-          <t>An anonymous Apple subscriber gets the tenure they paid for</t>
+          <t>Every RevenueCat delivery lands in the rc_events audit log</t>
         </is>
       </c>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>On iOS, buy Premium WITHOUT signing in (the App Review 5.1.1 path). Wait, or use an account whose Apple subscription is months old. Open Premium and read the panel, then open the Scrapbook and check how many keepsakes are offered this week.</t>
+          <t>After a Worker deploy, make any Apple subscription change (or replay an event from the RevenueCat dashboard). Then run the three queries in docs/operations.md against the rc_events table.</t>
         </is>
       </c>
       <c r="F224" s="9" t="inlineStr">
         <is>
-          <t>The renewal date is shown ('Renews {date}'), where before an anonymous buyer saw 'You are Premium' and was never told when they would next be charged. And the weekly keepsake allowance scales with the REAL tenure of the Apple subscription (1/week, 2 after two months, 4 after six), not the 1/week floor. The old code merged only a boolean from the device, so `since` stayed null and every anonymous subscriber sat on 1/week forever: the same money for a quarter of the product. A lifetime or non-expiring entitlement must NOT be shown as a scheduled cancel.</t>
+          <t>Every delivery is logged, including the ones the webhook deliberately ignores, each with an `outcome` saying why: applied, duplicate, transfer, unresolved-user, other-entitlement, stale-expiration, sandbox, no-op. `period_type` and `environment` are both captured, which is the whole point: 'was that a trial or a real charge, and was it even production' must be answerable from our own database in one query, without opening RevenueCat or App Store Connect. An ANONYMOUS purchase (no Supabase id) writes no entitlement row, as before, but now leaves a row here with user_id NULL, so a paying customer can never again be invisible to us. Breaking the table (or deploying before it exists) must NOT break the webhook: premium still gets granted, because the log fails silently by design.</t>
         </is>
       </c>
       <c r="G224" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="H224" s="7" t="inlineStr"/>
@@ -9698,7 +9698,7 @@
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>PREM-38</t>
+          <t>PREM-36</t>
         </is>
       </c>
       <c r="B225" s="7" t="inlineStr">
@@ -9706,24 +9706,24 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C225" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>The free month is not sitting under the buy button on iOS</t>
+          <t>A TestFlight (sandbox) purchase never grants server-side Premium</t>
         </is>
       </c>
       <c r="E225" s="9" t="inlineStr">
         <is>
-          <t>On iOS, signed in, open Premium as a free user. Look at what is directly under 'Go Premium'. Then scroll to the bottom of the Apple block. Repeat signed OUT, and repeat on web or Android.</t>
+          <t>On a TestFlight build, buy Premium with a sandbox Apple ID. Then check the D1 entitlements table for that user, and the rc_events log. Also confirm what the app itself shows on that device.</t>
         </is>
       </c>
       <c r="F225" s="9" t="inlineStr">
         <is>
-          <t>Signed in on iOS the free-month offer is NOT beneath the buy button any more: it sits in its own zone at the bottom, above a rule, with 'No card, no charge, and it never becomes a subscription on its own.' under it. It is still THERE and still one tap, because hiding it would move a genuinely free offer somewhere an iPhone user would never look. Signed OUT it does not render at all on any platform, since starting a trial can only answer 'sign in' there and we never show a control whose only outcome is an error. On web and Android it stays exactly where it was, inline, because nothing on that screen can take money without a Stripe redirect. The copy no longer opens with 'Or' in any of the five locales, which only parsed as an alternative to whatever sat above it.</t>
+          <t>The webhook answers 200 with {received:true, sandbox:true} and writes NO entitlements row: sandbox money is not money, and before this guard a TestFlight build could grant itself real Premium. The delivery IS logged in rc_events with outcome 'sandbox', so testing stays visible rather than becoming a blind spot. The tester still SEES Premium on their device, because RevenueCat grants the entitlement locally and the client merges that over the server's answer, so testing the paid surface still works. A real PRODUCTION purchase is unaffected. And a sandbox event for someone who is already a genuine paying subscriber must leave them exactly as they were: ignoring, rather than writing premium=0, is what makes that true.</t>
         </is>
       </c>
       <c r="G225" s="7" t="inlineStr">
@@ -9738,7 +9738,7 @@
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>PREM-39</t>
+          <t>PREM-37</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
@@ -9753,17 +9753,17 @@
       </c>
       <c r="D226" s="9" t="inlineStr">
         <is>
-          <t>An anonymous Apple purchase attaches itself when you sign in</t>
+          <t>An anonymous Apple subscriber gets the tenure they paid for</t>
         </is>
       </c>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>On iOS, buy Premium WITHOUT signing in. Confirm the D1 entitlements table has NO row for you. Then sign in inside the app. Wait a moment, then re-check D1, and open Premium on a SECOND device (or the web app) signed into the same account.</t>
+          <t>On iOS, buy Premium WITHOUT signing in (the App Review 5.1.1 path). Wait, or use an account whose Apple subscription is months old. Open Premium and read the panel, then open the Scrapbook and check how many keepsakes are offered this week.</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
         <is>
-          <t>Signing in calls RevenueCat's logIn, which aliases the Supabase id onto the anonymous customer, and the app then asks POST /apple/reconcile to look once. An entitlements row appears with source='apple' and the real period end, WITHOUT waiting for the next renewal webhook (which could be a month away, and might arrive as a TRANSFER we deliberately do not act on). Premium then works on the second device and on web. Before this, an anonymous buyer was invisible to us: no renewal date, no tenure-scaled keepsakes anywhere else, and no way for us to answer a support question about their own money.</t>
+          <t>The renewal date is shown ('Renews {date}'), where before an anonymous buyer saw 'You are Premium' and was never told when they would next be charged. And the weekly keepsake allowance scales with the REAL tenure of the Apple subscription (1/week, 2 after two months, 4 after six), not the 1/week floor. The old code merged only a boolean from the device, so `since` stayed null and every anonymous subscriber sat on 1/week forever: the same money for a quarter of the product. A lifetime or non-expiring entitlement must NOT be shown as a scheduled cancel.</t>
         </is>
       </c>
       <c r="G226" s="7" t="inlineStr">
@@ -9778,7 +9778,7 @@
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>PREM-40</t>
+          <t>PREM-38</t>
         </is>
       </c>
       <c r="B227" s="7" t="inlineStr">
@@ -9786,29 +9786,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C227" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C227" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>Reconcile cannot be used to claim somebody else's subscription</t>
+          <t>The free month is not sitting under the buy button on iOS</t>
         </is>
       </c>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>Signed in as a free account with no Apple purchase, sign in and watch the network call to /apple/reconcile. Try calling it by hand with no token, with a junk token, and with a body naming another user's id or a product.</t>
+          <t>On iOS, signed in, open Premium as a free user. Look at what is directly under 'Go Premium'. Then scroll to the bottom of the Apple block. Repeat signed OUT, and repeat on web or Android.</t>
         </is>
       </c>
       <c r="F227" s="9" t="inlineStr">
         <is>
-          <t>The request carries NO body at all: the server uses the cryptographically verified `sub` from your own Supabase token and asks RevenueCat about exactly that App User ID, so a caller can only ever reconcile themselves, and only into a purchase RevenueCat already agrees is theirs. No token or a forged one answers 401 and writes nothing. A free account gets a calm {attached:false} rather than an error, because that is the ordinary answer for every web user, every Android user and every free iOS user. A sandbox/TestFlight subscription is refused, so a tester cannot mint real Premium. A RevenueCat outage answers 502, NOT {attached:false}, because reporting an outage as 'you have no subscription' would read as a downgrade.</t>
+          <t>Signed in on iOS the free-month offer is NOT beneath the buy button any more: it sits in its own zone at the bottom, above a rule, with 'No card, no charge, and it never becomes a subscription on its own.' under it. It is still THERE and still one tap, because hiding it would move a genuinely free offer somewhere an iPhone user would never look. Signed OUT it does not render at all on any platform, since starting a trial can only answer 'sign in' there and we never show a control whose only outcome is an error. On web and Android it stays exactly where it was, inline, because nothing on that screen can take money without a Stripe redirect. The copy no longer opens with 'Or' in any of the five locales, which only parsed as an alternative to whatever sat above it.</t>
         </is>
       </c>
       <c r="G227" s="7" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H227" s="7" t="inlineStr"/>
@@ -9818,7 +9818,7 @@
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
         <is>
-          <t>PREM-29</t>
+          <t>PREM-39</t>
         </is>
       </c>
       <c r="B228" s="7" t="inlineStr">
@@ -9833,22 +9833,22 @@
       </c>
       <c r="D228" s="9" t="inlineStr">
         <is>
-          <t>The Android AAB does NOT contain Google Play Billing</t>
+          <t>An anonymous Apple purchase attaches itself when you sign in</t>
         </is>
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>Build the Android AAB, unzip it, and grep for com.android.billingclient. Also confirm the app still builds, installs, and Premium still sells via Stripe on Android.</t>
+          <t>On iOS, buy Premium WITHOUT signing in. Confirm the D1 entitlements table has NO row for you. Then sign in inside the app. Wait a moment, then re-check D1, and open Premium on a SECOND device (or the web app) signed into the same account.</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
         <is>
-          <t>react-native-purchases (and Play Billing) is absent from the AAB: the expo.autolinking.android.exclude in client/package.json drops it. Android Premium is unchanged (Stripe Checkout in the browser). This is the regression guard on adding the native module.</t>
+          <t>Signing in calls RevenueCat's logIn, which aliases the Supabase id onto the anonymous customer, and the app then asks POST /apple/reconcile to look once. An entitlements row appears with source='apple' and the real period end, WITHOUT waiting for the next renewal webhook (which could be a month away, and might arrive as a TRANSFER we deliberately do not act on). Premium then works on the second device and on web. Before this, an anonymous buyer was invisible to us: no renewal date, no tenure-scaled keepsakes anywhere else, and no way for us to answer a support question about their own money.</t>
         </is>
       </c>
       <c r="G228" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H228" s="7" t="inlineStr"/>
@@ -9858,7 +9858,7 @@
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>PREM-30</t>
+          <t>PREM-40</t>
         </is>
       </c>
       <c r="B229" s="7" t="inlineStr">
@@ -9873,22 +9873,22 @@
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>The web build is unchanged and still sells via Stripe</t>
+          <t>Reconcile cannot be used to claim somebody else's subscription</t>
         </is>
       </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>Build the production web export (expo export --platform web). Open /premium on web.</t>
+          <t>Signed in as a free account with no Apple purchase, sign in and watch the network call to /apple/reconcile. Try calling it by hand with no token, with a junk token, and with a body naming another user's id or a product.</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>The export succeeds (the native purchases module never enters the web bundle, proving the purchases.ts / purchases.ios.ts split). The web paywall shows the catalog price, the 'Billed securely via Stripe' line, NO Restore control, and the Stripe checkout path is unchanged. The regression guard on the paywall rewrite.</t>
+          <t>The request carries NO body at all: the server uses the cryptographically verified `sub` from your own Supabase token and asks RevenueCat about exactly that App User ID, so a caller can only ever reconcile themselves, and only into a purchase RevenueCat already agrees is theirs. No token or a forged one answers 401 and writes nothing. A free account gets a calm {attached:false} rather than an error, because that is the ordinary answer for every web user, every Android user and every free iOS user. A sandbox/TestFlight subscription is refused, so a tester cannot mint real Premium. A RevenueCat outage answers 502, NOT {attached:false}, because reporting an outage as 'you have no subscription' would read as a downgrade.</t>
         </is>
       </c>
       <c r="G229" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="H229" s="7" t="inlineStr"/>
@@ -9898,7 +9898,7 @@
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
         <is>
-          <t>PREM-32</t>
+          <t>PREM-29</t>
         </is>
       </c>
       <c r="B230" s="7" t="inlineStr">
@@ -9913,22 +9913,22 @@
       </c>
       <c r="D230" s="9" t="inlineStr">
         <is>
-          <t>PRODUCTION paywall price matches App Store Connect</t>
+          <t>The Android AAB does NOT contain Google Play Billing</t>
         </is>
       </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>After the app is RELEASED, install it from the App Store (not TestFlight) on an Australian account and open Premium. Read the monthly and annual prices.</t>
+          <t>Build the Android AAB, unzip it, and grep for com.android.billingclient. Also confirm the app still builds, installs, and Premium still sells via Stripe on Android.</t>
         </is>
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>The paywall reads A$5.00 / month and A$50.00 / year, matching the App Store Connect price schedule for Australia, and matching what Apple's purchase sheet charges. CRITICAL: TestFlight and sandbox CANNOT verify this. They are known to answer product queries for the US storefront regardless of the account's real region, so a TestFlight paywall showing US dollars is expected and is NOT the bug. Only a production App Store install proves it. If production still disagrees with the sheet, that is a misleading pre-purchase price (an Australian Consumer Law problem, not just a display bug): pull the release via Pricing and Availability, Remove from sale. Prerequisite: app released. Gate the RELEASE on this, never the submission.</t>
+          <t>react-native-purchases (and Play Billing) is absent from the AAB: the expo.autolinking.android.exclude in client/package.json drops it. Android Premium is unchanged (Stripe Checkout in the browser). This is the regression guard on adding the native module.</t>
         </is>
       </c>
       <c r="G230" s="7" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H230" s="7" t="inlineStr"/>
@@ -9938,7 +9938,7 @@
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>PREM-33</t>
+          <t>PREM-30</t>
         </is>
       </c>
       <c r="B231" s="7" t="inlineStr">
@@ -9953,22 +9953,22 @@
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>A dunning subscriber is never sold a second subscription</t>
+          <t>The web build is unchanged and still sells via Stripe</t>
         </is>
       </c>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>Put a test Stripe subscription into past_due (in Stripe test mode: attach a failing card, or use the test clock to fail a renewal). Open /premium signed in as that user. Read the panel, then try to buy.</t>
+          <t>Build the production web export (expo export --platform web). Open /premium on web.</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
         <is>
-          <t>Access has lapsed so the UPSELL panel shows, but with a calm notice at the top: 'Your Premium is paused while a payment retries. Updating your card brings it back. There is no need to buy again.' with an 'Update payment details' link that opens the Stripe portal (the customer id exists in this state). If the user taps Go Premium anyway, the server refuses with 409 billing_issue and the app explains the card is the fix, NEVER 'You're already on Premium' (false: they are not) and NEVER a second Checkout. REGRESSION GUARDS on the same server change (locked by stripe.test.ts): a LAPSED subscriber (status canceled, customer id kept) can still re-subscribe via a fresh Checkout, an abandoned checkout (incomplete) can still buy, and a trial still converts. The old guard keyed on premium &amp;&amp; customerId, so a past_due user could mint a SECOND subscription whose webhook overwrote stripe_customer_id and orphaned the first: paying twice with one visible.</t>
+          <t>The export succeeds (the native purchases module never enters the web bundle, proving the purchases.ts / purchases.ios.ts split). The web paywall shows the catalog price, the 'Billed securely via Stripe' line, NO Restore control, and the Stripe checkout path is unchanged. The regression guard on the paywall rewrite.</t>
         </is>
       </c>
       <c r="G231" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H231" s="7" t="inlineStr"/>
@@ -9978,7 +9978,7 @@
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
         <is>
-          <t>PREM-34</t>
+          <t>PREM-32</t>
         </is>
       </c>
       <c r="B232" s="7" t="inlineStr">
@@ -9993,22 +9993,22 @@
       </c>
       <c r="D232" s="9" t="inlineStr">
         <is>
-          <t>An ANNUAL subscriber is warned a week before the charge, once</t>
+          <t>PRODUCTION paywall price matches App Store Connect</t>
         </is>
       </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>Needs a Stripe test clock, because the whole feature is about a year passing. Put a test user on the ANNUAL price. Open the app once while the renewal is far away (this is what teaches the device the period is a year: it is only ever judged annual when first seen more than 40 days out). Advance the test clock to ~10 days before renewal and open Today again. Then open it several more times. Separately, repeat the whole thing with a MONTHLY subscriber, and again with an annual one that has been CANCELLED (cancel_at_period_end).</t>
+          <t>After the app is RELEASED, install it from the App Store (not TestFlight) on an Australian account and open Premium. Read the monthly and annual prices.</t>
         </is>
       </c>
       <c r="F232" s="9" t="inlineStr">
         <is>
-          <t>The annual subscriber gets ONE new task, dated SEVEN days before the charge (not on the day of it, which would be a receipt rather than a warning), reading 'Your DoubleDone year renews on &lt;date&gt;. Nothing to do.' Re-opening the app does NOT add a second: it is remembered against that period, and the next one is only noticed after the period rolls. The MONTHLY subscriber never gets one, however many times the app is opened (twelve notices a year is nagging). The CANCELLED subscriber never gets one either, because nothing is renewing and saying otherwise to someone who has decided to leave is both false and unkind. A device that first opens the app INSIDE the last 40 days gets no notice that year, by design, and self-corrects the next. This is the only place the app writes a task nobody typed, so a false positive here is a spine violation, not a cosmetic bug.</t>
+          <t>The paywall reads A$5.00 / month and A$50.00 / year, matching the App Store Connect price schedule for Australia, and matching what Apple's purchase sheet charges. CRITICAL: TestFlight and sandbox CANNOT verify this. They are known to answer product queries for the US storefront regardless of the account's real region, so a TestFlight paywall showing US dollars is expected and is NOT the bug. Only a production App Store install proves it. If production still disagrees with the sheet, that is a misleading pre-purchase price (an Australian Consumer Law problem, not just a display bug): pull the release via Pricing and Availability, Remove from sale. Prerequisite: app released. Gate the RELEASE on this, never the submission.</t>
         </is>
       </c>
       <c r="G232" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="H232" s="7" t="inlineStr"/>
@@ -10018,7 +10018,7 @@
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>PREM-31</t>
+          <t>PREM-33</t>
         </is>
       </c>
       <c r="B233" s="7" t="inlineStr">
@@ -10026,25 +10026,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C233" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>Sandbox tester + Restore Behavior confirmed in the RevenueCat dashboard</t>
-        </is>
-      </c>
-      <c r="E233" s="9" t="inlineStr"/>
+          <t>A dunning subscriber is never sold a second subscription</t>
+        </is>
+      </c>
+      <c r="E233" s="9" t="inlineStr">
+        <is>
+          <t>Put a test Stripe subscription into past_due (in Stripe test mode: attach a failing card, or use the test clock to fail a renewal). Open /premium signed in as that user. Read the panel, then try to buy.</t>
+        </is>
+      </c>
       <c r="F233" s="9" t="inlineStr">
         <is>
-          <t>In the RevenueCat dashboard: Restore Behavior is set to keep-with-original (so TRANSFER never fires), the App Store Connect API key + In-App-Purchase key are uploaded, both products read 'Ready to Submit', and the IAPs are attached to the SAME App Store submission as the first binary (a first-time subscription submitted separately is not reviewed). A Sandbox Apple ID exists for testing.</t>
+          <t>Access has lapsed so the UPSELL panel shows, but with a calm notice at the top: 'Your Premium is paused while a payment retries. Updating your card brings it back. There is no need to buy again.' with an 'Update payment details' link that opens the Stripe portal (the customer id exists in this state). If the user taps Go Premium anyway, the server refuses with 409 billing_issue and the app explains the card is the fix, NEVER 'You're already on Premium' (false: they are not) and NEVER a second Checkout. REGRESSION GUARDS on the same server change (locked by stripe.test.ts): a LAPSED subscriber (status canceled, customer id kept) can still re-subscribe via a fresh Checkout, an abandoned checkout (incomplete) can still buy, and a trial still converts. The old guard keyed on premium &amp;&amp; customerId, so a past_due user could mint a SECOND subscription whose webhook overwrote stripe_customer_id and orphaned the first: paying twice with one visible.</t>
         </is>
       </c>
       <c r="G233" s="7" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H233" s="7" t="inlineStr"/>
@@ -10054,12 +10058,12 @@
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
         <is>
-          <t>QUI-01</t>
+          <t>PREM-34</t>
         </is>
       </c>
       <c r="B234" s="7" t="inlineStr">
         <is>
-          <t>Interface</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
@@ -10069,17 +10073,17 @@
       </c>
       <c r="D234" s="9" t="inlineStr">
         <is>
-          <t>Premium unlocks the Quiet interface; free is gated</t>
+          <t>An ANNUAL subscriber is warned a week before the charge, once</t>
         </is>
       </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>As premium (or with the dev Premium override on), open Settings -&gt; Comfort -&gt; 'Interface' and tap 'Quiet', then reload. Then as a FREE user, tap 'Quiet'.</t>
+          <t>Needs a Stripe test clock, because the whole feature is about a year passing. Put a test user on the ANNUAL price. Open the app once while the renewal is far away (this is what teaches the device the period is a year: it is only ever judged annual when first seen more than 40 days out). Advance the test clock to ~10 days before renewal and open Today again. Then open it several more times. Separately, repeat the whole thing with a MONTHLY subscriber, and again with an annual one that has been CANCELLED (cancel_at_period_end).</t>
         </is>
       </c>
       <c r="F234" s="9" t="inlineStr">
         <is>
-          <t>Premium: the whole Today surface goes borderless. Card outlines drop, and every action that looked like a button or a link renders as plain text with no outline or fill: the header rooms pills, 'Focus on one thing', 'Lighten today', 'Close the day', and 'Plan my day' (which in Standard is the filled premium gradient) all become plain text (accent for the AI / premium ones, soft ink for the calm structural ones). The energy / weight-of-today gauge is KEPT, not removed: it shrinks to a 3px hairline bar so the day's load still reads at a glance. The choice survives reload with 'Quiet' ringed. 'Standard' is the default and looks identical to the app today (gradient button, 6px gauge, outlined actions all return). Free: the block shows a 'Premium' tag and tapping 'Quiet' routes to the paywall with NO change applied ('appearance.locked' logged). A lapsed subscriber keeps whichever appearance they chose.</t>
+          <t>The annual subscriber gets ONE new task, dated SEVEN days before the charge (not on the day of it, which would be a receipt rather than a warning), reading 'Your DoubleDone year renews on &lt;date&gt;. Nothing to do.' Re-opening the app does NOT add a second: it is remembered against that period, and the next one is only noticed after the period rolls. The MONTHLY subscriber never gets one, however many times the app is opened (twelve notices a year is nagging). The CANCELLED subscriber never gets one either, because nothing is renewing and saying otherwise to someone who has decided to leave is both false and unkind. A device that first opens the app INSIDE the last 40 days gets no notice that year, by design, and self-corrects the next. This is the only place the app writes a task nobody typed, so a false positive here is a spine violation, not a cosmetic bug.</t>
         </is>
       </c>
       <c r="G234" s="7" t="inlineStr">
@@ -10094,12 +10098,12 @@
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>QUI-02</t>
+          <t>PREM-31</t>
         </is>
       </c>
       <c r="B235" s="7" t="inlineStr">
         <is>
-          <t>Interface</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
@@ -10109,22 +10113,18 @@
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>Switching Standard &lt;-&gt; Quiet never moves the layout</t>
-        </is>
-      </c>
-      <c r="E235" s="9" t="inlineStr">
-        <is>
-          <t>With a handful of tasks on Today (some open, one or two done), toggle Interface between Standard and Quiet a few times, watching the task rows and the capture line. On ANDROID, specifically do the full round trip (Standard -&gt; Quiet -&gt; Standard) from the Settings screen and then return to Today.</t>
-        </is>
-      </c>
+          <t>Sandbox tester + Restore Behavior confirmed in the RevenueCat dashboard</t>
+        </is>
+      </c>
+      <c r="E235" s="9" t="inlineStr"/>
       <c r="F235" s="9" t="inlineStr">
         <is>
-          <t>Content stays put: no visible jump in row height or position as you toggle. Quiet removes chrome (row borders, fills, the per-task progress bar, the capture underline weight) but preserves spacing, so nothing shifts under the finger. On Android the round trip must leave rows pixel-perfect, in particular the row BOTTOMS never look clipped/'eaten' (regression: toggling while Today sat detached behind Settings in the native stack left rows at Quiet's slightly shorter measured height under Standard's styles; Today now remounts on an appearance change so native lays it out fresh).</t>
+          <t>In the RevenueCat dashboard: Restore Behavior is set to keep-with-original (so TRANSFER never fires), the App Store Connect API key + In-App-Purchase key are uploaded, both products read 'Ready to Submit', and the IAPs are attached to the SAME App Store submission as the first binary (a first-time subscription submitted separately is not reviewed). A Sandbox Apple ID exists for testing.</t>
         </is>
       </c>
       <c r="G235" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="H235" s="7" t="inlineStr"/>
@@ -10134,7 +10134,7 @@
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
         <is>
-          <t>QUI-03</t>
+          <t>QUI-01</t>
         </is>
       </c>
       <c r="B236" s="7" t="inlineStr">
@@ -10142,24 +10142,24 @@
           <t>Interface</t>
         </is>
       </c>
-      <c r="C236" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C236" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D236" s="9" t="inlineStr">
         <is>
-          <t>The held card is identical in Quiet and Standard (only the tint differs)</t>
+          <t>Premium unlocks the Quiet interface; free is gated</t>
         </is>
       </c>
       <c r="E236" s="9" t="inlineStr">
         <is>
-          <t>Hold the SAME one-off task on Today in Quiet, then switch appearance and hold it again in Standard. Compare them side by side. Then in Quiet also hold a 'Later' task and (if you have one) a recurring task.</t>
+          <t>As premium (or with the dev Premium override on), open Settings -&gt; Comfort -&gt; 'Interface' and tap 'Quiet', then reload. Then as a FREE user, tap 'Quiet'.</t>
         </is>
       </c>
       <c r="F236" s="9" t="inlineStr">
         <is>
-          <t>BOTH appearances now give the same in-place card with the same actions in the same order (see TOD-07): there is no longer a Quiet model and a Standard model. Only the treatment differs: Quiet gets a soft wash with a rounded bleed, Standard the accent tint. Mark-as-a-lot and Pin act-and-dismiss (the row updates, the card closes). Pin shows only on Today one-off rows (not Later, not recurring), matching PIN-05; a lapsed subscriber still on Quiet who taps Pin is routed to the paywall, never wrongly pinned. 'Select more' closes the card and drops into multi-select with THIS task pre-selected ('1 selected'); Combine appears once a second task is selected. The one-time 'hold a task for more' coachmark in Quiet is a faint line with a small accent dot, not a filled pill.</t>
+          <t>Premium: the whole Today surface goes borderless. Card outlines drop, and every action that looked like a button or a link renders as plain text with no outline or fill: the header rooms pills, 'Focus on one thing', 'Lighten today', 'Close the day', and 'Plan my day' (which in Standard is the filled premium gradient) all become plain text (accent for the AI / premium ones, soft ink for the calm structural ones). The energy / weight-of-today gauge is KEPT, not removed: it shrinks to a 3px hairline bar so the day's load still reads at a glance. The choice survives reload with 'Quiet' ringed. 'Standard' is the default and looks identical to the app today (gradient button, 6px gauge, outlined actions all return). Free: the block shows a 'Premium' tag and tapping 'Quiet' routes to the paywall with NO change applied ('appearance.locked' logged). A lapsed subscriber keeps whichever appearance they chose.</t>
         </is>
       </c>
       <c r="G236" s="7" t="inlineStr">
@@ -10174,7 +10174,7 @@
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>QUI-04</t>
+          <t>QUI-02</t>
         </is>
       </c>
       <c r="B237" s="7" t="inlineStr">
@@ -10189,17 +10189,17 @@
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>Quiet close-the-day reads as page text and stays reachable when full</t>
+          <t>Switching Standard &lt;-&gt; Quiet never moves the layout</t>
         </is>
       </c>
       <c r="E237" s="9" t="inlineStr">
         <is>
-          <t>In Quiet, finish several tasks, then also test a very full day (roughly 16+ finished), and tap 'Close the day'.</t>
+          <t>With a handful of tasks on Today (some open, one or two done), toggle Interface between Standard and Quiet a few times, watching the task rows and the capture line. On ANDROID, specifically do the full round trip (Standard -&gt; Quiet -&gt; Standard) from the Settings screen and then return to Today.</t>
         </is>
       </c>
       <c r="F237" s="9" t="inlineStr">
         <is>
-          <t>The wrap shows on the plain page colour with no dim scrim and no card outline, and 'Goodnight' is a plain accent text link, not a filled button. On a very full day the finished list still scrolls inside a bounded area and 'Goodnight' stays on screen and reachable, so the TOD-04d regression holds in Quiet too. Reopen / rested behaviour is unchanged.</t>
+          <t>Content stays put: no visible jump in row height or position as you toggle. Quiet removes chrome (row borders, fills, the per-task progress bar, the capture underline weight) but preserves spacing, so nothing shifts under the finger. On Android the round trip must leave rows pixel-perfect, in particular the row BOTTOMS never look clipped/'eaten' (regression: toggling while Today sat detached behind Settings in the native stack left rows at Quiet's slightly shorter measured height under Standard's styles; Today now remounts on an appearance change so native lays it out fresh).</t>
         </is>
       </c>
       <c r="G237" s="7" t="inlineStr">
@@ -10214,7 +10214,7 @@
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>QUI-05</t>
+          <t>QUI-03</t>
         </is>
       </c>
       <c r="B238" s="7" t="inlineStr">
@@ -10222,24 +10222,24 @@
           <t>Interface</t>
         </is>
       </c>
-      <c r="C238" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C238" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D238" s="9" t="inlineStr">
         <is>
-          <t>Quiet honours reduce-motion and every colour theme</t>
+          <t>The held card is identical in Quiet and Standard (only the tint differs)</t>
         </is>
       </c>
       <c r="E238" s="9" t="inlineStr">
         <is>
-          <t>In Quiet, set Settings -&gt; Motion -&gt; Reduce (or the OS reduce-motion), then complete a task, open the held-state, and close the day. Separately, view Quiet across a couple of colour themes (e.g. Dusk and Sage) in BOTH light and dark.</t>
+          <t>Hold the SAME one-off task on Today in Quiet, then switch appearance and hold it again in Standard. Compare them side by side. Then in Quiet also hold a 'Later' task and (if you have one) a recurring task.</t>
         </is>
       </c>
       <c r="F238" s="9" t="inlineStr">
         <is>
-          <t>Nothing animates beyond the app's reduce-motion baseline: the held-state and the wrap appear without motion. Quiet derives its hairlines and washes from the ACTIVE palette, so it looks right on every colour theme in light and dark (not only Dusk), with no washed-out or invisible text.</t>
+          <t>BOTH appearances now give the same in-place card with the same actions in the same order (see TOD-07): there is no longer a Quiet model and a Standard model. Only the treatment differs: Quiet gets a soft wash with a rounded bleed, Standard the accent tint. Mark-as-a-lot and Pin act-and-dismiss (the row updates, the card closes). Pin shows only on Today one-off rows (not Later, not recurring), matching PIN-05; a lapsed subscriber still on Quiet who taps Pin is routed to the paywall, never wrongly pinned. 'Select more' closes the card and drops into multi-select with THIS task pre-selected ('1 selected'); Combine appears once a second task is selected. The one-time 'hold a task for more' coachmark in Quiet is a faint line with a small accent dot, not a filled pill.</t>
         </is>
       </c>
       <c r="G238" s="7" t="inlineStr">
@@ -10254,32 +10254,32 @@
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>PIN-01</t>
+          <t>QUI-04</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
         <is>
-          <t>Pin</t>
-        </is>
-      </c>
-      <c r="C239" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="C239" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
-          <t>Premium: pin a task as the day's one thing</t>
+          <t>Quiet close-the-day reads as page text and stays reachable when full</t>
         </is>
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>As premium (or with the dev Premium override on), tap-and-hold a one-off task to select it, then tap 'Pin' in the held row's actions.</t>
+          <t>In Quiet, finish several tasks, then also test a very full day (roughly 16+ finished), and tap 'Close the day'.</t>
         </is>
       </c>
       <c r="F239" s="9" t="inlineStr">
         <is>
-          <t>The task gets a calm mauve PIN MARK (a drawn pushpin; the star it replaced read as favourite, not pin, per Melroy 2026-08-30, and a drawn SVG cannot hit the iOS missing-glyph failure the round-one flag did) and the thick accent border, and floats to the top of Today. 'Focus on one thing' then opens straight to it.</t>
+          <t>The wrap shows on the plain page colour with no dim scrim and no card outline, and 'Goodnight' is a plain accent text link, not a filled button. On a very full day the finished list still scrolls inside a bounded area and 'Goodnight' stays on screen and reachable, so the TOD-04d regression holds in Quiet too. Reopen / rested behaviour is unchanged.</t>
         </is>
       </c>
       <c r="G239" s="7" t="inlineStr">
@@ -10294,32 +10294,32 @@
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>PIN-02</t>
+          <t>QUI-05</t>
         </is>
       </c>
       <c r="B240" s="7" t="inlineStr">
         <is>
-          <t>Pin</t>
-        </is>
-      </c>
-      <c r="C240" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="C240" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
-          <t>Free: Pin routes to the upsell, never pins</t>
+          <t>Quiet honours reduce-motion and every colour theme</t>
         </is>
       </c>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>As a free user, select a single one-off task and tap the dimmed 'Pin' action.</t>
+          <t>In Quiet, set Settings -&gt; Motion -&gt; Reduce (or the OS reduce-motion), then complete a task, open the held-state, and close the day. Separately, view Quiet across a couple of colour themes (e.g. Dusk and Sage) in BOTH light and dark.</t>
         </is>
       </c>
       <c r="F240" s="9" t="inlineStr">
         <is>
-          <t>No task is pinned, and the Premium screen opens calmly (never a shaming wall). A 'premium.gate_hit' with reason 'pin' is logged.</t>
+          <t>Nothing animates beyond the app's reduce-motion baseline: the held-state and the wrap appear without motion. Quiet derives its hairlines and washes from the ACTIVE palette, so it looks right on every colour theme in light and dark (not only Dusk), with no washed-out or invisible text.</t>
         </is>
       </c>
       <c r="G240" s="7" t="inlineStr">
@@ -10334,7 +10334,7 @@
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>PIN-03</t>
+          <t>PIN-01</t>
         </is>
       </c>
       <c r="B241" s="7" t="inlineStr">
@@ -10342,24 +10342,24 @@
           <t>Pin</t>
         </is>
       </c>
-      <c r="C241" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C241" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>Only one task is pinned at a time</t>
+          <t>Premium: pin a task as the day's one thing</t>
         </is>
       </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
-          <t>As premium, pin task A, then hold task B and pin it.</t>
+          <t>As premium (or with the dev Premium override on), tap-and-hold a one-off task to select it, then tap 'Pin' in the held row's actions.</t>
         </is>
       </c>
       <c r="F241" s="9" t="inlineStr">
         <is>
-          <t>Task B is now pinned (pin-marked, floated to the top), and task A is no longer pinned. At most one pin ever exists.</t>
+          <t>The task gets a calm mauve PIN MARK (a drawn pushpin; the star it replaced read as favourite, not pin, per Melroy 2026-08-30, and a drawn SVG cannot hit the iOS missing-glyph failure the round-one flag did) and the thick accent border, and floats to the top of Today. 'Focus on one thing' then opens straight to it.</t>
         </is>
       </c>
       <c r="G241" s="7" t="inlineStr">
@@ -10374,7 +10374,7 @@
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>PIN-04</t>
+          <t>PIN-02</t>
         </is>
       </c>
       <c r="B242" s="7" t="inlineStr">
@@ -10382,24 +10382,24 @@
           <t>Pin</t>
         </is>
       </c>
-      <c r="C242" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C242" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D242" s="9" t="inlineStr">
         <is>
-          <t>A pin syncs across devices</t>
+          <t>Free: Pin routes to the upsell, never pins</t>
         </is>
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>As premium and signed in, pin a task, then sign out and back in (or open a second device).</t>
+          <t>As a free user, select a single one-off task and tap the dimmed 'Pin' action.</t>
         </is>
       </c>
       <c r="F242" s="9" t="inlineStr">
         <is>
-          <t>The task is still pinned after the sync round-trip (the pin mark and float persist). Needs the pinned_at column applied in Supabase.</t>
+          <t>No task is pinned, and the Premium screen opens calmly (never a shaming wall). A 'premium.gate_hit' with reason 'pin' is logged.</t>
         </is>
       </c>
       <c r="G242" s="7" t="inlineStr">
@@ -10414,7 +10414,7 @@
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>PIN-05</t>
+          <t>PIN-03</t>
         </is>
       </c>
       <c r="B243" s="7" t="inlineStr">
@@ -10422,24 +10422,24 @@
           <t>Pin</t>
         </is>
       </c>
-      <c r="C243" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C243" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>Pin is offered only on one-off Today rows</t>
+          <t>Only one task is pinned at a time</t>
         </is>
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
-          <t>Hold a recurring task, then hold a task in the 'Later' list.</t>
+          <t>As premium, pin task A, then hold task B and pin it.</t>
         </is>
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>No 'Pin' action appears on a recurring task's held card, and a Later task's card carries no Pin either (pinning is Today-only and one-offs only).</t>
+          <t>Task B is now pinned (pin-marked, floated to the top), and task A is no longer pinned. At most one pin ever exists.</t>
         </is>
       </c>
       <c r="G243" s="7" t="inlineStr">
@@ -10454,32 +10454,32 @@
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
         <is>
-          <t>NRG-01</t>
+          <t>PIN-04</t>
         </is>
       </c>
       <c r="B244" s="7" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C244" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Pin</t>
+        </is>
+      </c>
+      <c r="C244" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D244" s="9" t="inlineStr">
         <is>
-          <t>What fits right now: one question, one pick, propose-only</t>
+          <t>A pin syncs across devices</t>
         </is>
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>With AI on and 2+ open one-off tasks, tap 'Focus on one thing'; in the 'Which one?' picker, 'What fits right now?' sits above the task choices in a soft hairline pill (its border makes it read as tappable; it lives INSIDE Focus, not as a standalone Today button). Tap it, pick an energy level (Running low / Somewhere in between / Feeling good). Then tap 'Start with this'; separately try 'Not now'.</t>
+          <t>As premium and signed in, pin a task, then sign out and back in (or open a second device).</t>
         </is>
       </c>
       <c r="F244" s="9" t="inlineStr">
         <is>
-          <t>A calm one-question card with the privacy line ('Your open tasks go to Claude to pick one. Nothing is added or changed.'). Choosing a level shows ONE task from today's list with a short warm line on why it fits (never shaming, never about what's undone). 'Start with this' opens Focus mode on exactly that task; 'Not now' just closes, nothing changed. A failed call shows a calm 'Couldn't find a pick just now.' line and does NOT spend a free pick. The entry hides when AI is off or fewer than 2 tasks are open. Needs the Worker deployed with /energy.</t>
+          <t>The task is still pinned after the sync round-trip (the pin mark and float persist). Needs the pinned_at column applied in Supabase.</t>
         </is>
       </c>
       <c r="G244" s="7" t="inlineStr">
@@ -10494,32 +10494,32 @@
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>NRG-02</t>
+          <t>PIN-05</t>
         </is>
       </c>
       <c r="B245" s="7" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C245" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Pin</t>
+        </is>
+      </c>
+      <c r="C245" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>The freemium meter: 15 a month, reminders at 10 and 5, then the paywall</t>
+          <t>Pin is offered only on one-off Today rows</t>
         </is>
       </c>
       <c r="E245" s="9" t="inlineStr">
         <is>
-          <t>As a FREE user, use energy matching repeatedly in one calendar month (seed doubledone.energyUses.v1 to fast-forward). Watch the 10-left and 5-left moments, then the 16th tap. Then as premium, use it well past 15.</t>
+          <t>Hold a recurring task, then hold a task in the 'Later' list.</t>
         </is>
       </c>
       <c r="F245" s="9" t="inlineStr">
         <is>
-          <t>Each successful pick spends one of 15 free picks a calendar month (counted locally, like the scrapbook gate). Exactly at 10 left and at 5 left, the result shows one calm line: '10 of your 15 free picks left this month.' (then 5). Past 15, tapping the entry routes to the paywall (which lists 'Energy matching without limits'), never a shaming wall, and no AI call is made ('premium.gate_hit' reason 'energy' logs). The counter resets on the 1st of the month with no carry-over. Premium is unlimited and never sees a counter line.</t>
+          <t>No 'Pin' action appears on a recurring task's held card, and a Later task's card carries no Pin either (pinning is Today-only and one-offs only).</t>
         </is>
       </c>
       <c r="G245" s="7" t="inlineStr">
@@ -10534,12 +10534,12 @@
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
         <is>
-          <t>OCR-01</t>
+          <t>NRG-01</t>
         </is>
       </c>
       <c r="B246" s="7" t="inlineStr">
         <is>
-          <t>Scan</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C246" s="8" t="inlineStr">
@@ -10549,17 +10549,17 @@
       </c>
       <c r="D246" s="9" t="inlineStr">
         <is>
-          <t>Premium: the Scan button opens the camera</t>
+          <t>What fits right now: one question, one pick, propose-only</t>
         </is>
       </c>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>As premium, open the add panel and tap the Scan (camera) pill beside Speak.</t>
+          <t>With AI on and 2+ open one-off tasks, tap 'Focus on one thing'; in the 'Which one?' picker, 'What fits right now?' sits above the task choices in a soft hairline pill (its border makes it read as tappable; it lives INSIDE Focus, not as a standalone Today button). Tap it, pick an energy level (Running low / Somewhere in between / Feeling good). Then tap 'Start with this'; separately try 'Not now'.</t>
         </is>
       </c>
       <c r="F246" s="9" t="inlineStr">
         <is>
-          <t>The camera screen opens: a live viewfinder with a shutter and a Photos shortcut on a device, or a 'Choose a photo' prompt on web. No paywall.</t>
+          <t>A calm one-question card with the privacy line ('Your open tasks go to Claude to pick one. Nothing is added or changed.'). Choosing a level shows ONE task from today's list with a short warm line on why it fits (never shaming, never about what's undone). 'Start with this' opens Focus mode on exactly that task; 'Not now' just closes, nothing changed. A failed call shows a calm 'Couldn't find a pick just now.' line and does NOT spend a free pick. The entry hides when AI is off or fewer than 2 tasks are open. Needs the Worker deployed with /energy.</t>
         </is>
       </c>
       <c r="G246" s="7" t="inlineStr">
@@ -10574,12 +10574,12 @@
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>OCR-02</t>
+          <t>NRG-02</t>
         </is>
       </c>
       <c r="B247" s="7" t="inlineStr">
         <is>
-          <t>Scan</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C247" s="8" t="inlineStr">
@@ -10589,17 +10589,17 @@
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>Free: Scan routes to the upsell, never opens the camera</t>
+          <t>The freemium meter: 15 a month, reminders at 10 and 5, then the paywall</t>
         </is>
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>As a free user, open the add panel and tap the Scan pill.</t>
+          <t>As a FREE user, use energy matching repeatedly in one calendar month (seed doubledone.energyUses.v1 to fast-forward). Watch the 10-left and 5-left moments, then the 16th tap. Then as premium, use it well past 15.</t>
         </is>
       </c>
       <c r="F247" s="9" t="inlineStr">
         <is>
-          <t>Routed to the Premium screen calmly (never a wall). A 'premium.gate_hit' with reason 'ocr' is logged. No camera opens.</t>
+          <t>Each successful pick spends one of 15 free picks a calendar month (counted locally, like the scrapbook gate). Exactly at 10 left and at 5 left, the result shows one calm line: '10 of your 15 free picks left this month.' (then 5). Past 15, tapping the entry routes to the paywall (which lists 'Energy matching without limits'), never a shaming wall, and no AI call is made ('premium.gate_hit' reason 'energy' logs). The counter resets on the 1st of the month with no carry-over. Premium is unlimited and never sees a counter line.</t>
         </is>
       </c>
       <c r="G247" s="7" t="inlineStr">
@@ -10614,7 +10614,7 @@
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>OCR-03</t>
+          <t>OCR-01</t>
         </is>
       </c>
       <c r="B248" s="7" t="inlineStr">
@@ -10629,22 +10629,22 @@
       </c>
       <c r="D248" s="9" t="inlineStr">
         <is>
-          <t>Photograph a list and the tasks land in the box</t>
+          <t>Premium: the Scan button opens the camera</t>
         </is>
       </c>
       <c r="E248" s="9" t="inlineStr">
         <is>
-          <t>As premium on a device, tap Scan, photograph a short printed or handwritten list (fill the frame), wait for 'Reading your list...'.</t>
+          <t>As premium, open the add panel and tap the Scan (camera) pill beside Speak.</t>
         </is>
       </c>
       <c r="F248" s="9" t="inlineStr">
         <is>
-          <t>The tasks it reads appear in the brain-dump box, one per line, editable. Nothing is auto-added to Today, and tapping Add commits them. An 'ocr.captured' event is logged.</t>
+          <t>The camera screen opens: a live viewfinder with a shutter and a Photos shortcut on a device, or a 'Choose a photo' prompt on web. No paywall.</t>
         </is>
       </c>
       <c r="G248" s="7" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H248" s="7" t="inlineStr"/>
@@ -10654,7 +10654,7 @@
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>OCR-04</t>
+          <t>OCR-02</t>
         </is>
       </c>
       <c r="B249" s="7" t="inlineStr">
@@ -10662,24 +10662,24 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="C249" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>Gallery fallback reads an existing photo</t>
+          <t>Free: Scan routes to the upsell, never opens the camera</t>
         </is>
       </c>
       <c r="E249" s="9" t="inlineStr">
         <is>
-          <t>Tap Scan, then 'Photos' (device) or 'Choose a photo' (web), and pick a photo of a list, a note, or a whiteboard.</t>
+          <t>As a free user, open the add panel and tap the Scan pill.</t>
         </is>
       </c>
       <c r="F249" s="9" t="inlineStr">
         <is>
-          <t>Same result: the read tasks land in the box for review. Covers a screenshot of a texted list, or a photo taken earlier.</t>
+          <t>Routed to the Premium screen calmly (never a wall). A 'premium.gate_hit' with reason 'ocr' is logged. No camera opens.</t>
         </is>
       </c>
       <c r="G249" s="7" t="inlineStr">
@@ -10694,7 +10694,7 @@
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>OCR-05</t>
+          <t>OCR-03</t>
         </is>
       </c>
       <c r="B250" s="7" t="inlineStr">
@@ -10702,29 +10702,29 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="C250" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C250" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D250" s="9" t="inlineStr">
         <is>
-          <t>An unreadable photo fails calmly</t>
+          <t>Photograph a list and the tasks land in the box</t>
         </is>
       </c>
       <c r="E250" s="9" t="inlineStr">
         <is>
-          <t>Scan a blank, blurry, or list-free image.</t>
+          <t>As premium on a device, tap Scan, photograph a short printed or handwritten list (fill the frame), wait for 'Reading your list...'.</t>
         </is>
       </c>
       <c r="F250" s="9" t="inlineStr">
         <is>
-          <t>A calm line ('I couldn't read any tasks from that. Try again...'), the camera stays open, never a crash and never a shaming message.</t>
+          <t>The tasks it reads appear in the brain-dump box, one per line, editable. Nothing is auto-added to Today, and tapping Add commits them. An 'ocr.captured' event is logged.</t>
         </is>
       </c>
       <c r="G250" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="H250" s="7" t="inlineStr"/>
@@ -10734,7 +10734,7 @@
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>OCR-06</t>
+          <t>OCR-04</t>
         </is>
       </c>
       <c r="B251" s="7" t="inlineStr">
@@ -10749,22 +10749,22 @@
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>Camera denial is never a dead end</t>
+          <t>Gallery fallback reads an existing photo</t>
         </is>
       </c>
       <c r="E251" s="9" t="inlineStr">
         <is>
-          <t>On a device, deny the camera permission when prompted.</t>
+          <t>Tap Scan, then 'Photos' (device) or 'Choose a photo' (web), and pick a photo of a list, a note, or a whiteboard.</t>
         </is>
       </c>
       <c r="F251" s="9" t="inlineStr">
         <is>
-          <t>A calm screen offers 'Allow camera' and 'Choose from photos instead', and the gallery path still reads a list.</t>
+          <t>Same result: the read tasks land in the box for review. Covers a screenshot of a texted list, or a photo taken earlier.</t>
         </is>
       </c>
       <c r="G251" s="7" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H251" s="7" t="inlineStr"/>
@@ -10774,7 +10774,7 @@
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
         <is>
-          <t>OCR-07</t>
+          <t>OCR-05</t>
         </is>
       </c>
       <c r="B252" s="7" t="inlineStr">
@@ -10782,24 +10782,24 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="C252" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C252" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D252" s="9" t="inlineStr">
         <is>
-          <t>AI egress is disclosed at the point of use</t>
+          <t>An unreadable photo fails calmly</t>
         </is>
       </c>
       <c r="E252" s="9" t="inlineStr">
         <is>
-          <t>Open the Scan screen (device or web).</t>
+          <t>Scan a blank, blurry, or list-free image.</t>
         </is>
       </c>
       <c r="F252" s="9" t="inlineStr">
         <is>
-          <t>The note 'Your photo is sent to the AI to read your list, then discarded. It is never stored.' is visible. The D1 'ocr' telemetry row holds only the image size and task count, never the image or the titles.</t>
+          <t>A calm line ('I couldn't read any tasks from that. Try again...'), the camera stays open, never a crash and never a shaming message.</t>
         </is>
       </c>
       <c r="G252" s="7" t="inlineStr">
@@ -10814,37 +10814,37 @@
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>CHART-01</t>
+          <t>OCR-06</t>
         </is>
       </c>
       <c r="B253" s="7" t="inlineStr">
         <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C253" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Scan</t>
+        </is>
+      </c>
+      <c r="C253" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>Premium: chart a course toward a goal</t>
+          <t>Camera denial is never a dead end</t>
         </is>
       </c>
       <c r="E253" s="9" t="inlineStr">
         <is>
-          <t>As premium (or dev Premium override on), open Rooms, tap 'Chart a course', type a goal like 'get fit for a 10k', tap 'Suggest steps'.</t>
+          <t>On a device, deny the camera permission when prompted.</t>
         </is>
       </c>
       <c r="F253" s="9" t="inlineStr">
         <is>
-          <t>A calm one-line heading plus 3-7 ticked next steps appear, and nothing is added yet. Tapping 'Add N tasks' lands them on Today (the first undated, later ones spread forward), each an ordinary task, and returns to Today. The 'chart.requested' then 'chart.added' events are logged.</t>
+          <t>A calm screen offers 'Allow camera' and 'Choose from photos instead', and the gallery path still reads a list.</t>
         </is>
       </c>
       <c r="G253" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="H253" s="7" t="inlineStr"/>
@@ -10854,32 +10854,32 @@
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>CHART-02</t>
+          <t>OCR-07</t>
         </is>
       </c>
       <c r="B254" s="7" t="inlineStr">
         <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C254" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Scan</t>
+        </is>
+      </c>
+      <c r="C254" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
-          <t>Free: charting routes to the upsell, never plans</t>
+          <t>AI egress is disclosed at the point of use</t>
         </is>
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>As a free user, open Rooms, tap 'Chart a course', type a goal, tap 'Suggest steps'.</t>
+          <t>Open the Scan screen (device or web).</t>
         </is>
       </c>
       <c r="F254" s="9" t="inlineStr">
         <is>
-          <t>Routed to the Premium screen calmly (never a wall), and a 'premium.gate_hit' with reason 'chart' is logged. No plan is generated and nothing is added.</t>
+          <t>The note 'Your photo is sent to the AI to read your list, then discarded. It is never stored.' is visible. The D1 'ocr' telemetry row holds only the image size and task count, never the image or the titles.</t>
         </is>
       </c>
       <c r="G254" s="7" t="inlineStr">
@@ -10894,7 +10894,7 @@
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>CHART-03</t>
+          <t>CHART-01</t>
         </is>
       </c>
       <c r="B255" s="7" t="inlineStr">
@@ -10902,24 +10902,24 @@
           <t>Chart</t>
         </is>
       </c>
-      <c r="C255" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C255" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>Propose-then-accept: nothing auto-adds</t>
+          <t>Premium: chart a course toward a goal</t>
         </is>
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>As premium, generate a plan, untick two steps, then tap 'Add'. Separately, generate a plan and back out with 'Not these, start over' or Back.</t>
+          <t>As premium (or dev Premium override on), open Rooms, tap 'Chart a course', type a goal like 'get fit for a 10k', tap 'Suggest steps'.</t>
         </is>
       </c>
       <c r="F255" s="9" t="inlineStr">
         <is>
-          <t>Only the ticked steps are added as plain tasks, and backing out adds nothing. Today was unchanged before accepting.</t>
+          <t>A calm one-line heading plus 3-7 ticked next steps appear, and nothing is added yet. Tapping 'Add N tasks' lands them on Today (the first undated, later ones spread forward), each an ordinary task, and returns to Today. The 'chart.requested' then 'chart.added' events are logged.</t>
         </is>
       </c>
       <c r="G255" s="7" t="inlineStr">
@@ -10934,7 +10934,7 @@
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>CHART-04</t>
+          <t>CHART-02</t>
         </is>
       </c>
       <c r="B256" s="7" t="inlineStr">
@@ -10942,24 +10942,24 @@
           <t>Chart</t>
         </is>
       </c>
-      <c r="C256" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C256" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>A goal that cannot be mapped fails calmly</t>
+          <t>Free: charting routes to the upsell, never plans</t>
         </is>
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>Enter an empty goal (the button is disabled), then a nonsensical goal and submit.</t>
+          <t>As a free user, open Rooms, tap 'Chart a course', type a goal, tap 'Suggest steps'.</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>The empty case cannot submit. A nonsensical goal shows one calm line ('I couldn't map that out just now'), the goal stays editable, never a crash or a shaming message.</t>
+          <t>Routed to the Premium screen calmly (never a wall), and a 'premium.gate_hit' with reason 'chart' is logged. No plan is generated and nothing is added.</t>
         </is>
       </c>
       <c r="G256" s="7" t="inlineStr">
@@ -10974,7 +10974,7 @@
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>CHART-05</t>
+          <t>CHART-03</t>
         </is>
       </c>
       <c r="B257" s="7" t="inlineStr">
@@ -10989,17 +10989,17 @@
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>A deadline spreads the steps across the timeframe</t>
+          <t>Propose-then-accept: nothing auto-adds</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>As premium, type a goal, tap a 'By when?' chip (e.g. 'In 2 months'), then Suggest steps and Add.</t>
+          <t>As premium, generate a plan, untick two steps, then tap 'Add'. Separately, generate a plan and back out with 'Not these, start over' or Back.</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>The steps are paced for that timeframe, and the accepted tasks spread from Today out to the chosen date (not crammed into the next few days). 'No deadline' keeps the gentle one-per-day default.</t>
+          <t>Only the ticked steps are added as plain tasks, and backing out adds nothing. Today was unchanged before accepting.</t>
         </is>
       </c>
       <c r="G257" s="7" t="inlineStr">
@@ -11014,32 +11014,32 @@
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>SEQ-01</t>
+          <t>CHART-04</t>
         </is>
       </c>
       <c r="B258" s="7" t="inlineStr">
         <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="C258" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C258" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
-          <t>Premium: Plan my day suggests a calm sequence</t>
+          <t>A goal that cannot be mapped fails calmly</t>
         </is>
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>As premium with 3+ open one-off tasks on Today, tap 'Plan my day'. Answer the questions it asks first (or skip them).</t>
+          <t>Enter an empty goal (the button is disabled), then a nonsensical goal and submit.</t>
         </is>
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>A proposal card lists today's tasks in a suggested order, each with a short calm reason. Nothing reorders until 'Use this order' is tapped, then the list re-sequences in place (no dates change, no task moves to another day). A 'sequence.accepted' event is logged.</t>
+          <t>The empty case cannot submit. A nonsensical goal shows one calm line ('I couldn't map that out just now'), the goal stays editable, never a crash or a shaming message.</t>
         </is>
       </c>
       <c r="G258" s="7" t="inlineStr">
@@ -11054,32 +11054,32 @@
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>TOD-27</t>
+          <t>CHART-05</t>
         </is>
       </c>
       <c r="B259" s="7" t="inlineStr">
         <is>
-          <t>Today</t>
-        </is>
-      </c>
-      <c r="C259" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C259" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>The constant frame: one fixed action layer, a clock-set slot, Energy pills</t>
+          <t>A deadline spreads the steps across the timeframe</t>
         </is>
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>Open Today in the MORNING (before 11), around MIDDAY (11-17), and in the EVENING (17+), reading the 'RIGHT NOW' slot above the Add bar each time. Tap the caret next to it. Add and complete tasks and watch whether ANY control moves. Tap an unavailable (faded) tool. Set the Energy pills to High on a 7-task day and re-open the caret; set Low and read the gauge. Reload the app and check the pill. Turn AI off in Settings and re-open the caret. Also check with 0 tasks, and in select mode, and after closing the day.</t>
+          <t>As premium, type a goal, tap a 'By when?' chip (e.g. 'In 2 months'), then Suggest steps and Add.</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>ONE fixed layer sits above the Add bar, always the same pixels: an overline 'RIGHT NOW' + the tool that suits the HOUR (morning: Plan my day; midday: Focus on one thing; evening: Close the day), plus a 44px caret ('All day tools'). The occupant is set by the CLOCK at open and never changes mid-session; it NEVER shows Lighten today. The caret opens a panel growing upward with the SAME four tools in the SAME day order every time: Plan my day, Focus on one thing, Lighten today, Close the day, the current occupant tagged 'now'; behind it the list dims 40% and never moves; tapping the dim closes. NOTHING in this layer appears, vanishes or slides as tasks are added or completed: an unavailable tool stays in place at lowered contrast (no lock, no strikethrough) and tapping it explains in one plain line what the TOOL needs ('Plan my day needs two or more tasks.' / 'Lighten today is for a full day.'), never what the person lacks. The Energy pills (Low/Normal/High) sit under a small 'ENERGY' overline with the gauge at the top, and the WHOLE panel (gauge + label + pills) renders on EVERY open day, including an empty one, where the gauge reads 'A clear day.' (real-user report 2026-07-26: without the gauge the pills floated headerless and read as lost text). A fresh day defaults to Normal. High re-scales what 'full' means (7 tasks stop being heavy, so Lighten goes quiet until ~9), Low IS the low-capacity day (the old toggle is gone; the same warm affirm appears), and the choice survives a reload but RESETS to Normal next morning (a day-state, never a setting). With AI OFF the panel holds only Focus and Close (AI tools are gone, not faded, per the AI-off rule). The old pile is gone: no Focus button above the list, no 'Today's looking full' line, no stacked Lighten/Plan buttons, no separate wind-down line (in the evening the italic inscription under Add becomes the wind-down sentence), and Close the day is never buried under a long list again. The layer hides in select mode and on a closed day.</t>
+          <t>The steps are paced for that timeframe, and the accepted tasks spread from Today out to the chosen date (not crammed into the next few days). 'No deadline' keeps the gentle one-per-day default.</t>
         </is>
       </c>
       <c r="G259" s="7" t="inlineStr">
@@ -11094,32 +11094,32 @@
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>TOD-28</t>
+          <t>SEQ-01</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
         <is>
-          <t>Today</t>
-        </is>
-      </c>
-      <c r="C260" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Sequence</t>
+        </is>
+      </c>
+      <c r="C260" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
-          <t>The rested screen mentions the scrapbook once, at the earned moment (the ladder's last rung)</t>
+          <t>Premium: Plan my day suggests a calm sequence</t>
         </is>
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>With AI on, the reminder and widget asks already spent (or reminder on, widget placed), NO scrapbook ever made, and at least 3 finishes this week, close the day and read the rested screen. Tap 'See your Calendar'. Then close a day again on another evening. Separately: repeat with AI off, and repeat with only 1-2 finishes.</t>
+          <t>As premium with 3+ open one-off tasks on Today, tap 'Plan my day'. Answer the questions it asks first (or skip them).</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>One calm mention appears under the goodnight text: 'You've finished enough this week to make a keepsake of it. It's waiting in your Calendar.' with 'See your Calendar' and 'Not now'. Either answer spends the mention FOREVER (it is the third and LAST rung of the one-ask-at-a-time ladder; reminder and widget always win the evening if pending). 'See your Calendar' opens the Calendar where the scrapbook lives. It never shows with AI off, never with fewer than 3 finishes this week, never to someone who has already made a scrapbook, and never twice.</t>
+          <t>A proposal card lists today's tasks in a suggested order, each with a short calm reason. Nothing reorders until 'Use this order' is tapped, then the list re-sequences in place (no dates change, no task moves to another day). A 'sequence.accepted' event is logged.</t>
         </is>
       </c>
       <c r="G260" s="7" t="inlineStr">
@@ -11134,12 +11134,12 @@
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>SEQ-07</t>
+          <t>TOD-27</t>
         </is>
       </c>
       <c r="B261" s="7" t="inlineStr">
         <is>
-          <t>Sequence</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="C261" s="8" t="inlineStr">
@@ -11149,17 +11149,17 @@
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>Plan my day asks about the day BEFORE it sorts</t>
+          <t>The constant frame: one fixed action layer, a clock-set slot, Energy pills</t>
         </is>
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>As premium, tap 'Plan my day'. Read the sheet that opens. Tap an answer, then tap the SAME answer again. Try sorting with all three answered, with only one answered, and with none answered ('Sort today' straight away). Also tap 'Not now'. Separately, as a FREE user, tap 'Plan my day'.</t>
+          <t>Open Today in the MORNING (before 11), around MIDDAY (11-17), and in the EVENING (17+), reading the 'RIGHT NOW' slot above the Add bar each time. Tap the caret next to it. Add and complete tasks and watch whether ANY control moves. Tap an unavailable (faded) tool. Set the Energy pills to High on a 7-task day and re-open the caret; set Low and read the gauge. Reload the app and check the pill. Turn AI off in Settings and re-open the caret. Also check with 0 tasks, and in select mode, and after closing the day.</t>
         </is>
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>Before any sorting, a calm sheet asks three OPTIONAL questions: 'How's your energy?' (Running low / Somewhere in between / Feeling good), 'What kind of day?' (Work day / Day off) and 'Where are you?' (Indoors / Out and about / Either), under 'Answer what you like. Skip what you don't.'. A chosen answer tints (accent border, fill and bold accent text); tapping it AGAIN clears it, so a mis-tap is undone the way it was made. Skipping a question sends nothing for it, so it never becomes an assumption, and skipping all three sorts exactly as it always did. The order that comes back reflects what was said (a low-energy day starts small; a day off does not front-load work; 'out and about' clusters the errands), but the app NEVER comments on how you feel. 'Not now' closes with nothing sent and the day untouched. A FREE user hits the Premium screen BEFORE the questions, never after answering them. NEW (the constant frame): when the Energy PILLS at the top of Today were touched today, the sheet's energy question DOES NOT APPEAR at all, and the pill's answer rides the request instead (Low-&gt;low, Normal-&gt;medium, High-&gt;good): energy is read, never asked twice. Only when the pills are untouched does the sheet ask. NOTE: there is deliberately no weather question. A model has no live weather data, and a forecast would need an API plus a location permission; 'Where are you?' is what the sort actually needs.</t>
+          <t>ONE fixed layer sits above the Add bar, always the same pixels: an overline 'RIGHT NOW' + the tool that suits the HOUR (morning: Plan my day; midday: Focus on one thing; evening: Close the day), plus a 44px caret ('All day tools'). The occupant is set by the CLOCK at open and never changes mid-session; it NEVER shows Lighten today. The caret opens a panel growing upward with the SAME four tools in the SAME day order every time: Plan my day, Focus on one thing, Lighten today, Close the day, the current occupant tagged 'now'; behind it the list dims 40% and never moves; tapping the dim closes. NOTHING in this layer appears, vanishes or slides as tasks are added or completed: an unavailable tool stays in place at lowered contrast (no lock, no strikethrough) and tapping it explains in one plain line what the TOOL needs ('Plan my day needs two or more tasks.' / 'Lighten today is for a full day.'), never what the person lacks. The Energy pills (Low/Normal/High) sit under a small 'ENERGY' overline with the gauge at the top, and the WHOLE panel (gauge + label + pills) renders on EVERY open day, including an empty one, where the gauge reads 'A clear day.' (real-user report 2026-07-26: without the gauge the pills floated headerless and read as lost text). A fresh day defaults to Normal. High re-scales what 'full' means (7 tasks stop being heavy, so Lighten goes quiet until ~9), Low IS the low-capacity day (the old toggle is gone; the same warm affirm appears), and the choice survives a reload but RESETS to Normal next morning (a day-state, never a setting). With AI OFF the panel holds only Focus and Close (AI tools are gone, not faded, per the AI-off rule). The old pile is gone: no Focus button above the list, no 'Today's looking full' line, no stacked Lighten/Plan buttons, no separate wind-down line (in the evening the italic inscription under Add becomes the wind-down sentence), and Close the day is never buried under a long list again. The layer hides in select mode and on a closed day.</t>
         </is>
       </c>
       <c r="G261" s="7" t="inlineStr">
@@ -11174,32 +11174,32 @@
     <row r="262">
       <c r="A262" s="6" t="inlineStr">
         <is>
-          <t>SEQ-08</t>
+          <t>TOD-28</t>
         </is>
       </c>
       <c r="B262" s="7" t="inlineStr">
         <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="C262" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="C262" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D262" s="9" t="inlineStr">
         <is>
-          <t>The suggested order can be edited before it is used</t>
+          <t>The rested screen mentions the scrapbook once, at the earned moment (the ladder's last rung)</t>
         </is>
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>Get a proposal from 'Plan my day'. Use the up and down arrows on a row. Try the up arrow on the FIRST row and the down arrow on the LAST. Remove a row with x. Remove every row. Then tap 'Use this order'.</t>
+          <t>With AI on, the reminder and widget asks already spent (or reminder on, widget placed), NO scrapbook ever made, and at least 3 finishes this week, close the day and read the rested screen. Tap 'See your Calendar'. Then close a day again on another evening. Separately: repeat with AI off, and repeat with only 1-2 finishes.</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>Each row carries up / down / x. Up and down swap the row with its neighbour immediately, renumbering as they go; the first row's up and the last row's down are visibly dimmed and do nothing (they are disabled, not hidden, so rows never change shape as things move). 'x' takes that task OUT OF THIS PLAN ONLY: the task stays on Today untouched, is not deleted, and is not moved to another day. Removing everything is allowed and says 'Nothing left in the plan. That's allowed.' with the accept button gone (an empty plan cannot be applied). Nothing at all changes on Today until 'Use this order' is tapped; 'Not now' or closing discards every edit. Editing is by buttons, never drag: dragging is unusable with a screen reader and hard with shaky hands.</t>
+          <t>One calm mention appears under the goodnight text: 'You've finished enough this week to make a keepsake of it. It's waiting in your Calendar.' with 'See your Calendar' and 'Not now'. Either answer spends the mention FOREVER (it is the third and LAST rung of the one-ask-at-a-time ladder; reminder and widget always win the evening if pending). 'See your Calendar' opens the Calendar where the scrapbook lives. It never shows with AI off, never with fewer than 3 finishes this week, never to someone who has already made a scrapbook, and never twice.</t>
         </is>
       </c>
       <c r="G262" s="7" t="inlineStr">
@@ -11214,7 +11214,7 @@
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>SEQ-02</t>
+          <t>SEQ-07</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
@@ -11229,17 +11229,17 @@
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>Free: Plan my day routes to the upsell, never reorders</t>
+          <t>Plan my day asks about the day BEFORE it sorts</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>As a free user with 2+ tasks on Today, tap 'Plan my day'.</t>
+          <t>As premium, tap 'Plan my day'. Read the sheet that opens. Tap an answer, then tap the SAME answer again. Try sorting with all three answered, with only one answered, and with none answered ('Sort today' straight away). Also tap 'Not now'. Separately, as a FREE user, tap 'Plan my day'.</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>The Premium screen opens calmly (never a wall), a 'premium.gate_hit' with reason 'sequence' is logged, and the day's order is unchanged.</t>
+          <t>Before any sorting, a calm sheet asks three OPTIONAL questions: 'How's your energy?' (Running low / Somewhere in between / Feeling good), 'What kind of day?' (Work day / Day off) and 'Where are you?' (Indoors / Out and about / Either), under 'Answer what you like. Skip what you don't.'. A chosen answer tints (accent border, fill and bold accent text); tapping it AGAIN clears it, so a mis-tap is undone the way it was made. Skipping a question sends nothing for it, so it never becomes an assumption, and skipping all three sorts exactly as it always did. The order that comes back reflects what was said (a low-energy day starts small; a day off does not front-load work; 'out and about' clusters the errands), but the app NEVER comments on how you feel. 'Not now' closes with nothing sent and the day untouched. A FREE user hits the Premium screen BEFORE the questions, never after answering them. NEW (the constant frame): when the Energy PILLS at the top of Today were touched today, the sheet's energy question DOES NOT APPEAR at all, and the pill's answer rides the request instead (Low-&gt;low, Normal-&gt;medium, High-&gt;good): energy is read, never asked twice. Only when the pills are untouched does the sheet ask. NOTE: there is deliberately no weather question. A model has no live weather data, and a forecast would need an API plus a location permission; 'Where are you?' is what the sort actually needs.</t>
         </is>
       </c>
       <c r="G263" s="7" t="inlineStr">
@@ -11254,7 +11254,7 @@
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>SEQ-03</t>
+          <t>SEQ-08</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -11262,24 +11262,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C264" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C264" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>'Not now' leaves the day untouched</t>
+          <t>The suggested order can be edited before it is used</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>As premium, open the proposal, then tap 'Not now' or the backdrop.</t>
+          <t>Get a proposal from 'Plan my day'. Use the up and down arrows on a row. Try the up arrow on the FIRST row and the down arrow on the LAST. Remove a row with x. Remove every row. Then tap 'Use this order'.</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>The order is exactly as before, nothing reordered, and no manualOrder is written.</t>
+          <t>Each row carries up / down / x. Up and down swap the row with its neighbour immediately, renumbering as they go; the first row's up and the last row's down are visibly dimmed and do nothing (they are disabled, not hidden, so rows never change shape as things move). 'x' takes that task OUT OF THIS PLAN ONLY: the task stays on Today untouched, is not deleted, and is not moved to another day. Removing everything is allowed and says 'Nothing left in the plan. That's allowed.' with the accept button gone (an empty plan cannot be applied). Nothing at all changes on Today until 'Use this order' is tapped; 'Not now' or closing discards every edit. Editing is by buttons, never drag: dragging is unusable with a screen reader and hard with shaky hands.</t>
         </is>
       </c>
       <c r="G264" s="7" t="inlineStr">
@@ -11294,7 +11294,7 @@
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>SEQ-04</t>
+          <t>SEQ-02</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
@@ -11302,24 +11302,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C265" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C265" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>An accepted order survives a reload (local-first)</t>
+          <t>Free: Plan my day routes to the upsell, never reorders</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>As premium, accept an order, then fully reload the app.</t>
+          <t>As a free user with 2+ tasks on Today, tap 'Plan my day'.</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>Today still shows the accepted order after reload (manualOrder persists on-device). Note: the order does not yet sync across devices, which is a documented follow-up.</t>
+          <t>The Premium screen opens calmly (never a wall), a 'premium.gate_hit' with reason 'sequence' is logged, and the day's order is unchanged.</t>
         </is>
       </c>
       <c r="G265" s="7" t="inlineStr">
@@ -11334,7 +11334,7 @@
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>SEQ-05</t>
+          <t>SEQ-03</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -11342,24 +11342,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C266" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C266" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>A pinned task still wins the very top</t>
+          <t>'Not now' leaves the day untouched</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>As premium, pin a task, then accept a 'Plan my day' sequence that puts a different task first.</t>
+          <t>As premium, open the proposal, then tap 'Not now' or the backdrop.</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>The pinned task stays at the very top, and the accepted order applies to everything below it.</t>
+          <t>The order is exactly as before, nothing reordered, and no manualOrder is written.</t>
         </is>
       </c>
       <c r="G266" s="7" t="inlineStr">
@@ -11374,7 +11374,7 @@
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>SEQ-06</t>
+          <t>SEQ-04</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -11389,17 +11389,17 @@
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>Plan my day offers to lighten a heavy day</t>
+          <t>An accepted order survives a reload (local-first)</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>As premium on a heavy day (6+ tasks), tap 'Plan my day', accept the order.</t>
+          <t>As premium, accept an order, then fully reload the app.</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>After the order applies, a 'Still a full day?' card offers to push a few tasks out to later days. Yes runs the re-spread (propose-then-accept), No leaves it ordered. On a calm day the offer never appears.</t>
+          <t>Today still shows the accepted order after reload (manualOrder persists on-device). Note: the order does not yet sync across devices, which is a documented follow-up.</t>
         </is>
       </c>
       <c r="G267" s="7" t="inlineStr">
@@ -11414,32 +11414,32 @@
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>BIG-01</t>
+          <t>SEQ-05</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
         <is>
-          <t>Big task</t>
-        </is>
-      </c>
-      <c r="C268" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Sequence</t>
+        </is>
+      </c>
+      <c r="C268" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>Mark a task big: the tag, and the weight it adds</t>
+          <t>A pinned task still wins the very top</t>
         </is>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>On Today with a few one-off tasks, tap and hold one, then tap 'Mark as a lot' in the held row's actions. ALSO hold a RECURRING task and confirm 'Mark as a lot' is offered there too (a chore can be a lot; this used to be offered only via the bulk bar).</t>
+          <t>As premium, pin a task, then accept a 'Plan my day' sequence that puts a different task first.</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>The card closes and the task shows a calm accent 'Big' tag beside its title (never red, never a warning), with a brief validating note ('Marked as a lot...'). The weight gauge fills further and reads heavier (one big task floors the bar to at least 'A full day, but doable.'). Free for everyone, no upsell.</t>
+          <t>The pinned task stays at the very top, and the accepted order applies to everything below it.</t>
         </is>
       </c>
       <c r="G268" s="7" t="inlineStr">
@@ -11454,12 +11454,12 @@
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>BIG-02</t>
+          <t>SEQ-06</t>
         </is>
       </c>
       <c r="B269" s="7" t="inlineStr">
         <is>
-          <t>Big task</t>
+          <t>Sequence</t>
         </is>
       </c>
       <c r="C269" s="10" t="inlineStr">
@@ -11469,17 +11469,17 @@
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>Big is a multi-select toggle</t>
+          <t>Plan my day offers to lighten a heavy day</t>
         </is>
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>Hold a task, 'Select more', tick another, then tap 'Mark as a lot'; then re-select tasks that are all big and tap the action again (it now reads 'Not big').</t>
+          <t>As premium on a heavy day (6+ tasks), tap 'Plan my day', accept the order.</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>The first tap marks every selected task big at once. When all selected tasks are already big the action reads 'Not big' and clears the mark off all of them. A mixed selection marks all big (the additive default).</t>
+          <t>After the order applies, a 'Still a full day?' card offers to push a few tasks out to later days. Yes runs the re-spread (propose-then-accept), No leaves it ordered. On a calm day the offer never appears.</t>
         </is>
       </c>
       <c r="G269" s="7" t="inlineStr">
@@ -11494,7 +11494,7 @@
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>BIG-03</t>
+          <t>BIG-01</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
@@ -11502,24 +11502,24 @@
           <t>Big task</t>
         </is>
       </c>
-      <c r="C270" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C270" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>A lone big task lifts the bar but is not a re-spread problem</t>
+          <t>Mark a task big: the tag, and the weight it adds</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>Have just one or two tasks on Today, one marked big.</t>
+          <t>On Today with a few one-off tasks, tap and hold one, then tap 'Mark as a lot' in the held row's actions. ALSO hold a RECURRING task and confirm 'Mark as a lot' is offered there too (a chore can be a lot; this used to be offered only via the bulk bar).</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>The weight gauge reads at least 'A full day, but doable.' (the big task is felt), but 'Today's looking full' and 'Lighten today' do NOT appear for a lone big task (re-spreading cannot dissolve one big rock; Break it down is the tool). A big task plus a real pile (weighted load 6+) does surface Lighten today.</t>
+          <t>The card closes and the task shows a calm accent 'Big' tag beside its title (never red, never a warning), with a brief validating note ('Marked as a lot...'). The weight gauge fills further and reads heavier (one big task floors the bar to at least 'A full day, but doable.'). Free for everyone, no upsell.</t>
         </is>
       </c>
       <c r="G270" s="7" t="inlineStr">
@@ -11534,7 +11534,7 @@
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>BIG-04</t>
+          <t>BIG-02</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Finishing a big task is a big-win in the Calendar</t>
+          <t>Big is a multi-select toggle</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>Mark a task big, complete it, then open the Calendar to its day.</t>
+          <t>Hold a task, 'Select more', tick another, then tap 'Mark as a lot'; then re-select tasks that are all big and tap the action again (it now reads 'Not big').</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>The completed task carries the warmer 'a big one' treatment on its day, the same payoff a long-dreaded or chunky task earns. The big flag never adds disappointment if the task is left unfinished.</t>
+          <t>The first tap marks every selected task big at once. When all selected tasks are already big the action reads 'Not big' and clears the mark off all of them. A mixed selection marks all big (the additive default).</t>
         </is>
       </c>
       <c r="G271" s="7" t="inlineStr">
@@ -11574,7 +11574,7 @@
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>BIG-05</t>
+          <t>BIG-03</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -11589,17 +11589,17 @@
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Big syncs across devices (and old marks survive the upgrade)</t>
+          <t>A lone big task lifts the bar but is not a re-spread problem</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>Signed in on two devices (e.g. web + Android). Mark a task big on device 1, wait for or trigger a sync, then open device 2. Then unmark it on device 2 and check device 1. Prerequisite: an account with the same task on both.</t>
+          <t>Have just one or two tasks on Today, one marked big.</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>The Big tag appears on device 2 (with its weight-gauge effect), and the unmark travels back: no resurrection, the newest change wins. Marks made BEFORE this build (when big was device-only) are seeded up to the account on that device's first sync rather than erased. One known transition quirk: a device still on a PRE-sync build can re-surface a cleared big once when it upgrades; clearing it again sticks everywhere. Manual order (Plan my order) remains per-device by design.</t>
+          <t>The weight gauge reads at least 'A full day, but doable.' (the big task is felt), but 'Today's looking full' and 'Lighten today' do NOT appear for a lone big task (re-spreading cannot dissolve one big rock; Break it down is the tool). A big task plus a real pile (weighted load 6+) does surface Lighten today.</t>
         </is>
       </c>
       <c r="G272" s="7" t="inlineStr">
@@ -11614,37 +11614,37 @@
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>NAV-01</t>
+          <t>BIG-04</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
         <is>
-          <t>Rooms</t>
-        </is>
-      </c>
-      <c r="C273" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Big task</t>
+        </is>
+      </c>
+      <c r="C273" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Rooms sheet caps its width on wide web</t>
+          <t>Finishing a big task is a big-win in the Calendar</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>On a wide desktop browser, open Rooms (the header pill).</t>
+          <t>Mark a task big, complete it, then open the Calendar to its day.</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>The sheet is a centred column (about 560px, matching the page content), not full-bleed, so the 'Premium' gradient pill on 'Chart a course' sits beside its label rather than at the far screen edge. On a phone the sheet stays full-width with the pill at the row's edge.</t>
+          <t>The completed task carries the warmer 'a big one' treatment on its day, the same payoff a long-dreaded or chunky task earns. The big flag never adds disappointment if the task is left unfinished.</t>
         </is>
       </c>
       <c r="G273" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H273" s="7" t="inlineStr"/>
@@ -11654,32 +11654,32 @@
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>OUR-01</t>
+          <t>BIG-05</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C274" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Big task</t>
+        </is>
+      </c>
+      <c r="C274" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>The door only exists for an allowed account</t>
+          <t>Big syncs across devices (and old marks survive the upgrade)</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>Sign in as an account that is NOT on the ours_allowlist and open Settings. Then sign in as one that is.</t>
+          <t>Signed in on two devices (e.g. web + Android). Mark a task big on device 1, wait for or trigger a sync, then open device 2. Then unmark it on device 2 and check device 1. Prerequisite: an account with the same task on both.</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>The 'Ours' row is absent for the first account and present for the second. Nobody is ever offered a door that answers 'shared lists aren't open yet'.</t>
+          <t>The Big tag appears on device 2 (with its weight-gauge effect), and the unmark travels back: no resurrection, the newest change wins. Marks made BEFORE this build (when big was device-only) are seeded up to the account on that device's first sync rather than erased. One known transition quirk: a device still on a PRE-sync build can re-surface a cleared big once when it upgrades; clearing it again sticks everywhere. Manual order (Plan my order) remains per-device by design.</t>
         </is>
       </c>
       <c r="G274" s="7" t="inlineStr">
@@ -11694,37 +11694,37 @@
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>OUR-02</t>
+          <t>NAV-01</t>
         </is>
       </c>
       <c r="B275" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C275" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="C275" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>Signed out: the explanation, never a nag</t>
+          <t>Rooms sheet caps its width on wide web</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>Sign out, then open /ours directly.</t>
+          <t>On a wide desktop browser, open Rooms (the header pill).</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>A calm one-screen explanation of why sharing needs an account, and a way to sign in. No pressure, no count of what you are missing.</t>
+          <t>The sheet is a centred column (about 560px, matching the page content), not full-bleed, so the 'Premium' gradient pill on 'Chart a course' sits beside its label rather than at the far screen edge. On a phone the sheet stays full-width with the pill at the row's edge.</t>
         </is>
       </c>
       <c r="G275" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H275" s="7" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>OUR-03</t>
+          <t>OUR-01</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
@@ -11749,17 +11749,17 @@
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Name the list and mint a code</t>
+          <t>The door only exists for an allowed account</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>Ours &gt; Start a shared list. Pick 'The house'. Type your own name. Type the OTHER account's email exactly. Get a code.</t>
+          <t>Sign in as an account that is NOT on the ours_allowlist and open Settings. Then sign in as one that is.</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>A six-character code appears grouped as XXX-XXX, containing no 0, 1, I, L or O. The screen says it works once, for the next day, and only for the address you gave.</t>
+          <t>The 'Ours' row is absent for the first account and present for the second. Nobody is ever offered a door that answers 'shared lists aren't open yet'.</t>
         </is>
       </c>
       <c r="G276" s="7" t="inlineStr">
@@ -11774,7 +11774,7 @@
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>OUR-04</t>
+          <t>OUR-02</t>
         </is>
       </c>
       <c r="B277" s="7" t="inlineStr">
@@ -11789,17 +11789,17 @@
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Join from the second account</t>
+          <t>Signed out: the explanation, never a nag</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>On the second account, Ours &gt; Join with a code. Type the code (try it lower-case and with the dash). Type your own name. Join.</t>
+          <t>Sign out, then open /ours directly.</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>You land on the shared list showing the FIRST person's chosen name and the list's name ('The house'). No email address is shown anywhere, to either person.</t>
+          <t>A calm one-screen explanation of why sharing needs an account, and a way to sign in. No pressure, no count of what you are missing.</t>
         </is>
       </c>
       <c r="G277" s="7" t="inlineStr">
@@ -11814,7 +11814,7 @@
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>OUR-05</t>
+          <t>OUR-03</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>The first person sees the arrival without refreshing</t>
+          <t>Name the list and mint a code</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>Leave the first account sitting on the Ours screen while the second joins.</t>
+          <t>Ours &gt; Start a shared list. Pick 'The house'. Type your own name. Type the OTHER account's email exactly. Get a code.</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>Within about ten seconds it announces that they joined, with a way out for someone who meant a different person. It never says how long they took.</t>
+          <t>A six-character code appears grouped as XXX-XXX, containing no 0, 1, I, L or O. The screen says it works once, for the next day, and only for the address you gave.</t>
         </is>
       </c>
       <c r="G278" s="7" t="inlineStr">
@@ -11854,7 +11854,7 @@
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>OUR-06</t>
+          <t>OUR-04</t>
         </is>
       </c>
       <c r="B279" s="7" t="inlineStr">
@@ -11862,24 +11862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C279" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C279" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>A wrong code says one calm thing</t>
+          <t>Join from the second account</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>Try a made-up code, then a code meant for a different address, then the same code twice.</t>
+          <t>On the second account, Ours &gt; Join with a code. Type the code (try it lower-case and with the dash). Type your own name. Join.</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>Every one gives the SAME single line ('That code isn't valid.'). Nothing hints at which reason, so a guesser learns nothing. Repeated wrong tries eventually ask you to have a break.</t>
+          <t>You land on the shared list showing the FIRST person's chosen name and the list's name ('The house'). No email address is shown anywhere, to either person.</t>
         </is>
       </c>
       <c r="G279" s="7" t="inlineStr">
@@ -11894,7 +11894,7 @@
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>OUR-07</t>
+          <t>OUR-05</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -11902,24 +11902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C280" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C280" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Mistyped invitee address is recoverable</t>
+          <t>The first person sees the arrival without refreshing</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>Mint a code with a deliberately wrong email, then use 'Wrong address? Start again' and mint a fresh one with the right address.</t>
+          <t>Leave the first account sitting on the Ours screen while the second joins.</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>The new code works and the old one does not. Nothing had to be deleted to recover, and no address is ever displayed back to you.</t>
+          <t>Within about ten seconds it announces that they joined, with a way out for someone who meant a different person. It never says how long they took.</t>
         </is>
       </c>
       <c r="G280" s="7" t="inlineStr">
@@ -11934,7 +11934,7 @@
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>OUR-08</t>
+          <t>OUR-06</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Rename the list, and both sides see it</t>
+          <t>A wrong code says one calm thing</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>On the shared list, tap the list's name, type a new one, and confirm. Reopen Ours on the other account.</t>
+          <t>Try a made-up code, then a code meant for a different address, then the same code twice.</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>Both people see the new name. An emptied name falls back to the app's own word, in each person's own language.</t>
+          <t>Every one gives the SAME single line ('That code isn't valid.'). Nothing hints at which reason, so a guesser learns nothing. Repeated wrong tries eventually ask you to have a break.</t>
         </is>
       </c>
       <c r="G281" s="7" t="inlineStr">
@@ -11974,7 +11974,7 @@
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>OUR-09</t>
+          <t>OUR-07</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -11982,24 +11982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C282" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C282" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>Leaving freezes and takes nothing</t>
+          <t>Mistyped invitee address is recoverable</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>On one account, Leave this list. Then open Ours on BOTH accounts.</t>
+          <t>Mint a code with a deliberately wrong email, then use 'Wrong address? Start again' and mint a fresh one with the right address.</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>Both see 'This list is closed' and can still read everything. Nothing was deleted from either side. Neither person is told off, and neither is told what the other did.</t>
+          <t>The new code works and the old one does not. Nothing had to be deleted to recover, and no address is ever displayed back to you.</t>
         </is>
       </c>
       <c r="G282" s="7" t="inlineStr">
@@ -12014,7 +12014,7 @@
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>OUR-10</t>
+          <t>OUR-08</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
@@ -12029,17 +12029,17 @@
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>Remove a closed list from your side only</t>
+          <t>Rename the list, and both sides see it</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Remove this list'. Then check the other account.</t>
+          <t>On the shared list, tap the list's name, type a new one, and confirm. Reopen Ours on the other account.</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>It disappears for you. The other person still has their copy and is not notified.</t>
+          <t>Both people see the new name. An emptied name falls back to the app's own word, in each person's own language.</t>
         </is>
       </c>
       <c r="G283" s="7" t="inlineStr">
@@ -12054,7 +12054,7 @@
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>OUR-11</t>
+          <t>OUR-09</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -12069,17 +12069,17 @@
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>Nothing anywhere attributes a task to a person</t>
+          <t>Leaving freezes and takes nothing</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>With a shared list live, look at Ours, Today, the Lookback and Settings on both accounts.</t>
+          <t>On one account, Leave this list. Then open Ours on BOTH accounts.</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>No initials, no 'done by', no counts of who did what, no progress bar across two people, no activity feed. The data to build one does not exist.</t>
+          <t>Both see 'This list is closed' and can still read everything. Nothing was deleted from either side. Neither person is told off, and neither is told what the other did.</t>
         </is>
       </c>
       <c r="G284" s="7" t="inlineStr">
@@ -12094,7 +12094,7 @@
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>OUR-13</t>
+          <t>OUR-10</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
@@ -12102,24 +12102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C285" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C285" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>The code stays on screen from the moment it is minted</t>
+          <t>Remove a closed list from your side only</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>On a throttled connection (devtools, slow 3G), fill the create form and tap the code button.</t>
+          <t>On a closed list, tap 'Remove this list'. Then check the other account.</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>The six characters appear as soon as the button stops spinning and are NEVER replaced by the intro screen. The server returns that code exactly once, so a flash back to 'Start a shared list' loses it for good.</t>
+          <t>It disappears for you. The other person still has their copy and is not notified.</t>
         </is>
       </c>
       <c r="G285" s="7" t="inlineStr">
@@ -12134,7 +12134,7 @@
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>OUR-14</t>
+          <t>OUR-11</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -12149,17 +12149,17 @@
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>'Get a new code' reaches the form and mints a different code</t>
+          <t>Nothing anywhere attributes a task to a person</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>From the waiting screen, tap the get-a-new-code action. Change the email. Submit.</t>
+          <t>With a shared list live, look at Ours, Today, the Lookback and Settings on both accounts.</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>The create form appears with your name and list name already filled. Submitting shows a DIFFERENT six characters, and the old one no longer works. Your chosen name is unchanged afterwards.</t>
+          <t>No initials, no 'done by', no counts of who did what, no progress bar across two people, no activity feed. The data to build one does not exist.</t>
         </is>
       </c>
       <c r="G286" s="7" t="inlineStr">
@@ -12174,7 +12174,7 @@
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>OUR-120</t>
+          <t>OUR-13</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -12189,17 +12189,17 @@
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Waiting-with-no-code is reachable, says so, and the re-mint is a real button</t>
+          <t>The code stays on screen from the moment it is minted</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>Mint a code, leave Ours entirely (back to Today), then come back via the MENU's Ours row before anyone joins.</t>
+          <t>On a throttled connection (devtools, slow 3G), fill the create form and tap the code button.</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>The Menu lands on the shared LIST (usable solo while waiting), and the list's header line reads 'Waiting for your person - Get a new code' where 'Kept with {name}' will later sit; tapping it opens the pairing screen (both Melroy's C6 check and the field report hit this as a dead end before 2026-09-20). That screen is titled 'Waiting for your person', NOT 'Read this to your person' over an empty space (the code renders exactly once; the server keeps only a hash, so it can never be re-shown), and 'Get a new code' is a full primary button there, not a quiet text link. While the code IS still on screen, the old title and quiet link stay as they were.</t>
+          <t>The six characters appear as soon as the button stops spinning and are NEVER replaced by the intro screen. The server returns that code exactly once, so a flash back to 'Start a shared list' loses it for good.</t>
         </is>
       </c>
       <c r="G287" s="7" t="inlineStr">
@@ -12214,7 +12214,7 @@
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>OUR-121</t>
+          <t>OUR-14</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -12229,17 +12229,17 @@
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Whose email, and which code goes where</t>
+          <t>'Get a new code' reaches the form and mints a different code</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>Signed out: read the Menu's Ours line, open Ours, read the signed-out screen, tap Sign in and read the field. Then, on the sign-in code step, paste an Ours-style code (letters in it). Separately, signed in, open Ours 'I have a code' and type a 6-digit emailed sign-in code.</t>
+          <t>From the waiting screen, tap the get-a-new-code action. Change the email. Submit.</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>The Menu's Ours line reads 'A list kept with one person. Sign in first.' (the old 'Needs your email, no password' invited typing the PARTNER'S email; a real user did exactly that on 2026-09-13 and it became their account). The Ours signed-out screen opens with the plain fact 'You're not signed in on this phone.' The sign-in email field is labelled 'Your own email', and the subtitle says sharing happens later, in Ours, with a code, never by typing the partner's email here. Letters in the 6-digit code field draw the calm hint that it will be an Ours invite code (a hint, never an auto-redirect or a cleared field). Six bare digits failing in the Ours join field add one line naming the emailed sign-in code as the likely mix-up, alongside the unchanged honest failure.</t>
+          <t>The create form appears with your name and list name already filled. Submitting shows a DIFFERENT six characters, and the old one no longer works. Your chosen name is unchanged afterwards.</t>
         </is>
       </c>
       <c r="G288" s="7" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>OUR-15</t>
+          <t>OUR-120</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -12269,17 +12269,17 @@
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Leave a list, then start a new one WITHOUT deleting the old</t>
+          <t>Waiting-with-no-code is reachable, says so, and the re-mint is a real button</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>Leave a shared list. On the closed screen, start a new shared list with someone else.</t>
+          <t>Mint a code, leave Ours entirely (back to Today), then come back via the MENU's Ours row before anyone joins.</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>Starting a new list is offered on the closed screen itself and works. The old list is NOT deleted and is still readable. At no point is destroying it the only way forward.</t>
+          <t>The Menu lands on the shared LIST (usable solo while waiting), and the list's header line reads 'Waiting for your person - Get a new code' where 'Kept with {name}' will later sit; tapping it opens the pairing screen (both Melroy's C6 check and the field report hit this as a dead end before 2026-09-20). That screen is titled 'Waiting for your person', NOT 'Read this to your person' over an empty space (the code renders exactly once; the server keeps only a hash, so it can never be re-shown), and 'Get a new code' is a full primary button there, not a quiet text link. While the code IS still on screen, the old title and quiet link stay as they were.</t>
         </is>
       </c>
       <c r="G289" s="7" t="inlineStr">
@@ -12294,7 +12294,7 @@
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>OUR-16</t>
+          <t>OUR-121</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -12309,17 +12309,17 @@
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>A failed read never offers to start a list you already have</t>
+          <t>Whose email, and which code goes where</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, turn the network off and open Ours.</t>
+          <t>Signed out: read the Menu's Ours line, open Ours, read the signed-out screen, tap Sign in and read the field. Then, on the sign-in code step, paste an Ours-style code (letters in it). Separately, signed in, open Ours 'I have a code' and type a 6-digit emailed sign-in code.</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>A calm connection line. The screen never says you have no shared list and never offers to start one. Turning the network back on recovers without a restart.</t>
+          <t>The Menu's Ours line reads 'A list kept with one person. Sign in first.' (the old 'Needs your email, no password' invited typing the PARTNER'S email; a real user did exactly that on 2026-09-13 and it became their account). The Ours signed-out screen opens with the plain fact 'You're not signed in on this phone.' The sign-in email field is labelled 'Your own email', and the subtitle says sharing happens later, in Ours, with a code, never by typing the partner's email here. Letters in the 6-digit code field draw the calm hint that it will be an Ours invite code (a hint, never an auto-redirect or a cleared field). Six bare digits failing in the Ours join field add one line naming the emailed sign-in code as the likely mix-up, alongside the unchanged honest failure.</t>
         </is>
       </c>
       <c r="G290" s="7" t="inlineStr">
@@ -12334,7 +12334,7 @@
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>OUR-17</t>
+          <t>OUR-15</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
@@ -12342,24 +12342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C291" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C291" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>A list nobody joined can be left</t>
+          <t>Leave a list, then start a new one WITHOUT deleting the old</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>Create a list, get a code, give it to nobody. Return to Ours.</t>
+          <t>Leave a shared list. On the closed screen, start a new shared list with someone else.</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>There is a way out on the waiting screen, and its wording does not claim it closes for two people. After leaving, you can start or join a list again.</t>
+          <t>Starting a new list is offered on the closed screen itself and works. The old list is NOT deleted and is still readable. At no point is destroying it the only way forward.</t>
         </is>
       </c>
       <c r="G291" s="7" t="inlineStr">
@@ -12374,7 +12374,7 @@
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>OUR-18</t>
+          <t>OUR-16</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -12382,24 +12382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C292" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C292" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>The arrival announces once and stays announced</t>
+          <t>A failed read never offers to start a list you already have</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>Sit on the waiting screen while the other account joins. Background the app and return.</t>
+          <t>With a live shared list, turn the network off and open Ours.</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>The name appears once and does not flicker back to waiting and re-announce. The way out beside it ('that wasn't who I meant') never appears on a list you did not just gain a person on.</t>
+          <t>A calm connection line. The screen never says you have no shared list and never offers to start one. Turning the network back on recovers without a restart.</t>
         </is>
       </c>
       <c r="G292" s="7" t="inlineStr">
@@ -12414,7 +12414,7 @@
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>OUR-19</t>
+          <t>OUR-17</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
@@ -12429,17 +12429,17 @@
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>A repeat the app cannot read is SHOWN, never hidden</t>
+          <t>A list nobody joined can be left</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>Requires two app versions. On the newer one, set a shared task to a cadence the older build does not have. Open the list on the older build.</t>
+          <t>Create a list, get a code, give it to nobody. Return to Ours.</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>The task is visible on both, with whatever cadence line the newer app left. It is never silently absent from one person's list, and the older app does not erase the schedule when it syncs.</t>
+          <t>There is a way out on the waiting screen, and its wording does not claim it closes for two people. After leaving, you can start or join a list again.</t>
         </is>
       </c>
       <c r="G293" s="7" t="inlineStr">
@@ -12454,7 +12454,7 @@
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>OUR-20</t>
+          <t>OUR-18</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -12462,24 +12462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C294" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C294" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>The room opens from Today and from the Menu</t>
+          <t>The arrival announces once and stays announced</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, tap the 'Ours · {name}' row on Today. Then go back and reach it through Menu › Ours.</t>
+          <t>Sit on the waiting screen while the other account joins. Background the app and return.</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>Both land on the shared list itself, not the pairing screen. The header line reads 'Kept with {their name}' and tapping it goes to the pairing/management screen.</t>
+          <t>The name appears once and does not flicker back to waiting and re-announce. The way out beside it ('that wasn't who I meant') never appears on a list you did not just gain a person on.</t>
         </is>
       </c>
       <c r="G294" s="7" t="inlineStr">
@@ -12494,7 +12494,7 @@
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>OUR-21</t>
+          <t>OUR-19</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
@@ -12502,24 +12502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C295" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C295" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>Add, tick and UN-tick on the shared list</t>
+          <t>A repeat the app cannot read is SHOWN, never hidden</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>Add a task in the room. Tick it. Un-tick it. Watch the other account (reload or wait ~15s).</t>
+          <t>Requires two app versions. On the newer one, set a shared task to a cadence the older build does not have. Open the list on the older build.</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>Every step appears on both. Un-ticking works as easily as ticking, on both sides. No affirmation or celebration fires on Ours.</t>
+          <t>The task is visible on both, with whatever cadence line the newer app left. It is never silently absent from one person's list, and the older app does not erase the schedule when it syncs.</t>
         </is>
       </c>
       <c r="G295" s="7" t="inlineStr">
@@ -12534,7 +12534,7 @@
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>OUR-22</t>
+          <t>OUR-20</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -12549,17 +12549,17 @@
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>Un-tick a one-off the DAY AFTER it was ticked</t>
+          <t>The room opens from Today and from the Menu</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>Tick a shared one-off. Change the device date to tomorrow (or wait a day), reopen the room, tap it again.</t>
+          <t>With a live shared list, tap the 'Ours · {name}' row on Today. Then go back and reach it through Menu › Ours.</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>It un-ticks. (The pre-fix build could never un-tick it again, on any device, forever.)</t>
+          <t>Both land on the shared list itself, not the pairing screen. The header line reads 'Kept with {their name}' and tapping it goes to the pairing/management screen.</t>
         </is>
       </c>
       <c r="G296" s="7" t="inlineStr">
@@ -12574,7 +12574,7 @@
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>OUR-23</t>
+          <t>OUR-21</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -12589,17 +12589,17 @@
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>Bring to my Today makes a COPY, and marks only yours</t>
+          <t>Add, tick and UN-tick on the shared list</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>Hold a shared row, tap 'Bring to my Today'. Look at your Today, then at the shared list on BOTH accounts.</t>
+          <t>Add a task in the room. Tick it. Un-tick it. Watch the other account (reload or wait ~15s).</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>Your Today shows the task with a faint '· Ours'. The shared row is completely unchanged on both sides, with no marker of any kind. The held card now reads 'Already on your Today' and cannot make a second copy.</t>
+          <t>Every step appears on both. Un-ticking works as easily as ticking, on both sides. No affirmation or celebration fires on Ours.</t>
         </is>
       </c>
       <c r="G297" s="7" t="inlineStr">
@@ -12614,7 +12614,7 @@
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>OUR-24</t>
+          <t>OUR-22</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -12629,17 +12629,17 @@
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>Your tick on the copy closes both</t>
+          <t>Un-tick a one-off the DAY AFTER it was ticked</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>Tick the brought copy on your Today. Check the shared list on the other account.</t>
+          <t>Tick a shared one-off. Change the device date to tomorrow (or wait a day), reopen the room, tap it again.</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>The shared row is done. It enters YOUR Lookback. Nothing on the other side says who did it.</t>
+          <t>It un-ticks. (The pre-fix build could never un-tick it again, on any device, forever.)</t>
         </is>
       </c>
       <c r="G298" s="7" t="inlineStr">
@@ -12654,7 +12654,7 @@
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>OUR-25</t>
+          <t>OUR-23</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
@@ -12669,17 +12669,17 @@
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>Ticking a brought copy on a device that has NEVER opened the room</t>
+          <t>Bring to my Today makes a COPY, and marks only yours</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>Bring a task over on phone A. Sign in on a second device (or clear its local data) and go straight to Today WITHOUT opening Ours. Tick the copy there.</t>
+          <t>Hold a shared row, tap 'Bring to my Today'. Look at your Today, then at the shared list on BOTH accounts.</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>The shared row closes. (The pre-fix build silently discarded the tick with no error.)</t>
+          <t>Your Today shows the task with a faint '· Ours'. The shared row is completely unchanged on both sides, with no marker of any kind. The held card now reads 'Already on your Today' and cannot make a second copy.</t>
         </is>
       </c>
       <c r="G299" s="7" t="inlineStr">
@@ -12694,7 +12694,7 @@
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>OUR-26</t>
+          <t>OUR-24</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
@@ -12709,17 +12709,17 @@
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>Their tick leaves a rest-note, never a strike-through</t>
+          <t>Your tick on the copy closes both</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>Bring a task over. On the OTHER account, tick the shared row. Return to your Today.</t>
+          <t>Tick the brought copy on your Today. Check the shared list on the other account.</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>Your copy is gone from the day, replaced by a dashed sage line: 'Handled on Ours. It's off your day.' It is NOT struck through and does NOT appear in your Lookback. Leaving Today and coming back clears the note.</t>
+          <t>The shared row is done. It enters YOUR Lookback. Nothing on the other side says who did it.</t>
         </is>
       </c>
       <c r="G300" s="7" t="inlineStr">
@@ -12734,7 +12734,7 @@
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>OUR-27</t>
+          <t>OUR-25</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -12742,24 +12742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C301" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C301" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>Share to Ours warns about the length BEFORE it copies</t>
+          <t>Ticking a brought copy on a device that has NEVER opened the room</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>Hold one of your own Today tasks with a very long title (500+ chars), open More, tap 'Share to Ours'.</t>
+          <t>Bring a task over on phone A. Sign in on a second device (or clear its local data) and go straight to Today WITHOUT opening Ours. Tick the copy there.</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>A line says Ours keeps titles shorter and this one will be trimmed, BEFORE the copy is made. The copy appears on the shared list. 'Share to Ours' is absent entirely when there is no live list.</t>
+          <t>The shared row closes. (The pre-fix build silently discarded the tick with no error.)</t>
         </is>
       </c>
       <c r="G301" s="7" t="inlineStr">
@@ -12774,7 +12774,7 @@
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
         <is>
-          <t>OUR-28</t>
+          <t>OUR-26</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
@@ -12789,17 +12789,17 @@
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>A repeat set on Ours uses the SAME cadence sheet as home</t>
+          <t>Their tick leaves a rest-note, never a strike-through</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>Hold a shared row, tap 'Repeat…'. Compare with Menu › Repeating › Edit on a personal task.</t>
+          <t>Bring a task over. On the OTHER account, tick the shared row. Return to your Today.</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>Identical controls. The commit button NAMES the cadence ('Every day', 'Every 2 days'), on both. The Ours sheet adds one line: 'You'll both see it on its day.' It appears on its days for both people.</t>
+          <t>Your copy is gone from the day, replaced by a dashed sage line: 'Handled on Ours. It's off your day.' It is NOT struck through and does NOT appear in your Lookback. Leaving Today and coming back clears the note.</t>
         </is>
       </c>
       <c r="G302" s="7" t="inlineStr">
@@ -12814,7 +12814,7 @@
     <row r="303">
       <c r="A303" s="6" t="inlineStr">
         <is>
-          <t>OUR-29</t>
+          <t>OUR-27</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
@@ -12822,24 +12822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C303" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C303" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>A cadence this build cannot read is inert, and says why</t>
+          <t>Share to Ours warns about the length BEFORE it copies</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>Get a shared row carrying a recurrence this build does not understand (a newer build, or hand-write one via the API).</t>
+          <t>Hold one of your own Today tasks with a very long title (500+ chars), open More, tap 'Share to Ours'.</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>The row is SHOWN, never hidden. Tapping it does nothing and a line explains it is safe and will appear on its days after an update. 'Repeat…' is withheld. It never marks itself done.</t>
+          <t>A line says Ours keeps titles shorter and this one will be trimmed, BEFORE the copy is made. The copy appears on the shared list. 'Share to Ours' is absent entirely when there is no live list.</t>
         </is>
       </c>
       <c r="G303" s="7" t="inlineStr">
@@ -12854,7 +12854,7 @@
     <row r="304">
       <c r="A304" s="6" t="inlineStr">
         <is>
-          <t>OUR-30</t>
+          <t>OUR-28</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -12862,24 +12862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C304" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C304" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash marks what changed, and never your own edits</t>
+          <t>A repeat set on Ours uses the SAME cadence sheet as home</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>Have the other account add and change a few rows. Open the room. Then tick something yourself and reopen.</t>
+          <t>Hold a shared row, tap 'Repeat…'. Compare with Menu › Repeating › Edit on a personal task.</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>Their changed rows carry a tint and a firmer border on arrival; a screen reader says 'changed since you last looked'. Your OWN edits are never washed. Leaving and returning clears it.</t>
+          <t>Identical controls. The commit button NAMES the cadence ('Every day', 'Every 2 days'), on both. The Ours sheet adds one line: 'You'll both see it on its day.' It appears on its days for both people.</t>
         </is>
       </c>
       <c r="G304" s="7" t="inlineStr">
@@ -12894,7 +12894,7 @@
     <row r="305">
       <c r="A305" s="6" t="inlineStr">
         <is>
-          <t>OUR-31</t>
+          <t>OUR-29</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -12902,24 +12902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C305" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C305" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>Recently removed puts a task back</t>
+          <t>A cadence this build cannot read is inert, and says why</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>Remove a shared row. Scroll to the foot of the list.</t>
+          <t>Get a shared row carrying a recurrence this build does not understand (a newer build, or hand-write one via the API).</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>It sits under 'Recently removed', dimmed, with 'Put it back'. Restoring returns it for both people. Nothing anywhere says which of you removed it.</t>
+          <t>The row is SHOWN, never hidden. Tapping it does nothing and a line explains it is safe and will appear on its days after an update. 'Repeat…' is withheld. It never marks itself done.</t>
         </is>
       </c>
       <c r="G305" s="7" t="inlineStr">
@@ -12934,7 +12934,7 @@
     <row r="306">
       <c r="A306" s="6" t="inlineStr">
         <is>
-          <t>OUR-32</t>
+          <t>OUR-30</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -12949,17 +12949,17 @@
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>Removing a shared REPEAT does not pretend to be 'Skip today'</t>
+          <t>The quiet wash marks what changed, and never your own edits</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>Hold a repeating shared row and look at the shelf.</t>
+          <t>Have the other account add and change a few rows. Open the room. Then tick something yourself and reopen.</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>It reads 'Remove', not 'Skip today', and the spoken label names removing the repeat. (The shared list has no per-day skip; the pre-fix build promised one and deleted the series for both people.)</t>
+          <t>Their changed rows carry a tint and a firmer border on arrival; a screen reader says 'changed since you last looked'. Your OWN edits are never washed. Leaving and returning clears it.</t>
         </is>
       </c>
       <c r="G306" s="7" t="inlineStr">
@@ -12974,7 +12974,7 @@
     <row r="307">
       <c r="A307" s="6" t="inlineStr">
         <is>
-          <t>OUR-33</t>
+          <t>OUR-31</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
@@ -12982,24 +12982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C307" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C307" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>A closed list is still readable, and read-only</t>
+          <t>Recently removed puts a task back</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>Leave a list. Open it from the archive on the pairing screen.</t>
+          <t>Remove a shared row. Scroll to the foot of the list.</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>Every row is readable. The capture bar is GONE. Ticking, renaming, removing and re-cadencing all do nothing, and each row says why. Each row still offers taking a copy for yourself.</t>
+          <t>It sits under 'Recently removed', dimmed, with 'Put it back'. Restoring returns it for both people. Nothing anywhere says which of you removed it.</t>
         </is>
       </c>
       <c r="G307" s="7" t="inlineStr">
@@ -13014,7 +13014,7 @@
     <row r="308">
       <c r="A308" s="6" t="inlineStr">
         <is>
-          <t>OUR-34</t>
+          <t>OUR-32</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
@@ -13029,17 +13029,17 @@
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>The archive lists closed lists, and puts them away</t>
+          <t>Removing a shared REPEAT does not pretend to be 'Skip today'</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>With at least one closed list, look under 'Lists you have kept' on the pairing screen.</t>
+          <t>Hold a repeating shared row and look at the shelf.</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>Purpose and closed MONTH only, no counts of any kind. 'Put it away' hides it from the default view; 'Show the ones put away' brings it back. Nothing is deleted.</t>
+          <t>It reads 'Remove', not 'Skip today', and the spoken label names removing the repeat. (The shared list has no per-day skip; the pre-fix build promised one and deleted the series for both people.)</t>
         </is>
       </c>
       <c r="G308" s="7" t="inlineStr">
@@ -13054,7 +13054,7 @@
     <row r="309">
       <c r="A309" s="6" t="inlineStr">
         <is>
-          <t>OUR-35</t>
+          <t>OUR-33</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
@@ -13069,17 +13069,17 @@
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>Reopening together is a handshake, never unilateral</t>
+          <t>A closed list is still readable, and read-only</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Reopen together…' on ONE side only and STAY on that screen, hands off. Read the code to the second account. On that side, tap 'Got a code from them? Enter it to reopen.' (under the reopen hint on the closed-list screen) and enter it. Repeat with the closed list being the ONLY closed list on both accounts.</t>
+          <t>Leave a list. Open it from the archive on the pairing screen.</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>The offering side gets a code and nothing reopens yet. The other side has a named door to the join field and entering the code there reopens the list for both, with everything as it was. It is never asked which kind of code it is, and it works when the closed list on screen is the only one (the D2 'handshake purgatory', 2026-09-22). Within about ten seconds, with nothing touched, the offering side's screen changes on its own: the code is gone and the live list shows 'They used the code. The list is open again…'.</t>
+          <t>Every row is readable. The capture bar is GONE. Ticking, renaming, removing and re-cadencing all do nothing, and each row says why. Each row still offers taking a copy for yourself.</t>
         </is>
       </c>
       <c r="G309" s="7" t="inlineStr">
@@ -13094,7 +13094,7 @@
     <row r="310">
       <c r="A310" s="6" t="inlineStr">
         <is>
-          <t>OUR-122</t>
+          <t>OUR-34</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -13109,17 +13109,17 @@
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>Waiting screens look on their own, and 'Check now' is there for the impatient</t>
+          <t>The archive lists closed lists, and puts them away</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>A: mint a pairing code and stay on that screen, hands off. B: join. Watch A. Then, on a closed list: A taps 'Reopen together…' and stays; B redeems. Watch A. Then, on either waiting screen, tap 'Check now'.</t>
+          <t>With at least one closed list, look under 'Lists you have kept' on the pairing screen.</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>Both times A's screen changes on its own within about ten seconds: the pairing wait becomes '{name} joined.', and the closed list becomes the live list with the 'They used the code' line and the spent code gone. 'Check now' sits under the waiting text and under a minted reopen code, and does the same immediately. Once A has opened the list, the pairing screen underneath stops looking (nothing to see by eye; the rule is focus AND foreground AND under 30 minutes).</t>
+          <t>Purpose and closed MONTH only, no counts of any kind. 'Put it away' hides it from the default view; 'Show the ones put away' brings it back. Nothing is deleted.</t>
         </is>
       </c>
       <c r="G310" s="7" t="inlineStr">
@@ -13134,7 +13134,7 @@
     <row r="311">
       <c r="A311" s="6" t="inlineStr">
         <is>
-          <t>OUR-36</t>
+          <t>OUR-35</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -13149,17 +13149,17 @@
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>Delete for good commits when the screen closes, not on a timer</t>
+          <t>Reopening together is a handshake, never unilateral</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
+          <t>On a closed list, tap 'Reopen together…' on ONE side only and STAY on that screen, hands off. Read the code to the second account. On that side, tap 'Got a code from them? Enter it to reopen.' (under the reopen hint on the closed-list screen) and enter it. Repeat with the closed list being the ONLY closed list on both accounts.</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
+          <t>The offering side gets a code and nothing reopens yet. The other side has a named door to the join field and entering the code there reopens the list for both, with everything as it was. It is never asked which kind of code it is, and it works when the closed list on screen is the only one (the D2 'handshake purgatory', 2026-09-22). Within about ten seconds, with nothing touched, the offering side's screen changes on its own: the code is gone and the live list shows 'They used the code. The list is open again…'.</t>
         </is>
       </c>
       <c r="G311" s="7" t="inlineStr">
@@ -13174,7 +13174,7 @@
     <row r="312">
       <c r="A312" s="6" t="inlineStr">
         <is>
-          <t>OUR-37</t>
+          <t>OUR-122</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -13189,17 +13189,17 @@
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>Rename yourself, and only yourself</t>
+          <t>Waiting screens look on their own, and 'Check now' is there for the impatient</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
+          <t>A: mint a pairing code and stay on that screen, hands off. B: join. Watch A. Then, on a closed list: A taps 'Reopen together…' and stays; B redeems. Watch A. Then, on either waiting screen, tap 'Check now'.</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
+          <t>Both times A's screen changes on its own within about ten seconds: the pairing wait becomes '{name} joined.', and the closed list becomes the live list with the 'They used the code' line and the spent code gone. 'Check now' sits under the waiting text and under a minted reopen code, and does the same immediately. Once A has opened the list, the pairing screen underneath stops looking (nothing to see by eye; the rule is focus AND foreground AND under 30 minutes).</t>
         </is>
       </c>
       <c r="G312" s="7" t="inlineStr">
@@ -13214,7 +13214,7 @@
     <row r="313">
       <c r="A313" s="6" t="inlineStr">
         <is>
-          <t>OUR-38</t>
+          <t>OUR-36</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -13222,24 +13222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C313" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C313" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>A dropped signal never throws you out of the room</t>
+          <t>Delete for good commits when the screen closes, not on a timer</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
+          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
+          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
         </is>
       </c>
       <c r="G313" s="7" t="inlineStr">
@@ -13254,7 +13254,7 @@
     <row r="314">
       <c r="A314" s="6" t="inlineStr">
         <is>
-          <t>OUR-39</t>
+          <t>OUR-37</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -13262,24 +13262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C314" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C314" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>Report this list reaches us and tells nobody else</t>
+          <t>Rename yourself, and only yourself</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
+          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
+          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
         </is>
       </c>
       <c r="G314" s="7" t="inlineStr">
@@ -13294,7 +13294,7 @@
     <row r="315">
       <c r="A315" s="6" t="inlineStr">
         <is>
-          <t>OUR-40</t>
+          <t>OUR-38</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -13302,24 +13302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C315" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C315" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
+          <t>A dropped signal never throws you out of the room</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
+          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
+          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
         </is>
       </c>
       <c r="G315" s="7" t="inlineStr">
@@ -13334,7 +13334,7 @@
     <row r="316">
       <c r="A316" s="6" t="inlineStr">
         <is>
-          <t>OUR-41</t>
+          <t>OUR-39</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -13342,24 +13342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C316" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C316" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>Leaving is the block, and needs no reason</t>
+          <t>Report this list reaches us and tells nobody else</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap 'Leave this list'.</t>
+          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
+          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
         </is>
       </c>
       <c r="G316" s="7" t="inlineStr">
@@ -13374,32 +13374,32 @@
     <row r="317">
       <c r="A317" s="6" t="inlineStr">
         <is>
-          <t>LEG-05</t>
+          <t>OUR-40</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
         <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="C317" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="C317" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>The shared-list clauses are in both copies of both documents</t>
+          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
+          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
+          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
         </is>
       </c>
       <c r="G317" s="7" t="inlineStr">
@@ -13414,7 +13414,7 @@
     <row r="318">
       <c r="A318" s="6" t="inlineStr">
         <is>
-          <t>OUR-42</t>
+          <t>OUR-41</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -13422,24 +13422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C318" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C318" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>A change on one phone appears on the other WITHOUT touching it</t>
+          <t>Leaving is the block, and needs no reason</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
+          <t>On a live list, tap 'Leave this list'.</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
+          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
         </is>
       </c>
       <c r="G318" s="7" t="inlineStr">
@@ -13454,32 +13454,32 @@
     <row r="319">
       <c r="A319" s="6" t="inlineStr">
         <is>
-          <t>OUR-43</t>
+          <t>LEG-05</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C319" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C319" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>Opening your own list does not bounce you back</t>
+          <t>The shared-list clauses are in both copies of both documents</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
+          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
+          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
         </is>
       </c>
       <c r="G319" s="7" t="inlineStr">
@@ -13494,7 +13494,7 @@
     <row r="320">
       <c r="A320" s="6" t="inlineStr">
         <is>
-          <t>OUR-44</t>
+          <t>OUR-42</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -13502,24 +13502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C320" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C320" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>The pairing screen offers a way INTO the list</t>
+          <t>A change on one phone appears on the other WITHOUT touching it</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>Finish pairing, then look at the pairing screen.</t>
+          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
+          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
         </is>
       </c>
       <c r="G320" s="7" t="inlineStr">
@@ -13534,7 +13534,7 @@
     <row r="321">
       <c r="A321" s="6" t="inlineStr">
         <is>
-          <t>OUR-45</t>
+          <t>OUR-43</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -13542,24 +13542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C321" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C321" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash appears and then takes itself away</t>
+          <t>Opening your own list does not bounce you back</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
+          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
+          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
         </is>
       </c>
       <c r="G321" s="7" t="inlineStr">
@@ -13574,7 +13574,7 @@
     <row r="322">
       <c r="A322" s="6" t="inlineStr">
         <is>
-          <t>OUR-47</t>
+          <t>OUR-44</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -13589,17 +13589,17 @@
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>The Ours door on Today is findable</t>
+          <t>The pairing screen offers a way INTO the list</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>With a live list, look at Today.</t>
+          <t>Finish pairing, then look at the pairing screen.</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>A tinted, accented card carrying the list's name, not a hairline footnote. Absent entirely when there is no live list.</t>
+          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
         </is>
       </c>
       <c r="G322" s="7" t="inlineStr">
@@ -13614,7 +13614,7 @@
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
         <is>
-          <t>OUR-48</t>
+          <t>OUR-45</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -13622,24 +13622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C323" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C323" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
-          <t>Their tick marks your copy DONE and leaves it on your day</t>
+          <t>The quiet wash appears and then takes itself away</t>
         </is>
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
+          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
         </is>
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
+          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
         </is>
       </c>
       <c r="G323" s="7" t="inlineStr">
@@ -13654,7 +13654,7 @@
     <row r="324">
       <c r="A324" s="6" t="inlineStr">
         <is>
-          <t>OUR-49</t>
+          <t>OUR-47</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -13662,24 +13662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C324" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C324" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>A settled copy carries a completion DATE, not just a done flag</t>
+          <t>The Ours door on Today is findable</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
+          <t>With a live list, look at Today.</t>
         </is>
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
+          <t>A tinted, accented card carrying the list's name, not a hairline footnote. Absent entirely when there is no live list.</t>
         </is>
       </c>
       <c r="G324" s="7" t="inlineStr">
@@ -13694,7 +13694,7 @@
     <row r="325">
       <c r="A325" s="6" t="inlineStr">
         <is>
-          <t>OUR-50</t>
+          <t>OUR-48</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -13702,24 +13702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C325" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C325" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>A finished copy can be brought over again</t>
+          <t>Their tick marks your copy DONE and leaves it on your day</t>
         </is>
       </c>
       <c r="E325" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, hold that row in Ours.</t>
+          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
         </is>
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
+          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
         </is>
       </c>
       <c r="G325" s="7" t="inlineStr">
@@ -13734,7 +13734,7 @@
     <row r="326">
       <c r="A326" s="6" t="inlineStr">
         <is>
-          <t>OUR-51</t>
+          <t>OUR-49</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -13749,17 +13749,17 @@
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
-          <t>Your own edit never highlights; their later edit always does</t>
+          <t>A settled copy carries a completion DATE, not just a done flag</t>
         </is>
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
+          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
         </is>
       </c>
       <c r="F326" s="9" t="inlineStr">
         <is>
-          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
+          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
         </is>
       </c>
       <c r="G326" s="7" t="inlineStr">
@@ -13774,7 +13774,7 @@
     <row r="327">
       <c r="A327" s="6" t="inlineStr">
         <is>
-          <t>OUR-52</t>
+          <t>OUR-50</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -13789,17 +13789,17 @@
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>The highlight arrives at once and fades away</t>
+          <t>A finished copy can be brought over again</t>
         </is>
       </c>
       <c r="E327" s="9" t="inlineStr">
         <is>
-          <t>Have B change a row while A is on the list.</t>
+          <t>After OUR-48, hold that row in Ours.</t>
         </is>
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
+          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
         </is>
       </c>
       <c r="G327" s="7" t="inlineStr">
@@ -13814,7 +13814,7 @@
     <row r="328">
       <c r="A328" s="6" t="inlineStr">
         <is>
-          <t>OUR-53</t>
+          <t>OUR-51</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -13822,24 +13822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C328" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C328" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>Two devices share ONE clock</t>
+          <t>Your own edit never highlights; their later edit always does</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
+          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
         </is>
       </c>
       <c r="F328" s="9" t="inlineStr">
         <is>
-          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
+          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
         </is>
       </c>
       <c r="G328" s="7" t="inlineStr">
@@ -13854,7 +13854,7 @@
     <row r="329">
       <c r="A329" s="6" t="inlineStr">
         <is>
-          <t>OUR-54</t>
+          <t>OUR-52</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -13862,24 +13862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C329" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C329" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>The debug panel is opt-in and carries no task text</t>
+          <t>The highlight arrives at once and fades away</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
+          <t>Have B change a row while A is on the list.</t>
         </is>
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
+          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
         </is>
       </c>
       <c r="G329" s="7" t="inlineStr">
@@ -13894,7 +13894,7 @@
     <row r="330">
       <c r="A330" s="6" t="inlineStr">
         <is>
-          <t>OUR-55</t>
+          <t>OUR-53</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -13902,24 +13902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C330" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C330" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>Capture on Ours IS Today's capture</t>
+          <t>Two devices share ONE clock</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>Open a shared list and tap the launcher at the foot of the screen.</t>
+          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
         </is>
       </c>
       <c r="F330" s="9" t="inlineStr">
         <is>
-          <t>The same panel Today opens: the same input, the same Speak button (web), the same door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
+          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
         </is>
       </c>
       <c r="G330" s="7" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="331">
       <c r="A331" s="6" t="inlineStr">
         <is>
-          <t>OUR-56</t>
+          <t>OUR-54</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -13942,24 +13942,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C331" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C331" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D331" s="9" t="inlineStr">
         <is>
-          <t>Repeating can be set AT capture, without knowing a gesture</t>
+          <t>The debug panel is opt-in and carries no task text</t>
         </is>
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
+          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
         </is>
       </c>
       <c r="F331" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
+          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
         </is>
       </c>
       <c r="G331" s="7" t="inlineStr">
@@ -13974,7 +13974,7 @@
     <row r="332">
       <c r="A332" s="6" t="inlineStr">
         <is>
-          <t>OUR-57</t>
+          <t>OUR-55</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -13982,24 +13982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C332" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C332" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D332" s="9" t="inlineStr">
         <is>
-          <t>A dump becomes several shared rows, in the order typed</t>
+          <t>Capture on Ours IS Today's capture</t>
         </is>
       </c>
       <c r="E332" s="9" t="inlineStr">
         <is>
-          <t>Type three lines into the Ours capture and Add.</t>
+          <t>Open a shared list and tap the launcher at the foot of the screen.</t>
         </is>
       </c>
       <c r="F332" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
+          <t>The same panel Today opens: the same input, the same Speak button (web), the same door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
         </is>
       </c>
       <c r="G332" s="7" t="inlineStr">
@@ -14014,7 +14014,7 @@
     <row r="333">
       <c r="A333" s="6" t="inlineStr">
         <is>
-          <t>OUR-58</t>
+          <t>OUR-56</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -14029,17 +14029,17 @@
       </c>
       <c r="D333" s="9" t="inlineStr">
         <is>
-          <t>The shared door offers When and Repeating, never Steps</t>
+          <t>Repeating can be set AT capture, without knowing a gesture</t>
         </is>
       </c>
       <c r="E333" s="9" t="inlineStr">
         <is>
-          <t>Open the door on Ours and compare it with the door on Today.</t>
+          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
         </is>
       </c>
       <c r="F333" s="9" t="inlineStr">
         <is>
-          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
+          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
         </is>
       </c>
       <c r="G333" s="7" t="inlineStr">
@@ -14054,7 +14054,7 @@
     <row r="334">
       <c r="A334" s="6" t="inlineStr">
         <is>
-          <t>OUR-59</t>
+          <t>OUR-57</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -14069,17 +14069,17 @@
       </c>
       <c r="D334" s="9" t="inlineStr">
         <is>
-          <t>Typed text survives closing the panel</t>
+          <t>A dump becomes several shared rows, in the order typed</t>
         </is>
       </c>
       <c r="E334" s="9" t="inlineStr">
         <is>
-          <t>Type half a sentence into the Ours capture, tap Close, tick something, then reopen the panel.</t>
+          <t>Type three lines into the Ours capture and Add.</t>
         </is>
       </c>
       <c r="F334" s="9" t="inlineStr">
         <is>
-          <t>The half sentence is still there. The panel is hidden, never unmounted. The door resets to no-repeat, the words never reset.</t>
+          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
         </is>
       </c>
       <c r="G334" s="7" t="inlineStr">
@@ -14094,7 +14094,7 @@
     <row r="335">
       <c r="A335" s="6" t="inlineStr">
         <is>
-          <t>OUR-60</t>
+          <t>OUR-58</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -14102,29 +14102,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C335" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C335" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D335" s="9" t="inlineStr">
         <is>
-          <t>The Ours capture rides above the keyboard</t>
+          <t>The shared door offers When and Repeating, never Steps</t>
         </is>
       </c>
       <c r="E335" s="9" t="inlineStr">
         <is>
-          <t>On a real Android device, open the Ours capture and start typing.</t>
+          <t>Open the door on Ours and compare it with the door on Today.</t>
         </is>
       </c>
       <c r="F335" s="9" t="inlineStr">
         <is>
-          <t>The panel and its Add button stay visible above the keyboard. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
+          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
         </is>
       </c>
       <c r="G335" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H335" s="7" t="inlineStr"/>
@@ -14134,7 +14134,7 @@
     <row r="336">
       <c r="A336" s="6" t="inlineStr">
         <is>
-          <t>OUR-61</t>
+          <t>OUR-59</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -14142,24 +14142,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C336" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C336" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D336" s="9" t="inlineStr">
         <is>
-          <t>No AI on the shared capture</t>
+          <t>Typed text survives closing the panel</t>
         </is>
       </c>
       <c r="E336" s="9" t="inlineStr">
         <is>
-          <t>Open the Ours capture with AI enabled in Settings.</t>
+          <t>Type half a sentence into the Ours capture, tap Close, tick something, then reopen the panel.</t>
         </is>
       </c>
       <c r="F336" s="9" t="inlineStr">
         <is>
-          <t>No 'Break it down' and no 'Sort for me': steps a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
+          <t>The half sentence is still there. The panel is hidden, never unmounted. The door resets to no-repeat, the words never reset.</t>
         </is>
       </c>
       <c r="G336" s="7" t="inlineStr">
@@ -14174,7 +14174,7 @@
     <row r="337">
       <c r="A337" s="6" t="inlineStr">
         <is>
-          <t>OUR-62</t>
+          <t>OUR-60</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -14182,24 +14182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C337" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C337" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D337" s="9" t="inlineStr">
         <is>
-          <t>Scan (premium) reaches the shared capture</t>
+          <t>The Ours capture rides above the keyboard</t>
         </is>
       </c>
       <c r="E337" s="9" t="inlineStr">
         <is>
-          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
+          <t>On a real Android device, open the Ours capture and start typing.</t>
         </is>
       </c>
       <c r="F337" s="9" t="inlineStr">
         <is>
-          <t>The words land IN the capture box, not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
+          <t>The panel and its Add button stay visible above the keyboard. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
         </is>
       </c>
       <c r="G337" s="7" t="inlineStr">
@@ -14214,7 +14214,7 @@
     <row r="338">
       <c r="A338" s="6" t="inlineStr">
         <is>
-          <t>OUR-63</t>
+          <t>OUR-61</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -14222,24 +14222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C338" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C338" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D338" s="9" t="inlineStr">
         <is>
-          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
+          <t>No AI on the shared capture</t>
         </is>
       </c>
       <c r="E338" s="9" t="inlineStr">
         <is>
-          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
+          <t>Open the Ours capture with AI enabled in Settings.</t>
         </is>
       </c>
       <c r="F338" s="9" t="inlineStr">
         <is>
-          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
+          <t>No 'Break it down' and no 'Sort for me': steps a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
         </is>
       </c>
       <c r="G338" s="7" t="inlineStr">
@@ -14254,7 +14254,7 @@
     <row r="339">
       <c r="A339" s="6" t="inlineStr">
         <is>
-          <t>OUR-64</t>
+          <t>OUR-62</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -14262,29 +14262,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C339" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C339" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D339" s="9" t="inlineStr">
         <is>
-          <t>The photo never reaches the shared list</t>
+          <t>Scan (premium) reaches the shared capture</t>
         </is>
       </c>
       <c r="E339" s="9" t="inlineStr">
         <is>
-          <t>Scan something into Ours and Add it. Check the other device.</t>
+          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
         </is>
       </c>
       <c r="F339" s="9" t="inlineStr">
         <is>
-          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
+          <t>The words land IN the capture box, not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
         </is>
       </c>
       <c r="G339" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H339" s="7" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
     <row r="340">
       <c r="A340" s="6" t="inlineStr">
         <is>
-          <t>OUR-65</t>
+          <t>OUR-63</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -14302,24 +14302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C340" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C340" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D340" s="9" t="inlineStr">
         <is>
-          <t>Scan is absent when AI is off</t>
+          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
         </is>
       </c>
       <c r="E340" s="9" t="inlineStr">
         <is>
-          <t>Turn AI off in Settings, then open the Ours capture.</t>
+          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
         </is>
       </c>
       <c r="F340" s="9" t="inlineStr">
         <is>
-          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
+          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
         </is>
       </c>
       <c r="G340" s="7" t="inlineStr">
@@ -14334,7 +14334,7 @@
     <row r="341">
       <c r="A341" s="6" t="inlineStr">
         <is>
-          <t>OUR-66</t>
+          <t>OUR-64</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -14342,24 +14342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C341" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C341" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D341" s="9" t="inlineStr">
         <is>
-          <t>A repeating shared row appears on BOTH Todays on its day</t>
+          <t>The photo never reaches the shared list</t>
         </is>
       </c>
       <c r="E341" s="9" t="inlineStr">
         <is>
-          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
+          <t>Scan something into Ours and Add it. Check the other device.</t>
         </is>
       </c>
       <c r="F341" s="9" t="inlineStr">
         <is>
-          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
+          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
         </is>
       </c>
       <c r="G341" s="7" t="inlineStr">
@@ -14374,7 +14374,7 @@
     <row r="342">
       <c r="A342" s="6" t="inlineStr">
         <is>
-          <t>OUR-67</t>
+          <t>OUR-65</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -14382,24 +14382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C342" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C342" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>An UNDATED shared row never reaches Today</t>
+          <t>Scan is absent when AI is off</t>
         </is>
       </c>
       <c r="E342" s="9" t="inlineStr">
         <is>
-          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
+          <t>Turn AI off in Settings, then open the Ours capture.</t>
         </is>
       </c>
       <c r="F342" s="9" t="inlineStr">
         <is>
-          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
+          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
         </is>
       </c>
       <c r="G342" s="7" t="inlineStr">
@@ -14414,7 +14414,7 @@
     <row r="343">
       <c r="A343" s="6" t="inlineStr">
         <is>
-          <t>OUR-68</t>
+          <t>OUR-66</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -14429,17 +14429,17 @@
       </c>
       <c r="D343" s="9" t="inlineStr">
         <is>
-          <t>Shared rows never make the day look heavier</t>
+          <t>A repeating shared row appears on BOTH Todays on its day</t>
         </is>
       </c>
       <c r="E343" s="9" t="inlineStr">
         <is>
-          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
+          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
         </is>
       </c>
       <c r="F343" s="9" t="inlineStr">
         <is>
-          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
+          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
         </is>
       </c>
       <c r="G343" s="7" t="inlineStr">
@@ -14454,7 +14454,7 @@
     <row r="344">
       <c r="A344" s="6" t="inlineStr">
         <is>
-          <t>OUR-69</t>
+          <t>OUR-67</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -14469,17 +14469,17 @@
       </c>
       <c r="D344" s="9" t="inlineStr">
         <is>
-          <t>Ticking a shared row from Today closes it for both</t>
+          <t>An UNDATED shared row never reaches Today</t>
         </is>
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
+          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
         </is>
       </c>
       <c r="F344" s="9" t="inlineStr">
         <is>
-          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
+          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
         </is>
       </c>
       <c r="G344" s="7" t="inlineStr">
@@ -14494,7 +14494,7 @@
     <row r="345">
       <c r="A345" s="6" t="inlineStr">
         <is>
-          <t>OUR-70</t>
+          <t>OUR-68</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -14502,24 +14502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C345" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C345" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D345" s="9" t="inlineStr">
         <is>
-          <t>A dated shared row shows from its day onward, never before</t>
+          <t>Shared rows never make the day look heavier</t>
         </is>
       </c>
       <c r="E345" s="9" t="inlineStr">
         <is>
-          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
+          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
         </is>
       </c>
       <c r="F345" s="9" t="inlineStr">
         <is>
-          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
+          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
         </is>
       </c>
       <c r="G345" s="7" t="inlineStr">
@@ -14534,7 +14534,7 @@
     <row r="346">
       <c r="A346" s="6" t="inlineStr">
         <is>
-          <t>OUR-71</t>
+          <t>OUR-69</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -14549,17 +14549,17 @@
       </c>
       <c r="D346" s="9" t="inlineStr">
         <is>
-          <t>The shared capture rests on Anytime</t>
+          <t>Ticking a shared row from Today closes it for both</t>
         </is>
       </c>
       <c r="E346" s="9" t="inlineStr">
         <is>
-          <t>Open the Ours capture and open the door.</t>
+          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
         </is>
       </c>
       <c r="F346" s="9" t="inlineStr">
         <is>
-          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected. The Add button says just 'Add'. Choosing Today makes it read 'Add . Today', because that is the notable case: it will appear on both your days.</t>
+          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
         </is>
       </c>
       <c r="G346" s="7" t="inlineStr">
@@ -14574,7 +14574,7 @@
     <row r="347">
       <c r="A347" s="6" t="inlineStr">
         <is>
-          <t>OUR-112</t>
+          <t>OUR-70</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -14582,24 +14582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C347" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C347" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D347" s="9" t="inlineStr">
         <is>
-          <t>A shared row's WHEN can be changed, and cleared</t>
+          <t>A dated shared row shows from its day onward, never before</t>
         </is>
       </c>
       <c r="E347" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
+          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
         </is>
       </c>
       <c r="F347" s="9" t="inlineStr">
         <is>
-          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
+          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
         </is>
       </c>
       <c r="G347" s="7" t="inlineStr">
@@ -14614,7 +14614,7 @@
     <row r="348">
       <c r="A348" s="6" t="inlineStr">
         <is>
-          <t>OUR-113</t>
+          <t>OUR-71</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -14629,17 +14629,17 @@
       </c>
       <c r="D348" s="9" t="inlineStr">
         <is>
-          <t>Ending a rhythm does NOT mark the row done for both people</t>
+          <t>The shared capture rests on Anytime</t>
         </is>
       </c>
       <c r="E348" s="9" t="inlineStr">
         <is>
-          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
+          <t>Open the Ours capture and open the door.</t>
         </is>
       </c>
       <c r="F348" s="9" t="inlineStr">
         <is>
-          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
+          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected. The Add button says just 'Add'. Choosing Today makes it read 'Add . Today', because that is the notable case: it will appear on both your days.</t>
         </is>
       </c>
       <c r="G348" s="7" t="inlineStr">
@@ -14654,7 +14654,7 @@
     <row r="349">
       <c r="A349" s="6" t="inlineStr">
         <is>
-          <t>OUR-114</t>
+          <t>OUR-112</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -14662,24 +14662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C349" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C349" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D349" s="9" t="inlineStr">
         <is>
-          <t>The day zone changes its question when a rhythm is alive</t>
+          <t>A shared row's WHEN can be changed, and cleared</t>
         </is>
       </c>
       <c r="E349" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
+          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
         </is>
       </c>
       <c r="F349" s="9" t="inlineStr">
         <is>
-          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
+          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
         </is>
       </c>
       <c r="G349" s="7" t="inlineStr">
@@ -14694,7 +14694,7 @@
     <row r="350">
       <c r="A350" s="6" t="inlineStr">
         <is>
-          <t>OUR-115</t>
+          <t>OUR-113</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -14702,24 +14702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C350" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C350" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D350" s="9" t="inlineStr">
         <is>
-          <t>Setting a shared row to Today actually reaches both Todays</t>
+          <t>Ending a rhythm does NOT mark the row done for both people</t>
         </is>
       </c>
       <c r="E350" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
+          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
         </is>
       </c>
       <c r="F350" s="9" t="inlineStr">
         <is>
-          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
+          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
         </is>
       </c>
       <c r="G350" s="7" t="inlineStr">
@@ -14734,7 +14734,7 @@
     <row r="351">
       <c r="A351" s="6" t="inlineStr">
         <is>
-          <t>OUR-116</t>
+          <t>OUR-114</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -14742,24 +14742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C351" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C351" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D351" s="9" t="inlineStr">
         <is>
-          <t>An idle Set does not wash the row on the other device</t>
+          <t>The day zone changes its question when a rhythm is alive</t>
         </is>
       </c>
       <c r="E351" s="9" t="inlineStr">
         <is>
-          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
+          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
         </is>
       </c>
       <c r="F351" s="9" t="inlineStr">
         <is>
-          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
+          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
         </is>
       </c>
       <c r="G351" s="7" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="352">
       <c r="A352" s="6" t="inlineStr">
         <is>
-          <t>OUR-118</t>
+          <t>OUR-115</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -14782,24 +14782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C352" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C352" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D352" s="9" t="inlineStr">
         <is>
-          <t>A repeat you have already done today keeps its held card</t>
+          <t>Setting a shared row to Today actually reaches both Todays</t>
         </is>
       </c>
       <c r="E352" s="9" t="inlineStr">
         <is>
-          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
+          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
         </is>
       </c>
       <c r="F352" s="9" t="inlineStr">
         <is>
-          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
+          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
         </is>
       </c>
       <c r="G352" s="7" t="inlineStr">
@@ -14814,7 +14814,7 @@
     <row r="353">
       <c r="A353" s="6" t="inlineStr">
         <is>
-          <t>OUR-117</t>
+          <t>OUR-116</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -14822,24 +14822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C353" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C353" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D353" s="9" t="inlineStr">
         <is>
-          <t>The Repeating drawer is untouched by the When editor</t>
+          <t>An idle Set does not wash the row on the other device</t>
         </is>
       </c>
       <c r="E353" s="9" t="inlineStr">
         <is>
-          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
+          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
         </is>
       </c>
       <c r="F353" s="9" t="inlineStr">
         <is>
-          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the drawer.</t>
+          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
         </is>
       </c>
       <c r="G353" s="7" t="inlineStr">
@@ -14854,7 +14854,7 @@
     <row r="354">
       <c r="A354" s="6" t="inlineStr">
         <is>
-          <t>OUR-119</t>
+          <t>OUR-118</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -14862,24 +14862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C354" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C354" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D354" s="9" t="inlineStr">
         <is>
-          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
+          <t>A repeat you have already done today keeps its held card</t>
         </is>
       </c>
       <c r="E354" s="9" t="inlineStr">
         <is>
-          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
+          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
         </is>
       </c>
       <c r="F354" s="9" t="inlineStr">
         <is>
-          <t>Monthly is the fourth rhythm chip here too, from the same sheet the personal drawer uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
+          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
         </is>
       </c>
       <c r="G354" s="7" t="inlineStr">
@@ -14894,7 +14894,7 @@
     <row r="355">
       <c r="A355" s="6" t="inlineStr">
         <is>
-          <t>OUR-111</t>
+          <t>OUR-117</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -14902,24 +14902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C355" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C355" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D355" s="9" t="inlineStr">
         <is>
-          <t>A finished dated shared row leaves both Todays the next day</t>
+          <t>The Repeating drawer is untouched by the When editor</t>
         </is>
       </c>
       <c r="E355" s="9" t="inlineStr">
         <is>
-          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
+          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
         </is>
       </c>
       <c r="F355" s="9" t="inlineStr">
         <is>
-          <t>Today: still there on BOTH, struck through, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
+          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the drawer.</t>
         </is>
       </c>
       <c r="G355" s="7" t="inlineStr">
@@ -14934,7 +14934,7 @@
     <row r="356">
       <c r="A356" s="6" t="inlineStr">
         <is>
-          <t>OUR-72</t>
+          <t>OUR-119</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -14949,17 +14949,17 @@
       </c>
       <c r="D356" s="9" t="inlineStr">
         <is>
-          <t>A repeat supersedes the day rather than joining it</t>
+          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
         </is>
       </c>
       <c r="E356" s="9" t="inlineStr">
         <is>
-          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
+          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
         </is>
       </c>
       <c r="F356" s="9" t="inlineStr">
         <is>
-          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
+          <t>Monthly is the fourth rhythm chip here too, from the same sheet the personal drawer uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
         </is>
       </c>
       <c r="G356" s="7" t="inlineStr">
@@ -14974,7 +14974,7 @@
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
         <is>
-          <t>OUR-73</t>
+          <t>OUR-111</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -14982,24 +14982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C357" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C357" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D357" s="9" t="inlineStr">
         <is>
-          <t>An unreadable cadence is never placed on a day</t>
+          <t>A finished dated shared row leaves both Todays the next day</t>
         </is>
       </c>
       <c r="E357" s="9" t="inlineStr">
         <is>
-          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
+          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
         </is>
       </c>
       <c r="F357" s="9" t="inlineStr">
         <is>
-          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
+          <t>Today: still there on BOTH, struck through, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
         </is>
       </c>
       <c r="G357" s="7" t="inlineStr">
@@ -15014,7 +15014,7 @@
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
         <is>
-          <t>OUR-74</t>
+          <t>OUR-72</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -15022,24 +15022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C358" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C358" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D358" s="9" t="inlineStr">
         <is>
-          <t>The door says what changed since you looked, and clears when you look</t>
+          <t>A repeat supersedes the day rather than joining it</t>
         </is>
       </c>
       <c r="E358" s="9" t="inlineStr">
         <is>
-          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap through to Ours and come back.</t>
+          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
         </is>
       </c>
       <c r="F358" s="9" t="inlineStr">
         <is>
-          <t>The Ours door reads '1 since you looked'. After visiting, it is gone. The number is bounded by your own attention, not by the list's length, so it can never sit there climbing at you.</t>
+          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
         </is>
       </c>
       <c r="G358" s="7" t="inlineStr">
@@ -15054,7 +15054,7 @@
     <row r="359">
       <c r="A359" s="6" t="inlineStr">
         <is>
-          <t>OUR-75</t>
+          <t>OUR-73</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -15062,24 +15062,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C359" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C359" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D359" s="9" t="inlineStr">
         <is>
-          <t>Your OWN changes never appear in that count</t>
+          <t>An unreadable cadence is never placed on a day</t>
         </is>
       </c>
       <c r="E359" s="9" t="inlineStr">
         <is>
-          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
+          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
         </is>
       </c>
       <c r="F359" s="9" t="inlineStr">
         <is>
-          <t>No count on the door. It uses the room's own wash arithmetic, so the door and the room always agree about whose change it was.</t>
+          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
         </is>
       </c>
       <c r="G359" s="7" t="inlineStr">
@@ -15094,7 +15094,7 @@
     <row r="360">
       <c r="A360" s="6" t="inlineStr">
         <is>
-          <t>OUR-76</t>
+          <t>OUR-74</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -15102,24 +15102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C360" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C360" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D360" s="9" t="inlineStr">
         <is>
-          <t>A first-ever visit counts nothing</t>
+          <t>The door says what changed since you looked, and clears when you look</t>
         </is>
       </c>
       <c r="E360" s="9" t="inlineStr">
         <is>
-          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
+          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap through to Ours and come back.</t>
         </is>
       </c>
       <c r="F360" s="9" t="inlineStr">
         <is>
-          <t>No count. There is no 'last looked' to measure against, and inventing one would open the app with a number already on it.</t>
+          <t>The Ours door reads '1 since you looked'. After visiting, it is gone. The number is bounded by your own attention, not by the list's length, so it can never sit there climbing at you.</t>
         </is>
       </c>
       <c r="G360" s="7" t="inlineStr">
@@ -15134,7 +15134,7 @@
     <row r="361">
       <c r="A361" s="6" t="inlineStr">
         <is>
-          <t>OUR-77</t>
+          <t>OUR-75</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -15142,24 +15142,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C361" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C361" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D361" s="9" t="inlineStr">
         <is>
-          <t>The capture's AI note names only what that surface HAS</t>
+          <t>Your OWN changes never appear in that count</t>
         </is>
       </c>
       <c r="E361" s="9" t="inlineStr">
         <is>
-          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
+          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
         </is>
       </c>
       <c r="F361" s="9" t="inlineStr">
         <is>
-          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
+          <t>No count on the door. It uses the room's own wash arithmetic, so the door and the room always agree about whose change it was.</t>
         </is>
       </c>
       <c r="G361" s="7" t="inlineStr">
@@ -15174,7 +15174,7 @@
     <row r="362">
       <c r="A362" s="6" t="inlineStr">
         <is>
-          <t>OUR-78</t>
+          <t>OUR-76</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -15182,24 +15182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C362" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C362" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D362" s="9" t="inlineStr">
         <is>
-          <t>Scan discloses on every path that can reach a camera</t>
+          <t>A first-ever visit counts nothing</t>
         </is>
       </c>
       <c r="E362" s="9" t="inlineStr">
         <is>
-          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
+          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
         </is>
       </c>
       <c r="F362" s="9" t="inlineStr">
         <is>
-          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
+          <t>No count. There is no 'last looked' to measure against, and inventing one would open the app with a number already on it.</t>
         </is>
       </c>
       <c r="G362" s="7" t="inlineStr">
@@ -15214,7 +15214,7 @@
     <row r="363">
       <c r="A363" s="6" t="inlineStr">
         <is>
-          <t>OUR-79</t>
+          <t>OUR-77</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -15229,17 +15229,17 @@
       </c>
       <c r="D363" s="9" t="inlineStr">
         <is>
-          <t>Press and hold a From Ours row on Today</t>
+          <t>The capture's AI note names only what that surface HAS</t>
         </is>
       </c>
       <c r="E363" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Ours strip.</t>
+          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
         </is>
       </c>
       <c r="F363" s="9" t="inlineStr">
         <is>
-          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
+          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
         </is>
       </c>
       <c r="G363" s="7" t="inlineStr">
@@ -15254,7 +15254,7 @@
     <row r="364">
       <c r="A364" s="6" t="inlineStr">
         <is>
-          <t>OUR-80</t>
+          <t>OUR-78</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -15269,17 +15269,17 @@
       </c>
       <c r="D364" s="9" t="inlineStr">
         <is>
-          <t>Pin and Move-to never rearrange the other person's day</t>
+          <t>Scan discloses on every path that can reach a camera</t>
         </is>
       </c>
       <c r="E364" s="9" t="inlineStr">
         <is>
-          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
+          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
         </is>
       </c>
       <c r="F364" s="9" t="inlineStr">
         <is>
-          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
+          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
         </is>
       </c>
       <c r="G364" s="7" t="inlineStr">
@@ -15294,7 +15294,7 @@
     <row r="365">
       <c r="A365" s="6" t="inlineStr">
         <is>
-          <t>OUR-81</t>
+          <t>OUR-79</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -15302,24 +15302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C365" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C365" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D365" s="9" t="inlineStr">
         <is>
-          <t>A taken-on row is never on screen twice</t>
+          <t>Press and hold a From Ours row on Today</t>
         </is>
       </c>
       <c r="E365" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
+          <t>Hold a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F365" s="9" t="inlineStr">
         <is>
-          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
+          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
         </is>
       </c>
       <c r="G365" s="7" t="inlineStr">
@@ -15334,7 +15334,7 @@
     <row r="366">
       <c r="A366" s="6" t="inlineStr">
         <is>
-          <t>OUR-82</t>
+          <t>OUR-80</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -15342,24 +15342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C366" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C366" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D366" s="9" t="inlineStr">
         <is>
-          <t>Move-to is not offered on a repeating shared row</t>
+          <t>Pin and Move-to never rearrange the other person's day</t>
         </is>
       </c>
       <c r="E366" s="9" t="inlineStr">
         <is>
-          <t>Hold a repeating row in the From Ours strip.</t>
+          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
         </is>
       </c>
       <c r="F366" s="9" t="inlineStr">
         <is>
-          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
+          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
         </is>
       </c>
       <c r="G366" s="7" t="inlineStr">
@@ -15374,7 +15374,7 @@
     <row r="367">
       <c r="A367" s="6" t="inlineStr">
         <is>
-          <t>OUR-83</t>
+          <t>OUR-81</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -15382,24 +15382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C367" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C367" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D367" s="9" t="inlineStr">
         <is>
-          <t>One shared row, one route onto your day</t>
+          <t>A taken-on row is never on screen twice</t>
         </is>
       </c>
       <c r="E367" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
+          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
         </is>
       </c>
       <c r="F367" s="9" t="inlineStr">
         <is>
-          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
+          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
         </is>
       </c>
       <c r="G367" s="7" t="inlineStr">
@@ -15414,7 +15414,7 @@
     <row r="368">
       <c r="A368" s="6" t="inlineStr">
         <is>
-          <t>OUR-84</t>
+          <t>OUR-82</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -15422,24 +15422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C368" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C368" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D368" s="9" t="inlineStr">
         <is>
-          <t>Take a From Ours row on, and it becomes an ordinary task</t>
+          <t>Move-to is not offered on a repeating shared row</t>
         </is>
       </c>
       <c r="E368" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
+          <t>Hold a repeating row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F368" s="9" t="inlineStr">
         <is>
-          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
+          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
         </is>
       </c>
       <c r="G368" s="7" t="inlineStr">
@@ -15454,7 +15454,7 @@
     <row r="369">
       <c r="A369" s="6" t="inlineStr">
         <is>
-          <t>OUR-85</t>
+          <t>OUR-83</t>
         </is>
       </c>
       <c r="B369" s="7" t="inlineStr">
@@ -15462,24 +15462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C369" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C369" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D369" s="9" t="inlineStr">
         <is>
-          <t>Break it down works once taken on, and never touches the shared list</t>
+          <t>One shared row, one route onto your day</t>
         </is>
       </c>
       <c r="E369" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on, then Break it down.</t>
+          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
         </is>
       </c>
       <c r="F369" s="9" t="inlineStr">
         <is>
-          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
+          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
         </is>
       </c>
       <c r="G369" s="7" t="inlineStr">
@@ -15494,7 +15494,7 @@
     <row r="370">
       <c r="A370" s="6" t="inlineStr">
         <is>
-          <t>OUR-86</t>
+          <t>OUR-84</t>
         </is>
       </c>
       <c r="B370" s="7" t="inlineStr">
@@ -15509,17 +15509,17 @@
       </c>
       <c r="D370" s="9" t="inlineStr">
         <is>
-          <t>Select several rows in the room and tick them together</t>
+          <t>Take a From Ours row on, and it becomes an ordinary task</t>
         </is>
       </c>
       <c r="E370" s="9" t="inlineStr">
         <is>
-          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
+          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
         </is>
       </c>
       <c r="F370" s="9" t="inlineStr">
         <is>
-          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
+          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
         </is>
       </c>
       <c r="G370" s="7" t="inlineStr">
@@ -15534,7 +15534,7 @@
     <row r="371">
       <c r="A371" s="6" t="inlineStr">
         <is>
-          <t>OUR-87</t>
+          <t>OUR-85</t>
         </is>
       </c>
       <c r="B371" s="7" t="inlineStr">
@@ -15542,24 +15542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C371" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C371" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D371" s="9" t="inlineStr">
         <is>
-          <t>Bulk tick never UN-ticks</t>
+          <t>Break it down works once taken on, and never touches the shared list</t>
         </is>
       </c>
       <c r="E371" s="9" t="inlineStr">
         <is>
-          <t>Select a mix of done and not-done rows and tap Done.</t>
+          <t>Take a shared row on, then Break it down.</t>
         </is>
       </c>
       <c r="F371" s="9" t="inlineStr">
         <is>
-          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
+          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
         </is>
       </c>
       <c r="G371" s="7" t="inlineStr">
@@ -15574,7 +15574,7 @@
     <row r="372">
       <c r="A372" s="6" t="inlineStr">
         <is>
-          <t>OUR-88</t>
+          <t>OUR-86</t>
         </is>
       </c>
       <c r="B372" s="7" t="inlineStr">
@@ -15589,17 +15589,17 @@
       </c>
       <c r="D372" s="9" t="inlineStr">
         <is>
-          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
+          <t>Select several rows in the room and tick them together</t>
         </is>
       </c>
       <c r="E372" s="9" t="inlineStr">
         <is>
-          <t>Select a repeating row along with others. Read the shelf.</t>
+          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
         </is>
       </c>
       <c r="F372" s="9" t="inlineStr">
         <is>
-          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
+          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
         </is>
       </c>
       <c r="G372" s="7" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="373">
       <c r="A373" s="6" t="inlineStr">
         <is>
-          <t>OUR-89</t>
+          <t>OUR-87</t>
         </is>
       </c>
       <c r="B373" s="7" t="inlineStr">
@@ -15622,24 +15622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C373" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C373" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D373" s="9" t="inlineStr">
         <is>
-          <t>The select shelf takes the capture bar's seat</t>
+          <t>Bulk tick never UN-ticks</t>
         </is>
       </c>
       <c r="E373" s="9" t="inlineStr">
         <is>
-          <t>Enter select mode in the room.</t>
+          <t>Select a mix of done and not-done rows and tap Done.</t>
         </is>
       </c>
       <c r="F373" s="9" t="inlineStr">
         <is>
-          <t>The capture bar is gone while selecting, and back when you cancel. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
+          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
         </is>
       </c>
       <c r="G373" s="7" t="inlineStr">
@@ -15654,7 +15654,7 @@
     <row r="374">
       <c r="A374" s="6" t="inlineStr">
         <is>
-          <t>OUR-90</t>
+          <t>OUR-88</t>
         </is>
       </c>
       <c r="B374" s="7" t="inlineStr">
@@ -15662,24 +15662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C374" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C374" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D374" s="9" t="inlineStr">
         <is>
-          <t>No select mode on a closed list</t>
+          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
         </is>
       </c>
       <c r="E374" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list and hold a row.</t>
+          <t>Select a repeating row along with others. Read the shelf.</t>
         </is>
       </c>
       <c r="F374" s="9" t="inlineStr">
         <is>
-          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
+          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
         </is>
       </c>
       <c r="G374" s="7" t="inlineStr">
@@ -15694,7 +15694,7 @@
     <row r="375">
       <c r="A375" s="6" t="inlineStr">
         <is>
-          <t>OUR-91</t>
+          <t>OUR-89</t>
         </is>
       </c>
       <c r="B375" s="7" t="inlineStr">
@@ -15702,24 +15702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C375" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C375" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D375" s="9" t="inlineStr">
         <is>
-          <t>A copy says when its shared row was taken off the list</t>
+          <t>The select shelf takes the capture bar's seat</t>
         </is>
       </c>
       <c r="E375" s="9" t="inlineStr">
         <is>
-          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
+          <t>Enter select mode in the room.</t>
         </is>
       </c>
       <c r="F375" s="9" t="inlineStr">
         <is>
-          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
+          <t>The capture bar is gone while selecting, and back when you cancel. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
         </is>
       </c>
       <c r="G375" s="7" t="inlineStr">
@@ -15734,7 +15734,7 @@
     <row r="376">
       <c r="A376" s="6" t="inlineStr">
         <is>
-          <t>OUR-92</t>
+          <t>OUR-90</t>
         </is>
       </c>
       <c r="B376" s="7" t="inlineStr">
@@ -15742,24 +15742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C376" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C376" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D376" s="9" t="inlineStr">
         <is>
-          <t>That line never says who, and never says why</t>
+          <t>No select mode on a closed list</t>
         </is>
       </c>
       <c r="E376" s="9" t="inlineStr">
         <is>
-          <t>Read the line closely.</t>
+          <t>Open an archived list and hold a row.</t>
         </is>
       </c>
       <c r="F376" s="9" t="inlineStr">
         <is>
-          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
+          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
         </is>
       </c>
       <c r="G376" s="7" t="inlineStr">
@@ -15774,7 +15774,7 @@
     <row r="377">
       <c r="A377" s="6" t="inlineStr">
         <is>
-          <t>OUR-93</t>
+          <t>OUR-91</t>
         </is>
       </c>
       <c r="B377" s="7" t="inlineStr">
@@ -15782,24 +15782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C377" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C377" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D377" s="9" t="inlineStr">
         <is>
-          <t>No line on a copy you already finished or removed</t>
+          <t>A copy says when its shared row was taken off the list</t>
         </is>
       </c>
       <c r="E377" s="9" t="inlineStr">
         <is>
-          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
+          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
         </is>
       </c>
       <c r="F377" s="9" t="inlineStr">
         <is>
-          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
+          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
         </is>
       </c>
       <c r="G377" s="7" t="inlineStr">
@@ -15814,7 +15814,7 @@
     <row r="378">
       <c r="A378" s="6" t="inlineStr">
         <is>
-          <t>OUR-94</t>
+          <t>OUR-92</t>
         </is>
       </c>
       <c r="B378" s="7" t="inlineStr">
@@ -15822,24 +15822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C378" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C378" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D378" s="9" t="inlineStr">
         <is>
-          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
+          <t>That line never says who, and never says why</t>
         </is>
       </c>
       <c r="E378" s="9" t="inlineStr">
         <is>
-          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
+          <t>Read the line closely.</t>
         </is>
       </c>
       <c r="F378" s="9" t="inlineStr">
         <is>
-          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
+          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
         </is>
       </c>
       <c r="G378" s="7" t="inlineStr">
@@ -15854,7 +15854,7 @@
     <row r="379">
       <c r="A379" s="6" t="inlineStr">
         <is>
-          <t>OUR-95</t>
+          <t>OUR-93</t>
         </is>
       </c>
       <c r="B379" s="7" t="inlineStr">
@@ -15862,24 +15862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C379" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C379" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D379" s="9" t="inlineStr">
         <is>
-          <t>A row's note is VISIBLE, not only spoken</t>
+          <t>No line on a copy you already finished or removed</t>
         </is>
       </c>
       <c r="E379" s="9" t="inlineStr">
         <is>
-          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
+          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
         </is>
       </c>
       <c r="F379" s="9" t="inlineStr">
         <is>
-          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
+          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
         </is>
       </c>
       <c r="G379" s="7" t="inlineStr">
@@ -15894,7 +15894,7 @@
     <row r="380">
       <c r="A380" s="6" t="inlineStr">
         <is>
-          <t>OUR-96</t>
+          <t>OUR-94</t>
         </is>
       </c>
       <c r="B380" s="7" t="inlineStr">
@@ -15902,24 +15902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C380" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C380" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D380" s="9" t="inlineStr">
         <is>
-          <t>Rows WITHOUT a note are unchanged</t>
+          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
         </is>
       </c>
       <c r="E380" s="9" t="inlineStr">
         <is>
-          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
+          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
         </is>
       </c>
       <c r="F380" s="9" t="inlineStr">
         <is>
-          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
+          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
         </is>
       </c>
       <c r="G380" s="7" t="inlineStr">
@@ -15934,7 +15934,7 @@
     <row r="381">
       <c r="A381" s="6" t="inlineStr">
         <is>
-          <t>OUR-97</t>
+          <t>OUR-95</t>
         </is>
       </c>
       <c r="B381" s="7" t="inlineStr">
@@ -15949,17 +15949,17 @@
       </c>
       <c r="D381" s="9" t="inlineStr">
         <is>
-          <t>A tick after midnight lands on the RIGHT day</t>
+          <t>A row's note is VISIBLE, not only spoken</t>
         </is>
       </c>
       <c r="E381" s="9" t="inlineStr">
         <is>
-          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
+          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
         </is>
       </c>
       <c r="F381" s="9" t="inlineStr">
         <is>
-          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
+          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
         </is>
       </c>
       <c r="G381" s="7" t="inlineStr">
@@ -15974,7 +15974,7 @@
     <row r="382">
       <c r="A382" s="6" t="inlineStr">
         <is>
-          <t>OUR-98</t>
+          <t>OUR-96</t>
         </is>
       </c>
       <c r="B382" s="7" t="inlineStr">
@@ -15982,24 +15982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C382" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C382" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D382" s="9" t="inlineStr">
         <is>
-          <t>A tick made during a background sync is not undone</t>
+          <t>Rows WITHOUT a note are unchanged</t>
         </is>
       </c>
       <c r="E382" s="9" t="inlineStr">
         <is>
-          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
+          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
         </is>
       </c>
       <c r="F382" s="9" t="inlineStr">
         <is>
-          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
+          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
         </is>
       </c>
       <c r="G382" s="7" t="inlineStr">
@@ -16014,7 +16014,7 @@
     <row r="383">
       <c r="A383" s="6" t="inlineStr">
         <is>
-          <t>OUR-99</t>
+          <t>OUR-97</t>
         </is>
       </c>
       <c r="B383" s="7" t="inlineStr">
@@ -16029,17 +16029,17 @@
       </c>
       <c r="D383" s="9" t="inlineStr">
         <is>
-          <t>A tick survives a device that has never opened the room</t>
+          <t>A tick after midnight lands on the RIGHT day</t>
         </is>
       </c>
       <c r="E383" s="9" t="inlineStr">
         <is>
-          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
+          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
         </is>
       </c>
       <c r="F383" s="9" t="inlineStr">
         <is>
-          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
+          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
         </is>
       </c>
       <c r="G383" s="7" t="inlineStr">
@@ -16054,7 +16054,7 @@
     <row r="384">
       <c r="A384" s="6" t="inlineStr">
         <is>
-          <t>OUR-100</t>
+          <t>OUR-98</t>
         </is>
       </c>
       <c r="B384" s="7" t="inlineStr">
@@ -16069,17 +16069,17 @@
       </c>
       <c r="D384" s="9" t="inlineStr">
         <is>
-          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
+          <t>A tick made during a background sync is not undone</t>
         </is>
       </c>
       <c r="E384" s="9" t="inlineStr">
         <is>
-          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
+          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F384" s="9" t="inlineStr">
         <is>
-          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
+          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
         </is>
       </c>
       <c r="G384" s="7" t="inlineStr">
@@ -16094,7 +16094,7 @@
     <row r="385">
       <c r="A385" s="6" t="inlineStr">
         <is>
-          <t>OUR-101</t>
+          <t>OUR-99</t>
         </is>
       </c>
       <c r="B385" s="7" t="inlineStr">
@@ -16102,24 +16102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C385" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C385" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D385" s="9" t="inlineStr">
         <is>
-          <t>A closed list stops promising it keeps trying</t>
+          <t>A tick survives a device that has never opened the room</t>
         </is>
       </c>
       <c r="E385" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list that has unpushed local changes.</t>
+          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
         </is>
       </c>
       <c r="F385" s="9" t="inlineStr">
         <is>
-          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
+          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
         </is>
       </c>
       <c r="G385" s="7" t="inlineStr">
@@ -16134,7 +16134,7 @@
     <row r="386">
       <c r="A386" s="6" t="inlineStr">
         <is>
-          <t>OUR-102</t>
+          <t>OUR-100</t>
         </is>
       </c>
       <c r="B386" s="7" t="inlineStr">
@@ -16142,24 +16142,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C386" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C386" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D386" s="9" t="inlineStr">
         <is>
-          <t>Setting a rhythm clears any date the row was carrying</t>
+          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
         </is>
       </c>
       <c r="E386" s="9" t="inlineStr">
         <is>
-          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
+          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
         </is>
       </c>
       <c r="F386" s="9" t="inlineStr">
         <is>
-          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
+          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
         </is>
       </c>
       <c r="G386" s="7" t="inlineStr">
@@ -16174,7 +16174,7 @@
     <row r="387">
       <c r="A387" s="6" t="inlineStr">
         <is>
-          <t>OUR-103</t>
+          <t>OUR-101</t>
         </is>
       </c>
       <c r="B387" s="7" t="inlineStr">
@@ -16189,17 +16189,17 @@
       </c>
       <c r="D387" s="9" t="inlineStr">
         <is>
-          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
+          <t>A closed list stops promising it keeps trying</t>
         </is>
       </c>
       <c r="E387" s="9" t="inlineStr">
         <is>
-          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
+          <t>Open an archived list that has unpushed local changes.</t>
         </is>
       </c>
       <c r="F387" s="9" t="inlineStr">
         <is>
-          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
+          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
         </is>
       </c>
       <c r="G387" s="7" t="inlineStr">
@@ -16214,7 +16214,7 @@
     <row r="388">
       <c r="A388" s="6" t="inlineStr">
         <is>
-          <t>OUR-104</t>
+          <t>OUR-102</t>
         </is>
       </c>
       <c r="B388" s="7" t="inlineStr">
@@ -16222,24 +16222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C388" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C388" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D388" s="9" t="inlineStr">
         <is>
-          <t>No dead reorder rail on shared rows</t>
+          <t>Setting a rhythm clears any date the row was carrying</t>
         </is>
       </c>
       <c r="E388" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the room and in the From Ours strip.</t>
+          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
         </is>
       </c>
       <c r="F388" s="9" t="inlineStr">
         <is>
-          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
+          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
         </is>
       </c>
       <c r="G388" s="7" t="inlineStr">
@@ -16254,7 +16254,7 @@
     <row r="389">
       <c r="A389" s="6" t="inlineStr">
         <is>
-          <t>OUR-105</t>
+          <t>OUR-103</t>
         </is>
       </c>
       <c r="B389" s="7" t="inlineStr">
@@ -16262,24 +16262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C389" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C389" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D389" s="9" t="inlineStr">
         <is>
-          <t>First run introduces the shared list</t>
+          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
         </is>
       </c>
       <c r="E389" s="9" t="inlineStr">
         <is>
-          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
+          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
         </is>
       </c>
       <c r="F389" s="9" t="inlineStr">
         <is>
-          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
+          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
         </is>
       </c>
       <c r="G389" s="7" t="inlineStr">
@@ -16294,7 +16294,7 @@
     <row r="390">
       <c r="A390" s="6" t="inlineStr">
         <is>
-          <t>OUR-106</t>
+          <t>OUR-104</t>
         </is>
       </c>
       <c r="B390" s="7" t="inlineStr">
@@ -16302,24 +16302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C390" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C390" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D390" s="9" t="inlineStr">
         <is>
-          <t>Anyone can start a shared list, not just an allowlisted address</t>
+          <t>No dead reorder rail on shared rows</t>
         </is>
       </c>
       <c r="E390" s="9" t="inlineStr">
         <is>
-          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
+          <t>Hold a row in the room and in the From Ours strip.</t>
         </is>
       </c>
       <c r="F390" s="9" t="inlineStr">
         <is>
-          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
+          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
         </is>
       </c>
       <c r="G390" s="7" t="inlineStr">
@@ -16334,7 +16334,7 @@
     <row r="391">
       <c r="A391" s="6" t="inlineStr">
         <is>
-          <t>OUR-107</t>
+          <t>OUR-105</t>
         </is>
       </c>
       <c r="B391" s="7" t="inlineStr">
@@ -16349,17 +16349,17 @@
       </c>
       <c r="D391" s="9" t="inlineStr">
         <is>
-          <t>The shared-list onboarding step can actually be REACHED</t>
+          <t>First run introduces the shared list</t>
         </is>
       </c>
       <c r="E391" s="9" t="inlineStr">
         <is>
-          <t>Replay the first run and press the primary button through every step without skipping.</t>
+          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
         </is>
       </c>
       <c r="F391" s="9" t="inlineStr">
         <is>
-          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
+          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
         </is>
       </c>
       <c r="G391" s="7" t="inlineStr">
@@ -16374,7 +16374,7 @@
     <row r="392">
       <c r="A392" s="6" t="inlineStr">
         <is>
-          <t>OUR-108</t>
+          <t>OUR-106</t>
         </is>
       </c>
       <c r="B392" s="7" t="inlineStr">
@@ -16382,24 +16382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C392" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C392" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D392" s="9" t="inlineStr">
         <is>
-          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
+          <t>Anyone can start a shared list, not just an allowlisted address</t>
         </is>
       </c>
       <c r="E392" s="9" t="inlineStr">
         <is>
-          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
+          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
         </is>
       </c>
       <c r="F392" s="9" t="inlineStr">
         <is>
-          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
+          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
         </is>
       </c>
       <c r="G392" s="7" t="inlineStr">
@@ -16414,7 +16414,7 @@
     <row r="393">
       <c r="A393" s="6" t="inlineStr">
         <is>
-          <t>OUR-109</t>
+          <t>OUR-107</t>
         </is>
       </c>
       <c r="B393" s="7" t="inlineStr">
@@ -16429,17 +16429,17 @@
       </c>
       <c r="D393" s="9" t="inlineStr">
         <is>
-          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
+          <t>The shared-list onboarding step can actually be REACHED</t>
         </is>
       </c>
       <c r="E393" s="9" t="inlineStr">
         <is>
-          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
+          <t>Replay the first run and press the primary button through every step without skipping.</t>
         </is>
       </c>
       <c r="F393" s="9" t="inlineStr">
         <is>
-          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
+          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
         </is>
       </c>
       <c r="G393" s="7" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="394">
       <c r="A394" s="6" t="inlineStr">
         <is>
-          <t>OUR-110</t>
+          <t>OUR-108</t>
         </is>
       </c>
       <c r="B394" s="7" t="inlineStr">
@@ -16462,24 +16462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C394" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C394" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D394" s="9" t="inlineStr">
         <is>
-          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
+          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
         </is>
       </c>
       <c r="E394" s="9" t="inlineStr">
         <is>
-          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
+          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
         </is>
       </c>
       <c r="F394" s="9" t="inlineStr">
         <is>
-          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
+          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
         </is>
       </c>
       <c r="G394" s="7" t="inlineStr">
@@ -16494,12 +16494,12 @@
     <row r="395">
       <c r="A395" s="6" t="inlineStr">
         <is>
-          <t>UPD-01</t>
+          <t>OUR-109</t>
         </is>
       </c>
       <c r="B395" s="7" t="inlineStr">
         <is>
-          <t>Updates</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C395" s="8" t="inlineStr">
@@ -16509,17 +16509,17 @@
       </c>
       <c r="D395" s="9" t="inlineStr">
         <is>
-          <t>Settings states the version, and up-to-date is a fact</t>
+          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
         </is>
       </c>
       <c r="E395" s="9" t="inlineStr">
         <is>
-          <t>Open Settings and scroll to the foot.</t>
+          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
         </is>
       </c>
       <c r="F395" s="9" t="inlineStr">
         <is>
-          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
+          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
         </is>
       </c>
       <c r="G395" s="7" t="inlineStr">
@@ -16534,12 +16534,12 @@
     <row r="396">
       <c r="A396" s="6" t="inlineStr">
         <is>
-          <t>UPD-02</t>
+          <t>OUR-110</t>
         </is>
       </c>
       <c r="B396" s="7" t="inlineStr">
         <is>
-          <t>Updates</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C396" s="8" t="inlineStr">
@@ -16549,22 +16549,22 @@
       </c>
       <c r="D396" s="9" t="inlineStr">
         <is>
-          <t>Web offers a reload, and says drafts are kept</t>
+          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
         </is>
       </c>
       <c r="E396" s="9" t="inlineStr">
         <is>
-          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
+          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
         </is>
       </c>
       <c r="F396" s="9" t="inlineStr">
         <is>
-          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
+          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
         </is>
       </c>
       <c r="G396" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H396" s="7" t="inlineStr"/>
@@ -16574,7 +16574,7 @@
     <row r="397">
       <c r="A397" s="6" t="inlineStr">
         <is>
-          <t>UPD-03</t>
+          <t>UPD-01</t>
         </is>
       </c>
       <c r="B397" s="7" t="inlineStr">
@@ -16589,22 +16589,22 @@
       </c>
       <c r="D397" s="9" t="inlineStr">
         <is>
-          <t>Native points at the store, and says lists are untouched</t>
+          <t>Settings states the version, and up-to-date is a fact</t>
         </is>
       </c>
       <c r="E397" s="9" t="inlineStr">
         <is>
-          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
+          <t>Open Settings and scroll to the foot.</t>
         </is>
       </c>
       <c r="F397" s="9" t="inlineStr">
         <is>
-          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
+          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
         </is>
       </c>
       <c r="G397" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H397" s="7" t="inlineStr"/>
@@ -16614,7 +16614,7 @@
     <row r="398">
       <c r="A398" s="6" t="inlineStr">
         <is>
-          <t>UPD-04</t>
+          <t>UPD-02</t>
         </is>
       </c>
       <c r="B398" s="7" t="inlineStr">
@@ -16622,29 +16622,29 @@
           <t>Updates</t>
         </is>
       </c>
-      <c r="C398" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C398" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D398" s="9" t="inlineStr">
         <is>
-          <t>Unreachable server says NOTHING, never 'up to date'</t>
+          <t>Web offers a reload, and says drafts are kept</t>
         </is>
       </c>
       <c r="E398" s="9" t="inlineStr">
         <is>
-          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
+          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
         </is>
       </c>
       <c r="F398" s="9" t="inlineStr">
         <is>
-          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
+          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
         </is>
       </c>
       <c r="G398" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H398" s="7" t="inlineStr"/>
@@ -16654,7 +16654,7 @@
     <row r="399">
       <c r="A399" s="6" t="inlineStr">
         <is>
-          <t>UPD-05</t>
+          <t>UPD-03</t>
         </is>
       </c>
       <c r="B399" s="7" t="inlineStr">
@@ -16662,29 +16662,29 @@
           <t>Updates</t>
         </is>
       </c>
-      <c r="C399" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C399" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D399" s="9" t="inlineStr">
         <is>
-          <t>The goodnight mention is rare, and framed for the other person</t>
+          <t>Native points at the store, and says lists are untouched</t>
         </is>
       </c>
       <c r="E399" s="9" t="inlineStr">
         <is>
-          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
+          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
         </is>
       </c>
       <c r="F399" s="9" t="inlineStr">
         <is>
-          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
+          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
         </is>
       </c>
       <c r="G399" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H399" s="7" t="inlineStr"/>
@@ -16694,32 +16694,32 @@
     <row r="400">
       <c r="A400" s="6" t="inlineStr">
         <is>
-          <t>OUR-12</t>
+          <t>UPD-04</t>
         </is>
       </c>
       <c r="B400" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C400" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="C400" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D400" s="9" t="inlineStr">
         <is>
-          <t>Unnamed lists read in each person's language</t>
+          <t>Unreachable server says NOTHING, never 'up to date'</t>
         </is>
       </c>
       <c r="E400" s="9" t="inlineStr">
         <is>
-          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
         </is>
       </c>
       <c r="F400" s="9" t="inlineStr">
         <is>
-          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
         </is>
       </c>
       <c r="G400" s="7" t="inlineStr">
@@ -16731,9 +16731,89 @@
       <c r="I400" s="9" t="inlineStr"/>
       <c r="J400" s="7" t="inlineStr"/>
     </row>
+    <row r="401">
+      <c r="A401" s="6" t="inlineStr">
+        <is>
+          <t>UPD-05</t>
+        </is>
+      </c>
+      <c r="B401" s="7" t="inlineStr">
+        <is>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="C401" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D401" s="9" t="inlineStr">
+        <is>
+          <t>The goodnight mention is rare, and framed for the other person</t>
+        </is>
+      </c>
+      <c r="E401" s="9" t="inlineStr">
+        <is>
+          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
+        </is>
+      </c>
+      <c r="F401" s="9" t="inlineStr">
+        <is>
+          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
+        </is>
+      </c>
+      <c r="G401" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H401" s="7" t="inlineStr"/>
+      <c r="I401" s="9" t="inlineStr"/>
+      <c r="J401" s="7" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="6" t="inlineStr">
+        <is>
+          <t>OUR-12</t>
+        </is>
+      </c>
+      <c r="B402" s="7" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="C402" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D402" s="9" t="inlineStr">
+        <is>
+          <t>Unnamed lists read in each person's language</t>
+        </is>
+      </c>
+      <c r="E402" s="9" t="inlineStr">
+        <is>
+          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+        </is>
+      </c>
+      <c r="F402" s="9" t="inlineStr">
+        <is>
+          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+        </is>
+      </c>
+      <c r="G402" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H402" s="7" t="inlineStr"/>
+      <c r="I402" s="9" t="inlineStr"/>
+      <c r="J402" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J400"/>
-  <conditionalFormatting sqref="H2:H400">
+  <autoFilter ref="A1:J402"/>
+  <conditionalFormatting sqref="H2:H402">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -16745,7 +16825,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
+    <dataValidation sqref="H2:H402" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
       <formula1>"Pass,Fail,Blocked,Not run"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16781,7 +16861,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>401</t>
         </is>
       </c>
     </row>
@@ -16792,7 +16872,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF('Test Suite'!$H$2:$H$400,"Pass")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$402,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -16803,7 +16883,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF('Test Suite'!$H$2:$H$400,"Fail")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$402,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -16814,7 +16894,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Suite'!$H$2:$H$400,"Blocked")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$402,"Blocked")</f>
         <v/>
       </c>
     </row>
@@ -16825,7 +16905,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Suite'!$H$2:$H$400,"Not run")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$402,"Not run")</f>
         <v/>
       </c>
     </row>
@@ -16836,7 +16916,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>399-COUNTA('Test Suite'!$H$2:$H$400)</f>
+        <f>401-COUNTA('Test Suite'!$H$2:$H$402)</f>
         <v/>
       </c>
     </row>
@@ -16847,7 +16927,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF('Test Suite'!$C$2:$C$400,"P1")</f>
+        <f>COUNTIF('Test Suite'!$C$2:$C$402,"P1")</f>
         <v/>
       </c>
     </row>
@@ -16858,7 +16938,7 @@
         </is>
       </c>
       <c r="B10">
-        <f>COUNTIFS('Test Suite'!$C$2:$C$400,"P1",'Test Suite'!$H$2:$H$400,"Pass")</f>
+        <f>COUNTIFS('Test Suite'!$C$2:$C$402,"P1",'Test Suite'!$H$2:$H$402,"Pass")</f>
         <v/>
       </c>
     </row>

--- a/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
+++ b/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
@@ -1246,12 +1246,12 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>On a real Android phone (app and browser separately), tap the + pill, then tap the box, and watch the panel as the keyboard rises. Type a line, tap the When chip, pick Weekly, tap the box again, Add. Repeat at a large font-size setting, and on an iPhone.</t>
+          <t>On a real Android phone (app and browser separately), tap the + pill, then tap the box, and watch the panel as the keyboard rises. Type a line, tap the When chip, pick Weekly, tap the box again, Add. Repeat at a large font-size setting, on an iPhone in Safari (a normal tab), and in the iPhone home-screen app.</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>The panel sits on top of the keyboard: its heading and Close, the box (shrunk to its minimum first), the tools row, When and Add all stay in view, so you can see what you type and reach Add without dismissing the keyboard. Opening When puts the keyboard away and shows the choices; tapping the box brings the keyboard back and folds When to its chip. REGRESSION GUARD: a tester's v19 screenshots showed only 'ADD / Close' with everything else under the keyboard, because edge-to-edge Android ignores adjustResize and Chrome 108+ overlays the keyboard by default; the fix is the panel's own keyboard lift (native) + interactive-widget=resizes-content (web).</t>
+          <t>The panel sits on top of the keyboard: its heading and Close, the box (shrunk to its minimum first), the tools row, When and Add all stay in view, so you can see what you type and reach Add without dismissing the keyboard. Opening When puts the keyboard away and shows the choices; tapping the box brings the keyboard back and folds When to its chip. In iPhone Safari, Safari's own small address label floats just above the keyboard: When and Add sit clear above it, never under it (Melroy's screenshot, 2026-09-27, before lib/safari-chrome). REGRESSION GUARD: a tester's v19 screenshots showed only 'ADD / Close' with everything else under the keyboard, because edge-to-edge Android ignores adjustResize and Chrome 108+ overlays the keyboard by default; the fix is the panel's own keyboard lift (native) + interactive-widget=resizes-content (web).</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">

--- a/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
+++ b/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
@@ -1256,7 +1256,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>

--- a/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
+++ b/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$434</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$438</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J434"/>
+  <dimension ref="A1:J438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>No Premium pill on Chart a course for a subscriber. Dusk is never announced as Premium and tapping it as a free user selects it rather than bouncing. The signed-out paywall shows the Monthly / Annual toggle and both prices (checkout still needs sign-in). The edit-repeat button reads 'Save · Every Mon', with a verb. An empty day's note and '+ I also did that' sit above the dock, not under it. Spoken labels say '1 quieter action' and 'Removes 1 task'. Removing a rhythm says 'Rhythm removed.' and its name field is labelled 'Rhythm name'. The onboarding reveal rows show a small dot, not a tick-box replica. The 'big' chip stays visible in select mode. Focus with one open task opens straight on it, no 'Which one?'.</t>
+          <t>No Premium pill on Chart a course for a subscriber. Dusk is never announced as Premium and tapping it as a free user selects it rather than bouncing. On the web, the signed-out paywall shows the Monthly / Annual toggle and both prices (checkout still needs sign-in); on Android it shows no price at all (PREM-42). The edit-repeat button reads 'Save · Every Mon', with a verb. An empty day's note and '+ I also did that' sit above the dock, not under it. Spoken labels say '1 quieter action' and 'Removes 1 task'. Removing a rhythm says 'Rhythm removed.' and its name field is labelled 'Rhythm name'. The onboarding reveal rows show a small dot, not a tick-box replica. The 'big' chip stays visible in select mode. Focus with one open task opens straight on it, no 'Which one?'.</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="G215" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H215" s="7" t="inlineStr"/>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H218" s="7" t="inlineStr"/>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="G229" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H229" s="7" t="inlineStr"/>
@@ -9931,7 +9931,7 @@
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>First tap: a calm confirm, Premium turns on with NO card and NO Stripe (status 'trial'); the page shows 'Your free month', 'Free until &lt;date&gt;', and on web/Android the convert area shows the SAME monthly/annual toggle as the free paywall with the chosen price, and 'Go Premium to keep it' opens Stripe checkout for THAT plan (a trial member could only ever convert to monthly until 2026-08-01, when one asked to buy the year and could not; never 'Manage': a trial has no portal, so a Manage button here could only 404). On iOS the same trial copy shows with NO mid-trial CTA at all (StoreKit refuses a second purchase while premium and the trial never auto-charges; the 'Free until' line carries it), and never a Manage button. Second tap, same account: a gentle 'You've already had your free month' (never shame), no second trial granted. After expiry it reverts to free on its own, no charge ever. Signed out: an account is required (one trial per account), so the link routes to sign-in rather than granting. NOTE: this exact expected text was specified from the start, but the screen read the URL ?status= param instead of the entitlement status, so every trial user actually saw 'You're Premium' plus a dead Manage button until 2026-07-19. If this case regresses, that is the bug that came back.</t>
+          <t>First tap: a calm confirm, Premium turns on with NO card and NO Stripe (status 'trial'); the page shows 'Your free month', 'Free until &lt;date&gt;', and on the web the convert area shows the SAME monthly/annual toggle as the free paywall with the chosen price, and 'Go Premium to keep it' opens Stripe checkout for THAT plan (a trial member could only ever convert to monthly until 2026-08-01, when one asked to buy the year and could not; never 'Manage': a trial has no portal, so a Manage button here could only 404). On iOS the same trial copy shows with NO mid-trial CTA at all (StoreKit refuses a second purchase while premium and the trial never auto-charges; the 'Free until' line carries it), and never a Manage button. Second tap, same account: a gentle 'You've already had your free month' (never shame), no second trial granted. After expiry it reverts to free on its own, no charge ever. Signed out: an account is required (one trial per account), so the link routes to sign-in rather than granting. NOTE: this exact expected text was specified from the start, but the screen read the URL ?status= param instead of the entitlement status, so every trial user actually saw 'You're Premium' plus a dead Manage button until 2026-07-19. If this case regresses, that is the bug that came back.</t>
         </is>
       </c>
       <c r="G230" s="7" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="G231" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H231" s="7" t="inlineStr"/>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="G239" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H239" s="7" t="inlineStr"/>
@@ -10938,7 +10938,7 @@
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>PREM-29</t>
+          <t>PREM-42</t>
         </is>
       </c>
       <c r="B256" s="7" t="inlineStr">
@@ -10953,17 +10953,17 @@
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>The Android AAB does NOT contain Google Play Billing</t>
+          <t>Android sells nothing: the Premium page (Path C)</t>
         </is>
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>Build the Android AAB, unzip it, and grep for com.android.billingclient. Also confirm the app still builds, installs, and Premium still sells via Stripe on Android.</t>
+          <t>On an Android phone (the new build), open Premium signed OUT, then signed in as a FREE account, then from each gate: Scan, Pin, Plan my day, a colour theme, Quiet, a second keepsake in a month, and Your patterns. Repeat once with TalkBack on, listening to every label.</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>react-native-purchases (and Play Billing) is absent from the AAB: the expo.autolinking.android.exclude in client/package.json drops it. Android Premium is unchanged (Stripe Checkout in the browser). This is the regression guard on adding the native module.</t>
+          <t>The feature list and the gate's '&lt;feature&gt; is part of Premium.' line show, with 'The whole calm daily loop stays free, forever'. There is NO price or currency anywhere (no A$, no '/ month', no 'save 17%', no Monthly / Annual toggle), NO Go Premium, Subscribe or Upgrade, NO 'Billed securely via Stripe', and NO link to doubledone.app or Stripe. Signed out, the one button is 'Already have Premium? Sign in', which opens our own sign-in. Signed in and free, the only thing to take is 'Try Premium free for a month' with 'No card, no charge, and it never becomes a subscription on its own.' under it. TalkBack never speaks a dollar amount. This is the screen Google rejected 1.5.1 for (a fixed A$ price shown to a reviewer abroad).</t>
         </is>
       </c>
       <c r="G256" s="7" t="inlineStr">
@@ -10978,7 +10978,7 @@
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>PREM-30</t>
+          <t>PREM-43</t>
         </is>
       </c>
       <c r="B257" s="7" t="inlineStr">
@@ -10993,22 +10993,22 @@
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>The web build is unchanged and still sells via Stripe</t>
+          <t>Premium bought elsewhere works on Android, and is managed elsewhere</t>
         </is>
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>Build the production web export (expo export --platform web). Open /premium on web.</t>
+          <t>On the Android build, sign in as each of: a web (Stripe) subscriber, an Apple subscriber, a comp account, an account mid free-month, and a Stripe account in past_due. Open Premium each time.</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>The export succeeds (the native purchases module never enters the web bundle, proving the purchases.ts / purchases.ios.ts split). The web paywall shows the catalog price, the 'Billed securely via Stripe' line, NO Restore control, and the Stripe checkout path is unchanged. The regression guard on the paywall rewrite.</t>
+          <t>Every paying, comp or trial account shows Premium active, with its extras working. The Stripe subscriber sees one plain line, 'To change or cancel it, use the website where you subscribed, or email support@doubledone.app.', with no button and no link. The Apple subscriber sees the 'Apple handles it' line. The comp sees 'Your Premium is on us'. The free month shows 'Free until &lt;date&gt;, then back to the free monthly scrapbook. No charge, ever.' and no way to buy. The past_due account sees the paused notice with the support email and NO 'Update payment details' link. Nothing opens Stripe.</t>
         </is>
       </c>
       <c r="G257" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H257" s="7" t="inlineStr"/>
@@ -11018,7 +11018,7 @@
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>PREM-32</t>
+          <t>PREM-44</t>
         </is>
       </c>
       <c r="B258" s="7" t="inlineStr">
@@ -11026,29 +11026,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C258" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C258" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
-          <t>PRODUCTION paywall price matches App Store Connect</t>
+          <t>The rest of the Android app carries no price</t>
         </is>
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>After the app is RELEASED, install it from the App Store (not TestFlight) on an Australian account and open Premium. Read the monthly and annual prices.</t>
+          <t>On the Android build: walk the welcome to its Premium step; open Settings &gt; Terms, and Settings &gt; Privacy; with TalkBack, focus the Settings Premium card as a free account, and the Menu's Premium row as a subscriber; then, signed in as an account whose free month has already ended, tap 'Try Premium free for a month' and come back to Premium once more.</t>
         </is>
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>The paywall reads A$5.00 / month and A$50.00 / year, matching the App Store Connect price schedule for Australia, and matching what Apple's purchase sheet charges. CRITICAL: TestFlight and sandbox CANNOT verify this. They are known to answer product queries for the US storefront regardless of the account's real region, so a TestFlight paywall showing US dollars is expected and is NOT the bug. Only a production App Store install proves it. If production still disagrees with the sheet, that is a misleading pre-purchase price (an Australian Consumer Law problem, not just a display bug): pull the release via Pricing and Availability, Remove from sale. Prerequisite: app released. Gate the RELEASE on this, never the submission.</t>
+          <t>The welcome's fine print reads 'It's in Settings whenever you're curious. No ads, ever.' (no A$5). The Terms' 'Premium and billing' says Premium is optional and not sold in this app, with no price, and Refunds names Stripe billing for people who subscribed on the website or in an earlier version of the Android app, with no price and no way to buy. Privacy says Stripe processes payments on our website. The Premium card is read as 'DoubleDone Premium' (never 'see plans'), and the Menu row for a subscriber as 'Active. Every extra is yours.' (never 'Manage your subscription'). That tap says 'You've already had your free month.' (with the usual 'The free monthly scrapbook is always yours.' under it) and no nudge to buy, the link itself goes, and on the next visit it is not offered again.</t>
         </is>
       </c>
       <c r="G258" s="7" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H258" s="7" t="inlineStr"/>
@@ -11058,7 +11058,7 @@
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>PREM-33</t>
+          <t>PREM-45</t>
         </is>
       </c>
       <c r="B259" s="7" t="inlineStr">
@@ -11073,22 +11073,22 @@
       </c>
       <c r="D259" s="9" t="inlineStr">
         <is>
-          <t>A dunning subscriber is never sold a second subscription</t>
+          <t>The web and the iPhone still sell exactly as before</t>
         </is>
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>Put a test Stripe subscription into past_due (in Stripe test mode: attach a failing card, or use the test clock to fail a renewal). Open /premium signed in as that user. Read the panel, then try to buy.</t>
+          <t>After the Path C change: on the web, open Premium signed out and signed in; on an iPhone build, open Premium signed out.</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>Access has lapsed so the UPSELL panel shows, but with a calm notice at the top: 'Your Premium is paused while a payment retries. Updating your card brings it back. There is no need to buy again.' with an 'Update payment details' link that opens the Stripe portal (the customer id exists in this state). If the user taps Go Premium anyway, the server refuses with 409 billing_issue and the app explains the card is the fix, NEVER 'You're already on Premium' (false: they are not) and NEVER a second Checkout. REGRESSION GUARDS on the same server change (locked by stripe.test.ts): a LAPSED subscriber (status canceled, customer id kept) can still re-subscribe via a fresh Checkout, an abandoned checkout (incomplete) can still buy, and a trial still converts. The old guard keyed on premium &amp;&amp; customerId, so a past_due user could mint a SECOND subscription whose webhook overwrote stripe_customer_id and orphaned the first: paying twice with one visible.</t>
+          <t>Web: the Monthly / Annual toggle and both A$ prices, Go Premium opening Stripe Checkout, and 'Billed securely via Stripe. Terms and refunds' are all there, unchanged. iPhone: the StoreKit prices in the viewer's currency, the buy button, Restore, and Apple's renewal terms are all there, unchanged. REGRESSION GUARD: Path C is a compile-time Android-only switch (lib/storefront.android.ts), so a web or iOS difference is a bug.</t>
         </is>
       </c>
       <c r="G259" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H259" s="7" t="inlineStr"/>
@@ -11098,7 +11098,7 @@
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>PREM-34</t>
+          <t>PREM-29</t>
         </is>
       </c>
       <c r="B260" s="7" t="inlineStr">
@@ -11113,22 +11113,22 @@
       </c>
       <c r="D260" s="9" t="inlineStr">
         <is>
-          <t>An ANNUAL subscriber is warned a week before the charge, once</t>
+          <t>The Android AAB does NOT contain Google Play Billing</t>
         </is>
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>Needs a Stripe test clock, because the whole feature is about a year passing. Put a test user on the ANNUAL price. Open the app once while the renewal is far away (this is what teaches the device the period is a year: it is only ever judged annual when first seen more than 40 days out). Advance the test clock to ~10 days before renewal and open Today again. Then open it several more times. Separately, repeat the whole thing with a MONTHLY subscriber, and again with an annual one that has been CANCELLED (cancel_at_period_end).</t>
+          <t>Build the Android AAB, unzip it, and grep for com.android.billingclient. Also confirm the app still builds and installs, and that Premium is NOT sold on Android (PREM-42).</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>The annual subscriber gets ONE new task, dated SEVEN days before the charge (not on the day of it, which would be a receipt rather than a warning), reading 'Your DoubleDone year renews on &lt;date&gt;. Nothing to do.' Re-opening the app does NOT add a second: it is remembered against that period, and the next one is only noticed after the period rolls. The MONTHLY subscriber never gets one, however many times the app is opened (twelve notices a year is nagging). The CANCELLED subscriber never gets one either, because nothing is renewing and saying otherwise to someone who has decided to leave is both false and unkind. A device that first opens the app INSIDE the last 40 days gets no notice that year, by design, and self-corrects the next. This is the only place the app writes a task nobody typed, so a false positive here is a spine violation, not a cosmetic bug.</t>
+          <t>react-native-purchases (and Play Billing) is absent from the AAB: the expo.autolinking.android.exclude in client/package.json drops it. Android sells nothing (Path C, 2026-09-27): no price, no Go Premium, no Stripe. This is the regression guard on adding the native module.</t>
         </is>
       </c>
       <c r="G260" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H260" s="7" t="inlineStr"/>
@@ -11138,7 +11138,7 @@
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>PREM-31</t>
+          <t>PREM-30</t>
         </is>
       </c>
       <c r="B261" s="7" t="inlineStr">
@@ -11146,25 +11146,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C261" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C261" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
-          <t>Sandbox tester + Restore Behavior confirmed in the RevenueCat dashboard</t>
-        </is>
-      </c>
-      <c r="E261" s="9" t="inlineStr"/>
+          <t>The web build is unchanged and still sells via Stripe</t>
+        </is>
+      </c>
+      <c r="E261" s="9" t="inlineStr">
+        <is>
+          <t>Build the production web export (expo export --platform web). Open /premium on web.</t>
+        </is>
+      </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>In the RevenueCat dashboard: Restore Behavior is set to keep-with-original (so TRANSFER never fires), the App Store Connect API key + In-App-Purchase key are uploaded, both products read 'Ready to Submit', and the IAPs are attached to the SAME App Store submission as the first binary (a first-time subscription submitted separately is not reviewed). A Sandbox Apple ID exists for testing.</t>
+          <t>The export succeeds (the native purchases module never enters the web bundle, proving the purchases.ts / purchases.ios.ts split). The web paywall shows the catalog price, the 'Billed securely via Stripe' line, NO Restore control, and the Stripe checkout path is unchanged. The regression guard on the paywall rewrite.</t>
         </is>
       </c>
       <c r="G261" s="7" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H261" s="7" t="inlineStr"/>
@@ -11174,12 +11178,12 @@
     <row r="262">
       <c r="A262" s="6" t="inlineStr">
         <is>
-          <t>QUI-01</t>
+          <t>PREM-32</t>
         </is>
       </c>
       <c r="B262" s="7" t="inlineStr">
         <is>
-          <t>Interface</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C262" s="8" t="inlineStr">
@@ -11189,22 +11193,22 @@
       </c>
       <c r="D262" s="9" t="inlineStr">
         <is>
-          <t>Premium unlocks the Quiet interface; free is gated</t>
+          <t>PRODUCTION paywall price matches App Store Connect</t>
         </is>
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>As premium (or with the dev Premium override on), open Settings -&gt; Comfort -&gt; 'Interface' and tap 'Quiet', then reload. Then as a FREE user, tap 'Quiet'.</t>
+          <t>After the app is RELEASED, install it from the App Store (not TestFlight) on an Australian account and open Premium. Read the monthly and annual prices.</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>Premium: the whole Today surface goes borderless. Card outlines drop, and every action that looked like a button or a link renders as plain text with no outline or fill: the header Menu pill (which keeps just the word 'Menu', no dots), 'Focus on one thing', 'Lighten today', 'Close the day', and 'Plan my day' (which in Standard is the filled premium gradient) all become plain text (accent for the AI / premium ones, soft ink for the calm structural ones). The energy / weight-of-today gauge is KEPT, not removed: it shrinks to a 3px hairline bar so the day's load still reads at a glance. The choice survives reload with 'Quiet' ringed. 'Standard' is the default and looks identical to the app today (gradient button, 6px gauge, outlined actions all return). Free: the block shows a 'Premium' tag and tapping 'Quiet' routes to the paywall with NO change applied ('appearance.locked' logged). A lapsed subscriber keeps whichever appearance they chose.</t>
+          <t>The paywall reads A$5.00 / month and A$50.00 / year, matching the App Store Connect price schedule for Australia, and matching what Apple's purchase sheet charges. CRITICAL: TestFlight and sandbox CANNOT verify this. They are known to answer product queries for the US storefront regardless of the account's real region, so a TestFlight paywall showing US dollars is expected and is NOT the bug. Only a production App Store install proves it. If production still disagrees with the sheet, that is a misleading pre-purchase price (an Australian Consumer Law problem, not just a display bug): pull the release via Pricing and Availability, Remove from sale. Prerequisite: app released. Gate the RELEASE on this, never the submission.</t>
         </is>
       </c>
       <c r="G262" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="H262" s="7" t="inlineStr"/>
@@ -11214,37 +11218,37 @@
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>QUI-02</t>
+          <t>PREM-33</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
         <is>
-          <t>Interface</t>
-        </is>
-      </c>
-      <c r="C263" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="C263" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>Switching Standard &lt;-&gt; Quiet never moves the layout</t>
+          <t>A dunning subscriber is never sold a second subscription</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>With a handful of tasks on Today (some open, one or two done), toggle Interface between Standard and Quiet a few times, watching the task rows and the capture line. On ANDROID, specifically do the full round trip (Standard -&gt; Quiet -&gt; Standard) from the Settings screen and then return to Today.</t>
+          <t>Put a test Stripe subscription into past_due (in Stripe test mode: attach a failing card, or use the test clock to fail a renewal). Open /premium signed in as that user. Read the panel, then try to buy.</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>Content stays put: no visible jump in row height or position as you toggle. Quiet removes chrome (row borders, fills, the per-task progress bar, the capture underline weight) but preserves spacing, so nothing shifts under the finger. On Android the round trip must leave rows pixel-perfect, in particular the row BOTTOMS never look clipped/'eaten' (regression: toggling while Today sat detached behind Settings in the native stack left rows at Quiet's slightly shorter measured height under Standard's styles; Today now remounts on an appearance change so native lays it out fresh).</t>
+          <t>Access has lapsed so the UPSELL panel shows, but with a calm notice at the top: 'Your Premium is paused while a payment retries. Updating your card brings it back. There is no need to buy again.' with an 'Update payment details' link that opens the Stripe portal (the customer id exists in this state). If the user taps Go Premium anyway, the server refuses with 409 billing_issue and the app explains the card is the fix, NEVER 'You're already on Premium' (false: they are not) and NEVER a second Checkout. REGRESSION GUARDS on the same server change (locked by stripe.test.ts): a LAPSED subscriber (status canceled, customer id kept) can still re-subscribe via a fresh Checkout, an abandoned checkout (incomplete) can still buy, and a trial still converts. The old guard keyed on premium &amp;&amp; customerId, so a past_due user could mint a SECOND subscription whose webhook overwrote stripe_customer_id and orphaned the first: paying twice with one visible.</t>
         </is>
       </c>
       <c r="G263" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H263" s="7" t="inlineStr"/>
@@ -11254,32 +11258,32 @@
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>QUI-06</t>
+          <t>PREM-34</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
         <is>
-          <t>Interface</t>
-        </is>
-      </c>
-      <c r="C264" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="C264" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>Quiet draws Energy as three words</t>
+          <t>An ANNUAL subscriber is warned a week before the charge, once</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>Premium, Settings -&gt; Look -&gt; Interface -&gt; Quiet. Open Today and change Energy between Low, Normal and High.</t>
+          <t>Needs a Stripe test clock, because the whole feature is about a year passing. Put a test user on the ANNUAL price. Open the app once while the renewal is far away (this is what teaches the device the period is a year: it is only ever judged annual when first seen more than 40 days out). Advance the test clock to ~10 days before renewal and open Today again. Then open it several more times. Separately, repeat the whole thing with a MONTHLY subscriber, and again with an annual one that has been CANCELLED (cancel_at_period_end).</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>No pills: Low, Normal and High are plain words, the chosen one in bold ink, the others in soft ink. Each still has a full 44pt tap area and nothing shifts when the choice changes. Standard keeps the soft pill.</t>
+          <t>The annual subscriber gets ONE new task, dated SEVEN days before the charge (not on the day of it, which would be a receipt rather than a warning), reading 'Your DoubleDone year renews on &lt;date&gt;. Nothing to do.' Re-opening the app does NOT add a second: it is remembered against that period, and the next one is only noticed after the period rolls. The MONTHLY subscriber never gets one, however many times the app is opened (twelve notices a year is nagging). The CANCELLED subscriber never gets one either, because nothing is renewing and saying otherwise to someone who has decided to leave is both false and unkind. A device that first opens the app INSIDE the last 40 days gets no notice that year, by design, and self-corrects the next. This is the only place the app writes a task nobody typed, so a false positive here is a spine violation, not a cosmetic bug.</t>
         </is>
       </c>
       <c r="G264" s="7" t="inlineStr">
@@ -11294,12 +11298,12 @@
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>QUI-03</t>
+          <t>PREM-31</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
         <is>
-          <t>Interface</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
@@ -11309,22 +11313,18 @@
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>The held card is identical in Quiet and Standard (only the tint differs)</t>
-        </is>
-      </c>
-      <c r="E265" s="9" t="inlineStr">
-        <is>
-          <t>Hold the SAME one-off task on Today in Quiet, then switch appearance and hold it again in Standard. Compare them side by side. Then in Quiet also hold a 'Later' task and (if you have one) a recurring task.</t>
-        </is>
-      </c>
+          <t>Sandbox tester + Restore Behavior confirmed in the RevenueCat dashboard</t>
+        </is>
+      </c>
+      <c r="E265" s="9" t="inlineStr"/>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>BOTH appearances now give the same in-place card with the same actions in the same order (see TOD-07): there is no longer a Quiet model and a Standard model. Only the treatment differs: Quiet gets a soft wash with a rounded bleed, Standard the accent tint. Mark-as-a-lot and Pin act-and-dismiss (the row updates, the card closes). Pin shows only on Today one-off rows (not Later, not recurring), matching PIN-05; a lapsed subscriber still on Quiet who taps Pin is routed to the paywall, never wrongly pinned. 'Select more' closes the card and drops into multi-select with THIS task pre-selected ('1 selected'); Combine appears once a second task is selected. The one-time 'hold a task for more' coachmark in Quiet is a faint line with a small accent dot, not a filled pill.</t>
+          <t>In the RevenueCat dashboard: Restore Behavior is set to keep-with-original (so TRANSFER never fires), the App Store Connect API key + In-App-Purchase key are uploaded, both products read 'Ready to Submit', and the IAPs are attached to the SAME App Store submission as the first binary (a first-time subscription submitted separately is not reviewed). A Sandbox Apple ID exists for testing.</t>
         </is>
       </c>
       <c r="G265" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="H265" s="7" t="inlineStr"/>
@@ -11334,7 +11334,7 @@
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>QUI-04</t>
+          <t>QUI-01</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -11342,24 +11342,24 @@
           <t>Interface</t>
         </is>
       </c>
-      <c r="C266" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C266" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>Quiet close-the-day reads as page text and stays reachable when full</t>
+          <t>Premium unlocks the Quiet interface; free is gated</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>In Quiet, finish several tasks, then also test a very full day (roughly 16+ finished), and tap 'Close the day'.</t>
+          <t>As premium (or with the dev Premium override on), open Settings -&gt; Comfort -&gt; 'Interface' and tap 'Quiet', then reload. Then as a FREE user, tap 'Quiet'.</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>The wrap shows on the plain page colour with no dim scrim and no card outline, and 'Goodnight' is a plain accent text link, not a filled button. On a very full day the finished list still scrolls inside a bounded area and 'Goodnight' stays on screen and reachable, so the TOD-04d regression holds in Quiet too. Reopen / rested behaviour is unchanged.</t>
+          <t>Premium: the whole Today surface goes borderless. Card outlines drop, and every action that looked like a button or a link renders as plain text with no outline or fill: the header Menu pill (which keeps just the word 'Menu', no dots), 'Focus on one thing', 'Lighten today', 'Close the day', and 'Plan my day' (which in Standard is the filled premium gradient) all become plain text (accent for the AI / premium ones, soft ink for the calm structural ones). The energy / weight-of-today gauge is KEPT, not removed: it shrinks to a 3px hairline bar so the day's load still reads at a glance. The choice survives reload with 'Quiet' ringed. 'Standard' is the default and looks identical to the app today (gradient button, 6px gauge, outlined actions all return). Free: the block shows a 'Premium' tag and tapping 'Quiet' routes to the paywall with NO change applied ('appearance.locked' logged). A lapsed subscriber keeps whichever appearance they chose.</t>
         </is>
       </c>
       <c r="G266" s="7" t="inlineStr">
@@ -11374,7 +11374,7 @@
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>QUI-05</t>
+          <t>QUI-02</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -11382,24 +11382,24 @@
           <t>Interface</t>
         </is>
       </c>
-      <c r="C267" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C267" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>Quiet honours reduce-motion and every colour theme</t>
+          <t>Switching Standard &lt;-&gt; Quiet never moves the layout</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>In Quiet, set Settings -&gt; Motion -&gt; Reduce (or the OS reduce-motion), then complete a task, open the held-state, and close the day. Separately, view Quiet across a couple of colour themes (e.g. Dusk and Sage) in BOTH light and dark.</t>
+          <t>With a handful of tasks on Today (some open, one or two done), toggle Interface between Standard and Quiet a few times, watching the task rows and the capture line. On ANDROID, specifically do the full round trip (Standard -&gt; Quiet -&gt; Standard) from the Settings screen and then return to Today.</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>Nothing animates beyond the app's reduce-motion baseline: the held-state and the wrap appear without motion. Quiet derives its hairlines and washes from the ACTIVE palette, so it looks right on every colour theme in light and dark (not only Dusk), with no washed-out or invisible text.</t>
+          <t>Content stays put: no visible jump in row height or position as you toggle. Quiet removes chrome (row borders, fills, the per-task progress bar, the capture underline weight) but preserves spacing, so nothing shifts under the finger. On Android the round trip must leave rows pixel-perfect, in particular the row BOTTOMS never look clipped/'eaten' (regression: toggling while Today sat detached behind Settings in the native stack left rows at Quiet's slightly shorter measured height under Standard's styles; Today now remounts on an appearance change so native lays it out fresh).</t>
         </is>
       </c>
       <c r="G267" s="7" t="inlineStr">
@@ -11414,32 +11414,32 @@
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>PIN-01</t>
+          <t>QUI-06</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
         <is>
-          <t>Pin</t>
-        </is>
-      </c>
-      <c r="C268" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="C268" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>Premium: pin a task as the day's one thing</t>
+          <t>Quiet draws Energy as three words</t>
         </is>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>As premium (or with the dev Premium override on), tap-and-hold a one-off task to select it, then tap 'Pin' in the held row's actions.</t>
+          <t>Premium, Settings -&gt; Look -&gt; Interface -&gt; Quiet. Open Today and change Energy between Low, Normal and High.</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>The task gets a calm mauve PIN MARK (a drawn pushpin; the star it replaced read as favourite, not pin, per Melroy 2026-08-30, and a drawn SVG cannot hit the iOS missing-glyph failure the round-one flag did) and the thick accent border, and floats to the top of Today. 'Focus on one thing' then opens straight to it.</t>
+          <t>No pills: Low, Normal and High are plain words, the chosen one in bold ink, the others in soft ink. Each still has a full 44pt tap area and nothing shifts when the choice changes. Standard keeps the soft pill.</t>
         </is>
       </c>
       <c r="G268" s="7" t="inlineStr">
@@ -11454,32 +11454,32 @@
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>PIN-02</t>
+          <t>QUI-03</t>
         </is>
       </c>
       <c r="B269" s="7" t="inlineStr">
         <is>
-          <t>Pin</t>
-        </is>
-      </c>
-      <c r="C269" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="C269" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>Free: Pin routes to the upsell, never pins</t>
+          <t>The held card is identical in Quiet and Standard (only the tint differs)</t>
         </is>
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>As a free user, select a single one-off task and tap the dimmed 'Pin' action.</t>
+          <t>Hold the SAME one-off task on Today in Quiet, then switch appearance and hold it again in Standard. Compare them side by side. Then in Quiet also hold a 'Later' task and (if you have one) a recurring task.</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>No task is pinned, and the Premium screen opens calmly (never a shaming wall). A 'premium.gate_hit' with reason 'pin' is logged.</t>
+          <t>BOTH appearances now give the same in-place card with the same actions in the same order (see TOD-07): there is no longer a Quiet model and a Standard model. Only the treatment differs: Quiet gets a soft wash with a rounded bleed, Standard the accent tint. Mark-as-a-lot and Pin act-and-dismiss (the row updates, the card closes). Pin shows only on Today one-off rows (not Later, not recurring), matching PIN-05; a lapsed subscriber still on Quiet who taps Pin is routed to the paywall, never wrongly pinned. 'Select more' closes the card and drops into multi-select with THIS task pre-selected ('1 selected'); Combine appears once a second task is selected. The one-time 'hold a task for more' coachmark in Quiet is a faint line with a small accent dot, not a filled pill.</t>
         </is>
       </c>
       <c r="G269" s="7" t="inlineStr">
@@ -11494,12 +11494,12 @@
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>PIN-03</t>
+          <t>QUI-04</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
         <is>
-          <t>Pin</t>
+          <t>Interface</t>
         </is>
       </c>
       <c r="C270" s="10" t="inlineStr">
@@ -11509,17 +11509,17 @@
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>Only one task is pinned at a time</t>
+          <t>Quiet close-the-day reads as page text and stays reachable when full</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>As premium, pin task A, then hold task B and pin it.</t>
+          <t>In Quiet, finish several tasks, then also test a very full day (roughly 16+ finished), and tap 'Close the day'.</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>Task B is now pinned (pin-marked, floated to the top), and task A is no longer pinned. At most one pin ever exists.</t>
+          <t>The wrap shows on the plain page colour with no dim scrim and no card outline, and 'Goodnight' is a plain accent text link, not a filled button. On a very full day the finished list still scrolls inside a bounded area and 'Goodnight' stays on screen and reachable, so the TOD-04d regression holds in Quiet too. Reopen / rested behaviour is unchanged.</t>
         </is>
       </c>
       <c r="G270" s="7" t="inlineStr">
@@ -11534,32 +11534,32 @@
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>PIN-04</t>
+          <t>QUI-05</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
         <is>
-          <t>Pin</t>
-        </is>
-      </c>
-      <c r="C271" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="C271" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>A pin syncs across devices</t>
+          <t>Quiet honours reduce-motion and every colour theme</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>As premium and signed in, pin a task, then sign out and back in (or open a second device).</t>
+          <t>In Quiet, set Settings -&gt; Motion -&gt; Reduce (or the OS reduce-motion), then complete a task, open the held-state, and close the day. Separately, view Quiet across a couple of colour themes (e.g. Dusk and Sage) in BOTH light and dark.</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>The task is still pinned after the sync round-trip (the pin mark and float persist). Needs the pinned_at column applied in Supabase.</t>
+          <t>Nothing animates beyond the app's reduce-motion baseline: the held-state and the wrap appear without motion. Quiet derives its hairlines and washes from the ACTIVE palette, so it looks right on every colour theme in light and dark (not only Dusk), with no washed-out or invisible text.</t>
         </is>
       </c>
       <c r="G271" s="7" t="inlineStr">
@@ -11574,7 +11574,7 @@
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>PIN-05</t>
+          <t>PIN-01</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -11582,24 +11582,24 @@
           <t>Pin</t>
         </is>
       </c>
-      <c r="C272" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C272" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Pin is offered only on one-off Today rows</t>
+          <t>Premium: pin a task as the day's one thing</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>Hold a recurring task, then hold a task in the 'Later' list.</t>
+          <t>As premium (or with the dev Premium override on), tap-and-hold a one-off task to select it, then tap 'Pin' in the held row's actions.</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>No 'Pin' action appears on a recurring task's held card, and a Later task's card carries no Pin either (pinning is Today-only and one-offs only).</t>
+          <t>The task gets a calm mauve PIN MARK (a drawn pushpin; the star it replaced read as favourite, not pin, per Melroy 2026-08-30, and a drawn SVG cannot hit the iOS missing-glyph failure the round-one flag did) and the thick accent border, and floats to the top of Today. 'Focus on one thing' then opens straight to it.</t>
         </is>
       </c>
       <c r="G272" s="7" t="inlineStr">
@@ -11614,12 +11614,12 @@
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>NRG-01</t>
+          <t>PIN-02</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Pin</t>
         </is>
       </c>
       <c r="C273" s="8" t="inlineStr">
@@ -11629,17 +11629,17 @@
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>What fits right now: one question, one pick, propose-only</t>
+          <t>Free: Pin routes to the upsell, never pins</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>With AI on and 2+ open one-off tasks, tap 'Focus on one thing'; in the 'Which one?' picker, 'What fits right now?' sits above the task choices in a soft hairline pill (its border makes it read as tappable; it lives INSIDE Focus, not as a standalone Today button). Tap it, pick an energy level (Running low / Somewhere in between / Feeling good). Then tap 'Start with this'; separately try 'Not now'.</t>
+          <t>As a free user, select a single one-off task and tap the dimmed 'Pin' action.</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>A calm one-question card with the privacy line ('Your open tasks go to Claude to pick one. Nothing is added or changed.'). Choosing a level shows ONE task from today's list with a short warm line on why it fits (never shaming, never about what's undone). 'Start with this' opens Focus mode on exactly that task; 'Not now' just closes, nothing changed. A failed call shows a calm 'Couldn't find a pick just now.' line and does NOT spend a free pick. The entry hides when AI is off or fewer than 2 tasks are open. Needs the Worker deployed with /energy.</t>
+          <t>No task is pinned, and the Premium screen opens calmly (never a shaming wall). A 'premium.gate_hit' with reason 'pin' is logged.</t>
         </is>
       </c>
       <c r="G273" s="7" t="inlineStr">
@@ -11654,32 +11654,32 @@
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>NRG-02</t>
+          <t>PIN-03</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C274" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Pin</t>
+        </is>
+      </c>
+      <c r="C274" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>The freemium meter: 15 a month, reminders at 10 and 5, then the paywall</t>
+          <t>Only one task is pinned at a time</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>As a FREE user, use energy matching repeatedly in one calendar month (seed doubledone.energyUses.v1 to fast-forward). Watch the 10-left and 5-left moments, then the 16th tap. Then as premium, use it well past 15.</t>
+          <t>As premium, pin task A, then hold task B and pin it.</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>Each successful pick spends one of 15 free picks a calendar month (counted locally, like the scrapbook gate). Exactly at 10 left and at 5 left, the result shows one calm line: '10 of your 15 free picks left this month.' (then 5). Past 15, tapping the entry routes to the paywall (which lists 'Energy matching without limits'), never a shaming wall, and no AI call is made ('premium.gate_hit' reason 'energy' logs). The counter resets on the 1st of the month with no carry-over. Premium is unlimited and never sees a counter line.</t>
+          <t>Task B is now pinned (pin-marked, floated to the top), and task A is no longer pinned. At most one pin ever exists.</t>
         </is>
       </c>
       <c r="G274" s="7" t="inlineStr">
@@ -11694,32 +11694,32 @@
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>OCR-01</t>
+          <t>PIN-04</t>
         </is>
       </c>
       <c r="B275" s="7" t="inlineStr">
         <is>
-          <t>Scan</t>
-        </is>
-      </c>
-      <c r="C275" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Pin</t>
+        </is>
+      </c>
+      <c r="C275" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>Premium: the Scan button opens the camera</t>
+          <t>A pin syncs across devices</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>As premium, tap the + pill and then Scan (camera) beside Speak in the panel.</t>
+          <t>As premium and signed in, pin a task, then sign out and back in (or open a second device).</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>The camera screen opens: a live viewfinder with a shutter and a Photos shortcut on a device, or a 'Choose a photo' prompt on web. No paywall.</t>
+          <t>The task is still pinned after the sync round-trip (the pin mark and float persist). Needs the pinned_at column applied in Supabase.</t>
         </is>
       </c>
       <c r="G275" s="7" t="inlineStr">
@@ -11734,32 +11734,32 @@
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>OCR-02</t>
+          <t>PIN-05</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
         <is>
-          <t>Scan</t>
-        </is>
-      </c>
-      <c r="C276" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Pin</t>
+        </is>
+      </c>
+      <c r="C276" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Free: Scan routes to the upsell, never opens the camera</t>
+          <t>Pin is offered only on one-off Today rows</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>As a free user, tap the + pill and then Scan in the panel.</t>
+          <t>Hold a recurring task, then hold a task in the 'Later' list.</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>Routed to the Premium screen calmly (never a wall). A 'premium.gate_hit' with reason 'ocr' is logged. No camera opens.</t>
+          <t>No 'Pin' action appears on a recurring task's held card, and a Later task's card carries no Pin either (pinning is Today-only and one-offs only).</t>
         </is>
       </c>
       <c r="G276" s="7" t="inlineStr">
@@ -11774,12 +11774,12 @@
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>OCR-03</t>
+          <t>NRG-01</t>
         </is>
       </c>
       <c r="B277" s="7" t="inlineStr">
         <is>
-          <t>Scan</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C277" s="8" t="inlineStr">
@@ -11789,22 +11789,22 @@
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Photograph a list and the tasks land in the box</t>
+          <t>What fits right now: one question, one pick, propose-only</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>As premium on a device, tap Scan, photograph a short printed or handwritten list (fill the frame), wait for 'Reading your list...'.</t>
+          <t>With AI on and 2+ open one-off tasks, tap 'Focus on one thing'; in the 'Which one?' picker, 'What fits right now?' sits above the task choices in a soft hairline pill (its border makes it read as tappable; it lives INSIDE Focus, not as a standalone Today button). Tap it, pick an energy level (Running low / Somewhere in between / Feeling good). Then tap 'Start with this'; separately try 'Not now'.</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>The tasks it reads appear in the brain-dump box, one per line, editable. Nothing is auto-added to Today, and tapping Add commits them. An 'ocr.captured' event is logged.</t>
+          <t>A calm one-question card with the privacy line ('Your open tasks go to Claude to pick one. Nothing is added or changed.'). Choosing a level shows ONE task from today's list with a short warm line on why it fits (never shaming, never about what's undone). 'Start with this' opens Focus mode on exactly that task; 'Not now' just closes, nothing changed. A failed call shows a calm 'Couldn't find a pick just now.' line and does NOT spend a free pick. The entry hides when AI is off or fewer than 2 tasks are open. Needs the Worker deployed with /energy.</t>
         </is>
       </c>
       <c r="G277" s="7" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H277" s="7" t="inlineStr"/>
@@ -11814,32 +11814,32 @@
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>OCR-04</t>
+          <t>NRG-02</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
         <is>
-          <t>Scan</t>
-        </is>
-      </c>
-      <c r="C278" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C278" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>Gallery fallback reads an existing photo</t>
+          <t>The freemium meter: 15 a month, reminders at 10 and 5, then the paywall</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>Tap Scan, then 'Photos' (device) or 'Choose a photo' (web), and pick a photo of a list, a note, or a whiteboard.</t>
+          <t>As a FREE user, use energy matching repeatedly in one calendar month (seed doubledone.energyUses.v1 to fast-forward). Watch the 10-left and 5-left moments, then the 16th tap. Then as premium, use it well past 15.</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>Same result: the read tasks land in the box for review. Covers a screenshot of a texted list, or a photo taken earlier.</t>
+          <t>Each successful pick spends one of 15 free picks a calendar month (counted locally, like the scrapbook gate). Exactly at 10 left and at 5 left, the result shows one calm line: '10 of your 15 free picks left this month.' (then 5). Past 15, tapping the entry routes to the paywall (which lists 'Energy matching without limits'), never a shaming wall, and no AI call is made ('premium.gate_hit' reason 'energy' logs). The counter resets on the 1st of the month with no carry-over. Premium is unlimited and never sees a counter line.</t>
         </is>
       </c>
       <c r="G278" s="7" t="inlineStr">
@@ -11854,7 +11854,7 @@
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>OCR-05</t>
+          <t>OCR-01</t>
         </is>
       </c>
       <c r="B279" s="7" t="inlineStr">
@@ -11862,24 +11862,24 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="C279" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C279" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>An unreadable photo fails calmly</t>
+          <t>Premium: the Scan button opens the camera</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>Scan a blank, blurry, or list-free image.</t>
+          <t>As premium, tap the + pill and then Scan (camera) beside Speak in the panel.</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>A calm line ('I couldn't read any tasks from that. Try again...'), the camera stays open, never a crash and never a shaming message.</t>
+          <t>The camera screen opens: a live viewfinder with a shutter and a Photos shortcut on a device, or a 'Choose a photo' prompt on web. No paywall.</t>
         </is>
       </c>
       <c r="G279" s="7" t="inlineStr">
@@ -11894,7 +11894,7 @@
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>OCR-06</t>
+          <t>OCR-02</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -11902,29 +11902,29 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="C280" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C280" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Camera denial is never a dead end</t>
+          <t>Free: Scan routes to the upsell, never opens the camera</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>On a device, deny the camera permission when prompted.</t>
+          <t>As a free user, tap the + pill and then Scan in the panel.</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>A calm screen offers 'Allow camera' and 'Choose from photos instead', and the gallery path still reads a list.</t>
+          <t>Routed to the Premium screen calmly (never a wall). A 'premium.gate_hit' with reason 'ocr' is logged. No camera opens.</t>
         </is>
       </c>
       <c r="G280" s="7" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H280" s="7" t="inlineStr"/>
@@ -11934,7 +11934,7 @@
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>OCR-07</t>
+          <t>OCR-03</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
@@ -11942,29 +11942,29 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="C281" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C281" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>AI egress is disclosed at the point of use</t>
+          <t>Photograph a list and the tasks land in the box</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>Open the Scan screen (device or web).</t>
+          <t>As premium on a device, tap Scan, photograph a short printed or handwritten list (fill the frame), wait for 'Reading your list...'.</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>The note 'Your photo is sent to the AI to read your list, then discarded. It is never stored.' is visible. The D1 'ocr' telemetry row holds only the image size and task count, never the image or the titles.</t>
+          <t>The tasks it reads appear in the brain-dump box, one per line, editable. Nothing is auto-added to Today, and tapping Add commits them. An 'ocr.captured' event is logged.</t>
         </is>
       </c>
       <c r="G281" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="H281" s="7" t="inlineStr"/>
@@ -11974,32 +11974,32 @@
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>CHART-01</t>
+          <t>OCR-04</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
         <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C282" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Scan</t>
+        </is>
+      </c>
+      <c r="C282" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>Premium: chart a course toward a goal</t>
+          <t>Gallery fallback reads an existing photo</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>As premium (or dev Premium override on), open Rooms, tap 'Chart a course', type a goal like 'get fit for a 10k', tap 'Suggest steps'.</t>
+          <t>Tap Scan, then 'Photos' (device) or 'Choose a photo' (web), and pick a photo of a list, a note, or a whiteboard.</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>A calm one-line heading plus 3-7 ticked next steps appear, and nothing is added yet. Tapping 'Add N tasks' lands them on Today (the first undated, later ones spread forward), each an ordinary task, and returns to Today. The 'chart.requested' then 'chart.added' events are logged.</t>
+          <t>Same result: the read tasks land in the box for review. Covers a screenshot of a texted list, or a photo taken earlier.</t>
         </is>
       </c>
       <c r="G282" s="7" t="inlineStr">
@@ -12014,32 +12014,32 @@
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>CHART-02</t>
+          <t>OCR-05</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
         <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C283" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Scan</t>
+        </is>
+      </c>
+      <c r="C283" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>Free: charting routes to the upsell, never plans</t>
+          <t>An unreadable photo fails calmly</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>As a free user, open the Menu, tap 'Chart a course', type a goal, pick a timeframe, tap 'Suggest steps', then come back.</t>
+          <t>Scan a blank, blurry, or list-free image.</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>Before the tap the room already says '✦ Suggesting steps is part of Premium.' under the button, once and static. The tap routes to the Premium screen calmly (never a wall), and a 'premium.gate_hit' with reason 'chart' is logged. No plan is generated and nothing is added. Coming back, the goal and the chosen timeframe are still there, including after a purchase: on the phone the Premium panel's way out reads '‹ Chart a course', and on web a checkout round-trip brings the goal back the next time the room opens. Nothing is locked, blurred or priced.</t>
+          <t>A calm line ('I couldn't read any tasks from that. Try again...'), the camera stays open, never a crash and never a shaming message.</t>
         </is>
       </c>
       <c r="G283" s="7" t="inlineStr">
@@ -12054,12 +12054,12 @@
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>CHART-03</t>
+          <t>OCR-06</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
         <is>
-          <t>Chart</t>
+          <t>Scan</t>
         </is>
       </c>
       <c r="C284" s="10" t="inlineStr">
@@ -12069,22 +12069,22 @@
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>Propose-then-accept: nothing auto-adds</t>
+          <t>Camera denial is never a dead end</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>As premium, generate a plan, untick two steps, then tap 'Add'. Separately, generate a plan and back out with 'Not these, start over' or Back.</t>
+          <t>On a device, deny the camera permission when prompted.</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>Only the ticked steps are added as plain tasks, and backing out adds nothing. Today was unchanged before accepting.</t>
+          <t>A calm screen offers 'Allow camera' and 'Choose from photos instead', and the gallery path still reads a list.</t>
         </is>
       </c>
       <c r="G284" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="H284" s="7" t="inlineStr"/>
@@ -12094,32 +12094,32 @@
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>CHART-04</t>
+          <t>OCR-07</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
         <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C285" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Scan</t>
+        </is>
+      </c>
+      <c r="C285" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>A goal that cannot be mapped fails calmly</t>
+          <t>AI egress is disclosed at the point of use</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>Enter an empty goal (the button is disabled), then a nonsensical goal and submit.</t>
+          <t>Open the Scan screen (device or web).</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>The empty case cannot submit. A nonsensical goal shows one calm line ('I couldn't map that out just now'), the goal stays editable, never a crash or a shaming message.</t>
+          <t>The note 'Your photo is sent to the AI to read your list, then discarded. It is never stored.' is visible. The D1 'ocr' telemetry row holds only the image size and task count, never the image or the titles.</t>
         </is>
       </c>
       <c r="G285" s="7" t="inlineStr">
@@ -12134,7 +12134,7 @@
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>CHART-05</t>
+          <t>CHART-01</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -12142,24 +12142,24 @@
           <t>Chart</t>
         </is>
       </c>
-      <c r="C286" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C286" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>A deadline spreads the steps across the timeframe</t>
+          <t>Premium: chart a course toward a goal</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>As premium, type a goal, tap a 'By when?' chip (e.g. 'In 2 months'), then Suggest steps and Add.</t>
+          <t>As premium (or dev Premium override on), open Rooms, tap 'Chart a course', type a goal like 'get fit for a 10k', tap 'Suggest steps'.</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>The steps are paced for that timeframe, and the accepted tasks spread from Today out to the chosen date (not crammed into the next few days). 'No deadline' keeps the gentle one-per-day default.</t>
+          <t>A calm one-line heading plus 3-7 ticked next steps appear, and nothing is added yet. Tapping 'Add N tasks' lands them on Today (the first undated, later ones spread forward), each an ordinary task, and returns to Today. The 'chart.requested' then 'chart.added' events are logged.</t>
         </is>
       </c>
       <c r="G286" s="7" t="inlineStr">
@@ -12174,7 +12174,7 @@
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>CHART-06</t>
+          <t>CHART-02</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -12182,24 +12182,24 @@
           <t>Chart</t>
         </is>
       </c>
-      <c r="C287" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C287" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>The timeframe stays named once the steps arrive</t>
+          <t>Free: charting routes to the upsell, never plans</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>Premium. Type a goal, pick 'In 2 months', Suggest steps. Then 'Not these, start over', pick no deadline, and suggest again.</t>
+          <t>As a free user, open the Menu, tap 'Chart a course', type a goal, pick a timeframe, tap 'Suggest steps', then come back.</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>Once the steps arrive the chips step aside, and one quiet line above the heading keeps the choice named: 'By when · In 2 months' (then 'By when · No deadline'). The AI's heading is in italic serif; every step starts ticked, each with its minutes and a ✕. The button counts only what will be added.</t>
+          <t>Before the tap the room already says '✦ Suggesting steps is part of Premium.' under the button, once and static. The tap routes to the Premium screen calmly (never a wall), and a 'premium.gate_hit' with reason 'chart' is logged. No plan is generated and nothing is added. Coming back, the goal and the chosen timeframe are still there, including after a purchase: on the phone the Premium panel's way out reads '‹ Chart a course', and on web a checkout round-trip brings the goal back the next time the room opens. Nothing is locked, blurred or priced.</t>
         </is>
       </c>
       <c r="G287" s="7" t="inlineStr">
@@ -12214,7 +12214,7 @@
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>CHART-07</t>
+          <t>CHART-03</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -12229,17 +12229,17 @@
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>The steps show where they landed on Today</t>
+          <t>Propose-then-accept: nothing auto-adds</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>Premium. Chart a course, accept the steps with 'Add N tasks'.</t>
+          <t>As premium, generate a plan, untick two steps, then tap 'Add'. Separately, generate a plan and back out with 'Not these, start over' or Back.</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>You land on Today (never back on the spent proposal; back from Today does not return to it). The first step is on Today carrying the soft 'just added' tint, which fades away after a couple of seconds. The rest wait on their days.</t>
+          <t>Only the ticked steps are added as plain tasks, and backing out adds nothing. Today was unchanged before accepting.</t>
         </is>
       </c>
       <c r="G288" s="7" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>CHART-08</t>
+          <t>CHART-04</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -12262,24 +12262,24 @@
           <t>Chart</t>
         </is>
       </c>
-      <c r="C289" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C289" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>The small marks read on paper</t>
+          <t>A goal that cannot be mapped fails calmly</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>In light mode, open Chart a course, get a proposal, and look at an unticked box, a step's minutes, the ✕, the spread note and the note at the foot. Then look at a selected timeframe chip.</t>
+          <t>Enter an empty goal (the button is disabled), then a nonsensical goal and submit.</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>All of them read clearly (they moved from the faintest ink to the soft ink). The instruction under the title is in full ink. A selected chip keeps its tinted fill and border, and its label is ink rather than the accent, which was too faint on the tint. In dark mode the selected label stays the accent.</t>
+          <t>The empty case cannot submit. A nonsensical goal shows one calm line ('I couldn't map that out just now'), the goal stays editable, never a crash or a shaming message.</t>
         </is>
       </c>
       <c r="G289" s="7" t="inlineStr">
@@ -12294,32 +12294,32 @@
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>SEQ-01</t>
+          <t>CHART-05</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
         <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="C290" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C290" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>Premium: Plan my day suggests a calm sequence</t>
+          <t>A deadline spreads the steps across the timeframe</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>As premium with 3+ open one-off tasks on Today, tap 'Plan my day'. Answer the questions it asks first (or skip them).</t>
+          <t>As premium, type a goal, tap a 'By when?' chip (e.g. 'In 2 months'), then Suggest steps and Add.</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>A proposal card lists today's tasks in a suggested order, each with a short calm reason. Nothing reorders until 'Use this order' is tapped, then the list re-sequences in place (no dates change, no task moves to another day). A 'sequence.accepted' event is logged.</t>
+          <t>The steps are paced for that timeframe, and the accepted tasks spread from Today out to the chosen date (not crammed into the next few days). 'No deadline' keeps the gentle one-per-day default.</t>
         </is>
       </c>
       <c r="G290" s="7" t="inlineStr">
@@ -12334,32 +12334,32 @@
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>TOD-27</t>
+          <t>CHART-06</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
         <is>
-          <t>Today</t>
-        </is>
-      </c>
-      <c r="C291" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C291" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Right now: one card near the top, a clock-set slot, the tools open downward, Energy pills</t>
+          <t>The timeframe stays named once the steps arrive</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>Open Today in the MORNING (before 11), around MIDDAY (11-17), and in the EVENING (17+), reading the 'RIGHT NOW' card under Energy each time. Tap the caret at its right. Add and complete tasks and watch whether ANY control moves. Tap an unavailable (faded) tool. Set the Energy pills to High on a 7-task day and re-open the caret; set Low and read the gauge. Reload the app and check the pill. Turn AI off in Settings and re-open the caret. Also check with 0 tasks, in select mode, while typing in the composer, and after closing the day.</t>
+          <t>Premium. Type a goal, pick 'In 2 months', Suggest steps. Then 'Not these, start over', pick no deadline, and suggest again.</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>ONE card sits under the Energy pills, near the top: an overline 'RIGHT NOW' + the tool that suits the HOUR (morning: Plan my day; midday: Focus on one thing; evening: Close the day), plus a caret ('All day tools'). The occupant is set by the CLOCK at open and never changes mid-session; it NEVER shows Lighten today. The caret opens the tools DOWNWARD inside the same card, in the same day order every time: Plan my day, Focus on one thing, Lighten today, Settle, Close the day, the current occupant tagged 'now', Plan my day wearing the honey ✦ when you are not Premium. The list moves down to make room and nothing covers it (no dim, no scrim). NOTHING in the card appears, vanishes or slides as tasks are added or completed: an unavailable tool stays in place at lowered contrast and tapping it explains in one plain line what the TOOL needs ('Plan my day needs two or more tasks.' / 'Lighten today is for a full day.'), never what the person lacks. The Energy pills (Low/Normal/High) sit under a small 'ENERGY' overline with the gauge above, on EVERY open day, including an empty one ('A clear day.'). A fresh day defaults to Normal. High re-scales what 'full' means, Low IS the low-capacity day, and the choice survives a reload but RESETS to Normal next morning. With AI OFF the card holds only the non-AI tools (AI tools are gone, not faded). In select mode the card RESTS (dimmed, does not respond) rather than vanishing, so the list does not jump. While the composer is open the card steps aside with the rest of the heading. On a closed day it is gone.</t>
+          <t>Once the steps arrive the chips step aside, and one quiet line above the heading keeps the choice named: 'By when · In 2 months' (then 'By when · No deadline'). The AI's heading is in italic serif; every step starts ticked, each with its minutes and a ✕. The button counts only what will be added.</t>
         </is>
       </c>
       <c r="G291" s="7" t="inlineStr">
@@ -12374,12 +12374,12 @@
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>TOD-28</t>
+          <t>CHART-07</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Chart</t>
         </is>
       </c>
       <c r="C292" s="10" t="inlineStr">
@@ -12389,17 +12389,17 @@
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>The rested screen mentions the scrapbook once, at the earned moment (the ladder's last rung)</t>
+          <t>The steps show where they landed on Today</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>With AI on, the reminder and widget asks already spent (or reminder on, widget placed), NO scrapbook ever made, and at least 3 finishes this week, close the day and read the rested screen. Tap 'See your Calendar'. Then close a day again on another evening. Separately: repeat with AI off, and repeat with only 1-2 finishes.</t>
+          <t>Premium. Chart a course, accept the steps with 'Add N tasks'.</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>One calm mention appears under the goodnight text: 'You've finished enough this week to make a keepsake of it. It's waiting in your Calendar.' with 'See your Calendar' and 'Not now'. Either answer spends the mention FOREVER (it is the third and LAST rung of the one-ask-at-a-time ladder; reminder and widget always win the evening if pending). 'See your Calendar' opens the Calendar where the scrapbook lives. It never shows with AI off, never with fewer than 3 finishes this week, never to someone who has already made a scrapbook, and never twice.</t>
+          <t>You land on Today (never back on the spent proposal; back from Today does not return to it). The first step is on Today carrying the soft 'just added' tint, which fades away after a couple of seconds. The rest wait on their days.</t>
         </is>
       </c>
       <c r="G292" s="7" t="inlineStr">
@@ -12414,32 +12414,32 @@
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>SEQ-07</t>
+          <t>CHART-08</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
         <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="C293" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C293" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>Plan my day asks about the day BEFORE it sorts</t>
+          <t>The small marks read on paper</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>As premium, tap 'Plan my day'. Read the sheet that opens. Tap an answer, then tap the SAME answer again. Try sorting with all three answered, with only one answered, and with none answered ('Sort today' straight away). Also tap 'Not now'. Separately, as a FREE user, tap 'Plan my day'.</t>
+          <t>In light mode, open Chart a course, get a proposal, and look at an unticked box, a step's minutes, the ✕, the spread note and the note at the foot. Then look at a selected timeframe chip.</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>Before any sorting, a calm sheet asks three OPTIONAL questions: 'How's your energy?' (Running low / Somewhere in between / Feeling good), 'What kind of day?' (Work day / Day off) and 'Where are you?' (Indoors / Out and about / Either), under 'Answer what you like. Skip what you don't.'. A chosen answer tints (accent border, fill and bold accent text); tapping it AGAIN clears it, so a mis-tap is undone the way it was made. Skipping a question sends nothing for it, so it never becomes an assumption, and skipping all three sorts exactly as it always did. The order that comes back reflects what was said (a low-energy day starts small; a day off does not front-load work; 'out and about' clusters the errands), but the app NEVER comments on how you feel. 'Not now' closes with nothing sent and the day untouched. A FREE user hits the Premium screen BEFORE the questions, never after answering them. NEW (the constant frame): when the Energy PILLS at the top of Today were touched today, the sheet's energy question DOES NOT APPEAR at all, and the pill's answer rides the request instead (Low-&gt;low, Normal-&gt;medium, High-&gt;good): energy is read, never asked twice. Only when the pills are untouched does the sheet ask. NOTE: there is deliberately no weather question. A model has no live weather data, and a forecast would need an API plus a location permission; 'Where are you?' is what the sort actually needs.</t>
+          <t>All of them read clearly (they moved from the faintest ink to the soft ink). The instruction under the title is in full ink. A selected chip keeps its tinted fill and border, and its label is ink rather than the accent, which was too faint on the tint. In dark mode the selected label stays the accent.</t>
         </is>
       </c>
       <c r="G293" s="7" t="inlineStr">
@@ -12454,7 +12454,7 @@
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>SEQ-08</t>
+          <t>SEQ-01</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -12469,17 +12469,17 @@
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>The suggested order can be edited before it is used</t>
+          <t>Premium: Plan my day suggests a calm sequence</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>Get a proposal from 'Plan my day'. Use the up and down arrows on a row. Try the up arrow on the FIRST row and the down arrow on the LAST. Remove a row with x. Remove every row. Then tap 'Use this order'.</t>
+          <t>As premium with 3+ open one-off tasks on Today, tap 'Plan my day'. Answer the questions it asks first (or skip them).</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>Each row carries up / down / x. Up and down swap the row with its neighbour immediately, renumbering as they go; the first row's up and the last row's down are visibly dimmed and do nothing (they are disabled, not hidden, so rows never change shape as things move). 'x' takes that task OUT OF THIS PLAN ONLY: the task stays on Today untouched, is not deleted, and is not moved to another day. Removing everything is allowed and says 'Nothing left in the plan. That's allowed.' with the accept button gone (an empty plan cannot be applied). Nothing at all changes on Today until 'Use this order' is tapped; 'Not now' or closing discards every edit. Editing is by buttons, never drag: dragging is unusable with a screen reader and hard with shaky hands.</t>
+          <t>A proposal card lists today's tasks in a suggested order, each with a short calm reason. Nothing reorders until 'Use this order' is tapped, then the list re-sequences in place (no dates change, no task moves to another day). A 'sequence.accepted' event is logged.</t>
         </is>
       </c>
       <c r="G294" s="7" t="inlineStr">
@@ -12494,12 +12494,12 @@
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>SEQ-02</t>
+          <t>TOD-27</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
         <is>
-          <t>Sequence</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="C295" s="8" t="inlineStr">
@@ -12509,17 +12509,17 @@
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>Free: Plan my day routes to the upsell, never reorders</t>
+          <t>Right now: one card near the top, a clock-set slot, the tools open downward, Energy pills</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>As a free user with 2+ tasks on Today, tap 'Plan my day'.</t>
+          <t>Open Today in the MORNING (before 11), around MIDDAY (11-17), and in the EVENING (17+), reading the 'RIGHT NOW' card under Energy each time. Tap the caret at its right. Add and complete tasks and watch whether ANY control moves. Tap an unavailable (faded) tool. Set the Energy pills to High on a 7-task day and re-open the caret; set Low and read the gauge. Reload the app and check the pill. Turn AI off in Settings and re-open the caret. Also check with 0 tasks, in select mode, while typing in the composer, and after closing the day.</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>The Premium screen opens calmly (never a wall), a 'premium.gate_hit' with reason 'sequence' is logged, and the day's order is unchanged.</t>
+          <t>ONE card sits under the Energy pills, near the top: an overline 'RIGHT NOW' + the tool that suits the HOUR (morning: Plan my day; midday: Focus on one thing; evening: Close the day), plus a caret ('All day tools'). The occupant is set by the CLOCK at open and never changes mid-session; it NEVER shows Lighten today. The caret opens the tools DOWNWARD inside the same card, in the same day order every time: Plan my day, Focus on one thing, Lighten today, Settle, Close the day, the current occupant tagged 'now', Plan my day wearing the honey ✦ when you are not Premium. The list moves down to make room and nothing covers it (no dim, no scrim). NOTHING in the card appears, vanishes or slides as tasks are added or completed: an unavailable tool stays in place at lowered contrast and tapping it explains in one plain line what the TOOL needs ('Plan my day needs two or more tasks.' / 'Lighten today is for a full day.'), never what the person lacks. The Energy pills (Low/Normal/High) sit under a small 'ENERGY' overline with the gauge above, on EVERY open day, including an empty one ('A clear day.'). A fresh day defaults to Normal. High re-scales what 'full' means, Low IS the low-capacity day, and the choice survives a reload but RESETS to Normal next morning. With AI OFF the card holds only the non-AI tools (AI tools are gone, not faded). In select mode the card RESTS (dimmed, does not respond) rather than vanishing, so the list does not jump. While the composer is open the card steps aside with the rest of the heading. On a closed day it is gone.</t>
         </is>
       </c>
       <c r="G295" s="7" t="inlineStr">
@@ -12534,12 +12534,12 @@
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>SEQ-03</t>
+          <t>TOD-28</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
         <is>
-          <t>Sequence</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="C296" s="10" t="inlineStr">
@@ -12549,17 +12549,17 @@
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>'Not now' leaves the day untouched</t>
+          <t>The rested screen mentions the scrapbook once, at the earned moment (the ladder's last rung)</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>As premium, open the proposal, then tap 'Not now' or the backdrop.</t>
+          <t>With AI on, the reminder and widget asks already spent (or reminder on, widget placed), NO scrapbook ever made, and at least 3 finishes this week, close the day and read the rested screen. Tap 'See your Calendar'. Then close a day again on another evening. Separately: repeat with AI off, and repeat with only 1-2 finishes.</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>The order is exactly as before, nothing reordered, and no manualOrder is written.</t>
+          <t>One calm mention appears under the goodnight text: 'You've finished enough this week to make a keepsake of it. It's waiting in your Calendar.' with 'See your Calendar' and 'Not now'. Either answer spends the mention FOREVER (it is the third and LAST rung of the one-ask-at-a-time ladder; reminder and widget always win the evening if pending). 'See your Calendar' opens the Calendar where the scrapbook lives. It never shows with AI off, never with fewer than 3 finishes this week, never to someone who has already made a scrapbook, and never twice.</t>
         </is>
       </c>
       <c r="G296" s="7" t="inlineStr">
@@ -12574,7 +12574,7 @@
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>SEQ-04</t>
+          <t>SEQ-07</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -12582,24 +12582,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C297" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C297" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>An accepted order survives a reload (local-first)</t>
+          <t>Plan my day asks about the day BEFORE it sorts</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>As premium, accept an order, then fully reload the app.</t>
+          <t>As premium, tap 'Plan my day'. Read the sheet that opens. Tap an answer, then tap the SAME answer again. Try sorting with all three answered, with only one answered, and with none answered ('Sort today' straight away). Also tap 'Not now'. Separately, as a FREE user, tap 'Plan my day'.</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>Today still shows the accepted order after reload (manualOrder persists on-device). Note: the order does not yet sync across devices, which is a documented follow-up.</t>
+          <t>Before any sorting, a calm sheet asks three OPTIONAL questions: 'How's your energy?' (Running low / Somewhere in between / Feeling good), 'What kind of day?' (Work day / Day off) and 'Where are you?' (Indoors / Out and about / Either), under 'Answer what you like. Skip what you don't.'. A chosen answer tints (accent border, fill and bold accent text); tapping it AGAIN clears it, so a mis-tap is undone the way it was made. Skipping a question sends nothing for it, so it never becomes an assumption, and skipping all three sorts exactly as it always did. The order that comes back reflects what was said (a low-energy day starts small; a day off does not front-load work; 'out and about' clusters the errands), but the app NEVER comments on how you feel. 'Not now' closes with nothing sent and the day untouched. A FREE user hits the Premium screen BEFORE the questions, never after answering them. NEW (the constant frame): when the Energy PILLS at the top of Today were touched today, the sheet's energy question DOES NOT APPEAR at all, and the pill's answer rides the request instead (Low-&gt;low, Normal-&gt;medium, High-&gt;good): energy is read, never asked twice. Only when the pills are untouched does the sheet ask. NOTE: there is deliberately no weather question. A model has no live weather data, and a forecast would need an API plus a location permission; 'Where are you?' is what the sort actually needs.</t>
         </is>
       </c>
       <c r="G297" s="7" t="inlineStr">
@@ -12614,7 +12614,7 @@
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>SEQ-05</t>
+          <t>SEQ-08</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -12622,24 +12622,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C298" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C298" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>A pinned task still wins the very top</t>
+          <t>The suggested order can be edited before it is used</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>As premium, pin a task, then accept a 'Plan my day' sequence that puts a different task first.</t>
+          <t>Get a proposal from 'Plan my day'. Use the up and down arrows on a row. Try the up arrow on the FIRST row and the down arrow on the LAST. Remove a row with x. Remove every row. Then tap 'Use this order'.</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>The pinned task stays at the very top, and the accepted order applies to everything below it.</t>
+          <t>Each row carries up / down / x. Up and down swap the row with its neighbour immediately, renumbering as they go; the first row's up and the last row's down are visibly dimmed and do nothing (they are disabled, not hidden, so rows never change shape as things move). 'x' takes that task OUT OF THIS PLAN ONLY: the task stays on Today untouched, is not deleted, and is not moved to another day. Removing everything is allowed and says 'Nothing left in the plan. That's allowed.' with the accept button gone (an empty plan cannot be applied). Nothing at all changes on Today until 'Use this order' is tapped; 'Not now' or closing discards every edit. Editing is by buttons, never drag: dragging is unusable with a screen reader and hard with shaky hands.</t>
         </is>
       </c>
       <c r="G298" s="7" t="inlineStr">
@@ -12654,7 +12654,7 @@
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>SEQ-06</t>
+          <t>SEQ-02</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
@@ -12662,24 +12662,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C299" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C299" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>Plan my day offers to lighten a heavy day</t>
+          <t>Free: Plan my day routes to the upsell, never reorders</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>As premium on a heavy day (6+ tasks), tap 'Plan my day', accept the order.</t>
+          <t>As a free user with 2+ tasks on Today, tap 'Plan my day'.</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>After the order applies, a 'Still a full day?' card offers to push a few tasks out to later days. Yes runs the re-spread (propose-then-accept), No leaves it ordered. On a calm day the offer never appears.</t>
+          <t>The Premium screen opens calmly (never a wall), a 'premium.gate_hit' with reason 'sequence' is logged, and the day's order is unchanged.</t>
         </is>
       </c>
       <c r="G299" s="7" t="inlineStr">
@@ -12694,32 +12694,32 @@
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>BIG-01</t>
+          <t>SEQ-03</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
         <is>
-          <t>Big task</t>
-        </is>
-      </c>
-      <c r="C300" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Sequence</t>
+        </is>
+      </c>
+      <c r="C300" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>Mark a task big: the tag, and the weight it adds</t>
+          <t>'Not now' leaves the day untouched</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>On Today with a few one-off tasks, tap and hold one, then tap 'Mark as a lot' in the held row's actions. ALSO hold a RECURRING task and confirm 'Mark as a lot' is offered there too (a chore can be a lot; this used to be offered only via the bulk bar).</t>
+          <t>As premium, open the proposal, then tap 'Not now' or the backdrop.</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>The card closes and the task shows a calm accent 'Big' tag beside its title (never red, never a warning), with a brief validating note ('Marked as a lot...'). The weight gauge fills further and reads heavier (one big task floors the bar to at least 'A full day, but doable.'). Free for everyone, no upsell.</t>
+          <t>The order is exactly as before, nothing reordered, and no manualOrder is written.</t>
         </is>
       </c>
       <c r="G300" s="7" t="inlineStr">
@@ -12734,12 +12734,12 @@
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>BIG-02</t>
+          <t>SEQ-04</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
         <is>
-          <t>Big task</t>
+          <t>Sequence</t>
         </is>
       </c>
       <c r="C301" s="10" t="inlineStr">
@@ -12749,17 +12749,17 @@
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>Big is a multi-select toggle</t>
+          <t>An accepted order survives a reload (local-first)</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>Hold a task, 'Select more', tick another, then tap 'Mark as a lot'; then re-select tasks that are all big and tap the action again (it now reads 'Not big').</t>
+          <t>As premium, accept an order, then fully reload the app.</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>The first tap marks every selected task big at once. When all selected tasks are already big the action reads 'Not big' and clears the mark off all of them. A mixed selection marks all big (the additive default).</t>
+          <t>Today still shows the accepted order after reload (manualOrder persists on-device). Note: the order does not yet sync across devices, which is a documented follow-up.</t>
         </is>
       </c>
       <c r="G301" s="7" t="inlineStr">
@@ -12774,32 +12774,32 @@
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
         <is>
-          <t>BIG-03</t>
+          <t>SEQ-05</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
         <is>
-          <t>Big task</t>
-        </is>
-      </c>
-      <c r="C302" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Sequence</t>
+        </is>
+      </c>
+      <c r="C302" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>A lone big task lifts the bar but is not a re-spread problem</t>
+          <t>A pinned task still wins the very top</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>Have just one or two tasks on Today, one marked big.</t>
+          <t>As premium, pin a task, then accept a 'Plan my day' sequence that puts a different task first.</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>The weight gauge reads at least 'A full day, but doable.' (the big task is felt), but 'Today's looking full' and 'Lighten today' do NOT appear for a lone big task (re-spreading cannot dissolve one big rock; Break it down is the tool). A big task plus a real pile (weighted load 6+) does surface Lighten today.</t>
+          <t>The pinned task stays at the very top, and the accepted order applies to everything below it.</t>
         </is>
       </c>
       <c r="G302" s="7" t="inlineStr">
@@ -12814,12 +12814,12 @@
     <row r="303">
       <c r="A303" s="6" t="inlineStr">
         <is>
-          <t>BIG-04</t>
+          <t>SEQ-06</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
         <is>
-          <t>Big task</t>
+          <t>Sequence</t>
         </is>
       </c>
       <c r="C303" s="10" t="inlineStr">
@@ -12829,17 +12829,17 @@
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>Finishing a big task is a big-win in the Calendar</t>
+          <t>Plan my day offers to lighten a heavy day</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>Mark a task big, complete it, then open the Calendar to its day.</t>
+          <t>As premium on a heavy day (6+ tasks), tap 'Plan my day', accept the order.</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>The completed task carries the warmer 'a big one' treatment on its day, the same payoff a long-dreaded or chunky task earns. The big flag never adds disappointment if the task is left unfinished.</t>
+          <t>After the order applies, a 'Still a full day?' card offers to push a few tasks out to later days. Yes runs the re-spread (propose-then-accept), No leaves it ordered. On a calm day the offer never appears.</t>
         </is>
       </c>
       <c r="G303" s="7" t="inlineStr">
@@ -12854,7 +12854,7 @@
     <row r="304">
       <c r="A304" s="6" t="inlineStr">
         <is>
-          <t>BIG-05</t>
+          <t>BIG-01</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -12862,24 +12862,24 @@
           <t>Big task</t>
         </is>
       </c>
-      <c r="C304" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C304" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>Big syncs across devices (and old marks survive the upgrade)</t>
+          <t>Mark a task big: the tag, and the weight it adds</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>Signed in on two devices (e.g. web + Android). Mark a task big on device 1, wait for or trigger a sync, then open device 2. Then unmark it on device 2 and check device 1. Prerequisite: an account with the same task on both.</t>
+          <t>On Today with a few one-off tasks, tap and hold one, then tap 'Mark as a lot' in the held row's actions. ALSO hold a RECURRING task and confirm 'Mark as a lot' is offered there too (a chore can be a lot; this used to be offered only via the bulk bar).</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>The Big tag appears on device 2 (with its weight-gauge effect), and the unmark travels back: no resurrection, the newest change wins. Marks made BEFORE this build (when big was device-only) are seeded up to the account on that device's first sync rather than erased. One known transition quirk: a device still on a PRE-sync build can re-surface a cleared big once when it upgrades; clearing it again sticks everywhere. Manual order (Plan my order) remains per-device by design.</t>
+          <t>The card closes and the task shows a calm accent 'Big' tag beside its title (never red, never a warning), with a brief validating note ('Marked as a lot...'). The weight gauge fills further and reads heavier (one big task floors the bar to at least 'A full day, but doable.'). Free for everyone, no upsell.</t>
         </is>
       </c>
       <c r="G304" s="7" t="inlineStr">
@@ -12894,37 +12894,37 @@
     <row r="305">
       <c r="A305" s="6" t="inlineStr">
         <is>
-          <t>NAV-01</t>
+          <t>BIG-02</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
         <is>
-          <t>Rooms</t>
-        </is>
-      </c>
-      <c r="C305" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Big task</t>
+        </is>
+      </c>
+      <c r="C305" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>Rooms sheet caps its width on wide web</t>
+          <t>Big is a multi-select toggle</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>On a wide desktop browser, open Rooms (the header pill).</t>
+          <t>Hold a task, 'Select more', tick another, then tap 'Mark as a lot'; then re-select tasks that are all big and tap the action again (it now reads 'Not big').</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>The sheet is a centred column (about 560px, matching the page content), not full-bleed, so the 'Premium' gradient pill on 'Chart a course' sits beside its label rather than at the far screen edge. On a phone the sheet stays full-width with the pill at the row's edge.</t>
+          <t>The first tap marks every selected task big at once. When all selected tasks are already big the action reads 'Not big' and clears the mark off all of them. A mixed selection marks all big (the additive default).</t>
         </is>
       </c>
       <c r="G305" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H305" s="7" t="inlineStr"/>
@@ -12934,32 +12934,32 @@
     <row r="306">
       <c r="A306" s="6" t="inlineStr">
         <is>
-          <t>OUR-01</t>
+          <t>BIG-03</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C306" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Big task</t>
+        </is>
+      </c>
+      <c r="C306" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>The door only exists for an allowed account</t>
+          <t>A lone big task lifts the bar but is not a re-spread problem</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>Sign in as an account that is NOT on the ours_allowlist and open Settings. Then sign in as one that is.</t>
+          <t>Have just one or two tasks on Today, one marked big.</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>The 'Ours' row is absent for the first account and present for the second. Nobody is ever offered a door that answers 'shared lists aren't open yet'.</t>
+          <t>The weight gauge reads at least 'A full day, but doable.' (the big task is felt), but 'Today's looking full' and 'Lighten today' do NOT appear for a lone big task (re-spreading cannot dissolve one big rock; Break it down is the tool). A big task plus a real pile (weighted load 6+) does surface Lighten today.</t>
         </is>
       </c>
       <c r="G306" s="7" t="inlineStr">
@@ -12974,32 +12974,32 @@
     <row r="307">
       <c r="A307" s="6" t="inlineStr">
         <is>
-          <t>OUR-02</t>
+          <t>BIG-04</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C307" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Big task</t>
+        </is>
+      </c>
+      <c r="C307" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>Signed out: the explanation, never a nag</t>
+          <t>Finishing a big task is a big-win in the Calendar</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>Sign out, then open /ours directly.</t>
+          <t>Mark a task big, complete it, then open the Calendar to its day.</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>A calm one-screen explanation of why sharing needs an account, and a way to sign in. No pressure, no count of what you are missing.</t>
+          <t>The completed task carries the warmer 'a big one' treatment on its day, the same payoff a long-dreaded or chunky task earns. The big flag never adds disappointment if the task is left unfinished.</t>
         </is>
       </c>
       <c r="G307" s="7" t="inlineStr">
@@ -13014,32 +13014,32 @@
     <row r="308">
       <c r="A308" s="6" t="inlineStr">
         <is>
-          <t>OUR-03</t>
+          <t>BIG-05</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C308" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Big task</t>
+        </is>
+      </c>
+      <c r="C308" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>Name the list and mint a code</t>
+          <t>Big syncs across devices (and old marks survive the upgrade)</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>Ours &gt; Start a shared list. Pick 'The house'. Type your own name. Type the OTHER account's email exactly. Get a code.</t>
+          <t>Signed in on two devices (e.g. web + Android). Mark a task big on device 1, wait for or trigger a sync, then open device 2. Then unmark it on device 2 and check device 1. Prerequisite: an account with the same task on both.</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>A six-character code appears grouped as XXX-XXX, containing no 0, 1, I, L or O. The screen says it works once, for the next day, and only for the address you gave.</t>
+          <t>The Big tag appears on device 2 (with its weight-gauge effect), and the unmark travels back: no resurrection, the newest change wins. Marks made BEFORE this build (when big was device-only) are seeded up to the account on that device's first sync rather than erased. One known transition quirk: a device still on a PRE-sync build can re-surface a cleared big once when it upgrades; clearing it again sticks everywhere. Manual order (Plan my order) remains per-device by design.</t>
         </is>
       </c>
       <c r="G308" s="7" t="inlineStr">
@@ -13054,37 +13054,37 @@
     <row r="309">
       <c r="A309" s="6" t="inlineStr">
         <is>
-          <t>OUR-04</t>
+          <t>NAV-01</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C309" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="C309" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>Join from the second account</t>
+          <t>Rooms sheet caps its width on wide web</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>On the second account, Ours &gt; Join with a code. Type the code (try it lower-case and with the dash). Type your own name. Join.</t>
+          <t>On a wide desktop browser, open Rooms (the header pill).</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>You land on the shared list showing the FIRST person's chosen name and the list's name ('The house'). No email address is shown anywhere, to either person.</t>
+          <t>The sheet is a centred column (about 560px, matching the page content), not full-bleed, so the 'Premium' gradient pill on 'Chart a course' sits beside its label rather than at the far screen edge. On a phone the sheet stays full-width with the pill at the row's edge.</t>
         </is>
       </c>
       <c r="G309" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H309" s="7" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
     <row r="310">
       <c r="A310" s="6" t="inlineStr">
         <is>
-          <t>OUR-05</t>
+          <t>OUR-01</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -13109,17 +13109,17 @@
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>The first person sees the arrival without refreshing</t>
+          <t>The door only exists for an allowed account</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>Leave the first account sitting on the Ours screen while the second joins.</t>
+          <t>Sign in as an account that is NOT on the ours_allowlist and open Settings. Then sign in as one that is.</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>Within about ten seconds it announces that they joined, with a way out for someone who meant a different person. It never says how long they took.</t>
+          <t>The 'Ours' row is absent for the first account and present for the second. Nobody is ever offered a door that answers 'shared lists aren't open yet'.</t>
         </is>
       </c>
       <c r="G310" s="7" t="inlineStr">
@@ -13134,7 +13134,7 @@
     <row r="311">
       <c r="A311" s="6" t="inlineStr">
         <is>
-          <t>OUR-06</t>
+          <t>OUR-02</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -13142,24 +13142,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C311" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C311" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>A wrong code says one calm thing</t>
+          <t>Signed out: the explanation, never a nag</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>Try a made-up code, then a code meant for a different address, then the same code twice.</t>
+          <t>Sign out, then open /ours directly.</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>Every one gives the SAME single line ('That code isn't valid.'). Nothing hints at which reason, so a guesser learns nothing. Repeated wrong tries eventually ask you to have a break.</t>
+          <t>A calm one-screen explanation of why sharing needs an account, and a way to sign in. No pressure, no count of what you are missing.</t>
         </is>
       </c>
       <c r="G311" s="7" t="inlineStr">
@@ -13174,7 +13174,7 @@
     <row r="312">
       <c r="A312" s="6" t="inlineStr">
         <is>
-          <t>OUR-07</t>
+          <t>OUR-03</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -13182,24 +13182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C312" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C312" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>Mistyped invitee address is recoverable</t>
+          <t>Name the list and mint a code</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>Mint a code with a deliberately wrong email, then use 'Wrong address? Start again' and mint a fresh one with the right address.</t>
+          <t>Ours &gt; Start a shared list. Pick 'The house'. Type your own name. Type the OTHER account's email exactly. Get a code.</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>The new code works and the old one does not. Nothing had to be deleted to recover, and no address is ever displayed back to you.</t>
+          <t>A six-character code appears grouped as XXX-XXX, containing no 0, 1, I, L or O. The screen says it works once, for the next day, and only for the address you gave.</t>
         </is>
       </c>
       <c r="G312" s="7" t="inlineStr">
@@ -13214,7 +13214,7 @@
     <row r="313">
       <c r="A313" s="6" t="inlineStr">
         <is>
-          <t>OUR-08</t>
+          <t>OUR-04</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -13222,24 +13222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C313" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C313" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>Rename the list, and both sides see it</t>
+          <t>Join from the second account</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>On the shared list, tap the list's name, type a new one, and confirm. Reopen Ours on the other account.</t>
+          <t>On the second account, Ours &gt; Join with a code. Type the code (try it lower-case and with the dash). Type your own name. Join.</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>Both people see the new name. An emptied name falls back to the app's own word, in each person's own language.</t>
+          <t>You land on the shared list showing the FIRST person's chosen name and the list's name ('The house'). No email address is shown anywhere, to either person.</t>
         </is>
       </c>
       <c r="G313" s="7" t="inlineStr">
@@ -13254,7 +13254,7 @@
     <row r="314">
       <c r="A314" s="6" t="inlineStr">
         <is>
-          <t>OUR-09</t>
+          <t>OUR-05</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -13269,17 +13269,17 @@
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>Leaving freezes and takes nothing</t>
+          <t>The first person sees the arrival without refreshing</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>On one account, Leave this list. Then open Ours on BOTH accounts.</t>
+          <t>Leave the first account sitting on the Ours screen while the second joins.</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>Both see 'This list is closed' and can still read everything. Nothing was deleted from either side. Neither person is told off, and neither is told what the other did.</t>
+          <t>Within about ten seconds it announces that they joined, with a way out for someone who meant a different person. It never says how long they took.</t>
         </is>
       </c>
       <c r="G314" s="7" t="inlineStr">
@@ -13294,7 +13294,7 @@
     <row r="315">
       <c r="A315" s="6" t="inlineStr">
         <is>
-          <t>OUR-10</t>
+          <t>OUR-06</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -13309,17 +13309,17 @@
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>Remove a closed list from your side only</t>
+          <t>A wrong code says one calm thing</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Remove this list'. Then check the other account.</t>
+          <t>Try a made-up code, then a code meant for a different address, then the same code twice.</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>It disappears for you. The other person still has their copy and is not notified.</t>
+          <t>Every one gives the SAME single line ('That code isn't valid.'). Nothing hints at which reason, so a guesser learns nothing. Repeated wrong tries eventually ask you to have a break.</t>
         </is>
       </c>
       <c r="G315" s="7" t="inlineStr">
@@ -13334,7 +13334,7 @@
     <row r="316">
       <c r="A316" s="6" t="inlineStr">
         <is>
-          <t>OUR-11</t>
+          <t>OUR-07</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -13342,24 +13342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C316" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C316" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>Nothing anywhere attributes a task to a person</t>
+          <t>Mistyped invitee address is recoverable</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>With a shared list live, look at Ours, Today, the Lookback and Settings on both accounts.</t>
+          <t>Mint a code with a deliberately wrong email, then use 'Wrong address? Start again' and mint a fresh one with the right address.</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>No initials, no 'done by', no counts of who did what, no progress bar across two people, no activity feed. The data to build one does not exist.</t>
+          <t>The new code works and the old one does not. Nothing had to be deleted to recover, and no address is ever displayed back to you.</t>
         </is>
       </c>
       <c r="G316" s="7" t="inlineStr">
@@ -13374,7 +13374,7 @@
     <row r="317">
       <c r="A317" s="6" t="inlineStr">
         <is>
-          <t>OUR-13</t>
+          <t>OUR-08</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -13382,24 +13382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C317" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C317" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>The code stays on screen from the moment it is minted</t>
+          <t>Rename the list, and both sides see it</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>On a throttled connection (devtools, slow 3G), fill the create form and tap the code button.</t>
+          <t>On the shared list, tap the list's name, type a new one, and confirm. Reopen Ours on the other account.</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>The six characters appear as soon as the button stops spinning and are NEVER replaced by the intro screen. The server returns that code exactly once, so a flash back to 'Start a shared list' loses it for good.</t>
+          <t>Both people see the new name. An emptied name falls back to the app's own word, in each person's own language.</t>
         </is>
       </c>
       <c r="G317" s="7" t="inlineStr">
@@ -13414,7 +13414,7 @@
     <row r="318">
       <c r="A318" s="6" t="inlineStr">
         <is>
-          <t>OUR-14</t>
+          <t>OUR-09</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -13429,17 +13429,17 @@
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>'Get a new code' reaches the form and mints a different code</t>
+          <t>Leaving freezes and takes nothing</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>From the waiting screen, tap the get-a-new-code action. Change the email. Submit.</t>
+          <t>On one account, Leave this list. Then open Ours on BOTH accounts.</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>The create form appears with your name and list name already filled. Submitting shows a DIFFERENT six characters, and the old one no longer works. Your chosen name is unchanged afterwards.</t>
+          <t>Both see 'This list is closed' and can still read everything. Nothing was deleted from either side. Neither person is told off, and neither is told what the other did.</t>
         </is>
       </c>
       <c r="G318" s="7" t="inlineStr">
@@ -13454,7 +13454,7 @@
     <row r="319">
       <c r="A319" s="6" t="inlineStr">
         <is>
-          <t>OUR-120</t>
+          <t>OUR-10</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -13462,24 +13462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C319" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C319" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>Waiting-with-no-code is reachable, says so, and the re-mint is a real button</t>
+          <t>Remove a closed list from your side only</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>Mint a code, leave Ours entirely (back to Today), then come back via the MENU's Ours row before anyone joins.</t>
+          <t>On a closed list, tap 'Remove this list'. Then check the other account.</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>The Menu lands on the shared LIST (usable solo while waiting), and the list's header line reads 'Waiting for your person - Get a new code' where 'Kept with {name}' will later sit; tapping it opens the pairing screen (both Melroy's C6 check and the field report hit this as a dead end before 2026-09-20). That screen is titled 'Waiting for your person', NOT 'Read this to your person' over an empty space (the code renders exactly once; the server keeps only a hash, so it can never be re-shown), and 'Get a new code' is a full primary button there, not a quiet text link. While the code IS still on screen, the old title and quiet link stay as they were.</t>
+          <t>It disappears for you. The other person still has their copy and is not notified.</t>
         </is>
       </c>
       <c r="G319" s="7" t="inlineStr">
@@ -13494,7 +13494,7 @@
     <row r="320">
       <c r="A320" s="6" t="inlineStr">
         <is>
-          <t>OUR-121</t>
+          <t>OUR-11</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -13509,17 +13509,17 @@
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>Whose email, and which code goes where</t>
+          <t>Nothing anywhere attributes a task to a person</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>Signed out: read the Menu's Ours line, open Ours, read the signed-out screen, tap Sign in and read the field. Then, on the sign-in code step, paste an Ours-style code (letters in it). Separately, signed in, open Ours 'I have a code' and type a 6-digit emailed sign-in code.</t>
+          <t>With a shared list live, look at Ours, Today, the Lookback and Settings on both accounts.</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>The Menu's Ours line reads 'A list kept with one person. Sign in first.' (the old 'Needs your email, no password' invited typing the PARTNER'S email; a real user did exactly that on 2026-09-13 and it became their account). The Ours signed-out screen opens with the plain fact 'You're not signed in on this phone.' The sign-in email field is labelled 'Your own email', and the subtitle says sharing happens later, in Ours, with a code, never by typing the partner's email here. Letters in the 6-digit code field draw the calm hint that it will be an Ours invite code (a hint, never an auto-redirect or a cleared field). Six bare digits failing in the Ours join field add one line naming the emailed sign-in code as the likely mix-up, alongside the unchanged honest failure.</t>
+          <t>No initials, no 'done by', no counts of who did what, no progress bar across two people, no activity feed. The data to build one does not exist.</t>
         </is>
       </c>
       <c r="G320" s="7" t="inlineStr">
@@ -13534,7 +13534,7 @@
     <row r="321">
       <c r="A321" s="6" t="inlineStr">
         <is>
-          <t>OUR-15</t>
+          <t>OUR-13</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -13549,17 +13549,17 @@
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Leave a list, then start a new one WITHOUT deleting the old</t>
+          <t>The code stays on screen from the moment it is minted</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>Leave a shared list. On the closed screen, start a new shared list with someone else.</t>
+          <t>On a throttled connection (devtools, slow 3G), fill the create form and tap the code button.</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>Starting a new list is offered on the closed screen itself and works. The old list is NOT deleted and is still readable. At no point is destroying it the only way forward.</t>
+          <t>The six characters appear as soon as the button stops spinning and are NEVER replaced by the intro screen. The server returns that code exactly once, so a flash back to 'Start a shared list' loses it for good.</t>
         </is>
       </c>
       <c r="G321" s="7" t="inlineStr">
@@ -13574,7 +13574,7 @@
     <row r="322">
       <c r="A322" s="6" t="inlineStr">
         <is>
-          <t>OUR-16</t>
+          <t>OUR-14</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -13589,17 +13589,17 @@
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>A failed read never offers to start a list you already have</t>
+          <t>'Get a new code' reaches the form and mints a different code</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, turn the network off and open Ours.</t>
+          <t>From the waiting screen, tap the get-a-new-code action. Change the email. Submit.</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>A calm connection line. The screen never says you have no shared list and never offers to start one. Turning the network back on recovers without a restart.</t>
+          <t>The create form appears with your name and list name already filled. Submitting shows a DIFFERENT six characters, and the old one no longer works. Your chosen name is unchanged afterwards.</t>
         </is>
       </c>
       <c r="G322" s="7" t="inlineStr">
@@ -13614,7 +13614,7 @@
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
         <is>
-          <t>OUR-17</t>
+          <t>OUR-120</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -13622,24 +13622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C323" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C323" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
-          <t>A list nobody joined can be left</t>
+          <t>Waiting-with-no-code is reachable, says so, and the re-mint is a real button</t>
         </is>
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>Create a list, get a code, give it to nobody. Return to Ours.</t>
+          <t>Mint a code, leave Ours entirely (back to Today), then come back via the MENU's Ours row before anyone joins.</t>
         </is>
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>There is a way out on the waiting screen, and its wording does not claim it closes for two people. After leaving, you can start or join a list again.</t>
+          <t>The Menu lands on the shared LIST (usable solo while waiting), and the list's header line reads 'Waiting for your person - Get a new code' where 'Kept with {name}' will later sit; tapping it opens the pairing screen (both Melroy's C6 check and the field report hit this as a dead end before 2026-09-20). That screen is titled 'Waiting for your person', NOT 'Read this to your person' over an empty space (the code renders exactly once; the server keeps only a hash, so it can never be re-shown), and 'Get a new code' is a full primary button there, not a quiet text link. While the code IS still on screen, the old title and quiet link stay as they were.</t>
         </is>
       </c>
       <c r="G323" s="7" t="inlineStr">
@@ -13654,7 +13654,7 @@
     <row r="324">
       <c r="A324" s="6" t="inlineStr">
         <is>
-          <t>OUR-18</t>
+          <t>OUR-121</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -13662,24 +13662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C324" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C324" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>The arrival announces once and stays announced</t>
+          <t>Whose email, and which code goes where</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>Sit on the waiting screen while the other account joins. Background the app and return.</t>
+          <t>Signed out: read the Menu's Ours line, open Ours, read the signed-out screen, tap Sign in and read the field. Then, on the sign-in code step, paste an Ours-style code (letters in it). Separately, signed in, open Ours 'I have a code' and type a 6-digit emailed sign-in code.</t>
         </is>
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>The name appears once and does not flicker back to waiting and re-announce. The way out beside it ('that wasn't who I meant') never appears on a list you did not just gain a person on.</t>
+          <t>The Menu's Ours line reads 'A list kept with one person. Sign in first.' (the old 'Needs your email, no password' invited typing the PARTNER'S email; a real user did exactly that on 2026-09-13 and it became their account). The Ours signed-out screen opens with the plain fact 'You're not signed in on this phone.' The sign-in email field is labelled 'Your own email', and the subtitle says sharing happens later, in Ours, with a code, never by typing the partner's email here. Letters in the 6-digit code field draw the calm hint that it will be an Ours invite code (a hint, never an auto-redirect or a cleared field). Six bare digits failing in the Ours join field add one line naming the emailed sign-in code as the likely mix-up, alongside the unchanged honest failure.</t>
         </is>
       </c>
       <c r="G324" s="7" t="inlineStr">
@@ -13694,7 +13694,7 @@
     <row r="325">
       <c r="A325" s="6" t="inlineStr">
         <is>
-          <t>OUR-19</t>
+          <t>OUR-15</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -13702,24 +13702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C325" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C325" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>A repeat the app cannot read is SHOWN, never hidden</t>
+          <t>Leave a list, then start a new one WITHOUT deleting the old</t>
         </is>
       </c>
       <c r="E325" s="9" t="inlineStr">
         <is>
-          <t>Requires two app versions. On the newer one, set a shared task to a cadence the older build does not have. Open the list on the older build.</t>
+          <t>Leave a shared list. On the closed screen, start a new shared list with someone else.</t>
         </is>
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>The task is visible on both, with whatever cadence line the newer app left. It is never silently absent from one person's list, and the older app does not erase the schedule when it syncs.</t>
+          <t>Starting a new list is offered on the closed screen itself and works. The old list is NOT deleted and is still readable. At no point is destroying it the only way forward.</t>
         </is>
       </c>
       <c r="G325" s="7" t="inlineStr">
@@ -13734,7 +13734,7 @@
     <row r="326">
       <c r="A326" s="6" t="inlineStr">
         <is>
-          <t>OUR-20</t>
+          <t>OUR-16</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -13749,17 +13749,17 @@
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
-          <t>The room opens from Today's heading and from the Menu</t>
+          <t>A failed read never offers to start a list you already have</t>
         </is>
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, tap the list's name beside 'Today' in Today's heading. Then go back and reach it through Menu › Ours.</t>
+          <t>With a live shared list, turn the network off and open Ours.</t>
         </is>
       </c>
       <c r="F326" s="9" t="inlineStr">
         <is>
-          <t>Both land on the shared list itself, not the pairing screen, with a fade (a tab changing), not a sideways slide. The room's heading reads 'Today' and the list's name side by side, the name underlined as the current one, then the line 'Shared. Anything with a day reaches both your Todays on that day.' The date and the same Menu pill sit above it. 'Kept with {their name} ›' still goes to the pairing/management screen. Tapping 'Today' in the room's heading goes back to Today.</t>
+          <t>A calm connection line. The screen never says you have no shared list and never offers to start one. Turning the network back on recovers without a restart.</t>
         </is>
       </c>
       <c r="G326" s="7" t="inlineStr">
@@ -13774,7 +13774,7 @@
     <row r="327">
       <c r="A327" s="6" t="inlineStr">
         <is>
-          <t>OUR-21</t>
+          <t>OUR-17</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -13782,24 +13782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C327" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C327" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>Add, tick and UN-tick on the shared list</t>
+          <t>A list nobody joined can be left</t>
         </is>
       </c>
       <c r="E327" s="9" t="inlineStr">
         <is>
-          <t>Add a task in the room. Tick it. Un-tick it. Watch the other account (reload or wait ~15s).</t>
+          <t>Create a list, get a code, give it to nobody. Return to Ours.</t>
         </is>
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>Every step appears on both. Un-ticking works as easily as ticking, on both sides. No affirmation or celebration fires on Ours.</t>
+          <t>There is a way out on the waiting screen, and its wording does not claim it closes for two people. After leaving, you can start or join a list again.</t>
         </is>
       </c>
       <c r="G327" s="7" t="inlineStr">
@@ -13814,7 +13814,7 @@
     <row r="328">
       <c r="A328" s="6" t="inlineStr">
         <is>
-          <t>OUR-22</t>
+          <t>OUR-18</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -13822,24 +13822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C328" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C328" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>Un-tick a one-off the DAY AFTER it was ticked</t>
+          <t>The arrival announces once and stays announced</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>Tick a shared one-off. Change the device date to tomorrow (or wait a day), reopen the room, tap it again.</t>
+          <t>Sit on the waiting screen while the other account joins. Background the app and return.</t>
         </is>
       </c>
       <c r="F328" s="9" t="inlineStr">
         <is>
-          <t>It un-ticks. (The pre-fix build could never un-tick it again, on any device, forever.)</t>
+          <t>The name appears once and does not flicker back to waiting and re-announce. The way out beside it ('that wasn't who I meant') never appears on a list you did not just gain a person on.</t>
         </is>
       </c>
       <c r="G328" s="7" t="inlineStr">
@@ -13854,7 +13854,7 @@
     <row r="329">
       <c r="A329" s="6" t="inlineStr">
         <is>
-          <t>OUR-23</t>
+          <t>OUR-19</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -13862,24 +13862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C329" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C329" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>Bring to my Today makes a COPY, and marks only yours</t>
+          <t>A repeat the app cannot read is SHOWN, never hidden</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>Hold a shared row, tap 'Bring to my Today'. Look at your Today, then at the shared list on BOTH accounts.</t>
+          <t>Requires two app versions. On the newer one, set a shared task to a cadence the older build does not have. Open the list on the older build.</t>
         </is>
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>Your Today shows the task with a faint '· Ours'. The shared row is completely unchanged on both sides, with no marker of any kind. The held card now reads 'Already on your Today' and cannot make a second copy.</t>
+          <t>The task is visible on both, with whatever cadence line the newer app left. It is never silently absent from one person's list, and the older app does not erase the schedule when it syncs.</t>
         </is>
       </c>
       <c r="G329" s="7" t="inlineStr">
@@ -13894,7 +13894,7 @@
     <row r="330">
       <c r="A330" s="6" t="inlineStr">
         <is>
-          <t>OUR-24</t>
+          <t>OUR-20</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -13909,17 +13909,17 @@
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>Your tick on the copy closes both</t>
+          <t>The room opens from Today's heading and from the Menu</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>Tick the brought copy on your Today. Check the shared list on the other account.</t>
+          <t>With a live shared list, tap the list's name beside 'Today' in Today's heading. Then go back and reach it through Menu › Ours.</t>
         </is>
       </c>
       <c r="F330" s="9" t="inlineStr">
         <is>
-          <t>The shared row is done. It enters YOUR Lookback. Nothing on the other side says who did it.</t>
+          <t>Both land on the shared list itself, not the pairing screen, with a fade (a tab changing), not a sideways slide. The room's heading reads 'Today' and the list's name side by side, the name underlined as the current one, then the line 'Shared. Anything with a day reaches both your Todays on that day.' The date and the same Menu pill sit above it. 'Kept with {their name} ›' still goes to the pairing/management screen. Tapping 'Today' in the room's heading goes back to Today.</t>
         </is>
       </c>
       <c r="G330" s="7" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="331">
       <c r="A331" s="6" t="inlineStr">
         <is>
-          <t>OUR-25</t>
+          <t>OUR-21</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -13949,17 +13949,17 @@
       </c>
       <c r="D331" s="9" t="inlineStr">
         <is>
-          <t>Ticking a brought copy on a device that has NEVER opened the room</t>
+          <t>Add, tick and UN-tick on the shared list</t>
         </is>
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>Bring a task over on phone A. Sign in on a second device (or clear its local data) and go straight to Today WITHOUT opening Ours. Tick the copy there.</t>
+          <t>Add a task in the room. Tick it. Un-tick it. Watch the other account (reload or wait ~15s).</t>
         </is>
       </c>
       <c r="F331" s="9" t="inlineStr">
         <is>
-          <t>The shared row closes. (The pre-fix build silently discarded the tick with no error.)</t>
+          <t>Every step appears on both. Un-ticking works as easily as ticking, on both sides. No affirmation or celebration fires on Ours.</t>
         </is>
       </c>
       <c r="G331" s="7" t="inlineStr">
@@ -13974,7 +13974,7 @@
     <row r="332">
       <c r="A332" s="6" t="inlineStr">
         <is>
-          <t>OUR-26</t>
+          <t>OUR-22</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -13989,17 +13989,17 @@
       </c>
       <c r="D332" s="9" t="inlineStr">
         <is>
-          <t>Their tick leaves a rest-note, never a strike-through</t>
+          <t>Un-tick a one-off the DAY AFTER it was ticked</t>
         </is>
       </c>
       <c r="E332" s="9" t="inlineStr">
         <is>
-          <t>Bring a task over. On the OTHER account, tick the shared row. Return to your Today.</t>
+          <t>Tick a shared one-off. Change the device date to tomorrow (or wait a day), reopen the room, tap it again.</t>
         </is>
       </c>
       <c r="F332" s="9" t="inlineStr">
         <is>
-          <t>Your copy is gone from the day, replaced by a dashed sage line: 'Handled on Ours. It's off your day.' It is NOT struck through and does NOT appear in your Lookback. Leaving Today and coming back clears the note.</t>
+          <t>It un-ticks. (The pre-fix build could never un-tick it again, on any device, forever.)</t>
         </is>
       </c>
       <c r="G332" s="7" t="inlineStr">
@@ -14014,7 +14014,7 @@
     <row r="333">
       <c r="A333" s="6" t="inlineStr">
         <is>
-          <t>OUR-27</t>
+          <t>OUR-23</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -14022,24 +14022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C333" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C333" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D333" s="9" t="inlineStr">
         <is>
-          <t>Share to Ours warns about the length BEFORE it copies</t>
+          <t>Bring to my Today makes a COPY, and marks only yours</t>
         </is>
       </c>
       <c r="E333" s="9" t="inlineStr">
         <is>
-          <t>Hold one of your own Today tasks with a very long title (500+ chars), open More, tap 'Share to Ours'.</t>
+          <t>Hold a shared row, tap 'Bring to my Today'. Look at your Today, then at the shared list on BOTH accounts.</t>
         </is>
       </c>
       <c r="F333" s="9" t="inlineStr">
         <is>
-          <t>A line says Ours keeps titles shorter and this one will be trimmed, BEFORE the copy is made. The copy appears on the shared list. 'Share to Ours' is absent entirely when there is no live list.</t>
+          <t>Your Today shows the task with a faint '· Ours'. The shared row is completely unchanged on both sides, with no marker of any kind. The held card now reads 'Already on your Today' and cannot make a second copy.</t>
         </is>
       </c>
       <c r="G333" s="7" t="inlineStr">
@@ -14054,7 +14054,7 @@
     <row r="334">
       <c r="A334" s="6" t="inlineStr">
         <is>
-          <t>OUR-28</t>
+          <t>OUR-24</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -14069,17 +14069,17 @@
       </c>
       <c r="D334" s="9" t="inlineStr">
         <is>
-          <t>A repeat set on Ours uses the SAME cadence sheet as home</t>
+          <t>Your tick on the copy closes both</t>
         </is>
       </c>
       <c r="E334" s="9" t="inlineStr">
         <is>
-          <t>Hold a shared row, tap 'Repeat…'. Compare with Menu › Repeating › Edit on a personal task.</t>
+          <t>Tick the brought copy on your Today. Check the shared list on the other account.</t>
         </is>
       </c>
       <c r="F334" s="9" t="inlineStr">
         <is>
-          <t>Identical controls. The commit button NAMES the cadence ('Every day', 'Every 2 days'), on both. The Ours sheet adds one line: 'You'll both see it on its day.' It appears on its days for both people.</t>
+          <t>The shared row is done. It enters YOUR Lookback. Nothing on the other side says who did it.</t>
         </is>
       </c>
       <c r="G334" s="7" t="inlineStr">
@@ -14094,7 +14094,7 @@
     <row r="335">
       <c r="A335" s="6" t="inlineStr">
         <is>
-          <t>OUR-29</t>
+          <t>OUR-25</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -14109,17 +14109,17 @@
       </c>
       <c r="D335" s="9" t="inlineStr">
         <is>
-          <t>A cadence this build cannot read is inert, and says why</t>
+          <t>Ticking a brought copy on a device that has NEVER opened the room</t>
         </is>
       </c>
       <c r="E335" s="9" t="inlineStr">
         <is>
-          <t>Get a shared row carrying a recurrence this build does not understand (a newer build, or hand-write one via the API).</t>
+          <t>Bring a task over on phone A. Sign in on a second device (or clear its local data) and go straight to Today WITHOUT opening Ours. Tick the copy there.</t>
         </is>
       </c>
       <c r="F335" s="9" t="inlineStr">
         <is>
-          <t>The row is SHOWN, never hidden. Tapping it does nothing and a line explains it is safe and will appear on its days after an update. 'Repeat…' is withheld. It never marks itself done.</t>
+          <t>The shared row closes. (The pre-fix build silently discarded the tick with no error.)</t>
         </is>
       </c>
       <c r="G335" s="7" t="inlineStr">
@@ -14134,7 +14134,7 @@
     <row r="336">
       <c r="A336" s="6" t="inlineStr">
         <is>
-          <t>OUR-30</t>
+          <t>OUR-26</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -14142,24 +14142,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C336" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C336" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D336" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash marks what changed, and never your own edits</t>
+          <t>Their tick leaves a rest-note, never a strike-through</t>
         </is>
       </c>
       <c r="E336" s="9" t="inlineStr">
         <is>
-          <t>Have the other account add and change a few rows. Open the room. Then tick something yourself and reopen.</t>
+          <t>Bring a task over. On the OTHER account, tick the shared row. Return to your Today.</t>
         </is>
       </c>
       <c r="F336" s="9" t="inlineStr">
         <is>
-          <t>Their changed rows carry a tint and a firmer border on arrival; a screen reader says 'changed since you last looked'. Your OWN edits are never washed. Leaving and returning clears it.</t>
+          <t>Your copy is gone from the day, replaced by a dashed sage line: 'Handled on Ours. It's off your day.' It is NOT struck through and does NOT appear in your Lookback. Leaving Today and coming back clears the note.</t>
         </is>
       </c>
       <c r="G336" s="7" t="inlineStr">
@@ -14174,7 +14174,7 @@
     <row r="337">
       <c r="A337" s="6" t="inlineStr">
         <is>
-          <t>OUR-31</t>
+          <t>OUR-27</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -14189,17 +14189,17 @@
       </c>
       <c r="D337" s="9" t="inlineStr">
         <is>
-          <t>Recently removed puts a task back</t>
+          <t>Share to Ours warns about the length BEFORE it copies</t>
         </is>
       </c>
       <c r="E337" s="9" t="inlineStr">
         <is>
-          <t>Remove a shared row. Scroll to the foot of the list.</t>
+          <t>Hold one of your own Today tasks with a very long title (500+ chars), open More, tap 'Share to Ours'.</t>
         </is>
       </c>
       <c r="F337" s="9" t="inlineStr">
         <is>
-          <t>It sits under 'Recently removed', dimmed, with 'Put it back'. Restoring returns it for both people. Nothing anywhere says which of you removed it.</t>
+          <t>A line says Ours keeps titles shorter and this one will be trimmed, BEFORE the copy is made. The copy appears on the shared list. 'Share to Ours' is absent entirely when there is no live list.</t>
         </is>
       </c>
       <c r="G337" s="7" t="inlineStr">
@@ -14214,7 +14214,7 @@
     <row r="338">
       <c r="A338" s="6" t="inlineStr">
         <is>
-          <t>OUR-32</t>
+          <t>OUR-28</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -14222,24 +14222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C338" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C338" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D338" s="9" t="inlineStr">
         <is>
-          <t>Removing a shared REPEAT does not pretend to be 'Skip today'</t>
+          <t>A repeat set on Ours uses the SAME cadence sheet as home</t>
         </is>
       </c>
       <c r="E338" s="9" t="inlineStr">
         <is>
-          <t>Hold a repeating shared row and look at the shelf.</t>
+          <t>Hold a shared row, tap 'Repeat…'. Compare with Menu › Repeating › Edit on a personal task.</t>
         </is>
       </c>
       <c r="F338" s="9" t="inlineStr">
         <is>
-          <t>It reads 'Remove', not 'Skip today', and the spoken label names removing the repeat. (The shared list has no per-day skip; the pre-fix build promised one and deleted the series for both people.)</t>
+          <t>Identical controls. The commit button NAMES the cadence ('Every day', 'Every 2 days'), on both. The Ours sheet adds one line: 'You'll both see it on its day.' It appears on its days for both people.</t>
         </is>
       </c>
       <c r="G338" s="7" t="inlineStr">
@@ -14254,7 +14254,7 @@
     <row r="339">
       <c r="A339" s="6" t="inlineStr">
         <is>
-          <t>OUR-33</t>
+          <t>OUR-29</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -14269,17 +14269,17 @@
       </c>
       <c r="D339" s="9" t="inlineStr">
         <is>
-          <t>A closed list is still readable, and read-only</t>
+          <t>A cadence this build cannot read is inert, and says why</t>
         </is>
       </c>
       <c r="E339" s="9" t="inlineStr">
         <is>
-          <t>Leave a list. Open it from the archive on the pairing screen.</t>
+          <t>Get a shared row carrying a recurrence this build does not understand (a newer build, or hand-write one via the API).</t>
         </is>
       </c>
       <c r="F339" s="9" t="inlineStr">
         <is>
-          <t>Every row is readable. There is no + pill at all. Ticking, renaming, removing and re-cadencing all do nothing, and each row says why. Each row still offers taking a copy for yourself.</t>
+          <t>The row is SHOWN, never hidden. Tapping it does nothing and a line explains it is safe and will appear on its days after an update. 'Repeat…' is withheld. It never marks itself done.</t>
         </is>
       </c>
       <c r="G339" s="7" t="inlineStr">
@@ -14294,7 +14294,7 @@
     <row r="340">
       <c r="A340" s="6" t="inlineStr">
         <is>
-          <t>OUR-34</t>
+          <t>OUR-30</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -14309,17 +14309,17 @@
       </c>
       <c r="D340" s="9" t="inlineStr">
         <is>
-          <t>The archive lists closed lists, and puts them away</t>
+          <t>The quiet wash marks what changed, and never your own edits</t>
         </is>
       </c>
       <c r="E340" s="9" t="inlineStr">
         <is>
-          <t>With at least one closed list, look under 'Lists you have kept' on the pairing screen.</t>
+          <t>Have the other account add and change a few rows. Open the room. Then tick something yourself and reopen.</t>
         </is>
       </c>
       <c r="F340" s="9" t="inlineStr">
         <is>
-          <t>Purpose and closed MONTH only, no counts of any kind. 'Put it away' hides it from the default view; 'Show the ones put away' brings it back. Nothing is deleted.</t>
+          <t>Their changed rows carry a tint and a firmer border on arrival; a screen reader says 'changed since you last looked'. Your OWN edits are never washed. Leaving and returning clears it.</t>
         </is>
       </c>
       <c r="G340" s="7" t="inlineStr">
@@ -14334,7 +14334,7 @@
     <row r="341">
       <c r="A341" s="6" t="inlineStr">
         <is>
-          <t>OUR-35</t>
+          <t>OUR-31</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -14342,24 +14342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C341" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C341" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D341" s="9" t="inlineStr">
         <is>
-          <t>Reopening together is a handshake, never unilateral</t>
+          <t>Recently removed puts a task back</t>
         </is>
       </c>
       <c r="E341" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Reopen together…' on ONE side only and STAY on that screen, hands off. Read the code to the second account. On that side, tap 'Got a code from them? Enter it to reopen.' (under the reopen hint on the closed-list screen) and enter it. Repeat with the closed list being the ONLY closed list on both accounts.</t>
+          <t>Remove a shared row. Scroll to the foot of the list.</t>
         </is>
       </c>
       <c r="F341" s="9" t="inlineStr">
         <is>
-          <t>The offering side gets a code and nothing reopens yet. The other side has a named door to the join field and entering the code there reopens the list for both, with everything as it was. It is never asked which kind of code it is, and it works when the closed list on screen is the only one (the D2 'handshake purgatory', 2026-09-22). Within about ten seconds, with nothing touched, the offering side's screen changes on its own: the code is gone and the live list shows 'They used the code. The list is open again…'.</t>
+          <t>It sits under 'Recently removed', dimmed, with 'Put it back'. Restoring returns it for both people. Nothing anywhere says which of you removed it.</t>
         </is>
       </c>
       <c r="G341" s="7" t="inlineStr">
@@ -14374,7 +14374,7 @@
     <row r="342">
       <c r="A342" s="6" t="inlineStr">
         <is>
-          <t>OUR-122</t>
+          <t>OUR-32</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -14389,17 +14389,17 @@
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>Waiting screens look on their own, and 'Check now' is there for the impatient</t>
+          <t>Removing a shared REPEAT does not pretend to be 'Skip today'</t>
         </is>
       </c>
       <c r="E342" s="9" t="inlineStr">
         <is>
-          <t>A: mint a pairing code and stay on that screen, hands off. B: join. Watch A. Then, on a closed list: A taps 'Reopen together…' and stays; B redeems. Watch A. Then, on either waiting screen, tap 'Check now'.</t>
+          <t>Hold a repeating shared row and look at the shelf.</t>
         </is>
       </c>
       <c r="F342" s="9" t="inlineStr">
         <is>
-          <t>Both times A's screen changes on its own within about ten seconds: the pairing wait becomes '{name} joined.', and the closed list becomes the live list with the 'They used the code' line and the spent code gone. 'Check now' sits under the waiting text and under a minted reopen code, and does the same immediately. Once A has opened the list, the pairing screen underneath stops looking (nothing to see by eye; the rule is focus AND foreground AND under 30 minutes).</t>
+          <t>It reads 'Remove', not 'Skip today', and the spoken label names removing the repeat. (The shared list has no per-day skip; the pre-fix build promised one and deleted the series for both people.)</t>
         </is>
       </c>
       <c r="G342" s="7" t="inlineStr">
@@ -14414,7 +14414,7 @@
     <row r="343">
       <c r="A343" s="6" t="inlineStr">
         <is>
-          <t>OUR-123</t>
+          <t>OUR-33</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -14429,17 +14429,17 @@
       </c>
       <c r="D343" s="9" t="inlineStr">
         <is>
-          <t>The Ours card goes home rather than into a room</t>
+          <t>A closed list is still readable, and read-only</t>
         </is>
       </c>
       <c r="E343" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, open the Menu and tap Ours. Then open the Menu from the Ours tab and tap Ours again. Then, with no shared list yet (signed in), tap Ours from the Menu.</t>
+          <t>Leave a list. Open it from the archive on the pairing screen.</t>
         </is>
       </c>
       <c r="F343" s="9" t="inlineStr">
         <is>
-          <t>With a live list the contents page closes and you land on Today's Ours tab (the list's name underlined) in one short fade; back from there does not return to the contents page. From the Ours tab's own Menu, the Ours card simply goes back to it. With no list yet it opens the invite screen as a room: '‹ Menu' and the two-mugs picture as a band, then the invite screen as it was.</t>
+          <t>Every row is readable. There is no + pill at all. Ticking, renaming, removing and re-cadencing all do nothing, and each row says why. Each row still offers taking a copy for yourself.</t>
         </is>
       </c>
       <c r="G343" s="7" t="inlineStr">
@@ -14454,7 +14454,7 @@
     <row r="344">
       <c r="A344" s="6" t="inlineStr">
         <is>
-          <t>OUR-124</t>
+          <t>OUR-34</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -14469,17 +14469,17 @@
       </c>
       <c r="D344" s="9" t="inlineStr">
         <is>
-          <t>The room opens with your list's own name, in any language</t>
+          <t>The archive lists closed lists, and puts them away</t>
         </is>
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>With a named shared list (e.g. 'Just us') and the app set to Italian (or German, Spanish, French), tap the list's name in Today's heading.</t>
+          <t>With at least one closed list, look under 'Lists you have kept' on the pairing screen.</t>
         </is>
       </c>
       <c r="F344" s="9" t="inlineStr">
         <is>
-          <t>The room's heading shows your list's own name from the first frame, and the capture panel's heading reads 'Aggiungi a Just us'. It never shows the default ('La nostra lista') for a beat and then flips, which read as the app changing language. A list with no name shows the default in the app's language. The list's own name is shown as you typed it, in whatever language that was.</t>
+          <t>Purpose and closed MONTH only, no counts of any kind. 'Put it away' hides it from the default view; 'Show the ones put away' brings it back. Nothing is deleted.</t>
         </is>
       </c>
       <c r="G344" s="7" t="inlineStr">
@@ -14494,7 +14494,7 @@
     <row r="345">
       <c r="A345" s="6" t="inlineStr">
         <is>
-          <t>OUR-36</t>
+          <t>OUR-35</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -14509,17 +14509,17 @@
       </c>
       <c r="D345" s="9" t="inlineStr">
         <is>
-          <t>Delete for good commits when the screen closes, not on a timer</t>
+          <t>Reopening together is a handshake, never unilateral</t>
         </is>
       </c>
       <c r="E345" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
+          <t>On a closed list, tap 'Reopen together…' on ONE side only and STAY on that screen, hands off. Read the code to the second account. On that side, tap 'Got a code from them? Enter it to reopen.' (under the reopen hint on the closed-list screen) and enter it. Repeat with the closed list being the ONLY closed list on both accounts.</t>
         </is>
       </c>
       <c r="F345" s="9" t="inlineStr">
         <is>
-          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
+          <t>The offering side gets a code and nothing reopens yet. The other side has a named door to the join field and entering the code there reopens the list for both, with everything as it was. It is never asked which kind of code it is, and it works when the closed list on screen is the only one (the D2 'handshake purgatory', 2026-09-22). Within about ten seconds, with nothing touched, the offering side's screen changes on its own: the code is gone and the live list shows 'They used the code. The list is open again…'.</t>
         </is>
       </c>
       <c r="G345" s="7" t="inlineStr">
@@ -14534,7 +14534,7 @@
     <row r="346">
       <c r="A346" s="6" t="inlineStr">
         <is>
-          <t>OUR-37</t>
+          <t>OUR-122</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -14549,17 +14549,17 @@
       </c>
       <c r="D346" s="9" t="inlineStr">
         <is>
-          <t>Rename yourself, and only yourself</t>
+          <t>Waiting screens look on their own, and 'Check now' is there for the impatient</t>
         </is>
       </c>
       <c r="E346" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
+          <t>A: mint a pairing code and stay on that screen, hands off. B: join. Watch A. Then, on a closed list: A taps 'Reopen together…' and stays; B redeems. Watch A. Then, on either waiting screen, tap 'Check now'.</t>
         </is>
       </c>
       <c r="F346" s="9" t="inlineStr">
         <is>
-          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
+          <t>Both times A's screen changes on its own within about ten seconds: the pairing wait becomes '{name} joined.', and the closed list becomes the live list with the 'They used the code' line and the spent code gone. 'Check now' sits under the waiting text and under a minted reopen code, and does the same immediately. Once A has opened the list, the pairing screen underneath stops looking (nothing to see by eye; the rule is focus AND foreground AND under 30 minutes).</t>
         </is>
       </c>
       <c r="G346" s="7" t="inlineStr">
@@ -14574,7 +14574,7 @@
     <row r="347">
       <c r="A347" s="6" t="inlineStr">
         <is>
-          <t>OUR-38</t>
+          <t>OUR-123</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -14582,24 +14582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C347" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C347" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D347" s="9" t="inlineStr">
         <is>
-          <t>A dropped signal never throws you out of the room</t>
+          <t>The Ours card goes home rather than into a room</t>
         </is>
       </c>
       <c r="E347" s="9" t="inlineStr">
         <is>
-          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
+          <t>With a live shared list, open the Menu and tap Ours. Then open the Menu from the Ours tab and tap Ours again. Then, with no shared list yet (signed in), tap Ours from the Menu.</t>
         </is>
       </c>
       <c r="F347" s="9" t="inlineStr">
         <is>
-          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
+          <t>With a live list the contents page closes and you land on Today's Ours tab (the list's name underlined) in one short fade; back from there does not return to the contents page. From the Ours tab's own Menu, the Ours card simply goes back to it. With no list yet it opens the invite screen as a room: '‹ Menu' and the two-mugs picture as a band, then the invite screen as it was.</t>
         </is>
       </c>
       <c r="G347" s="7" t="inlineStr">
@@ -14614,7 +14614,7 @@
     <row r="348">
       <c r="A348" s="6" t="inlineStr">
         <is>
-          <t>OUR-39</t>
+          <t>OUR-124</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -14622,24 +14622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C348" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C348" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D348" s="9" t="inlineStr">
         <is>
-          <t>Report this list reaches us and tells nobody else</t>
+          <t>The room opens with your list's own name, in any language</t>
         </is>
       </c>
       <c r="E348" s="9" t="inlineStr">
         <is>
-          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
+          <t>With a named shared list (e.g. 'Just us') and the app set to Italian (or German, Spanish, French), tap the list's name in Today's heading.</t>
         </is>
       </c>
       <c r="F348" s="9" t="inlineStr">
         <is>
-          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
+          <t>The room's heading shows your list's own name from the first frame, and the capture panel's heading reads 'Aggiungi a Just us'. It never shows the default ('La nostra lista') for a beat and then flips, which read as the app changing language. A list with no name shows the default in the app's language. The list's own name is shown as you typed it, in whatever language that was.</t>
         </is>
       </c>
       <c r="G348" s="7" t="inlineStr">
@@ -14654,7 +14654,7 @@
     <row r="349">
       <c r="A349" s="6" t="inlineStr">
         <is>
-          <t>OUR-40</t>
+          <t>OUR-36</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -14669,17 +14669,17 @@
       </c>
       <c r="D349" s="9" t="inlineStr">
         <is>
-          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
+          <t>Delete for good commits when the screen closes, not on a timer</t>
         </is>
       </c>
       <c r="E349" s="9" t="inlineStr">
         <is>
-          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
+          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
         </is>
       </c>
       <c r="F349" s="9" t="inlineStr">
         <is>
-          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
+          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
         </is>
       </c>
       <c r="G349" s="7" t="inlineStr">
@@ -14694,7 +14694,7 @@
     <row r="350">
       <c r="A350" s="6" t="inlineStr">
         <is>
-          <t>OUR-41</t>
+          <t>OUR-37</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -14709,17 +14709,17 @@
       </c>
       <c r="D350" s="9" t="inlineStr">
         <is>
-          <t>Leaving is the block, and needs no reason</t>
+          <t>Rename yourself, and only yourself</t>
         </is>
       </c>
       <c r="E350" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap 'Leave this list'.</t>
+          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
         </is>
       </c>
       <c r="F350" s="9" t="inlineStr">
         <is>
-          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
+          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
         </is>
       </c>
       <c r="G350" s="7" t="inlineStr">
@@ -14734,12 +14734,12 @@
     <row r="351">
       <c r="A351" s="6" t="inlineStr">
         <is>
-          <t>LEG-05</t>
+          <t>OUR-38</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C351" s="10" t="inlineStr">
@@ -14749,17 +14749,17 @@
       </c>
       <c r="D351" s="9" t="inlineStr">
         <is>
-          <t>The shared-list clauses are in both copies of both documents</t>
+          <t>A dropped signal never throws you out of the room</t>
         </is>
       </c>
       <c r="E351" s="9" t="inlineStr">
         <is>
-          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
+          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
         </is>
       </c>
       <c r="F351" s="9" t="inlineStr">
         <is>
-          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
+          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
         </is>
       </c>
       <c r="G351" s="7" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="352">
       <c r="A352" s="6" t="inlineStr">
         <is>
-          <t>OUR-42</t>
+          <t>OUR-39</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -14789,17 +14789,17 @@
       </c>
       <c r="D352" s="9" t="inlineStr">
         <is>
-          <t>A change on one phone appears on the other WITHOUT touching it</t>
+          <t>Report this list reaches us and tells nobody else</t>
         </is>
       </c>
       <c r="E352" s="9" t="inlineStr">
         <is>
-          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
+          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
         </is>
       </c>
       <c r="F352" s="9" t="inlineStr">
         <is>
-          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
+          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
         </is>
       </c>
       <c r="G352" s="7" t="inlineStr">
@@ -14814,7 +14814,7 @@
     <row r="353">
       <c r="A353" s="6" t="inlineStr">
         <is>
-          <t>OUR-43</t>
+          <t>OUR-40</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -14829,17 +14829,17 @@
       </c>
       <c r="D353" s="9" t="inlineStr">
         <is>
-          <t>Opening your own list does not bounce you back</t>
+          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
         </is>
       </c>
       <c r="E353" s="9" t="inlineStr">
         <is>
-          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
+          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
         </is>
       </c>
       <c r="F353" s="9" t="inlineStr">
         <is>
-          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
+          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
         </is>
       </c>
       <c r="G353" s="7" t="inlineStr">
@@ -14854,7 +14854,7 @@
     <row r="354">
       <c r="A354" s="6" t="inlineStr">
         <is>
-          <t>OUR-44</t>
+          <t>OUR-41</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -14869,17 +14869,17 @@
       </c>
       <c r="D354" s="9" t="inlineStr">
         <is>
-          <t>The pairing screen offers a way INTO the list</t>
+          <t>Leaving is the block, and needs no reason</t>
         </is>
       </c>
       <c r="E354" s="9" t="inlineStr">
         <is>
-          <t>Finish pairing, then look at the pairing screen.</t>
+          <t>On a live list, tap 'Leave this list'.</t>
         </is>
       </c>
       <c r="F354" s="9" t="inlineStr">
         <is>
-          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
+          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
         </is>
       </c>
       <c r="G354" s="7" t="inlineStr">
@@ -14894,12 +14894,12 @@
     <row r="355">
       <c r="A355" s="6" t="inlineStr">
         <is>
-          <t>OUR-45</t>
+          <t>LEG-05</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="C355" s="10" t="inlineStr">
@@ -14909,17 +14909,17 @@
       </c>
       <c r="D355" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash appears and then takes itself away</t>
+          <t>The shared-list clauses are in both copies of both documents</t>
         </is>
       </c>
       <c r="E355" s="9" t="inlineStr">
         <is>
-          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
+          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
         </is>
       </c>
       <c r="F355" s="9" t="inlineStr">
         <is>
-          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
+          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
         </is>
       </c>
       <c r="G355" s="7" t="inlineStr">
@@ -14934,7 +14934,7 @@
     <row r="356">
       <c r="A356" s="6" t="inlineStr">
         <is>
-          <t>OUR-47</t>
+          <t>OUR-42</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -14949,17 +14949,17 @@
       </c>
       <c r="D356" s="9" t="inlineStr">
         <is>
-          <t>Ours lives in Today's heading (Today v3)</t>
+          <t>A change on one phone appears on the other WITHOUT touching it</t>
         </is>
       </c>
       <c r="E356" s="9" t="inlineStr">
         <is>
-          <t>With a live list, look at the top of Today. Then leave the list (or sign out) and look again. With a screen reader, move through the heading.</t>
+          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
         </is>
       </c>
       <c r="F356" s="9" t="inlineStr">
         <is>
-          <t>With a live list the heading reads 'Today' and the list's name side by side (its own name when it has one, else 'Ours'), 'Today' underlined as the current tab. With no live list there is only 'Today', and no empty space where Ours would be. A screen reader hears them as tabs, 'Today, selected' and '{name}'. The old Ours door card under the list is gone.</t>
+          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
         </is>
       </c>
       <c r="G356" s="7" t="inlineStr">
@@ -14974,7 +14974,7 @@
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
         <is>
-          <t>OUR-48</t>
+          <t>OUR-43</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -14989,17 +14989,17 @@
       </c>
       <c r="D357" s="9" t="inlineStr">
         <is>
-          <t>Their tick marks your copy DONE and leaves it on your day</t>
+          <t>Opening your own list does not bounce you back</t>
         </is>
       </c>
       <c r="E357" s="9" t="inlineStr">
         <is>
-          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
+          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
         </is>
       </c>
       <c r="F357" s="9" t="inlineStr">
         <is>
-          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
+          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
         </is>
       </c>
       <c r="G357" s="7" t="inlineStr">
@@ -15014,7 +15014,7 @@
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
         <is>
-          <t>OUR-49</t>
+          <t>OUR-44</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -15022,24 +15022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C358" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C358" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D358" s="9" t="inlineStr">
         <is>
-          <t>A settled copy carries a completion DATE, not just a done flag</t>
+          <t>The pairing screen offers a way INTO the list</t>
         </is>
       </c>
       <c r="E358" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
+          <t>Finish pairing, then look at the pairing screen.</t>
         </is>
       </c>
       <c r="F358" s="9" t="inlineStr">
         <is>
-          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
+          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
         </is>
       </c>
       <c r="G358" s="7" t="inlineStr">
@@ -15054,7 +15054,7 @@
     <row r="359">
       <c r="A359" s="6" t="inlineStr">
         <is>
-          <t>OUR-50</t>
+          <t>OUR-45</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -15069,17 +15069,17 @@
       </c>
       <c r="D359" s="9" t="inlineStr">
         <is>
-          <t>A finished copy can be brought over again</t>
+          <t>The quiet wash appears and then takes itself away</t>
         </is>
       </c>
       <c r="E359" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, hold that row in Ours.</t>
+          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
         </is>
       </c>
       <c r="F359" s="9" t="inlineStr">
         <is>
-          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
+          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
         </is>
       </c>
       <c r="G359" s="7" t="inlineStr">
@@ -15094,7 +15094,7 @@
     <row r="360">
       <c r="A360" s="6" t="inlineStr">
         <is>
-          <t>OUR-51</t>
+          <t>OUR-47</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -15109,17 +15109,17 @@
       </c>
       <c r="D360" s="9" t="inlineStr">
         <is>
-          <t>Your own edit never highlights; their later edit always does</t>
+          <t>Ours lives in Today's heading (Today v3)</t>
         </is>
       </c>
       <c r="E360" s="9" t="inlineStr">
         <is>
-          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
+          <t>With a live list, look at the top of Today. Then leave the list (or sign out) and look again. With a screen reader, move through the heading.</t>
         </is>
       </c>
       <c r="F360" s="9" t="inlineStr">
         <is>
-          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
+          <t>With a live list the heading reads 'Today' and the list's name side by side (its own name when it has one, else 'Ours'), 'Today' underlined as the current tab. With no live list there is only 'Today', and no empty space where Ours would be. A screen reader hears them as tabs, 'Today, selected' and '{name}'. The old Ours door card under the list is gone.</t>
         </is>
       </c>
       <c r="G360" s="7" t="inlineStr">
@@ -15134,7 +15134,7 @@
     <row r="361">
       <c r="A361" s="6" t="inlineStr">
         <is>
-          <t>OUR-52</t>
+          <t>OUR-48</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -15142,24 +15142,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C361" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C361" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D361" s="9" t="inlineStr">
         <is>
-          <t>The highlight arrives at once and fades away</t>
+          <t>Their tick marks your copy DONE and leaves it on your day</t>
         </is>
       </c>
       <c r="E361" s="9" t="inlineStr">
         <is>
-          <t>Have B change a row while A is on the list.</t>
+          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
         </is>
       </c>
       <c r="F361" s="9" t="inlineStr">
         <is>
-          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
+          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
         </is>
       </c>
       <c r="G361" s="7" t="inlineStr">
@@ -15174,7 +15174,7 @@
     <row r="362">
       <c r="A362" s="6" t="inlineStr">
         <is>
-          <t>OUR-53</t>
+          <t>OUR-49</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -15182,24 +15182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C362" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C362" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D362" s="9" t="inlineStr">
         <is>
-          <t>Two devices share ONE clock</t>
+          <t>A settled copy carries a completion DATE, not just a done flag</t>
         </is>
       </c>
       <c r="E362" s="9" t="inlineStr">
         <is>
-          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
+          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
         </is>
       </c>
       <c r="F362" s="9" t="inlineStr">
         <is>
-          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
+          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
         </is>
       </c>
       <c r="G362" s="7" t="inlineStr">
@@ -15214,7 +15214,7 @@
     <row r="363">
       <c r="A363" s="6" t="inlineStr">
         <is>
-          <t>OUR-54</t>
+          <t>OUR-50</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -15222,24 +15222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C363" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C363" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D363" s="9" t="inlineStr">
         <is>
-          <t>The debug panel is opt-in and carries no task text</t>
+          <t>A finished copy can be brought over again</t>
         </is>
       </c>
       <c r="E363" s="9" t="inlineStr">
         <is>
-          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
+          <t>After OUR-48, hold that row in Ours.</t>
         </is>
       </c>
       <c r="F363" s="9" t="inlineStr">
         <is>
-          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
+          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
         </is>
       </c>
       <c r="G363" s="7" t="inlineStr">
@@ -15254,7 +15254,7 @@
     <row r="364">
       <c r="A364" s="6" t="inlineStr">
         <is>
-          <t>OUR-55</t>
+          <t>OUR-51</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -15269,17 +15269,17 @@
       </c>
       <c r="D364" s="9" t="inlineStr">
         <is>
-          <t>Capture on Ours IS Today's capture</t>
+          <t>Your own edit never highlights; their later edit always does</t>
         </is>
       </c>
       <c r="E364" s="9" t="inlineStr">
         <is>
-          <t>Open a shared list and tap the + pill at the foot of the screen.</t>
+          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
         </is>
       </c>
       <c r="F364" s="9" t="inlineStr">
         <is>
-          <t>The same pill and the same panel Today has, headed 'Add to {name}': the same box, the same Speak button (web), the same When chip and door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
+          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
         </is>
       </c>
       <c r="G364" s="7" t="inlineStr">
@@ -15294,7 +15294,7 @@
     <row r="365">
       <c r="A365" s="6" t="inlineStr">
         <is>
-          <t>OUR-56</t>
+          <t>OUR-52</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -15302,24 +15302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C365" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C365" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D365" s="9" t="inlineStr">
         <is>
-          <t>Repeating can be set AT capture, without knowing a gesture</t>
+          <t>The highlight arrives at once and fades away</t>
         </is>
       </c>
       <c r="E365" s="9" t="inlineStr">
         <is>
-          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
+          <t>Have B change a row while A is on the list.</t>
         </is>
       </c>
       <c r="F365" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
+          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
         </is>
       </c>
       <c r="G365" s="7" t="inlineStr">
@@ -15334,7 +15334,7 @@
     <row r="366">
       <c r="A366" s="6" t="inlineStr">
         <is>
-          <t>OUR-57</t>
+          <t>OUR-53</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -15349,17 +15349,17 @@
       </c>
       <c r="D366" s="9" t="inlineStr">
         <is>
-          <t>A dump becomes several shared rows, in the order typed</t>
+          <t>Two devices share ONE clock</t>
         </is>
       </c>
       <c r="E366" s="9" t="inlineStr">
         <is>
-          <t>Type three lines into the Ours capture and Add.</t>
+          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
         </is>
       </c>
       <c r="F366" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
+          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
         </is>
       </c>
       <c r="G366" s="7" t="inlineStr">
@@ -15374,7 +15374,7 @@
     <row r="367">
       <c r="A367" s="6" t="inlineStr">
         <is>
-          <t>OUR-58</t>
+          <t>OUR-54</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -15382,24 +15382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C367" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C367" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D367" s="9" t="inlineStr">
         <is>
-          <t>The shared door offers When and Repeating, never Steps</t>
+          <t>The debug panel is opt-in and carries no task text</t>
         </is>
       </c>
       <c r="E367" s="9" t="inlineStr">
         <is>
-          <t>Open the door on Ours and compare it with the door on Today.</t>
+          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
         </is>
       </c>
       <c r="F367" s="9" t="inlineStr">
         <is>
-          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
+          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
         </is>
       </c>
       <c r="G367" s="7" t="inlineStr">
@@ -15414,7 +15414,7 @@
     <row r="368">
       <c r="A368" s="6" t="inlineStr">
         <is>
-          <t>OUR-59</t>
+          <t>OUR-55</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -15422,24 +15422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C368" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C368" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D368" s="9" t="inlineStr">
         <is>
-          <t>Typed text survives the panel going</t>
+          <t>Capture on Ours IS Today's capture</t>
         </is>
       </c>
       <c r="E368" s="9" t="inlineStr">
         <is>
-          <t>Type half a sentence into the Ours panel, Close it, tick something, then tap the pill again.</t>
+          <t>Open a shared list and tap the + pill at the foot of the screen.</t>
         </is>
       </c>
       <c r="F368" s="9" t="inlineStr">
         <is>
-          <t>The pill shows '+' and three dots while words wait, and the half sentence is still there. The panel is always mounted, never unmounted. Only an Add resets the door; the words never reset on their own.</t>
+          <t>The same pill and the same panel Today has, headed 'Add to {name}': the same box, the same Speak button (web), the same When chip and door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
         </is>
       </c>
       <c r="G368" s="7" t="inlineStr">
@@ -15454,7 +15454,7 @@
     <row r="369">
       <c r="A369" s="6" t="inlineStr">
         <is>
-          <t>OUR-60</t>
+          <t>OUR-56</t>
         </is>
       </c>
       <c r="B369" s="7" t="inlineStr">
@@ -15462,29 +15462,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C369" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C369" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D369" s="9" t="inlineStr">
         <is>
-          <t>The Ours panel rides above the keyboard</t>
+          <t>Repeating can be set AT capture, without knowing a gesture</t>
         </is>
       </c>
       <c r="E369" s="9" t="inlineStr">
         <is>
-          <t>On a real Android device, tap the + pill on the Ours list, tap the box and start typing.</t>
+          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
         </is>
       </c>
       <c r="F369" s="9" t="inlineStr">
         <is>
-          <t>The panel and its Add button stay visible above the keyboard while you type. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
+          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
         </is>
       </c>
       <c r="G369" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H369" s="7" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
     <row r="370">
       <c r="A370" s="6" t="inlineStr">
         <is>
-          <t>OUR-61</t>
+          <t>OUR-57</t>
         </is>
       </c>
       <c r="B370" s="7" t="inlineStr">
@@ -15502,24 +15502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C370" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C370" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D370" s="9" t="inlineStr">
         <is>
-          <t>No AI on the shared capture</t>
+          <t>A dump becomes several shared rows, in the order typed</t>
         </is>
       </c>
       <c r="E370" s="9" t="inlineStr">
         <is>
-          <t>Open the Ours capture panel with AI enabled in Settings, and type a long run-on line.</t>
+          <t>Type three lines into the Ours capture and Add.</t>
         </is>
       </c>
       <c r="F370" s="9" t="inlineStr">
         <is>
-          <t>No 'Break it down', no 'Sort for me', and no 'Tidy this into tasks': steps or rewrites a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
+          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
         </is>
       </c>
       <c r="G370" s="7" t="inlineStr">
@@ -15534,7 +15534,7 @@
     <row r="371">
       <c r="A371" s="6" t="inlineStr">
         <is>
-          <t>OUR-62</t>
+          <t>OUR-58</t>
         </is>
       </c>
       <c r="B371" s="7" t="inlineStr">
@@ -15549,22 +15549,22 @@
       </c>
       <c r="D371" s="9" t="inlineStr">
         <is>
-          <t>Scan (premium) reaches the shared capture</t>
+          <t>The shared door offers When and Repeating, never Steps</t>
         </is>
       </c>
       <c r="E371" s="9" t="inlineStr">
         <is>
-          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
+          <t>Open the door on Ours and compare it with the door on Today.</t>
         </is>
       </c>
       <c r="F371" s="9" t="inlineStr">
         <is>
-          <t>The panel rises with the words IN its box (keyboard down), not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
+          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
         </is>
       </c>
       <c r="G371" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H371" s="7" t="inlineStr"/>
@@ -15574,7 +15574,7 @@
     <row r="372">
       <c r="A372" s="6" t="inlineStr">
         <is>
-          <t>OUR-63</t>
+          <t>OUR-59</t>
         </is>
       </c>
       <c r="B372" s="7" t="inlineStr">
@@ -15582,24 +15582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C372" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C372" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D372" s="9" t="inlineStr">
         <is>
-          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
+          <t>Typed text survives the panel going</t>
         </is>
       </c>
       <c r="E372" s="9" t="inlineStr">
         <is>
-          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
+          <t>Type half a sentence into the Ours panel, Close it, tick something, then tap the pill again.</t>
         </is>
       </c>
       <c r="F372" s="9" t="inlineStr">
         <is>
-          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
+          <t>The pill shows '+' and three dots while words wait, and the half sentence is still there. The panel is always mounted, never unmounted. Only an Add resets the door; the words never reset on their own.</t>
         </is>
       </c>
       <c r="G372" s="7" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="373">
       <c r="A373" s="6" t="inlineStr">
         <is>
-          <t>OUR-64</t>
+          <t>OUR-60</t>
         </is>
       </c>
       <c r="B373" s="7" t="inlineStr">
@@ -15629,22 +15629,22 @@
       </c>
       <c r="D373" s="9" t="inlineStr">
         <is>
-          <t>The photo never reaches the shared list</t>
+          <t>The Ours panel rides above the keyboard</t>
         </is>
       </c>
       <c r="E373" s="9" t="inlineStr">
         <is>
-          <t>Scan something into Ours and Add it. Check the other device.</t>
+          <t>On a real Android device, tap the + pill on the Ours list, tap the box and start typing.</t>
         </is>
       </c>
       <c r="F373" s="9" t="inlineStr">
         <is>
-          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
+          <t>The panel and its Add button stay visible above the keyboard while you type. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
         </is>
       </c>
       <c r="G373" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H373" s="7" t="inlineStr"/>
@@ -15654,7 +15654,7 @@
     <row r="374">
       <c r="A374" s="6" t="inlineStr">
         <is>
-          <t>OUR-65</t>
+          <t>OUR-61</t>
         </is>
       </c>
       <c r="B374" s="7" t="inlineStr">
@@ -15669,17 +15669,17 @@
       </c>
       <c r="D374" s="9" t="inlineStr">
         <is>
-          <t>Scan is absent when AI is off</t>
+          <t>No AI on the shared capture</t>
         </is>
       </c>
       <c r="E374" s="9" t="inlineStr">
         <is>
-          <t>Turn AI off in Settings, then open the Ours capture.</t>
+          <t>Open the Ours capture panel with AI enabled in Settings, and type a long run-on line.</t>
         </is>
       </c>
       <c r="F374" s="9" t="inlineStr">
         <is>
-          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
+          <t>No 'Break it down', no 'Sort for me', and no 'Tidy this into tasks': steps or rewrites a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
         </is>
       </c>
       <c r="G374" s="7" t="inlineStr">
@@ -15694,7 +15694,7 @@
     <row r="375">
       <c r="A375" s="6" t="inlineStr">
         <is>
-          <t>OUR-66</t>
+          <t>OUR-62</t>
         </is>
       </c>
       <c r="B375" s="7" t="inlineStr">
@@ -15709,22 +15709,22 @@
       </c>
       <c r="D375" s="9" t="inlineStr">
         <is>
-          <t>A repeating shared row appears on BOTH Todays on its day</t>
+          <t>Scan (premium) reaches the shared capture</t>
         </is>
       </c>
       <c r="E375" s="9" t="inlineStr">
         <is>
-          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
+          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
         </is>
       </c>
       <c r="F375" s="9" t="inlineStr">
         <is>
-          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
+          <t>The panel rises with the words IN its box (keyboard down), not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
         </is>
       </c>
       <c r="G375" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H375" s="7" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
     <row r="376">
       <c r="A376" s="6" t="inlineStr">
         <is>
-          <t>OUR-67</t>
+          <t>OUR-63</t>
         </is>
       </c>
       <c r="B376" s="7" t="inlineStr">
@@ -15749,17 +15749,17 @@
       </c>
       <c r="D376" s="9" t="inlineStr">
         <is>
-          <t>An UNDATED shared row never reaches Today</t>
+          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
         </is>
       </c>
       <c r="E376" s="9" t="inlineStr">
         <is>
-          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
+          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
         </is>
       </c>
       <c r="F376" s="9" t="inlineStr">
         <is>
-          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
+          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
         </is>
       </c>
       <c r="G376" s="7" t="inlineStr">
@@ -15774,7 +15774,7 @@
     <row r="377">
       <c r="A377" s="6" t="inlineStr">
         <is>
-          <t>OUR-68</t>
+          <t>OUR-64</t>
         </is>
       </c>
       <c r="B377" s="7" t="inlineStr">
@@ -15782,24 +15782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C377" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C377" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D377" s="9" t="inlineStr">
         <is>
-          <t>Shared rows never make the day look heavier</t>
+          <t>The photo never reaches the shared list</t>
         </is>
       </c>
       <c r="E377" s="9" t="inlineStr">
         <is>
-          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
+          <t>Scan something into Ours and Add it. Check the other device.</t>
         </is>
       </c>
       <c r="F377" s="9" t="inlineStr">
         <is>
-          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
+          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
         </is>
       </c>
       <c r="G377" s="7" t="inlineStr">
@@ -15814,7 +15814,7 @@
     <row r="378">
       <c r="A378" s="6" t="inlineStr">
         <is>
-          <t>OUR-69</t>
+          <t>OUR-65</t>
         </is>
       </c>
       <c r="B378" s="7" t="inlineStr">
@@ -15822,24 +15822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C378" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C378" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D378" s="9" t="inlineStr">
         <is>
-          <t>Ticking a shared row from Today closes it for both</t>
+          <t>Scan is absent when AI is off</t>
         </is>
       </c>
       <c r="E378" s="9" t="inlineStr">
         <is>
-          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
+          <t>Turn AI off in Settings, then open the Ours capture.</t>
         </is>
       </c>
       <c r="F378" s="9" t="inlineStr">
         <is>
-          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
+          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
         </is>
       </c>
       <c r="G378" s="7" t="inlineStr">
@@ -15854,7 +15854,7 @@
     <row r="379">
       <c r="A379" s="6" t="inlineStr">
         <is>
-          <t>OUR-70</t>
+          <t>OUR-66</t>
         </is>
       </c>
       <c r="B379" s="7" t="inlineStr">
@@ -15862,24 +15862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C379" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C379" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D379" s="9" t="inlineStr">
         <is>
-          <t>A dated shared row shows from its day onward, never before</t>
+          <t>A repeating shared row appears on BOTH Todays on its day</t>
         </is>
       </c>
       <c r="E379" s="9" t="inlineStr">
         <is>
-          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
+          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
         </is>
       </c>
       <c r="F379" s="9" t="inlineStr">
         <is>
-          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
+          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
         </is>
       </c>
       <c r="G379" s="7" t="inlineStr">
@@ -15894,7 +15894,7 @@
     <row r="380">
       <c r="A380" s="6" t="inlineStr">
         <is>
-          <t>OUR-71</t>
+          <t>OUR-67</t>
         </is>
       </c>
       <c r="B380" s="7" t="inlineStr">
@@ -15909,17 +15909,17 @@
       </c>
       <c r="D380" s="9" t="inlineStr">
         <is>
-          <t>The shared capture rests on Anytime, and says what a day means</t>
+          <t>An UNDATED shared row never reaches Today</t>
         </is>
       </c>
       <c r="E380" s="9" t="inlineStr">
         <is>
-          <t>Tap the + pill on Ours and read the line beside the When chip. Open the door. Pick Today, then Tomorrow, then Daily, reading that line each time.</t>
+          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
         </is>
       </c>
       <c r="F380" s="9" t="inlineStr">
         <is>
-          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected, and the Add button says just 'Add'. Choosing Today makes it read 'Add · Today', because that is the notable case: it will appear on both your days. The line beside the chip says, in plain words, what the current choice means on a shared list (no day lives here; a day reaches both Todays; a rhythm repeats for both of you), before you add.</t>
+          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
         </is>
       </c>
       <c r="G380" s="7" t="inlineStr">
@@ -15934,7 +15934,7 @@
     <row r="381">
       <c r="A381" s="6" t="inlineStr">
         <is>
-          <t>OUR-112</t>
+          <t>OUR-68</t>
         </is>
       </c>
       <c r="B381" s="7" t="inlineStr">
@@ -15949,17 +15949,17 @@
       </c>
       <c r="D381" s="9" t="inlineStr">
         <is>
-          <t>A shared row's WHEN can be changed, and cleared</t>
+          <t>Shared rows never make the day look heavier</t>
         </is>
       </c>
       <c r="E381" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
+          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
         </is>
       </c>
       <c r="F381" s="9" t="inlineStr">
         <is>
-          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
+          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
         </is>
       </c>
       <c r="G381" s="7" t="inlineStr">
@@ -15974,7 +15974,7 @@
     <row r="382">
       <c r="A382" s="6" t="inlineStr">
         <is>
-          <t>OUR-113</t>
+          <t>OUR-69</t>
         </is>
       </c>
       <c r="B382" s="7" t="inlineStr">
@@ -15989,17 +15989,17 @@
       </c>
       <c r="D382" s="9" t="inlineStr">
         <is>
-          <t>Ending a rhythm does NOT mark the row done for both people</t>
+          <t>Ticking a shared row from Today closes it for both</t>
         </is>
       </c>
       <c r="E382" s="9" t="inlineStr">
         <is>
-          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
+          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
         </is>
       </c>
       <c r="F382" s="9" t="inlineStr">
         <is>
-          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
+          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
         </is>
       </c>
       <c r="G382" s="7" t="inlineStr">
@@ -16014,7 +16014,7 @@
     <row r="383">
       <c r="A383" s="6" t="inlineStr">
         <is>
-          <t>OUR-114</t>
+          <t>OUR-70</t>
         </is>
       </c>
       <c r="B383" s="7" t="inlineStr">
@@ -16029,17 +16029,17 @@
       </c>
       <c r="D383" s="9" t="inlineStr">
         <is>
-          <t>The day zone changes its question when a rhythm is alive</t>
+          <t>A dated shared row shows from its day onward, never before</t>
         </is>
       </c>
       <c r="E383" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
+          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
         </is>
       </c>
       <c r="F383" s="9" t="inlineStr">
         <is>
-          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
+          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
         </is>
       </c>
       <c r="G383" s="7" t="inlineStr">
@@ -16054,7 +16054,7 @@
     <row r="384">
       <c r="A384" s="6" t="inlineStr">
         <is>
-          <t>OUR-115</t>
+          <t>OUR-71</t>
         </is>
       </c>
       <c r="B384" s="7" t="inlineStr">
@@ -16062,24 +16062,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C384" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C384" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D384" s="9" t="inlineStr">
         <is>
-          <t>Setting a shared row to Today actually reaches both Todays</t>
+          <t>The shared capture rests on Anytime, and says what a day means</t>
         </is>
       </c>
       <c r="E384" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
+          <t>Tap the + pill on Ours and read the line beside the When chip. Open the door. Pick Today, then Tomorrow, then Daily, reading that line each time.</t>
         </is>
       </c>
       <c r="F384" s="9" t="inlineStr">
         <is>
-          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
+          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected, and the Add button says just 'Add'. Choosing Today makes it read 'Add · Today', because that is the notable case: it will appear on both your days. The line beside the chip says, in plain words, what the current choice means on a shared list (no day lives here; a day reaches both Todays; a rhythm repeats for both of you), before you add.</t>
         </is>
       </c>
       <c r="G384" s="7" t="inlineStr">
@@ -16094,7 +16094,7 @@
     <row r="385">
       <c r="A385" s="6" t="inlineStr">
         <is>
-          <t>OUR-116</t>
+          <t>OUR-112</t>
         </is>
       </c>
       <c r="B385" s="7" t="inlineStr">
@@ -16102,24 +16102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C385" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C385" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D385" s="9" t="inlineStr">
         <is>
-          <t>An idle Set does not wash the row on the other device</t>
+          <t>A shared row's WHEN can be changed, and cleared</t>
         </is>
       </c>
       <c r="E385" s="9" t="inlineStr">
         <is>
-          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
+          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
         </is>
       </c>
       <c r="F385" s="9" t="inlineStr">
         <is>
-          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
+          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
         </is>
       </c>
       <c r="G385" s="7" t="inlineStr">
@@ -16134,7 +16134,7 @@
     <row r="386">
       <c r="A386" s="6" t="inlineStr">
         <is>
-          <t>OUR-118</t>
+          <t>OUR-113</t>
         </is>
       </c>
       <c r="B386" s="7" t="inlineStr">
@@ -16149,17 +16149,17 @@
       </c>
       <c r="D386" s="9" t="inlineStr">
         <is>
-          <t>A repeat you have already done today keeps its held card</t>
+          <t>Ending a rhythm does NOT mark the row done for both people</t>
         </is>
       </c>
       <c r="E386" s="9" t="inlineStr">
         <is>
-          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
+          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
         </is>
       </c>
       <c r="F386" s="9" t="inlineStr">
         <is>
-          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
+          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
         </is>
       </c>
       <c r="G386" s="7" t="inlineStr">
@@ -16174,7 +16174,7 @@
     <row r="387">
       <c r="A387" s="6" t="inlineStr">
         <is>
-          <t>OUR-117</t>
+          <t>OUR-114</t>
         </is>
       </c>
       <c r="B387" s="7" t="inlineStr">
@@ -16189,17 +16189,17 @@
       </c>
       <c r="D387" s="9" t="inlineStr">
         <is>
-          <t>The Repeating room's Edit sheet is untouched by the When editor</t>
+          <t>The day zone changes its question when a rhythm is alive</t>
         </is>
       </c>
       <c r="E387" s="9" t="inlineStr">
         <is>
-          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
+          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
         </is>
       </c>
       <c r="F387" s="9" t="inlineStr">
         <is>
-          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the Repeating room.</t>
+          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
         </is>
       </c>
       <c r="G387" s="7" t="inlineStr">
@@ -16214,7 +16214,7 @@
     <row r="388">
       <c r="A388" s="6" t="inlineStr">
         <is>
-          <t>OUR-119</t>
+          <t>OUR-115</t>
         </is>
       </c>
       <c r="B388" s="7" t="inlineStr">
@@ -16229,17 +16229,17 @@
       </c>
       <c r="D388" s="9" t="inlineStr">
         <is>
-          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
+          <t>Setting a shared row to Today actually reaches both Todays</t>
         </is>
       </c>
       <c r="E388" s="9" t="inlineStr">
         <is>
-          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
+          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
         </is>
       </c>
       <c r="F388" s="9" t="inlineStr">
         <is>
-          <t>Monthly is the fourth rhythm chip here too, from the same sheet the Repeating room uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
+          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
         </is>
       </c>
       <c r="G388" s="7" t="inlineStr">
@@ -16254,7 +16254,7 @@
     <row r="389">
       <c r="A389" s="6" t="inlineStr">
         <is>
-          <t>OUR-111</t>
+          <t>OUR-116</t>
         </is>
       </c>
       <c r="B389" s="7" t="inlineStr">
@@ -16262,24 +16262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C389" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C389" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D389" s="9" t="inlineStr">
         <is>
-          <t>A finished dated shared row leaves both Todays the next day</t>
+          <t>An idle Set does not wash the row on the other device</t>
         </is>
       </c>
       <c r="E389" s="9" t="inlineStr">
         <is>
-          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
+          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
         </is>
       </c>
       <c r="F389" s="9" t="inlineStr">
         <is>
-          <t>Today: still there on BOTH, ticked, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
+          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
         </is>
       </c>
       <c r="G389" s="7" t="inlineStr">
@@ -16294,7 +16294,7 @@
     <row r="390">
       <c r="A390" s="6" t="inlineStr">
         <is>
-          <t>OUR-72</t>
+          <t>OUR-118</t>
         </is>
       </c>
       <c r="B390" s="7" t="inlineStr">
@@ -16302,24 +16302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C390" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C390" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D390" s="9" t="inlineStr">
         <is>
-          <t>A repeat supersedes the day rather than joining it</t>
+          <t>A repeat you have already done today keeps its held card</t>
         </is>
       </c>
       <c r="E390" s="9" t="inlineStr">
         <is>
-          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
+          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
         </is>
       </c>
       <c r="F390" s="9" t="inlineStr">
         <is>
-          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
+          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
         </is>
       </c>
       <c r="G390" s="7" t="inlineStr">
@@ -16334,7 +16334,7 @@
     <row r="391">
       <c r="A391" s="6" t="inlineStr">
         <is>
-          <t>OUR-73</t>
+          <t>OUR-117</t>
         </is>
       </c>
       <c r="B391" s="7" t="inlineStr">
@@ -16342,24 +16342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C391" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C391" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D391" s="9" t="inlineStr">
         <is>
-          <t>An unreadable cadence is never placed on a day</t>
+          <t>The Repeating room's Edit sheet is untouched by the When editor</t>
         </is>
       </c>
       <c r="E391" s="9" t="inlineStr">
         <is>
-          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
+          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
         </is>
       </c>
       <c r="F391" s="9" t="inlineStr">
         <is>
-          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
+          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the Repeating room.</t>
         </is>
       </c>
       <c r="G391" s="7" t="inlineStr">
@@ -16374,7 +16374,7 @@
     <row r="392">
       <c r="A392" s="6" t="inlineStr">
         <is>
-          <t>OUR-74</t>
+          <t>OUR-119</t>
         </is>
       </c>
       <c r="B392" s="7" t="inlineStr">
@@ -16382,24 +16382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C392" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C392" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D392" s="9" t="inlineStr">
         <is>
-          <t>The heading's '!' says something changed since you looked, and clears when you look</t>
+          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
         </is>
       </c>
       <c r="E392" s="9" t="inlineStr">
         <is>
-          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap the list's name in the heading and come back. Also have device B delete a row and check again.</t>
+          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
         </is>
       </c>
       <c r="F392" s="9" t="inlineStr">
         <is>
-          <t>A small tinted '!' sits beside the list's name in Today's heading, and a screen reader hears '{name}. 1 since you looked'. After visiting, it is gone. A deleted row never raises it. The mark is bounded by your own attention, not by the list's length, and it never shows a climbing number.</t>
+          <t>Monthly is the fourth rhythm chip here too, from the same sheet the Repeating room uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
         </is>
       </c>
       <c r="G392" s="7" t="inlineStr">
@@ -16414,7 +16414,7 @@
     <row r="393">
       <c r="A393" s="6" t="inlineStr">
         <is>
-          <t>OUR-75</t>
+          <t>OUR-111</t>
         </is>
       </c>
       <c r="B393" s="7" t="inlineStr">
@@ -16422,24 +16422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C393" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C393" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D393" s="9" t="inlineStr">
         <is>
-          <t>Your OWN changes never raise the '!'</t>
+          <t>A finished dated shared row leaves both Todays the next day</t>
         </is>
       </c>
       <c r="E393" s="9" t="inlineStr">
         <is>
-          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
+          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
         </is>
       </c>
       <c r="F393" s="9" t="inlineStr">
         <is>
-          <t>No '!' in the heading. It uses the room's own wash arithmetic, so the heading and the room always agree about whose change it was.</t>
+          <t>Today: still there on BOTH, ticked, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
         </is>
       </c>
       <c r="G393" s="7" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="394">
       <c r="A394" s="6" t="inlineStr">
         <is>
-          <t>OUR-76</t>
+          <t>OUR-72</t>
         </is>
       </c>
       <c r="B394" s="7" t="inlineStr">
@@ -16469,17 +16469,17 @@
       </c>
       <c r="D394" s="9" t="inlineStr">
         <is>
-          <t>A first-ever visit raises nothing</t>
+          <t>A repeat supersedes the day rather than joining it</t>
         </is>
       </c>
       <c r="E394" s="9" t="inlineStr">
         <is>
-          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
+          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
         </is>
       </c>
       <c r="F394" s="9" t="inlineStr">
         <is>
-          <t>No '!'. There is no 'last looked' to measure against, and inventing one would open the app with a mark already on it.</t>
+          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
         </is>
       </c>
       <c r="G394" s="7" t="inlineStr">
@@ -16494,7 +16494,7 @@
     <row r="395">
       <c r="A395" s="6" t="inlineStr">
         <is>
-          <t>OUR-77</t>
+          <t>OUR-73</t>
         </is>
       </c>
       <c r="B395" s="7" t="inlineStr">
@@ -16502,24 +16502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C395" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C395" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D395" s="9" t="inlineStr">
         <is>
-          <t>The capture's AI note names only what that surface HAS</t>
+          <t>An unreadable cadence is never placed on a day</t>
         </is>
       </c>
       <c r="E395" s="9" t="inlineStr">
         <is>
-          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
+          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
         </is>
       </c>
       <c r="F395" s="9" t="inlineStr">
         <is>
-          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
+          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
         </is>
       </c>
       <c r="G395" s="7" t="inlineStr">
@@ -16534,7 +16534,7 @@
     <row r="396">
       <c r="A396" s="6" t="inlineStr">
         <is>
-          <t>OUR-78</t>
+          <t>OUR-74</t>
         </is>
       </c>
       <c r="B396" s="7" t="inlineStr">
@@ -16549,17 +16549,17 @@
       </c>
       <c r="D396" s="9" t="inlineStr">
         <is>
-          <t>Scan discloses on every path that can reach a camera</t>
+          <t>The heading's '!' says something changed since you looked, and clears when you look</t>
         </is>
       </c>
       <c r="E396" s="9" t="inlineStr">
         <is>
-          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
+          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap the list's name in the heading and come back. Also have device B delete a row and check again.</t>
         </is>
       </c>
       <c r="F396" s="9" t="inlineStr">
         <is>
-          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
+          <t>A small tinted '!' sits beside the list's name in Today's heading, and a screen reader hears '{name}. 1 since you looked'. After visiting, it is gone. A deleted row never raises it. The mark is bounded by your own attention, not by the list's length, and it never shows a climbing number.</t>
         </is>
       </c>
       <c r="G396" s="7" t="inlineStr">
@@ -16574,7 +16574,7 @@
     <row r="397">
       <c r="A397" s="6" t="inlineStr">
         <is>
-          <t>OUR-79</t>
+          <t>OUR-75</t>
         </is>
       </c>
       <c r="B397" s="7" t="inlineStr">
@@ -16582,24 +16582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C397" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C397" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D397" s="9" t="inlineStr">
         <is>
-          <t>Press and hold a From Ours row on Today</t>
+          <t>Your OWN changes never raise the '!'</t>
         </is>
       </c>
       <c r="E397" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Ours strip.</t>
+          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
         </is>
       </c>
       <c r="F397" s="9" t="inlineStr">
         <is>
-          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
+          <t>No '!' in the heading. It uses the room's own wash arithmetic, so the heading and the room always agree about whose change it was.</t>
         </is>
       </c>
       <c r="G397" s="7" t="inlineStr">
@@ -16614,7 +16614,7 @@
     <row r="398">
       <c r="A398" s="6" t="inlineStr">
         <is>
-          <t>OUR-80</t>
+          <t>OUR-76</t>
         </is>
       </c>
       <c r="B398" s="7" t="inlineStr">
@@ -16622,24 +16622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C398" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C398" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D398" s="9" t="inlineStr">
         <is>
-          <t>Pin and Move-to never rearrange the other person's day</t>
+          <t>A first-ever visit raises nothing</t>
         </is>
       </c>
       <c r="E398" s="9" t="inlineStr">
         <is>
-          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
+          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
         </is>
       </c>
       <c r="F398" s="9" t="inlineStr">
         <is>
-          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
+          <t>No '!'. There is no 'last looked' to measure against, and inventing one would open the app with a mark already on it.</t>
         </is>
       </c>
       <c r="G398" s="7" t="inlineStr">
@@ -16654,7 +16654,7 @@
     <row r="399">
       <c r="A399" s="6" t="inlineStr">
         <is>
-          <t>OUR-81</t>
+          <t>OUR-77</t>
         </is>
       </c>
       <c r="B399" s="7" t="inlineStr">
@@ -16662,24 +16662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C399" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C399" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D399" s="9" t="inlineStr">
         <is>
-          <t>A taken-on row is never on screen twice</t>
+          <t>The capture's AI note names only what that surface HAS</t>
         </is>
       </c>
       <c r="E399" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
+          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
         </is>
       </c>
       <c r="F399" s="9" t="inlineStr">
         <is>
-          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
+          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
         </is>
       </c>
       <c r="G399" s="7" t="inlineStr">
@@ -16694,7 +16694,7 @@
     <row r="400">
       <c r="A400" s="6" t="inlineStr">
         <is>
-          <t>OUR-82</t>
+          <t>OUR-78</t>
         </is>
       </c>
       <c r="B400" s="7" t="inlineStr">
@@ -16702,24 +16702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C400" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C400" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D400" s="9" t="inlineStr">
         <is>
-          <t>Move-to is not offered on a repeating shared row</t>
+          <t>Scan discloses on every path that can reach a camera</t>
         </is>
       </c>
       <c r="E400" s="9" t="inlineStr">
         <is>
-          <t>Hold a repeating row in the From Ours strip.</t>
+          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
         </is>
       </c>
       <c r="F400" s="9" t="inlineStr">
         <is>
-          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
+          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
         </is>
       </c>
       <c r="G400" s="7" t="inlineStr">
@@ -16734,7 +16734,7 @@
     <row r="401">
       <c r="A401" s="6" t="inlineStr">
         <is>
-          <t>OUR-83</t>
+          <t>OUR-79</t>
         </is>
       </c>
       <c r="B401" s="7" t="inlineStr">
@@ -16749,17 +16749,17 @@
       </c>
       <c r="D401" s="9" t="inlineStr">
         <is>
-          <t>One shared row, one route onto your day</t>
+          <t>Press and hold a From Ours row on Today</t>
         </is>
       </c>
       <c r="E401" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
+          <t>Hold a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F401" s="9" t="inlineStr">
         <is>
-          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
+          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
         </is>
       </c>
       <c r="G401" s="7" t="inlineStr">
@@ -16774,7 +16774,7 @@
     <row r="402">
       <c r="A402" s="6" t="inlineStr">
         <is>
-          <t>OUR-84</t>
+          <t>OUR-80</t>
         </is>
       </c>
       <c r="B402" s="7" t="inlineStr">
@@ -16789,17 +16789,17 @@
       </c>
       <c r="D402" s="9" t="inlineStr">
         <is>
-          <t>Take a From Ours row on, and it becomes an ordinary task</t>
+          <t>Pin and Move-to never rearrange the other person's day</t>
         </is>
       </c>
       <c r="E402" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
+          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
         </is>
       </c>
       <c r="F402" s="9" t="inlineStr">
         <is>
-          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
+          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
         </is>
       </c>
       <c r="G402" s="7" t="inlineStr">
@@ -16814,7 +16814,7 @@
     <row r="403">
       <c r="A403" s="6" t="inlineStr">
         <is>
-          <t>OUR-85</t>
+          <t>OUR-81</t>
         </is>
       </c>
       <c r="B403" s="7" t="inlineStr">
@@ -16829,17 +16829,17 @@
       </c>
       <c r="D403" s="9" t="inlineStr">
         <is>
-          <t>Break it down works once taken on, and never touches the shared list</t>
+          <t>A taken-on row is never on screen twice</t>
         </is>
       </c>
       <c r="E403" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on, then Break it down.</t>
+          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
         </is>
       </c>
       <c r="F403" s="9" t="inlineStr">
         <is>
-          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
+          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
         </is>
       </c>
       <c r="G403" s="7" t="inlineStr">
@@ -16854,7 +16854,7 @@
     <row r="404">
       <c r="A404" s="6" t="inlineStr">
         <is>
-          <t>OUR-86</t>
+          <t>OUR-82</t>
         </is>
       </c>
       <c r="B404" s="7" t="inlineStr">
@@ -16862,24 +16862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C404" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C404" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D404" s="9" t="inlineStr">
         <is>
-          <t>Select several rows in the room and tick them together</t>
+          <t>Move-to is not offered on a repeating shared row</t>
         </is>
       </c>
       <c r="E404" s="9" t="inlineStr">
         <is>
-          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
+          <t>Hold a repeating row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F404" s="9" t="inlineStr">
         <is>
-          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
+          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
         </is>
       </c>
       <c r="G404" s="7" t="inlineStr">
@@ -16894,7 +16894,7 @@
     <row r="405">
       <c r="A405" s="6" t="inlineStr">
         <is>
-          <t>OUR-87</t>
+          <t>OUR-83</t>
         </is>
       </c>
       <c r="B405" s="7" t="inlineStr">
@@ -16909,17 +16909,17 @@
       </c>
       <c r="D405" s="9" t="inlineStr">
         <is>
-          <t>Bulk tick never UN-ticks</t>
+          <t>One shared row, one route onto your day</t>
         </is>
       </c>
       <c r="E405" s="9" t="inlineStr">
         <is>
-          <t>Select a mix of done and not-done rows and tap Done.</t>
+          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
         </is>
       </c>
       <c r="F405" s="9" t="inlineStr">
         <is>
-          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
+          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
         </is>
       </c>
       <c r="G405" s="7" t="inlineStr">
@@ -16934,7 +16934,7 @@
     <row r="406">
       <c r="A406" s="6" t="inlineStr">
         <is>
-          <t>OUR-88</t>
+          <t>OUR-84</t>
         </is>
       </c>
       <c r="B406" s="7" t="inlineStr">
@@ -16949,17 +16949,17 @@
       </c>
       <c r="D406" s="9" t="inlineStr">
         <is>
-          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
+          <t>Take a From Ours row on, and it becomes an ordinary task</t>
         </is>
       </c>
       <c r="E406" s="9" t="inlineStr">
         <is>
-          <t>Select a repeating row along with others. Read the shelf.</t>
+          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
         </is>
       </c>
       <c r="F406" s="9" t="inlineStr">
         <is>
-          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
+          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
         </is>
       </c>
       <c r="G406" s="7" t="inlineStr">
@@ -16974,7 +16974,7 @@
     <row r="407">
       <c r="A407" s="6" t="inlineStr">
         <is>
-          <t>OUR-89</t>
+          <t>OUR-85</t>
         </is>
       </c>
       <c r="B407" s="7" t="inlineStr">
@@ -16989,17 +16989,17 @@
       </c>
       <c r="D407" s="9" t="inlineStr">
         <is>
-          <t>The pill steps aside for the select shelf</t>
+          <t>Break it down works once taken on, and never touches the shared list</t>
         </is>
       </c>
       <c r="E407" s="9" t="inlineStr">
         <is>
-          <t>Enter select mode in the room with a few words waiting in the capture panel.</t>
+          <t>Take a shared row on, then Break it down.</t>
         </is>
       </c>
       <c r="F407" s="9" t="inlineStr">
         <is>
-          <t>The pill is gone while selecting (the select shelf docks at the foot), and back when you cancel, still showing its waiting words. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
+          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
         </is>
       </c>
       <c r="G407" s="7" t="inlineStr">
@@ -17014,7 +17014,7 @@
     <row r="408">
       <c r="A408" s="6" t="inlineStr">
         <is>
-          <t>OUR-90</t>
+          <t>OUR-86</t>
         </is>
       </c>
       <c r="B408" s="7" t="inlineStr">
@@ -17022,24 +17022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C408" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C408" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D408" s="9" t="inlineStr">
         <is>
-          <t>No select mode on a closed list</t>
+          <t>Select several rows in the room and tick them together</t>
         </is>
       </c>
       <c r="E408" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list and hold a row.</t>
+          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
         </is>
       </c>
       <c r="F408" s="9" t="inlineStr">
         <is>
-          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
+          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
         </is>
       </c>
       <c r="G408" s="7" t="inlineStr">
@@ -17054,7 +17054,7 @@
     <row r="409">
       <c r="A409" s="6" t="inlineStr">
         <is>
-          <t>OUR-91</t>
+          <t>OUR-87</t>
         </is>
       </c>
       <c r="B409" s="7" t="inlineStr">
@@ -17069,17 +17069,17 @@
       </c>
       <c r="D409" s="9" t="inlineStr">
         <is>
-          <t>A copy says when its shared row was taken off the list</t>
+          <t>Bulk tick never UN-ticks</t>
         </is>
       </c>
       <c r="E409" s="9" t="inlineStr">
         <is>
-          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
+          <t>Select a mix of done and not-done rows and tap Done.</t>
         </is>
       </c>
       <c r="F409" s="9" t="inlineStr">
         <is>
-          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
+          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
         </is>
       </c>
       <c r="G409" s="7" t="inlineStr">
@@ -17094,7 +17094,7 @@
     <row r="410">
       <c r="A410" s="6" t="inlineStr">
         <is>
-          <t>OUR-92</t>
+          <t>OUR-88</t>
         </is>
       </c>
       <c r="B410" s="7" t="inlineStr">
@@ -17109,17 +17109,17 @@
       </c>
       <c r="D410" s="9" t="inlineStr">
         <is>
-          <t>That line never says who, and never says why</t>
+          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
         </is>
       </c>
       <c r="E410" s="9" t="inlineStr">
         <is>
-          <t>Read the line closely.</t>
+          <t>Select a repeating row along with others. Read the shelf.</t>
         </is>
       </c>
       <c r="F410" s="9" t="inlineStr">
         <is>
-          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
+          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
         </is>
       </c>
       <c r="G410" s="7" t="inlineStr">
@@ -17134,7 +17134,7 @@
     <row r="411">
       <c r="A411" s="6" t="inlineStr">
         <is>
-          <t>OUR-93</t>
+          <t>OUR-89</t>
         </is>
       </c>
       <c r="B411" s="7" t="inlineStr">
@@ -17149,17 +17149,17 @@
       </c>
       <c r="D411" s="9" t="inlineStr">
         <is>
-          <t>No line on a copy you already finished or removed</t>
+          <t>The pill steps aside for the select shelf</t>
         </is>
       </c>
       <c r="E411" s="9" t="inlineStr">
         <is>
-          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
+          <t>Enter select mode in the room with a few words waiting in the capture panel.</t>
         </is>
       </c>
       <c r="F411" s="9" t="inlineStr">
         <is>
-          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
+          <t>The pill is gone while selecting (the select shelf docks at the foot), and back when you cancel, still showing its waiting words. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
         </is>
       </c>
       <c r="G411" s="7" t="inlineStr">
@@ -17174,7 +17174,7 @@
     <row r="412">
       <c r="A412" s="6" t="inlineStr">
         <is>
-          <t>OUR-94</t>
+          <t>OUR-90</t>
         </is>
       </c>
       <c r="B412" s="7" t="inlineStr">
@@ -17189,17 +17189,17 @@
       </c>
       <c r="D412" s="9" t="inlineStr">
         <is>
-          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
+          <t>No select mode on a closed list</t>
         </is>
       </c>
       <c r="E412" s="9" t="inlineStr">
         <is>
-          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
+          <t>Open an archived list and hold a row.</t>
         </is>
       </c>
       <c r="F412" s="9" t="inlineStr">
         <is>
-          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
+          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
         </is>
       </c>
       <c r="G412" s="7" t="inlineStr">
@@ -17214,7 +17214,7 @@
     <row r="413">
       <c r="A413" s="6" t="inlineStr">
         <is>
-          <t>OUR-95</t>
+          <t>OUR-91</t>
         </is>
       </c>
       <c r="B413" s="7" t="inlineStr">
@@ -17229,17 +17229,17 @@
       </c>
       <c r="D413" s="9" t="inlineStr">
         <is>
-          <t>A row's note is VISIBLE, not only spoken</t>
+          <t>A copy says when its shared row was taken off the list</t>
         </is>
       </c>
       <c r="E413" s="9" t="inlineStr">
         <is>
-          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
+          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
         </is>
       </c>
       <c r="F413" s="9" t="inlineStr">
         <is>
-          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
+          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
         </is>
       </c>
       <c r="G413" s="7" t="inlineStr">
@@ -17254,7 +17254,7 @@
     <row r="414">
       <c r="A414" s="6" t="inlineStr">
         <is>
-          <t>OUR-96</t>
+          <t>OUR-92</t>
         </is>
       </c>
       <c r="B414" s="7" t="inlineStr">
@@ -17262,24 +17262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C414" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C414" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D414" s="9" t="inlineStr">
         <is>
-          <t>Rows WITHOUT a note are unchanged</t>
+          <t>That line never says who, and never says why</t>
         </is>
       </c>
       <c r="E414" s="9" t="inlineStr">
         <is>
-          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
+          <t>Read the line closely.</t>
         </is>
       </c>
       <c r="F414" s="9" t="inlineStr">
         <is>
-          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
+          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
         </is>
       </c>
       <c r="G414" s="7" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="415">
       <c r="A415" s="6" t="inlineStr">
         <is>
-          <t>OUR-97</t>
+          <t>OUR-93</t>
         </is>
       </c>
       <c r="B415" s="7" t="inlineStr">
@@ -17302,24 +17302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C415" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C415" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D415" s="9" t="inlineStr">
         <is>
-          <t>A tick after midnight lands on the RIGHT day</t>
+          <t>No line on a copy you already finished or removed</t>
         </is>
       </c>
       <c r="E415" s="9" t="inlineStr">
         <is>
-          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
+          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
         </is>
       </c>
       <c r="F415" s="9" t="inlineStr">
         <is>
-          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
+          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
         </is>
       </c>
       <c r="G415" s="7" t="inlineStr">
@@ -17334,7 +17334,7 @@
     <row r="416">
       <c r="A416" s="6" t="inlineStr">
         <is>
-          <t>OUR-98</t>
+          <t>OUR-94</t>
         </is>
       </c>
       <c r="B416" s="7" t="inlineStr">
@@ -17342,24 +17342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C416" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C416" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D416" s="9" t="inlineStr">
         <is>
-          <t>A tick made during a background sync is not undone</t>
+          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
         </is>
       </c>
       <c r="E416" s="9" t="inlineStr">
         <is>
-          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
+          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
         </is>
       </c>
       <c r="F416" s="9" t="inlineStr">
         <is>
-          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
+          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
         </is>
       </c>
       <c r="G416" s="7" t="inlineStr">
@@ -17374,7 +17374,7 @@
     <row r="417">
       <c r="A417" s="6" t="inlineStr">
         <is>
-          <t>OUR-99</t>
+          <t>OUR-95</t>
         </is>
       </c>
       <c r="B417" s="7" t="inlineStr">
@@ -17389,17 +17389,17 @@
       </c>
       <c r="D417" s="9" t="inlineStr">
         <is>
-          <t>A tick survives a device that has never opened the room</t>
+          <t>A row's note is VISIBLE, not only spoken</t>
         </is>
       </c>
       <c r="E417" s="9" t="inlineStr">
         <is>
-          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
+          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
         </is>
       </c>
       <c r="F417" s="9" t="inlineStr">
         <is>
-          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
+          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
         </is>
       </c>
       <c r="G417" s="7" t="inlineStr">
@@ -17414,7 +17414,7 @@
     <row r="418">
       <c r="A418" s="6" t="inlineStr">
         <is>
-          <t>OUR-100</t>
+          <t>OUR-96</t>
         </is>
       </c>
       <c r="B418" s="7" t="inlineStr">
@@ -17422,24 +17422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C418" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C418" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D418" s="9" t="inlineStr">
         <is>
-          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
+          <t>Rows WITHOUT a note are unchanged</t>
         </is>
       </c>
       <c r="E418" s="9" t="inlineStr">
         <is>
-          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
+          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
         </is>
       </c>
       <c r="F418" s="9" t="inlineStr">
         <is>
-          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
+          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
         </is>
       </c>
       <c r="G418" s="7" t="inlineStr">
@@ -17454,7 +17454,7 @@
     <row r="419">
       <c r="A419" s="6" t="inlineStr">
         <is>
-          <t>OUR-101</t>
+          <t>OUR-97</t>
         </is>
       </c>
       <c r="B419" s="7" t="inlineStr">
@@ -17462,24 +17462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C419" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C419" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D419" s="9" t="inlineStr">
         <is>
-          <t>A closed list stops promising it keeps trying</t>
+          <t>A tick after midnight lands on the RIGHT day</t>
         </is>
       </c>
       <c r="E419" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list that has unpushed local changes.</t>
+          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
         </is>
       </c>
       <c r="F419" s="9" t="inlineStr">
         <is>
-          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
+          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
         </is>
       </c>
       <c r="G419" s="7" t="inlineStr">
@@ -17494,7 +17494,7 @@
     <row r="420">
       <c r="A420" s="6" t="inlineStr">
         <is>
-          <t>OUR-102</t>
+          <t>OUR-98</t>
         </is>
       </c>
       <c r="B420" s="7" t="inlineStr">
@@ -17502,24 +17502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C420" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C420" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D420" s="9" t="inlineStr">
         <is>
-          <t>Setting a rhythm clears any date the row was carrying</t>
+          <t>A tick made during a background sync is not undone</t>
         </is>
       </c>
       <c r="E420" s="9" t="inlineStr">
         <is>
-          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
+          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F420" s="9" t="inlineStr">
         <is>
-          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
+          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
         </is>
       </c>
       <c r="G420" s="7" t="inlineStr">
@@ -17534,7 +17534,7 @@
     <row r="421">
       <c r="A421" s="6" t="inlineStr">
         <is>
-          <t>OUR-103</t>
+          <t>OUR-99</t>
         </is>
       </c>
       <c r="B421" s="7" t="inlineStr">
@@ -17542,24 +17542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C421" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C421" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D421" s="9" t="inlineStr">
         <is>
-          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
+          <t>A tick survives a device that has never opened the room</t>
         </is>
       </c>
       <c r="E421" s="9" t="inlineStr">
         <is>
-          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
+          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
         </is>
       </c>
       <c r="F421" s="9" t="inlineStr">
         <is>
-          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
+          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
         </is>
       </c>
       <c r="G421" s="7" t="inlineStr">
@@ -17574,7 +17574,7 @@
     <row r="422">
       <c r="A422" s="6" t="inlineStr">
         <is>
-          <t>OUR-104</t>
+          <t>OUR-100</t>
         </is>
       </c>
       <c r="B422" s="7" t="inlineStr">
@@ -17582,24 +17582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C422" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C422" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D422" s="9" t="inlineStr">
         <is>
-          <t>No dead reorder rail on shared rows</t>
+          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
         </is>
       </c>
       <c r="E422" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the room and in the From Ours strip.</t>
+          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
         </is>
       </c>
       <c r="F422" s="9" t="inlineStr">
         <is>
-          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
+          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
         </is>
       </c>
       <c r="G422" s="7" t="inlineStr">
@@ -17614,7 +17614,7 @@
     <row r="423">
       <c r="A423" s="6" t="inlineStr">
         <is>
-          <t>OUR-105</t>
+          <t>OUR-101</t>
         </is>
       </c>
       <c r="B423" s="7" t="inlineStr">
@@ -17622,24 +17622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C423" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C423" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D423" s="9" t="inlineStr">
         <is>
-          <t>First run introduces the shared list</t>
+          <t>A closed list stops promising it keeps trying</t>
         </is>
       </c>
       <c r="E423" s="9" t="inlineStr">
         <is>
-          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
+          <t>Open an archived list that has unpushed local changes.</t>
         </is>
       </c>
       <c r="F423" s="9" t="inlineStr">
         <is>
-          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
+          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
         </is>
       </c>
       <c r="G423" s="7" t="inlineStr">
@@ -17654,7 +17654,7 @@
     <row r="424">
       <c r="A424" s="6" t="inlineStr">
         <is>
-          <t>OUR-106</t>
+          <t>OUR-102</t>
         </is>
       </c>
       <c r="B424" s="7" t="inlineStr">
@@ -17662,24 +17662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C424" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C424" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D424" s="9" t="inlineStr">
         <is>
-          <t>Anyone can start a shared list, not just an allowlisted address</t>
+          <t>Setting a rhythm clears any date the row was carrying</t>
         </is>
       </c>
       <c r="E424" s="9" t="inlineStr">
         <is>
-          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
+          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
         </is>
       </c>
       <c r="F424" s="9" t="inlineStr">
         <is>
-          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
+          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
         </is>
       </c>
       <c r="G424" s="7" t="inlineStr">
@@ -17694,7 +17694,7 @@
     <row r="425">
       <c r="A425" s="6" t="inlineStr">
         <is>
-          <t>OUR-107</t>
+          <t>OUR-103</t>
         </is>
       </c>
       <c r="B425" s="7" t="inlineStr">
@@ -17702,24 +17702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C425" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C425" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D425" s="9" t="inlineStr">
         <is>
-          <t>The shared-list onboarding step can actually be REACHED</t>
+          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
         </is>
       </c>
       <c r="E425" s="9" t="inlineStr">
         <is>
-          <t>Replay the first run and press the primary button through every step without skipping.</t>
+          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
         </is>
       </c>
       <c r="F425" s="9" t="inlineStr">
         <is>
-          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
+          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
         </is>
       </c>
       <c r="G425" s="7" t="inlineStr">
@@ -17734,7 +17734,7 @@
     <row r="426">
       <c r="A426" s="6" t="inlineStr">
         <is>
-          <t>OUR-108</t>
+          <t>OUR-104</t>
         </is>
       </c>
       <c r="B426" s="7" t="inlineStr">
@@ -17742,24 +17742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C426" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C426" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D426" s="9" t="inlineStr">
         <is>
-          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
+          <t>No dead reorder rail on shared rows</t>
         </is>
       </c>
       <c r="E426" s="9" t="inlineStr">
         <is>
-          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
+          <t>Hold a row in the room and in the From Ours strip.</t>
         </is>
       </c>
       <c r="F426" s="9" t="inlineStr">
         <is>
-          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
+          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
         </is>
       </c>
       <c r="G426" s="7" t="inlineStr">
@@ -17774,7 +17774,7 @@
     <row r="427">
       <c r="A427" s="6" t="inlineStr">
         <is>
-          <t>OUR-109</t>
+          <t>OUR-105</t>
         </is>
       </c>
       <c r="B427" s="7" t="inlineStr">
@@ -17789,17 +17789,17 @@
       </c>
       <c r="D427" s="9" t="inlineStr">
         <is>
-          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
+          <t>First run introduces the shared list</t>
         </is>
       </c>
       <c r="E427" s="9" t="inlineStr">
         <is>
-          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
+          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
         </is>
       </c>
       <c r="F427" s="9" t="inlineStr">
         <is>
-          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
+          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
         </is>
       </c>
       <c r="G427" s="7" t="inlineStr">
@@ -17814,7 +17814,7 @@
     <row r="428">
       <c r="A428" s="6" t="inlineStr">
         <is>
-          <t>OUR-110</t>
+          <t>OUR-106</t>
         </is>
       </c>
       <c r="B428" s="7" t="inlineStr">
@@ -17829,17 +17829,17 @@
       </c>
       <c r="D428" s="9" t="inlineStr">
         <is>
-          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
+          <t>Anyone can start a shared list, not just an allowlisted address</t>
         </is>
       </c>
       <c r="E428" s="9" t="inlineStr">
         <is>
-          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
+          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
         </is>
       </c>
       <c r="F428" s="9" t="inlineStr">
         <is>
-          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
+          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
         </is>
       </c>
       <c r="G428" s="7" t="inlineStr">
@@ -17854,12 +17854,12 @@
     <row r="429">
       <c r="A429" s="6" t="inlineStr">
         <is>
-          <t>UPD-01</t>
+          <t>OUR-107</t>
         </is>
       </c>
       <c r="B429" s="7" t="inlineStr">
         <is>
-          <t>Updates</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C429" s="8" t="inlineStr">
@@ -17869,17 +17869,17 @@
       </c>
       <c r="D429" s="9" t="inlineStr">
         <is>
-          <t>Settings states the version, and up-to-date is a fact</t>
+          <t>The shared-list onboarding step can actually be REACHED</t>
         </is>
       </c>
       <c r="E429" s="9" t="inlineStr">
         <is>
-          <t>Open Settings and scroll to the foot.</t>
+          <t>Replay the first run and press the primary button through every step without skipping.</t>
         </is>
       </c>
       <c r="F429" s="9" t="inlineStr">
         <is>
-          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
+          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
         </is>
       </c>
       <c r="G429" s="7" t="inlineStr">
@@ -17894,37 +17894,37 @@
     <row r="430">
       <c r="A430" s="6" t="inlineStr">
         <is>
-          <t>UPD-02</t>
+          <t>OUR-108</t>
         </is>
       </c>
       <c r="B430" s="7" t="inlineStr">
         <is>
-          <t>Updates</t>
-        </is>
-      </c>
-      <c r="C430" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="C430" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D430" s="9" t="inlineStr">
         <is>
-          <t>Web offers a reload, and says drafts are kept</t>
+          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
         </is>
       </c>
       <c r="E430" s="9" t="inlineStr">
         <is>
-          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
+          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
         </is>
       </c>
       <c r="F430" s="9" t="inlineStr">
         <is>
-          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
+          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
         </is>
       </c>
       <c r="G430" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H430" s="7" t="inlineStr"/>
@@ -17934,12 +17934,12 @@
     <row r="431">
       <c r="A431" s="6" t="inlineStr">
         <is>
-          <t>UPD-03</t>
+          <t>OUR-109</t>
         </is>
       </c>
       <c r="B431" s="7" t="inlineStr">
         <is>
-          <t>Updates</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C431" s="8" t="inlineStr">
@@ -17949,22 +17949,22 @@
       </c>
       <c r="D431" s="9" t="inlineStr">
         <is>
-          <t>Native points at the store, and says lists are untouched</t>
+          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
         </is>
       </c>
       <c r="E431" s="9" t="inlineStr">
         <is>
-          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
+          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
         </is>
       </c>
       <c r="F431" s="9" t="inlineStr">
         <is>
-          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
+          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
         </is>
       </c>
       <c r="G431" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H431" s="7" t="inlineStr"/>
@@ -17974,32 +17974,32 @@
     <row r="432">
       <c r="A432" s="6" t="inlineStr">
         <is>
-          <t>UPD-04</t>
+          <t>OUR-110</t>
         </is>
       </c>
       <c r="B432" s="7" t="inlineStr">
         <is>
-          <t>Updates</t>
-        </is>
-      </c>
-      <c r="C432" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="C432" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D432" s="9" t="inlineStr">
         <is>
-          <t>Unreachable server says NOTHING, never 'up to date'</t>
+          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
         </is>
       </c>
       <c r="E432" s="9" t="inlineStr">
         <is>
-          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
+          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
         </is>
       </c>
       <c r="F432" s="9" t="inlineStr">
         <is>
-          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
+          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
         </is>
       </c>
       <c r="G432" s="7" t="inlineStr">
@@ -18014,7 +18014,7 @@
     <row r="433">
       <c r="A433" s="6" t="inlineStr">
         <is>
-          <t>UPD-05</t>
+          <t>UPD-01</t>
         </is>
       </c>
       <c r="B433" s="7" t="inlineStr">
@@ -18022,24 +18022,24 @@
           <t>Updates</t>
         </is>
       </c>
-      <c r="C433" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C433" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D433" s="9" t="inlineStr">
         <is>
-          <t>The goodnight mention is rare, and framed for the other person</t>
+          <t>Settings states the version, and up-to-date is a fact</t>
         </is>
       </c>
       <c r="E433" s="9" t="inlineStr">
         <is>
-          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
+          <t>Open Settings and scroll to the foot.</t>
         </is>
       </c>
       <c r="F433" s="9" t="inlineStr">
         <is>
-          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
+          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
         </is>
       </c>
       <c r="G433" s="7" t="inlineStr">
@@ -18054,46 +18054,206 @@
     <row r="434">
       <c r="A434" s="6" t="inlineStr">
         <is>
-          <t>OUR-12</t>
+          <t>UPD-02</t>
         </is>
       </c>
       <c r="B434" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C434" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="C434" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D434" s="9" t="inlineStr">
         <is>
-          <t>Unnamed lists read in each person's language</t>
+          <t>Web offers a reload, and says drafts are kept</t>
         </is>
       </c>
       <c r="E434" s="9" t="inlineStr">
         <is>
-          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
         </is>
       </c>
       <c r="F434" s="9" t="inlineStr">
         <is>
-          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
         </is>
       </c>
       <c r="G434" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H434" s="7" t="inlineStr"/>
       <c r="I434" s="9" t="inlineStr"/>
       <c r="J434" s="7" t="inlineStr"/>
     </row>
+    <row r="435">
+      <c r="A435" s="6" t="inlineStr">
+        <is>
+          <t>UPD-03</t>
+        </is>
+      </c>
+      <c r="B435" s="7" t="inlineStr">
+        <is>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="C435" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D435" s="9" t="inlineStr">
+        <is>
+          <t>Native points at the store, and says lists are untouched</t>
+        </is>
+      </c>
+      <c r="E435" s="9" t="inlineStr">
+        <is>
+          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
+        </is>
+      </c>
+      <c r="F435" s="9" t="inlineStr">
+        <is>
+          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
+        </is>
+      </c>
+      <c r="G435" s="7" t="inlineStr">
+        <is>
+          <t>Android</t>
+        </is>
+      </c>
+      <c r="H435" s="7" t="inlineStr"/>
+      <c r="I435" s="9" t="inlineStr"/>
+      <c r="J435" s="7" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="6" t="inlineStr">
+        <is>
+          <t>UPD-04</t>
+        </is>
+      </c>
+      <c r="B436" s="7" t="inlineStr">
+        <is>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="C436" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D436" s="9" t="inlineStr">
+        <is>
+          <t>Unreachable server says NOTHING, never 'up to date'</t>
+        </is>
+      </c>
+      <c r="E436" s="9" t="inlineStr">
+        <is>
+          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
+        </is>
+      </c>
+      <c r="F436" s="9" t="inlineStr">
+        <is>
+          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
+        </is>
+      </c>
+      <c r="G436" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H436" s="7" t="inlineStr"/>
+      <c r="I436" s="9" t="inlineStr"/>
+      <c r="J436" s="7" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="6" t="inlineStr">
+        <is>
+          <t>UPD-05</t>
+        </is>
+      </c>
+      <c r="B437" s="7" t="inlineStr">
+        <is>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="C437" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D437" s="9" t="inlineStr">
+        <is>
+          <t>The goodnight mention is rare, and framed for the other person</t>
+        </is>
+      </c>
+      <c r="E437" s="9" t="inlineStr">
+        <is>
+          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
+        </is>
+      </c>
+      <c r="F437" s="9" t="inlineStr">
+        <is>
+          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
+        </is>
+      </c>
+      <c r="G437" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H437" s="7" t="inlineStr"/>
+      <c r="I437" s="9" t="inlineStr"/>
+      <c r="J437" s="7" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="6" t="inlineStr">
+        <is>
+          <t>OUR-12</t>
+        </is>
+      </c>
+      <c r="B438" s="7" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="C438" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D438" s="9" t="inlineStr">
+        <is>
+          <t>Unnamed lists read in each person's language</t>
+        </is>
+      </c>
+      <c r="E438" s="9" t="inlineStr">
+        <is>
+          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+        </is>
+      </c>
+      <c r="F438" s="9" t="inlineStr">
+        <is>
+          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+        </is>
+      </c>
+      <c r="G438" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H438" s="7" t="inlineStr"/>
+      <c r="I438" s="9" t="inlineStr"/>
+      <c r="J438" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J434"/>
-  <conditionalFormatting sqref="H2:H434">
+  <autoFilter ref="A1:J438"/>
+  <conditionalFormatting sqref="H2:H438">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -18105,7 +18265,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H434" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
+    <dataValidation sqref="H2:H438" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
       <formula1>"Pass,Fail,Blocked,Not run"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18141,7 +18301,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>437</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18312,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF('Test Suite'!$H$2:$H$434,"Pass")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$438,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -18163,7 +18323,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF('Test Suite'!$H$2:$H$434,"Fail")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$438,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -18174,7 +18334,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Suite'!$H$2:$H$434,"Blocked")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$438,"Blocked")</f>
         <v/>
       </c>
     </row>
@@ -18185,7 +18345,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Suite'!$H$2:$H$434,"Not run")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$438,"Not run")</f>
         <v/>
       </c>
     </row>
@@ -18196,7 +18356,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>433-COUNTA('Test Suite'!$H$2:$H$434)</f>
+        <f>437-COUNTA('Test Suite'!$H$2:$H$438)</f>
         <v/>
       </c>
     </row>
@@ -18207,7 +18367,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF('Test Suite'!$C$2:$C$434,"P1")</f>
+        <f>COUNTIF('Test Suite'!$C$2:$C$438,"P1")</f>
         <v/>
       </c>
     </row>
@@ -18218,7 +18378,7 @@
         </is>
       </c>
       <c r="B10">
-        <f>COUNTIFS('Test Suite'!$C$2:$C$434,"P1",'Test Suite'!$H$2:$H$434,"Pass")</f>
+        <f>COUNTIFS('Test Suite'!$C$2:$C$438,"P1",'Test Suite'!$H$2:$H$438,"Pass")</f>
         <v/>
       </c>
     </row>

--- a/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
+++ b/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$438</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$439</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J438"/>
+  <dimension ref="A1:J439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4046,12 +4046,12 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Free account: open the Right now caret and read 'Plan my day'. Tap it. Back. Then: Chart a course &gt; Suggest steps; Settings &gt; a locked colour theme; Settings &gt; Quiet; long-press a task &gt; Pin.</t>
+          <t>Free account: open the Right now caret and read 'Plan my day'. Tap it. Back. Then: Chart a course &gt; Suggest steps; Settings &gt; a locked colour theme; long-press a task &gt; Pin.</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>Plan my day carries the honey ✦ mark (the same one Pin wears in the fold) and its screen-reader label says Premium. Every gate lands on the Premium page with one accent line under the title naming the feature that sent you ('Plan my day is part of Premium.', 'Chart a course is part of Premium.', 'Colour themes…', 'The Quiet look…', 'Pin…'). Opening Premium from the Menu or Settings directly shows no such line.</t>
+          <t>Plan my day carries the honey ✦ mark (the same one Pin wears in the fold) and its screen-reader label says Premium. Every gate lands on the Premium page with one accent line under the title naming the feature that sent you ('Plan my day is part of Premium.', 'Chart a course is part of Premium.', 'Colour themes…', 'Pin…'). Opening Premium from the Menu or Settings directly shows no such line.</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="F196" s="9" t="inlineStr">
         <is>
-          <t>'‹ Menu' at the top, then the unchanged title and line. Five sections, each a card under a serif heading: Comfort (Theme, Text size, Motion, Daily reminder with its time), Look (Colour theme and Interface, each marked '✦ Premium' in soft ink for a free user), AI (the status line, a 'Turn AI off ›' row, and, signed in, one 'AI agent access (MCP)' row), Access &amp; data (signed in: Account with your email as its value; then Export your data, Privacy &amp; data, Terms; signed in: Delete account and data last), then the Premium card, then Help (Send feedback, See the welcome again). Links are whole rows with a › in soft ink, never mauve text links. There is no Ours row any more. The footnote, version, update block and developer band are at the foot as before. In Quiet the cards lose their fill and border and the headings and hairlines do the separating.</t>
+          <t>'‹ Menu' at the top, then the unchanged title and line. Five sections, each a card under a serif heading: Comfort (Theme, Text size, Motion, Daily reminder with its time), Look (Colour theme marked '✦ Premium' in soft ink for a free user; Interface carries no mark), AI (the status line, a 'Turn AI off ›' row, and, signed in, one 'AI agent access (MCP)' row), Access &amp; data (signed in: Account with your email as its value; then Export your data, Privacy &amp; data, Terms; signed in: Delete account and data last), then the Premium card, then Help (Send feedback, See the welcome again). Links are whole rows with a › in soft ink, never mauve text links. There is no Ours row any more. The footnote, version, update block and developer band are at the foot as before. In Quiet the cards lose their fill and border and the headings and hairlines do the separating.</t>
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="F215" s="9" t="inlineStr">
         <is>
-          <t>The calm 'Keep every week' pitch, the A$5/mo price, the 1 -&gt; 2 -&gt; 4 tenure tiers. The feature list includes the personalisation pair (Quiet, the borderless look, and the seven colour themes) alongside Scan, Pin and the AI suite, so a user sent here from the Interface gate can see the thing they tapped.</t>
+          <t>The calm 'Keep every week' pitch, the A$5/mo price, the 1 -&gt; 2 -&gt; 4 tenure tiers. The feature list shows the seven colour themes alongside Scan, Pin and the AI suite, and does not list Quiet (Quiet is free for everyone, see QUI-01).</t>
         </is>
       </c>
       <c r="G215" s="7" t="inlineStr">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>On an Android phone (the new build), open Premium signed OUT, then signed in as a FREE account, then from each gate: Scan, Pin, Plan my day, a colour theme, Quiet, a second keepsake in a month, and Your patterns. Repeat once with TalkBack on, listening to every label.</t>
+          <t>On an Android phone (the new build), open Premium signed OUT, then signed in as a FREE account, then from each gate: Scan, Pin, Plan my day, a colour theme, a second keepsake in a month, and Your patterns. Repeat once with TalkBack on, listening to every label.</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
@@ -11349,17 +11349,17 @@
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>Premium unlocks the Quiet interface; free is gated</t>
+          <t>The Quiet interface is free, both ways</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>As premium (or with the dev Premium override on), open Settings -&gt; Comfort -&gt; 'Interface' and tap 'Quiet', then reload. Then as a FREE user, tap 'Quiet'.</t>
+          <t>As a FREE or signed-out user, open Settings -&gt; Look -&gt; 'Interface' and tap 'Quiet', then reload. Then tap 'Standard'. Then, as an account whose Premium or trial ended while it was on Quiet, open Settings -&gt; Look -&gt; 'Interface' and tap 'Standard'.</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>Premium: the whole Today surface goes borderless. Card outlines drop, and every action that looked like a button or a link renders as plain text with no outline or fill: the header Menu pill (which keeps just the word 'Menu', no dots), 'Focus on one thing', 'Lighten today', 'Close the day', and 'Plan my day' (which in Standard is the filled premium gradient) all become plain text (accent for the AI / premium ones, soft ink for the calm structural ones). The energy / weight-of-today gauge is KEPT, not removed: it shrinks to a 3px hairline bar so the day's load still reads at a glance. The choice survives reload with 'Quiet' ringed. 'Standard' is the default and looks identical to the app today (gradient button, 6px gauge, outlined actions all return). Free: the block shows a 'Premium' tag and tapping 'Quiet' routes to the paywall with NO change applied ('appearance.locked' logged). A lapsed subscriber keeps whichever appearance they chose.</t>
+          <t>The Interface row carries no '✦ Premium' tag and shows one hint ('Quiet strips the interface back to calm text. Standard keeps the cards and buttons.'). The change applies live in both directions, the paywall never opens, and 'appearance.locked' is never logged. In Quiet the whole Today surface goes borderless. Card outlines drop, and every action that looked like a button or a link renders as plain text with no outline or fill: the header Menu pill (which keeps just the word 'Menu', no dots), 'Focus on one thing', 'Lighten today', 'Close the day', and 'Plan my day' (which in Standard is the filled premium gradient) all become plain text (accent for the AI / premium ones, soft ink for the calm structural ones). The energy / weight-of-today gauge is KEPT, not removed: it shrinks to a 3px hairline bar so the day's load still reads at a glance. The choice survives reload with 'Quiet' ringed. 'Standard' is the default and looks identical to the app today (gradient button, 6px gauge, outlined actions all return). The account whose Premium or trial ended can leave Quiet with one tap: before 2026-09-27 every tap, Standard included, bounced to the paywall, so it was stuck in Quiet with no way out (and none at all on Android, whose Premium page sells nothing).</t>
         </is>
       </c>
       <c r="G266" s="7" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>Premium, Settings -&gt; Look -&gt; Interface -&gt; Quiet. Open Today and change Energy between Low, Normal and High.</t>
+          <t>Settings -&gt; Look -&gt; Interface -&gt; Quiet. Open Today and change Energy between Low, Normal and High.</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>BOTH appearances now give the same in-place card with the same actions in the same order (see TOD-07): there is no longer a Quiet model and a Standard model. Only the treatment differs: Quiet gets a soft wash with a rounded bleed, Standard the accent tint. Mark-as-a-lot and Pin act-and-dismiss (the row updates, the card closes). Pin shows only on Today one-off rows (not Later, not recurring), matching PIN-05; a lapsed subscriber still on Quiet who taps Pin is routed to the paywall, never wrongly pinned. 'Select more' closes the card and drops into multi-select with THIS task pre-selected ('1 selected'); Combine appears once a second task is selected. The one-time 'hold a task for more' coachmark in Quiet is a faint line with a small accent dot, not a filled pill.</t>
+          <t>BOTH appearances now give the same in-place card with the same actions in the same order (see TOD-07): there is no longer a Quiet model and a Standard model. Only the treatment differs: Quiet gets a soft wash with a rounded bleed, Standard the accent tint. Mark-as-a-lot and Pin act-and-dismiss (the row updates, the card closes). Pin shows only on Today one-off rows (not Later, not recurring), matching PIN-05; a free user on Quiet who taps Pin is routed to the paywall, never wrongly pinned. 'Select more' closes the card and drops into multi-select with THIS task pre-selected ('1 selected'); Combine appears once a second task is selected. The one-time 'hold a task for more' coachmark in Quiet is a faint line with a small accent dot, not a filled pill.</t>
         </is>
       </c>
       <c r="G269" s="7" t="inlineStr">
@@ -11574,12 +11574,12 @@
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>PIN-01</t>
+          <t>QUI-07</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
         <is>
-          <t>Pin</t>
+          <t>Interface</t>
         </is>
       </c>
       <c r="C272" s="8" t="inlineStr">
@@ -11589,17 +11589,17 @@
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Premium: pin a task as the day's one thing</t>
+          <t>A free account turns Quiet on in Settings, and nothing mentions Premium</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>As premium (or with the dev Premium override on), tap-and-hold a one-off task to select it, then tap 'Pin' in the held row's actions.</t>
+          <t>Signed in as a FREE account (no trial, no dev override), open Settings -&gt; Look -&gt; 'Interface'. Read the row, then tap 'Quiet'. Open Premium from the Settings card and read the feature list. Replay the welcome from Settings to its Premium screen, once with AI on and once with AI off. Then, still in Quiet, look at every Premium mark that remains: Plan my day in Right now and in the tools panel, the dimmed Pin in the More fold of a held task, the Colour theme row and the Premium card in Settings, and the energy allowance line (use 'What fits right now?' until it reads '10 of your 15 free picks left this month.').</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>The task gets a calm mauve PIN MARK (a drawn pushpin; the star it replaced read as favourite, not pin, per Melroy 2026-08-30, and a drawn SVG cannot hit the iOS missing-glyph failure the round-one flag did) and the thick accent border, and floats to the top of Today. 'Focus on one thing' then opens straight to it.</t>
+          <t>The Interface row has no '✦ Premium' tag and its hint never says Premium. Tapping 'Quiet' applies at once, with no paywall and nothing in the row naming Premium. The Premium page does not list Quiet, and the welcome's Premium screen does not list 'Quiet interface' (with AI off it shows just Your colour and Pin). In Quiet every remaining Premium mark still reads: Plan my day keeps its honey ✦ in Right now and in the tools panel, Pin stays dimmed with its ✦ in the More fold, the Colour theme row keeps its soft-ink '✦ Premium', the Premium card keeps its gradient with a clear white label, and the energy allowance line is legible. Until 2026-09-27 only subscribers ever saw Quiet, so these had never been looked at by a free user.</t>
         </is>
       </c>
       <c r="G272" s="7" t="inlineStr">
@@ -11614,7 +11614,7 @@
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>PIN-02</t>
+          <t>PIN-01</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
@@ -11629,17 +11629,17 @@
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Free: Pin routes to the upsell, never pins</t>
+          <t>Premium: pin a task as the day's one thing</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>As a free user, select a single one-off task and tap the dimmed 'Pin' action.</t>
+          <t>As premium (or with the dev Premium override on), tap-and-hold a one-off task to select it, then tap 'Pin' in the held row's actions.</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>No task is pinned, and the Premium screen opens calmly (never a shaming wall). A 'premium.gate_hit' with reason 'pin' is logged.</t>
+          <t>The task gets a calm mauve PIN MARK (a drawn pushpin; the star it replaced read as favourite, not pin, per Melroy 2026-08-30, and a drawn SVG cannot hit the iOS missing-glyph failure the round-one flag did) and the thick accent border, and floats to the top of Today. 'Focus on one thing' then opens straight to it.</t>
         </is>
       </c>
       <c r="G273" s="7" t="inlineStr">
@@ -11654,7 +11654,7 @@
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>PIN-03</t>
+          <t>PIN-02</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -11662,24 +11662,24 @@
           <t>Pin</t>
         </is>
       </c>
-      <c r="C274" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C274" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>Only one task is pinned at a time</t>
+          <t>Free: Pin routes to the upsell, never pins</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>As premium, pin task A, then hold task B and pin it.</t>
+          <t>As a free user, select a single one-off task and tap the dimmed 'Pin' action.</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>Task B is now pinned (pin-marked, floated to the top), and task A is no longer pinned. At most one pin ever exists.</t>
+          <t>No task is pinned, and the Premium screen opens calmly (never a shaming wall). A 'premium.gate_hit' with reason 'pin' is logged.</t>
         </is>
       </c>
       <c r="G274" s="7" t="inlineStr">
@@ -11694,7 +11694,7 @@
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>PIN-04</t>
+          <t>PIN-03</t>
         </is>
       </c>
       <c r="B275" s="7" t="inlineStr">
@@ -11709,17 +11709,17 @@
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>A pin syncs across devices</t>
+          <t>Only one task is pinned at a time</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>As premium and signed in, pin a task, then sign out and back in (or open a second device).</t>
+          <t>As premium, pin task A, then hold task B and pin it.</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>The task is still pinned after the sync round-trip (the pin mark and float persist). Needs the pinned_at column applied in Supabase.</t>
+          <t>Task B is now pinned (pin-marked, floated to the top), and task A is no longer pinned. At most one pin ever exists.</t>
         </is>
       </c>
       <c r="G275" s="7" t="inlineStr">
@@ -11734,7 +11734,7 @@
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>PIN-05</t>
+          <t>PIN-04</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
@@ -11742,24 +11742,24 @@
           <t>Pin</t>
         </is>
       </c>
-      <c r="C276" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C276" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Pin is offered only on one-off Today rows</t>
+          <t>A pin syncs across devices</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>Hold a recurring task, then hold a task in the 'Later' list.</t>
+          <t>As premium and signed in, pin a task, then sign out and back in (or open a second device).</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>No 'Pin' action appears on a recurring task's held card, and a Later task's card carries no Pin either (pinning is Today-only and one-offs only).</t>
+          <t>The task is still pinned after the sync round-trip (the pin mark and float persist). Needs the pinned_at column applied in Supabase.</t>
         </is>
       </c>
       <c r="G276" s="7" t="inlineStr">
@@ -11774,32 +11774,32 @@
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>NRG-01</t>
+          <t>PIN-05</t>
         </is>
       </c>
       <c r="B277" s="7" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C277" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Pin</t>
+        </is>
+      </c>
+      <c r="C277" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>What fits right now: one question, one pick, propose-only</t>
+          <t>Pin is offered only on one-off Today rows</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>With AI on and 2+ open one-off tasks, tap 'Focus on one thing'; in the 'Which one?' picker, 'What fits right now?' sits above the task choices in a soft hairline pill (its border makes it read as tappable; it lives INSIDE Focus, not as a standalone Today button). Tap it, pick an energy level (Running low / Somewhere in between / Feeling good). Then tap 'Start with this'; separately try 'Not now'.</t>
+          <t>Hold a recurring task, then hold a task in the 'Later' list.</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>A calm one-question card with the privacy line ('Your open tasks go to Claude to pick one. Nothing is added or changed.'). Choosing a level shows ONE task from today's list with a short warm line on why it fits (never shaming, never about what's undone). 'Start with this' opens Focus mode on exactly that task; 'Not now' just closes, nothing changed. A failed call shows a calm 'Couldn't find a pick just now.' line and does NOT spend a free pick. The entry hides when AI is off or fewer than 2 tasks are open. Needs the Worker deployed with /energy.</t>
+          <t>No 'Pin' action appears on a recurring task's held card, and a Later task's card carries no Pin either (pinning is Today-only and one-offs only).</t>
         </is>
       </c>
       <c r="G277" s="7" t="inlineStr">
@@ -11814,7 +11814,7 @@
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>NRG-02</t>
+          <t>NRG-01</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>The freemium meter: 15 a month, reminders at 10 and 5, then the paywall</t>
+          <t>What fits right now: one question, one pick, propose-only</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>As a FREE user, use energy matching repeatedly in one calendar month (seed doubledone.energyUses.v1 to fast-forward). Watch the 10-left and 5-left moments, then the 16th tap. Then as premium, use it well past 15.</t>
+          <t>With AI on and 2+ open one-off tasks, tap 'Focus on one thing'; in the 'Which one?' picker, 'What fits right now?' sits above the task choices in a soft hairline pill (its border makes it read as tappable; it lives INSIDE Focus, not as a standalone Today button). Tap it, pick an energy level (Running low / Somewhere in between / Feeling good). Then tap 'Start with this'; separately try 'Not now'.</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>Each successful pick spends one of 15 free picks a calendar month (counted locally, like the scrapbook gate). Exactly at 10 left and at 5 left, the result shows one calm line: '10 of your 15 free picks left this month.' (then 5). Past 15, tapping the entry routes to the paywall (which lists 'Energy matching without limits'), never a shaming wall, and no AI call is made ('premium.gate_hit' reason 'energy' logs). The counter resets on the 1st of the month with no carry-over. Premium is unlimited and never sees a counter line.</t>
+          <t>A calm one-question card with the privacy line ('Your open tasks go to Claude to pick one. Nothing is added or changed.'). Choosing a level shows ONE task from today's list with a short warm line on why it fits (never shaming, never about what's undone). 'Start with this' opens Focus mode on exactly that task; 'Not now' just closes, nothing changed. A failed call shows a calm 'Couldn't find a pick just now.' line and does NOT spend a free pick. The entry hides when AI is off or fewer than 2 tasks are open. Needs the Worker deployed with /energy.</t>
         </is>
       </c>
       <c r="G278" s="7" t="inlineStr">
@@ -11854,12 +11854,12 @@
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>OCR-01</t>
+          <t>NRG-02</t>
         </is>
       </c>
       <c r="B279" s="7" t="inlineStr">
         <is>
-          <t>Scan</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C279" s="8" t="inlineStr">
@@ -11869,17 +11869,17 @@
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>Premium: the Scan button opens the camera</t>
+          <t>The freemium meter: 15 a month, reminders at 10 and 5, then the paywall</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>As premium, tap the + pill and then Scan (camera) beside Speak in the panel.</t>
+          <t>As a FREE user, use energy matching repeatedly in one calendar month (seed doubledone.energyUses.v1 to fast-forward). Watch the 10-left and 5-left moments, then the 16th tap. Then as premium, use it well past 15.</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>The camera screen opens: a live viewfinder with a shutter and a Photos shortcut on a device, or a 'Choose a photo' prompt on web. No paywall.</t>
+          <t>Each successful pick spends one of 15 free picks a calendar month (counted locally, like the scrapbook gate). Exactly at 10 left and at 5 left, the result shows one calm line: '10 of your 15 free picks left this month.' (then 5). Past 15, tapping the entry routes to the paywall (which lists 'Energy matching without limits'), never a shaming wall, and no AI call is made ('premium.gate_hit' reason 'energy' logs). The counter resets on the 1st of the month with no carry-over. Premium is unlimited and never sees a counter line.</t>
         </is>
       </c>
       <c r="G279" s="7" t="inlineStr">
@@ -11894,7 +11894,7 @@
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>OCR-02</t>
+          <t>OCR-01</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -11909,17 +11909,17 @@
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Free: Scan routes to the upsell, never opens the camera</t>
+          <t>Premium: the Scan button opens the camera</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>As a free user, tap the + pill and then Scan in the panel.</t>
+          <t>As premium, tap the + pill and then Scan (camera) beside Speak in the panel.</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>Routed to the Premium screen calmly (never a wall). A 'premium.gate_hit' with reason 'ocr' is logged. No camera opens.</t>
+          <t>The camera screen opens: a live viewfinder with a shutter and a Photos shortcut on a device, or a 'Choose a photo' prompt on web. No paywall.</t>
         </is>
       </c>
       <c r="G280" s="7" t="inlineStr">
@@ -11934,7 +11934,7 @@
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>OCR-03</t>
+          <t>OCR-02</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
@@ -11949,22 +11949,22 @@
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Photograph a list and the tasks land in the box</t>
+          <t>Free: Scan routes to the upsell, never opens the camera</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>As premium on a device, tap Scan, photograph a short printed or handwritten list (fill the frame), wait for 'Reading your list...'.</t>
+          <t>As a free user, tap the + pill and then Scan in the panel.</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>The tasks it reads appear in the brain-dump box, one per line, editable. Nothing is auto-added to Today, and tapping Add commits them. An 'ocr.captured' event is logged.</t>
+          <t>Routed to the Premium screen calmly (never a wall). A 'premium.gate_hit' with reason 'ocr' is logged. No camera opens.</t>
         </is>
       </c>
       <c r="G281" s="7" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H281" s="7" t="inlineStr"/>
@@ -11974,7 +11974,7 @@
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>OCR-04</t>
+          <t>OCR-03</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -11982,29 +11982,29 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="C282" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C282" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>Gallery fallback reads an existing photo</t>
+          <t>Photograph a list and the tasks land in the box</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>Tap Scan, then 'Photos' (device) or 'Choose a photo' (web), and pick a photo of a list, a note, or a whiteboard.</t>
+          <t>As premium on a device, tap Scan, photograph a short printed or handwritten list (fill the frame), wait for 'Reading your list...'.</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>Same result: the read tasks land in the box for review. Covers a screenshot of a texted list, or a photo taken earlier.</t>
+          <t>The tasks it reads appear in the brain-dump box, one per line, editable. Nothing is auto-added to Today, and tapping Add commits them. An 'ocr.captured' event is logged.</t>
         </is>
       </c>
       <c r="G282" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="H282" s="7" t="inlineStr"/>
@@ -12014,7 +12014,7 @@
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>OCR-05</t>
+          <t>OCR-04</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
@@ -12029,17 +12029,17 @@
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>An unreadable photo fails calmly</t>
+          <t>Gallery fallback reads an existing photo</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>Scan a blank, blurry, or list-free image.</t>
+          <t>Tap Scan, then 'Photos' (device) or 'Choose a photo' (web), and pick a photo of a list, a note, or a whiteboard.</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>A calm line ('I couldn't read any tasks from that. Try again...'), the camera stays open, never a crash and never a shaming message.</t>
+          <t>Same result: the read tasks land in the box for review. Covers a screenshot of a texted list, or a photo taken earlier.</t>
         </is>
       </c>
       <c r="G283" s="7" t="inlineStr">
@@ -12054,7 +12054,7 @@
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>OCR-06</t>
+          <t>OCR-05</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -12069,22 +12069,22 @@
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>Camera denial is never a dead end</t>
+          <t>An unreadable photo fails calmly</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>On a device, deny the camera permission when prompted.</t>
+          <t>Scan a blank, blurry, or list-free image.</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>A calm screen offers 'Allow camera' and 'Choose from photos instead', and the gallery path still reads a list.</t>
+          <t>A calm line ('I couldn't read any tasks from that. Try again...'), the camera stays open, never a crash and never a shaming message.</t>
         </is>
       </c>
       <c r="G284" s="7" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H284" s="7" t="inlineStr"/>
@@ -12094,7 +12094,7 @@
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>OCR-07</t>
+          <t>OCR-06</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
@@ -12102,29 +12102,29 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="C285" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C285" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>AI egress is disclosed at the point of use</t>
+          <t>Camera denial is never a dead end</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>Open the Scan screen (device or web).</t>
+          <t>On a device, deny the camera permission when prompted.</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>The note 'Your photo is sent to the AI to read your list, then discarded. It is never stored.' is visible. The D1 'ocr' telemetry row holds only the image size and task count, never the image or the titles.</t>
+          <t>A calm screen offers 'Allow camera' and 'Choose from photos instead', and the gallery path still reads a list.</t>
         </is>
       </c>
       <c r="G285" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="H285" s="7" t="inlineStr"/>
@@ -12134,32 +12134,32 @@
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>CHART-01</t>
+          <t>OCR-07</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
         <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C286" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Scan</t>
+        </is>
+      </c>
+      <c r="C286" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>Premium: chart a course toward a goal</t>
+          <t>AI egress is disclosed at the point of use</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>As premium (or dev Premium override on), open Rooms, tap 'Chart a course', type a goal like 'get fit for a 10k', tap 'Suggest steps'.</t>
+          <t>Open the Scan screen (device or web).</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>A calm one-line heading plus 3-7 ticked next steps appear, and nothing is added yet. Tapping 'Add N tasks' lands them on Today (the first undated, later ones spread forward), each an ordinary task, and returns to Today. The 'chart.requested' then 'chart.added' events are logged.</t>
+          <t>The note 'Your photo is sent to the AI to read your list, then discarded. It is never stored.' is visible. The D1 'ocr' telemetry row holds only the image size and task count, never the image or the titles.</t>
         </is>
       </c>
       <c r="G286" s="7" t="inlineStr">
@@ -12174,7 +12174,7 @@
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>CHART-02</t>
+          <t>CHART-01</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -12189,17 +12189,17 @@
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Free: charting routes to the upsell, never plans</t>
+          <t>Premium: chart a course toward a goal</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>As a free user, open the Menu, tap 'Chart a course', type a goal, pick a timeframe, tap 'Suggest steps', then come back.</t>
+          <t>As premium (or dev Premium override on), open Rooms, tap 'Chart a course', type a goal like 'get fit for a 10k', tap 'Suggest steps'.</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>Before the tap the room already says '✦ Suggesting steps is part of Premium.' under the button, once and static. The tap routes to the Premium screen calmly (never a wall), and a 'premium.gate_hit' with reason 'chart' is logged. No plan is generated and nothing is added. Coming back, the goal and the chosen timeframe are still there, including after a purchase: on the phone the Premium panel's way out reads '‹ Chart a course', and on web a checkout round-trip brings the goal back the next time the room opens. Nothing is locked, blurred or priced.</t>
+          <t>A calm one-line heading plus 3-7 ticked next steps appear, and nothing is added yet. Tapping 'Add N tasks' lands them on Today (the first undated, later ones spread forward), each an ordinary task, and returns to Today. The 'chart.requested' then 'chart.added' events are logged.</t>
         </is>
       </c>
       <c r="G287" s="7" t="inlineStr">
@@ -12214,7 +12214,7 @@
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>CHART-03</t>
+          <t>CHART-02</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -12222,24 +12222,24 @@
           <t>Chart</t>
         </is>
       </c>
-      <c r="C288" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C288" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Propose-then-accept: nothing auto-adds</t>
+          <t>Free: charting routes to the upsell, never plans</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>As premium, generate a plan, untick two steps, then tap 'Add'. Separately, generate a plan and back out with 'Not these, start over' or Back.</t>
+          <t>As a free user, open the Menu, tap 'Chart a course', type a goal, pick a timeframe, tap 'Suggest steps', then come back.</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>Only the ticked steps are added as plain tasks, and backing out adds nothing. Today was unchanged before accepting.</t>
+          <t>Before the tap the room already says '✦ Suggesting steps is part of Premium.' under the button, once and static. The tap routes to the Premium screen calmly (never a wall), and a 'premium.gate_hit' with reason 'chart' is logged. No plan is generated and nothing is added. Coming back, the goal and the chosen timeframe are still there, including after a purchase: on the phone the Premium panel's way out reads '‹ Chart a course', and on web a checkout round-trip brings the goal back the next time the room opens. Nothing is locked, blurred or priced.</t>
         </is>
       </c>
       <c r="G288" s="7" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>CHART-04</t>
+          <t>CHART-03</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -12269,17 +12269,17 @@
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>A goal that cannot be mapped fails calmly</t>
+          <t>Propose-then-accept: nothing auto-adds</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>Enter an empty goal (the button is disabled), then a nonsensical goal and submit.</t>
+          <t>As premium, generate a plan, untick two steps, then tap 'Add'. Separately, generate a plan and back out with 'Not these, start over' or Back.</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>The empty case cannot submit. A nonsensical goal shows one calm line ('I couldn't map that out just now'), the goal stays editable, never a crash or a shaming message.</t>
+          <t>Only the ticked steps are added as plain tasks, and backing out adds nothing. Today was unchanged before accepting.</t>
         </is>
       </c>
       <c r="G289" s="7" t="inlineStr">
@@ -12294,7 +12294,7 @@
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>CHART-05</t>
+          <t>CHART-04</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -12309,17 +12309,17 @@
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>A deadline spreads the steps across the timeframe</t>
+          <t>A goal that cannot be mapped fails calmly</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>As premium, type a goal, tap a 'By when?' chip (e.g. 'In 2 months'), then Suggest steps and Add.</t>
+          <t>Enter an empty goal (the button is disabled), then a nonsensical goal and submit.</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>The steps are paced for that timeframe, and the accepted tasks spread from Today out to the chosen date (not crammed into the next few days). 'No deadline' keeps the gentle one-per-day default.</t>
+          <t>The empty case cannot submit. A nonsensical goal shows one calm line ('I couldn't map that out just now'), the goal stays editable, never a crash or a shaming message.</t>
         </is>
       </c>
       <c r="G290" s="7" t="inlineStr">
@@ -12334,7 +12334,7 @@
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>CHART-06</t>
+          <t>CHART-05</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
@@ -12349,17 +12349,17 @@
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>The timeframe stays named once the steps arrive</t>
+          <t>A deadline spreads the steps across the timeframe</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>Premium. Type a goal, pick 'In 2 months', Suggest steps. Then 'Not these, start over', pick no deadline, and suggest again.</t>
+          <t>As premium, type a goal, tap a 'By when?' chip (e.g. 'In 2 months'), then Suggest steps and Add.</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>Once the steps arrive the chips step aside, and one quiet line above the heading keeps the choice named: 'By when · In 2 months' (then 'By when · No deadline'). The AI's heading is in italic serif; every step starts ticked, each with its minutes and a ✕. The button counts only what will be added.</t>
+          <t>The steps are paced for that timeframe, and the accepted tasks spread from Today out to the chosen date (not crammed into the next few days). 'No deadline' keeps the gentle one-per-day default.</t>
         </is>
       </c>
       <c r="G291" s="7" t="inlineStr">
@@ -12374,7 +12374,7 @@
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>CHART-07</t>
+          <t>CHART-06</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -12389,17 +12389,17 @@
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>The steps show where they landed on Today</t>
+          <t>The timeframe stays named once the steps arrive</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>Premium. Chart a course, accept the steps with 'Add N tasks'.</t>
+          <t>Premium. Type a goal, pick 'In 2 months', Suggest steps. Then 'Not these, start over', pick no deadline, and suggest again.</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>You land on Today (never back on the spent proposal; back from Today does not return to it). The first step is on Today carrying the soft 'just added' tint, which fades away after a couple of seconds. The rest wait on their days.</t>
+          <t>Once the steps arrive the chips step aside, and one quiet line above the heading keeps the choice named: 'By when · In 2 months' (then 'By when · No deadline'). The AI's heading is in italic serif; every step starts ticked, each with its minutes and a ✕. The button counts only what will be added.</t>
         </is>
       </c>
       <c r="G292" s="7" t="inlineStr">
@@ -12414,7 +12414,7 @@
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>CHART-08</t>
+          <t>CHART-07</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
@@ -12422,24 +12422,24 @@
           <t>Chart</t>
         </is>
       </c>
-      <c r="C293" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C293" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>The small marks read on paper</t>
+          <t>The steps show where they landed on Today</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>In light mode, open Chart a course, get a proposal, and look at an unticked box, a step's minutes, the ✕, the spread note and the note at the foot. Then look at a selected timeframe chip.</t>
+          <t>Premium. Chart a course, accept the steps with 'Add N tasks'.</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>All of them read clearly (they moved from the faintest ink to the soft ink). The instruction under the title is in full ink. A selected chip keeps its tinted fill and border, and its label is ink rather than the accent, which was too faint on the tint. In dark mode the selected label stays the accent.</t>
+          <t>You land on Today (never back on the spent proposal; back from Today does not return to it). The first step is on Today carrying the soft 'just added' tint, which fades away after a couple of seconds. The rest wait on their days.</t>
         </is>
       </c>
       <c r="G293" s="7" t="inlineStr">
@@ -12454,32 +12454,32 @@
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>SEQ-01</t>
+          <t>CHART-08</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
         <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="C294" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C294" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>Premium: Plan my day suggests a calm sequence</t>
+          <t>The small marks read on paper</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>As premium with 3+ open one-off tasks on Today, tap 'Plan my day'. Answer the questions it asks first (or skip them).</t>
+          <t>In light mode, open Chart a course, get a proposal, and look at an unticked box, a step's minutes, the ✕, the spread note and the note at the foot. Then look at a selected timeframe chip.</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>A proposal card lists today's tasks in a suggested order, each with a short calm reason. Nothing reorders until 'Use this order' is tapped, then the list re-sequences in place (no dates change, no task moves to another day). A 'sequence.accepted' event is logged.</t>
+          <t>All of them read clearly (they moved from the faintest ink to the soft ink). The instruction under the title is in full ink. A selected chip keeps its tinted fill and border, and its label is ink rather than the accent, which was too faint on the tint. In dark mode the selected label stays the accent.</t>
         </is>
       </c>
       <c r="G294" s="7" t="inlineStr">
@@ -12494,12 +12494,12 @@
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>TOD-27</t>
+          <t>SEQ-01</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Sequence</t>
         </is>
       </c>
       <c r="C295" s="8" t="inlineStr">
@@ -12509,17 +12509,17 @@
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>Right now: one card near the top, a clock-set slot, the tools open downward, Energy pills</t>
+          <t>Premium: Plan my day suggests a calm sequence</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>Open Today in the MORNING (before 11), around MIDDAY (11-17), and in the EVENING (17+), reading the 'RIGHT NOW' card under Energy each time. Tap the caret at its right. Add and complete tasks and watch whether ANY control moves. Tap an unavailable (faded) tool. Set the Energy pills to High on a 7-task day and re-open the caret; set Low and read the gauge. Reload the app and check the pill. Turn AI off in Settings and re-open the caret. Also check with 0 tasks, in select mode, while typing in the composer, and after closing the day.</t>
+          <t>As premium with 3+ open one-off tasks on Today, tap 'Plan my day'. Answer the questions it asks first (or skip them).</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>ONE card sits under the Energy pills, near the top: an overline 'RIGHT NOW' + the tool that suits the HOUR (morning: Plan my day; midday: Focus on one thing; evening: Close the day), plus a caret ('All day tools'). The occupant is set by the CLOCK at open and never changes mid-session; it NEVER shows Lighten today. The caret opens the tools DOWNWARD inside the same card, in the same day order every time: Plan my day, Focus on one thing, Lighten today, Settle, Close the day, the current occupant tagged 'now', Plan my day wearing the honey ✦ when you are not Premium. The list moves down to make room and nothing covers it (no dim, no scrim). NOTHING in the card appears, vanishes or slides as tasks are added or completed: an unavailable tool stays in place at lowered contrast and tapping it explains in one plain line what the TOOL needs ('Plan my day needs two or more tasks.' / 'Lighten today is for a full day.'), never what the person lacks. The Energy pills (Low/Normal/High) sit under a small 'ENERGY' overline with the gauge above, on EVERY open day, including an empty one ('A clear day.'). A fresh day defaults to Normal. High re-scales what 'full' means, Low IS the low-capacity day, and the choice survives a reload but RESETS to Normal next morning. With AI OFF the card holds only the non-AI tools (AI tools are gone, not faded). In select mode the card RESTS (dimmed, does not respond) rather than vanishing, so the list does not jump. While the composer is open the card steps aside with the rest of the heading. On a closed day it is gone.</t>
+          <t>A proposal card lists today's tasks in a suggested order, each with a short calm reason. Nothing reorders until 'Use this order' is tapped, then the list re-sequences in place (no dates change, no task moves to another day). A 'sequence.accepted' event is logged.</t>
         </is>
       </c>
       <c r="G295" s="7" t="inlineStr">
@@ -12534,7 +12534,7 @@
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>TOD-28</t>
+          <t>TOD-27</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -12542,24 +12542,24 @@
           <t>Today</t>
         </is>
       </c>
-      <c r="C296" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C296" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>The rested screen mentions the scrapbook once, at the earned moment (the ladder's last rung)</t>
+          <t>Right now: one card near the top, a clock-set slot, the tools open downward, Energy pills</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>With AI on, the reminder and widget asks already spent (or reminder on, widget placed), NO scrapbook ever made, and at least 3 finishes this week, close the day and read the rested screen. Tap 'See your Calendar'. Then close a day again on another evening. Separately: repeat with AI off, and repeat with only 1-2 finishes.</t>
+          <t>Open Today in the MORNING (before 11), around MIDDAY (11-17), and in the EVENING (17+), reading the 'RIGHT NOW' card under Energy each time. Tap the caret at its right. Add and complete tasks and watch whether ANY control moves. Tap an unavailable (faded) tool. Set the Energy pills to High on a 7-task day and re-open the caret; set Low and read the gauge. Reload the app and check the pill. Turn AI off in Settings and re-open the caret. Also check with 0 tasks, in select mode, while typing in the composer, and after closing the day.</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>One calm mention appears under the goodnight text: 'You've finished enough this week to make a keepsake of it. It's waiting in your Calendar.' with 'See your Calendar' and 'Not now'. Either answer spends the mention FOREVER (it is the third and LAST rung of the one-ask-at-a-time ladder; reminder and widget always win the evening if pending). 'See your Calendar' opens the Calendar where the scrapbook lives. It never shows with AI off, never with fewer than 3 finishes this week, never to someone who has already made a scrapbook, and never twice.</t>
+          <t>ONE card sits under the Energy pills, near the top: an overline 'RIGHT NOW' + the tool that suits the HOUR (morning: Plan my day; midday: Focus on one thing; evening: Close the day), plus a caret ('All day tools'). The occupant is set by the CLOCK at open and never changes mid-session; it NEVER shows Lighten today. The caret opens the tools DOWNWARD inside the same card, in the same day order every time: Plan my day, Focus on one thing, Lighten today, Settle, Close the day, the current occupant tagged 'now', Plan my day wearing the honey ✦ when you are not Premium. The list moves down to make room and nothing covers it (no dim, no scrim). NOTHING in the card appears, vanishes or slides as tasks are added or completed: an unavailable tool stays in place at lowered contrast and tapping it explains in one plain line what the TOOL needs ('Plan my day needs two or more tasks.' / 'Lighten today is for a full day.'), never what the person lacks. The Energy pills (Low/Normal/High) sit under a small 'ENERGY' overline with the gauge above, on EVERY open day, including an empty one ('A clear day.'). A fresh day defaults to Normal. High re-scales what 'full' means, Low IS the low-capacity day, and the choice survives a reload but RESETS to Normal next morning. With AI OFF the card holds only the non-AI tools (AI tools are gone, not faded). In select mode the card RESTS (dimmed, does not respond) rather than vanishing, so the list does not jump. While the composer is open the card steps aside with the rest of the heading. On a closed day it is gone.</t>
         </is>
       </c>
       <c r="G296" s="7" t="inlineStr">
@@ -12574,32 +12574,32 @@
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>SEQ-07</t>
+          <t>TOD-28</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
         <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="C297" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="C297" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>Plan my day asks about the day BEFORE it sorts</t>
+          <t>The rested screen mentions the scrapbook once, at the earned moment (the ladder's last rung)</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>As premium, tap 'Plan my day'. Read the sheet that opens. Tap an answer, then tap the SAME answer again. Try sorting with all three answered, with only one answered, and with none answered ('Sort today' straight away). Also tap 'Not now'. Separately, as a FREE user, tap 'Plan my day'.</t>
+          <t>With AI on, the reminder and widget asks already spent (or reminder on, widget placed), NO scrapbook ever made, and at least 3 finishes this week, close the day and read the rested screen. Tap 'See your Calendar'. Then close a day again on another evening. Separately: repeat with AI off, and repeat with only 1-2 finishes.</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>Before any sorting, a calm sheet asks three OPTIONAL questions: 'How's your energy?' (Running low / Somewhere in between / Feeling good), 'What kind of day?' (Work day / Day off) and 'Where are you?' (Indoors / Out and about / Either), under 'Answer what you like. Skip what you don't.'. A chosen answer tints (accent border, fill and bold accent text); tapping it AGAIN clears it, so a mis-tap is undone the way it was made. Skipping a question sends nothing for it, so it never becomes an assumption, and skipping all three sorts exactly as it always did. The order that comes back reflects what was said (a low-energy day starts small; a day off does not front-load work; 'out and about' clusters the errands), but the app NEVER comments on how you feel. 'Not now' closes with nothing sent and the day untouched. A FREE user hits the Premium screen BEFORE the questions, never after answering them. NEW (the constant frame): when the Energy PILLS at the top of Today were touched today, the sheet's energy question DOES NOT APPEAR at all, and the pill's answer rides the request instead (Low-&gt;low, Normal-&gt;medium, High-&gt;good): energy is read, never asked twice. Only when the pills are untouched does the sheet ask. NOTE: there is deliberately no weather question. A model has no live weather data, and a forecast would need an API plus a location permission; 'Where are you?' is what the sort actually needs.</t>
+          <t>One calm mention appears under the goodnight text: 'You've finished enough this week to make a keepsake of it. It's waiting in your Calendar.' with 'See your Calendar' and 'Not now'. Either answer spends the mention FOREVER (it is the third and LAST rung of the one-ask-at-a-time ladder; reminder and widget always win the evening if pending). 'See your Calendar' opens the Calendar where the scrapbook lives. It never shows with AI off, never with fewer than 3 finishes this week, never to someone who has already made a scrapbook, and never twice.</t>
         </is>
       </c>
       <c r="G297" s="7" t="inlineStr">
@@ -12614,7 +12614,7 @@
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>SEQ-08</t>
+          <t>SEQ-07</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -12629,17 +12629,17 @@
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>The suggested order can be edited before it is used</t>
+          <t>Plan my day asks about the day BEFORE it sorts</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>Get a proposal from 'Plan my day'. Use the up and down arrows on a row. Try the up arrow on the FIRST row and the down arrow on the LAST. Remove a row with x. Remove every row. Then tap 'Use this order'.</t>
+          <t>As premium, tap 'Plan my day'. Read the sheet that opens. Tap an answer, then tap the SAME answer again. Try sorting with all three answered, with only one answered, and with none answered ('Sort today' straight away). Also tap 'Not now'. Separately, as a FREE user, tap 'Plan my day'.</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>Each row carries up / down / x. Up and down swap the row with its neighbour immediately, renumbering as they go; the first row's up and the last row's down are visibly dimmed and do nothing (they are disabled, not hidden, so rows never change shape as things move). 'x' takes that task OUT OF THIS PLAN ONLY: the task stays on Today untouched, is not deleted, and is not moved to another day. Removing everything is allowed and says 'Nothing left in the plan. That's allowed.' with the accept button gone (an empty plan cannot be applied). Nothing at all changes on Today until 'Use this order' is tapped; 'Not now' or closing discards every edit. Editing is by buttons, never drag: dragging is unusable with a screen reader and hard with shaky hands.</t>
+          <t>Before any sorting, a calm sheet asks three OPTIONAL questions: 'How's your energy?' (Running low / Somewhere in between / Feeling good), 'What kind of day?' (Work day / Day off) and 'Where are you?' (Indoors / Out and about / Either), under 'Answer what you like. Skip what you don't.'. A chosen answer tints (accent border, fill and bold accent text); tapping it AGAIN clears it, so a mis-tap is undone the way it was made. Skipping a question sends nothing for it, so it never becomes an assumption, and skipping all three sorts exactly as it always did. The order that comes back reflects what was said (a low-energy day starts small; a day off does not front-load work; 'out and about' clusters the errands), but the app NEVER comments on how you feel. 'Not now' closes with nothing sent and the day untouched. A FREE user hits the Premium screen BEFORE the questions, never after answering them. NEW (the constant frame): when the Energy PILLS at the top of Today were touched today, the sheet's energy question DOES NOT APPEAR at all, and the pill's answer rides the request instead (Low-&gt;low, Normal-&gt;medium, High-&gt;good): energy is read, never asked twice. Only when the pills are untouched does the sheet ask. NOTE: there is deliberately no weather question. A model has no live weather data, and a forecast would need an API plus a location permission; 'Where are you?' is what the sort actually needs.</t>
         </is>
       </c>
       <c r="G298" s="7" t="inlineStr">
@@ -12654,7 +12654,7 @@
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>SEQ-02</t>
+          <t>SEQ-08</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
@@ -12669,17 +12669,17 @@
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>Free: Plan my day routes to the upsell, never reorders</t>
+          <t>The suggested order can be edited before it is used</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>As a free user with 2+ tasks on Today, tap 'Plan my day'.</t>
+          <t>Get a proposal from 'Plan my day'. Use the up and down arrows on a row. Try the up arrow on the FIRST row and the down arrow on the LAST. Remove a row with x. Remove every row. Then tap 'Use this order'.</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>The Premium screen opens calmly (never a wall), a 'premium.gate_hit' with reason 'sequence' is logged, and the day's order is unchanged.</t>
+          <t>Each row carries up / down / x. Up and down swap the row with its neighbour immediately, renumbering as they go; the first row's up and the last row's down are visibly dimmed and do nothing (they are disabled, not hidden, so rows never change shape as things move). 'x' takes that task OUT OF THIS PLAN ONLY: the task stays on Today untouched, is not deleted, and is not moved to another day. Removing everything is allowed and says 'Nothing left in the plan. That's allowed.' with the accept button gone (an empty plan cannot be applied). Nothing at all changes on Today until 'Use this order' is tapped; 'Not now' or closing discards every edit. Editing is by buttons, never drag: dragging is unusable with a screen reader and hard with shaky hands.</t>
         </is>
       </c>
       <c r="G299" s="7" t="inlineStr">
@@ -12694,7 +12694,7 @@
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>SEQ-03</t>
+          <t>SEQ-02</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
@@ -12702,24 +12702,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C300" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C300" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>'Not now' leaves the day untouched</t>
+          <t>Free: Plan my day routes to the upsell, never reorders</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>As premium, open the proposal, then tap 'Not now' or the backdrop.</t>
+          <t>As a free user with 2+ tasks on Today, tap 'Plan my day'.</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>The order is exactly as before, nothing reordered, and no manualOrder is written.</t>
+          <t>The Premium screen opens calmly (never a wall), a 'premium.gate_hit' with reason 'sequence' is logged, and the day's order is unchanged.</t>
         </is>
       </c>
       <c r="G300" s="7" t="inlineStr">
@@ -12734,7 +12734,7 @@
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>SEQ-04</t>
+          <t>SEQ-03</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -12749,17 +12749,17 @@
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>An accepted order survives a reload (local-first)</t>
+          <t>'Not now' leaves the day untouched</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>As premium, accept an order, then fully reload the app.</t>
+          <t>As premium, open the proposal, then tap 'Not now' or the backdrop.</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>Today still shows the accepted order after reload (manualOrder persists on-device). Note: the order does not yet sync across devices, which is a documented follow-up.</t>
+          <t>The order is exactly as before, nothing reordered, and no manualOrder is written.</t>
         </is>
       </c>
       <c r="G301" s="7" t="inlineStr">
@@ -12774,7 +12774,7 @@
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
         <is>
-          <t>SEQ-05</t>
+          <t>SEQ-04</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
@@ -12782,24 +12782,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C302" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C302" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>A pinned task still wins the very top</t>
+          <t>An accepted order survives a reload (local-first)</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>As premium, pin a task, then accept a 'Plan my day' sequence that puts a different task first.</t>
+          <t>As premium, accept an order, then fully reload the app.</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>The pinned task stays at the very top, and the accepted order applies to everything below it.</t>
+          <t>Today still shows the accepted order after reload (manualOrder persists on-device). Note: the order does not yet sync across devices, which is a documented follow-up.</t>
         </is>
       </c>
       <c r="G302" s="7" t="inlineStr">
@@ -12814,7 +12814,7 @@
     <row r="303">
       <c r="A303" s="6" t="inlineStr">
         <is>
-          <t>SEQ-06</t>
+          <t>SEQ-05</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
@@ -12822,24 +12822,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C303" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C303" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>Plan my day offers to lighten a heavy day</t>
+          <t>A pinned task still wins the very top</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>As premium on a heavy day (6+ tasks), tap 'Plan my day', accept the order.</t>
+          <t>As premium, pin a task, then accept a 'Plan my day' sequence that puts a different task first.</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>After the order applies, a 'Still a full day?' card offers to push a few tasks out to later days. Yes runs the re-spread (propose-then-accept), No leaves it ordered. On a calm day the offer never appears.</t>
+          <t>The pinned task stays at the very top, and the accepted order applies to everything below it.</t>
         </is>
       </c>
       <c r="G303" s="7" t="inlineStr">
@@ -12854,32 +12854,32 @@
     <row r="304">
       <c r="A304" s="6" t="inlineStr">
         <is>
-          <t>BIG-01</t>
+          <t>SEQ-06</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
         <is>
-          <t>Big task</t>
-        </is>
-      </c>
-      <c r="C304" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Sequence</t>
+        </is>
+      </c>
+      <c r="C304" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>Mark a task big: the tag, and the weight it adds</t>
+          <t>Plan my day offers to lighten a heavy day</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>On Today with a few one-off tasks, tap and hold one, then tap 'Mark as a lot' in the held row's actions. ALSO hold a RECURRING task and confirm 'Mark as a lot' is offered there too (a chore can be a lot; this used to be offered only via the bulk bar).</t>
+          <t>As premium on a heavy day (6+ tasks), tap 'Plan my day', accept the order.</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>The card closes and the task shows a calm accent 'Big' tag beside its title (never red, never a warning), with a brief validating note ('Marked as a lot...'). The weight gauge fills further and reads heavier (one big task floors the bar to at least 'A full day, but doable.'). Free for everyone, no upsell.</t>
+          <t>After the order applies, a 'Still a full day?' card offers to push a few tasks out to later days. Yes runs the re-spread (propose-then-accept), No leaves it ordered. On a calm day the offer never appears.</t>
         </is>
       </c>
       <c r="G304" s="7" t="inlineStr">
@@ -12894,7 +12894,7 @@
     <row r="305">
       <c r="A305" s="6" t="inlineStr">
         <is>
-          <t>BIG-02</t>
+          <t>BIG-01</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -12902,24 +12902,24 @@
           <t>Big task</t>
         </is>
       </c>
-      <c r="C305" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C305" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>Big is a multi-select toggle</t>
+          <t>Mark a task big: the tag, and the weight it adds</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>Hold a task, 'Select more', tick another, then tap 'Mark as a lot'; then re-select tasks that are all big and tap the action again (it now reads 'Not big').</t>
+          <t>On Today with a few one-off tasks, tap and hold one, then tap 'Mark as a lot' in the held row's actions. ALSO hold a RECURRING task and confirm 'Mark as a lot' is offered there too (a chore can be a lot; this used to be offered only via the bulk bar).</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>The first tap marks every selected task big at once. When all selected tasks are already big the action reads 'Not big' and clears the mark off all of them. A mixed selection marks all big (the additive default).</t>
+          <t>The card closes and the task shows a calm accent 'Big' tag beside its title (never red, never a warning), with a brief validating note ('Marked as a lot...'). The weight gauge fills further and reads heavier (one big task floors the bar to at least 'A full day, but doable.'). Free for everyone, no upsell.</t>
         </is>
       </c>
       <c r="G305" s="7" t="inlineStr">
@@ -12934,7 +12934,7 @@
     <row r="306">
       <c r="A306" s="6" t="inlineStr">
         <is>
-          <t>BIG-03</t>
+          <t>BIG-02</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -12949,17 +12949,17 @@
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>A lone big task lifts the bar but is not a re-spread problem</t>
+          <t>Big is a multi-select toggle</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>Have just one or two tasks on Today, one marked big.</t>
+          <t>Hold a task, 'Select more', tick another, then tap 'Mark as a lot'; then re-select tasks that are all big and tap the action again (it now reads 'Not big').</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>The weight gauge reads at least 'A full day, but doable.' (the big task is felt), but 'Today's looking full' and 'Lighten today' do NOT appear for a lone big task (re-spreading cannot dissolve one big rock; Break it down is the tool). A big task plus a real pile (weighted load 6+) does surface Lighten today.</t>
+          <t>The first tap marks every selected task big at once. When all selected tasks are already big the action reads 'Not big' and clears the mark off all of them. A mixed selection marks all big (the additive default).</t>
         </is>
       </c>
       <c r="G306" s="7" t="inlineStr">
@@ -12974,7 +12974,7 @@
     <row r="307">
       <c r="A307" s="6" t="inlineStr">
         <is>
-          <t>BIG-04</t>
+          <t>BIG-03</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
@@ -12989,17 +12989,17 @@
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>Finishing a big task is a big-win in the Calendar</t>
+          <t>A lone big task lifts the bar but is not a re-spread problem</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>Mark a task big, complete it, then open the Calendar to its day.</t>
+          <t>Have just one or two tasks on Today, one marked big.</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>The completed task carries the warmer 'a big one' treatment on its day, the same payoff a long-dreaded or chunky task earns. The big flag never adds disappointment if the task is left unfinished.</t>
+          <t>The weight gauge reads at least 'A full day, but doable.' (the big task is felt), but 'Today's looking full' and 'Lighten today' do NOT appear for a lone big task (re-spreading cannot dissolve one big rock; Break it down is the tool). A big task plus a real pile (weighted load 6+) does surface Lighten today.</t>
         </is>
       </c>
       <c r="G307" s="7" t="inlineStr">
@@ -13014,7 +13014,7 @@
     <row r="308">
       <c r="A308" s="6" t="inlineStr">
         <is>
-          <t>BIG-05</t>
+          <t>BIG-04</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
@@ -13029,17 +13029,17 @@
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>Big syncs across devices (and old marks survive the upgrade)</t>
+          <t>Finishing a big task is a big-win in the Calendar</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>Signed in on two devices (e.g. web + Android). Mark a task big on device 1, wait for or trigger a sync, then open device 2. Then unmark it on device 2 and check device 1. Prerequisite: an account with the same task on both.</t>
+          <t>Mark a task big, complete it, then open the Calendar to its day.</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>The Big tag appears on device 2 (with its weight-gauge effect), and the unmark travels back: no resurrection, the newest change wins. Marks made BEFORE this build (when big was device-only) are seeded up to the account on that device's first sync rather than erased. One known transition quirk: a device still on a PRE-sync build can re-surface a cleared big once when it upgrades; clearing it again sticks everywhere. Manual order (Plan my order) remains per-device by design.</t>
+          <t>The completed task carries the warmer 'a big one' treatment on its day, the same payoff a long-dreaded or chunky task earns. The big flag never adds disappointment if the task is left unfinished.</t>
         </is>
       </c>
       <c r="G308" s="7" t="inlineStr">
@@ -13054,37 +13054,37 @@
     <row r="309">
       <c r="A309" s="6" t="inlineStr">
         <is>
-          <t>NAV-01</t>
+          <t>BIG-05</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
         <is>
-          <t>Rooms</t>
-        </is>
-      </c>
-      <c r="C309" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Big task</t>
+        </is>
+      </c>
+      <c r="C309" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>Rooms sheet caps its width on wide web</t>
+          <t>Big syncs across devices (and old marks survive the upgrade)</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>On a wide desktop browser, open Rooms (the header pill).</t>
+          <t>Signed in on two devices (e.g. web + Android). Mark a task big on device 1, wait for or trigger a sync, then open device 2. Then unmark it on device 2 and check device 1. Prerequisite: an account with the same task on both.</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>The sheet is a centred column (about 560px, matching the page content), not full-bleed, so the 'Premium' gradient pill on 'Chart a course' sits beside its label rather than at the far screen edge. On a phone the sheet stays full-width with the pill at the row's edge.</t>
+          <t>The Big tag appears on device 2 (with its weight-gauge effect), and the unmark travels back: no resurrection, the newest change wins. Marks made BEFORE this build (when big was device-only) are seeded up to the account on that device's first sync rather than erased. One known transition quirk: a device still on a PRE-sync build can re-surface a cleared big once when it upgrades; clearing it again sticks everywhere. Manual order (Plan my order) remains per-device by design.</t>
         </is>
       </c>
       <c r="G309" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H309" s="7" t="inlineStr"/>
@@ -13094,37 +13094,37 @@
     <row r="310">
       <c r="A310" s="6" t="inlineStr">
         <is>
-          <t>OUR-01</t>
+          <t>NAV-01</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C310" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="C310" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>The door only exists for an allowed account</t>
+          <t>Rooms sheet caps its width on wide web</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>Sign in as an account that is NOT on the ours_allowlist and open Settings. Then sign in as one that is.</t>
+          <t>On a wide desktop browser, open Rooms (the header pill).</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>The 'Ours' row is absent for the first account and present for the second. Nobody is ever offered a door that answers 'shared lists aren't open yet'.</t>
+          <t>The sheet is a centred column (about 560px, matching the page content), not full-bleed, so the 'Premium' gradient pill on 'Chart a course' sits beside its label rather than at the far screen edge. On a phone the sheet stays full-width with the pill at the row's edge.</t>
         </is>
       </c>
       <c r="G310" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H310" s="7" t="inlineStr"/>
@@ -13134,7 +13134,7 @@
     <row r="311">
       <c r="A311" s="6" t="inlineStr">
         <is>
-          <t>OUR-02</t>
+          <t>OUR-01</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -13149,17 +13149,17 @@
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>Signed out: the explanation, never a nag</t>
+          <t>The door only exists for an allowed account</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>Sign out, then open /ours directly.</t>
+          <t>Sign in as an account that is NOT on the ours_allowlist and open Settings. Then sign in as one that is.</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>A calm one-screen explanation of why sharing needs an account, and a way to sign in. No pressure, no count of what you are missing.</t>
+          <t>The 'Ours' row is absent for the first account and present for the second. Nobody is ever offered a door that answers 'shared lists aren't open yet'.</t>
         </is>
       </c>
       <c r="G311" s="7" t="inlineStr">
@@ -13174,7 +13174,7 @@
     <row r="312">
       <c r="A312" s="6" t="inlineStr">
         <is>
-          <t>OUR-03</t>
+          <t>OUR-02</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -13189,17 +13189,17 @@
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>Name the list and mint a code</t>
+          <t>Signed out: the explanation, never a nag</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>Ours &gt; Start a shared list. Pick 'The house'. Type your own name. Type the OTHER account's email exactly. Get a code.</t>
+          <t>Sign out, then open /ours directly.</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>A six-character code appears grouped as XXX-XXX, containing no 0, 1, I, L or O. The screen says it works once, for the next day, and only for the address you gave.</t>
+          <t>A calm one-screen explanation of why sharing needs an account, and a way to sign in. No pressure, no count of what you are missing.</t>
         </is>
       </c>
       <c r="G312" s="7" t="inlineStr">
@@ -13214,7 +13214,7 @@
     <row r="313">
       <c r="A313" s="6" t="inlineStr">
         <is>
-          <t>OUR-04</t>
+          <t>OUR-03</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -13229,17 +13229,17 @@
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>Join from the second account</t>
+          <t>Name the list and mint a code</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>On the second account, Ours &gt; Join with a code. Type the code (try it lower-case and with the dash). Type your own name. Join.</t>
+          <t>Ours &gt; Start a shared list. Pick 'The house'. Type your own name. Type the OTHER account's email exactly. Get a code.</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>You land on the shared list showing the FIRST person's chosen name and the list's name ('The house'). No email address is shown anywhere, to either person.</t>
+          <t>A six-character code appears grouped as XXX-XXX, containing no 0, 1, I, L or O. The screen says it works once, for the next day, and only for the address you gave.</t>
         </is>
       </c>
       <c r="G313" s="7" t="inlineStr">
@@ -13254,7 +13254,7 @@
     <row r="314">
       <c r="A314" s="6" t="inlineStr">
         <is>
-          <t>OUR-05</t>
+          <t>OUR-04</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
@@ -13269,17 +13269,17 @@
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>The first person sees the arrival without refreshing</t>
+          <t>Join from the second account</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>Leave the first account sitting on the Ours screen while the second joins.</t>
+          <t>On the second account, Ours &gt; Join with a code. Type the code (try it lower-case and with the dash). Type your own name. Join.</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>Within about ten seconds it announces that they joined, with a way out for someone who meant a different person. It never says how long they took.</t>
+          <t>You land on the shared list showing the FIRST person's chosen name and the list's name ('The house'). No email address is shown anywhere, to either person.</t>
         </is>
       </c>
       <c r="G314" s="7" t="inlineStr">
@@ -13294,7 +13294,7 @@
     <row r="315">
       <c r="A315" s="6" t="inlineStr">
         <is>
-          <t>OUR-06</t>
+          <t>OUR-05</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -13302,24 +13302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C315" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C315" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>A wrong code says one calm thing</t>
+          <t>The first person sees the arrival without refreshing</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>Try a made-up code, then a code meant for a different address, then the same code twice.</t>
+          <t>Leave the first account sitting on the Ours screen while the second joins.</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>Every one gives the SAME single line ('That code isn't valid.'). Nothing hints at which reason, so a guesser learns nothing. Repeated wrong tries eventually ask you to have a break.</t>
+          <t>Within about ten seconds it announces that they joined, with a way out for someone who meant a different person. It never says how long they took.</t>
         </is>
       </c>
       <c r="G315" s="7" t="inlineStr">
@@ -13334,7 +13334,7 @@
     <row r="316">
       <c r="A316" s="6" t="inlineStr">
         <is>
-          <t>OUR-07</t>
+          <t>OUR-06</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -13349,17 +13349,17 @@
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>Mistyped invitee address is recoverable</t>
+          <t>A wrong code says one calm thing</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>Mint a code with a deliberately wrong email, then use 'Wrong address? Start again' and mint a fresh one with the right address.</t>
+          <t>Try a made-up code, then a code meant for a different address, then the same code twice.</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>The new code works and the old one does not. Nothing had to be deleted to recover, and no address is ever displayed back to you.</t>
+          <t>Every one gives the SAME single line ('That code isn't valid.'). Nothing hints at which reason, so a guesser learns nothing. Repeated wrong tries eventually ask you to have a break.</t>
         </is>
       </c>
       <c r="G316" s="7" t="inlineStr">
@@ -13374,7 +13374,7 @@
     <row r="317">
       <c r="A317" s="6" t="inlineStr">
         <is>
-          <t>OUR-08</t>
+          <t>OUR-07</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -13389,17 +13389,17 @@
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>Rename the list, and both sides see it</t>
+          <t>Mistyped invitee address is recoverable</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>On the shared list, tap the list's name, type a new one, and confirm. Reopen Ours on the other account.</t>
+          <t>Mint a code with a deliberately wrong email, then use 'Wrong address? Start again' and mint a fresh one with the right address.</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>Both people see the new name. An emptied name falls back to the app's own word, in each person's own language.</t>
+          <t>The new code works and the old one does not. Nothing had to be deleted to recover, and no address is ever displayed back to you.</t>
         </is>
       </c>
       <c r="G317" s="7" t="inlineStr">
@@ -13414,7 +13414,7 @@
     <row r="318">
       <c r="A318" s="6" t="inlineStr">
         <is>
-          <t>OUR-09</t>
+          <t>OUR-08</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -13422,24 +13422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C318" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C318" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>Leaving freezes and takes nothing</t>
+          <t>Rename the list, and both sides see it</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>On one account, Leave this list. Then open Ours on BOTH accounts.</t>
+          <t>On the shared list, tap the list's name, type a new one, and confirm. Reopen Ours on the other account.</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>Both see 'This list is closed' and can still read everything. Nothing was deleted from either side. Neither person is told off, and neither is told what the other did.</t>
+          <t>Both people see the new name. An emptied name falls back to the app's own word, in each person's own language.</t>
         </is>
       </c>
       <c r="G318" s="7" t="inlineStr">
@@ -13454,7 +13454,7 @@
     <row r="319">
       <c r="A319" s="6" t="inlineStr">
         <is>
-          <t>OUR-10</t>
+          <t>OUR-09</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -13462,24 +13462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C319" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C319" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>Remove a closed list from your side only</t>
+          <t>Leaving freezes and takes nothing</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Remove this list'. Then check the other account.</t>
+          <t>On one account, Leave this list. Then open Ours on BOTH accounts.</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>It disappears for you. The other person still has their copy and is not notified.</t>
+          <t>Both see 'This list is closed' and can still read everything. Nothing was deleted from either side. Neither person is told off, and neither is told what the other did.</t>
         </is>
       </c>
       <c r="G319" s="7" t="inlineStr">
@@ -13494,7 +13494,7 @@
     <row r="320">
       <c r="A320" s="6" t="inlineStr">
         <is>
-          <t>OUR-11</t>
+          <t>OUR-10</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -13502,24 +13502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C320" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C320" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>Nothing anywhere attributes a task to a person</t>
+          <t>Remove a closed list from your side only</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>With a shared list live, look at Ours, Today, the Lookback and Settings on both accounts.</t>
+          <t>On a closed list, tap 'Remove this list'. Then check the other account.</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>No initials, no 'done by', no counts of who did what, no progress bar across two people, no activity feed. The data to build one does not exist.</t>
+          <t>It disappears for you. The other person still has their copy and is not notified.</t>
         </is>
       </c>
       <c r="G320" s="7" t="inlineStr">
@@ -13534,7 +13534,7 @@
     <row r="321">
       <c r="A321" s="6" t="inlineStr">
         <is>
-          <t>OUR-13</t>
+          <t>OUR-11</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -13549,17 +13549,17 @@
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>The code stays on screen from the moment it is minted</t>
+          <t>Nothing anywhere attributes a task to a person</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>On a throttled connection (devtools, slow 3G), fill the create form and tap the code button.</t>
+          <t>With a shared list live, look at Ours, Today, the Lookback and Settings on both accounts.</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>The six characters appear as soon as the button stops spinning and are NEVER replaced by the intro screen. The server returns that code exactly once, so a flash back to 'Start a shared list' loses it for good.</t>
+          <t>No initials, no 'done by', no counts of who did what, no progress bar across two people, no activity feed. The data to build one does not exist.</t>
         </is>
       </c>
       <c r="G321" s="7" t="inlineStr">
@@ -13574,7 +13574,7 @@
     <row r="322">
       <c r="A322" s="6" t="inlineStr">
         <is>
-          <t>OUR-14</t>
+          <t>OUR-13</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -13589,17 +13589,17 @@
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>'Get a new code' reaches the form and mints a different code</t>
+          <t>The code stays on screen from the moment it is minted</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>From the waiting screen, tap the get-a-new-code action. Change the email. Submit.</t>
+          <t>On a throttled connection (devtools, slow 3G), fill the create form and tap the code button.</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>The create form appears with your name and list name already filled. Submitting shows a DIFFERENT six characters, and the old one no longer works. Your chosen name is unchanged afterwards.</t>
+          <t>The six characters appear as soon as the button stops spinning and are NEVER replaced by the intro screen. The server returns that code exactly once, so a flash back to 'Start a shared list' loses it for good.</t>
         </is>
       </c>
       <c r="G322" s="7" t="inlineStr">
@@ -13614,7 +13614,7 @@
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
         <is>
-          <t>OUR-120</t>
+          <t>OUR-14</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -13629,17 +13629,17 @@
       </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
-          <t>Waiting-with-no-code is reachable, says so, and the re-mint is a real button</t>
+          <t>'Get a new code' reaches the form and mints a different code</t>
         </is>
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>Mint a code, leave Ours entirely (back to Today), then come back via the MENU's Ours row before anyone joins.</t>
+          <t>From the waiting screen, tap the get-a-new-code action. Change the email. Submit.</t>
         </is>
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>The Menu lands on the shared LIST (usable solo while waiting), and the list's header line reads 'Waiting for your person - Get a new code' where 'Kept with {name}' will later sit; tapping it opens the pairing screen (both Melroy's C6 check and the field report hit this as a dead end before 2026-09-20). That screen is titled 'Waiting for your person', NOT 'Read this to your person' over an empty space (the code renders exactly once; the server keeps only a hash, so it can never be re-shown), and 'Get a new code' is a full primary button there, not a quiet text link. While the code IS still on screen, the old title and quiet link stay as they were.</t>
+          <t>The create form appears with your name and list name already filled. Submitting shows a DIFFERENT six characters, and the old one no longer works. Your chosen name is unchanged afterwards.</t>
         </is>
       </c>
       <c r="G323" s="7" t="inlineStr">
@@ -13654,7 +13654,7 @@
     <row r="324">
       <c r="A324" s="6" t="inlineStr">
         <is>
-          <t>OUR-121</t>
+          <t>OUR-120</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -13669,17 +13669,17 @@
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>Whose email, and which code goes where</t>
+          <t>Waiting-with-no-code is reachable, says so, and the re-mint is a real button</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>Signed out: read the Menu's Ours line, open Ours, read the signed-out screen, tap Sign in and read the field. Then, on the sign-in code step, paste an Ours-style code (letters in it). Separately, signed in, open Ours 'I have a code' and type a 6-digit emailed sign-in code.</t>
+          <t>Mint a code, leave Ours entirely (back to Today), then come back via the MENU's Ours row before anyone joins.</t>
         </is>
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>The Menu's Ours line reads 'A list kept with one person. Sign in first.' (the old 'Needs your email, no password' invited typing the PARTNER'S email; a real user did exactly that on 2026-09-13 and it became their account). The Ours signed-out screen opens with the plain fact 'You're not signed in on this phone.' The sign-in email field is labelled 'Your own email', and the subtitle says sharing happens later, in Ours, with a code, never by typing the partner's email here. Letters in the 6-digit code field draw the calm hint that it will be an Ours invite code (a hint, never an auto-redirect or a cleared field). Six bare digits failing in the Ours join field add one line naming the emailed sign-in code as the likely mix-up, alongside the unchanged honest failure.</t>
+          <t>The Menu lands on the shared LIST (usable solo while waiting), and the list's header line reads 'Waiting for your person - Get a new code' where 'Kept with {name}' will later sit; tapping it opens the pairing screen (both Melroy's C6 check and the field report hit this as a dead end before 2026-09-20). That screen is titled 'Waiting for your person', NOT 'Read this to your person' over an empty space (the code renders exactly once; the server keeps only a hash, so it can never be re-shown), and 'Get a new code' is a full primary button there, not a quiet text link. While the code IS still on screen, the old title and quiet link stay as they were.</t>
         </is>
       </c>
       <c r="G324" s="7" t="inlineStr">
@@ -13694,7 +13694,7 @@
     <row r="325">
       <c r="A325" s="6" t="inlineStr">
         <is>
-          <t>OUR-15</t>
+          <t>OUR-121</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -13709,17 +13709,17 @@
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>Leave a list, then start a new one WITHOUT deleting the old</t>
+          <t>Whose email, and which code goes where</t>
         </is>
       </c>
       <c r="E325" s="9" t="inlineStr">
         <is>
-          <t>Leave a shared list. On the closed screen, start a new shared list with someone else.</t>
+          <t>Signed out: read the Menu's Ours line, open Ours, read the signed-out screen, tap Sign in and read the field. Then, on the sign-in code step, paste an Ours-style code (letters in it). Separately, signed in, open Ours 'I have a code' and type a 6-digit emailed sign-in code.</t>
         </is>
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>Starting a new list is offered on the closed screen itself and works. The old list is NOT deleted and is still readable. At no point is destroying it the only way forward.</t>
+          <t>The Menu's Ours line reads 'A list kept with one person. Sign in first.' (the old 'Needs your email, no password' invited typing the PARTNER'S email; a real user did exactly that on 2026-09-13 and it became their account). The Ours signed-out screen opens with the plain fact 'You're not signed in on this phone.' The sign-in email field is labelled 'Your own email', and the subtitle says sharing happens later, in Ours, with a code, never by typing the partner's email here. Letters in the 6-digit code field draw the calm hint that it will be an Ours invite code (a hint, never an auto-redirect or a cleared field). Six bare digits failing in the Ours join field add one line naming the emailed sign-in code as the likely mix-up, alongside the unchanged honest failure.</t>
         </is>
       </c>
       <c r="G325" s="7" t="inlineStr">
@@ -13734,7 +13734,7 @@
     <row r="326">
       <c r="A326" s="6" t="inlineStr">
         <is>
-          <t>OUR-16</t>
+          <t>OUR-15</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -13749,17 +13749,17 @@
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
-          <t>A failed read never offers to start a list you already have</t>
+          <t>Leave a list, then start a new one WITHOUT deleting the old</t>
         </is>
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, turn the network off and open Ours.</t>
+          <t>Leave a shared list. On the closed screen, start a new shared list with someone else.</t>
         </is>
       </c>
       <c r="F326" s="9" t="inlineStr">
         <is>
-          <t>A calm connection line. The screen never says you have no shared list and never offers to start one. Turning the network back on recovers without a restart.</t>
+          <t>Starting a new list is offered on the closed screen itself and works. The old list is NOT deleted and is still readable. At no point is destroying it the only way forward.</t>
         </is>
       </c>
       <c r="G326" s="7" t="inlineStr">
@@ -13774,7 +13774,7 @@
     <row r="327">
       <c r="A327" s="6" t="inlineStr">
         <is>
-          <t>OUR-17</t>
+          <t>OUR-16</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -13782,24 +13782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C327" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C327" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>A list nobody joined can be left</t>
+          <t>A failed read never offers to start a list you already have</t>
         </is>
       </c>
       <c r="E327" s="9" t="inlineStr">
         <is>
-          <t>Create a list, get a code, give it to nobody. Return to Ours.</t>
+          <t>With a live shared list, turn the network off and open Ours.</t>
         </is>
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>There is a way out on the waiting screen, and its wording does not claim it closes for two people. After leaving, you can start or join a list again.</t>
+          <t>A calm connection line. The screen never says you have no shared list and never offers to start one. Turning the network back on recovers without a restart.</t>
         </is>
       </c>
       <c r="G327" s="7" t="inlineStr">
@@ -13814,7 +13814,7 @@
     <row r="328">
       <c r="A328" s="6" t="inlineStr">
         <is>
-          <t>OUR-18</t>
+          <t>OUR-17</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -13829,17 +13829,17 @@
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>The arrival announces once and stays announced</t>
+          <t>A list nobody joined can be left</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>Sit on the waiting screen while the other account joins. Background the app and return.</t>
+          <t>Create a list, get a code, give it to nobody. Return to Ours.</t>
         </is>
       </c>
       <c r="F328" s="9" t="inlineStr">
         <is>
-          <t>The name appears once and does not flicker back to waiting and re-announce. The way out beside it ('that wasn't who I meant') never appears on a list you did not just gain a person on.</t>
+          <t>There is a way out on the waiting screen, and its wording does not claim it closes for two people. After leaving, you can start or join a list again.</t>
         </is>
       </c>
       <c r="G328" s="7" t="inlineStr">
@@ -13854,7 +13854,7 @@
     <row r="329">
       <c r="A329" s="6" t="inlineStr">
         <is>
-          <t>OUR-19</t>
+          <t>OUR-18</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -13869,17 +13869,17 @@
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>A repeat the app cannot read is SHOWN, never hidden</t>
+          <t>The arrival announces once and stays announced</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>Requires two app versions. On the newer one, set a shared task to a cadence the older build does not have. Open the list on the older build.</t>
+          <t>Sit on the waiting screen while the other account joins. Background the app and return.</t>
         </is>
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>The task is visible on both, with whatever cadence line the newer app left. It is never silently absent from one person's list, and the older app does not erase the schedule when it syncs.</t>
+          <t>The name appears once and does not flicker back to waiting and re-announce. The way out beside it ('that wasn't who I meant') never appears on a list you did not just gain a person on.</t>
         </is>
       </c>
       <c r="G329" s="7" t="inlineStr">
@@ -13894,7 +13894,7 @@
     <row r="330">
       <c r="A330" s="6" t="inlineStr">
         <is>
-          <t>OUR-20</t>
+          <t>OUR-19</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -13902,24 +13902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C330" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C330" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>The room opens from Today's heading and from the Menu</t>
+          <t>A repeat the app cannot read is SHOWN, never hidden</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, tap the list's name beside 'Today' in Today's heading. Then go back and reach it through Menu › Ours.</t>
+          <t>Requires two app versions. On the newer one, set a shared task to a cadence the older build does not have. Open the list on the older build.</t>
         </is>
       </c>
       <c r="F330" s="9" t="inlineStr">
         <is>
-          <t>Both land on the shared list itself, not the pairing screen, with a fade (a tab changing), not a sideways slide. The room's heading reads 'Today' and the list's name side by side, the name underlined as the current one, then the line 'Shared. Anything with a day reaches both your Todays on that day.' The date and the same Menu pill sit above it. 'Kept with {their name} ›' still goes to the pairing/management screen. Tapping 'Today' in the room's heading goes back to Today.</t>
+          <t>The task is visible on both, with whatever cadence line the newer app left. It is never silently absent from one person's list, and the older app does not erase the schedule when it syncs.</t>
         </is>
       </c>
       <c r="G330" s="7" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="331">
       <c r="A331" s="6" t="inlineStr">
         <is>
-          <t>OUR-21</t>
+          <t>OUR-20</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -13949,17 +13949,17 @@
       </c>
       <c r="D331" s="9" t="inlineStr">
         <is>
-          <t>Add, tick and UN-tick on the shared list</t>
+          <t>The room opens from Today's heading and from the Menu</t>
         </is>
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>Add a task in the room. Tick it. Un-tick it. Watch the other account (reload or wait ~15s).</t>
+          <t>With a live shared list, tap the list's name beside 'Today' in Today's heading. Then go back and reach it through Menu › Ours.</t>
         </is>
       </c>
       <c r="F331" s="9" t="inlineStr">
         <is>
-          <t>Every step appears on both. Un-ticking works as easily as ticking, on both sides. No affirmation or celebration fires on Ours.</t>
+          <t>Both land on the shared list itself, not the pairing screen, with a fade (a tab changing), not a sideways slide. The room's heading reads 'Today' and the list's name side by side, the name underlined as the current one, then the line 'Shared. Anything with a day reaches both your Todays on that day.' The date and the same Menu pill sit above it. 'Kept with {their name} ›' still goes to the pairing/management screen. Tapping 'Today' in the room's heading goes back to Today.</t>
         </is>
       </c>
       <c r="G331" s="7" t="inlineStr">
@@ -13974,7 +13974,7 @@
     <row r="332">
       <c r="A332" s="6" t="inlineStr">
         <is>
-          <t>OUR-22</t>
+          <t>OUR-21</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -13989,17 +13989,17 @@
       </c>
       <c r="D332" s="9" t="inlineStr">
         <is>
-          <t>Un-tick a one-off the DAY AFTER it was ticked</t>
+          <t>Add, tick and UN-tick on the shared list</t>
         </is>
       </c>
       <c r="E332" s="9" t="inlineStr">
         <is>
-          <t>Tick a shared one-off. Change the device date to tomorrow (or wait a day), reopen the room, tap it again.</t>
+          <t>Add a task in the room. Tick it. Un-tick it. Watch the other account (reload or wait ~15s).</t>
         </is>
       </c>
       <c r="F332" s="9" t="inlineStr">
         <is>
-          <t>It un-ticks. (The pre-fix build could never un-tick it again, on any device, forever.)</t>
+          <t>Every step appears on both. Un-ticking works as easily as ticking, on both sides. No affirmation or celebration fires on Ours.</t>
         </is>
       </c>
       <c r="G332" s="7" t="inlineStr">
@@ -14014,7 +14014,7 @@
     <row r="333">
       <c r="A333" s="6" t="inlineStr">
         <is>
-          <t>OUR-23</t>
+          <t>OUR-22</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -14029,17 +14029,17 @@
       </c>
       <c r="D333" s="9" t="inlineStr">
         <is>
-          <t>Bring to my Today makes a COPY, and marks only yours</t>
+          <t>Un-tick a one-off the DAY AFTER it was ticked</t>
         </is>
       </c>
       <c r="E333" s="9" t="inlineStr">
         <is>
-          <t>Hold a shared row, tap 'Bring to my Today'. Look at your Today, then at the shared list on BOTH accounts.</t>
+          <t>Tick a shared one-off. Change the device date to tomorrow (or wait a day), reopen the room, tap it again.</t>
         </is>
       </c>
       <c r="F333" s="9" t="inlineStr">
         <is>
-          <t>Your Today shows the task with a faint '· Ours'. The shared row is completely unchanged on both sides, with no marker of any kind. The held card now reads 'Already on your Today' and cannot make a second copy.</t>
+          <t>It un-ticks. (The pre-fix build could never un-tick it again, on any device, forever.)</t>
         </is>
       </c>
       <c r="G333" s="7" t="inlineStr">
@@ -14054,7 +14054,7 @@
     <row r="334">
       <c r="A334" s="6" t="inlineStr">
         <is>
-          <t>OUR-24</t>
+          <t>OUR-23</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -14069,17 +14069,17 @@
       </c>
       <c r="D334" s="9" t="inlineStr">
         <is>
-          <t>Your tick on the copy closes both</t>
+          <t>Bring to my Today makes a COPY, and marks only yours</t>
         </is>
       </c>
       <c r="E334" s="9" t="inlineStr">
         <is>
-          <t>Tick the brought copy on your Today. Check the shared list on the other account.</t>
+          <t>Hold a shared row, tap 'Bring to my Today'. Look at your Today, then at the shared list on BOTH accounts.</t>
         </is>
       </c>
       <c r="F334" s="9" t="inlineStr">
         <is>
-          <t>The shared row is done. It enters YOUR Lookback. Nothing on the other side says who did it.</t>
+          <t>Your Today shows the task with a faint '· Ours'. The shared row is completely unchanged on both sides, with no marker of any kind. The held card now reads 'Already on your Today' and cannot make a second copy.</t>
         </is>
       </c>
       <c r="G334" s="7" t="inlineStr">
@@ -14094,7 +14094,7 @@
     <row r="335">
       <c r="A335" s="6" t="inlineStr">
         <is>
-          <t>OUR-25</t>
+          <t>OUR-24</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -14109,17 +14109,17 @@
       </c>
       <c r="D335" s="9" t="inlineStr">
         <is>
-          <t>Ticking a brought copy on a device that has NEVER opened the room</t>
+          <t>Your tick on the copy closes both</t>
         </is>
       </c>
       <c r="E335" s="9" t="inlineStr">
         <is>
-          <t>Bring a task over on phone A. Sign in on a second device (or clear its local data) and go straight to Today WITHOUT opening Ours. Tick the copy there.</t>
+          <t>Tick the brought copy on your Today. Check the shared list on the other account.</t>
         </is>
       </c>
       <c r="F335" s="9" t="inlineStr">
         <is>
-          <t>The shared row closes. (The pre-fix build silently discarded the tick with no error.)</t>
+          <t>The shared row is done. It enters YOUR Lookback. Nothing on the other side says who did it.</t>
         </is>
       </c>
       <c r="G335" s="7" t="inlineStr">
@@ -14134,7 +14134,7 @@
     <row r="336">
       <c r="A336" s="6" t="inlineStr">
         <is>
-          <t>OUR-26</t>
+          <t>OUR-25</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -14149,17 +14149,17 @@
       </c>
       <c r="D336" s="9" t="inlineStr">
         <is>
-          <t>Their tick leaves a rest-note, never a strike-through</t>
+          <t>Ticking a brought copy on a device that has NEVER opened the room</t>
         </is>
       </c>
       <c r="E336" s="9" t="inlineStr">
         <is>
-          <t>Bring a task over. On the OTHER account, tick the shared row. Return to your Today.</t>
+          <t>Bring a task over on phone A. Sign in on a second device (or clear its local data) and go straight to Today WITHOUT opening Ours. Tick the copy there.</t>
         </is>
       </c>
       <c r="F336" s="9" t="inlineStr">
         <is>
-          <t>Your copy is gone from the day, replaced by a dashed sage line: 'Handled on Ours. It's off your day.' It is NOT struck through and does NOT appear in your Lookback. Leaving Today and coming back clears the note.</t>
+          <t>The shared row closes. (The pre-fix build silently discarded the tick with no error.)</t>
         </is>
       </c>
       <c r="G336" s="7" t="inlineStr">
@@ -14174,7 +14174,7 @@
     <row r="337">
       <c r="A337" s="6" t="inlineStr">
         <is>
-          <t>OUR-27</t>
+          <t>OUR-26</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -14182,24 +14182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C337" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C337" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D337" s="9" t="inlineStr">
         <is>
-          <t>Share to Ours warns about the length BEFORE it copies</t>
+          <t>Their tick leaves a rest-note, never a strike-through</t>
         </is>
       </c>
       <c r="E337" s="9" t="inlineStr">
         <is>
-          <t>Hold one of your own Today tasks with a very long title (500+ chars), open More, tap 'Share to Ours'.</t>
+          <t>Bring a task over. On the OTHER account, tick the shared row. Return to your Today.</t>
         </is>
       </c>
       <c r="F337" s="9" t="inlineStr">
         <is>
-          <t>A line says Ours keeps titles shorter and this one will be trimmed, BEFORE the copy is made. The copy appears on the shared list. 'Share to Ours' is absent entirely when there is no live list.</t>
+          <t>Your copy is gone from the day, replaced by a dashed sage line: 'Handled on Ours. It's off your day.' It is NOT struck through and does NOT appear in your Lookback. Leaving Today and coming back clears the note.</t>
         </is>
       </c>
       <c r="G337" s="7" t="inlineStr">
@@ -14214,7 +14214,7 @@
     <row r="338">
       <c r="A338" s="6" t="inlineStr">
         <is>
-          <t>OUR-28</t>
+          <t>OUR-27</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -14222,24 +14222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C338" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C338" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D338" s="9" t="inlineStr">
         <is>
-          <t>A repeat set on Ours uses the SAME cadence sheet as home</t>
+          <t>Share to Ours warns about the length BEFORE it copies</t>
         </is>
       </c>
       <c r="E338" s="9" t="inlineStr">
         <is>
-          <t>Hold a shared row, tap 'Repeat…'. Compare with Menu › Repeating › Edit on a personal task.</t>
+          <t>Hold one of your own Today tasks with a very long title (500+ chars), open More, tap 'Share to Ours'.</t>
         </is>
       </c>
       <c r="F338" s="9" t="inlineStr">
         <is>
-          <t>Identical controls. The commit button NAMES the cadence ('Every day', 'Every 2 days'), on both. The Ours sheet adds one line: 'You'll both see it on its day.' It appears on its days for both people.</t>
+          <t>A line says Ours keeps titles shorter and this one will be trimmed, BEFORE the copy is made. The copy appears on the shared list. 'Share to Ours' is absent entirely when there is no live list.</t>
         </is>
       </c>
       <c r="G338" s="7" t="inlineStr">
@@ -14254,7 +14254,7 @@
     <row r="339">
       <c r="A339" s="6" t="inlineStr">
         <is>
-          <t>OUR-29</t>
+          <t>OUR-28</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -14269,17 +14269,17 @@
       </c>
       <c r="D339" s="9" t="inlineStr">
         <is>
-          <t>A cadence this build cannot read is inert, and says why</t>
+          <t>A repeat set on Ours uses the SAME cadence sheet as home</t>
         </is>
       </c>
       <c r="E339" s="9" t="inlineStr">
         <is>
-          <t>Get a shared row carrying a recurrence this build does not understand (a newer build, or hand-write one via the API).</t>
+          <t>Hold a shared row, tap 'Repeat…'. Compare with Menu › Repeating › Edit on a personal task.</t>
         </is>
       </c>
       <c r="F339" s="9" t="inlineStr">
         <is>
-          <t>The row is SHOWN, never hidden. Tapping it does nothing and a line explains it is safe and will appear on its days after an update. 'Repeat…' is withheld. It never marks itself done.</t>
+          <t>Identical controls. The commit button NAMES the cadence ('Every day', 'Every 2 days'), on both. The Ours sheet adds one line: 'You'll both see it on its day.' It appears on its days for both people.</t>
         </is>
       </c>
       <c r="G339" s="7" t="inlineStr">
@@ -14294,7 +14294,7 @@
     <row r="340">
       <c r="A340" s="6" t="inlineStr">
         <is>
-          <t>OUR-30</t>
+          <t>OUR-29</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -14302,24 +14302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C340" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C340" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D340" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash marks what changed, and never your own edits</t>
+          <t>A cadence this build cannot read is inert, and says why</t>
         </is>
       </c>
       <c r="E340" s="9" t="inlineStr">
         <is>
-          <t>Have the other account add and change a few rows. Open the room. Then tick something yourself and reopen.</t>
+          <t>Get a shared row carrying a recurrence this build does not understand (a newer build, or hand-write one via the API).</t>
         </is>
       </c>
       <c r="F340" s="9" t="inlineStr">
         <is>
-          <t>Their changed rows carry a tint and a firmer border on arrival; a screen reader says 'changed since you last looked'. Your OWN edits are never washed. Leaving and returning clears it.</t>
+          <t>The row is SHOWN, never hidden. Tapping it does nothing and a line explains it is safe and will appear on its days after an update. 'Repeat…' is withheld. It never marks itself done.</t>
         </is>
       </c>
       <c r="G340" s="7" t="inlineStr">
@@ -14334,7 +14334,7 @@
     <row r="341">
       <c r="A341" s="6" t="inlineStr">
         <is>
-          <t>OUR-31</t>
+          <t>OUR-30</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -14349,17 +14349,17 @@
       </c>
       <c r="D341" s="9" t="inlineStr">
         <is>
-          <t>Recently removed puts a task back</t>
+          <t>The quiet wash marks what changed, and never your own edits</t>
         </is>
       </c>
       <c r="E341" s="9" t="inlineStr">
         <is>
-          <t>Remove a shared row. Scroll to the foot of the list.</t>
+          <t>Have the other account add and change a few rows. Open the room. Then tick something yourself and reopen.</t>
         </is>
       </c>
       <c r="F341" s="9" t="inlineStr">
         <is>
-          <t>It sits under 'Recently removed', dimmed, with 'Put it back'. Restoring returns it for both people. Nothing anywhere says which of you removed it.</t>
+          <t>Their changed rows carry a tint and a firmer border on arrival; a screen reader says 'changed since you last looked'. Your OWN edits are never washed. Leaving and returning clears it.</t>
         </is>
       </c>
       <c r="G341" s="7" t="inlineStr">
@@ -14374,7 +14374,7 @@
     <row r="342">
       <c r="A342" s="6" t="inlineStr">
         <is>
-          <t>OUR-32</t>
+          <t>OUR-31</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -14389,17 +14389,17 @@
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>Removing a shared REPEAT does not pretend to be 'Skip today'</t>
+          <t>Recently removed puts a task back</t>
         </is>
       </c>
       <c r="E342" s="9" t="inlineStr">
         <is>
-          <t>Hold a repeating shared row and look at the shelf.</t>
+          <t>Remove a shared row. Scroll to the foot of the list.</t>
         </is>
       </c>
       <c r="F342" s="9" t="inlineStr">
         <is>
-          <t>It reads 'Remove', not 'Skip today', and the spoken label names removing the repeat. (The shared list has no per-day skip; the pre-fix build promised one and deleted the series for both people.)</t>
+          <t>It sits under 'Recently removed', dimmed, with 'Put it back'. Restoring returns it for both people. Nothing anywhere says which of you removed it.</t>
         </is>
       </c>
       <c r="G342" s="7" t="inlineStr">
@@ -14414,7 +14414,7 @@
     <row r="343">
       <c r="A343" s="6" t="inlineStr">
         <is>
-          <t>OUR-33</t>
+          <t>OUR-32</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -14422,24 +14422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C343" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C343" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D343" s="9" t="inlineStr">
         <is>
-          <t>A closed list is still readable, and read-only</t>
+          <t>Removing a shared REPEAT does not pretend to be 'Skip today'</t>
         </is>
       </c>
       <c r="E343" s="9" t="inlineStr">
         <is>
-          <t>Leave a list. Open it from the archive on the pairing screen.</t>
+          <t>Hold a repeating shared row and look at the shelf.</t>
         </is>
       </c>
       <c r="F343" s="9" t="inlineStr">
         <is>
-          <t>Every row is readable. There is no + pill at all. Ticking, renaming, removing and re-cadencing all do nothing, and each row says why. Each row still offers taking a copy for yourself.</t>
+          <t>It reads 'Remove', not 'Skip today', and the spoken label names removing the repeat. (The shared list has no per-day skip; the pre-fix build promised one and deleted the series for both people.)</t>
         </is>
       </c>
       <c r="G343" s="7" t="inlineStr">
@@ -14454,7 +14454,7 @@
     <row r="344">
       <c r="A344" s="6" t="inlineStr">
         <is>
-          <t>OUR-34</t>
+          <t>OUR-33</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -14462,24 +14462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C344" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C344" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D344" s="9" t="inlineStr">
         <is>
-          <t>The archive lists closed lists, and puts them away</t>
+          <t>A closed list is still readable, and read-only</t>
         </is>
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>With at least one closed list, look under 'Lists you have kept' on the pairing screen.</t>
+          <t>Leave a list. Open it from the archive on the pairing screen.</t>
         </is>
       </c>
       <c r="F344" s="9" t="inlineStr">
         <is>
-          <t>Purpose and closed MONTH only, no counts of any kind. 'Put it away' hides it from the default view; 'Show the ones put away' brings it back. Nothing is deleted.</t>
+          <t>Every row is readable. There is no + pill at all. Ticking, renaming, removing and re-cadencing all do nothing, and each row says why. Each row still offers taking a copy for yourself.</t>
         </is>
       </c>
       <c r="G344" s="7" t="inlineStr">
@@ -14494,7 +14494,7 @@
     <row r="345">
       <c r="A345" s="6" t="inlineStr">
         <is>
-          <t>OUR-35</t>
+          <t>OUR-34</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -14502,24 +14502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C345" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C345" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D345" s="9" t="inlineStr">
         <is>
-          <t>Reopening together is a handshake, never unilateral</t>
+          <t>The archive lists closed lists, and puts them away</t>
         </is>
       </c>
       <c r="E345" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Reopen together…' on ONE side only and STAY on that screen, hands off. Read the code to the second account. On that side, tap 'Got a code from them? Enter it to reopen.' (under the reopen hint on the closed-list screen) and enter it. Repeat with the closed list being the ONLY closed list on both accounts.</t>
+          <t>With at least one closed list, look under 'Lists you have kept' on the pairing screen.</t>
         </is>
       </c>
       <c r="F345" s="9" t="inlineStr">
         <is>
-          <t>The offering side gets a code and nothing reopens yet. The other side has a named door to the join field and entering the code there reopens the list for both, with everything as it was. It is never asked which kind of code it is, and it works when the closed list on screen is the only one (the D2 'handshake purgatory', 2026-09-22). Within about ten seconds, with nothing touched, the offering side's screen changes on its own: the code is gone and the live list shows 'They used the code. The list is open again…'.</t>
+          <t>Purpose and closed MONTH only, no counts of any kind. 'Put it away' hides it from the default view; 'Show the ones put away' brings it back. Nothing is deleted.</t>
         </is>
       </c>
       <c r="G345" s="7" t="inlineStr">
@@ -14534,7 +14534,7 @@
     <row r="346">
       <c r="A346" s="6" t="inlineStr">
         <is>
-          <t>OUR-122</t>
+          <t>OUR-35</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -14542,24 +14542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C346" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C346" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D346" s="9" t="inlineStr">
         <is>
-          <t>Waiting screens look on their own, and 'Check now' is there for the impatient</t>
+          <t>Reopening together is a handshake, never unilateral</t>
         </is>
       </c>
       <c r="E346" s="9" t="inlineStr">
         <is>
-          <t>A: mint a pairing code and stay on that screen, hands off. B: join. Watch A. Then, on a closed list: A taps 'Reopen together…' and stays; B redeems. Watch A. Then, on either waiting screen, tap 'Check now'.</t>
+          <t>On a closed list, tap 'Reopen together…' on ONE side only and STAY on that screen, hands off. Read the code to the second account. On that side, tap 'Got a code from them? Enter it to reopen.' (under the reopen hint on the closed-list screen) and enter it. Repeat with the closed list being the ONLY closed list on both accounts.</t>
         </is>
       </c>
       <c r="F346" s="9" t="inlineStr">
         <is>
-          <t>Both times A's screen changes on its own within about ten seconds: the pairing wait becomes '{name} joined.', and the closed list becomes the live list with the 'They used the code' line and the spent code gone. 'Check now' sits under the waiting text and under a minted reopen code, and does the same immediately. Once A has opened the list, the pairing screen underneath stops looking (nothing to see by eye; the rule is focus AND foreground AND under 30 minutes).</t>
+          <t>The offering side gets a code and nothing reopens yet. The other side has a named door to the join field and entering the code there reopens the list for both, with everything as it was. It is never asked which kind of code it is, and it works when the closed list on screen is the only one (the D2 'handshake purgatory', 2026-09-22). Within about ten seconds, with nothing touched, the offering side's screen changes on its own: the code is gone and the live list shows 'They used the code. The list is open again…'.</t>
         </is>
       </c>
       <c r="G346" s="7" t="inlineStr">
@@ -14574,7 +14574,7 @@
     <row r="347">
       <c r="A347" s="6" t="inlineStr">
         <is>
-          <t>OUR-123</t>
+          <t>OUR-122</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -14582,24 +14582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C347" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C347" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D347" s="9" t="inlineStr">
         <is>
-          <t>The Ours card goes home rather than into a room</t>
+          <t>Waiting screens look on their own, and 'Check now' is there for the impatient</t>
         </is>
       </c>
       <c r="E347" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, open the Menu and tap Ours. Then open the Menu from the Ours tab and tap Ours again. Then, with no shared list yet (signed in), tap Ours from the Menu.</t>
+          <t>A: mint a pairing code and stay on that screen, hands off. B: join. Watch A. Then, on a closed list: A taps 'Reopen together…' and stays; B redeems. Watch A. Then, on either waiting screen, tap 'Check now'.</t>
         </is>
       </c>
       <c r="F347" s="9" t="inlineStr">
         <is>
-          <t>With a live list the contents page closes and you land on Today's Ours tab (the list's name underlined) in one short fade; back from there does not return to the contents page. From the Ours tab's own Menu, the Ours card simply goes back to it. With no list yet it opens the invite screen as a room: '‹ Menu' and the two-mugs picture as a band, then the invite screen as it was.</t>
+          <t>Both times A's screen changes on its own within about ten seconds: the pairing wait becomes '{name} joined.', and the closed list becomes the live list with the 'They used the code' line and the spent code gone. 'Check now' sits under the waiting text and under a minted reopen code, and does the same immediately. Once A has opened the list, the pairing screen underneath stops looking (nothing to see by eye; the rule is focus AND foreground AND under 30 minutes).</t>
         </is>
       </c>
       <c r="G347" s="7" t="inlineStr">
@@ -14614,7 +14614,7 @@
     <row r="348">
       <c r="A348" s="6" t="inlineStr">
         <is>
-          <t>OUR-124</t>
+          <t>OUR-123</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -14622,24 +14622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C348" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C348" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D348" s="9" t="inlineStr">
         <is>
-          <t>The room opens with your list's own name, in any language</t>
+          <t>The Ours card goes home rather than into a room</t>
         </is>
       </c>
       <c r="E348" s="9" t="inlineStr">
         <is>
-          <t>With a named shared list (e.g. 'Just us') and the app set to Italian (or German, Spanish, French), tap the list's name in Today's heading.</t>
+          <t>With a live shared list, open the Menu and tap Ours. Then open the Menu from the Ours tab and tap Ours again. Then, with no shared list yet (signed in), tap Ours from the Menu.</t>
         </is>
       </c>
       <c r="F348" s="9" t="inlineStr">
         <is>
-          <t>The room's heading shows your list's own name from the first frame, and the capture panel's heading reads 'Aggiungi a Just us'. It never shows the default ('La nostra lista') for a beat and then flips, which read as the app changing language. A list with no name shows the default in the app's language. The list's own name is shown as you typed it, in whatever language that was.</t>
+          <t>With a live list the contents page closes and you land on Today's Ours tab (the list's name underlined) in one short fade; back from there does not return to the contents page. From the Ours tab's own Menu, the Ours card simply goes back to it. With no list yet it opens the invite screen as a room: '‹ Menu' and the two-mugs picture as a band, then the invite screen as it was.</t>
         </is>
       </c>
       <c r="G348" s="7" t="inlineStr">
@@ -14654,7 +14654,7 @@
     <row r="349">
       <c r="A349" s="6" t="inlineStr">
         <is>
-          <t>OUR-36</t>
+          <t>OUR-124</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -14662,24 +14662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C349" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C349" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D349" s="9" t="inlineStr">
         <is>
-          <t>Delete for good commits when the screen closes, not on a timer</t>
+          <t>The room opens with your list's own name, in any language</t>
         </is>
       </c>
       <c r="E349" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
+          <t>With a named shared list (e.g. 'Just us') and the app set to Italian (or German, Spanish, French), tap the list's name in Today's heading.</t>
         </is>
       </c>
       <c r="F349" s="9" t="inlineStr">
         <is>
-          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
+          <t>The room's heading shows your list's own name from the first frame, and the capture panel's heading reads 'Aggiungi a Just us'. It never shows the default ('La nostra lista') for a beat and then flips, which read as the app changing language. A list with no name shows the default in the app's language. The list's own name is shown as you typed it, in whatever language that was.</t>
         </is>
       </c>
       <c r="G349" s="7" t="inlineStr">
@@ -14694,7 +14694,7 @@
     <row r="350">
       <c r="A350" s="6" t="inlineStr">
         <is>
-          <t>OUR-37</t>
+          <t>OUR-36</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -14702,24 +14702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C350" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C350" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D350" s="9" t="inlineStr">
         <is>
-          <t>Rename yourself, and only yourself</t>
+          <t>Delete for good commits when the screen closes, not on a timer</t>
         </is>
       </c>
       <c r="E350" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
+          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
         </is>
       </c>
       <c r="F350" s="9" t="inlineStr">
         <is>
-          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
+          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
         </is>
       </c>
       <c r="G350" s="7" t="inlineStr">
@@ -14734,7 +14734,7 @@
     <row r="351">
       <c r="A351" s="6" t="inlineStr">
         <is>
-          <t>OUR-38</t>
+          <t>OUR-37</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -14749,17 +14749,17 @@
       </c>
       <c r="D351" s="9" t="inlineStr">
         <is>
-          <t>A dropped signal never throws you out of the room</t>
+          <t>Rename yourself, and only yourself</t>
         </is>
       </c>
       <c r="E351" s="9" t="inlineStr">
         <is>
-          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
+          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
         </is>
       </c>
       <c r="F351" s="9" t="inlineStr">
         <is>
-          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
+          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
         </is>
       </c>
       <c r="G351" s="7" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="352">
       <c r="A352" s="6" t="inlineStr">
         <is>
-          <t>OUR-39</t>
+          <t>OUR-38</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -14782,24 +14782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C352" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C352" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D352" s="9" t="inlineStr">
         <is>
-          <t>Report this list reaches us and tells nobody else</t>
+          <t>A dropped signal never throws you out of the room</t>
         </is>
       </c>
       <c r="E352" s="9" t="inlineStr">
         <is>
-          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
+          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
         </is>
       </c>
       <c r="F352" s="9" t="inlineStr">
         <is>
-          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
+          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
         </is>
       </c>
       <c r="G352" s="7" t="inlineStr">
@@ -14814,7 +14814,7 @@
     <row r="353">
       <c r="A353" s="6" t="inlineStr">
         <is>
-          <t>OUR-40</t>
+          <t>OUR-39</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -14829,17 +14829,17 @@
       </c>
       <c r="D353" s="9" t="inlineStr">
         <is>
-          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
+          <t>Report this list reaches us and tells nobody else</t>
         </is>
       </c>
       <c r="E353" s="9" t="inlineStr">
         <is>
-          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
+          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
         </is>
       </c>
       <c r="F353" s="9" t="inlineStr">
         <is>
-          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
+          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
         </is>
       </c>
       <c r="G353" s="7" t="inlineStr">
@@ -14854,7 +14854,7 @@
     <row r="354">
       <c r="A354" s="6" t="inlineStr">
         <is>
-          <t>OUR-41</t>
+          <t>OUR-40</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -14862,24 +14862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C354" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C354" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D354" s="9" t="inlineStr">
         <is>
-          <t>Leaving is the block, and needs no reason</t>
+          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
         </is>
       </c>
       <c r="E354" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap 'Leave this list'.</t>
+          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
         </is>
       </c>
       <c r="F354" s="9" t="inlineStr">
         <is>
-          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
+          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
         </is>
       </c>
       <c r="G354" s="7" t="inlineStr">
@@ -14894,12 +14894,12 @@
     <row r="355">
       <c r="A355" s="6" t="inlineStr">
         <is>
-          <t>LEG-05</t>
+          <t>OUR-41</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C355" s="10" t="inlineStr">
@@ -14909,17 +14909,17 @@
       </c>
       <c r="D355" s="9" t="inlineStr">
         <is>
-          <t>The shared-list clauses are in both copies of both documents</t>
+          <t>Leaving is the block, and needs no reason</t>
         </is>
       </c>
       <c r="E355" s="9" t="inlineStr">
         <is>
-          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
+          <t>On a live list, tap 'Leave this list'.</t>
         </is>
       </c>
       <c r="F355" s="9" t="inlineStr">
         <is>
-          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
+          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
         </is>
       </c>
       <c r="G355" s="7" t="inlineStr">
@@ -14934,32 +14934,32 @@
     <row r="356">
       <c r="A356" s="6" t="inlineStr">
         <is>
-          <t>OUR-42</t>
+          <t>LEG-05</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C356" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C356" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D356" s="9" t="inlineStr">
         <is>
-          <t>A change on one phone appears on the other WITHOUT touching it</t>
+          <t>The shared-list clauses are in both copies of both documents</t>
         </is>
       </c>
       <c r="E356" s="9" t="inlineStr">
         <is>
-          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
+          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
         </is>
       </c>
       <c r="F356" s="9" t="inlineStr">
         <is>
-          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
+          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
         </is>
       </c>
       <c r="G356" s="7" t="inlineStr">
@@ -14974,7 +14974,7 @@
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
         <is>
-          <t>OUR-43</t>
+          <t>OUR-42</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -14989,17 +14989,17 @@
       </c>
       <c r="D357" s="9" t="inlineStr">
         <is>
-          <t>Opening your own list does not bounce you back</t>
+          <t>A change on one phone appears on the other WITHOUT touching it</t>
         </is>
       </c>
       <c r="E357" s="9" t="inlineStr">
         <is>
-          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
+          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
         </is>
       </c>
       <c r="F357" s="9" t="inlineStr">
         <is>
-          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
+          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
         </is>
       </c>
       <c r="G357" s="7" t="inlineStr">
@@ -15014,7 +15014,7 @@
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
         <is>
-          <t>OUR-44</t>
+          <t>OUR-43</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -15022,24 +15022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C358" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C358" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D358" s="9" t="inlineStr">
         <is>
-          <t>The pairing screen offers a way INTO the list</t>
+          <t>Opening your own list does not bounce you back</t>
         </is>
       </c>
       <c r="E358" s="9" t="inlineStr">
         <is>
-          <t>Finish pairing, then look at the pairing screen.</t>
+          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
         </is>
       </c>
       <c r="F358" s="9" t="inlineStr">
         <is>
-          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
+          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
         </is>
       </c>
       <c r="G358" s="7" t="inlineStr">
@@ -15054,7 +15054,7 @@
     <row r="359">
       <c r="A359" s="6" t="inlineStr">
         <is>
-          <t>OUR-45</t>
+          <t>OUR-44</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -15069,17 +15069,17 @@
       </c>
       <c r="D359" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash appears and then takes itself away</t>
+          <t>The pairing screen offers a way INTO the list</t>
         </is>
       </c>
       <c r="E359" s="9" t="inlineStr">
         <is>
-          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
+          <t>Finish pairing, then look at the pairing screen.</t>
         </is>
       </c>
       <c r="F359" s="9" t="inlineStr">
         <is>
-          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
+          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
         </is>
       </c>
       <c r="G359" s="7" t="inlineStr">
@@ -15094,7 +15094,7 @@
     <row r="360">
       <c r="A360" s="6" t="inlineStr">
         <is>
-          <t>OUR-47</t>
+          <t>OUR-45</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -15102,24 +15102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C360" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C360" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D360" s="9" t="inlineStr">
         <is>
-          <t>Ours lives in Today's heading (Today v3)</t>
+          <t>The quiet wash appears and then takes itself away</t>
         </is>
       </c>
       <c r="E360" s="9" t="inlineStr">
         <is>
-          <t>With a live list, look at the top of Today. Then leave the list (or sign out) and look again. With a screen reader, move through the heading.</t>
+          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
         </is>
       </c>
       <c r="F360" s="9" t="inlineStr">
         <is>
-          <t>With a live list the heading reads 'Today' and the list's name side by side (its own name when it has one, else 'Ours'), 'Today' underlined as the current tab. With no live list there is only 'Today', and no empty space where Ours would be. A screen reader hears them as tabs, 'Today, selected' and '{name}'. The old Ours door card under the list is gone.</t>
+          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
         </is>
       </c>
       <c r="G360" s="7" t="inlineStr">
@@ -15134,7 +15134,7 @@
     <row r="361">
       <c r="A361" s="6" t="inlineStr">
         <is>
-          <t>OUR-48</t>
+          <t>OUR-47</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -15149,17 +15149,17 @@
       </c>
       <c r="D361" s="9" t="inlineStr">
         <is>
-          <t>Their tick marks your copy DONE and leaves it on your day</t>
+          <t>Ours lives in Today's heading (Today v3)</t>
         </is>
       </c>
       <c r="E361" s="9" t="inlineStr">
         <is>
-          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
+          <t>With a live list, look at the top of Today. Then leave the list (or sign out) and look again. With a screen reader, move through the heading.</t>
         </is>
       </c>
       <c r="F361" s="9" t="inlineStr">
         <is>
-          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
+          <t>With a live list the heading reads 'Today' and the list's name side by side (its own name when it has one, else 'Ours'), 'Today' underlined as the current tab. With no live list there is only 'Today', and no empty space where Ours would be. A screen reader hears them as tabs, 'Today, selected' and '{name}'. The old Ours door card under the list is gone.</t>
         </is>
       </c>
       <c r="G361" s="7" t="inlineStr">
@@ -15174,7 +15174,7 @@
     <row r="362">
       <c r="A362" s="6" t="inlineStr">
         <is>
-          <t>OUR-49</t>
+          <t>OUR-48</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -15189,17 +15189,17 @@
       </c>
       <c r="D362" s="9" t="inlineStr">
         <is>
-          <t>A settled copy carries a completion DATE, not just a done flag</t>
+          <t>Their tick marks your copy DONE and leaves it on your day</t>
         </is>
       </c>
       <c r="E362" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
+          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
         </is>
       </c>
       <c r="F362" s="9" t="inlineStr">
         <is>
-          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
+          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
         </is>
       </c>
       <c r="G362" s="7" t="inlineStr">
@@ -15214,7 +15214,7 @@
     <row r="363">
       <c r="A363" s="6" t="inlineStr">
         <is>
-          <t>OUR-50</t>
+          <t>OUR-49</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -15222,24 +15222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C363" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C363" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D363" s="9" t="inlineStr">
         <is>
-          <t>A finished copy can be brought over again</t>
+          <t>A settled copy carries a completion DATE, not just a done flag</t>
         </is>
       </c>
       <c r="E363" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, hold that row in Ours.</t>
+          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
         </is>
       </c>
       <c r="F363" s="9" t="inlineStr">
         <is>
-          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
+          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
         </is>
       </c>
       <c r="G363" s="7" t="inlineStr">
@@ -15254,7 +15254,7 @@
     <row r="364">
       <c r="A364" s="6" t="inlineStr">
         <is>
-          <t>OUR-51</t>
+          <t>OUR-50</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -15262,24 +15262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C364" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C364" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D364" s="9" t="inlineStr">
         <is>
-          <t>Your own edit never highlights; their later edit always does</t>
+          <t>A finished copy can be brought over again</t>
         </is>
       </c>
       <c r="E364" s="9" t="inlineStr">
         <is>
-          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
+          <t>After OUR-48, hold that row in Ours.</t>
         </is>
       </c>
       <c r="F364" s="9" t="inlineStr">
         <is>
-          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
+          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
         </is>
       </c>
       <c r="G364" s="7" t="inlineStr">
@@ -15294,7 +15294,7 @@
     <row r="365">
       <c r="A365" s="6" t="inlineStr">
         <is>
-          <t>OUR-52</t>
+          <t>OUR-51</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -15302,24 +15302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C365" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C365" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D365" s="9" t="inlineStr">
         <is>
-          <t>The highlight arrives at once and fades away</t>
+          <t>Your own edit never highlights; their later edit always does</t>
         </is>
       </c>
       <c r="E365" s="9" t="inlineStr">
         <is>
-          <t>Have B change a row while A is on the list.</t>
+          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
         </is>
       </c>
       <c r="F365" s="9" t="inlineStr">
         <is>
-          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
+          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
         </is>
       </c>
       <c r="G365" s="7" t="inlineStr">
@@ -15334,7 +15334,7 @@
     <row r="366">
       <c r="A366" s="6" t="inlineStr">
         <is>
-          <t>OUR-53</t>
+          <t>OUR-52</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -15349,17 +15349,17 @@
       </c>
       <c r="D366" s="9" t="inlineStr">
         <is>
-          <t>Two devices share ONE clock</t>
+          <t>The highlight arrives at once and fades away</t>
         </is>
       </c>
       <c r="E366" s="9" t="inlineStr">
         <is>
-          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
+          <t>Have B change a row while A is on the list.</t>
         </is>
       </c>
       <c r="F366" s="9" t="inlineStr">
         <is>
-          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
+          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
         </is>
       </c>
       <c r="G366" s="7" t="inlineStr">
@@ -15374,7 +15374,7 @@
     <row r="367">
       <c r="A367" s="6" t="inlineStr">
         <is>
-          <t>OUR-54</t>
+          <t>OUR-53</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -15382,24 +15382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C367" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C367" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D367" s="9" t="inlineStr">
         <is>
-          <t>The debug panel is opt-in and carries no task text</t>
+          <t>Two devices share ONE clock</t>
         </is>
       </c>
       <c r="E367" s="9" t="inlineStr">
         <is>
-          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
+          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
         </is>
       </c>
       <c r="F367" s="9" t="inlineStr">
         <is>
-          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
+          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
         </is>
       </c>
       <c r="G367" s="7" t="inlineStr">
@@ -15414,7 +15414,7 @@
     <row r="368">
       <c r="A368" s="6" t="inlineStr">
         <is>
-          <t>OUR-55</t>
+          <t>OUR-54</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -15422,24 +15422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C368" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C368" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D368" s="9" t="inlineStr">
         <is>
-          <t>Capture on Ours IS Today's capture</t>
+          <t>The debug panel is opt-in and carries no task text</t>
         </is>
       </c>
       <c r="E368" s="9" t="inlineStr">
         <is>
-          <t>Open a shared list and tap the + pill at the foot of the screen.</t>
+          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
         </is>
       </c>
       <c r="F368" s="9" t="inlineStr">
         <is>
-          <t>The same pill and the same panel Today has, headed 'Add to {name}': the same box, the same Speak button (web), the same When chip and door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
+          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
         </is>
       </c>
       <c r="G368" s="7" t="inlineStr">
@@ -15454,7 +15454,7 @@
     <row r="369">
       <c r="A369" s="6" t="inlineStr">
         <is>
-          <t>OUR-56</t>
+          <t>OUR-55</t>
         </is>
       </c>
       <c r="B369" s="7" t="inlineStr">
@@ -15469,17 +15469,17 @@
       </c>
       <c r="D369" s="9" t="inlineStr">
         <is>
-          <t>Repeating can be set AT capture, without knowing a gesture</t>
+          <t>Capture on Ours IS Today's capture</t>
         </is>
       </c>
       <c r="E369" s="9" t="inlineStr">
         <is>
-          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
+          <t>Open a shared list and tap the + pill at the foot of the screen.</t>
         </is>
       </c>
       <c r="F369" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
+          <t>The same pill and the same panel Today has, headed 'Add to {name}': the same box, the same Speak button (web), the same When chip and door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
         </is>
       </c>
       <c r="G369" s="7" t="inlineStr">
@@ -15494,7 +15494,7 @@
     <row r="370">
       <c r="A370" s="6" t="inlineStr">
         <is>
-          <t>OUR-57</t>
+          <t>OUR-56</t>
         </is>
       </c>
       <c r="B370" s="7" t="inlineStr">
@@ -15502,24 +15502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C370" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C370" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D370" s="9" t="inlineStr">
         <is>
-          <t>A dump becomes several shared rows, in the order typed</t>
+          <t>Repeating can be set AT capture, without knowing a gesture</t>
         </is>
       </c>
       <c r="E370" s="9" t="inlineStr">
         <is>
-          <t>Type three lines into the Ours capture and Add.</t>
+          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
         </is>
       </c>
       <c r="F370" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
+          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
         </is>
       </c>
       <c r="G370" s="7" t="inlineStr">
@@ -15534,7 +15534,7 @@
     <row r="371">
       <c r="A371" s="6" t="inlineStr">
         <is>
-          <t>OUR-58</t>
+          <t>OUR-57</t>
         </is>
       </c>
       <c r="B371" s="7" t="inlineStr">
@@ -15542,24 +15542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C371" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C371" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D371" s="9" t="inlineStr">
         <is>
-          <t>The shared door offers When and Repeating, never Steps</t>
+          <t>A dump becomes several shared rows, in the order typed</t>
         </is>
       </c>
       <c r="E371" s="9" t="inlineStr">
         <is>
-          <t>Open the door on Ours and compare it with the door on Today.</t>
+          <t>Type three lines into the Ours capture and Add.</t>
         </is>
       </c>
       <c r="F371" s="9" t="inlineStr">
         <is>
-          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
+          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
         </is>
       </c>
       <c r="G371" s="7" t="inlineStr">
@@ -15574,7 +15574,7 @@
     <row r="372">
       <c r="A372" s="6" t="inlineStr">
         <is>
-          <t>OUR-59</t>
+          <t>OUR-58</t>
         </is>
       </c>
       <c r="B372" s="7" t="inlineStr">
@@ -15582,24 +15582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C372" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C372" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D372" s="9" t="inlineStr">
         <is>
-          <t>Typed text survives the panel going</t>
+          <t>The shared door offers When and Repeating, never Steps</t>
         </is>
       </c>
       <c r="E372" s="9" t="inlineStr">
         <is>
-          <t>Type half a sentence into the Ours panel, Close it, tick something, then tap the pill again.</t>
+          <t>Open the door on Ours and compare it with the door on Today.</t>
         </is>
       </c>
       <c r="F372" s="9" t="inlineStr">
         <is>
-          <t>The pill shows '+' and three dots while words wait, and the half sentence is still there. The panel is always mounted, never unmounted. Only an Add resets the door; the words never reset on their own.</t>
+          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
         </is>
       </c>
       <c r="G372" s="7" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="373">
       <c r="A373" s="6" t="inlineStr">
         <is>
-          <t>OUR-60</t>
+          <t>OUR-59</t>
         </is>
       </c>
       <c r="B373" s="7" t="inlineStr">
@@ -15629,22 +15629,22 @@
       </c>
       <c r="D373" s="9" t="inlineStr">
         <is>
-          <t>The Ours panel rides above the keyboard</t>
+          <t>Typed text survives the panel going</t>
         </is>
       </c>
       <c r="E373" s="9" t="inlineStr">
         <is>
-          <t>On a real Android device, tap the + pill on the Ours list, tap the box and start typing.</t>
+          <t>Type half a sentence into the Ours panel, Close it, tick something, then tap the pill again.</t>
         </is>
       </c>
       <c r="F373" s="9" t="inlineStr">
         <is>
-          <t>The panel and its Add button stay visible above the keyboard while you type. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
+          <t>The pill shows '+' and three dots while words wait, and the half sentence is still there. The panel is always mounted, never unmounted. Only an Add resets the door; the words never reset on their own.</t>
         </is>
       </c>
       <c r="G373" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H373" s="7" t="inlineStr"/>
@@ -15654,7 +15654,7 @@
     <row r="374">
       <c r="A374" s="6" t="inlineStr">
         <is>
-          <t>OUR-61</t>
+          <t>OUR-60</t>
         </is>
       </c>
       <c r="B374" s="7" t="inlineStr">
@@ -15662,29 +15662,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C374" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C374" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D374" s="9" t="inlineStr">
         <is>
-          <t>No AI on the shared capture</t>
+          <t>The Ours panel rides above the keyboard</t>
         </is>
       </c>
       <c r="E374" s="9" t="inlineStr">
         <is>
-          <t>Open the Ours capture panel with AI enabled in Settings, and type a long run-on line.</t>
+          <t>On a real Android device, tap the + pill on the Ours list, tap the box and start typing.</t>
         </is>
       </c>
       <c r="F374" s="9" t="inlineStr">
         <is>
-          <t>No 'Break it down', no 'Sort for me', and no 'Tidy this into tasks': steps or rewrites a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
+          <t>The panel and its Add button stay visible above the keyboard while you type. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
         </is>
       </c>
       <c r="G374" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H374" s="7" t="inlineStr"/>
@@ -15694,7 +15694,7 @@
     <row r="375">
       <c r="A375" s="6" t="inlineStr">
         <is>
-          <t>OUR-62</t>
+          <t>OUR-61</t>
         </is>
       </c>
       <c r="B375" s="7" t="inlineStr">
@@ -15702,29 +15702,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C375" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C375" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D375" s="9" t="inlineStr">
         <is>
-          <t>Scan (premium) reaches the shared capture</t>
+          <t>No AI on the shared capture</t>
         </is>
       </c>
       <c r="E375" s="9" t="inlineStr">
         <is>
-          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
+          <t>Open the Ours capture panel with AI enabled in Settings, and type a long run-on line.</t>
         </is>
       </c>
       <c r="F375" s="9" t="inlineStr">
         <is>
-          <t>The panel rises with the words IN its box (keyboard down), not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
+          <t>No 'Break it down', no 'Sort for me', and no 'Tidy this into tasks': steps or rewrites a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
         </is>
       </c>
       <c r="G375" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H375" s="7" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
     <row r="376">
       <c r="A376" s="6" t="inlineStr">
         <is>
-          <t>OUR-63</t>
+          <t>OUR-62</t>
         </is>
       </c>
       <c r="B376" s="7" t="inlineStr">
@@ -15749,22 +15749,22 @@
       </c>
       <c r="D376" s="9" t="inlineStr">
         <is>
-          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
+          <t>Scan (premium) reaches the shared capture</t>
         </is>
       </c>
       <c r="E376" s="9" t="inlineStr">
         <is>
-          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
+          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
         </is>
       </c>
       <c r="F376" s="9" t="inlineStr">
         <is>
-          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
+          <t>The panel rises with the words IN its box (keyboard down), not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
         </is>
       </c>
       <c r="G376" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H376" s="7" t="inlineStr"/>
@@ -15774,7 +15774,7 @@
     <row r="377">
       <c r="A377" s="6" t="inlineStr">
         <is>
-          <t>OUR-64</t>
+          <t>OUR-63</t>
         </is>
       </c>
       <c r="B377" s="7" t="inlineStr">
@@ -15782,24 +15782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C377" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C377" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D377" s="9" t="inlineStr">
         <is>
-          <t>The photo never reaches the shared list</t>
+          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
         </is>
       </c>
       <c r="E377" s="9" t="inlineStr">
         <is>
-          <t>Scan something into Ours and Add it. Check the other device.</t>
+          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
         </is>
       </c>
       <c r="F377" s="9" t="inlineStr">
         <is>
-          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
+          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
         </is>
       </c>
       <c r="G377" s="7" t="inlineStr">
@@ -15814,7 +15814,7 @@
     <row r="378">
       <c r="A378" s="6" t="inlineStr">
         <is>
-          <t>OUR-65</t>
+          <t>OUR-64</t>
         </is>
       </c>
       <c r="B378" s="7" t="inlineStr">
@@ -15822,24 +15822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C378" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C378" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D378" s="9" t="inlineStr">
         <is>
-          <t>Scan is absent when AI is off</t>
+          <t>The photo never reaches the shared list</t>
         </is>
       </c>
       <c r="E378" s="9" t="inlineStr">
         <is>
-          <t>Turn AI off in Settings, then open the Ours capture.</t>
+          <t>Scan something into Ours and Add it. Check the other device.</t>
         </is>
       </c>
       <c r="F378" s="9" t="inlineStr">
         <is>
-          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
+          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
         </is>
       </c>
       <c r="G378" s="7" t="inlineStr">
@@ -15854,7 +15854,7 @@
     <row r="379">
       <c r="A379" s="6" t="inlineStr">
         <is>
-          <t>OUR-66</t>
+          <t>OUR-65</t>
         </is>
       </c>
       <c r="B379" s="7" t="inlineStr">
@@ -15862,24 +15862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C379" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C379" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D379" s="9" t="inlineStr">
         <is>
-          <t>A repeating shared row appears on BOTH Todays on its day</t>
+          <t>Scan is absent when AI is off</t>
         </is>
       </c>
       <c r="E379" s="9" t="inlineStr">
         <is>
-          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
+          <t>Turn AI off in Settings, then open the Ours capture.</t>
         </is>
       </c>
       <c r="F379" s="9" t="inlineStr">
         <is>
-          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
+          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
         </is>
       </c>
       <c r="G379" s="7" t="inlineStr">
@@ -15894,7 +15894,7 @@
     <row r="380">
       <c r="A380" s="6" t="inlineStr">
         <is>
-          <t>OUR-67</t>
+          <t>OUR-66</t>
         </is>
       </c>
       <c r="B380" s="7" t="inlineStr">
@@ -15909,17 +15909,17 @@
       </c>
       <c r="D380" s="9" t="inlineStr">
         <is>
-          <t>An UNDATED shared row never reaches Today</t>
+          <t>A repeating shared row appears on BOTH Todays on its day</t>
         </is>
       </c>
       <c r="E380" s="9" t="inlineStr">
         <is>
-          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
+          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
         </is>
       </c>
       <c r="F380" s="9" t="inlineStr">
         <is>
-          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
+          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
         </is>
       </c>
       <c r="G380" s="7" t="inlineStr">
@@ -15934,7 +15934,7 @@
     <row r="381">
       <c r="A381" s="6" t="inlineStr">
         <is>
-          <t>OUR-68</t>
+          <t>OUR-67</t>
         </is>
       </c>
       <c r="B381" s="7" t="inlineStr">
@@ -15949,17 +15949,17 @@
       </c>
       <c r="D381" s="9" t="inlineStr">
         <is>
-          <t>Shared rows never make the day look heavier</t>
+          <t>An UNDATED shared row never reaches Today</t>
         </is>
       </c>
       <c r="E381" s="9" t="inlineStr">
         <is>
-          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
+          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
         </is>
       </c>
       <c r="F381" s="9" t="inlineStr">
         <is>
-          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
+          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
         </is>
       </c>
       <c r="G381" s="7" t="inlineStr">
@@ -15974,7 +15974,7 @@
     <row r="382">
       <c r="A382" s="6" t="inlineStr">
         <is>
-          <t>OUR-69</t>
+          <t>OUR-68</t>
         </is>
       </c>
       <c r="B382" s="7" t="inlineStr">
@@ -15989,17 +15989,17 @@
       </c>
       <c r="D382" s="9" t="inlineStr">
         <is>
-          <t>Ticking a shared row from Today closes it for both</t>
+          <t>Shared rows never make the day look heavier</t>
         </is>
       </c>
       <c r="E382" s="9" t="inlineStr">
         <is>
-          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
+          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
         </is>
       </c>
       <c r="F382" s="9" t="inlineStr">
         <is>
-          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
+          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
         </is>
       </c>
       <c r="G382" s="7" t="inlineStr">
@@ -16014,7 +16014,7 @@
     <row r="383">
       <c r="A383" s="6" t="inlineStr">
         <is>
-          <t>OUR-70</t>
+          <t>OUR-69</t>
         </is>
       </c>
       <c r="B383" s="7" t="inlineStr">
@@ -16022,24 +16022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C383" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C383" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D383" s="9" t="inlineStr">
         <is>
-          <t>A dated shared row shows from its day onward, never before</t>
+          <t>Ticking a shared row from Today closes it for both</t>
         </is>
       </c>
       <c r="E383" s="9" t="inlineStr">
         <is>
-          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
+          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
         </is>
       </c>
       <c r="F383" s="9" t="inlineStr">
         <is>
-          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
+          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
         </is>
       </c>
       <c r="G383" s="7" t="inlineStr">
@@ -16054,7 +16054,7 @@
     <row r="384">
       <c r="A384" s="6" t="inlineStr">
         <is>
-          <t>OUR-71</t>
+          <t>OUR-70</t>
         </is>
       </c>
       <c r="B384" s="7" t="inlineStr">
@@ -16062,24 +16062,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C384" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C384" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D384" s="9" t="inlineStr">
         <is>
-          <t>The shared capture rests on Anytime, and says what a day means</t>
+          <t>A dated shared row shows from its day onward, never before</t>
         </is>
       </c>
       <c r="E384" s="9" t="inlineStr">
         <is>
-          <t>Tap the + pill on Ours and read the line beside the When chip. Open the door. Pick Today, then Tomorrow, then Daily, reading that line each time.</t>
+          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
         </is>
       </c>
       <c r="F384" s="9" t="inlineStr">
         <is>
-          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected, and the Add button says just 'Add'. Choosing Today makes it read 'Add · Today', because that is the notable case: it will appear on both your days. The line beside the chip says, in plain words, what the current choice means on a shared list (no day lives here; a day reaches both Todays; a rhythm repeats for both of you), before you add.</t>
+          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
         </is>
       </c>
       <c r="G384" s="7" t="inlineStr">
@@ -16094,7 +16094,7 @@
     <row r="385">
       <c r="A385" s="6" t="inlineStr">
         <is>
-          <t>OUR-112</t>
+          <t>OUR-71</t>
         </is>
       </c>
       <c r="B385" s="7" t="inlineStr">
@@ -16109,17 +16109,17 @@
       </c>
       <c r="D385" s="9" t="inlineStr">
         <is>
-          <t>A shared row's WHEN can be changed, and cleared</t>
+          <t>The shared capture rests on Anytime, and says what a day means</t>
         </is>
       </c>
       <c r="E385" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
+          <t>Tap the + pill on Ours and read the line beside the When chip. Open the door. Pick Today, then Tomorrow, then Daily, reading that line each time.</t>
         </is>
       </c>
       <c r="F385" s="9" t="inlineStr">
         <is>
-          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
+          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected, and the Add button says just 'Add'. Choosing Today makes it read 'Add · Today', because that is the notable case: it will appear on both your days. The line beside the chip says, in plain words, what the current choice means on a shared list (no day lives here; a day reaches both Todays; a rhythm repeats for both of you), before you add.</t>
         </is>
       </c>
       <c r="G385" s="7" t="inlineStr">
@@ -16134,7 +16134,7 @@
     <row r="386">
       <c r="A386" s="6" t="inlineStr">
         <is>
-          <t>OUR-113</t>
+          <t>OUR-112</t>
         </is>
       </c>
       <c r="B386" s="7" t="inlineStr">
@@ -16149,17 +16149,17 @@
       </c>
       <c r="D386" s="9" t="inlineStr">
         <is>
-          <t>Ending a rhythm does NOT mark the row done for both people</t>
+          <t>A shared row's WHEN can be changed, and cleared</t>
         </is>
       </c>
       <c r="E386" s="9" t="inlineStr">
         <is>
-          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
+          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
         </is>
       </c>
       <c r="F386" s="9" t="inlineStr">
         <is>
-          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
+          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
         </is>
       </c>
       <c r="G386" s="7" t="inlineStr">
@@ -16174,7 +16174,7 @@
     <row r="387">
       <c r="A387" s="6" t="inlineStr">
         <is>
-          <t>OUR-114</t>
+          <t>OUR-113</t>
         </is>
       </c>
       <c r="B387" s="7" t="inlineStr">
@@ -16182,24 +16182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C387" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C387" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D387" s="9" t="inlineStr">
         <is>
-          <t>The day zone changes its question when a rhythm is alive</t>
+          <t>Ending a rhythm does NOT mark the row done for both people</t>
         </is>
       </c>
       <c r="E387" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
+          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
         </is>
       </c>
       <c r="F387" s="9" t="inlineStr">
         <is>
-          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
+          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
         </is>
       </c>
       <c r="G387" s="7" t="inlineStr">
@@ -16214,7 +16214,7 @@
     <row r="388">
       <c r="A388" s="6" t="inlineStr">
         <is>
-          <t>OUR-115</t>
+          <t>OUR-114</t>
         </is>
       </c>
       <c r="B388" s="7" t="inlineStr">
@@ -16229,17 +16229,17 @@
       </c>
       <c r="D388" s="9" t="inlineStr">
         <is>
-          <t>Setting a shared row to Today actually reaches both Todays</t>
+          <t>The day zone changes its question when a rhythm is alive</t>
         </is>
       </c>
       <c r="E388" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
+          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
         </is>
       </c>
       <c r="F388" s="9" t="inlineStr">
         <is>
-          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
+          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
         </is>
       </c>
       <c r="G388" s="7" t="inlineStr">
@@ -16254,7 +16254,7 @@
     <row r="389">
       <c r="A389" s="6" t="inlineStr">
         <is>
-          <t>OUR-116</t>
+          <t>OUR-115</t>
         </is>
       </c>
       <c r="B389" s="7" t="inlineStr">
@@ -16262,24 +16262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C389" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C389" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D389" s="9" t="inlineStr">
         <is>
-          <t>An idle Set does not wash the row on the other device</t>
+          <t>Setting a shared row to Today actually reaches both Todays</t>
         </is>
       </c>
       <c r="E389" s="9" t="inlineStr">
         <is>
-          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
+          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
         </is>
       </c>
       <c r="F389" s="9" t="inlineStr">
         <is>
-          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
+          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
         </is>
       </c>
       <c r="G389" s="7" t="inlineStr">
@@ -16294,7 +16294,7 @@
     <row r="390">
       <c r="A390" s="6" t="inlineStr">
         <is>
-          <t>OUR-118</t>
+          <t>OUR-116</t>
         </is>
       </c>
       <c r="B390" s="7" t="inlineStr">
@@ -16302,24 +16302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C390" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C390" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D390" s="9" t="inlineStr">
         <is>
-          <t>A repeat you have already done today keeps its held card</t>
+          <t>An idle Set does not wash the row on the other device</t>
         </is>
       </c>
       <c r="E390" s="9" t="inlineStr">
         <is>
-          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
+          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
         </is>
       </c>
       <c r="F390" s="9" t="inlineStr">
         <is>
-          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
+          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
         </is>
       </c>
       <c r="G390" s="7" t="inlineStr">
@@ -16334,7 +16334,7 @@
     <row r="391">
       <c r="A391" s="6" t="inlineStr">
         <is>
-          <t>OUR-117</t>
+          <t>OUR-118</t>
         </is>
       </c>
       <c r="B391" s="7" t="inlineStr">
@@ -16342,24 +16342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C391" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C391" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D391" s="9" t="inlineStr">
         <is>
-          <t>The Repeating room's Edit sheet is untouched by the When editor</t>
+          <t>A repeat you have already done today keeps its held card</t>
         </is>
       </c>
       <c r="E391" s="9" t="inlineStr">
         <is>
-          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
+          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
         </is>
       </c>
       <c r="F391" s="9" t="inlineStr">
         <is>
-          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the Repeating room.</t>
+          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
         </is>
       </c>
       <c r="G391" s="7" t="inlineStr">
@@ -16374,7 +16374,7 @@
     <row r="392">
       <c r="A392" s="6" t="inlineStr">
         <is>
-          <t>OUR-119</t>
+          <t>OUR-117</t>
         </is>
       </c>
       <c r="B392" s="7" t="inlineStr">
@@ -16389,17 +16389,17 @@
       </c>
       <c r="D392" s="9" t="inlineStr">
         <is>
-          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
+          <t>The Repeating room's Edit sheet is untouched by the When editor</t>
         </is>
       </c>
       <c r="E392" s="9" t="inlineStr">
         <is>
-          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
+          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
         </is>
       </c>
       <c r="F392" s="9" t="inlineStr">
         <is>
-          <t>Monthly is the fourth rhythm chip here too, from the same sheet the Repeating room uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
+          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the Repeating room.</t>
         </is>
       </c>
       <c r="G392" s="7" t="inlineStr">
@@ -16414,7 +16414,7 @@
     <row r="393">
       <c r="A393" s="6" t="inlineStr">
         <is>
-          <t>OUR-111</t>
+          <t>OUR-119</t>
         </is>
       </c>
       <c r="B393" s="7" t="inlineStr">
@@ -16422,24 +16422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C393" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C393" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D393" s="9" t="inlineStr">
         <is>
-          <t>A finished dated shared row leaves both Todays the next day</t>
+          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
         </is>
       </c>
       <c r="E393" s="9" t="inlineStr">
         <is>
-          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
+          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
         </is>
       </c>
       <c r="F393" s="9" t="inlineStr">
         <is>
-          <t>Today: still there on BOTH, ticked, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
+          <t>Monthly is the fourth rhythm chip here too, from the same sheet the Repeating room uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
         </is>
       </c>
       <c r="G393" s="7" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="394">
       <c r="A394" s="6" t="inlineStr">
         <is>
-          <t>OUR-72</t>
+          <t>OUR-111</t>
         </is>
       </c>
       <c r="B394" s="7" t="inlineStr">
@@ -16462,24 +16462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C394" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C394" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D394" s="9" t="inlineStr">
         <is>
-          <t>A repeat supersedes the day rather than joining it</t>
+          <t>A finished dated shared row leaves both Todays the next day</t>
         </is>
       </c>
       <c r="E394" s="9" t="inlineStr">
         <is>
-          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
+          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
         </is>
       </c>
       <c r="F394" s="9" t="inlineStr">
         <is>
-          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
+          <t>Today: still there on BOTH, ticked, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
         </is>
       </c>
       <c r="G394" s="7" t="inlineStr">
@@ -16494,7 +16494,7 @@
     <row r="395">
       <c r="A395" s="6" t="inlineStr">
         <is>
-          <t>OUR-73</t>
+          <t>OUR-72</t>
         </is>
       </c>
       <c r="B395" s="7" t="inlineStr">
@@ -16502,24 +16502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C395" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C395" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D395" s="9" t="inlineStr">
         <is>
-          <t>An unreadable cadence is never placed on a day</t>
+          <t>A repeat supersedes the day rather than joining it</t>
         </is>
       </c>
       <c r="E395" s="9" t="inlineStr">
         <is>
-          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
+          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
         </is>
       </c>
       <c r="F395" s="9" t="inlineStr">
         <is>
-          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
+          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
         </is>
       </c>
       <c r="G395" s="7" t="inlineStr">
@@ -16534,7 +16534,7 @@
     <row r="396">
       <c r="A396" s="6" t="inlineStr">
         <is>
-          <t>OUR-74</t>
+          <t>OUR-73</t>
         </is>
       </c>
       <c r="B396" s="7" t="inlineStr">
@@ -16542,24 +16542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C396" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C396" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D396" s="9" t="inlineStr">
         <is>
-          <t>The heading's '!' says something changed since you looked, and clears when you look</t>
+          <t>An unreadable cadence is never placed on a day</t>
         </is>
       </c>
       <c r="E396" s="9" t="inlineStr">
         <is>
-          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap the list's name in the heading and come back. Also have device B delete a row and check again.</t>
+          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
         </is>
       </c>
       <c r="F396" s="9" t="inlineStr">
         <is>
-          <t>A small tinted '!' sits beside the list's name in Today's heading, and a screen reader hears '{name}. 1 since you looked'. After visiting, it is gone. A deleted row never raises it. The mark is bounded by your own attention, not by the list's length, and it never shows a climbing number.</t>
+          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
         </is>
       </c>
       <c r="G396" s="7" t="inlineStr">
@@ -16574,7 +16574,7 @@
     <row r="397">
       <c r="A397" s="6" t="inlineStr">
         <is>
-          <t>OUR-75</t>
+          <t>OUR-74</t>
         </is>
       </c>
       <c r="B397" s="7" t="inlineStr">
@@ -16582,24 +16582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C397" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C397" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D397" s="9" t="inlineStr">
         <is>
-          <t>Your OWN changes never raise the '!'</t>
+          <t>The heading's '!' says something changed since you looked, and clears when you look</t>
         </is>
       </c>
       <c r="E397" s="9" t="inlineStr">
         <is>
-          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
+          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap the list's name in the heading and come back. Also have device B delete a row and check again.</t>
         </is>
       </c>
       <c r="F397" s="9" t="inlineStr">
         <is>
-          <t>No '!' in the heading. It uses the room's own wash arithmetic, so the heading and the room always agree about whose change it was.</t>
+          <t>A small tinted '!' sits beside the list's name in Today's heading, and a screen reader hears '{name}. 1 since you looked'. After visiting, it is gone. A deleted row never raises it. The mark is bounded by your own attention, not by the list's length, and it never shows a climbing number.</t>
         </is>
       </c>
       <c r="G397" s="7" t="inlineStr">
@@ -16614,7 +16614,7 @@
     <row r="398">
       <c r="A398" s="6" t="inlineStr">
         <is>
-          <t>OUR-76</t>
+          <t>OUR-75</t>
         </is>
       </c>
       <c r="B398" s="7" t="inlineStr">
@@ -16629,17 +16629,17 @@
       </c>
       <c r="D398" s="9" t="inlineStr">
         <is>
-          <t>A first-ever visit raises nothing</t>
+          <t>Your OWN changes never raise the '!'</t>
         </is>
       </c>
       <c r="E398" s="9" t="inlineStr">
         <is>
-          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
+          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
         </is>
       </c>
       <c r="F398" s="9" t="inlineStr">
         <is>
-          <t>No '!'. There is no 'last looked' to measure against, and inventing one would open the app with a mark already on it.</t>
+          <t>No '!' in the heading. It uses the room's own wash arithmetic, so the heading and the room always agree about whose change it was.</t>
         </is>
       </c>
       <c r="G398" s="7" t="inlineStr">
@@ -16654,7 +16654,7 @@
     <row r="399">
       <c r="A399" s="6" t="inlineStr">
         <is>
-          <t>OUR-77</t>
+          <t>OUR-76</t>
         </is>
       </c>
       <c r="B399" s="7" t="inlineStr">
@@ -16662,24 +16662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C399" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C399" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D399" s="9" t="inlineStr">
         <is>
-          <t>The capture's AI note names only what that surface HAS</t>
+          <t>A first-ever visit raises nothing</t>
         </is>
       </c>
       <c r="E399" s="9" t="inlineStr">
         <is>
-          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
+          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
         </is>
       </c>
       <c r="F399" s="9" t="inlineStr">
         <is>
-          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
+          <t>No '!'. There is no 'last looked' to measure against, and inventing one would open the app with a mark already on it.</t>
         </is>
       </c>
       <c r="G399" s="7" t="inlineStr">
@@ -16694,7 +16694,7 @@
     <row r="400">
       <c r="A400" s="6" t="inlineStr">
         <is>
-          <t>OUR-78</t>
+          <t>OUR-77</t>
         </is>
       </c>
       <c r="B400" s="7" t="inlineStr">
@@ -16709,17 +16709,17 @@
       </c>
       <c r="D400" s="9" t="inlineStr">
         <is>
-          <t>Scan discloses on every path that can reach a camera</t>
+          <t>The capture's AI note names only what that surface HAS</t>
         </is>
       </c>
       <c r="E400" s="9" t="inlineStr">
         <is>
-          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
+          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
         </is>
       </c>
       <c r="F400" s="9" t="inlineStr">
         <is>
-          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
+          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
         </is>
       </c>
       <c r="G400" s="7" t="inlineStr">
@@ -16734,7 +16734,7 @@
     <row r="401">
       <c r="A401" s="6" t="inlineStr">
         <is>
-          <t>OUR-79</t>
+          <t>OUR-78</t>
         </is>
       </c>
       <c r="B401" s="7" t="inlineStr">
@@ -16749,17 +16749,17 @@
       </c>
       <c r="D401" s="9" t="inlineStr">
         <is>
-          <t>Press and hold a From Ours row on Today</t>
+          <t>Scan discloses on every path that can reach a camera</t>
         </is>
       </c>
       <c r="E401" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Ours strip.</t>
+          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
         </is>
       </c>
       <c r="F401" s="9" t="inlineStr">
         <is>
-          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
+          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
         </is>
       </c>
       <c r="G401" s="7" t="inlineStr">
@@ -16774,7 +16774,7 @@
     <row r="402">
       <c r="A402" s="6" t="inlineStr">
         <is>
-          <t>OUR-80</t>
+          <t>OUR-79</t>
         </is>
       </c>
       <c r="B402" s="7" t="inlineStr">
@@ -16789,17 +16789,17 @@
       </c>
       <c r="D402" s="9" t="inlineStr">
         <is>
-          <t>Pin and Move-to never rearrange the other person's day</t>
+          <t>Press and hold a From Ours row on Today</t>
         </is>
       </c>
       <c r="E402" s="9" t="inlineStr">
         <is>
-          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
+          <t>Hold a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F402" s="9" t="inlineStr">
         <is>
-          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
+          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
         </is>
       </c>
       <c r="G402" s="7" t="inlineStr">
@@ -16814,7 +16814,7 @@
     <row r="403">
       <c r="A403" s="6" t="inlineStr">
         <is>
-          <t>OUR-81</t>
+          <t>OUR-80</t>
         </is>
       </c>
       <c r="B403" s="7" t="inlineStr">
@@ -16822,24 +16822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C403" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C403" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D403" s="9" t="inlineStr">
         <is>
-          <t>A taken-on row is never on screen twice</t>
+          <t>Pin and Move-to never rearrange the other person's day</t>
         </is>
       </c>
       <c r="E403" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
+          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
         </is>
       </c>
       <c r="F403" s="9" t="inlineStr">
         <is>
-          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
+          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
         </is>
       </c>
       <c r="G403" s="7" t="inlineStr">
@@ -16854,7 +16854,7 @@
     <row r="404">
       <c r="A404" s="6" t="inlineStr">
         <is>
-          <t>OUR-82</t>
+          <t>OUR-81</t>
         </is>
       </c>
       <c r="B404" s="7" t="inlineStr">
@@ -16869,17 +16869,17 @@
       </c>
       <c r="D404" s="9" t="inlineStr">
         <is>
-          <t>Move-to is not offered on a repeating shared row</t>
+          <t>A taken-on row is never on screen twice</t>
         </is>
       </c>
       <c r="E404" s="9" t="inlineStr">
         <is>
-          <t>Hold a repeating row in the From Ours strip.</t>
+          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
         </is>
       </c>
       <c r="F404" s="9" t="inlineStr">
         <is>
-          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
+          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
         </is>
       </c>
       <c r="G404" s="7" t="inlineStr">
@@ -16894,7 +16894,7 @@
     <row r="405">
       <c r="A405" s="6" t="inlineStr">
         <is>
-          <t>OUR-83</t>
+          <t>OUR-82</t>
         </is>
       </c>
       <c r="B405" s="7" t="inlineStr">
@@ -16902,24 +16902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C405" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C405" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D405" s="9" t="inlineStr">
         <is>
-          <t>One shared row, one route onto your day</t>
+          <t>Move-to is not offered on a repeating shared row</t>
         </is>
       </c>
       <c r="E405" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
+          <t>Hold a repeating row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F405" s="9" t="inlineStr">
         <is>
-          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
+          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
         </is>
       </c>
       <c r="G405" s="7" t="inlineStr">
@@ -16934,7 +16934,7 @@
     <row r="406">
       <c r="A406" s="6" t="inlineStr">
         <is>
-          <t>OUR-84</t>
+          <t>OUR-83</t>
         </is>
       </c>
       <c r="B406" s="7" t="inlineStr">
@@ -16949,17 +16949,17 @@
       </c>
       <c r="D406" s="9" t="inlineStr">
         <is>
-          <t>Take a From Ours row on, and it becomes an ordinary task</t>
+          <t>One shared row, one route onto your day</t>
         </is>
       </c>
       <c r="E406" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
+          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
         </is>
       </c>
       <c r="F406" s="9" t="inlineStr">
         <is>
-          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
+          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
         </is>
       </c>
       <c r="G406" s="7" t="inlineStr">
@@ -16974,7 +16974,7 @@
     <row r="407">
       <c r="A407" s="6" t="inlineStr">
         <is>
-          <t>OUR-85</t>
+          <t>OUR-84</t>
         </is>
       </c>
       <c r="B407" s="7" t="inlineStr">
@@ -16982,24 +16982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C407" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C407" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D407" s="9" t="inlineStr">
         <is>
-          <t>Break it down works once taken on, and never touches the shared list</t>
+          <t>Take a From Ours row on, and it becomes an ordinary task</t>
         </is>
       </c>
       <c r="E407" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on, then Break it down.</t>
+          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
         </is>
       </c>
       <c r="F407" s="9" t="inlineStr">
         <is>
-          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
+          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
         </is>
       </c>
       <c r="G407" s="7" t="inlineStr">
@@ -17014,7 +17014,7 @@
     <row r="408">
       <c r="A408" s="6" t="inlineStr">
         <is>
-          <t>OUR-86</t>
+          <t>OUR-85</t>
         </is>
       </c>
       <c r="B408" s="7" t="inlineStr">
@@ -17022,24 +17022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C408" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C408" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D408" s="9" t="inlineStr">
         <is>
-          <t>Select several rows in the room and tick them together</t>
+          <t>Break it down works once taken on, and never touches the shared list</t>
         </is>
       </c>
       <c r="E408" s="9" t="inlineStr">
         <is>
-          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
+          <t>Take a shared row on, then Break it down.</t>
         </is>
       </c>
       <c r="F408" s="9" t="inlineStr">
         <is>
-          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
+          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
         </is>
       </c>
       <c r="G408" s="7" t="inlineStr">
@@ -17054,7 +17054,7 @@
     <row r="409">
       <c r="A409" s="6" t="inlineStr">
         <is>
-          <t>OUR-87</t>
+          <t>OUR-86</t>
         </is>
       </c>
       <c r="B409" s="7" t="inlineStr">
@@ -17069,17 +17069,17 @@
       </c>
       <c r="D409" s="9" t="inlineStr">
         <is>
-          <t>Bulk tick never UN-ticks</t>
+          <t>Select several rows in the room and tick them together</t>
         </is>
       </c>
       <c r="E409" s="9" t="inlineStr">
         <is>
-          <t>Select a mix of done and not-done rows and tap Done.</t>
+          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
         </is>
       </c>
       <c r="F409" s="9" t="inlineStr">
         <is>
-          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
+          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
         </is>
       </c>
       <c r="G409" s="7" t="inlineStr">
@@ -17094,7 +17094,7 @@
     <row r="410">
       <c r="A410" s="6" t="inlineStr">
         <is>
-          <t>OUR-88</t>
+          <t>OUR-87</t>
         </is>
       </c>
       <c r="B410" s="7" t="inlineStr">
@@ -17109,17 +17109,17 @@
       </c>
       <c r="D410" s="9" t="inlineStr">
         <is>
-          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
+          <t>Bulk tick never UN-ticks</t>
         </is>
       </c>
       <c r="E410" s="9" t="inlineStr">
         <is>
-          <t>Select a repeating row along with others. Read the shelf.</t>
+          <t>Select a mix of done and not-done rows and tap Done.</t>
         </is>
       </c>
       <c r="F410" s="9" t="inlineStr">
         <is>
-          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
+          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
         </is>
       </c>
       <c r="G410" s="7" t="inlineStr">
@@ -17134,7 +17134,7 @@
     <row r="411">
       <c r="A411" s="6" t="inlineStr">
         <is>
-          <t>OUR-89</t>
+          <t>OUR-88</t>
         </is>
       </c>
       <c r="B411" s="7" t="inlineStr">
@@ -17142,24 +17142,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C411" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C411" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D411" s="9" t="inlineStr">
         <is>
-          <t>The pill steps aside for the select shelf</t>
+          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
         </is>
       </c>
       <c r="E411" s="9" t="inlineStr">
         <is>
-          <t>Enter select mode in the room with a few words waiting in the capture panel.</t>
+          <t>Select a repeating row along with others. Read the shelf.</t>
         </is>
       </c>
       <c r="F411" s="9" t="inlineStr">
         <is>
-          <t>The pill is gone while selecting (the select shelf docks at the foot), and back when you cancel, still showing its waiting words. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
+          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
         </is>
       </c>
       <c r="G411" s="7" t="inlineStr">
@@ -17174,7 +17174,7 @@
     <row r="412">
       <c r="A412" s="6" t="inlineStr">
         <is>
-          <t>OUR-90</t>
+          <t>OUR-89</t>
         </is>
       </c>
       <c r="B412" s="7" t="inlineStr">
@@ -17182,24 +17182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C412" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C412" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D412" s="9" t="inlineStr">
         <is>
-          <t>No select mode on a closed list</t>
+          <t>The pill steps aside for the select shelf</t>
         </is>
       </c>
       <c r="E412" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list and hold a row.</t>
+          <t>Enter select mode in the room with a few words waiting in the capture panel.</t>
         </is>
       </c>
       <c r="F412" s="9" t="inlineStr">
         <is>
-          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
+          <t>The pill is gone while selecting (the select shelf docks at the foot), and back when you cancel, still showing its waiting words. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
         </is>
       </c>
       <c r="G412" s="7" t="inlineStr">
@@ -17214,7 +17214,7 @@
     <row r="413">
       <c r="A413" s="6" t="inlineStr">
         <is>
-          <t>OUR-91</t>
+          <t>OUR-90</t>
         </is>
       </c>
       <c r="B413" s="7" t="inlineStr">
@@ -17222,24 +17222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C413" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C413" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D413" s="9" t="inlineStr">
         <is>
-          <t>A copy says when its shared row was taken off the list</t>
+          <t>No select mode on a closed list</t>
         </is>
       </c>
       <c r="E413" s="9" t="inlineStr">
         <is>
-          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
+          <t>Open an archived list and hold a row.</t>
         </is>
       </c>
       <c r="F413" s="9" t="inlineStr">
         <is>
-          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
+          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
         </is>
       </c>
       <c r="G413" s="7" t="inlineStr">
@@ -17254,7 +17254,7 @@
     <row r="414">
       <c r="A414" s="6" t="inlineStr">
         <is>
-          <t>OUR-92</t>
+          <t>OUR-91</t>
         </is>
       </c>
       <c r="B414" s="7" t="inlineStr">
@@ -17269,17 +17269,17 @@
       </c>
       <c r="D414" s="9" t="inlineStr">
         <is>
-          <t>That line never says who, and never says why</t>
+          <t>A copy says when its shared row was taken off the list</t>
         </is>
       </c>
       <c r="E414" s="9" t="inlineStr">
         <is>
-          <t>Read the line closely.</t>
+          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
         </is>
       </c>
       <c r="F414" s="9" t="inlineStr">
         <is>
-          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
+          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
         </is>
       </c>
       <c r="G414" s="7" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="415">
       <c r="A415" s="6" t="inlineStr">
         <is>
-          <t>OUR-93</t>
+          <t>OUR-92</t>
         </is>
       </c>
       <c r="B415" s="7" t="inlineStr">
@@ -17302,24 +17302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C415" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C415" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D415" s="9" t="inlineStr">
         <is>
-          <t>No line on a copy you already finished or removed</t>
+          <t>That line never says who, and never says why</t>
         </is>
       </c>
       <c r="E415" s="9" t="inlineStr">
         <is>
-          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
+          <t>Read the line closely.</t>
         </is>
       </c>
       <c r="F415" s="9" t="inlineStr">
         <is>
-          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
+          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
         </is>
       </c>
       <c r="G415" s="7" t="inlineStr">
@@ -17334,7 +17334,7 @@
     <row r="416">
       <c r="A416" s="6" t="inlineStr">
         <is>
-          <t>OUR-94</t>
+          <t>OUR-93</t>
         </is>
       </c>
       <c r="B416" s="7" t="inlineStr">
@@ -17342,24 +17342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C416" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C416" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D416" s="9" t="inlineStr">
         <is>
-          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
+          <t>No line on a copy you already finished or removed</t>
         </is>
       </c>
       <c r="E416" s="9" t="inlineStr">
         <is>
-          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
+          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
         </is>
       </c>
       <c r="F416" s="9" t="inlineStr">
         <is>
-          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
+          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
         </is>
       </c>
       <c r="G416" s="7" t="inlineStr">
@@ -17374,7 +17374,7 @@
     <row r="417">
       <c r="A417" s="6" t="inlineStr">
         <is>
-          <t>OUR-95</t>
+          <t>OUR-94</t>
         </is>
       </c>
       <c r="B417" s="7" t="inlineStr">
@@ -17382,24 +17382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C417" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C417" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D417" s="9" t="inlineStr">
         <is>
-          <t>A row's note is VISIBLE, not only spoken</t>
+          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
         </is>
       </c>
       <c r="E417" s="9" t="inlineStr">
         <is>
-          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
+          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
         </is>
       </c>
       <c r="F417" s="9" t="inlineStr">
         <is>
-          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
+          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
         </is>
       </c>
       <c r="G417" s="7" t="inlineStr">
@@ -17414,7 +17414,7 @@
     <row r="418">
       <c r="A418" s="6" t="inlineStr">
         <is>
-          <t>OUR-96</t>
+          <t>OUR-95</t>
         </is>
       </c>
       <c r="B418" s="7" t="inlineStr">
@@ -17422,24 +17422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C418" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C418" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D418" s="9" t="inlineStr">
         <is>
-          <t>Rows WITHOUT a note are unchanged</t>
+          <t>A row's note is VISIBLE, not only spoken</t>
         </is>
       </c>
       <c r="E418" s="9" t="inlineStr">
         <is>
-          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
+          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
         </is>
       </c>
       <c r="F418" s="9" t="inlineStr">
         <is>
-          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
+          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
         </is>
       </c>
       <c r="G418" s="7" t="inlineStr">
@@ -17454,7 +17454,7 @@
     <row r="419">
       <c r="A419" s="6" t="inlineStr">
         <is>
-          <t>OUR-97</t>
+          <t>OUR-96</t>
         </is>
       </c>
       <c r="B419" s="7" t="inlineStr">
@@ -17462,24 +17462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C419" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C419" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D419" s="9" t="inlineStr">
         <is>
-          <t>A tick after midnight lands on the RIGHT day</t>
+          <t>Rows WITHOUT a note are unchanged</t>
         </is>
       </c>
       <c r="E419" s="9" t="inlineStr">
         <is>
-          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
+          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
         </is>
       </c>
       <c r="F419" s="9" t="inlineStr">
         <is>
-          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
+          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
         </is>
       </c>
       <c r="G419" s="7" t="inlineStr">
@@ -17494,7 +17494,7 @@
     <row r="420">
       <c r="A420" s="6" t="inlineStr">
         <is>
-          <t>OUR-98</t>
+          <t>OUR-97</t>
         </is>
       </c>
       <c r="B420" s="7" t="inlineStr">
@@ -17509,17 +17509,17 @@
       </c>
       <c r="D420" s="9" t="inlineStr">
         <is>
-          <t>A tick made during a background sync is not undone</t>
+          <t>A tick after midnight lands on the RIGHT day</t>
         </is>
       </c>
       <c r="E420" s="9" t="inlineStr">
         <is>
-          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
+          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
         </is>
       </c>
       <c r="F420" s="9" t="inlineStr">
         <is>
-          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
+          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
         </is>
       </c>
       <c r="G420" s="7" t="inlineStr">
@@ -17534,7 +17534,7 @@
     <row r="421">
       <c r="A421" s="6" t="inlineStr">
         <is>
-          <t>OUR-99</t>
+          <t>OUR-98</t>
         </is>
       </c>
       <c r="B421" s="7" t="inlineStr">
@@ -17549,17 +17549,17 @@
       </c>
       <c r="D421" s="9" t="inlineStr">
         <is>
-          <t>A tick survives a device that has never opened the room</t>
+          <t>A tick made during a background sync is not undone</t>
         </is>
       </c>
       <c r="E421" s="9" t="inlineStr">
         <is>
-          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
+          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F421" s="9" t="inlineStr">
         <is>
-          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
+          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
         </is>
       </c>
       <c r="G421" s="7" t="inlineStr">
@@ -17574,7 +17574,7 @@
     <row r="422">
       <c r="A422" s="6" t="inlineStr">
         <is>
-          <t>OUR-100</t>
+          <t>OUR-99</t>
         </is>
       </c>
       <c r="B422" s="7" t="inlineStr">
@@ -17589,17 +17589,17 @@
       </c>
       <c r="D422" s="9" t="inlineStr">
         <is>
-          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
+          <t>A tick survives a device that has never opened the room</t>
         </is>
       </c>
       <c r="E422" s="9" t="inlineStr">
         <is>
-          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
+          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
         </is>
       </c>
       <c r="F422" s="9" t="inlineStr">
         <is>
-          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
+          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
         </is>
       </c>
       <c r="G422" s="7" t="inlineStr">
@@ -17614,7 +17614,7 @@
     <row r="423">
       <c r="A423" s="6" t="inlineStr">
         <is>
-          <t>OUR-101</t>
+          <t>OUR-100</t>
         </is>
       </c>
       <c r="B423" s="7" t="inlineStr">
@@ -17622,24 +17622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C423" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C423" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D423" s="9" t="inlineStr">
         <is>
-          <t>A closed list stops promising it keeps trying</t>
+          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
         </is>
       </c>
       <c r="E423" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list that has unpushed local changes.</t>
+          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
         </is>
       </c>
       <c r="F423" s="9" t="inlineStr">
         <is>
-          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
+          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
         </is>
       </c>
       <c r="G423" s="7" t="inlineStr">
@@ -17654,7 +17654,7 @@
     <row r="424">
       <c r="A424" s="6" t="inlineStr">
         <is>
-          <t>OUR-102</t>
+          <t>OUR-101</t>
         </is>
       </c>
       <c r="B424" s="7" t="inlineStr">
@@ -17669,17 +17669,17 @@
       </c>
       <c r="D424" s="9" t="inlineStr">
         <is>
-          <t>Setting a rhythm clears any date the row was carrying</t>
+          <t>A closed list stops promising it keeps trying</t>
         </is>
       </c>
       <c r="E424" s="9" t="inlineStr">
         <is>
-          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
+          <t>Open an archived list that has unpushed local changes.</t>
         </is>
       </c>
       <c r="F424" s="9" t="inlineStr">
         <is>
-          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
+          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
         </is>
       </c>
       <c r="G424" s="7" t="inlineStr">
@@ -17694,7 +17694,7 @@
     <row r="425">
       <c r="A425" s="6" t="inlineStr">
         <is>
-          <t>OUR-103</t>
+          <t>OUR-102</t>
         </is>
       </c>
       <c r="B425" s="7" t="inlineStr">
@@ -17709,17 +17709,17 @@
       </c>
       <c r="D425" s="9" t="inlineStr">
         <is>
-          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
+          <t>Setting a rhythm clears any date the row was carrying</t>
         </is>
       </c>
       <c r="E425" s="9" t="inlineStr">
         <is>
-          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
+          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
         </is>
       </c>
       <c r="F425" s="9" t="inlineStr">
         <is>
-          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
+          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
         </is>
       </c>
       <c r="G425" s="7" t="inlineStr">
@@ -17734,7 +17734,7 @@
     <row r="426">
       <c r="A426" s="6" t="inlineStr">
         <is>
-          <t>OUR-104</t>
+          <t>OUR-103</t>
         </is>
       </c>
       <c r="B426" s="7" t="inlineStr">
@@ -17742,24 +17742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C426" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C426" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D426" s="9" t="inlineStr">
         <is>
-          <t>No dead reorder rail on shared rows</t>
+          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
         </is>
       </c>
       <c r="E426" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the room and in the From Ours strip.</t>
+          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
         </is>
       </c>
       <c r="F426" s="9" t="inlineStr">
         <is>
-          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
+          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
         </is>
       </c>
       <c r="G426" s="7" t="inlineStr">
@@ -17774,7 +17774,7 @@
     <row r="427">
       <c r="A427" s="6" t="inlineStr">
         <is>
-          <t>OUR-105</t>
+          <t>OUR-104</t>
         </is>
       </c>
       <c r="B427" s="7" t="inlineStr">
@@ -17782,24 +17782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C427" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C427" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D427" s="9" t="inlineStr">
         <is>
-          <t>First run introduces the shared list</t>
+          <t>No dead reorder rail on shared rows</t>
         </is>
       </c>
       <c r="E427" s="9" t="inlineStr">
         <is>
-          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
+          <t>Hold a row in the room and in the From Ours strip.</t>
         </is>
       </c>
       <c r="F427" s="9" t="inlineStr">
         <is>
-          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
+          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
         </is>
       </c>
       <c r="G427" s="7" t="inlineStr">
@@ -17814,7 +17814,7 @@
     <row r="428">
       <c r="A428" s="6" t="inlineStr">
         <is>
-          <t>OUR-106</t>
+          <t>OUR-105</t>
         </is>
       </c>
       <c r="B428" s="7" t="inlineStr">
@@ -17829,17 +17829,17 @@
       </c>
       <c r="D428" s="9" t="inlineStr">
         <is>
-          <t>Anyone can start a shared list, not just an allowlisted address</t>
+          <t>First run introduces the shared list</t>
         </is>
       </c>
       <c r="E428" s="9" t="inlineStr">
         <is>
-          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
+          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
         </is>
       </c>
       <c r="F428" s="9" t="inlineStr">
         <is>
-          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
+          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
         </is>
       </c>
       <c r="G428" s="7" t="inlineStr">
@@ -17854,7 +17854,7 @@
     <row r="429">
       <c r="A429" s="6" t="inlineStr">
         <is>
-          <t>OUR-107</t>
+          <t>OUR-106</t>
         </is>
       </c>
       <c r="B429" s="7" t="inlineStr">
@@ -17869,17 +17869,17 @@
       </c>
       <c r="D429" s="9" t="inlineStr">
         <is>
-          <t>The shared-list onboarding step can actually be REACHED</t>
+          <t>Anyone can start a shared list, not just an allowlisted address</t>
         </is>
       </c>
       <c r="E429" s="9" t="inlineStr">
         <is>
-          <t>Replay the first run and press the primary button through every step without skipping.</t>
+          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
         </is>
       </c>
       <c r="F429" s="9" t="inlineStr">
         <is>
-          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
+          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
         </is>
       </c>
       <c r="G429" s="7" t="inlineStr">
@@ -17894,7 +17894,7 @@
     <row r="430">
       <c r="A430" s="6" t="inlineStr">
         <is>
-          <t>OUR-108</t>
+          <t>OUR-107</t>
         </is>
       </c>
       <c r="B430" s="7" t="inlineStr">
@@ -17902,24 +17902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C430" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C430" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D430" s="9" t="inlineStr">
         <is>
-          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
+          <t>The shared-list onboarding step can actually be REACHED</t>
         </is>
       </c>
       <c r="E430" s="9" t="inlineStr">
         <is>
-          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
+          <t>Replay the first run and press the primary button through every step without skipping.</t>
         </is>
       </c>
       <c r="F430" s="9" t="inlineStr">
         <is>
-          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
+          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
         </is>
       </c>
       <c r="G430" s="7" t="inlineStr">
@@ -17934,7 +17934,7 @@
     <row r="431">
       <c r="A431" s="6" t="inlineStr">
         <is>
-          <t>OUR-109</t>
+          <t>OUR-108</t>
         </is>
       </c>
       <c r="B431" s="7" t="inlineStr">
@@ -17942,24 +17942,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C431" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C431" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D431" s="9" t="inlineStr">
         <is>
-          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
+          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
         </is>
       </c>
       <c r="E431" s="9" t="inlineStr">
         <is>
-          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
+          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
         </is>
       </c>
       <c r="F431" s="9" t="inlineStr">
         <is>
-          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
+          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
         </is>
       </c>
       <c r="G431" s="7" t="inlineStr">
@@ -17974,7 +17974,7 @@
     <row r="432">
       <c r="A432" s="6" t="inlineStr">
         <is>
-          <t>OUR-110</t>
+          <t>OUR-109</t>
         </is>
       </c>
       <c r="B432" s="7" t="inlineStr">
@@ -17989,17 +17989,17 @@
       </c>
       <c r="D432" s="9" t="inlineStr">
         <is>
-          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
+          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
         </is>
       </c>
       <c r="E432" s="9" t="inlineStr">
         <is>
-          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
+          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
         </is>
       </c>
       <c r="F432" s="9" t="inlineStr">
         <is>
-          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
+          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
         </is>
       </c>
       <c r="G432" s="7" t="inlineStr">
@@ -18014,12 +18014,12 @@
     <row r="433">
       <c r="A433" s="6" t="inlineStr">
         <is>
-          <t>UPD-01</t>
+          <t>OUR-110</t>
         </is>
       </c>
       <c r="B433" s="7" t="inlineStr">
         <is>
-          <t>Updates</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C433" s="8" t="inlineStr">
@@ -18029,17 +18029,17 @@
       </c>
       <c r="D433" s="9" t="inlineStr">
         <is>
-          <t>Settings states the version, and up-to-date is a fact</t>
+          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
         </is>
       </c>
       <c r="E433" s="9" t="inlineStr">
         <is>
-          <t>Open Settings and scroll to the foot.</t>
+          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
         </is>
       </c>
       <c r="F433" s="9" t="inlineStr">
         <is>
-          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
+          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
         </is>
       </c>
       <c r="G433" s="7" t="inlineStr">
@@ -18054,7 +18054,7 @@
     <row r="434">
       <c r="A434" s="6" t="inlineStr">
         <is>
-          <t>UPD-02</t>
+          <t>UPD-01</t>
         </is>
       </c>
       <c r="B434" s="7" t="inlineStr">
@@ -18069,22 +18069,22 @@
       </c>
       <c r="D434" s="9" t="inlineStr">
         <is>
-          <t>Web offers a reload, and says drafts are kept</t>
+          <t>Settings states the version, and up-to-date is a fact</t>
         </is>
       </c>
       <c r="E434" s="9" t="inlineStr">
         <is>
-          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
+          <t>Open Settings and scroll to the foot.</t>
         </is>
       </c>
       <c r="F434" s="9" t="inlineStr">
         <is>
-          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
+          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
         </is>
       </c>
       <c r="G434" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H434" s="7" t="inlineStr"/>
@@ -18094,7 +18094,7 @@
     <row r="435">
       <c r="A435" s="6" t="inlineStr">
         <is>
-          <t>UPD-03</t>
+          <t>UPD-02</t>
         </is>
       </c>
       <c r="B435" s="7" t="inlineStr">
@@ -18109,22 +18109,22 @@
       </c>
       <c r="D435" s="9" t="inlineStr">
         <is>
-          <t>Native points at the store, and says lists are untouched</t>
+          <t>Web offers a reload, and says drafts are kept</t>
         </is>
       </c>
       <c r="E435" s="9" t="inlineStr">
         <is>
-          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
+          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
         </is>
       </c>
       <c r="F435" s="9" t="inlineStr">
         <is>
-          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
+          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
         </is>
       </c>
       <c r="G435" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H435" s="7" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
     <row r="436">
       <c r="A436" s="6" t="inlineStr">
         <is>
-          <t>UPD-04</t>
+          <t>UPD-03</t>
         </is>
       </c>
       <c r="B436" s="7" t="inlineStr">
@@ -18142,29 +18142,29 @@
           <t>Updates</t>
         </is>
       </c>
-      <c r="C436" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C436" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D436" s="9" t="inlineStr">
         <is>
-          <t>Unreachable server says NOTHING, never 'up to date'</t>
+          <t>Native points at the store, and says lists are untouched</t>
         </is>
       </c>
       <c r="E436" s="9" t="inlineStr">
         <is>
-          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
+          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
         </is>
       </c>
       <c r="F436" s="9" t="inlineStr">
         <is>
-          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
+          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
         </is>
       </c>
       <c r="G436" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H436" s="7" t="inlineStr"/>
@@ -18174,7 +18174,7 @@
     <row r="437">
       <c r="A437" s="6" t="inlineStr">
         <is>
-          <t>UPD-05</t>
+          <t>UPD-04</t>
         </is>
       </c>
       <c r="B437" s="7" t="inlineStr">
@@ -18189,17 +18189,17 @@
       </c>
       <c r="D437" s="9" t="inlineStr">
         <is>
-          <t>The goodnight mention is rare, and framed for the other person</t>
+          <t>Unreachable server says NOTHING, never 'up to date'</t>
         </is>
       </c>
       <c r="E437" s="9" t="inlineStr">
         <is>
-          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
+          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
         </is>
       </c>
       <c r="F437" s="9" t="inlineStr">
         <is>
-          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
+          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
         </is>
       </c>
       <c r="G437" s="7" t="inlineStr">
@@ -18214,32 +18214,32 @@
     <row r="438">
       <c r="A438" s="6" t="inlineStr">
         <is>
-          <t>OUR-12</t>
+          <t>UPD-05</t>
         </is>
       </c>
       <c r="B438" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C438" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="C438" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D438" s="9" t="inlineStr">
         <is>
-          <t>Unnamed lists read in each person's language</t>
+          <t>The goodnight mention is rare, and framed for the other person</t>
         </is>
       </c>
       <c r="E438" s="9" t="inlineStr">
         <is>
-          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
         </is>
       </c>
       <c r="F438" s="9" t="inlineStr">
         <is>
-          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
         </is>
       </c>
       <c r="G438" s="7" t="inlineStr">
@@ -18251,9 +18251,49 @@
       <c r="I438" s="9" t="inlineStr"/>
       <c r="J438" s="7" t="inlineStr"/>
     </row>
+    <row r="439">
+      <c r="A439" s="6" t="inlineStr">
+        <is>
+          <t>OUR-12</t>
+        </is>
+      </c>
+      <c r="B439" s="7" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="C439" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D439" s="9" t="inlineStr">
+        <is>
+          <t>Unnamed lists read in each person's language</t>
+        </is>
+      </c>
+      <c r="E439" s="9" t="inlineStr">
+        <is>
+          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+        </is>
+      </c>
+      <c r="F439" s="9" t="inlineStr">
+        <is>
+          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+        </is>
+      </c>
+      <c r="G439" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H439" s="7" t="inlineStr"/>
+      <c r="I439" s="9" t="inlineStr"/>
+      <c r="J439" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J438"/>
-  <conditionalFormatting sqref="H2:H438">
+  <autoFilter ref="A1:J439"/>
+  <conditionalFormatting sqref="H2:H439">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -18265,7 +18305,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H438" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
+    <dataValidation sqref="H2:H439" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
       <formula1>"Pass,Fail,Blocked,Not run"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18301,7 +18341,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>438</t>
         </is>
       </c>
     </row>
@@ -18312,7 +18352,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF('Test Suite'!$H$2:$H$438,"Pass")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$439,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -18323,7 +18363,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF('Test Suite'!$H$2:$H$438,"Fail")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$439,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -18334,7 +18374,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Suite'!$H$2:$H$438,"Blocked")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$439,"Blocked")</f>
         <v/>
       </c>
     </row>
@@ -18345,7 +18385,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Suite'!$H$2:$H$438,"Not run")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$439,"Not run")</f>
         <v/>
       </c>
     </row>
@@ -18356,7 +18396,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>437-COUNTA('Test Suite'!$H$2:$H$438)</f>
+        <f>438-COUNTA('Test Suite'!$H$2:$H$439)</f>
         <v/>
       </c>
     </row>
@@ -18367,7 +18407,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF('Test Suite'!$C$2:$C$438,"P1")</f>
+        <f>COUNTIF('Test Suite'!$C$2:$C$439,"P1")</f>
         <v/>
       </c>
     </row>
@@ -18378,7 +18418,7 @@
         </is>
       </c>
       <c r="B10">
-        <f>COUNTIFS('Test Suite'!$C$2:$C$438,"P1",'Test Suite'!$H$2:$H$438,"Pass")</f>
+        <f>COUNTIFS('Test Suite'!$C$2:$C$439,"P1",'Test Suite'!$H$2:$H$439,"Pass")</f>
         <v/>
       </c>
     </row>

--- a/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
+++ b/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
@@ -7251,7 +7251,7 @@
       </c>
       <c r="F163" s="9" t="inlineStr">
         <is>
-          <t>Under the usual warning, one extra line: 'Your Premium is billed by Apple, so deleting your account does not stop it. Cancel it first on your iPhone or iPad: Settings, tap your name, then Subscriptions.' It is plain text, not a link, and Delete stays available (it warns, it never blocks). A Stripe subscriber and a free account never see this line. The same account opened on the web or Android shows the same line.</t>
+          <t>Under the usual warning, one extra line: 'Your Premium is billed by Apple, so deleting your account does not stop it. Cancel it first on your iPhone or iPad: Settings, tap your name, then Subscriptions.' It is plain text, not a link, and Delete stays available (it warns, it never blocks). A Stripe subscriber and a free account never see this line. On the web or Android the same account shows the line only when its Apple subscription is a real App Store purchase: a TestFlight or sandbox purchase correctly has no server-side Apple row (see PREM-36), so there it shows no line.</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">

--- a/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
+++ b/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$442</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$443</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J442"/>
+  <dimension ref="A1:J443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>The feature list and the gate's '&lt;feature&gt; is part of Premium.' line show, with 'The whole calm daily loop stays free, forever'. There is NO price or currency anywhere (no A$, no '/ month', no 'save 17%', no Monthly / Annual toggle), NO Go Premium, Subscribe or Upgrade, NO 'Billed securely via Stripe', and NO link to doubledone.app or Stripe. Signed out, the one button is 'Already have Premium? Sign in', which opens our own sign-in. Signed in and free, the only thing to take is 'Try Premium free for a month' with 'No card, no charge, and it never becomes a subscription on its own.' under it. TalkBack never speaks a dollar amount. This is the screen Google rejected 1.5.1 for (a fixed A$ price shown to a reviewer abroad).</t>
+          <t>The feature list and the gate's '&lt;feature&gt; is part of Premium.' line show, with 'The whole calm daily loop stays free, forever'. There is NO price or currency anywhere (no A$, no '/ month', no 'save 17%', no Monthly / Annual toggle), NO Go Premium, Subscribe or Upgrade, NO 'Billed securely via Stripe', and NO link to doubledone.app or Stripe. There is no 'grows the longer you stay' scrapbook ladder. Signed out, the one button is 'Sign in to start your free month', which opens our own sign-in, and the foot reads 'Already have Premium? Sign in with the same account and it's here too.' Signed in and free, the only thing to take is 'Start a free month of Premium' with 'No card and no charge. It isn't a subscription, so when the month ends there is nothing to cancel.' under it. TalkBack never speaks a dollar amount. This is the screen Google rejected 1.5.1 for (a fixed A$ price shown to a reviewer abroad).</t>
         </is>
       </c>
       <c r="G259" s="7" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>Every paying, comp or trial account shows Premium active, with its extras working. The Stripe subscriber sees one plain line, 'To change or cancel it, use the website where you subscribed, or email support@doubledone.app.', with no button and no link. The Apple subscriber sees the 'Apple handles it' line. The comp sees 'Your Premium is on us'. The free month shows 'Free until &lt;date&gt;, then back to the free monthly scrapbook. No charge, ever.' and no way to buy. The past_due account sees the paused notice with the support email and NO 'Update payment details' link. Nothing opens Stripe.</t>
+          <t>Every paying, comp or trial account shows Premium active, with its extras working. The Stripe subscriber sees one plain line, 'Your subscription isn't billed through Google Play, so it won't show in the Play Store. To cancel it, sign in on the DoubleDone website with the same email, or email support@doubledone.app and we'll cancel it for you.', with no button and no link (and no line at all once it is set to end, where 'Premium until &lt;date&gt;' says it). The Apple subscriber sees the 'Apple handles it' line. The comp sees 'Your Premium is on us'. The free month reads 'Everything is unlocked for your free month: ...' and 'Free until &lt;date&gt;, then the extras switch off on their own. Your tasks and everything else stay as they are. Nothing to cancel, no charge, ever.', with no way to buy and no 'even if you cancel'. The past_due account sees 'Your Premium is paused because a payment on your subscription hasn't gone through yet. Your subscription is still there and nothing is lost. Email support@doubledone.app and we'll help you sort it.', with NO 'Update payment details' link and no free-month offer under it. Nothing opens Stripe.</t>
         </is>
       </c>
       <c r="G260" s="7" t="inlineStr">
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>On the Android build: walk the welcome to its Premium step; open Settings &gt; Terms, and Settings &gt; Privacy; with TalkBack, focus the Settings Premium card as a free account, and the Menu's Premium row as a subscriber; then, signed in as an account whose free month has already ended, tap 'Try Premium free for a month' and come back to Premium once more.</t>
+          <t>On the Android build: walk the welcome to its Premium step; open Settings &gt; Terms, and Settings &gt; Privacy; with TalkBack, focus the Settings Premium card as a free account, and the Menu's Premium row as a subscriber; then, signed in as an account whose free month has already ended, tap 'Start a free month of Premium' and come back to Premium once more.</t>
         </is>
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>The welcome's fine print reads 'It's in Settings whenever you're curious. No ads, ever.' (no A$5). The Terms' 'Premium and billing' says Premium is optional and not sold in this app, with no price, and Refunds names Stripe billing for people who subscribed on the website or in an earlier version of the Android app, with no price and no way to buy. Privacy says Stripe processes payments on our website. The Premium card is read as 'DoubleDone Premium' (never 'see plans'), and the Menu row for a subscriber as 'Active. Every extra is yours.' (never 'Manage your subscription'). That tap says 'You've already had your free month.' (with the usual 'The free monthly scrapbook is always yours.' under it) and no nudge to buy, the link itself goes, and on the next visit it is not offered again.</t>
+          <t>The welcome's fine print reads 'It's in Settings whenever you're curious. No ads, ever.' (no A$5). The Terms' 'Premium and billing' says Premium is optional and not sold in this app, with no price, and says each account can have the free 30 days once, with nothing to cancel after; Refunds opens 'If Stripe bills you for Premium', with no mention of an earlier Android app, no price and no way to buy. Both say 'Last updated 27 September 2026.' Privacy says Stripe processes payments on our website. The Premium card is read as 'DoubleDone Premium' (never 'see plans'), and the Menu row for a subscriber as 'Active. Every extra is yours.' (never 'Manage your subscription'). That tap says 'You've already had your free month.' (with the usual 'The free monthly scrapbook is always yours.' under it) and no nudge to buy, the link itself goes, and on the next visit it is not offered again.</t>
         </is>
       </c>
       <c r="G261" s="7" t="inlineStr">
@@ -11218,7 +11218,7 @@
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>PREM-29</t>
+          <t>PREM-46</t>
         </is>
       </c>
       <c r="B263" s="7" t="inlineStr">
@@ -11226,29 +11226,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C263" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C263" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
-          <t>The Android AAB does NOT contain Google Play Billing</t>
+          <t>Nobody is told 'even if you cancel' when there is nothing to cancel</t>
         </is>
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>Build the Android AAB, unzip it, and grep for com.android.billingclient. Also confirm the app still builds and installs, and that Premium is NOT sold on Android (PREM-42).</t>
+          <t>Open Premium as a comp account, as an account mid free-month, as a subscriber already set to end (cancelled, not yet expired), and as an active renewing subscriber. On the web and on a phone.</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>react-native-purchases (and Play Billing) is absent from the AAB: the expo.autolinking.android.exclude in client/package.json drops it. Android sells nothing (Path C, 2026-09-27): no price, no Go Premium, no Stripe. This is the regression guard on adding the native module.</t>
+          <t>Only the active, renewing subscriber reads 'The free monthly scrapbook is always yours, even if you cancel.' The comp, the free month and the already-cancelled subscriber read 'The free monthly scrapbook is always yours.' instead, because they have nothing to cancel.</t>
         </is>
       </c>
       <c r="G263" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H263" s="7" t="inlineStr"/>
@@ -11258,7 +11258,7 @@
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>PREM-30</t>
+          <t>PREM-29</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -11273,22 +11273,22 @@
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>The web build is unchanged and still sells via Stripe</t>
+          <t>The Android AAB does NOT contain Google Play Billing</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>Build the production web export (expo export --platform web). Open /premium on web.</t>
+          <t>Build the Android AAB, unzip it, and grep for com.android.billingclient. Also confirm the app still builds and installs, and that Premium is NOT sold on Android (PREM-42).</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>The export succeeds (the native purchases module never enters the web bundle, proving the purchases.ts / purchases.ios.ts split). The web paywall shows the catalog price, the 'Billed securely via Stripe' line, NO Restore control, and the Stripe checkout path is unchanged. The regression guard on the paywall rewrite.</t>
+          <t>react-native-purchases (and Play Billing) is absent from the AAB: the expo.autolinking.android.exclude in client/package.json drops it. Android sells nothing (Path C, 2026-09-27): no price, no Go Premium, no Stripe. This is the regression guard on adding the native module.</t>
         </is>
       </c>
       <c r="G264" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H264" s="7" t="inlineStr"/>
@@ -11298,7 +11298,7 @@
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>PREM-32</t>
+          <t>PREM-30</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
@@ -11313,22 +11313,22 @@
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>PRODUCTION paywall price matches App Store Connect</t>
+          <t>The web build is unchanged and still sells via Stripe</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>After the app is RELEASED, install it from the App Store (not TestFlight) on an Australian account and open Premium. Read the monthly and annual prices.</t>
+          <t>Build the production web export (expo export --platform web). Open /premium on web.</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>The paywall reads A$5.00 / month and A$50.00 / year, matching the App Store Connect price schedule for Australia, and matching what Apple's purchase sheet charges. CRITICAL: TestFlight and sandbox CANNOT verify this. They are known to answer product queries for the US storefront regardless of the account's real region, so a TestFlight paywall showing US dollars is expected and is NOT the bug. Only a production App Store install proves it. If production still disagrees with the sheet, that is a misleading pre-purchase price (an Australian Consumer Law problem, not just a display bug): pull the release via Pricing and Availability, Remove from sale. Prerequisite: app released. Gate the RELEASE on this, never the submission.</t>
+          <t>The export succeeds (the native purchases module never enters the web bundle, proving the purchases.ts / purchases.ios.ts split). The web paywall shows the catalog price, the 'Billed securely via Stripe' line, NO Restore control, and the Stripe checkout path is unchanged. The regression guard on the paywall rewrite.</t>
         </is>
       </c>
       <c r="G265" s="7" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H265" s="7" t="inlineStr"/>
@@ -11338,7 +11338,7 @@
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>PREM-33</t>
+          <t>PREM-32</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -11353,22 +11353,22 @@
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>A dunning subscriber is never sold a second subscription</t>
+          <t>PRODUCTION paywall price matches App Store Connect</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>Put a test Stripe subscription into past_due (in Stripe test mode: attach a failing card, or use the test clock to fail a renewal). Open /premium signed in as that user. Read the panel, then try to buy.</t>
+          <t>After the app is RELEASED, install it from the App Store (not TestFlight) on an Australian account and open Premium. Read the monthly and annual prices.</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>Access has lapsed so the UPSELL panel shows, but with a calm notice at the top: 'Your Premium is paused while a payment retries. Updating your card brings it back. There is no need to buy again.' with an 'Update payment details' link that opens the Stripe portal (the customer id exists in this state). If the user taps Go Premium anyway, the server refuses with 409 billing_issue and the app explains the card is the fix, NEVER 'You're already on Premium' (false: they are not) and NEVER a second Checkout. REGRESSION GUARDS on the same server change (locked by stripe.test.ts): a LAPSED subscriber (status canceled, customer id kept) can still re-subscribe via a fresh Checkout, an abandoned checkout (incomplete) can still buy, and a trial still converts. The old guard keyed on premium &amp;&amp; customerId, so a past_due user could mint a SECOND subscription whose webhook overwrote stripe_customer_id and orphaned the first: paying twice with one visible.</t>
+          <t>The paywall reads A$5.00 / month and A$50.00 / year, matching the App Store Connect price schedule for Australia, and matching what Apple's purchase sheet charges. CRITICAL: TestFlight and sandbox CANNOT verify this. They are known to answer product queries for the US storefront regardless of the account's real region, so a TestFlight paywall showing US dollars is expected and is NOT the bug. Only a production App Store install proves it. If production still disagrees with the sheet, that is a misleading pre-purchase price (an Australian Consumer Law problem, not just a display bug): pull the release via Pricing and Availability, Remove from sale. Prerequisite: app released. Gate the RELEASE on this, never the submission.</t>
         </is>
       </c>
       <c r="G266" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="H266" s="7" t="inlineStr"/>
@@ -11378,7 +11378,7 @@
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>PREM-34</t>
+          <t>PREM-33</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -11393,22 +11393,22 @@
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>An ANNUAL subscriber is warned a week before the charge, once</t>
+          <t>A dunning subscriber is never sold a second subscription</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>Needs a Stripe test clock, because the whole feature is about a year passing. Put a test user on the ANNUAL price. Open the app once while the renewal is far away (this is what teaches the device the period is a year: it is only ever judged annual when first seen more than 40 days out). Advance the test clock to ~10 days before renewal and open Today again. Then open it several more times. Separately, repeat the whole thing with a MONTHLY subscriber, and again with an annual one that has been CANCELLED (cancel_at_period_end).</t>
+          <t>Put a test Stripe subscription into past_due (in Stripe test mode: attach a failing card, or use the test clock to fail a renewal). Open /premium signed in as that user. Read the panel, then try to buy.</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>The annual subscriber gets ONE new task, dated SEVEN days before the charge (not on the day of it, which would be a receipt rather than a warning), reading 'Your DoubleDone year renews on &lt;date&gt;. Nothing to do.' Re-opening the app does NOT add a second: it is remembered against that period, and the next one is only noticed after the period rolls. The MONTHLY subscriber never gets one, however many times the app is opened (twelve notices a year is nagging). The CANCELLED subscriber never gets one either, because nothing is renewing and saying otherwise to someone who has decided to leave is both false and unkind. A device that first opens the app INSIDE the last 40 days gets no notice that year, by design, and self-corrects the next. This is the only place the app writes a task nobody typed, so a false positive here is a spine violation, not a cosmetic bug.</t>
+          <t>Access has lapsed so the UPSELL panel shows, but with a calm notice at the top: 'Your Premium is paused while a payment retries. Updating your card brings it back. There is no need to buy again.' with an 'Update payment details' link that opens the Stripe portal (the customer id exists in this state). If the user taps Go Premium anyway, the server refuses with 409 billing_issue and the app explains the card is the fix, NEVER 'You're already on Premium' (false: they are not) and NEVER a second Checkout. REGRESSION GUARDS on the same server change (locked by stripe.test.ts): a LAPSED subscriber (status canceled, customer id kept) can still re-subscribe via a fresh Checkout, an abandoned checkout (incomplete) can still buy, and a trial still converts. The old guard keyed on premium &amp;&amp; customerId, so a past_due user could mint a SECOND subscription whose webhook overwrote stripe_customer_id and orphaned the first: paying twice with one visible.</t>
         </is>
       </c>
       <c r="G267" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H267" s="7" t="inlineStr"/>
@@ -11418,7 +11418,7 @@
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>PREM-31</t>
+          <t>PREM-34</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
@@ -11426,25 +11426,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C268" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C268" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>Sandbox tester + Restore Behavior confirmed in the RevenueCat dashboard</t>
-        </is>
-      </c>
-      <c r="E268" s="9" t="inlineStr"/>
+          <t>An ANNUAL subscriber is warned a week before the charge, once</t>
+        </is>
+      </c>
+      <c r="E268" s="9" t="inlineStr">
+        <is>
+          <t>Needs a Stripe test clock, because the whole feature is about a year passing. Put a test user on the ANNUAL price. Open the app once while the renewal is far away (this is what teaches the device the period is a year: it is only ever judged annual when first seen more than 40 days out). Advance the test clock to ~10 days before renewal and open Today again. Then open it several more times. Separately, repeat the whole thing with a MONTHLY subscriber, and again with an annual one that has been CANCELLED (cancel_at_period_end).</t>
+        </is>
+      </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>In the RevenueCat dashboard: Restore Behavior is set to keep-with-original (so TRANSFER never fires), the App Store Connect API key + In-App-Purchase key are uploaded, both products read 'Ready to Submit', and the IAPs are attached to the SAME App Store submission as the first binary (a first-time subscription submitted separately is not reviewed). A Sandbox Apple ID exists for testing.</t>
+          <t>The annual subscriber gets ONE new task, dated SEVEN days before the charge (not on the day of it, which would be a receipt rather than a warning), reading 'Your DoubleDone year renews on &lt;date&gt;. Nothing to do.' Re-opening the app does NOT add a second: it is remembered against that period, and the next one is only noticed after the period rolls. The MONTHLY subscriber never gets one, however many times the app is opened (twelve notices a year is nagging). The CANCELLED subscriber never gets one either, because nothing is renewing and saying otherwise to someone who has decided to leave is both false and unkind. A device that first opens the app INSIDE the last 40 days gets no notice that year, by design, and self-corrects the next. This is the only place the app writes a task nobody typed, so a false positive here is a spine violation, not a cosmetic bug.</t>
         </is>
       </c>
       <c r="G268" s="7" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H268" s="7" t="inlineStr"/>
@@ -11454,37 +11458,33 @@
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>QUI-01</t>
+          <t>PREM-31</t>
         </is>
       </c>
       <c r="B269" s="7" t="inlineStr">
         <is>
-          <t>Interface</t>
-        </is>
-      </c>
-      <c r="C269" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="C269" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>The Quiet interface is free, both ways</t>
-        </is>
-      </c>
-      <c r="E269" s="9" t="inlineStr">
-        <is>
-          <t>As a FREE or signed-out user, open Settings -&gt; Look -&gt; 'Interface' and tap 'Quiet', then reload. Then tap 'Standard'. Then, as an account whose Premium or trial ended while it was on Quiet, open Settings -&gt; Look -&gt; 'Interface' and tap 'Standard'.</t>
-        </is>
-      </c>
+          <t>Sandbox tester + Restore Behavior confirmed in the RevenueCat dashboard</t>
+        </is>
+      </c>
+      <c r="E269" s="9" t="inlineStr"/>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>The Interface row carries no '✦ Premium' tag and shows one hint ('Quiet strips the interface back to calm text. Standard keeps the cards and buttons.'). The change applies live in both directions, the paywall never opens, and 'appearance.locked' is never logged. In Quiet the whole Today surface goes borderless. Card outlines drop, and every action that looked like a button or a link renders as plain text with no outline or fill: the header Menu pill (which keeps just the word 'Menu', no dots), 'Focus on one thing', 'Lighten today', 'Close the day', and 'Plan my day' (which in Standard is the filled premium gradient) all become plain text (accent for the AI / premium ones, soft ink for the calm structural ones). The energy / weight-of-today gauge is KEPT, not removed: it shrinks to a 3px hairline bar so the day's load still reads at a glance. The choice survives reload with 'Quiet' ringed. 'Standard' is the default and looks identical to the app today (gradient button, 6px gauge, outlined actions all return). The account whose Premium or trial ended can leave Quiet with one tap: before 2026-09-27 every tap, Standard included, bounced to the paywall, so it was stuck in Quiet with no way out (and none at all on Android, whose Premium page sells nothing).</t>
+          <t>In the RevenueCat dashboard: Restore Behavior is set to keep-with-original (so TRANSFER never fires), the App Store Connect API key + In-App-Purchase key are uploaded, both products read 'Ready to Submit', and the IAPs are attached to the SAME App Store submission as the first binary (a first-time subscription submitted separately is not reviewed). A Sandbox Apple ID exists for testing.</t>
         </is>
       </c>
       <c r="G269" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="H269" s="7" t="inlineStr"/>
@@ -11494,7 +11494,7 @@
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>QUI-02</t>
+          <t>QUI-01</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
@@ -11502,24 +11502,24 @@
           <t>Interface</t>
         </is>
       </c>
-      <c r="C270" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C270" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>Switching Standard &lt;-&gt; Quiet never moves the layout</t>
+          <t>The Quiet interface is free, both ways</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>With a handful of tasks on Today (some open, one or two done), toggle Interface between Standard and Quiet a few times, watching the task rows and the capture line. On ANDROID, specifically do the full round trip (Standard -&gt; Quiet -&gt; Standard) from the Settings screen and then return to Today.</t>
+          <t>As a FREE or signed-out user, open Settings -&gt; Look -&gt; 'Interface' and tap 'Quiet', then reload. Then tap 'Standard'. Then, as an account whose Premium or trial ended while it was on Quiet, open Settings -&gt; Look -&gt; 'Interface' and tap 'Standard'.</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>Content stays put: no visible jump in row height or position as you toggle. Quiet removes chrome (row borders, fills, the per-task progress bar, the capture underline weight) but preserves spacing, so nothing shifts under the finger. On Android the round trip must leave rows pixel-perfect, in particular the row BOTTOMS never look clipped/'eaten' (regression: toggling while Today sat detached behind Settings in the native stack left rows at Quiet's slightly shorter measured height under Standard's styles; Today now remounts on an appearance change so native lays it out fresh).</t>
+          <t>The Interface row carries no '✦ Premium' tag and shows one hint ('Quiet strips the interface back to calm text. Standard keeps the cards and buttons.'). The change applies live in both directions, the paywall never opens, and 'appearance.locked' is never logged. In Quiet the whole Today surface goes borderless. Card outlines drop, and every action that looked like a button or a link renders as plain text with no outline or fill: the header Menu pill (which keeps just the word 'Menu', no dots), 'Focus on one thing', 'Lighten today', 'Close the day', and 'Plan my day' (which in Standard is the filled premium gradient) all become plain text (accent for the AI / premium ones, soft ink for the calm structural ones). The energy / weight-of-today gauge is KEPT, not removed: it shrinks to a 3px hairline bar so the day's load still reads at a glance. The choice survives reload with 'Quiet' ringed. 'Standard' is the default and looks identical to the app today (gradient button, 6px gauge, outlined actions all return). The account whose Premium or trial ended can leave Quiet with one tap: before 2026-09-27 every tap, Standard included, bounced to the paywall, so it was stuck in Quiet with no way out (and none at all on Android, whose Premium page sells nothing).</t>
         </is>
       </c>
       <c r="G270" s="7" t="inlineStr">
@@ -11534,7 +11534,7 @@
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>QUI-06</t>
+          <t>QUI-02</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Quiet draws Energy as three words</t>
+          <t>Switching Standard &lt;-&gt; Quiet never moves the layout</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>Settings -&gt; Look -&gt; Interface -&gt; Quiet. Open Today and change Energy between Low, Normal and High.</t>
+          <t>With a handful of tasks on Today (some open, one or two done), toggle Interface between Standard and Quiet a few times, watching the task rows and the capture line. On ANDROID, specifically do the full round trip (Standard -&gt; Quiet -&gt; Standard) from the Settings screen and then return to Today.</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>No pills: Low, Normal and High are plain words, the chosen one in bold ink, the others in soft ink. Each still has a full 44pt tap area and nothing shifts when the choice changes. Standard keeps the soft pill.</t>
+          <t>Content stays put: no visible jump in row height or position as you toggle. Quiet removes chrome (row borders, fills, the per-task progress bar, the capture underline weight) but preserves spacing, so nothing shifts under the finger. On Android the round trip must leave rows pixel-perfect, in particular the row BOTTOMS never look clipped/'eaten' (regression: toggling while Today sat detached behind Settings in the native stack left rows at Quiet's slightly shorter measured height under Standard's styles; Today now remounts on an appearance change so native lays it out fresh).</t>
         </is>
       </c>
       <c r="G271" s="7" t="inlineStr">
@@ -11574,7 +11574,7 @@
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>QUI-03</t>
+          <t>QUI-06</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -11589,17 +11589,17 @@
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>The held card is identical in Quiet and Standard (only the tint differs)</t>
+          <t>Quiet draws Energy as three words</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>Hold the SAME one-off task on Today in Quiet, then switch appearance and hold it again in Standard. Compare them side by side. Then in Quiet also hold a 'Later' task and (if you have one) a recurring task.</t>
+          <t>Settings -&gt; Look -&gt; Interface -&gt; Quiet. Open Today and change Energy between Low, Normal and High.</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>BOTH appearances now give the same in-place card with the same actions in the same order (see TOD-07): there is no longer a Quiet model and a Standard model. Only the treatment differs: Quiet gets a soft wash with a rounded bleed, Standard the accent tint. Mark-as-a-lot and Pin act-and-dismiss (the row updates, the card closes). Pin shows only on Today one-off rows (not Later, not recurring), matching PIN-05; a free user on Quiet who taps Pin is routed to the paywall, never wrongly pinned. 'Select more' closes the card and drops into multi-select with THIS task pre-selected ('1 selected'); Combine appears once a second task is selected. The one-time 'hold a task for more' coachmark in Quiet is a faint line with a small accent dot, not a filled pill.</t>
+          <t>No pills: Low, Normal and High are plain words, the chosen one in bold ink, the others in soft ink. Each still has a full 44pt tap area and nothing shifts when the choice changes. Standard keeps the soft pill.</t>
         </is>
       </c>
       <c r="G272" s="7" t="inlineStr">
@@ -11614,7 +11614,7 @@
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>QUI-04</t>
+          <t>QUI-03</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
@@ -11629,17 +11629,17 @@
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>Quiet close-the-day reads as page text and stays reachable when full</t>
+          <t>The held card is identical in Quiet and Standard (only the tint differs)</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>In Quiet, finish several tasks, then also test a very full day (roughly 16+ finished), and tap 'Close the day'.</t>
+          <t>Hold the SAME one-off task on Today in Quiet, then switch appearance and hold it again in Standard. Compare them side by side. Then in Quiet also hold a 'Later' task and (if you have one) a recurring task.</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>The wrap shows on the plain page colour with no dim scrim and no card outline, and 'Goodnight' is a plain accent text link, not a filled button. On a very full day the finished list still scrolls inside a bounded area and 'Goodnight' stays on screen and reachable, so the TOD-04d regression holds in Quiet too. Reopen / rested behaviour is unchanged.</t>
+          <t>BOTH appearances now give the same in-place card with the same actions in the same order (see TOD-07): there is no longer a Quiet model and a Standard model. Only the treatment differs: Quiet gets a soft wash with a rounded bleed, Standard the accent tint. Mark-as-a-lot and Pin act-and-dismiss (the row updates, the card closes). Pin shows only on Today one-off rows (not Later, not recurring), matching PIN-05; a free user on Quiet who taps Pin is routed to the paywall, never wrongly pinned. 'Select more' closes the card and drops into multi-select with THIS task pre-selected ('1 selected'); Combine appears once a second task is selected. The one-time 'hold a task for more' coachmark in Quiet is a faint line with a small accent dot, not a filled pill.</t>
         </is>
       </c>
       <c r="G273" s="7" t="inlineStr">
@@ -11654,7 +11654,7 @@
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>QUI-05</t>
+          <t>QUI-04</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -11662,24 +11662,24 @@
           <t>Interface</t>
         </is>
       </c>
-      <c r="C274" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C274" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>Quiet honours reduce-motion and every colour theme</t>
+          <t>Quiet close-the-day reads as page text and stays reachable when full</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>In Quiet, set Settings -&gt; Motion -&gt; Reduce (or the OS reduce-motion), then complete a task, open the held-state, and close the day. Separately, view Quiet across a couple of colour themes (e.g. Dusk and Sage) in BOTH light and dark.</t>
+          <t>In Quiet, finish several tasks, then also test a very full day (roughly 16+ finished), and tap 'Close the day'.</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>Nothing animates beyond the app's reduce-motion baseline: the held-state and the wrap appear without motion. Quiet derives its hairlines and washes from the ACTIVE palette, so it looks right on every colour theme in light and dark (not only Dusk), with no washed-out or invisible text.</t>
+          <t>The wrap shows on the plain page colour with no dim scrim and no card outline, and 'Goodnight' is a plain accent text link, not a filled button. On a very full day the finished list still scrolls inside a bounded area and 'Goodnight' stays on screen and reachable, so the TOD-04d regression holds in Quiet too. Reopen / rested behaviour is unchanged.</t>
         </is>
       </c>
       <c r="G274" s="7" t="inlineStr">
@@ -11694,7 +11694,7 @@
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>QUI-07</t>
+          <t>QUI-05</t>
         </is>
       </c>
       <c r="B275" s="7" t="inlineStr">
@@ -11702,24 +11702,24 @@
           <t>Interface</t>
         </is>
       </c>
-      <c r="C275" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C275" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>A free account turns Quiet on in Settings, and nothing mentions Premium</t>
+          <t>Quiet honours reduce-motion and every colour theme</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>Signed in as a FREE account (no trial, no dev override), open Settings -&gt; Look -&gt; 'Interface'. Read the row, then tap 'Quiet'. Open Premium from the Settings card and read the feature list. Replay the welcome from Settings to its Premium screen, once with AI on and once with AI off. Then, still in Quiet, look at every Premium mark that remains: Plan my day in Right now and in the tools panel, the dimmed Pin in the More fold of a held task, the Colour theme row and the Premium card in Settings, and the energy allowance line (use 'What fits right now?' until it reads '10 of your 15 free picks left this month.').</t>
+          <t>In Quiet, set Settings -&gt; Motion -&gt; Reduce (or the OS reduce-motion), then complete a task, open the held-state, and close the day. Separately, view Quiet across a couple of colour themes (e.g. Dusk and Sage) in BOTH light and dark.</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>The Interface row has no '✦ Premium' tag and its hint never says Premium. Tapping 'Quiet' applies at once, with no paywall and nothing in the row naming Premium. The Premium page does not list Quiet, and the welcome's Premium screen does not list 'Quiet interface' (with AI off it shows just Your colour and Pin). In Quiet every remaining Premium mark still reads: Plan my day keeps its honey ✦ in Right now and in the tools panel, Pin stays dimmed with its ✦ in the More fold, the Colour theme row keeps its soft-ink '✦ Premium', the Premium card keeps its gradient with a clear white label, and the energy allowance line is legible. Until 2026-09-27 only subscribers ever saw Quiet, so these had never been looked at by a free user.</t>
+          <t>Nothing animates beyond the app's reduce-motion baseline: the held-state and the wrap appear without motion. Quiet derives its hairlines and washes from the ACTIVE palette, so it looks right on every colour theme in light and dark (not only Dusk), with no washed-out or invisible text.</t>
         </is>
       </c>
       <c r="G275" s="7" t="inlineStr">
@@ -11734,12 +11734,12 @@
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>PIN-01</t>
+          <t>QUI-07</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
         <is>
-          <t>Pin</t>
+          <t>Interface</t>
         </is>
       </c>
       <c r="C276" s="8" t="inlineStr">
@@ -11749,17 +11749,17 @@
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>Premium: pin a task as the day's one thing</t>
+          <t>A free account turns Quiet on in Settings, and nothing mentions Premium</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>As premium (or with the dev Premium override on), tap-and-hold a one-off task to select it, then tap 'Pin' in the held row's actions.</t>
+          <t>Signed in as a FREE account (no trial, no dev override), open Settings -&gt; Look -&gt; 'Interface'. Read the row, then tap 'Quiet'. Open Premium from the Settings card and read the feature list. Replay the welcome from Settings to its Premium screen, once with AI on and once with AI off. Then, still in Quiet, look at every Premium mark that remains: Plan my day in Right now and in the tools panel, the dimmed Pin in the More fold of a held task, the Colour theme row and the Premium card in Settings, and the energy allowance line (use 'What fits right now?' until it reads '10 of your 15 free picks left this month.').</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>The task gets a calm mauve PIN MARK (a drawn pushpin; the star it replaced read as favourite, not pin, per Melroy 2026-08-30, and a drawn SVG cannot hit the iOS missing-glyph failure the round-one flag did) and the thick accent border, and floats to the top of Today. 'Focus on one thing' then opens straight to it.</t>
+          <t>The Interface row has no '✦ Premium' tag and its hint never says Premium. Tapping 'Quiet' applies at once, with no paywall and nothing in the row naming Premium. The Premium page does not list Quiet, and the welcome's Premium screen does not list 'Quiet interface' (with AI off it shows just Your colour and Pin). In Quiet every remaining Premium mark still reads: Plan my day keeps its honey ✦ in Right now and in the tools panel, Pin stays dimmed with its ✦ in the More fold, the Colour theme row keeps its soft-ink '✦ Premium', the Premium card keeps its gradient with a clear white label, and the energy allowance line is legible. Until 2026-09-27 only subscribers ever saw Quiet, so these had never been looked at by a free user.</t>
         </is>
       </c>
       <c r="G276" s="7" t="inlineStr">
@@ -11774,7 +11774,7 @@
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>PIN-02</t>
+          <t>PIN-01</t>
         </is>
       </c>
       <c r="B277" s="7" t="inlineStr">
@@ -11789,17 +11789,17 @@
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Free: Pin routes to the upsell, never pins</t>
+          <t>Premium: pin a task as the day's one thing</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>As a free user, select a single one-off task and tap the dimmed 'Pin' action.</t>
+          <t>As premium (or with the dev Premium override on), tap-and-hold a one-off task to select it, then tap 'Pin' in the held row's actions.</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>No task is pinned, and the Premium screen opens calmly (never a shaming wall). A 'premium.gate_hit' with reason 'pin' is logged.</t>
+          <t>The task gets a calm mauve PIN MARK (a drawn pushpin; the star it replaced read as favourite, not pin, per Melroy 2026-08-30, and a drawn SVG cannot hit the iOS missing-glyph failure the round-one flag did) and the thick accent border, and floats to the top of Today. 'Focus on one thing' then opens straight to it.</t>
         </is>
       </c>
       <c r="G277" s="7" t="inlineStr">
@@ -11814,7 +11814,7 @@
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>PIN-03</t>
+          <t>PIN-02</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -11822,24 +11822,24 @@
           <t>Pin</t>
         </is>
       </c>
-      <c r="C278" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C278" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>Only one task is pinned at a time</t>
+          <t>Free: Pin routes to the upsell, never pins</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>As premium, pin task A, then hold task B and pin it.</t>
+          <t>As a free user, select a single one-off task and tap the dimmed 'Pin' action.</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>Task B is now pinned (pin-marked, floated to the top), and task A is no longer pinned. At most one pin ever exists.</t>
+          <t>No task is pinned, and the Premium screen opens calmly (never a shaming wall). A 'premium.gate_hit' with reason 'pin' is logged.</t>
         </is>
       </c>
       <c r="G278" s="7" t="inlineStr">
@@ -11854,7 +11854,7 @@
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>PIN-04</t>
+          <t>PIN-03</t>
         </is>
       </c>
       <c r="B279" s="7" t="inlineStr">
@@ -11869,17 +11869,17 @@
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>A pin syncs across devices</t>
+          <t>Only one task is pinned at a time</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>As premium and signed in, pin a task, then sign out and back in (or open a second device).</t>
+          <t>As premium, pin task A, then hold task B and pin it.</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>The task is still pinned after the sync round-trip (the pin mark and float persist). Needs the pinned_at column applied in Supabase.</t>
+          <t>Task B is now pinned (pin-marked, floated to the top), and task A is no longer pinned. At most one pin ever exists.</t>
         </is>
       </c>
       <c r="G279" s="7" t="inlineStr">
@@ -11894,7 +11894,7 @@
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>PIN-05</t>
+          <t>PIN-04</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -11902,24 +11902,24 @@
           <t>Pin</t>
         </is>
       </c>
-      <c r="C280" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C280" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>Pin is offered only on one-off Today rows</t>
+          <t>A pin syncs across devices</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>Hold a recurring task, then hold a task in the 'Later' list.</t>
+          <t>As premium and signed in, pin a task, then sign out and back in (or open a second device).</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>No 'Pin' action appears on a recurring task's held card, and a Later task's card carries no Pin either (pinning is Today-only and one-offs only).</t>
+          <t>The task is still pinned after the sync round-trip (the pin mark and float persist). Needs the pinned_at column applied in Supabase.</t>
         </is>
       </c>
       <c r="G280" s="7" t="inlineStr">
@@ -11934,32 +11934,32 @@
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>NRG-01</t>
+          <t>PIN-05</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C281" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Pin</t>
+        </is>
+      </c>
+      <c r="C281" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>What fits right now: one question, one pick, propose-only</t>
+          <t>Pin is offered only on one-off Today rows</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>With AI on and 2+ open one-off tasks, tap 'Focus on one thing'; in the 'Which one?' picker, 'What fits right now?' sits above the task choices in a soft hairline pill (its border makes it read as tappable; it lives INSIDE Focus, not as a standalone Today button). Tap it, pick an energy level (Running low / Somewhere in between / Feeling good). Then tap 'Start with this'; separately try 'Not now'.</t>
+          <t>Hold a recurring task, then hold a task in the 'Later' list.</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>A calm one-question card with the privacy line ('Your open tasks go to Claude to pick one. Nothing is added or changed.'). Choosing a level shows ONE task from today's list with a short warm line on why it fits (never shaming, never about what's undone). 'Start with this' opens Focus mode on exactly that task; 'Not now' just closes, nothing changed. A failed call shows a calm 'Couldn't find a pick just now.' line and does NOT spend a free pick. The entry hides when AI is off or fewer than 2 tasks are open. Needs the Worker deployed with /energy.</t>
+          <t>No 'Pin' action appears on a recurring task's held card, and a Later task's card carries no Pin either (pinning is Today-only and one-offs only).</t>
         </is>
       </c>
       <c r="G281" s="7" t="inlineStr">
@@ -11974,7 +11974,7 @@
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>NRG-02</t>
+          <t>NRG-01</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
@@ -11989,17 +11989,17 @@
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>The freemium meter: 15 a month, reminders at 10 and 5, then the paywall</t>
+          <t>What fits right now: one question, one pick, propose-only</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>As a FREE user, use energy matching repeatedly in one calendar month (seed doubledone.energyUses.v1 to fast-forward). Watch the 10-left and 5-left moments, then the 16th tap. Then as premium, use it well past 15.</t>
+          <t>With AI on and 2+ open one-off tasks, tap 'Focus on one thing'; in the 'Which one?' picker, 'What fits right now?' sits above the task choices in a soft hairline pill (its border makes it read as tappable; it lives INSIDE Focus, not as a standalone Today button). Tap it, pick an energy level (Running low / Somewhere in between / Feeling good). Then tap 'Start with this'; separately try 'Not now'.</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>Each successful pick spends one of 15 free picks a calendar month (counted locally, like the scrapbook gate). Exactly at 10 left and at 5 left, the result shows one calm line: '10 of your 15 free picks left this month.' (then 5). Past 15, tapping the entry routes to the paywall (which lists 'Energy matching without limits'), never a shaming wall, and no AI call is made ('premium.gate_hit' reason 'energy' logs). The counter resets on the 1st of the month with no carry-over. Premium is unlimited and never sees a counter line.</t>
+          <t>A calm one-question card with the privacy line ('Your open tasks go to Claude to pick one. Nothing is added or changed.'). Choosing a level shows ONE task from today's list with a short warm line on why it fits (never shaming, never about what's undone). 'Start with this' opens Focus mode on exactly that task; 'Not now' just closes, nothing changed. A failed call shows a calm 'Couldn't find a pick just now.' line and does NOT spend a free pick. The entry hides when AI is off or fewer than 2 tasks are open. Needs the Worker deployed with /energy.</t>
         </is>
       </c>
       <c r="G282" s="7" t="inlineStr">
@@ -12014,12 +12014,12 @@
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>OCR-01</t>
+          <t>NRG-02</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
         <is>
-          <t>Scan</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C283" s="8" t="inlineStr">
@@ -12029,17 +12029,17 @@
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>Premium: the Scan button opens the camera</t>
+          <t>The freemium meter: 15 a month, reminders at 10 and 5, then the paywall</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>As premium, tap the + pill and then Scan (camera) beside Speak in the panel.</t>
+          <t>As a FREE user, use energy matching repeatedly in one calendar month (seed doubledone.energyUses.v1 to fast-forward). Watch the 10-left and 5-left moments, then the 16th tap. Then as premium, use it well past 15.</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>The camera screen opens: a live viewfinder with a shutter and a Photos shortcut on a device, or a 'Choose a photo' prompt on web. No paywall.</t>
+          <t>Each successful pick spends one of 15 free picks a calendar month (counted locally, like the scrapbook gate). Exactly at 10 left and at 5 left, the result shows one calm line: '10 of your 15 free picks left this month.' (then 5). Past 15, tapping the entry routes to the paywall (which lists 'Energy matching without limits'), never a shaming wall, and no AI call is made ('premium.gate_hit' reason 'energy' logs). The counter resets on the 1st of the month with no carry-over. Premium is unlimited and never sees a counter line.</t>
         </is>
       </c>
       <c r="G283" s="7" t="inlineStr">
@@ -12054,7 +12054,7 @@
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>OCR-02</t>
+          <t>OCR-01</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
@@ -12069,17 +12069,17 @@
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>Free: Scan routes to the upsell, never opens the camera</t>
+          <t>Premium: the Scan button opens the camera</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>As a free user, tap the + pill and then Scan in the panel.</t>
+          <t>As premium, tap the + pill and then Scan (camera) beside Speak in the panel.</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>Routed to the Premium screen calmly (never a wall). A 'premium.gate_hit' with reason 'ocr' is logged. No camera opens.</t>
+          <t>The camera screen opens: a live viewfinder with a shutter and a Photos shortcut on a device, or a 'Choose a photo' prompt on web. No paywall.</t>
         </is>
       </c>
       <c r="G284" s="7" t="inlineStr">
@@ -12094,7 +12094,7 @@
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>OCR-03</t>
+          <t>OCR-02</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
@@ -12109,22 +12109,22 @@
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>Photograph a list and the tasks land in the box</t>
+          <t>Free: Scan routes to the upsell, never opens the camera</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>As premium on a device, tap Scan, photograph a short printed or handwritten list (fill the frame), wait for 'Reading your list...'.</t>
+          <t>As a free user, tap the + pill and then Scan in the panel.</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>The tasks it reads appear in the brain-dump box, one per line, editable. Nothing is auto-added to Today, and tapping Add commits them. An 'ocr.captured' event is logged.</t>
+          <t>Routed to the Premium screen calmly (never a wall). A 'premium.gate_hit' with reason 'ocr' is logged. No camera opens.</t>
         </is>
       </c>
       <c r="G285" s="7" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H285" s="7" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>OCR-04</t>
+          <t>OCR-03</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -12142,29 +12142,29 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="C286" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C286" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>Gallery fallback reads an existing photo</t>
+          <t>Photograph a list and the tasks land in the box</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>Tap Scan, then 'Photos' (device) or 'Choose a photo' (web), and pick a photo of a list, a note, or a whiteboard.</t>
+          <t>As premium on a device, tap Scan, photograph a short printed or handwritten list (fill the frame), wait for 'Reading your list...'.</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>Same result: the read tasks land in the box for review. Covers a screenshot of a texted list, or a photo taken earlier.</t>
+          <t>The tasks it reads appear in the brain-dump box, one per line, editable. Nothing is auto-added to Today, and tapping Add commits them. An 'ocr.captured' event is logged.</t>
         </is>
       </c>
       <c r="G286" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="H286" s="7" t="inlineStr"/>
@@ -12174,7 +12174,7 @@
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>OCR-05</t>
+          <t>OCR-04</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -12189,17 +12189,17 @@
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>An unreadable photo fails calmly</t>
+          <t>Gallery fallback reads an existing photo</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>Scan a blank, blurry, or list-free image.</t>
+          <t>Tap Scan, then 'Photos' (device) or 'Choose a photo' (web), and pick a photo of a list, a note, or a whiteboard.</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>A calm line ('I couldn't read any tasks from that. Try again...'), the camera stays open, never a crash and never a shaming message.</t>
+          <t>Same result: the read tasks land in the box for review. Covers a screenshot of a texted list, or a photo taken earlier.</t>
         </is>
       </c>
       <c r="G287" s="7" t="inlineStr">
@@ -12214,7 +12214,7 @@
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>OCR-06</t>
+          <t>OCR-05</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -12229,22 +12229,22 @@
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>Camera denial is never a dead end</t>
+          <t>An unreadable photo fails calmly</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>On a device, deny the camera permission when prompted.</t>
+          <t>Scan a blank, blurry, or list-free image.</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>A calm screen offers 'Allow camera' and 'Choose from photos instead', and the gallery path still reads a list.</t>
+          <t>A calm line ('I couldn't read any tasks from that. Try again...'), the camera stays open, never a crash and never a shaming message.</t>
         </is>
       </c>
       <c r="G288" s="7" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H288" s="7" t="inlineStr"/>
@@ -12254,7 +12254,7 @@
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>OCR-07</t>
+          <t>OCR-06</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -12262,29 +12262,29 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="C289" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C289" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>AI egress is disclosed at the point of use</t>
+          <t>Camera denial is never a dead end</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>Open the Scan screen (device or web).</t>
+          <t>On a device, deny the camera permission when prompted.</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>The note 'Your photo is sent to the AI to read your list, then discarded. It is never stored.' is visible. The D1 'ocr' telemetry row holds only the image size and task count, never the image or the titles.</t>
+          <t>A calm screen offers 'Allow camera' and 'Choose from photos instead', and the gallery path still reads a list.</t>
         </is>
       </c>
       <c r="G289" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="H289" s="7" t="inlineStr"/>
@@ -12294,32 +12294,32 @@
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>CHART-01</t>
+          <t>OCR-07</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
         <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C290" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Scan</t>
+        </is>
+      </c>
+      <c r="C290" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>Premium: chart a course toward a goal</t>
+          <t>AI egress is disclosed at the point of use</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>As premium (or dev Premium override on), open Rooms, tap 'Chart a course', type a goal like 'get fit for a 10k', tap 'Suggest steps'.</t>
+          <t>Open the Scan screen (device or web).</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>A calm one-line heading plus 3-7 ticked next steps appear, and nothing is added yet. Tapping 'Add N tasks' lands them on Today (the first undated, later ones spread forward), each an ordinary task, and returns to Today. The 'chart.requested' then 'chart.added' events are logged.</t>
+          <t>The note 'Your photo is sent to the AI to read your list, then discarded. It is never stored.' is visible. The D1 'ocr' telemetry row holds only the image size and task count, never the image or the titles.</t>
         </is>
       </c>
       <c r="G290" s="7" t="inlineStr">
@@ -12334,7 +12334,7 @@
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>CHART-02</t>
+          <t>CHART-01</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
@@ -12349,17 +12349,17 @@
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Free: charting routes to the upsell, never plans</t>
+          <t>Premium: chart a course toward a goal</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>As a free user, open the Menu, tap 'Chart a course', type a goal, pick a timeframe, tap 'Suggest steps', then come back.</t>
+          <t>As premium (or dev Premium override on), open Rooms, tap 'Chart a course', type a goal like 'get fit for a 10k', tap 'Suggest steps'.</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>Before the tap the room already says '✦ Suggesting steps is part of Premium.' under the button, once and static. The tap routes to the Premium screen calmly (never a wall), and a 'premium.gate_hit' with reason 'chart' is logged. No plan is generated and nothing is added. Coming back, the goal and the chosen timeframe are still there, including after a purchase: on the phone the Premium panel's way out reads '‹ Chart a course', and on web a checkout round-trip brings the goal back the next time the room opens. Nothing is locked, blurred or priced.</t>
+          <t>A calm one-line heading plus 3-7 ticked next steps appear, and nothing is added yet. Tapping 'Add N tasks' lands them on Today (the first undated, later ones spread forward), each an ordinary task, and returns to Today. The 'chart.requested' then 'chart.added' events are logged.</t>
         </is>
       </c>
       <c r="G291" s="7" t="inlineStr">
@@ -12374,7 +12374,7 @@
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>CHART-03</t>
+          <t>CHART-02</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -12382,24 +12382,24 @@
           <t>Chart</t>
         </is>
       </c>
-      <c r="C292" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C292" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>Propose-then-accept: nothing auto-adds</t>
+          <t>Free: charting routes to the upsell, never plans</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>As premium, generate a plan, untick two steps, then tap 'Add'. Separately, generate a plan and back out with 'Not these, start over' or Back.</t>
+          <t>As a free user, open the Menu, tap 'Chart a course', type a goal, pick a timeframe, tap 'Suggest steps', then come back.</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>Only the ticked steps are added as plain tasks, and backing out adds nothing. Today was unchanged before accepting.</t>
+          <t>Before the tap the room already says '✦ Suggesting steps is part of Premium.' under the button, once and static. The tap routes to the Premium screen calmly (never a wall), and a 'premium.gate_hit' with reason 'chart' is logged. No plan is generated and nothing is added. Coming back, the goal and the chosen timeframe are still there, including after a purchase: on the phone the Premium panel's way out reads '‹ Chart a course', and on web a checkout round-trip brings the goal back the next time the room opens. Nothing is locked, blurred or priced.</t>
         </is>
       </c>
       <c r="G292" s="7" t="inlineStr">
@@ -12414,7 +12414,7 @@
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>CHART-04</t>
+          <t>CHART-03</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
@@ -12429,17 +12429,17 @@
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>A goal that cannot be mapped fails calmly</t>
+          <t>Propose-then-accept: nothing auto-adds</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>Enter an empty goal (the button is disabled), then a nonsensical goal and submit.</t>
+          <t>As premium, generate a plan, untick two steps, then tap 'Add'. Separately, generate a plan and back out with 'Not these, start over' or Back.</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>The empty case cannot submit. A nonsensical goal shows one calm line ('I couldn't map that out just now'), the goal stays editable, never a crash or a shaming message.</t>
+          <t>Only the ticked steps are added as plain tasks, and backing out adds nothing. Today was unchanged before accepting.</t>
         </is>
       </c>
       <c r="G293" s="7" t="inlineStr">
@@ -12454,7 +12454,7 @@
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>CHART-05</t>
+          <t>CHART-04</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -12469,17 +12469,17 @@
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>A deadline spreads the steps across the timeframe</t>
+          <t>A goal that cannot be mapped fails calmly</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>As premium, type a goal, tap a 'By when?' chip (e.g. 'In 2 months'), then Suggest steps and Add.</t>
+          <t>Enter an empty goal (the button is disabled), then a nonsensical goal and submit.</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>The steps are paced for that timeframe, and the accepted tasks spread from Today out to the chosen date (not crammed into the next few days). 'No deadline' keeps the gentle one-per-day default.</t>
+          <t>The empty case cannot submit. A nonsensical goal shows one calm line ('I couldn't map that out just now'), the goal stays editable, never a crash or a shaming message.</t>
         </is>
       </c>
       <c r="G294" s="7" t="inlineStr">
@@ -12494,7 +12494,7 @@
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>CHART-06</t>
+          <t>CHART-05</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
@@ -12509,17 +12509,17 @@
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>The timeframe stays named once the steps arrive</t>
+          <t>A deadline spreads the steps across the timeframe</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>Premium. Type a goal, pick 'In 2 months', Suggest steps. Then 'Not these, start over', pick no deadline, and suggest again.</t>
+          <t>As premium, type a goal, tap a 'By when?' chip (e.g. 'In 2 months'), then Suggest steps and Add.</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>Once the steps arrive the chips step aside, and one quiet line above the heading keeps the choice named: 'By when · In 2 months' (then 'By when · No deadline'). The AI's heading is in italic serif; every step starts ticked, each with its minutes and a ✕. The button counts only what will be added.</t>
+          <t>The steps are paced for that timeframe, and the accepted tasks spread from Today out to the chosen date (not crammed into the next few days). 'No deadline' keeps the gentle one-per-day default.</t>
         </is>
       </c>
       <c r="G295" s="7" t="inlineStr">
@@ -12534,7 +12534,7 @@
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>CHART-07</t>
+          <t>CHART-06</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -12549,17 +12549,17 @@
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>The steps show where they landed on Today</t>
+          <t>The timeframe stays named once the steps arrive</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>Premium. Chart a course, accept the steps with 'Add N tasks'.</t>
+          <t>Premium. Type a goal, pick 'In 2 months', Suggest steps. Then 'Not these, start over', pick no deadline, and suggest again.</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>You land on Today (never back on the spent proposal; back from Today does not return to it). The first step is on Today carrying the soft 'just added' tint, which fades away after a couple of seconds. The rest wait on their days.</t>
+          <t>Once the steps arrive the chips step aside, and one quiet line above the heading keeps the choice named: 'By when · In 2 months' (then 'By when · No deadline'). The AI's heading is in italic serif; every step starts ticked, each with its minutes and a ✕. The button counts only what will be added.</t>
         </is>
       </c>
       <c r="G296" s="7" t="inlineStr">
@@ -12574,7 +12574,7 @@
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>CHART-08</t>
+          <t>CHART-07</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -12582,24 +12582,24 @@
           <t>Chart</t>
         </is>
       </c>
-      <c r="C297" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C297" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>The small marks read on paper</t>
+          <t>The steps show where they landed on Today</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>In light mode, open Chart a course, get a proposal, and look at an unticked box, a step's minutes, the ✕, the spread note and the note at the foot. Then look at a selected timeframe chip.</t>
+          <t>Premium. Chart a course, accept the steps with 'Add N tasks'.</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>All of them read clearly (they moved from the faintest ink to the soft ink). The instruction under the title is in full ink. A selected chip keeps its tinted fill and border, and its label is ink rather than the accent, which was too faint on the tint. In dark mode the selected label stays the accent.</t>
+          <t>You land on Today (never back on the spent proposal; back from Today does not return to it). The first step is on Today carrying the soft 'just added' tint, which fades away after a couple of seconds. The rest wait on their days.</t>
         </is>
       </c>
       <c r="G297" s="7" t="inlineStr">
@@ -12614,32 +12614,32 @@
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>SEQ-01</t>
+          <t>CHART-08</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
         <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="C298" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C298" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>Premium: Plan my day suggests a calm sequence</t>
+          <t>The small marks read on paper</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>As premium with 3+ open one-off tasks on Today, tap 'Plan my day'. Answer the questions it asks first (or skip them).</t>
+          <t>In light mode, open Chart a course, get a proposal, and look at an unticked box, a step's minutes, the ✕, the spread note and the note at the foot. Then look at a selected timeframe chip.</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>A proposal card lists today's tasks in a suggested order, each with a short calm reason. Nothing reorders until 'Use this order' is tapped, then the list re-sequences in place (no dates change, no task moves to another day). A 'sequence.accepted' event is logged.</t>
+          <t>All of them read clearly (they moved from the faintest ink to the soft ink). The instruction under the title is in full ink. A selected chip keeps its tinted fill and border, and its label is ink rather than the accent, which was too faint on the tint. In dark mode the selected label stays the accent.</t>
         </is>
       </c>
       <c r="G298" s="7" t="inlineStr">
@@ -12654,12 +12654,12 @@
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>TOD-27</t>
+          <t>SEQ-01</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Sequence</t>
         </is>
       </c>
       <c r="C299" s="8" t="inlineStr">
@@ -12669,17 +12669,17 @@
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>Right now: one card near the top, a clock-set slot, the tools open downward, Energy pills</t>
+          <t>Premium: Plan my day suggests a calm sequence</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>Open Today in the MORNING (before 11), around MIDDAY (11-17), and in the EVENING (17+), reading the 'RIGHT NOW' card under Energy each time. Tap the caret at its right. Add and complete tasks and watch whether ANY control moves. Tap an unavailable (faded) tool. Set the Energy pills to High on a 7-task day and re-open the caret; set Low and read the gauge. Reload the app and check the pill. Turn AI off in Settings and re-open the caret. Also check with 0 tasks, in select mode, while typing in the composer, and after closing the day.</t>
+          <t>As premium with 3+ open one-off tasks on Today, tap 'Plan my day'. Answer the questions it asks first (or skip them).</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>ONE card sits under the Energy pills, near the top: an overline 'RIGHT NOW' + the tool that suits the HOUR (morning: Plan my day; midday: Focus on one thing; evening: Close the day), plus a caret ('All day tools'). The occupant is set by the CLOCK at open and never changes mid-session; it NEVER shows Lighten today. The caret opens the tools DOWNWARD inside the same card, in the same day order every time: Plan my day, Focus on one thing, Lighten today, Settle, Close the day, the current occupant tagged 'now', Plan my day wearing the honey ✦ when you are not Premium. The list moves down to make room and nothing covers it (no dim, no scrim). NOTHING in the card appears, vanishes or slides as tasks are added or completed: an unavailable tool stays in place at lowered contrast and tapping it explains in one plain line what the TOOL needs ('Plan my day needs two or more tasks.' / 'Lighten today is for a full day.'), never what the person lacks. The Energy pills (Low/Normal/High) sit under a small 'ENERGY' overline with the gauge above, on EVERY open day, including an empty one ('A clear day.'). A fresh day defaults to Normal. High re-scales what 'full' means, Low IS the low-capacity day, and the choice survives a reload but RESETS to Normal next morning. With AI OFF the card holds only the non-AI tools (AI tools are gone, not faded). In select mode the card RESTS (dimmed, does not respond) rather than vanishing, so the list does not jump. While the composer is open the card steps aside with the rest of the heading. On a closed day it is gone.</t>
+          <t>A proposal card lists today's tasks in a suggested order, each with a short calm reason. Nothing reorders until 'Use this order' is tapped, then the list re-sequences in place (no dates change, no task moves to another day). A 'sequence.accepted' event is logged.</t>
         </is>
       </c>
       <c r="G299" s="7" t="inlineStr">
@@ -12694,7 +12694,7 @@
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>TOD-28</t>
+          <t>TOD-27</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
@@ -12702,24 +12702,24 @@
           <t>Today</t>
         </is>
       </c>
-      <c r="C300" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C300" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>The rested screen mentions the scrapbook once, at the earned moment (the ladder's last rung)</t>
+          <t>Right now: one card near the top, a clock-set slot, the tools open downward, Energy pills</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>With AI on, the reminder and widget asks already spent (or reminder on, widget placed), NO scrapbook ever made, and at least 3 finishes this week, close the day and read the rested screen. Tap 'See your Calendar'. Then close a day again on another evening. Separately: repeat with AI off, and repeat with only 1-2 finishes.</t>
+          <t>Open Today in the MORNING (before 11), around MIDDAY (11-17), and in the EVENING (17+), reading the 'RIGHT NOW' card under Energy each time. Tap the caret at its right. Add and complete tasks and watch whether ANY control moves. Tap an unavailable (faded) tool. Set the Energy pills to High on a 7-task day and re-open the caret; set Low and read the gauge. Reload the app and check the pill. Turn AI off in Settings and re-open the caret. Also check with 0 tasks, in select mode, while typing in the composer, and after closing the day.</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>One calm mention appears under the goodnight text: 'You've finished enough this week to make a keepsake of it. It's waiting in your Calendar.' with 'See your Calendar' and 'Not now'. Either answer spends the mention FOREVER (it is the third and LAST rung of the one-ask-at-a-time ladder; reminder and widget always win the evening if pending). 'See your Calendar' opens the Calendar where the scrapbook lives. It never shows with AI off, never with fewer than 3 finishes this week, never to someone who has already made a scrapbook, and never twice.</t>
+          <t>ONE card sits under the Energy pills, near the top: an overline 'RIGHT NOW' + the tool that suits the HOUR (morning: Plan my day; midday: Focus on one thing; evening: Close the day), plus a caret ('All day tools'). The occupant is set by the CLOCK at open and never changes mid-session; it NEVER shows Lighten today. The caret opens the tools DOWNWARD inside the same card, in the same day order every time: Plan my day, Focus on one thing, Lighten today, Settle, Close the day, the current occupant tagged 'now', Plan my day wearing the honey ✦ when you are not Premium. The list moves down to make room and nothing covers it (no dim, no scrim). NOTHING in the card appears, vanishes or slides as tasks are added or completed: an unavailable tool stays in place at lowered contrast and tapping it explains in one plain line what the TOOL needs ('Plan my day needs two or more tasks.' / 'Lighten today is for a full day.'), never what the person lacks. The Energy pills (Low/Normal/High) sit under a small 'ENERGY' overline with the gauge above, on EVERY open day, including an empty one ('A clear day.'). A fresh day defaults to Normal. High re-scales what 'full' means, Low IS the low-capacity day, and the choice survives a reload but RESETS to Normal next morning. With AI OFF the card holds only the non-AI tools (AI tools are gone, not faded). In select mode the card RESTS (dimmed, does not respond) rather than vanishing, so the list does not jump. While the composer is open the card steps aside with the rest of the heading. On a closed day it is gone.</t>
         </is>
       </c>
       <c r="G300" s="7" t="inlineStr">
@@ -12734,32 +12734,32 @@
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>SEQ-07</t>
+          <t>TOD-28</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
         <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="C301" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="C301" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>Plan my day asks about the day BEFORE it sorts</t>
+          <t>The rested screen mentions the scrapbook once, at the earned moment (the ladder's last rung)</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>As premium, tap 'Plan my day'. Read the sheet that opens. Tap an answer, then tap the SAME answer again. Try sorting with all three answered, with only one answered, and with none answered ('Sort today' straight away). Also tap 'Not now'. Separately, as a FREE user, tap 'Plan my day'.</t>
+          <t>With AI on, the reminder and widget asks already spent (or reminder on, widget placed), NO scrapbook ever made, and at least 3 finishes this week, close the day and read the rested screen. Tap 'See your Calendar'. Then close a day again on another evening. Separately: repeat with AI off, and repeat with only 1-2 finishes.</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>Before any sorting, a calm sheet asks three OPTIONAL questions: 'How's your energy?' (Running low / Somewhere in between / Feeling good), 'What kind of day?' (Work day / Day off) and 'Where are you?' (Indoors / Out and about / Either), under 'Answer what you like. Skip what you don't.'. A chosen answer tints (accent border, fill and bold accent text); tapping it AGAIN clears it, so a mis-tap is undone the way it was made. Skipping a question sends nothing for it, so it never becomes an assumption, and skipping all three sorts exactly as it always did. The order that comes back reflects what was said (a low-energy day starts small; a day off does not front-load work; 'out and about' clusters the errands), but the app NEVER comments on how you feel. 'Not now' closes with nothing sent and the day untouched. A FREE user hits the Premium screen BEFORE the questions, never after answering them. NEW (the constant frame): when the Energy PILLS at the top of Today were touched today, the sheet's energy question DOES NOT APPEAR at all, and the pill's answer rides the request instead (Low-&gt;low, Normal-&gt;medium, High-&gt;good): energy is read, never asked twice. Only when the pills are untouched does the sheet ask. NOTE: there is deliberately no weather question. A model has no live weather data, and a forecast would need an API plus a location permission; 'Where are you?' is what the sort actually needs.</t>
+          <t>One calm mention appears under the goodnight text: 'You've finished enough this week to make a keepsake of it. It's waiting in your Calendar.' with 'See your Calendar' and 'Not now'. Either answer spends the mention FOREVER (it is the third and LAST rung of the one-ask-at-a-time ladder; reminder and widget always win the evening if pending). 'See your Calendar' opens the Calendar where the scrapbook lives. It never shows with AI off, never with fewer than 3 finishes this week, never to someone who has already made a scrapbook, and never twice.</t>
         </is>
       </c>
       <c r="G301" s="7" t="inlineStr">
@@ -12774,7 +12774,7 @@
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
         <is>
-          <t>SEQ-08</t>
+          <t>SEQ-07</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
@@ -12789,17 +12789,17 @@
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>The suggested order can be edited before it is used</t>
+          <t>Plan my day asks about the day BEFORE it sorts</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>Get a proposal from 'Plan my day'. Use the up and down arrows on a row. Try the up arrow on the FIRST row and the down arrow on the LAST. Remove a row with x. Remove every row. Then tap 'Use this order'.</t>
+          <t>As premium, tap 'Plan my day'. Read the sheet that opens. Tap an answer, then tap the SAME answer again. Try sorting with all three answered, with only one answered, and with none answered ('Sort today' straight away). Also tap 'Not now'. Separately, as a FREE user, tap 'Plan my day'.</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>Each row carries up / down / x. Up and down swap the row with its neighbour immediately, renumbering as they go; the first row's up and the last row's down are visibly dimmed and do nothing (they are disabled, not hidden, so rows never change shape as things move). 'x' takes that task OUT OF THIS PLAN ONLY: the task stays on Today untouched, is not deleted, and is not moved to another day. Removing everything is allowed and says 'Nothing left in the plan. That's allowed.' with the accept button gone (an empty plan cannot be applied). Nothing at all changes on Today until 'Use this order' is tapped; 'Not now' or closing discards every edit. Editing is by buttons, never drag: dragging is unusable with a screen reader and hard with shaky hands.</t>
+          <t>Before any sorting, a calm sheet asks three OPTIONAL questions: 'How's your energy?' (Running low / Somewhere in between / Feeling good), 'What kind of day?' (Work day / Day off) and 'Where are you?' (Indoors / Out and about / Either), under 'Answer what you like. Skip what you don't.'. A chosen answer tints (accent border, fill and bold accent text); tapping it AGAIN clears it, so a mis-tap is undone the way it was made. Skipping a question sends nothing for it, so it never becomes an assumption, and skipping all three sorts exactly as it always did. The order that comes back reflects what was said (a low-energy day starts small; a day off does not front-load work; 'out and about' clusters the errands), but the app NEVER comments on how you feel. 'Not now' closes with nothing sent and the day untouched. A FREE user hits the Premium screen BEFORE the questions, never after answering them. NEW (the constant frame): when the Energy PILLS at the top of Today were touched today, the sheet's energy question DOES NOT APPEAR at all, and the pill's answer rides the request instead (Low-&gt;low, Normal-&gt;medium, High-&gt;good): energy is read, never asked twice. Only when the pills are untouched does the sheet ask. NOTE: there is deliberately no weather question. A model has no live weather data, and a forecast would need an API plus a location permission; 'Where are you?' is what the sort actually needs.</t>
         </is>
       </c>
       <c r="G302" s="7" t="inlineStr">
@@ -12814,7 +12814,7 @@
     <row r="303">
       <c r="A303" s="6" t="inlineStr">
         <is>
-          <t>SEQ-02</t>
+          <t>SEQ-08</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
@@ -12829,17 +12829,17 @@
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>Free: Plan my day routes to the upsell, never reorders</t>
+          <t>The suggested order can be edited before it is used</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>As a free user with 2+ tasks on Today, tap 'Plan my day'.</t>
+          <t>Get a proposal from 'Plan my day'. Use the up and down arrows on a row. Try the up arrow on the FIRST row and the down arrow on the LAST. Remove a row with x. Remove every row. Then tap 'Use this order'.</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>The Premium screen opens calmly (never a wall), a 'premium.gate_hit' with reason 'sequence' is logged, and the day's order is unchanged.</t>
+          <t>Each row carries up / down / x. Up and down swap the row with its neighbour immediately, renumbering as they go; the first row's up and the last row's down are visibly dimmed and do nothing (they are disabled, not hidden, so rows never change shape as things move). 'x' takes that task OUT OF THIS PLAN ONLY: the task stays on Today untouched, is not deleted, and is not moved to another day. Removing everything is allowed and says 'Nothing left in the plan. That's allowed.' with the accept button gone (an empty plan cannot be applied). Nothing at all changes on Today until 'Use this order' is tapped; 'Not now' or closing discards every edit. Editing is by buttons, never drag: dragging is unusable with a screen reader and hard with shaky hands.</t>
         </is>
       </c>
       <c r="G303" s="7" t="inlineStr">
@@ -12854,7 +12854,7 @@
     <row r="304">
       <c r="A304" s="6" t="inlineStr">
         <is>
-          <t>SEQ-03</t>
+          <t>SEQ-02</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -12862,24 +12862,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C304" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C304" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>'Not now' leaves the day untouched</t>
+          <t>Free: Plan my day routes to the upsell, never reorders</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>As premium, open the proposal, then tap 'Not now' or the backdrop.</t>
+          <t>As a free user with 2+ tasks on Today, tap 'Plan my day'.</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>The order is exactly as before, nothing reordered, and no manualOrder is written.</t>
+          <t>The Premium screen opens calmly (never a wall), a 'premium.gate_hit' with reason 'sequence' is logged, and the day's order is unchanged.</t>
         </is>
       </c>
       <c r="G304" s="7" t="inlineStr">
@@ -12894,7 +12894,7 @@
     <row r="305">
       <c r="A305" s="6" t="inlineStr">
         <is>
-          <t>SEQ-04</t>
+          <t>SEQ-03</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -12909,17 +12909,17 @@
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>An accepted order survives a reload (local-first)</t>
+          <t>'Not now' leaves the day untouched</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>As premium, accept an order, then fully reload the app.</t>
+          <t>As premium, open the proposal, then tap 'Not now' or the backdrop.</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>Today still shows the accepted order after reload (manualOrder persists on-device). Note: the order does not yet sync across devices, which is a documented follow-up.</t>
+          <t>The order is exactly as before, nothing reordered, and no manualOrder is written.</t>
         </is>
       </c>
       <c r="G305" s="7" t="inlineStr">
@@ -12934,7 +12934,7 @@
     <row r="306">
       <c r="A306" s="6" t="inlineStr">
         <is>
-          <t>SEQ-05</t>
+          <t>SEQ-04</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -12942,24 +12942,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C306" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C306" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>A pinned task still wins the very top</t>
+          <t>An accepted order survives a reload (local-first)</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>As premium, pin a task, then accept a 'Plan my day' sequence that puts a different task first.</t>
+          <t>As premium, accept an order, then fully reload the app.</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>The pinned task stays at the very top, and the accepted order applies to everything below it.</t>
+          <t>Today still shows the accepted order after reload (manualOrder persists on-device). Note: the order does not yet sync across devices, which is a documented follow-up.</t>
         </is>
       </c>
       <c r="G306" s="7" t="inlineStr">
@@ -12974,7 +12974,7 @@
     <row r="307">
       <c r="A307" s="6" t="inlineStr">
         <is>
-          <t>SEQ-06</t>
+          <t>SEQ-05</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
@@ -12982,24 +12982,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C307" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C307" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>Plan my day offers to lighten a heavy day</t>
+          <t>A pinned task still wins the very top</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>As premium on a heavy day (6+ tasks), tap 'Plan my day', accept the order.</t>
+          <t>As premium, pin a task, then accept a 'Plan my day' sequence that puts a different task first.</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>After the order applies, a 'Still a full day?' card offers to push a few tasks out to later days. Yes runs the re-spread (propose-then-accept), No leaves it ordered. On a calm day the offer never appears.</t>
+          <t>The pinned task stays at the very top, and the accepted order applies to everything below it.</t>
         </is>
       </c>
       <c r="G307" s="7" t="inlineStr">
@@ -13014,32 +13014,32 @@
     <row r="308">
       <c r="A308" s="6" t="inlineStr">
         <is>
-          <t>BIG-01</t>
+          <t>SEQ-06</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
         <is>
-          <t>Big task</t>
-        </is>
-      </c>
-      <c r="C308" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Sequence</t>
+        </is>
+      </c>
+      <c r="C308" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>Mark a task big: the tag, and the weight it adds</t>
+          <t>Plan my day offers to lighten a heavy day</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>On Today with a few one-off tasks, tap and hold one, then tap 'Mark as a lot' in the held row's actions. ALSO hold a RECURRING task and confirm 'Mark as a lot' is offered there too (a chore can be a lot; this used to be offered only via the bulk bar).</t>
+          <t>As premium on a heavy day (6+ tasks), tap 'Plan my day', accept the order.</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>The card closes and the task shows a calm accent 'Big' tag beside its title (never red, never a warning), with a brief validating note ('Marked as a lot...'). The weight gauge fills further and reads heavier (one big task floors the bar to at least 'A full day, but doable.'). Free for everyone, no upsell.</t>
+          <t>After the order applies, a 'Still a full day?' card offers to push a few tasks out to later days. Yes runs the re-spread (propose-then-accept), No leaves it ordered. On a calm day the offer never appears.</t>
         </is>
       </c>
       <c r="G308" s="7" t="inlineStr">
@@ -13054,7 +13054,7 @@
     <row r="309">
       <c r="A309" s="6" t="inlineStr">
         <is>
-          <t>BIG-02</t>
+          <t>BIG-01</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
@@ -13062,24 +13062,24 @@
           <t>Big task</t>
         </is>
       </c>
-      <c r="C309" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C309" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>Big is a multi-select toggle</t>
+          <t>Mark a task big: the tag, and the weight it adds</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>Hold a task, 'Select more', tick another, then tap 'Mark as a lot'; then re-select tasks that are all big and tap the action again (it now reads 'Not big').</t>
+          <t>On Today with a few one-off tasks, tap and hold one, then tap 'Mark as a lot' in the held row's actions. ALSO hold a RECURRING task and confirm 'Mark as a lot' is offered there too (a chore can be a lot; this used to be offered only via the bulk bar).</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>The first tap marks every selected task big at once. When all selected tasks are already big the action reads 'Not big' and clears the mark off all of them. A mixed selection marks all big (the additive default).</t>
+          <t>The card closes and the task shows a calm accent 'Big' tag beside its title (never red, never a warning), with a brief validating note ('Marked as a lot...'). The weight gauge fills further and reads heavier (one big task floors the bar to at least 'A full day, but doable.'). Free for everyone, no upsell.</t>
         </is>
       </c>
       <c r="G309" s="7" t="inlineStr">
@@ -13094,7 +13094,7 @@
     <row r="310">
       <c r="A310" s="6" t="inlineStr">
         <is>
-          <t>BIG-03</t>
+          <t>BIG-02</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -13109,17 +13109,17 @@
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>A lone big task lifts the bar but is not a re-spread problem</t>
+          <t>Big is a multi-select toggle</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>Have just one or two tasks on Today, one marked big.</t>
+          <t>Hold a task, 'Select more', tick another, then tap 'Mark as a lot'; then re-select tasks that are all big and tap the action again (it now reads 'Not big').</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>The weight gauge reads at least 'A full day, but doable.' (the big task is felt), but 'Today's looking full' and 'Lighten today' do NOT appear for a lone big task (re-spreading cannot dissolve one big rock; Break it down is the tool). A big task plus a real pile (weighted load 6+) does surface Lighten today.</t>
+          <t>The first tap marks every selected task big at once. When all selected tasks are already big the action reads 'Not big' and clears the mark off all of them. A mixed selection marks all big (the additive default).</t>
         </is>
       </c>
       <c r="G310" s="7" t="inlineStr">
@@ -13134,7 +13134,7 @@
     <row r="311">
       <c r="A311" s="6" t="inlineStr">
         <is>
-          <t>BIG-04</t>
+          <t>BIG-03</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -13149,17 +13149,17 @@
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>Finishing a big task is a big-win in the Calendar</t>
+          <t>A lone big task lifts the bar but is not a re-spread problem</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>Mark a task big, complete it, then open the Calendar to its day.</t>
+          <t>Have just one or two tasks on Today, one marked big.</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>The completed task carries the warmer 'a big one' treatment on its day, the same payoff a long-dreaded or chunky task earns. The big flag never adds disappointment if the task is left unfinished.</t>
+          <t>The weight gauge reads at least 'A full day, but doable.' (the big task is felt), but 'Today's looking full' and 'Lighten today' do NOT appear for a lone big task (re-spreading cannot dissolve one big rock; Break it down is the tool). A big task plus a real pile (weighted load 6+) does surface Lighten today.</t>
         </is>
       </c>
       <c r="G311" s="7" t="inlineStr">
@@ -13174,7 +13174,7 @@
     <row r="312">
       <c r="A312" s="6" t="inlineStr">
         <is>
-          <t>BIG-05</t>
+          <t>BIG-04</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -13189,17 +13189,17 @@
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>Big syncs across devices (and old marks survive the upgrade)</t>
+          <t>Finishing a big task is a big-win in the Calendar</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>Signed in on two devices (e.g. web + Android). Mark a task big on device 1, wait for or trigger a sync, then open device 2. Then unmark it on device 2 and check device 1. Prerequisite: an account with the same task on both.</t>
+          <t>Mark a task big, complete it, then open the Calendar to its day.</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>The Big tag appears on device 2 (with its weight-gauge effect), and the unmark travels back: no resurrection, the newest change wins. Marks made BEFORE this build (when big was device-only) are seeded up to the account on that device's first sync rather than erased. One known transition quirk: a device still on a PRE-sync build can re-surface a cleared big once when it upgrades; clearing it again sticks everywhere. Manual order (Plan my order) remains per-device by design.</t>
+          <t>The completed task carries the warmer 'a big one' treatment on its day, the same payoff a long-dreaded or chunky task earns. The big flag never adds disappointment if the task is left unfinished.</t>
         </is>
       </c>
       <c r="G312" s="7" t="inlineStr">
@@ -13214,37 +13214,37 @@
     <row r="313">
       <c r="A313" s="6" t="inlineStr">
         <is>
-          <t>NAV-01</t>
+          <t>BIG-05</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
         <is>
-          <t>Rooms</t>
-        </is>
-      </c>
-      <c r="C313" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Big task</t>
+        </is>
+      </c>
+      <c r="C313" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>Rooms sheet caps its width on wide web</t>
+          <t>Big syncs across devices (and old marks survive the upgrade)</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>On a wide desktop browser, open Rooms (the header pill).</t>
+          <t>Signed in on two devices (e.g. web + Android). Mark a task big on device 1, wait for or trigger a sync, then open device 2. Then unmark it on device 2 and check device 1. Prerequisite: an account with the same task on both.</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>The sheet is a centred column (about 560px, matching the page content), not full-bleed, so the 'Premium' gradient pill on 'Chart a course' sits beside its label rather than at the far screen edge. On a phone the sheet stays full-width with the pill at the row's edge.</t>
+          <t>The Big tag appears on device 2 (with its weight-gauge effect), and the unmark travels back: no resurrection, the newest change wins. Marks made BEFORE this build (when big was device-only) are seeded up to the account on that device's first sync rather than erased. One known transition quirk: a device still on a PRE-sync build can re-surface a cleared big once when it upgrades; clearing it again sticks everywhere. Manual order (Plan my order) remains per-device by design.</t>
         </is>
       </c>
       <c r="G313" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H313" s="7" t="inlineStr"/>
@@ -13254,37 +13254,37 @@
     <row r="314">
       <c r="A314" s="6" t="inlineStr">
         <is>
-          <t>OUR-01</t>
+          <t>NAV-01</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C314" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="C314" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>The door only exists for an allowed account</t>
+          <t>Rooms sheet caps its width on wide web</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>Sign in as an account that is NOT on the ours_allowlist and open Settings. Then sign in as one that is.</t>
+          <t>On a wide desktop browser, open Rooms (the header pill).</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>The 'Ours' row is absent for the first account and present for the second. Nobody is ever offered a door that answers 'shared lists aren't open yet'.</t>
+          <t>The sheet is a centred column (about 560px, matching the page content), not full-bleed, so the 'Premium' gradient pill on 'Chart a course' sits beside its label rather than at the far screen edge. On a phone the sheet stays full-width with the pill at the row's edge.</t>
         </is>
       </c>
       <c r="G314" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H314" s="7" t="inlineStr"/>
@@ -13294,7 +13294,7 @@
     <row r="315">
       <c r="A315" s="6" t="inlineStr">
         <is>
-          <t>OUR-02</t>
+          <t>OUR-01</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
@@ -13309,17 +13309,17 @@
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>Signed out: the explanation, never a nag</t>
+          <t>The door only exists for an allowed account</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>Sign out, then open /ours directly.</t>
+          <t>Sign in as an account that is NOT on the ours_allowlist and open Settings. Then sign in as one that is.</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>A calm one-screen explanation of why sharing needs an account, and a way to sign in. No pressure, no count of what you are missing.</t>
+          <t>The 'Ours' row is absent for the first account and present for the second. Nobody is ever offered a door that answers 'shared lists aren't open yet'.</t>
         </is>
       </c>
       <c r="G315" s="7" t="inlineStr">
@@ -13334,7 +13334,7 @@
     <row r="316">
       <c r="A316" s="6" t="inlineStr">
         <is>
-          <t>OUR-03</t>
+          <t>OUR-02</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -13349,17 +13349,17 @@
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>Name the list and mint a code</t>
+          <t>Signed out: the explanation, never a nag</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>Ours &gt; Start a shared list. Pick 'The house'. Type your own name. Type the OTHER account's email exactly. Get a code.</t>
+          <t>Sign out, then open /ours directly.</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>A six-character code appears grouped as XXX-XXX, containing no 0, 1, I, L or O. The screen says it works once, for the next day, and only for the address you gave.</t>
+          <t>A calm one-screen explanation of why sharing needs an account, and a way to sign in. No pressure, no count of what you are missing.</t>
         </is>
       </c>
       <c r="G316" s="7" t="inlineStr">
@@ -13374,7 +13374,7 @@
     <row r="317">
       <c r="A317" s="6" t="inlineStr">
         <is>
-          <t>OUR-04</t>
+          <t>OUR-03</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -13389,17 +13389,17 @@
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>Join from the second account</t>
+          <t>Name the list and mint a code</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>On the second account, Ours &gt; Join with a code. Type the code (try it lower-case and with the dash). Type your own name. Join.</t>
+          <t>Ours &gt; Start a shared list. Pick 'The house'. Type your own name. Type the OTHER account's email exactly. Get a code.</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>You land on the shared list showing the FIRST person's chosen name and the list's name ('The house'). No email address is shown anywhere, to either person.</t>
+          <t>A six-character code appears grouped as XXX-XXX, containing no 0, 1, I, L or O. The screen says it works once, for the next day, and only for the address you gave.</t>
         </is>
       </c>
       <c r="G317" s="7" t="inlineStr">
@@ -13414,7 +13414,7 @@
     <row r="318">
       <c r="A318" s="6" t="inlineStr">
         <is>
-          <t>OUR-05</t>
+          <t>OUR-04</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -13429,17 +13429,17 @@
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>The first person sees the arrival without refreshing</t>
+          <t>Join from the second account</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>Leave the first account sitting on the Ours screen while the second joins.</t>
+          <t>On the second account, Ours &gt; Join with a code. Type the code (try it lower-case and with the dash). Type your own name. Join.</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>Within about ten seconds it announces that they joined, with a way out for someone who meant a different person. It never says how long they took.</t>
+          <t>You land on the shared list showing the FIRST person's chosen name and the list's name ('The house'). No email address is shown anywhere, to either person.</t>
         </is>
       </c>
       <c r="G318" s="7" t="inlineStr">
@@ -13454,7 +13454,7 @@
     <row r="319">
       <c r="A319" s="6" t="inlineStr">
         <is>
-          <t>OUR-06</t>
+          <t>OUR-05</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -13462,24 +13462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C319" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C319" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>A wrong code says one calm thing</t>
+          <t>The first person sees the arrival without refreshing</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>Try a made-up code, then a code meant for a different address, then the same code twice.</t>
+          <t>Leave the first account sitting on the Ours screen while the second joins.</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>Every one gives the SAME single line ('That code isn't valid.'). Nothing hints at which reason, so a guesser learns nothing. Repeated wrong tries eventually ask you to have a break.</t>
+          <t>Within about ten seconds it announces that they joined, with a way out for someone who meant a different person. It never says how long they took.</t>
         </is>
       </c>
       <c r="G319" s="7" t="inlineStr">
@@ -13494,7 +13494,7 @@
     <row r="320">
       <c r="A320" s="6" t="inlineStr">
         <is>
-          <t>OUR-07</t>
+          <t>OUR-06</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -13509,17 +13509,17 @@
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>Mistyped invitee address is recoverable</t>
+          <t>A wrong code says one calm thing</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>Mint a code with a deliberately wrong email, then use 'Wrong address? Start again' and mint a fresh one with the right address.</t>
+          <t>Try a made-up code, then a code meant for a different address, then the same code twice.</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>The new code works and the old one does not. Nothing had to be deleted to recover, and no address is ever displayed back to you.</t>
+          <t>Every one gives the SAME single line ('That code isn't valid.'). Nothing hints at which reason, so a guesser learns nothing. Repeated wrong tries eventually ask you to have a break.</t>
         </is>
       </c>
       <c r="G320" s="7" t="inlineStr">
@@ -13534,7 +13534,7 @@
     <row r="321">
       <c r="A321" s="6" t="inlineStr">
         <is>
-          <t>OUR-08</t>
+          <t>OUR-07</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -13549,17 +13549,17 @@
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Rename the list, and both sides see it</t>
+          <t>Mistyped invitee address is recoverable</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>On the shared list, tap the list's name, type a new one, and confirm. Reopen Ours on the other account.</t>
+          <t>Mint a code with a deliberately wrong email, then use 'Wrong address? Start again' and mint a fresh one with the right address.</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>Both people see the new name. An emptied name falls back to the app's own word, in each person's own language.</t>
+          <t>The new code works and the old one does not. Nothing had to be deleted to recover, and no address is ever displayed back to you.</t>
         </is>
       </c>
       <c r="G321" s="7" t="inlineStr">
@@ -13574,7 +13574,7 @@
     <row r="322">
       <c r="A322" s="6" t="inlineStr">
         <is>
-          <t>OUR-09</t>
+          <t>OUR-08</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -13582,24 +13582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C322" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C322" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>Leaving freezes and takes nothing</t>
+          <t>Rename the list, and both sides see it</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>On one account, Leave this list. Then open Ours on BOTH accounts.</t>
+          <t>On the shared list, tap the list's name, type a new one, and confirm. Reopen Ours on the other account.</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>Both see 'This list is closed' and can still read everything. Nothing was deleted from either side. Neither person is told off, and neither is told what the other did.</t>
+          <t>Both people see the new name. An emptied name falls back to the app's own word, in each person's own language.</t>
         </is>
       </c>
       <c r="G322" s="7" t="inlineStr">
@@ -13614,7 +13614,7 @@
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
         <is>
-          <t>OUR-10</t>
+          <t>OUR-09</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -13622,24 +13622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C323" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C323" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
-          <t>Remove a closed list from your side only</t>
+          <t>Leaving freezes and takes nothing</t>
         </is>
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Remove this list'. Then check the other account.</t>
+          <t>On one account, Leave this list. Then open Ours on BOTH accounts.</t>
         </is>
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>It disappears for you. The other person still has their copy and is not notified.</t>
+          <t>Both see 'This list is closed' and can still read everything. Nothing was deleted from either side. Neither person is told off, and neither is told what the other did.</t>
         </is>
       </c>
       <c r="G323" s="7" t="inlineStr">
@@ -13654,7 +13654,7 @@
     <row r="324">
       <c r="A324" s="6" t="inlineStr">
         <is>
-          <t>OUR-11</t>
+          <t>OUR-10</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -13662,24 +13662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C324" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C324" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>Nothing anywhere attributes a task to a person</t>
+          <t>Remove a closed list from your side only</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>With a shared list live, look at Ours, Today, the Lookback and Settings on both accounts.</t>
+          <t>On a closed list, tap 'Remove this list'. Then check the other account.</t>
         </is>
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>No initials, no 'done by', no counts of who did what, no progress bar across two people, no activity feed. The data to build one does not exist.</t>
+          <t>It disappears for you. The other person still has their copy and is not notified.</t>
         </is>
       </c>
       <c r="G324" s="7" t="inlineStr">
@@ -13694,7 +13694,7 @@
     <row r="325">
       <c r="A325" s="6" t="inlineStr">
         <is>
-          <t>OUR-13</t>
+          <t>OUR-11</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -13709,17 +13709,17 @@
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>The code stays on screen from the moment it is minted</t>
+          <t>Nothing anywhere attributes a task to a person</t>
         </is>
       </c>
       <c r="E325" s="9" t="inlineStr">
         <is>
-          <t>On a throttled connection (devtools, slow 3G), fill the create form and tap the code button.</t>
+          <t>With a shared list live, look at Ours, Today, the Lookback and Settings on both accounts.</t>
         </is>
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>The six characters appear as soon as the button stops spinning and are NEVER replaced by the intro screen. The server returns that code exactly once, so a flash back to 'Start a shared list' loses it for good.</t>
+          <t>No initials, no 'done by', no counts of who did what, no progress bar across two people, no activity feed. The data to build one does not exist.</t>
         </is>
       </c>
       <c r="G325" s="7" t="inlineStr">
@@ -13734,7 +13734,7 @@
     <row r="326">
       <c r="A326" s="6" t="inlineStr">
         <is>
-          <t>OUR-14</t>
+          <t>OUR-13</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -13749,17 +13749,17 @@
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
-          <t>'Get a new code' reaches the form and mints a different code</t>
+          <t>The code stays on screen from the moment it is minted</t>
         </is>
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>From the waiting screen, tap the get-a-new-code action. Change the email. Submit.</t>
+          <t>On a throttled connection (devtools, slow 3G), fill the create form and tap the code button.</t>
         </is>
       </c>
       <c r="F326" s="9" t="inlineStr">
         <is>
-          <t>The create form appears with your name and list name already filled. Submitting shows a DIFFERENT six characters, and the old one no longer works. Your chosen name is unchanged afterwards.</t>
+          <t>The six characters appear as soon as the button stops spinning and are NEVER replaced by the intro screen. The server returns that code exactly once, so a flash back to 'Start a shared list' loses it for good.</t>
         </is>
       </c>
       <c r="G326" s="7" t="inlineStr">
@@ -13774,7 +13774,7 @@
     <row r="327">
       <c r="A327" s="6" t="inlineStr">
         <is>
-          <t>OUR-120</t>
+          <t>OUR-14</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -13789,17 +13789,17 @@
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>Waiting-with-no-code is reachable, says so, and the re-mint is a real button</t>
+          <t>'Get a new code' reaches the form and mints a different code</t>
         </is>
       </c>
       <c r="E327" s="9" t="inlineStr">
         <is>
-          <t>Mint a code, leave Ours entirely (back to Today), then come back via the MENU's Ours row before anyone joins.</t>
+          <t>From the waiting screen, tap the get-a-new-code action. Change the email. Submit.</t>
         </is>
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>The Menu lands on the shared LIST (usable solo while waiting), and the list's header line reads 'Waiting for your person - Get a new code' where 'Kept with {name}' will later sit; tapping it opens the pairing screen (both Melroy's C6 check and the field report hit this as a dead end before 2026-09-20). That screen is titled 'Waiting for your person', NOT 'Read this to your person' over an empty space (the code renders exactly once; the server keeps only a hash, so it can never be re-shown), and 'Get a new code' is a full primary button there, not a quiet text link. While the code IS still on screen, the old title and quiet link stay as they were.</t>
+          <t>The create form appears with your name and list name already filled. Submitting shows a DIFFERENT six characters, and the old one no longer works. Your chosen name is unchanged afterwards.</t>
         </is>
       </c>
       <c r="G327" s="7" t="inlineStr">
@@ -13814,7 +13814,7 @@
     <row r="328">
       <c r="A328" s="6" t="inlineStr">
         <is>
-          <t>OUR-121</t>
+          <t>OUR-120</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -13829,17 +13829,17 @@
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>Whose email, and which code goes where</t>
+          <t>Waiting-with-no-code is reachable, says so, and the re-mint is a real button</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>Signed out: read the Menu's Ours line, open Ours, read the signed-out screen, tap Sign in and read the field. Then, on the sign-in code step, paste an Ours-style code (letters in it). Separately, signed in, open Ours 'I have a code' and type a 6-digit emailed sign-in code.</t>
+          <t>Mint a code, leave Ours entirely (back to Today), then come back via the MENU's Ours row before anyone joins.</t>
         </is>
       </c>
       <c r="F328" s="9" t="inlineStr">
         <is>
-          <t>The Menu's Ours line reads 'A list kept with one person. Sign in first.' (the old 'Needs your email, no password' invited typing the PARTNER'S email; a real user did exactly that on 2026-09-13 and it became their account). The Ours signed-out screen opens with the plain fact 'You're not signed in on this phone.' The sign-in email field is labelled 'Your own email', and the subtitle says sharing happens later, in Ours, with a code, never by typing the partner's email here. Letters in the 6-digit code field draw the calm hint that it will be an Ours invite code (a hint, never an auto-redirect or a cleared field). Six bare digits failing in the Ours join field add one line naming the emailed sign-in code as the likely mix-up, alongside the unchanged honest failure.</t>
+          <t>The Menu lands on the shared LIST (usable solo while waiting), and the list's header line reads 'Waiting for your person - Get a new code' where 'Kept with {name}' will later sit; tapping it opens the pairing screen (both Melroy's C6 check and the field report hit this as a dead end before 2026-09-20). That screen is titled 'Waiting for your person', NOT 'Read this to your person' over an empty space (the code renders exactly once; the server keeps only a hash, so it can never be re-shown), and 'Get a new code' is a full primary button there, not a quiet text link. While the code IS still on screen, the old title and quiet link stay as they were.</t>
         </is>
       </c>
       <c r="G328" s="7" t="inlineStr">
@@ -13854,7 +13854,7 @@
     <row r="329">
       <c r="A329" s="6" t="inlineStr">
         <is>
-          <t>OUR-15</t>
+          <t>OUR-121</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -13869,17 +13869,17 @@
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>Leave a list, then start a new one WITHOUT deleting the old</t>
+          <t>Whose email, and which code goes where</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>Leave a shared list. On the closed screen, start a new shared list with someone else.</t>
+          <t>Signed out: read the Menu's Ours line, open Ours, read the signed-out screen, tap Sign in and read the field. Then, on the sign-in code step, paste an Ours-style code (letters in it). Separately, signed in, open Ours 'I have a code' and type a 6-digit emailed sign-in code.</t>
         </is>
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>Starting a new list is offered on the closed screen itself and works. The old list is NOT deleted and is still readable. At no point is destroying it the only way forward.</t>
+          <t>The Menu's Ours line reads 'A list kept with one person. Sign in first.' (the old 'Needs your email, no password' invited typing the PARTNER'S email; a real user did exactly that on 2026-09-13 and it became their account). The Ours signed-out screen opens with the plain fact 'You're not signed in on this phone.' The sign-in email field is labelled 'Your own email', and the subtitle says sharing happens later, in Ours, with a code, never by typing the partner's email here. Letters in the 6-digit code field draw the calm hint that it will be an Ours invite code (a hint, never an auto-redirect or a cleared field). Six bare digits failing in the Ours join field add one line naming the emailed sign-in code as the likely mix-up, alongside the unchanged honest failure.</t>
         </is>
       </c>
       <c r="G329" s="7" t="inlineStr">
@@ -13894,7 +13894,7 @@
     <row r="330">
       <c r="A330" s="6" t="inlineStr">
         <is>
-          <t>OUR-16</t>
+          <t>OUR-15</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -13909,17 +13909,17 @@
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>A failed read never offers to start a list you already have</t>
+          <t>Leave a list, then start a new one WITHOUT deleting the old</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, turn the network off and open Ours.</t>
+          <t>Leave a shared list. On the closed screen, start a new shared list with someone else.</t>
         </is>
       </c>
       <c r="F330" s="9" t="inlineStr">
         <is>
-          <t>A calm connection line. The screen never says you have no shared list and never offers to start one. Turning the network back on recovers without a restart.</t>
+          <t>Starting a new list is offered on the closed screen itself and works. The old list is NOT deleted and is still readable. At no point is destroying it the only way forward.</t>
         </is>
       </c>
       <c r="G330" s="7" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="331">
       <c r="A331" s="6" t="inlineStr">
         <is>
-          <t>OUR-17</t>
+          <t>OUR-16</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -13942,24 +13942,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C331" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C331" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D331" s="9" t="inlineStr">
         <is>
-          <t>A list nobody joined can be left</t>
+          <t>A failed read never offers to start a list you already have</t>
         </is>
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>Create a list, get a code, give it to nobody. Return to Ours.</t>
+          <t>With a live shared list, turn the network off and open Ours.</t>
         </is>
       </c>
       <c r="F331" s="9" t="inlineStr">
         <is>
-          <t>There is a way out on the waiting screen, and its wording does not claim it closes for two people. After leaving, you can start or join a list again.</t>
+          <t>A calm connection line. The screen never says you have no shared list and never offers to start one. Turning the network back on recovers without a restart.</t>
         </is>
       </c>
       <c r="G331" s="7" t="inlineStr">
@@ -13974,7 +13974,7 @@
     <row r="332">
       <c r="A332" s="6" t="inlineStr">
         <is>
-          <t>OUR-18</t>
+          <t>OUR-17</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -13989,17 +13989,17 @@
       </c>
       <c r="D332" s="9" t="inlineStr">
         <is>
-          <t>The arrival announces once and stays announced</t>
+          <t>A list nobody joined can be left</t>
         </is>
       </c>
       <c r="E332" s="9" t="inlineStr">
         <is>
-          <t>Sit on the waiting screen while the other account joins. Background the app and return.</t>
+          <t>Create a list, get a code, give it to nobody. Return to Ours.</t>
         </is>
       </c>
       <c r="F332" s="9" t="inlineStr">
         <is>
-          <t>The name appears once and does not flicker back to waiting and re-announce. The way out beside it ('that wasn't who I meant') never appears on a list you did not just gain a person on.</t>
+          <t>There is a way out on the waiting screen, and its wording does not claim it closes for two people. After leaving, you can start or join a list again.</t>
         </is>
       </c>
       <c r="G332" s="7" t="inlineStr">
@@ -14014,7 +14014,7 @@
     <row r="333">
       <c r="A333" s="6" t="inlineStr">
         <is>
-          <t>OUR-19</t>
+          <t>OUR-18</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -14029,17 +14029,17 @@
       </c>
       <c r="D333" s="9" t="inlineStr">
         <is>
-          <t>A repeat the app cannot read is SHOWN, never hidden</t>
+          <t>The arrival announces once and stays announced</t>
         </is>
       </c>
       <c r="E333" s="9" t="inlineStr">
         <is>
-          <t>Requires two app versions. On the newer one, set a shared task to a cadence the older build does not have. Open the list on the older build.</t>
+          <t>Sit on the waiting screen while the other account joins. Background the app and return.</t>
         </is>
       </c>
       <c r="F333" s="9" t="inlineStr">
         <is>
-          <t>The task is visible on both, with whatever cadence line the newer app left. It is never silently absent from one person's list, and the older app does not erase the schedule when it syncs.</t>
+          <t>The name appears once and does not flicker back to waiting and re-announce. The way out beside it ('that wasn't who I meant') never appears on a list you did not just gain a person on.</t>
         </is>
       </c>
       <c r="G333" s="7" t="inlineStr">
@@ -14054,7 +14054,7 @@
     <row r="334">
       <c r="A334" s="6" t="inlineStr">
         <is>
-          <t>OUR-20</t>
+          <t>OUR-19</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -14062,24 +14062,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C334" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C334" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D334" s="9" t="inlineStr">
         <is>
-          <t>The room opens from Today's heading and from the Menu</t>
+          <t>A repeat the app cannot read is SHOWN, never hidden</t>
         </is>
       </c>
       <c r="E334" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, tap the list's name beside 'Today' in Today's heading. Then go back and reach it through Menu › Ours.</t>
+          <t>Requires two app versions. On the newer one, set a shared task to a cadence the older build does not have. Open the list on the older build.</t>
         </is>
       </c>
       <c r="F334" s="9" t="inlineStr">
         <is>
-          <t>Both land on the shared list itself, not the pairing screen, with a fade (a tab changing), not a sideways slide. The room's heading reads 'Today' and the list's name side by side, the name underlined as the current one, then the line 'Shared. Anything with a day reaches both your Todays on that day.' The date and the same Menu pill sit above it. 'Kept with {their name} ›' still goes to the pairing/management screen. Tapping 'Today' in the room's heading goes back to Today.</t>
+          <t>The task is visible on both, with whatever cadence line the newer app left. It is never silently absent from one person's list, and the older app does not erase the schedule when it syncs.</t>
         </is>
       </c>
       <c r="G334" s="7" t="inlineStr">
@@ -14094,7 +14094,7 @@
     <row r="335">
       <c r="A335" s="6" t="inlineStr">
         <is>
-          <t>OUR-21</t>
+          <t>OUR-20</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -14109,17 +14109,17 @@
       </c>
       <c r="D335" s="9" t="inlineStr">
         <is>
-          <t>Add, tick and UN-tick on the shared list</t>
+          <t>The room opens from Today's heading and from the Menu</t>
         </is>
       </c>
       <c r="E335" s="9" t="inlineStr">
         <is>
-          <t>Add a task in the room. Tick it. Un-tick it. Watch the other account (reload or wait ~15s).</t>
+          <t>With a live shared list, tap the list's name beside 'Today' in Today's heading. Then go back and reach it through Menu › Ours.</t>
         </is>
       </c>
       <c r="F335" s="9" t="inlineStr">
         <is>
-          <t>Every step appears on both. Un-ticking works as easily as ticking, on both sides. No affirmation or celebration fires on Ours.</t>
+          <t>Both land on the shared list itself, not the pairing screen, with a fade (a tab changing), not a sideways slide. The room's heading reads 'Today' and the list's name side by side, the name underlined as the current one, then the line 'Shared. Anything with a day reaches both your Todays on that day.' The date and the same Menu pill sit above it. 'Kept with {their name} ›' still goes to the pairing/management screen. Tapping 'Today' in the room's heading goes back to Today.</t>
         </is>
       </c>
       <c r="G335" s="7" t="inlineStr">
@@ -14134,7 +14134,7 @@
     <row r="336">
       <c r="A336" s="6" t="inlineStr">
         <is>
-          <t>OUR-22</t>
+          <t>OUR-21</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -14149,17 +14149,17 @@
       </c>
       <c r="D336" s="9" t="inlineStr">
         <is>
-          <t>Un-tick a one-off the DAY AFTER it was ticked</t>
+          <t>Add, tick and UN-tick on the shared list</t>
         </is>
       </c>
       <c r="E336" s="9" t="inlineStr">
         <is>
-          <t>Tick a shared one-off. Change the device date to tomorrow (or wait a day), reopen the room, tap it again.</t>
+          <t>Add a task in the room. Tick it. Un-tick it. Watch the other account (reload or wait ~15s).</t>
         </is>
       </c>
       <c r="F336" s="9" t="inlineStr">
         <is>
-          <t>It un-ticks. (The pre-fix build could never un-tick it again, on any device, forever.)</t>
+          <t>Every step appears on both. Un-ticking works as easily as ticking, on both sides. No affirmation or celebration fires on Ours.</t>
         </is>
       </c>
       <c r="G336" s="7" t="inlineStr">
@@ -14174,7 +14174,7 @@
     <row r="337">
       <c r="A337" s="6" t="inlineStr">
         <is>
-          <t>OUR-23</t>
+          <t>OUR-22</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -14189,17 +14189,17 @@
       </c>
       <c r="D337" s="9" t="inlineStr">
         <is>
-          <t>Bring to my Today makes a COPY, and marks only yours</t>
+          <t>Un-tick a one-off the DAY AFTER it was ticked</t>
         </is>
       </c>
       <c r="E337" s="9" t="inlineStr">
         <is>
-          <t>Hold a shared row, tap 'Bring to my Today'. Look at your Today, then at the shared list on BOTH accounts.</t>
+          <t>Tick a shared one-off. Change the device date to tomorrow (or wait a day), reopen the room, tap it again.</t>
         </is>
       </c>
       <c r="F337" s="9" t="inlineStr">
         <is>
-          <t>Your Today shows the task with a faint '· Ours'. The shared row is completely unchanged on both sides, with no marker of any kind. The held card now reads 'Already on your Today' and cannot make a second copy.</t>
+          <t>It un-ticks. (The pre-fix build could never un-tick it again, on any device, forever.)</t>
         </is>
       </c>
       <c r="G337" s="7" t="inlineStr">
@@ -14214,7 +14214,7 @@
     <row r="338">
       <c r="A338" s="6" t="inlineStr">
         <is>
-          <t>OUR-24</t>
+          <t>OUR-23</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -14229,17 +14229,17 @@
       </c>
       <c r="D338" s="9" t="inlineStr">
         <is>
-          <t>Your tick on the copy closes both</t>
+          <t>Bring to my Today makes a COPY, and marks only yours</t>
         </is>
       </c>
       <c r="E338" s="9" t="inlineStr">
         <is>
-          <t>Tick the brought copy on your Today. Check the shared list on the other account.</t>
+          <t>Hold a shared row, tap 'Bring to my Today'. Look at your Today, then at the shared list on BOTH accounts.</t>
         </is>
       </c>
       <c r="F338" s="9" t="inlineStr">
         <is>
-          <t>The shared row is done. It enters YOUR Lookback. Nothing on the other side says who did it.</t>
+          <t>Your Today shows the task with a faint '· Ours'. The shared row is completely unchanged on both sides, with no marker of any kind. The held card now reads 'Already on your Today' and cannot make a second copy.</t>
         </is>
       </c>
       <c r="G338" s="7" t="inlineStr">
@@ -14254,7 +14254,7 @@
     <row r="339">
       <c r="A339" s="6" t="inlineStr">
         <is>
-          <t>OUR-25</t>
+          <t>OUR-24</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -14269,17 +14269,17 @@
       </c>
       <c r="D339" s="9" t="inlineStr">
         <is>
-          <t>Ticking a brought copy on a device that has NEVER opened the room</t>
+          <t>Your tick on the copy closes both</t>
         </is>
       </c>
       <c r="E339" s="9" t="inlineStr">
         <is>
-          <t>Bring a task over on phone A. Sign in on a second device (or clear its local data) and go straight to Today WITHOUT opening Ours. Tick the copy there.</t>
+          <t>Tick the brought copy on your Today. Check the shared list on the other account.</t>
         </is>
       </c>
       <c r="F339" s="9" t="inlineStr">
         <is>
-          <t>The shared row closes. (The pre-fix build silently discarded the tick with no error.)</t>
+          <t>The shared row is done. It enters YOUR Lookback. Nothing on the other side says who did it.</t>
         </is>
       </c>
       <c r="G339" s="7" t="inlineStr">
@@ -14294,7 +14294,7 @@
     <row r="340">
       <c r="A340" s="6" t="inlineStr">
         <is>
-          <t>OUR-26</t>
+          <t>OUR-25</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -14309,17 +14309,17 @@
       </c>
       <c r="D340" s="9" t="inlineStr">
         <is>
-          <t>Their tick leaves a rest-note, never a strike-through</t>
+          <t>Ticking a brought copy on a device that has NEVER opened the room</t>
         </is>
       </c>
       <c r="E340" s="9" t="inlineStr">
         <is>
-          <t>Bring a task over. On the OTHER account, tick the shared row. Return to your Today.</t>
+          <t>Bring a task over on phone A. Sign in on a second device (or clear its local data) and go straight to Today WITHOUT opening Ours. Tick the copy there.</t>
         </is>
       </c>
       <c r="F340" s="9" t="inlineStr">
         <is>
-          <t>Your copy is gone from the day, replaced by a dashed sage line: 'Handled on Ours. It's off your day.' It is NOT struck through and does NOT appear in your Lookback. Leaving Today and coming back clears the note.</t>
+          <t>The shared row closes. (The pre-fix build silently discarded the tick with no error.)</t>
         </is>
       </c>
       <c r="G340" s="7" t="inlineStr">
@@ -14334,7 +14334,7 @@
     <row r="341">
       <c r="A341" s="6" t="inlineStr">
         <is>
-          <t>OUR-27</t>
+          <t>OUR-26</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -14342,24 +14342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C341" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C341" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D341" s="9" t="inlineStr">
         <is>
-          <t>Share to Ours warns about the length BEFORE it copies</t>
+          <t>Their tick leaves a rest-note, never a strike-through</t>
         </is>
       </c>
       <c r="E341" s="9" t="inlineStr">
         <is>
-          <t>Hold one of your own Today tasks with a very long title (500+ chars), open More, tap 'Share to Ours'.</t>
+          <t>Bring a task over. On the OTHER account, tick the shared row. Return to your Today.</t>
         </is>
       </c>
       <c r="F341" s="9" t="inlineStr">
         <is>
-          <t>A line says Ours keeps titles shorter and this one will be trimmed, BEFORE the copy is made. The copy appears on the shared list. 'Share to Ours' is absent entirely when there is no live list.</t>
+          <t>Your copy is gone from the day, replaced by a dashed sage line: 'Handled on Ours. It's off your day.' It is NOT struck through and does NOT appear in your Lookback. Leaving Today and coming back clears the note.</t>
         </is>
       </c>
       <c r="G341" s="7" t="inlineStr">
@@ -14374,7 +14374,7 @@
     <row r="342">
       <c r="A342" s="6" t="inlineStr">
         <is>
-          <t>OUR-28</t>
+          <t>OUR-27</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -14382,24 +14382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C342" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C342" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>A repeat set on Ours uses the SAME cadence sheet as home</t>
+          <t>Share to Ours warns about the length BEFORE it copies</t>
         </is>
       </c>
       <c r="E342" s="9" t="inlineStr">
         <is>
-          <t>Hold a shared row, tap 'Repeat…'. Compare with Menu › Repeating › Edit on a personal task.</t>
+          <t>Hold one of your own Today tasks with a very long title (500+ chars), open More, tap 'Share to Ours'.</t>
         </is>
       </c>
       <c r="F342" s="9" t="inlineStr">
         <is>
-          <t>Identical controls. The commit button NAMES the cadence ('Every day', 'Every 2 days'), on both. The Ours sheet adds one line: 'You'll both see it on its day.' It appears on its days for both people.</t>
+          <t>A line says Ours keeps titles shorter and this one will be trimmed, BEFORE the copy is made. The copy appears on the shared list. 'Share to Ours' is absent entirely when there is no live list.</t>
         </is>
       </c>
       <c r="G342" s="7" t="inlineStr">
@@ -14414,7 +14414,7 @@
     <row r="343">
       <c r="A343" s="6" t="inlineStr">
         <is>
-          <t>OUR-29</t>
+          <t>OUR-28</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -14429,17 +14429,17 @@
       </c>
       <c r="D343" s="9" t="inlineStr">
         <is>
-          <t>A cadence this build cannot read is inert, and says why</t>
+          <t>A repeat set on Ours uses the SAME cadence sheet as home</t>
         </is>
       </c>
       <c r="E343" s="9" t="inlineStr">
         <is>
-          <t>Get a shared row carrying a recurrence this build does not understand (a newer build, or hand-write one via the API).</t>
+          <t>Hold a shared row, tap 'Repeat…'. Compare with Menu › Repeating › Edit on a personal task.</t>
         </is>
       </c>
       <c r="F343" s="9" t="inlineStr">
         <is>
-          <t>The row is SHOWN, never hidden. Tapping it does nothing and a line explains it is safe and will appear on its days after an update. 'Repeat…' is withheld. It never marks itself done.</t>
+          <t>Identical controls. The commit button NAMES the cadence ('Every day', 'Every 2 days'), on both. The Ours sheet adds one line: 'You'll both see it on its day.' It appears on its days for both people.</t>
         </is>
       </c>
       <c r="G343" s="7" t="inlineStr">
@@ -14454,7 +14454,7 @@
     <row r="344">
       <c r="A344" s="6" t="inlineStr">
         <is>
-          <t>OUR-30</t>
+          <t>OUR-29</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -14462,24 +14462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C344" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C344" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D344" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash marks what changed, and never your own edits</t>
+          <t>A cadence this build cannot read is inert, and says why</t>
         </is>
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>Have the other account add and change a few rows. Open the room. Then tick something yourself and reopen.</t>
+          <t>Get a shared row carrying a recurrence this build does not understand (a newer build, or hand-write one via the API).</t>
         </is>
       </c>
       <c r="F344" s="9" t="inlineStr">
         <is>
-          <t>Their changed rows carry a tint and a firmer border on arrival; a screen reader says 'changed since you last looked'. Your OWN edits are never washed. Leaving and returning clears it.</t>
+          <t>The row is SHOWN, never hidden. Tapping it does nothing and a line explains it is safe and will appear on its days after an update. 'Repeat…' is withheld. It never marks itself done.</t>
         </is>
       </c>
       <c r="G344" s="7" t="inlineStr">
@@ -14494,7 +14494,7 @@
     <row r="345">
       <c r="A345" s="6" t="inlineStr">
         <is>
-          <t>OUR-31</t>
+          <t>OUR-30</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -14509,17 +14509,17 @@
       </c>
       <c r="D345" s="9" t="inlineStr">
         <is>
-          <t>Recently removed puts a task back</t>
+          <t>The quiet wash marks what changed, and never your own edits</t>
         </is>
       </c>
       <c r="E345" s="9" t="inlineStr">
         <is>
-          <t>Remove a shared row. Scroll to the foot of the list.</t>
+          <t>Have the other account add and change a few rows. Open the room. Then tick something yourself and reopen.</t>
         </is>
       </c>
       <c r="F345" s="9" t="inlineStr">
         <is>
-          <t>It sits under 'Recently removed', dimmed, with 'Put it back'. Restoring returns it for both people. Nothing anywhere says which of you removed it.</t>
+          <t>Their changed rows carry a tint and a firmer border on arrival; a screen reader says 'changed since you last looked'. Your OWN edits are never washed. Leaving and returning clears it.</t>
         </is>
       </c>
       <c r="G345" s="7" t="inlineStr">
@@ -14534,7 +14534,7 @@
     <row r="346">
       <c r="A346" s="6" t="inlineStr">
         <is>
-          <t>OUR-32</t>
+          <t>OUR-31</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -14549,17 +14549,17 @@
       </c>
       <c r="D346" s="9" t="inlineStr">
         <is>
-          <t>Removing a shared REPEAT does not pretend to be 'Skip today'</t>
+          <t>Recently removed puts a task back</t>
         </is>
       </c>
       <c r="E346" s="9" t="inlineStr">
         <is>
-          <t>Hold a repeating shared row and look at the shelf.</t>
+          <t>Remove a shared row. Scroll to the foot of the list.</t>
         </is>
       </c>
       <c r="F346" s="9" t="inlineStr">
         <is>
-          <t>It reads 'Remove', not 'Skip today', and the spoken label names removing the repeat. (The shared list has no per-day skip; the pre-fix build promised one and deleted the series for both people.)</t>
+          <t>It sits under 'Recently removed', dimmed, with 'Put it back'. Restoring returns it for both people. Nothing anywhere says which of you removed it.</t>
         </is>
       </c>
       <c r="G346" s="7" t="inlineStr">
@@ -14574,7 +14574,7 @@
     <row r="347">
       <c r="A347" s="6" t="inlineStr">
         <is>
-          <t>OUR-33</t>
+          <t>OUR-32</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -14582,24 +14582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C347" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C347" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D347" s="9" t="inlineStr">
         <is>
-          <t>A closed list is still readable, and read-only</t>
+          <t>Removing a shared REPEAT does not pretend to be 'Skip today'</t>
         </is>
       </c>
       <c r="E347" s="9" t="inlineStr">
         <is>
-          <t>Leave a list. Open it from the archive on the pairing screen.</t>
+          <t>Hold a repeating shared row and look at the shelf.</t>
         </is>
       </c>
       <c r="F347" s="9" t="inlineStr">
         <is>
-          <t>Every row is readable. There is no + pill at all. Ticking, renaming, removing and re-cadencing all do nothing, and each row says why. Each row still offers taking a copy for yourself.</t>
+          <t>It reads 'Remove', not 'Skip today', and the spoken label names removing the repeat. (The shared list has no per-day skip; the pre-fix build promised one and deleted the series for both people.)</t>
         </is>
       </c>
       <c r="G347" s="7" t="inlineStr">
@@ -14614,7 +14614,7 @@
     <row r="348">
       <c r="A348" s="6" t="inlineStr">
         <is>
-          <t>OUR-34</t>
+          <t>OUR-33</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -14622,24 +14622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C348" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C348" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D348" s="9" t="inlineStr">
         <is>
-          <t>The archive lists closed lists, and puts them away</t>
+          <t>A closed list is still readable, and read-only</t>
         </is>
       </c>
       <c r="E348" s="9" t="inlineStr">
         <is>
-          <t>With at least one closed list, look under 'Lists you have kept' on the pairing screen.</t>
+          <t>Leave a list. Open it from the archive on the pairing screen.</t>
         </is>
       </c>
       <c r="F348" s="9" t="inlineStr">
         <is>
-          <t>Purpose and closed MONTH only, no counts of any kind. 'Put it away' hides it from the default view; 'Show the ones put away' brings it back. Nothing is deleted.</t>
+          <t>Every row is readable. There is no + pill at all. Ticking, renaming, removing and re-cadencing all do nothing, and each row says why. Each row still offers taking a copy for yourself.</t>
         </is>
       </c>
       <c r="G348" s="7" t="inlineStr">
@@ -14654,7 +14654,7 @@
     <row r="349">
       <c r="A349" s="6" t="inlineStr">
         <is>
-          <t>OUR-35</t>
+          <t>OUR-34</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -14662,24 +14662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C349" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C349" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D349" s="9" t="inlineStr">
         <is>
-          <t>Reopening together is a handshake, never unilateral</t>
+          <t>The archive lists closed lists, and puts them away</t>
         </is>
       </c>
       <c r="E349" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Reopen together…' on ONE side only and STAY on that screen, hands off. Read the code to the second account. On that side, tap 'Got a code from them? Enter it to reopen.' (under the reopen hint on the closed-list screen) and enter it. Repeat with the closed list being the ONLY closed list on both accounts.</t>
+          <t>With at least one closed list, look under 'Lists you have kept' on the pairing screen.</t>
         </is>
       </c>
       <c r="F349" s="9" t="inlineStr">
         <is>
-          <t>The offering side gets a code and nothing reopens yet. The other side has a named door to the join field and entering the code there reopens the list for both, with everything as it was. It is never asked which kind of code it is, and it works when the closed list on screen is the only one (the D2 'handshake purgatory', 2026-09-22). Within about ten seconds, with nothing touched, the offering side's screen changes on its own: the code is gone and the live list shows 'They used the code. The list is open again…'.</t>
+          <t>Purpose and closed MONTH only, no counts of any kind. 'Put it away' hides it from the default view; 'Show the ones put away' brings it back. Nothing is deleted.</t>
         </is>
       </c>
       <c r="G349" s="7" t="inlineStr">
@@ -14694,7 +14694,7 @@
     <row r="350">
       <c r="A350" s="6" t="inlineStr">
         <is>
-          <t>OUR-122</t>
+          <t>OUR-35</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -14702,24 +14702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C350" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C350" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D350" s="9" t="inlineStr">
         <is>
-          <t>Waiting screens look on their own, and 'Check now' is there for the impatient</t>
+          <t>Reopening together is a handshake, never unilateral</t>
         </is>
       </c>
       <c r="E350" s="9" t="inlineStr">
         <is>
-          <t>A: mint a pairing code and stay on that screen, hands off. B: join. Watch A. Then, on a closed list: A taps 'Reopen together…' and stays; B redeems. Watch A. Then, on either waiting screen, tap 'Check now'.</t>
+          <t>On a closed list, tap 'Reopen together…' on ONE side only and STAY on that screen, hands off. Read the code to the second account. On that side, tap 'Got a code from them? Enter it to reopen.' (under the reopen hint on the closed-list screen) and enter it. Repeat with the closed list being the ONLY closed list on both accounts.</t>
         </is>
       </c>
       <c r="F350" s="9" t="inlineStr">
         <is>
-          <t>Both times A's screen changes on its own within about ten seconds: the pairing wait becomes '{name} joined.', and the closed list becomes the live list with the 'They used the code' line and the spent code gone. 'Check now' sits under the waiting text and under a minted reopen code, and does the same immediately. Once A has opened the list, the pairing screen underneath stops looking (nothing to see by eye; the rule is focus AND foreground AND under 30 minutes).</t>
+          <t>The offering side gets a code and nothing reopens yet. The other side has a named door to the join field and entering the code there reopens the list for both, with everything as it was. It is never asked which kind of code it is, and it works when the closed list on screen is the only one (the D2 'handshake purgatory', 2026-09-22). Within about ten seconds, with nothing touched, the offering side's screen changes on its own: the code is gone and the live list shows 'They used the code. The list is open again…'.</t>
         </is>
       </c>
       <c r="G350" s="7" t="inlineStr">
@@ -14734,7 +14734,7 @@
     <row r="351">
       <c r="A351" s="6" t="inlineStr">
         <is>
-          <t>OUR-123</t>
+          <t>OUR-122</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -14742,24 +14742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C351" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C351" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D351" s="9" t="inlineStr">
         <is>
-          <t>The Ours card goes home rather than into a room</t>
+          <t>Waiting screens look on their own, and 'Check now' is there for the impatient</t>
         </is>
       </c>
       <c r="E351" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, open the Menu and tap Ours. Then open the Menu from the Ours tab and tap Ours again. Then, with no shared list yet (signed in), tap Ours from the Menu.</t>
+          <t>A: mint a pairing code and stay on that screen, hands off. B: join. Watch A. Then, on a closed list: A taps 'Reopen together…' and stays; B redeems. Watch A. Then, on either waiting screen, tap 'Check now'.</t>
         </is>
       </c>
       <c r="F351" s="9" t="inlineStr">
         <is>
-          <t>With a live list the contents page closes and you land on Today's Ours tab (the list's name underlined) in one short fade; back from there does not return to the contents page. From the Ours tab's own Menu, the Ours card simply goes back to it. With no list yet it opens the invite screen as a room: '‹ Menu' and the two-mugs picture as a band, then the invite screen as it was.</t>
+          <t>Both times A's screen changes on its own within about ten seconds: the pairing wait becomes '{name} joined.', and the closed list becomes the live list with the 'They used the code' line and the spent code gone. 'Check now' sits under the waiting text and under a minted reopen code, and does the same immediately. Once A has opened the list, the pairing screen underneath stops looking (nothing to see by eye; the rule is focus AND foreground AND under 30 minutes).</t>
         </is>
       </c>
       <c r="G351" s="7" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="352">
       <c r="A352" s="6" t="inlineStr">
         <is>
-          <t>OUR-124</t>
+          <t>OUR-123</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -14782,24 +14782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C352" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C352" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D352" s="9" t="inlineStr">
         <is>
-          <t>The room opens with your list's own name, in any language</t>
+          <t>The Ours card goes home rather than into a room</t>
         </is>
       </c>
       <c r="E352" s="9" t="inlineStr">
         <is>
-          <t>With a named shared list (e.g. 'Just us') and the app set to Italian (or German, Spanish, French), tap the list's name in Today's heading.</t>
+          <t>With a live shared list, open the Menu and tap Ours. Then open the Menu from the Ours tab and tap Ours again. Then, with no shared list yet (signed in), tap Ours from the Menu.</t>
         </is>
       </c>
       <c r="F352" s="9" t="inlineStr">
         <is>
-          <t>The room's heading shows your list's own name from the first frame, and the capture panel's heading reads 'Aggiungi a Just us'. It never shows the default ('La nostra lista') for a beat and then flips, which read as the app changing language. A list with no name shows the default in the app's language. The list's own name is shown as you typed it, in whatever language that was.</t>
+          <t>With a live list the contents page closes and you land on Today's Ours tab (the list's name underlined) in one short fade; back from there does not return to the contents page. From the Ours tab's own Menu, the Ours card simply goes back to it. With no list yet it opens the invite screen as a room: '‹ Menu' and the two-mugs picture as a band, then the invite screen as it was.</t>
         </is>
       </c>
       <c r="G352" s="7" t="inlineStr">
@@ -14814,7 +14814,7 @@
     <row r="353">
       <c r="A353" s="6" t="inlineStr">
         <is>
-          <t>OUR-36</t>
+          <t>OUR-124</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -14822,24 +14822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C353" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C353" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D353" s="9" t="inlineStr">
         <is>
-          <t>Delete for good commits when the screen closes, not on a timer</t>
+          <t>The room opens with your list's own name, in any language</t>
         </is>
       </c>
       <c r="E353" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
+          <t>With a named shared list (e.g. 'Just us') and the app set to Italian (or German, Spanish, French), tap the list's name in Today's heading.</t>
         </is>
       </c>
       <c r="F353" s="9" t="inlineStr">
         <is>
-          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
+          <t>The room's heading shows your list's own name from the first frame, and the capture panel's heading reads 'Aggiungi a Just us'. It never shows the default ('La nostra lista') for a beat and then flips, which read as the app changing language. A list with no name shows the default in the app's language. The list's own name is shown as you typed it, in whatever language that was.</t>
         </is>
       </c>
       <c r="G353" s="7" t="inlineStr">
@@ -14854,7 +14854,7 @@
     <row r="354">
       <c r="A354" s="6" t="inlineStr">
         <is>
-          <t>OUR-37</t>
+          <t>OUR-36</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -14862,24 +14862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C354" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C354" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D354" s="9" t="inlineStr">
         <is>
-          <t>Rename yourself, and only yourself</t>
+          <t>Delete for good commits when the screen closes, not on a timer</t>
         </is>
       </c>
       <c r="E354" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
+          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
         </is>
       </c>
       <c r="F354" s="9" t="inlineStr">
         <is>
-          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
+          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
         </is>
       </c>
       <c r="G354" s="7" t="inlineStr">
@@ -14894,7 +14894,7 @@
     <row r="355">
       <c r="A355" s="6" t="inlineStr">
         <is>
-          <t>OUR-38</t>
+          <t>OUR-37</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -14909,17 +14909,17 @@
       </c>
       <c r="D355" s="9" t="inlineStr">
         <is>
-          <t>A dropped signal never throws you out of the room</t>
+          <t>Rename yourself, and only yourself</t>
         </is>
       </c>
       <c r="E355" s="9" t="inlineStr">
         <is>
-          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
+          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
         </is>
       </c>
       <c r="F355" s="9" t="inlineStr">
         <is>
-          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
+          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
         </is>
       </c>
       <c r="G355" s="7" t="inlineStr">
@@ -14934,7 +14934,7 @@
     <row r="356">
       <c r="A356" s="6" t="inlineStr">
         <is>
-          <t>OUR-39</t>
+          <t>OUR-38</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -14942,24 +14942,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C356" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C356" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D356" s="9" t="inlineStr">
         <is>
-          <t>Report this list reaches us and tells nobody else</t>
+          <t>A dropped signal never throws you out of the room</t>
         </is>
       </c>
       <c r="E356" s="9" t="inlineStr">
         <is>
-          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
+          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
         </is>
       </c>
       <c r="F356" s="9" t="inlineStr">
         <is>
-          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
+          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
         </is>
       </c>
       <c r="G356" s="7" t="inlineStr">
@@ -14974,7 +14974,7 @@
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
         <is>
-          <t>OUR-40</t>
+          <t>OUR-39</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -14989,17 +14989,17 @@
       </c>
       <c r="D357" s="9" t="inlineStr">
         <is>
-          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
+          <t>Report this list reaches us and tells nobody else</t>
         </is>
       </c>
       <c r="E357" s="9" t="inlineStr">
         <is>
-          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
+          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
         </is>
       </c>
       <c r="F357" s="9" t="inlineStr">
         <is>
-          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
+          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
         </is>
       </c>
       <c r="G357" s="7" t="inlineStr">
@@ -15014,7 +15014,7 @@
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
         <is>
-          <t>OUR-41</t>
+          <t>OUR-40</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -15022,24 +15022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C358" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C358" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D358" s="9" t="inlineStr">
         <is>
-          <t>Leaving is the block, and needs no reason</t>
+          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
         </is>
       </c>
       <c r="E358" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap 'Leave this list'.</t>
+          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
         </is>
       </c>
       <c r="F358" s="9" t="inlineStr">
         <is>
-          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
+          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
         </is>
       </c>
       <c r="G358" s="7" t="inlineStr">
@@ -15054,12 +15054,12 @@
     <row r="359">
       <c r="A359" s="6" t="inlineStr">
         <is>
-          <t>LEG-05</t>
+          <t>OUR-41</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C359" s="10" t="inlineStr">
@@ -15069,17 +15069,17 @@
       </c>
       <c r="D359" s="9" t="inlineStr">
         <is>
-          <t>The shared-list clauses are in both copies of both documents</t>
+          <t>Leaving is the block, and needs no reason</t>
         </is>
       </c>
       <c r="E359" s="9" t="inlineStr">
         <is>
-          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
+          <t>On a live list, tap 'Leave this list'.</t>
         </is>
       </c>
       <c r="F359" s="9" t="inlineStr">
         <is>
-          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
+          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
         </is>
       </c>
       <c r="G359" s="7" t="inlineStr">
@@ -15094,32 +15094,32 @@
     <row r="360">
       <c r="A360" s="6" t="inlineStr">
         <is>
-          <t>OUR-42</t>
+          <t>LEG-05</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C360" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C360" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D360" s="9" t="inlineStr">
         <is>
-          <t>A change on one phone appears on the other WITHOUT touching it</t>
+          <t>The shared-list clauses are in both copies of both documents</t>
         </is>
       </c>
       <c r="E360" s="9" t="inlineStr">
         <is>
-          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
+          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
         </is>
       </c>
       <c r="F360" s="9" t="inlineStr">
         <is>
-          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
+          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
         </is>
       </c>
       <c r="G360" s="7" t="inlineStr">
@@ -15134,7 +15134,7 @@
     <row r="361">
       <c r="A361" s="6" t="inlineStr">
         <is>
-          <t>OUR-43</t>
+          <t>OUR-42</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
@@ -15149,17 +15149,17 @@
       </c>
       <c r="D361" s="9" t="inlineStr">
         <is>
-          <t>Opening your own list does not bounce you back</t>
+          <t>A change on one phone appears on the other WITHOUT touching it</t>
         </is>
       </c>
       <c r="E361" s="9" t="inlineStr">
         <is>
-          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
+          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
         </is>
       </c>
       <c r="F361" s="9" t="inlineStr">
         <is>
-          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
+          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
         </is>
       </c>
       <c r="G361" s="7" t="inlineStr">
@@ -15174,7 +15174,7 @@
     <row r="362">
       <c r="A362" s="6" t="inlineStr">
         <is>
-          <t>OUR-44</t>
+          <t>OUR-43</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -15182,24 +15182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C362" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C362" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D362" s="9" t="inlineStr">
         <is>
-          <t>The pairing screen offers a way INTO the list</t>
+          <t>Opening your own list does not bounce you back</t>
         </is>
       </c>
       <c r="E362" s="9" t="inlineStr">
         <is>
-          <t>Finish pairing, then look at the pairing screen.</t>
+          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
         </is>
       </c>
       <c r="F362" s="9" t="inlineStr">
         <is>
-          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
+          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
         </is>
       </c>
       <c r="G362" s="7" t="inlineStr">
@@ -15214,7 +15214,7 @@
     <row r="363">
       <c r="A363" s="6" t="inlineStr">
         <is>
-          <t>OUR-45</t>
+          <t>OUR-44</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -15229,17 +15229,17 @@
       </c>
       <c r="D363" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash appears and then takes itself away</t>
+          <t>The pairing screen offers a way INTO the list</t>
         </is>
       </c>
       <c r="E363" s="9" t="inlineStr">
         <is>
-          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
+          <t>Finish pairing, then look at the pairing screen.</t>
         </is>
       </c>
       <c r="F363" s="9" t="inlineStr">
         <is>
-          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
+          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
         </is>
       </c>
       <c r="G363" s="7" t="inlineStr">
@@ -15254,7 +15254,7 @@
     <row r="364">
       <c r="A364" s="6" t="inlineStr">
         <is>
-          <t>OUR-47</t>
+          <t>OUR-45</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -15262,24 +15262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C364" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C364" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D364" s="9" t="inlineStr">
         <is>
-          <t>Ours lives in Today's heading (Today v3)</t>
+          <t>The quiet wash appears and then takes itself away</t>
         </is>
       </c>
       <c r="E364" s="9" t="inlineStr">
         <is>
-          <t>With a live list, look at the top of Today. Then leave the list (or sign out) and look again. With a screen reader, move through the heading.</t>
+          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
         </is>
       </c>
       <c r="F364" s="9" t="inlineStr">
         <is>
-          <t>With a live list the heading reads 'Today' and the list's name side by side (its own name when it has one, else 'Ours'), 'Today' underlined as the current tab. With no live list there is only 'Today', and no empty space where Ours would be. A screen reader hears them as tabs, 'Today, selected' and '{name}'. The old Ours door card under the list is gone.</t>
+          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
         </is>
       </c>
       <c r="G364" s="7" t="inlineStr">
@@ -15294,7 +15294,7 @@
     <row r="365">
       <c r="A365" s="6" t="inlineStr">
         <is>
-          <t>OUR-48</t>
+          <t>OUR-47</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -15309,17 +15309,17 @@
       </c>
       <c r="D365" s="9" t="inlineStr">
         <is>
-          <t>Their tick marks your copy DONE and leaves it on your day</t>
+          <t>Ours lives in Today's heading (Today v3)</t>
         </is>
       </c>
       <c r="E365" s="9" t="inlineStr">
         <is>
-          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
+          <t>With a live list, look at the top of Today. Then leave the list (or sign out) and look again. With a screen reader, move through the heading.</t>
         </is>
       </c>
       <c r="F365" s="9" t="inlineStr">
         <is>
-          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
+          <t>With a live list the heading reads 'Today' and the list's name side by side (its own name when it has one, else 'Ours'), 'Today' underlined as the current tab. With no live list there is only 'Today', and no empty space where Ours would be. A screen reader hears them as tabs, 'Today, selected' and '{name}'. The old Ours door card under the list is gone.</t>
         </is>
       </c>
       <c r="G365" s="7" t="inlineStr">
@@ -15334,7 +15334,7 @@
     <row r="366">
       <c r="A366" s="6" t="inlineStr">
         <is>
-          <t>OUR-49</t>
+          <t>OUR-48</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -15349,17 +15349,17 @@
       </c>
       <c r="D366" s="9" t="inlineStr">
         <is>
-          <t>A settled copy carries a completion DATE, not just a done flag</t>
+          <t>Their tick marks your copy DONE and leaves it on your day</t>
         </is>
       </c>
       <c r="E366" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
+          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
         </is>
       </c>
       <c r="F366" s="9" t="inlineStr">
         <is>
-          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
+          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
         </is>
       </c>
       <c r="G366" s="7" t="inlineStr">
@@ -15374,7 +15374,7 @@
     <row r="367">
       <c r="A367" s="6" t="inlineStr">
         <is>
-          <t>OUR-50</t>
+          <t>OUR-49</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -15382,24 +15382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C367" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C367" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D367" s="9" t="inlineStr">
         <is>
-          <t>A finished copy can be brought over again</t>
+          <t>A settled copy carries a completion DATE, not just a done flag</t>
         </is>
       </c>
       <c r="E367" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, hold that row in Ours.</t>
+          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
         </is>
       </c>
       <c r="F367" s="9" t="inlineStr">
         <is>
-          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
+          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
         </is>
       </c>
       <c r="G367" s="7" t="inlineStr">
@@ -15414,7 +15414,7 @@
     <row r="368">
       <c r="A368" s="6" t="inlineStr">
         <is>
-          <t>OUR-51</t>
+          <t>OUR-50</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -15422,24 +15422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C368" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C368" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D368" s="9" t="inlineStr">
         <is>
-          <t>Your own edit never highlights; their later edit always does</t>
+          <t>A finished copy can be brought over again</t>
         </is>
       </c>
       <c r="E368" s="9" t="inlineStr">
         <is>
-          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
+          <t>After OUR-48, hold that row in Ours.</t>
         </is>
       </c>
       <c r="F368" s="9" t="inlineStr">
         <is>
-          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
+          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
         </is>
       </c>
       <c r="G368" s="7" t="inlineStr">
@@ -15454,7 +15454,7 @@
     <row r="369">
       <c r="A369" s="6" t="inlineStr">
         <is>
-          <t>OUR-52</t>
+          <t>OUR-51</t>
         </is>
       </c>
       <c r="B369" s="7" t="inlineStr">
@@ -15462,24 +15462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C369" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C369" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D369" s="9" t="inlineStr">
         <is>
-          <t>The highlight arrives at once and fades away</t>
+          <t>Your own edit never highlights; their later edit always does</t>
         </is>
       </c>
       <c r="E369" s="9" t="inlineStr">
         <is>
-          <t>Have B change a row while A is on the list.</t>
+          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
         </is>
       </c>
       <c r="F369" s="9" t="inlineStr">
         <is>
-          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
+          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
         </is>
       </c>
       <c r="G369" s="7" t="inlineStr">
@@ -15494,7 +15494,7 @@
     <row r="370">
       <c r="A370" s="6" t="inlineStr">
         <is>
-          <t>OUR-53</t>
+          <t>OUR-52</t>
         </is>
       </c>
       <c r="B370" s="7" t="inlineStr">
@@ -15509,17 +15509,17 @@
       </c>
       <c r="D370" s="9" t="inlineStr">
         <is>
-          <t>Two devices share ONE clock</t>
+          <t>The highlight arrives at once and fades away</t>
         </is>
       </c>
       <c r="E370" s="9" t="inlineStr">
         <is>
-          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
+          <t>Have B change a row while A is on the list.</t>
         </is>
       </c>
       <c r="F370" s="9" t="inlineStr">
         <is>
-          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
+          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
         </is>
       </c>
       <c r="G370" s="7" t="inlineStr">
@@ -15534,7 +15534,7 @@
     <row r="371">
       <c r="A371" s="6" t="inlineStr">
         <is>
-          <t>OUR-54</t>
+          <t>OUR-53</t>
         </is>
       </c>
       <c r="B371" s="7" t="inlineStr">
@@ -15542,24 +15542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C371" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C371" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D371" s="9" t="inlineStr">
         <is>
-          <t>The debug panel is opt-in and carries no task text</t>
+          <t>Two devices share ONE clock</t>
         </is>
       </c>
       <c r="E371" s="9" t="inlineStr">
         <is>
-          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
+          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
         </is>
       </c>
       <c r="F371" s="9" t="inlineStr">
         <is>
-          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
+          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
         </is>
       </c>
       <c r="G371" s="7" t="inlineStr">
@@ -15574,7 +15574,7 @@
     <row r="372">
       <c r="A372" s="6" t="inlineStr">
         <is>
-          <t>OUR-55</t>
+          <t>OUR-54</t>
         </is>
       </c>
       <c r="B372" s="7" t="inlineStr">
@@ -15582,24 +15582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C372" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C372" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D372" s="9" t="inlineStr">
         <is>
-          <t>Capture on Ours IS Today's capture</t>
+          <t>The debug panel is opt-in and carries no task text</t>
         </is>
       </c>
       <c r="E372" s="9" t="inlineStr">
         <is>
-          <t>Open a shared list and tap the + pill at the foot of the screen.</t>
+          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
         </is>
       </c>
       <c r="F372" s="9" t="inlineStr">
         <is>
-          <t>The same pill and the same panel Today has, headed 'Add to {name}': the same box, the same Speak button (web), the same When chip and door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
+          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
         </is>
       </c>
       <c r="G372" s="7" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="373">
       <c r="A373" s="6" t="inlineStr">
         <is>
-          <t>OUR-56</t>
+          <t>OUR-55</t>
         </is>
       </c>
       <c r="B373" s="7" t="inlineStr">
@@ -15629,17 +15629,17 @@
       </c>
       <c r="D373" s="9" t="inlineStr">
         <is>
-          <t>Repeating can be set AT capture, without knowing a gesture</t>
+          <t>Capture on Ours IS Today's capture</t>
         </is>
       </c>
       <c r="E373" s="9" t="inlineStr">
         <is>
-          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
+          <t>Open a shared list and tap the + pill at the foot of the screen.</t>
         </is>
       </c>
       <c r="F373" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
+          <t>The same pill and the same panel Today has, headed 'Add to {name}': the same box, the same Speak button (web), the same When chip and door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
         </is>
       </c>
       <c r="G373" s="7" t="inlineStr">
@@ -15654,7 +15654,7 @@
     <row r="374">
       <c r="A374" s="6" t="inlineStr">
         <is>
-          <t>OUR-57</t>
+          <t>OUR-56</t>
         </is>
       </c>
       <c r="B374" s="7" t="inlineStr">
@@ -15662,24 +15662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C374" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C374" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D374" s="9" t="inlineStr">
         <is>
-          <t>A dump becomes several shared rows, in the order typed</t>
+          <t>Repeating can be set AT capture, without knowing a gesture</t>
         </is>
       </c>
       <c r="E374" s="9" t="inlineStr">
         <is>
-          <t>Type three lines into the Ours capture and Add.</t>
+          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
         </is>
       </c>
       <c r="F374" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
+          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
         </is>
       </c>
       <c r="G374" s="7" t="inlineStr">
@@ -15694,7 +15694,7 @@
     <row r="375">
       <c r="A375" s="6" t="inlineStr">
         <is>
-          <t>OUR-58</t>
+          <t>OUR-57</t>
         </is>
       </c>
       <c r="B375" s="7" t="inlineStr">
@@ -15702,24 +15702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C375" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C375" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D375" s="9" t="inlineStr">
         <is>
-          <t>The shared door offers When and Repeating, never Steps</t>
+          <t>A dump becomes several shared rows, in the order typed</t>
         </is>
       </c>
       <c r="E375" s="9" t="inlineStr">
         <is>
-          <t>Open the door on Ours and compare it with the door on Today.</t>
+          <t>Type three lines into the Ours capture and Add.</t>
         </is>
       </c>
       <c r="F375" s="9" t="inlineStr">
         <is>
-          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
+          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
         </is>
       </c>
       <c r="G375" s="7" t="inlineStr">
@@ -15734,7 +15734,7 @@
     <row r="376">
       <c r="A376" s="6" t="inlineStr">
         <is>
-          <t>OUR-59</t>
+          <t>OUR-58</t>
         </is>
       </c>
       <c r="B376" s="7" t="inlineStr">
@@ -15742,24 +15742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C376" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C376" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D376" s="9" t="inlineStr">
         <is>
-          <t>Typed text survives the panel going</t>
+          <t>The shared door offers When and Repeating, never Steps</t>
         </is>
       </c>
       <c r="E376" s="9" t="inlineStr">
         <is>
-          <t>Type half a sentence into the Ours panel, Close it, tick something, then tap the pill again.</t>
+          <t>Open the door on Ours and compare it with the door on Today.</t>
         </is>
       </c>
       <c r="F376" s="9" t="inlineStr">
         <is>
-          <t>The pill shows '+' and three dots while words wait, and the half sentence is still there. The panel is always mounted, never unmounted. Only an Add resets the door; the words never reset on their own.</t>
+          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
         </is>
       </c>
       <c r="G376" s="7" t="inlineStr">
@@ -15774,7 +15774,7 @@
     <row r="377">
       <c r="A377" s="6" t="inlineStr">
         <is>
-          <t>OUR-60</t>
+          <t>OUR-59</t>
         </is>
       </c>
       <c r="B377" s="7" t="inlineStr">
@@ -15789,22 +15789,22 @@
       </c>
       <c r="D377" s="9" t="inlineStr">
         <is>
-          <t>The Ours panel rides above the keyboard</t>
+          <t>Typed text survives the panel going</t>
         </is>
       </c>
       <c r="E377" s="9" t="inlineStr">
         <is>
-          <t>On a real Android device, tap the + pill on the Ours list, tap the box and start typing.</t>
+          <t>Type half a sentence into the Ours panel, Close it, tick something, then tap the pill again.</t>
         </is>
       </c>
       <c r="F377" s="9" t="inlineStr">
         <is>
-          <t>The panel and its Add button stay visible above the keyboard while you type. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
+          <t>The pill shows '+' and three dots while words wait, and the half sentence is still there. The panel is always mounted, never unmounted. Only an Add resets the door; the words never reset on their own.</t>
         </is>
       </c>
       <c r="G377" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H377" s="7" t="inlineStr"/>
@@ -15814,7 +15814,7 @@
     <row r="378">
       <c r="A378" s="6" t="inlineStr">
         <is>
-          <t>OUR-61</t>
+          <t>OUR-60</t>
         </is>
       </c>
       <c r="B378" s="7" t="inlineStr">
@@ -15822,29 +15822,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C378" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C378" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D378" s="9" t="inlineStr">
         <is>
-          <t>No AI on the shared capture</t>
+          <t>The Ours panel rides above the keyboard</t>
         </is>
       </c>
       <c r="E378" s="9" t="inlineStr">
         <is>
-          <t>Open the Ours capture panel with AI enabled in Settings, and type a long run-on line.</t>
+          <t>On a real Android device, tap the + pill on the Ours list, tap the box and start typing.</t>
         </is>
       </c>
       <c r="F378" s="9" t="inlineStr">
         <is>
-          <t>No 'Break it down', no 'Sort for me', and no 'Tidy this into tasks': steps or rewrites a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
+          <t>The panel and its Add button stay visible above the keyboard while you type. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
         </is>
       </c>
       <c r="G378" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H378" s="7" t="inlineStr"/>
@@ -15854,7 +15854,7 @@
     <row r="379">
       <c r="A379" s="6" t="inlineStr">
         <is>
-          <t>OUR-62</t>
+          <t>OUR-61</t>
         </is>
       </c>
       <c r="B379" s="7" t="inlineStr">
@@ -15862,29 +15862,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C379" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C379" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D379" s="9" t="inlineStr">
         <is>
-          <t>Scan (premium) reaches the shared capture</t>
+          <t>No AI on the shared capture</t>
         </is>
       </c>
       <c r="E379" s="9" t="inlineStr">
         <is>
-          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
+          <t>Open the Ours capture panel with AI enabled in Settings, and type a long run-on line.</t>
         </is>
       </c>
       <c r="F379" s="9" t="inlineStr">
         <is>
-          <t>The panel rises with the words IN its box (keyboard down), not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
+          <t>No 'Break it down', no 'Sort for me', and no 'Tidy this into tasks': steps or rewrites a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
         </is>
       </c>
       <c r="G379" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H379" s="7" t="inlineStr"/>
@@ -15894,7 +15894,7 @@
     <row r="380">
       <c r="A380" s="6" t="inlineStr">
         <is>
-          <t>OUR-63</t>
+          <t>OUR-62</t>
         </is>
       </c>
       <c r="B380" s="7" t="inlineStr">
@@ -15909,22 +15909,22 @@
       </c>
       <c r="D380" s="9" t="inlineStr">
         <is>
-          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
+          <t>Scan (premium) reaches the shared capture</t>
         </is>
       </c>
       <c r="E380" s="9" t="inlineStr">
         <is>
-          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
+          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
         </is>
       </c>
       <c r="F380" s="9" t="inlineStr">
         <is>
-          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
+          <t>The panel rises with the words IN its box (keyboard down), not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
         </is>
       </c>
       <c r="G380" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H380" s="7" t="inlineStr"/>
@@ -15934,7 +15934,7 @@
     <row r="381">
       <c r="A381" s="6" t="inlineStr">
         <is>
-          <t>OUR-64</t>
+          <t>OUR-63</t>
         </is>
       </c>
       <c r="B381" s="7" t="inlineStr">
@@ -15942,24 +15942,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C381" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C381" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D381" s="9" t="inlineStr">
         <is>
-          <t>The photo never reaches the shared list</t>
+          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
         </is>
       </c>
       <c r="E381" s="9" t="inlineStr">
         <is>
-          <t>Scan something into Ours and Add it. Check the other device.</t>
+          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
         </is>
       </c>
       <c r="F381" s="9" t="inlineStr">
         <is>
-          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
+          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
         </is>
       </c>
       <c r="G381" s="7" t="inlineStr">
@@ -15974,7 +15974,7 @@
     <row r="382">
       <c r="A382" s="6" t="inlineStr">
         <is>
-          <t>OUR-65</t>
+          <t>OUR-64</t>
         </is>
       </c>
       <c r="B382" s="7" t="inlineStr">
@@ -15982,24 +15982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C382" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C382" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D382" s="9" t="inlineStr">
         <is>
-          <t>Scan is absent when AI is off</t>
+          <t>The photo never reaches the shared list</t>
         </is>
       </c>
       <c r="E382" s="9" t="inlineStr">
         <is>
-          <t>Turn AI off in Settings, then open the Ours capture.</t>
+          <t>Scan something into Ours and Add it. Check the other device.</t>
         </is>
       </c>
       <c r="F382" s="9" t="inlineStr">
         <is>
-          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
+          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
         </is>
       </c>
       <c r="G382" s="7" t="inlineStr">
@@ -16014,7 +16014,7 @@
     <row r="383">
       <c r="A383" s="6" t="inlineStr">
         <is>
-          <t>OUR-66</t>
+          <t>OUR-65</t>
         </is>
       </c>
       <c r="B383" s="7" t="inlineStr">
@@ -16022,24 +16022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C383" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C383" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D383" s="9" t="inlineStr">
         <is>
-          <t>A repeating shared row appears on BOTH Todays on its day</t>
+          <t>Scan is absent when AI is off</t>
         </is>
       </c>
       <c r="E383" s="9" t="inlineStr">
         <is>
-          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
+          <t>Turn AI off in Settings, then open the Ours capture.</t>
         </is>
       </c>
       <c r="F383" s="9" t="inlineStr">
         <is>
-          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
+          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
         </is>
       </c>
       <c r="G383" s="7" t="inlineStr">
@@ -16054,7 +16054,7 @@
     <row r="384">
       <c r="A384" s="6" t="inlineStr">
         <is>
-          <t>OUR-67</t>
+          <t>OUR-66</t>
         </is>
       </c>
       <c r="B384" s="7" t="inlineStr">
@@ -16069,17 +16069,17 @@
       </c>
       <c r="D384" s="9" t="inlineStr">
         <is>
-          <t>An UNDATED shared row never reaches Today</t>
+          <t>A repeating shared row appears on BOTH Todays on its day</t>
         </is>
       </c>
       <c r="E384" s="9" t="inlineStr">
         <is>
-          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
+          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
         </is>
       </c>
       <c r="F384" s="9" t="inlineStr">
         <is>
-          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
+          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
         </is>
       </c>
       <c r="G384" s="7" t="inlineStr">
@@ -16094,7 +16094,7 @@
     <row r="385">
       <c r="A385" s="6" t="inlineStr">
         <is>
-          <t>OUR-68</t>
+          <t>OUR-67</t>
         </is>
       </c>
       <c r="B385" s="7" t="inlineStr">
@@ -16109,17 +16109,17 @@
       </c>
       <c r="D385" s="9" t="inlineStr">
         <is>
-          <t>Shared rows never make the day look heavier</t>
+          <t>An UNDATED shared row never reaches Today</t>
         </is>
       </c>
       <c r="E385" s="9" t="inlineStr">
         <is>
-          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
+          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
         </is>
       </c>
       <c r="F385" s="9" t="inlineStr">
         <is>
-          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
+          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
         </is>
       </c>
       <c r="G385" s="7" t="inlineStr">
@@ -16134,7 +16134,7 @@
     <row r="386">
       <c r="A386" s="6" t="inlineStr">
         <is>
-          <t>OUR-69</t>
+          <t>OUR-68</t>
         </is>
       </c>
       <c r="B386" s="7" t="inlineStr">
@@ -16149,17 +16149,17 @@
       </c>
       <c r="D386" s="9" t="inlineStr">
         <is>
-          <t>Ticking a shared row from Today closes it for both</t>
+          <t>Shared rows never make the day look heavier</t>
         </is>
       </c>
       <c r="E386" s="9" t="inlineStr">
         <is>
-          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
+          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
         </is>
       </c>
       <c r="F386" s="9" t="inlineStr">
         <is>
-          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
+          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
         </is>
       </c>
       <c r="G386" s="7" t="inlineStr">
@@ -16174,7 +16174,7 @@
     <row r="387">
       <c r="A387" s="6" t="inlineStr">
         <is>
-          <t>OUR-70</t>
+          <t>OUR-69</t>
         </is>
       </c>
       <c r="B387" s="7" t="inlineStr">
@@ -16182,24 +16182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C387" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C387" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D387" s="9" t="inlineStr">
         <is>
-          <t>A dated shared row shows from its day onward, never before</t>
+          <t>Ticking a shared row from Today closes it for both</t>
         </is>
       </c>
       <c r="E387" s="9" t="inlineStr">
         <is>
-          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
+          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
         </is>
       </c>
       <c r="F387" s="9" t="inlineStr">
         <is>
-          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
+          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
         </is>
       </c>
       <c r="G387" s="7" t="inlineStr">
@@ -16214,7 +16214,7 @@
     <row r="388">
       <c r="A388" s="6" t="inlineStr">
         <is>
-          <t>OUR-71</t>
+          <t>OUR-70</t>
         </is>
       </c>
       <c r="B388" s="7" t="inlineStr">
@@ -16222,24 +16222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C388" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C388" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D388" s="9" t="inlineStr">
         <is>
-          <t>The shared capture rests on Anytime, and says what a day means</t>
+          <t>A dated shared row shows from its day onward, never before</t>
         </is>
       </c>
       <c r="E388" s="9" t="inlineStr">
         <is>
-          <t>Tap the + pill on Ours and read the line beside the When chip. Open the door. Pick Today, then Tomorrow, then Daily, reading that line each time.</t>
+          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
         </is>
       </c>
       <c r="F388" s="9" t="inlineStr">
         <is>
-          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected, and the Add button says just 'Add'. Choosing Today makes it read 'Add · Today', because that is the notable case: it will appear on both your days. The line beside the chip says, in plain words, what the current choice means on a shared list (no day lives here; a day reaches both Todays; a rhythm repeats for both of you), before you add.</t>
+          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
         </is>
       </c>
       <c r="G388" s="7" t="inlineStr">
@@ -16254,7 +16254,7 @@
     <row r="389">
       <c r="A389" s="6" t="inlineStr">
         <is>
-          <t>OUR-112</t>
+          <t>OUR-71</t>
         </is>
       </c>
       <c r="B389" s="7" t="inlineStr">
@@ -16269,17 +16269,17 @@
       </c>
       <c r="D389" s="9" t="inlineStr">
         <is>
-          <t>A shared row's WHEN can be changed, and cleared</t>
+          <t>The shared capture rests on Anytime, and says what a day means</t>
         </is>
       </c>
       <c r="E389" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
+          <t>Tap the + pill on Ours and read the line beside the When chip. Open the door. Pick Today, then Tomorrow, then Daily, reading that line each time.</t>
         </is>
       </c>
       <c r="F389" s="9" t="inlineStr">
         <is>
-          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
+          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected, and the Add button says just 'Add'. Choosing Today makes it read 'Add · Today', because that is the notable case: it will appear on both your days. The line beside the chip says, in plain words, what the current choice means on a shared list (no day lives here; a day reaches both Todays; a rhythm repeats for both of you), before you add.</t>
         </is>
       </c>
       <c r="G389" s="7" t="inlineStr">
@@ -16294,7 +16294,7 @@
     <row r="390">
       <c r="A390" s="6" t="inlineStr">
         <is>
-          <t>OUR-113</t>
+          <t>OUR-112</t>
         </is>
       </c>
       <c r="B390" s="7" t="inlineStr">
@@ -16309,17 +16309,17 @@
       </c>
       <c r="D390" s="9" t="inlineStr">
         <is>
-          <t>Ending a rhythm does NOT mark the row done for both people</t>
+          <t>A shared row's WHEN can be changed, and cleared</t>
         </is>
       </c>
       <c r="E390" s="9" t="inlineStr">
         <is>
-          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
+          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
         </is>
       </c>
       <c r="F390" s="9" t="inlineStr">
         <is>
-          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
+          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
         </is>
       </c>
       <c r="G390" s="7" t="inlineStr">
@@ -16334,7 +16334,7 @@
     <row r="391">
       <c r="A391" s="6" t="inlineStr">
         <is>
-          <t>OUR-114</t>
+          <t>OUR-113</t>
         </is>
       </c>
       <c r="B391" s="7" t="inlineStr">
@@ -16342,24 +16342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C391" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C391" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D391" s="9" t="inlineStr">
         <is>
-          <t>The day zone changes its question when a rhythm is alive</t>
+          <t>Ending a rhythm does NOT mark the row done for both people</t>
         </is>
       </c>
       <c r="E391" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
+          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
         </is>
       </c>
       <c r="F391" s="9" t="inlineStr">
         <is>
-          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
+          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
         </is>
       </c>
       <c r="G391" s="7" t="inlineStr">
@@ -16374,7 +16374,7 @@
     <row r="392">
       <c r="A392" s="6" t="inlineStr">
         <is>
-          <t>OUR-115</t>
+          <t>OUR-114</t>
         </is>
       </c>
       <c r="B392" s="7" t="inlineStr">
@@ -16389,17 +16389,17 @@
       </c>
       <c r="D392" s="9" t="inlineStr">
         <is>
-          <t>Setting a shared row to Today actually reaches both Todays</t>
+          <t>The day zone changes its question when a rhythm is alive</t>
         </is>
       </c>
       <c r="E392" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
+          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
         </is>
       </c>
       <c r="F392" s="9" t="inlineStr">
         <is>
-          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
+          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
         </is>
       </c>
       <c r="G392" s="7" t="inlineStr">
@@ -16414,7 +16414,7 @@
     <row r="393">
       <c r="A393" s="6" t="inlineStr">
         <is>
-          <t>OUR-116</t>
+          <t>OUR-115</t>
         </is>
       </c>
       <c r="B393" s="7" t="inlineStr">
@@ -16422,24 +16422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C393" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C393" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D393" s="9" t="inlineStr">
         <is>
-          <t>An idle Set does not wash the row on the other device</t>
+          <t>Setting a shared row to Today actually reaches both Todays</t>
         </is>
       </c>
       <c r="E393" s="9" t="inlineStr">
         <is>
-          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
+          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
         </is>
       </c>
       <c r="F393" s="9" t="inlineStr">
         <is>
-          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
+          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
         </is>
       </c>
       <c r="G393" s="7" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="394">
       <c r="A394" s="6" t="inlineStr">
         <is>
-          <t>OUR-118</t>
+          <t>OUR-116</t>
         </is>
       </c>
       <c r="B394" s="7" t="inlineStr">
@@ -16462,24 +16462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C394" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C394" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D394" s="9" t="inlineStr">
         <is>
-          <t>A repeat you have already done today keeps its held card</t>
+          <t>An idle Set does not wash the row on the other device</t>
         </is>
       </c>
       <c r="E394" s="9" t="inlineStr">
         <is>
-          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
+          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
         </is>
       </c>
       <c r="F394" s="9" t="inlineStr">
         <is>
-          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
+          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
         </is>
       </c>
       <c r="G394" s="7" t="inlineStr">
@@ -16494,7 +16494,7 @@
     <row r="395">
       <c r="A395" s="6" t="inlineStr">
         <is>
-          <t>OUR-117</t>
+          <t>OUR-118</t>
         </is>
       </c>
       <c r="B395" s="7" t="inlineStr">
@@ -16502,24 +16502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C395" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C395" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D395" s="9" t="inlineStr">
         <is>
-          <t>The Repeating room's Edit sheet is untouched by the When editor</t>
+          <t>A repeat you have already done today keeps its held card</t>
         </is>
       </c>
       <c r="E395" s="9" t="inlineStr">
         <is>
-          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
+          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
         </is>
       </c>
       <c r="F395" s="9" t="inlineStr">
         <is>
-          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the Repeating room.</t>
+          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
         </is>
       </c>
       <c r="G395" s="7" t="inlineStr">
@@ -16534,7 +16534,7 @@
     <row r="396">
       <c r="A396" s="6" t="inlineStr">
         <is>
-          <t>OUR-119</t>
+          <t>OUR-117</t>
         </is>
       </c>
       <c r="B396" s="7" t="inlineStr">
@@ -16549,17 +16549,17 @@
       </c>
       <c r="D396" s="9" t="inlineStr">
         <is>
-          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
+          <t>The Repeating room's Edit sheet is untouched by the When editor</t>
         </is>
       </c>
       <c r="E396" s="9" t="inlineStr">
         <is>
-          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
+          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
         </is>
       </c>
       <c r="F396" s="9" t="inlineStr">
         <is>
-          <t>Monthly is the fourth rhythm chip here too, from the same sheet the Repeating room uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
+          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the Repeating room.</t>
         </is>
       </c>
       <c r="G396" s="7" t="inlineStr">
@@ -16574,7 +16574,7 @@
     <row r="397">
       <c r="A397" s="6" t="inlineStr">
         <is>
-          <t>OUR-111</t>
+          <t>OUR-119</t>
         </is>
       </c>
       <c r="B397" s="7" t="inlineStr">
@@ -16582,24 +16582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C397" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C397" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D397" s="9" t="inlineStr">
         <is>
-          <t>A finished dated shared row leaves both Todays the next day</t>
+          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
         </is>
       </c>
       <c r="E397" s="9" t="inlineStr">
         <is>
-          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
+          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
         </is>
       </c>
       <c r="F397" s="9" t="inlineStr">
         <is>
-          <t>Today: still there on BOTH, ticked, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
+          <t>Monthly is the fourth rhythm chip here too, from the same sheet the Repeating room uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
         </is>
       </c>
       <c r="G397" s="7" t="inlineStr">
@@ -16614,7 +16614,7 @@
     <row r="398">
       <c r="A398" s="6" t="inlineStr">
         <is>
-          <t>OUR-72</t>
+          <t>OUR-111</t>
         </is>
       </c>
       <c r="B398" s="7" t="inlineStr">
@@ -16622,24 +16622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C398" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C398" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D398" s="9" t="inlineStr">
         <is>
-          <t>A repeat supersedes the day rather than joining it</t>
+          <t>A finished dated shared row leaves both Todays the next day</t>
         </is>
       </c>
       <c r="E398" s="9" t="inlineStr">
         <is>
-          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
+          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
         </is>
       </c>
       <c r="F398" s="9" t="inlineStr">
         <is>
-          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
+          <t>Today: still there on BOTH, ticked, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
         </is>
       </c>
       <c r="G398" s="7" t="inlineStr">
@@ -16654,7 +16654,7 @@
     <row r="399">
       <c r="A399" s="6" t="inlineStr">
         <is>
-          <t>OUR-73</t>
+          <t>OUR-72</t>
         </is>
       </c>
       <c r="B399" s="7" t="inlineStr">
@@ -16662,24 +16662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C399" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C399" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D399" s="9" t="inlineStr">
         <is>
-          <t>An unreadable cadence is never placed on a day</t>
+          <t>A repeat supersedes the day rather than joining it</t>
         </is>
       </c>
       <c r="E399" s="9" t="inlineStr">
         <is>
-          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
+          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
         </is>
       </c>
       <c r="F399" s="9" t="inlineStr">
         <is>
-          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
+          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
         </is>
       </c>
       <c r="G399" s="7" t="inlineStr">
@@ -16694,7 +16694,7 @@
     <row r="400">
       <c r="A400" s="6" t="inlineStr">
         <is>
-          <t>OUR-74</t>
+          <t>OUR-73</t>
         </is>
       </c>
       <c r="B400" s="7" t="inlineStr">
@@ -16702,24 +16702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C400" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C400" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D400" s="9" t="inlineStr">
         <is>
-          <t>The heading's '!' says something changed since you looked, and clears when you look</t>
+          <t>An unreadable cadence is never placed on a day</t>
         </is>
       </c>
       <c r="E400" s="9" t="inlineStr">
         <is>
-          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap the list's name in the heading and come back. Also have device B delete a row and check again.</t>
+          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
         </is>
       </c>
       <c r="F400" s="9" t="inlineStr">
         <is>
-          <t>A small tinted '!' sits beside the list's name in Today's heading, and a screen reader hears '{name}. 1 since you looked'. After visiting, it is gone. A deleted row never raises it. The mark is bounded by your own attention, not by the list's length, and it never shows a climbing number.</t>
+          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
         </is>
       </c>
       <c r="G400" s="7" t="inlineStr">
@@ -16734,7 +16734,7 @@
     <row r="401">
       <c r="A401" s="6" t="inlineStr">
         <is>
-          <t>OUR-75</t>
+          <t>OUR-74</t>
         </is>
       </c>
       <c r="B401" s="7" t="inlineStr">
@@ -16742,24 +16742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C401" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C401" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D401" s="9" t="inlineStr">
         <is>
-          <t>Your OWN changes never raise the '!'</t>
+          <t>The heading's '!' says something changed since you looked, and clears when you look</t>
         </is>
       </c>
       <c r="E401" s="9" t="inlineStr">
         <is>
-          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
+          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap the list's name in the heading and come back. Also have device B delete a row and check again.</t>
         </is>
       </c>
       <c r="F401" s="9" t="inlineStr">
         <is>
-          <t>No '!' in the heading. It uses the room's own wash arithmetic, so the heading and the room always agree about whose change it was.</t>
+          <t>A small tinted '!' sits beside the list's name in Today's heading, and a screen reader hears '{name}. 1 since you looked'. After visiting, it is gone. A deleted row never raises it. The mark is bounded by your own attention, not by the list's length, and it never shows a climbing number.</t>
         </is>
       </c>
       <c r="G401" s="7" t="inlineStr">
@@ -16774,7 +16774,7 @@
     <row r="402">
       <c r="A402" s="6" t="inlineStr">
         <is>
-          <t>OUR-76</t>
+          <t>OUR-75</t>
         </is>
       </c>
       <c r="B402" s="7" t="inlineStr">
@@ -16789,17 +16789,17 @@
       </c>
       <c r="D402" s="9" t="inlineStr">
         <is>
-          <t>A first-ever visit raises nothing</t>
+          <t>Your OWN changes never raise the '!'</t>
         </is>
       </c>
       <c r="E402" s="9" t="inlineStr">
         <is>
-          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
+          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
         </is>
       </c>
       <c r="F402" s="9" t="inlineStr">
         <is>
-          <t>No '!'. There is no 'last looked' to measure against, and inventing one would open the app with a mark already on it.</t>
+          <t>No '!' in the heading. It uses the room's own wash arithmetic, so the heading and the room always agree about whose change it was.</t>
         </is>
       </c>
       <c r="G402" s="7" t="inlineStr">
@@ -16814,7 +16814,7 @@
     <row r="403">
       <c r="A403" s="6" t="inlineStr">
         <is>
-          <t>OUR-77</t>
+          <t>OUR-76</t>
         </is>
       </c>
       <c r="B403" s="7" t="inlineStr">
@@ -16822,24 +16822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C403" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C403" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D403" s="9" t="inlineStr">
         <is>
-          <t>The capture's AI note names only what that surface HAS</t>
+          <t>A first-ever visit raises nothing</t>
         </is>
       </c>
       <c r="E403" s="9" t="inlineStr">
         <is>
-          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
+          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
         </is>
       </c>
       <c r="F403" s="9" t="inlineStr">
         <is>
-          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
+          <t>No '!'. There is no 'last looked' to measure against, and inventing one would open the app with a mark already on it.</t>
         </is>
       </c>
       <c r="G403" s="7" t="inlineStr">
@@ -16854,7 +16854,7 @@
     <row r="404">
       <c r="A404" s="6" t="inlineStr">
         <is>
-          <t>OUR-78</t>
+          <t>OUR-77</t>
         </is>
       </c>
       <c r="B404" s="7" t="inlineStr">
@@ -16869,17 +16869,17 @@
       </c>
       <c r="D404" s="9" t="inlineStr">
         <is>
-          <t>Scan discloses on every path that can reach a camera</t>
+          <t>The capture's AI note names only what that surface HAS</t>
         </is>
       </c>
       <c r="E404" s="9" t="inlineStr">
         <is>
-          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
+          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
         </is>
       </c>
       <c r="F404" s="9" t="inlineStr">
         <is>
-          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
+          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
         </is>
       </c>
       <c r="G404" s="7" t="inlineStr">
@@ -16894,7 +16894,7 @@
     <row r="405">
       <c r="A405" s="6" t="inlineStr">
         <is>
-          <t>OUR-79</t>
+          <t>OUR-78</t>
         </is>
       </c>
       <c r="B405" s="7" t="inlineStr">
@@ -16909,17 +16909,17 @@
       </c>
       <c r="D405" s="9" t="inlineStr">
         <is>
-          <t>Press and hold a From Ours row on Today</t>
+          <t>Scan discloses on every path that can reach a camera</t>
         </is>
       </c>
       <c r="E405" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Ours strip.</t>
+          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
         </is>
       </c>
       <c r="F405" s="9" t="inlineStr">
         <is>
-          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
+          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
         </is>
       </c>
       <c r="G405" s="7" t="inlineStr">
@@ -16934,7 +16934,7 @@
     <row r="406">
       <c r="A406" s="6" t="inlineStr">
         <is>
-          <t>OUR-80</t>
+          <t>OUR-79</t>
         </is>
       </c>
       <c r="B406" s="7" t="inlineStr">
@@ -16949,17 +16949,17 @@
       </c>
       <c r="D406" s="9" t="inlineStr">
         <is>
-          <t>Pin and Move-to never rearrange the other person's day</t>
+          <t>Press and hold a From Ours row on Today</t>
         </is>
       </c>
       <c r="E406" s="9" t="inlineStr">
         <is>
-          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
+          <t>Hold a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F406" s="9" t="inlineStr">
         <is>
-          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
+          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
         </is>
       </c>
       <c r="G406" s="7" t="inlineStr">
@@ -16974,7 +16974,7 @@
     <row r="407">
       <c r="A407" s="6" t="inlineStr">
         <is>
-          <t>OUR-81</t>
+          <t>OUR-80</t>
         </is>
       </c>
       <c r="B407" s="7" t="inlineStr">
@@ -16982,24 +16982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C407" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C407" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D407" s="9" t="inlineStr">
         <is>
-          <t>A taken-on row is never on screen twice</t>
+          <t>Pin and Move-to never rearrange the other person's day</t>
         </is>
       </c>
       <c r="E407" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
+          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
         </is>
       </c>
       <c r="F407" s="9" t="inlineStr">
         <is>
-          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
+          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
         </is>
       </c>
       <c r="G407" s="7" t="inlineStr">
@@ -17014,7 +17014,7 @@
     <row r="408">
       <c r="A408" s="6" t="inlineStr">
         <is>
-          <t>OUR-82</t>
+          <t>OUR-81</t>
         </is>
       </c>
       <c r="B408" s="7" t="inlineStr">
@@ -17029,17 +17029,17 @@
       </c>
       <c r="D408" s="9" t="inlineStr">
         <is>
-          <t>Move-to is not offered on a repeating shared row</t>
+          <t>A taken-on row is never on screen twice</t>
         </is>
       </c>
       <c r="E408" s="9" t="inlineStr">
         <is>
-          <t>Hold a repeating row in the From Ours strip.</t>
+          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
         </is>
       </c>
       <c r="F408" s="9" t="inlineStr">
         <is>
-          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
+          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
         </is>
       </c>
       <c r="G408" s="7" t="inlineStr">
@@ -17054,7 +17054,7 @@
     <row r="409">
       <c r="A409" s="6" t="inlineStr">
         <is>
-          <t>OUR-83</t>
+          <t>OUR-82</t>
         </is>
       </c>
       <c r="B409" s="7" t="inlineStr">
@@ -17062,24 +17062,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C409" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C409" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D409" s="9" t="inlineStr">
         <is>
-          <t>One shared row, one route onto your day</t>
+          <t>Move-to is not offered on a repeating shared row</t>
         </is>
       </c>
       <c r="E409" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
+          <t>Hold a repeating row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F409" s="9" t="inlineStr">
         <is>
-          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
+          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
         </is>
       </c>
       <c r="G409" s="7" t="inlineStr">
@@ -17094,7 +17094,7 @@
     <row r="410">
       <c r="A410" s="6" t="inlineStr">
         <is>
-          <t>OUR-84</t>
+          <t>OUR-83</t>
         </is>
       </c>
       <c r="B410" s="7" t="inlineStr">
@@ -17109,17 +17109,17 @@
       </c>
       <c r="D410" s="9" t="inlineStr">
         <is>
-          <t>Take a From Ours row on, and it becomes an ordinary task</t>
+          <t>One shared row, one route onto your day</t>
         </is>
       </c>
       <c r="E410" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
+          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
         </is>
       </c>
       <c r="F410" s="9" t="inlineStr">
         <is>
-          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
+          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
         </is>
       </c>
       <c r="G410" s="7" t="inlineStr">
@@ -17134,7 +17134,7 @@
     <row r="411">
       <c r="A411" s="6" t="inlineStr">
         <is>
-          <t>OUR-85</t>
+          <t>OUR-84</t>
         </is>
       </c>
       <c r="B411" s="7" t="inlineStr">
@@ -17142,24 +17142,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C411" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C411" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D411" s="9" t="inlineStr">
         <is>
-          <t>Break it down works once taken on, and never touches the shared list</t>
+          <t>Take a From Ours row on, and it becomes an ordinary task</t>
         </is>
       </c>
       <c r="E411" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on, then Break it down.</t>
+          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
         </is>
       </c>
       <c r="F411" s="9" t="inlineStr">
         <is>
-          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
+          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
         </is>
       </c>
       <c r="G411" s="7" t="inlineStr">
@@ -17174,7 +17174,7 @@
     <row r="412">
       <c r="A412" s="6" t="inlineStr">
         <is>
-          <t>OUR-86</t>
+          <t>OUR-85</t>
         </is>
       </c>
       <c r="B412" s="7" t="inlineStr">
@@ -17182,24 +17182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C412" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C412" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D412" s="9" t="inlineStr">
         <is>
-          <t>Select several rows in the room and tick them together</t>
+          <t>Break it down works once taken on, and never touches the shared list</t>
         </is>
       </c>
       <c r="E412" s="9" t="inlineStr">
         <is>
-          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
+          <t>Take a shared row on, then Break it down.</t>
         </is>
       </c>
       <c r="F412" s="9" t="inlineStr">
         <is>
-          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
+          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
         </is>
       </c>
       <c r="G412" s="7" t="inlineStr">
@@ -17214,7 +17214,7 @@
     <row r="413">
       <c r="A413" s="6" t="inlineStr">
         <is>
-          <t>OUR-87</t>
+          <t>OUR-86</t>
         </is>
       </c>
       <c r="B413" s="7" t="inlineStr">
@@ -17229,17 +17229,17 @@
       </c>
       <c r="D413" s="9" t="inlineStr">
         <is>
-          <t>Bulk tick never UN-ticks</t>
+          <t>Select several rows in the room and tick them together</t>
         </is>
       </c>
       <c r="E413" s="9" t="inlineStr">
         <is>
-          <t>Select a mix of done and not-done rows and tap Done.</t>
+          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
         </is>
       </c>
       <c r="F413" s="9" t="inlineStr">
         <is>
-          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
+          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
         </is>
       </c>
       <c r="G413" s="7" t="inlineStr">
@@ -17254,7 +17254,7 @@
     <row r="414">
       <c r="A414" s="6" t="inlineStr">
         <is>
-          <t>OUR-88</t>
+          <t>OUR-87</t>
         </is>
       </c>
       <c r="B414" s="7" t="inlineStr">
@@ -17269,17 +17269,17 @@
       </c>
       <c r="D414" s="9" t="inlineStr">
         <is>
-          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
+          <t>Bulk tick never UN-ticks</t>
         </is>
       </c>
       <c r="E414" s="9" t="inlineStr">
         <is>
-          <t>Select a repeating row along with others. Read the shelf.</t>
+          <t>Select a mix of done and not-done rows and tap Done.</t>
         </is>
       </c>
       <c r="F414" s="9" t="inlineStr">
         <is>
-          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
+          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
         </is>
       </c>
       <c r="G414" s="7" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="415">
       <c r="A415" s="6" t="inlineStr">
         <is>
-          <t>OUR-89</t>
+          <t>OUR-88</t>
         </is>
       </c>
       <c r="B415" s="7" t="inlineStr">
@@ -17302,24 +17302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C415" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C415" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D415" s="9" t="inlineStr">
         <is>
-          <t>The pill steps aside for the select shelf</t>
+          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
         </is>
       </c>
       <c r="E415" s="9" t="inlineStr">
         <is>
-          <t>Enter select mode in the room with a few words waiting in the capture panel.</t>
+          <t>Select a repeating row along with others. Read the shelf.</t>
         </is>
       </c>
       <c r="F415" s="9" t="inlineStr">
         <is>
-          <t>The pill is gone while selecting (the select shelf docks at the foot), and back when you cancel, still showing its waiting words. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
+          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
         </is>
       </c>
       <c r="G415" s="7" t="inlineStr">
@@ -17334,7 +17334,7 @@
     <row r="416">
       <c r="A416" s="6" t="inlineStr">
         <is>
-          <t>OUR-90</t>
+          <t>OUR-89</t>
         </is>
       </c>
       <c r="B416" s="7" t="inlineStr">
@@ -17342,24 +17342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C416" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C416" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D416" s="9" t="inlineStr">
         <is>
-          <t>No select mode on a closed list</t>
+          <t>The pill steps aside for the select shelf</t>
         </is>
       </c>
       <c r="E416" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list and hold a row.</t>
+          <t>Enter select mode in the room with a few words waiting in the capture panel.</t>
         </is>
       </c>
       <c r="F416" s="9" t="inlineStr">
         <is>
-          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
+          <t>The pill is gone while selecting (the select shelf docks at the foot), and back when you cancel, still showing its waiting words. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
         </is>
       </c>
       <c r="G416" s="7" t="inlineStr">
@@ -17374,7 +17374,7 @@
     <row r="417">
       <c r="A417" s="6" t="inlineStr">
         <is>
-          <t>OUR-91</t>
+          <t>OUR-90</t>
         </is>
       </c>
       <c r="B417" s="7" t="inlineStr">
@@ -17382,24 +17382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C417" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C417" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D417" s="9" t="inlineStr">
         <is>
-          <t>A copy says when its shared row was taken off the list</t>
+          <t>No select mode on a closed list</t>
         </is>
       </c>
       <c r="E417" s="9" t="inlineStr">
         <is>
-          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
+          <t>Open an archived list and hold a row.</t>
         </is>
       </c>
       <c r="F417" s="9" t="inlineStr">
         <is>
-          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
+          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
         </is>
       </c>
       <c r="G417" s="7" t="inlineStr">
@@ -17414,7 +17414,7 @@
     <row r="418">
       <c r="A418" s="6" t="inlineStr">
         <is>
-          <t>OUR-92</t>
+          <t>OUR-91</t>
         </is>
       </c>
       <c r="B418" s="7" t="inlineStr">
@@ -17429,17 +17429,17 @@
       </c>
       <c r="D418" s="9" t="inlineStr">
         <is>
-          <t>That line never says who, and never says why</t>
+          <t>A copy says when its shared row was taken off the list</t>
         </is>
       </c>
       <c r="E418" s="9" t="inlineStr">
         <is>
-          <t>Read the line closely.</t>
+          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
         </is>
       </c>
       <c r="F418" s="9" t="inlineStr">
         <is>
-          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
+          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
         </is>
       </c>
       <c r="G418" s="7" t="inlineStr">
@@ -17454,7 +17454,7 @@
     <row r="419">
       <c r="A419" s="6" t="inlineStr">
         <is>
-          <t>OUR-93</t>
+          <t>OUR-92</t>
         </is>
       </c>
       <c r="B419" s="7" t="inlineStr">
@@ -17462,24 +17462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C419" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C419" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D419" s="9" t="inlineStr">
         <is>
-          <t>No line on a copy you already finished or removed</t>
+          <t>That line never says who, and never says why</t>
         </is>
       </c>
       <c r="E419" s="9" t="inlineStr">
         <is>
-          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
+          <t>Read the line closely.</t>
         </is>
       </c>
       <c r="F419" s="9" t="inlineStr">
         <is>
-          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
+          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
         </is>
       </c>
       <c r="G419" s="7" t="inlineStr">
@@ -17494,7 +17494,7 @@
     <row r="420">
       <c r="A420" s="6" t="inlineStr">
         <is>
-          <t>OUR-94</t>
+          <t>OUR-93</t>
         </is>
       </c>
       <c r="B420" s="7" t="inlineStr">
@@ -17502,24 +17502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C420" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C420" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D420" s="9" t="inlineStr">
         <is>
-          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
+          <t>No line on a copy you already finished or removed</t>
         </is>
       </c>
       <c r="E420" s="9" t="inlineStr">
         <is>
-          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
+          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
         </is>
       </c>
       <c r="F420" s="9" t="inlineStr">
         <is>
-          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
+          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
         </is>
       </c>
       <c r="G420" s="7" t="inlineStr">
@@ -17534,7 +17534,7 @@
     <row r="421">
       <c r="A421" s="6" t="inlineStr">
         <is>
-          <t>OUR-95</t>
+          <t>OUR-94</t>
         </is>
       </c>
       <c r="B421" s="7" t="inlineStr">
@@ -17542,24 +17542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C421" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C421" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D421" s="9" t="inlineStr">
         <is>
-          <t>A row's note is VISIBLE, not only spoken</t>
+          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
         </is>
       </c>
       <c r="E421" s="9" t="inlineStr">
         <is>
-          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
+          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
         </is>
       </c>
       <c r="F421" s="9" t="inlineStr">
         <is>
-          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
+          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
         </is>
       </c>
       <c r="G421" s="7" t="inlineStr">
@@ -17574,7 +17574,7 @@
     <row r="422">
       <c r="A422" s="6" t="inlineStr">
         <is>
-          <t>OUR-96</t>
+          <t>OUR-95</t>
         </is>
       </c>
       <c r="B422" s="7" t="inlineStr">
@@ -17582,24 +17582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C422" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C422" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D422" s="9" t="inlineStr">
         <is>
-          <t>Rows WITHOUT a note are unchanged</t>
+          <t>A row's note is VISIBLE, not only spoken</t>
         </is>
       </c>
       <c r="E422" s="9" t="inlineStr">
         <is>
-          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
+          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
         </is>
       </c>
       <c r="F422" s="9" t="inlineStr">
         <is>
-          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
+          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
         </is>
       </c>
       <c r="G422" s="7" t="inlineStr">
@@ -17614,7 +17614,7 @@
     <row r="423">
       <c r="A423" s="6" t="inlineStr">
         <is>
-          <t>OUR-97</t>
+          <t>OUR-96</t>
         </is>
       </c>
       <c r="B423" s="7" t="inlineStr">
@@ -17622,24 +17622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C423" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C423" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D423" s="9" t="inlineStr">
         <is>
-          <t>A tick after midnight lands on the RIGHT day</t>
+          <t>Rows WITHOUT a note are unchanged</t>
         </is>
       </c>
       <c r="E423" s="9" t="inlineStr">
         <is>
-          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
+          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
         </is>
       </c>
       <c r="F423" s="9" t="inlineStr">
         <is>
-          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
+          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
         </is>
       </c>
       <c r="G423" s="7" t="inlineStr">
@@ -17654,7 +17654,7 @@
     <row r="424">
       <c r="A424" s="6" t="inlineStr">
         <is>
-          <t>OUR-98</t>
+          <t>OUR-97</t>
         </is>
       </c>
       <c r="B424" s="7" t="inlineStr">
@@ -17669,17 +17669,17 @@
       </c>
       <c r="D424" s="9" t="inlineStr">
         <is>
-          <t>A tick made during a background sync is not undone</t>
+          <t>A tick after midnight lands on the RIGHT day</t>
         </is>
       </c>
       <c r="E424" s="9" t="inlineStr">
         <is>
-          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
+          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
         </is>
       </c>
       <c r="F424" s="9" t="inlineStr">
         <is>
-          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
+          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
         </is>
       </c>
       <c r="G424" s="7" t="inlineStr">
@@ -17694,7 +17694,7 @@
     <row r="425">
       <c r="A425" s="6" t="inlineStr">
         <is>
-          <t>OUR-99</t>
+          <t>OUR-98</t>
         </is>
       </c>
       <c r="B425" s="7" t="inlineStr">
@@ -17709,17 +17709,17 @@
       </c>
       <c r="D425" s="9" t="inlineStr">
         <is>
-          <t>A tick survives a device that has never opened the room</t>
+          <t>A tick made during a background sync is not undone</t>
         </is>
       </c>
       <c r="E425" s="9" t="inlineStr">
         <is>
-          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
+          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F425" s="9" t="inlineStr">
         <is>
-          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
+          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
         </is>
       </c>
       <c r="G425" s="7" t="inlineStr">
@@ -17734,7 +17734,7 @@
     <row r="426">
       <c r="A426" s="6" t="inlineStr">
         <is>
-          <t>OUR-100</t>
+          <t>OUR-99</t>
         </is>
       </c>
       <c r="B426" s="7" t="inlineStr">
@@ -17749,17 +17749,17 @@
       </c>
       <c r="D426" s="9" t="inlineStr">
         <is>
-          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
+          <t>A tick survives a device that has never opened the room</t>
         </is>
       </c>
       <c r="E426" s="9" t="inlineStr">
         <is>
-          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
+          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
         </is>
       </c>
       <c r="F426" s="9" t="inlineStr">
         <is>
-          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
+          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
         </is>
       </c>
       <c r="G426" s="7" t="inlineStr">
@@ -17774,7 +17774,7 @@
     <row r="427">
       <c r="A427" s="6" t="inlineStr">
         <is>
-          <t>OUR-101</t>
+          <t>OUR-100</t>
         </is>
       </c>
       <c r="B427" s="7" t="inlineStr">
@@ -17782,24 +17782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C427" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C427" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D427" s="9" t="inlineStr">
         <is>
-          <t>A closed list stops promising it keeps trying</t>
+          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
         </is>
       </c>
       <c r="E427" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list that has unpushed local changes.</t>
+          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
         </is>
       </c>
       <c r="F427" s="9" t="inlineStr">
         <is>
-          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
+          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
         </is>
       </c>
       <c r="G427" s="7" t="inlineStr">
@@ -17814,7 +17814,7 @@
     <row r="428">
       <c r="A428" s="6" t="inlineStr">
         <is>
-          <t>OUR-102</t>
+          <t>OUR-101</t>
         </is>
       </c>
       <c r="B428" s="7" t="inlineStr">
@@ -17829,17 +17829,17 @@
       </c>
       <c r="D428" s="9" t="inlineStr">
         <is>
-          <t>Setting a rhythm clears any date the row was carrying</t>
+          <t>A closed list stops promising it keeps trying</t>
         </is>
       </c>
       <c r="E428" s="9" t="inlineStr">
         <is>
-          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
+          <t>Open an archived list that has unpushed local changes.</t>
         </is>
       </c>
       <c r="F428" s="9" t="inlineStr">
         <is>
-          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
+          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
         </is>
       </c>
       <c r="G428" s="7" t="inlineStr">
@@ -17854,7 +17854,7 @@
     <row r="429">
       <c r="A429" s="6" t="inlineStr">
         <is>
-          <t>OUR-103</t>
+          <t>OUR-102</t>
         </is>
       </c>
       <c r="B429" s="7" t="inlineStr">
@@ -17869,17 +17869,17 @@
       </c>
       <c r="D429" s="9" t="inlineStr">
         <is>
-          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
+          <t>Setting a rhythm clears any date the row was carrying</t>
         </is>
       </c>
       <c r="E429" s="9" t="inlineStr">
         <is>
-          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
+          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
         </is>
       </c>
       <c r="F429" s="9" t="inlineStr">
         <is>
-          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
+          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
         </is>
       </c>
       <c r="G429" s="7" t="inlineStr">
@@ -17894,7 +17894,7 @@
     <row r="430">
       <c r="A430" s="6" t="inlineStr">
         <is>
-          <t>OUR-104</t>
+          <t>OUR-103</t>
         </is>
       </c>
       <c r="B430" s="7" t="inlineStr">
@@ -17902,24 +17902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C430" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C430" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D430" s="9" t="inlineStr">
         <is>
-          <t>No dead reorder rail on shared rows</t>
+          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
         </is>
       </c>
       <c r="E430" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the room and in the From Ours strip.</t>
+          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
         </is>
       </c>
       <c r="F430" s="9" t="inlineStr">
         <is>
-          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
+          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
         </is>
       </c>
       <c r="G430" s="7" t="inlineStr">
@@ -17934,7 +17934,7 @@
     <row r="431">
       <c r="A431" s="6" t="inlineStr">
         <is>
-          <t>OUR-105</t>
+          <t>OUR-104</t>
         </is>
       </c>
       <c r="B431" s="7" t="inlineStr">
@@ -17942,24 +17942,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C431" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C431" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D431" s="9" t="inlineStr">
         <is>
-          <t>First run introduces the shared list</t>
+          <t>No dead reorder rail on shared rows</t>
         </is>
       </c>
       <c r="E431" s="9" t="inlineStr">
         <is>
-          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
+          <t>Hold a row in the room and in the From Ours strip.</t>
         </is>
       </c>
       <c r="F431" s="9" t="inlineStr">
         <is>
-          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
+          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
         </is>
       </c>
       <c r="G431" s="7" t="inlineStr">
@@ -17974,7 +17974,7 @@
     <row r="432">
       <c r="A432" s="6" t="inlineStr">
         <is>
-          <t>OUR-106</t>
+          <t>OUR-105</t>
         </is>
       </c>
       <c r="B432" s="7" t="inlineStr">
@@ -17989,17 +17989,17 @@
       </c>
       <c r="D432" s="9" t="inlineStr">
         <is>
-          <t>Anyone can start a shared list, not just an allowlisted address</t>
+          <t>First run introduces the shared list</t>
         </is>
       </c>
       <c r="E432" s="9" t="inlineStr">
         <is>
-          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
+          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
         </is>
       </c>
       <c r="F432" s="9" t="inlineStr">
         <is>
-          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
+          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
         </is>
       </c>
       <c r="G432" s="7" t="inlineStr">
@@ -18014,7 +18014,7 @@
     <row r="433">
       <c r="A433" s="6" t="inlineStr">
         <is>
-          <t>OUR-107</t>
+          <t>OUR-106</t>
         </is>
       </c>
       <c r="B433" s="7" t="inlineStr">
@@ -18029,17 +18029,17 @@
       </c>
       <c r="D433" s="9" t="inlineStr">
         <is>
-          <t>The shared-list onboarding step can actually be REACHED</t>
+          <t>Anyone can start a shared list, not just an allowlisted address</t>
         </is>
       </c>
       <c r="E433" s="9" t="inlineStr">
         <is>
-          <t>Replay the first run and press the primary button through every step without skipping.</t>
+          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
         </is>
       </c>
       <c r="F433" s="9" t="inlineStr">
         <is>
-          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
+          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
         </is>
       </c>
       <c r="G433" s="7" t="inlineStr">
@@ -18054,7 +18054,7 @@
     <row r="434">
       <c r="A434" s="6" t="inlineStr">
         <is>
-          <t>OUR-108</t>
+          <t>OUR-107</t>
         </is>
       </c>
       <c r="B434" s="7" t="inlineStr">
@@ -18062,24 +18062,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C434" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C434" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D434" s="9" t="inlineStr">
         <is>
-          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
+          <t>The shared-list onboarding step can actually be REACHED</t>
         </is>
       </c>
       <c r="E434" s="9" t="inlineStr">
         <is>
-          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
+          <t>Replay the first run and press the primary button through every step without skipping.</t>
         </is>
       </c>
       <c r="F434" s="9" t="inlineStr">
         <is>
-          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
+          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
         </is>
       </c>
       <c r="G434" s="7" t="inlineStr">
@@ -18094,7 +18094,7 @@
     <row r="435">
       <c r="A435" s="6" t="inlineStr">
         <is>
-          <t>OUR-109</t>
+          <t>OUR-108</t>
         </is>
       </c>
       <c r="B435" s="7" t="inlineStr">
@@ -18102,24 +18102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C435" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C435" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D435" s="9" t="inlineStr">
         <is>
-          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
+          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
         </is>
       </c>
       <c r="E435" s="9" t="inlineStr">
         <is>
-          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
+          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
         </is>
       </c>
       <c r="F435" s="9" t="inlineStr">
         <is>
-          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
+          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
         </is>
       </c>
       <c r="G435" s="7" t="inlineStr">
@@ -18134,7 +18134,7 @@
     <row r="436">
       <c r="A436" s="6" t="inlineStr">
         <is>
-          <t>OUR-110</t>
+          <t>OUR-109</t>
         </is>
       </c>
       <c r="B436" s="7" t="inlineStr">
@@ -18149,17 +18149,17 @@
       </c>
       <c r="D436" s="9" t="inlineStr">
         <is>
-          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
+          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
         </is>
       </c>
       <c r="E436" s="9" t="inlineStr">
         <is>
-          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
+          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
         </is>
       </c>
       <c r="F436" s="9" t="inlineStr">
         <is>
-          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
+          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
         </is>
       </c>
       <c r="G436" s="7" t="inlineStr">
@@ -18174,12 +18174,12 @@
     <row r="437">
       <c r="A437" s="6" t="inlineStr">
         <is>
-          <t>UPD-01</t>
+          <t>OUR-110</t>
         </is>
       </c>
       <c r="B437" s="7" t="inlineStr">
         <is>
-          <t>Updates</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C437" s="8" t="inlineStr">
@@ -18189,17 +18189,17 @@
       </c>
       <c r="D437" s="9" t="inlineStr">
         <is>
-          <t>Settings states the version, and up-to-date is a fact</t>
+          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
         </is>
       </c>
       <c r="E437" s="9" t="inlineStr">
         <is>
-          <t>Open Settings and scroll to the foot.</t>
+          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
         </is>
       </c>
       <c r="F437" s="9" t="inlineStr">
         <is>
-          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
+          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
         </is>
       </c>
       <c r="G437" s="7" t="inlineStr">
@@ -18214,7 +18214,7 @@
     <row r="438">
       <c r="A438" s="6" t="inlineStr">
         <is>
-          <t>UPD-02</t>
+          <t>UPD-01</t>
         </is>
       </c>
       <c r="B438" s="7" t="inlineStr">
@@ -18229,22 +18229,22 @@
       </c>
       <c r="D438" s="9" t="inlineStr">
         <is>
-          <t>Web offers a reload, and says drafts are kept</t>
+          <t>Settings states the version, and up-to-date is a fact</t>
         </is>
       </c>
       <c r="E438" s="9" t="inlineStr">
         <is>
-          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
+          <t>Open Settings and scroll to the foot.</t>
         </is>
       </c>
       <c r="F438" s="9" t="inlineStr">
         <is>
-          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
+          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
         </is>
       </c>
       <c r="G438" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H438" s="7" t="inlineStr"/>
@@ -18254,7 +18254,7 @@
     <row r="439">
       <c r="A439" s="6" t="inlineStr">
         <is>
-          <t>UPD-03</t>
+          <t>UPD-02</t>
         </is>
       </c>
       <c r="B439" s="7" t="inlineStr">
@@ -18269,22 +18269,22 @@
       </c>
       <c r="D439" s="9" t="inlineStr">
         <is>
-          <t>Native points at the store, and says lists are untouched</t>
+          <t>Web offers a reload, and says drafts are kept</t>
         </is>
       </c>
       <c r="E439" s="9" t="inlineStr">
         <is>
-          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
+          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
         </is>
       </c>
       <c r="F439" s="9" t="inlineStr">
         <is>
-          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
+          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
         </is>
       </c>
       <c r="G439" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H439" s="7" t="inlineStr"/>
@@ -18294,7 +18294,7 @@
     <row r="440">
       <c r="A440" s="6" t="inlineStr">
         <is>
-          <t>UPD-04</t>
+          <t>UPD-03</t>
         </is>
       </c>
       <c r="B440" s="7" t="inlineStr">
@@ -18302,29 +18302,29 @@
           <t>Updates</t>
         </is>
       </c>
-      <c r="C440" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C440" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D440" s="9" t="inlineStr">
         <is>
-          <t>Unreachable server says NOTHING, never 'up to date'</t>
+          <t>Native points at the store, and says lists are untouched</t>
         </is>
       </c>
       <c r="E440" s="9" t="inlineStr">
         <is>
-          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
+          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
         </is>
       </c>
       <c r="F440" s="9" t="inlineStr">
         <is>
-          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
+          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
         </is>
       </c>
       <c r="G440" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H440" s="7" t="inlineStr"/>
@@ -18334,7 +18334,7 @@
     <row r="441">
       <c r="A441" s="6" t="inlineStr">
         <is>
-          <t>UPD-05</t>
+          <t>UPD-04</t>
         </is>
       </c>
       <c r="B441" s="7" t="inlineStr">
@@ -18349,17 +18349,17 @@
       </c>
       <c r="D441" s="9" t="inlineStr">
         <is>
-          <t>The goodnight mention is rare, and framed for the other person</t>
+          <t>Unreachable server says NOTHING, never 'up to date'</t>
         </is>
       </c>
       <c r="E441" s="9" t="inlineStr">
         <is>
-          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
+          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
         </is>
       </c>
       <c r="F441" s="9" t="inlineStr">
         <is>
-          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
+          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
         </is>
       </c>
       <c r="G441" s="7" t="inlineStr">
@@ -18374,32 +18374,32 @@
     <row r="442">
       <c r="A442" s="6" t="inlineStr">
         <is>
-          <t>OUR-12</t>
+          <t>UPD-05</t>
         </is>
       </c>
       <c r="B442" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C442" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="C442" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D442" s="9" t="inlineStr">
         <is>
-          <t>Unnamed lists read in each person's language</t>
+          <t>The goodnight mention is rare, and framed for the other person</t>
         </is>
       </c>
       <c r="E442" s="9" t="inlineStr">
         <is>
-          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
         </is>
       </c>
       <c r="F442" s="9" t="inlineStr">
         <is>
-          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
         </is>
       </c>
       <c r="G442" s="7" t="inlineStr">
@@ -18411,9 +18411,49 @@
       <c r="I442" s="9" t="inlineStr"/>
       <c r="J442" s="7" t="inlineStr"/>
     </row>
+    <row r="443">
+      <c r="A443" s="6" t="inlineStr">
+        <is>
+          <t>OUR-12</t>
+        </is>
+      </c>
+      <c r="B443" s="7" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="C443" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D443" s="9" t="inlineStr">
+        <is>
+          <t>Unnamed lists read in each person's language</t>
+        </is>
+      </c>
+      <c r="E443" s="9" t="inlineStr">
+        <is>
+          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+        </is>
+      </c>
+      <c r="F443" s="9" t="inlineStr">
+        <is>
+          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+        </is>
+      </c>
+      <c r="G443" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H443" s="7" t="inlineStr"/>
+      <c r="I443" s="9" t="inlineStr"/>
+      <c r="J443" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J442"/>
-  <conditionalFormatting sqref="H2:H442">
+  <autoFilter ref="A1:J443"/>
+  <conditionalFormatting sqref="H2:H443">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -18425,7 +18465,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H442" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
+    <dataValidation sqref="H2:H443" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
       <formula1>"Pass,Fail,Blocked,Not run"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18461,7 +18501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>442</t>
         </is>
       </c>
     </row>
@@ -18472,7 +18512,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF('Test Suite'!$H$2:$H$442,"Pass")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$443,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -18483,7 +18523,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF('Test Suite'!$H$2:$H$442,"Fail")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$443,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -18494,7 +18534,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Suite'!$H$2:$H$442,"Blocked")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$443,"Blocked")</f>
         <v/>
       </c>
     </row>
@@ -18505,7 +18545,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Suite'!$H$2:$H$442,"Not run")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$443,"Not run")</f>
         <v/>
       </c>
     </row>
@@ -18516,7 +18556,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>441-COUNTA('Test Suite'!$H$2:$H$442)</f>
+        <f>442-COUNTA('Test Suite'!$H$2:$H$443)</f>
         <v/>
       </c>
     </row>
@@ -18527,7 +18567,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF('Test Suite'!$C$2:$C$442,"P1")</f>
+        <f>COUNTIF('Test Suite'!$C$2:$C$443,"P1")</f>
         <v/>
       </c>
     </row>
@@ -18538,7 +18578,7 @@
         </is>
       </c>
       <c r="B10">
-        <f>COUNTIFS('Test Suite'!$C$2:$C$442,"P1",'Test Suite'!$H$2:$H$442,"Pass")</f>
+        <f>COUNTIFS('Test Suite'!$C$2:$C$443,"P1",'Test Suite'!$H$2:$H$443,"Pass")</f>
         <v/>
       </c>
     </row>

--- a/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
+++ b/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$443</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$444</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J443"/>
+  <dimension ref="A1:J444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14854,7 +14854,7 @@
     <row r="354">
       <c r="A354" s="6" t="inlineStr">
         <is>
-          <t>OUR-36</t>
+          <t>OUR-125</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -14862,24 +14862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C354" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C354" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D354" s="9" t="inlineStr">
         <is>
-          <t>Delete for good commits when the screen closes, not on a timer</t>
+          <t>Today and the Ours tab look like one page</t>
         </is>
       </c>
       <c r="E354" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
+          <t>With a live shared list, on a phone, tap the list's name in Today's heading, then 'Today', a few times. Do it in light and dark, at dawn or dusk if you can, and on an iPhone as well as Android.</t>
         </is>
       </c>
       <c r="F354" s="9" t="inlineStr">
         <is>
-          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
+          <t>The date, the Menu pill and the two heading words sit at exactly the same height on both, so nothing jumps as you flip. The Ours tab has Today's own background (the warm time-of-day gradient, and on iPhone and web the soft drifting glow), and the glow does not jump or restart during the fade: it is in the same place on both. A closed list opened from the archive keeps the plain room background and its '‹ Back'.</t>
         </is>
       </c>
       <c r="G354" s="7" t="inlineStr">
@@ -14894,7 +14894,7 @@
     <row r="355">
       <c r="A355" s="6" t="inlineStr">
         <is>
-          <t>OUR-37</t>
+          <t>OUR-36</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -14902,24 +14902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C355" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C355" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D355" s="9" t="inlineStr">
         <is>
-          <t>Rename yourself, and only yourself</t>
+          <t>Delete for good commits when the screen closes, not on a timer</t>
         </is>
       </c>
       <c r="E355" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
+          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
         </is>
       </c>
       <c r="F355" s="9" t="inlineStr">
         <is>
-          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
+          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
         </is>
       </c>
       <c r="G355" s="7" t="inlineStr">
@@ -14934,7 +14934,7 @@
     <row r="356">
       <c r="A356" s="6" t="inlineStr">
         <is>
-          <t>OUR-38</t>
+          <t>OUR-37</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -14949,17 +14949,17 @@
       </c>
       <c r="D356" s="9" t="inlineStr">
         <is>
-          <t>A dropped signal never throws you out of the room</t>
+          <t>Rename yourself, and only yourself</t>
         </is>
       </c>
       <c r="E356" s="9" t="inlineStr">
         <is>
-          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
+          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
         </is>
       </c>
       <c r="F356" s="9" t="inlineStr">
         <is>
-          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
+          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
         </is>
       </c>
       <c r="G356" s="7" t="inlineStr">
@@ -14974,7 +14974,7 @@
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
         <is>
-          <t>OUR-39</t>
+          <t>OUR-38</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -14982,24 +14982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C357" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C357" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D357" s="9" t="inlineStr">
         <is>
-          <t>Report this list reaches us and tells nobody else</t>
+          <t>A dropped signal never throws you out of the room</t>
         </is>
       </c>
       <c r="E357" s="9" t="inlineStr">
         <is>
-          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
+          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
         </is>
       </c>
       <c r="F357" s="9" t="inlineStr">
         <is>
-          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
+          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
         </is>
       </c>
       <c r="G357" s="7" t="inlineStr">
@@ -15014,7 +15014,7 @@
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
         <is>
-          <t>OUR-40</t>
+          <t>OUR-39</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -15029,17 +15029,17 @@
       </c>
       <c r="D358" s="9" t="inlineStr">
         <is>
-          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
+          <t>Report this list reaches us and tells nobody else</t>
         </is>
       </c>
       <c r="E358" s="9" t="inlineStr">
         <is>
-          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
+          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
         </is>
       </c>
       <c r="F358" s="9" t="inlineStr">
         <is>
-          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
+          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
         </is>
       </c>
       <c r="G358" s="7" t="inlineStr">
@@ -15054,7 +15054,7 @@
     <row r="359">
       <c r="A359" s="6" t="inlineStr">
         <is>
-          <t>OUR-41</t>
+          <t>OUR-40</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -15062,24 +15062,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C359" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C359" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D359" s="9" t="inlineStr">
         <is>
-          <t>Leaving is the block, and needs no reason</t>
+          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
         </is>
       </c>
       <c r="E359" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap 'Leave this list'.</t>
+          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
         </is>
       </c>
       <c r="F359" s="9" t="inlineStr">
         <is>
-          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
+          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
         </is>
       </c>
       <c r="G359" s="7" t="inlineStr">
@@ -15094,12 +15094,12 @@
     <row r="360">
       <c r="A360" s="6" t="inlineStr">
         <is>
-          <t>LEG-05</t>
+          <t>OUR-41</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C360" s="10" t="inlineStr">
@@ -15109,17 +15109,17 @@
       </c>
       <c r="D360" s="9" t="inlineStr">
         <is>
-          <t>The shared-list clauses are in both copies of both documents</t>
+          <t>Leaving is the block, and needs no reason</t>
         </is>
       </c>
       <c r="E360" s="9" t="inlineStr">
         <is>
-          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
+          <t>On a live list, tap 'Leave this list'.</t>
         </is>
       </c>
       <c r="F360" s="9" t="inlineStr">
         <is>
-          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
+          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
         </is>
       </c>
       <c r="G360" s="7" t="inlineStr">
@@ -15134,32 +15134,32 @@
     <row r="361">
       <c r="A361" s="6" t="inlineStr">
         <is>
-          <t>OUR-42</t>
+          <t>LEG-05</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C361" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C361" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D361" s="9" t="inlineStr">
         <is>
-          <t>A change on one phone appears on the other WITHOUT touching it</t>
+          <t>The shared-list clauses are in both copies of both documents</t>
         </is>
       </c>
       <c r="E361" s="9" t="inlineStr">
         <is>
-          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
+          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
         </is>
       </c>
       <c r="F361" s="9" t="inlineStr">
         <is>
-          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
+          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
         </is>
       </c>
       <c r="G361" s="7" t="inlineStr">
@@ -15174,7 +15174,7 @@
     <row r="362">
       <c r="A362" s="6" t="inlineStr">
         <is>
-          <t>OUR-43</t>
+          <t>OUR-42</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
@@ -15189,17 +15189,17 @@
       </c>
       <c r="D362" s="9" t="inlineStr">
         <is>
-          <t>Opening your own list does not bounce you back</t>
+          <t>A change on one phone appears on the other WITHOUT touching it</t>
         </is>
       </c>
       <c r="E362" s="9" t="inlineStr">
         <is>
-          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
+          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
         </is>
       </c>
       <c r="F362" s="9" t="inlineStr">
         <is>
-          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
+          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
         </is>
       </c>
       <c r="G362" s="7" t="inlineStr">
@@ -15214,7 +15214,7 @@
     <row r="363">
       <c r="A363" s="6" t="inlineStr">
         <is>
-          <t>OUR-44</t>
+          <t>OUR-43</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -15222,24 +15222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C363" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C363" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D363" s="9" t="inlineStr">
         <is>
-          <t>The pairing screen offers a way INTO the list</t>
+          <t>Opening your own list does not bounce you back</t>
         </is>
       </c>
       <c r="E363" s="9" t="inlineStr">
         <is>
-          <t>Finish pairing, then look at the pairing screen.</t>
+          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
         </is>
       </c>
       <c r="F363" s="9" t="inlineStr">
         <is>
-          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
+          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
         </is>
       </c>
       <c r="G363" s="7" t="inlineStr">
@@ -15254,7 +15254,7 @@
     <row r="364">
       <c r="A364" s="6" t="inlineStr">
         <is>
-          <t>OUR-45</t>
+          <t>OUR-44</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -15269,17 +15269,17 @@
       </c>
       <c r="D364" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash appears and then takes itself away</t>
+          <t>The pairing screen offers a way INTO the list</t>
         </is>
       </c>
       <c r="E364" s="9" t="inlineStr">
         <is>
-          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
+          <t>Finish pairing, then look at the pairing screen.</t>
         </is>
       </c>
       <c r="F364" s="9" t="inlineStr">
         <is>
-          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
+          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
         </is>
       </c>
       <c r="G364" s="7" t="inlineStr">
@@ -15294,7 +15294,7 @@
     <row r="365">
       <c r="A365" s="6" t="inlineStr">
         <is>
-          <t>OUR-47</t>
+          <t>OUR-45</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -15302,24 +15302,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C365" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C365" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D365" s="9" t="inlineStr">
         <is>
-          <t>Ours lives in Today's heading (Today v3)</t>
+          <t>The quiet wash appears and then takes itself away</t>
         </is>
       </c>
       <c r="E365" s="9" t="inlineStr">
         <is>
-          <t>With a live list, look at the top of Today. Then leave the list (or sign out) and look again. With a screen reader, move through the heading.</t>
+          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
         </is>
       </c>
       <c r="F365" s="9" t="inlineStr">
         <is>
-          <t>With a live list the heading reads 'Today' and the list's name side by side (its own name when it has one, else 'Ours'), 'Today' underlined as the current tab. With no live list there is only 'Today', and no empty space where Ours would be. A screen reader hears them as tabs, 'Today, selected' and '{name}'. The old Ours door card under the list is gone.</t>
+          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
         </is>
       </c>
       <c r="G365" s="7" t="inlineStr">
@@ -15334,7 +15334,7 @@
     <row r="366">
       <c r="A366" s="6" t="inlineStr">
         <is>
-          <t>OUR-48</t>
+          <t>OUR-47</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -15349,17 +15349,17 @@
       </c>
       <c r="D366" s="9" t="inlineStr">
         <is>
-          <t>Their tick marks your copy DONE and leaves it on your day</t>
+          <t>Ours lives in Today's heading (Today v3)</t>
         </is>
       </c>
       <c r="E366" s="9" t="inlineStr">
         <is>
-          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
+          <t>With a live list, look at the top of Today. Then leave the list (or sign out) and look again. With a screen reader, move through the heading.</t>
         </is>
       </c>
       <c r="F366" s="9" t="inlineStr">
         <is>
-          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
+          <t>With a live list the heading reads 'Today' and the list's name side by side (its own name when it has one, else 'Ours'), 'Today' underlined as the current tab. With no live list there is only 'Today', and no empty space where Ours would be. A screen reader hears them as tabs, 'Today, selected' and '{name}'. The old Ours door card under the list is gone.</t>
         </is>
       </c>
       <c r="G366" s="7" t="inlineStr">
@@ -15374,7 +15374,7 @@
     <row r="367">
       <c r="A367" s="6" t="inlineStr">
         <is>
-          <t>OUR-49</t>
+          <t>OUR-48</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -15389,17 +15389,17 @@
       </c>
       <c r="D367" s="9" t="inlineStr">
         <is>
-          <t>A settled copy carries a completion DATE, not just a done flag</t>
+          <t>Their tick marks your copy DONE and leaves it on your day</t>
         </is>
       </c>
       <c r="E367" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
+          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
         </is>
       </c>
       <c r="F367" s="9" t="inlineStr">
         <is>
-          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
+          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
         </is>
       </c>
       <c r="G367" s="7" t="inlineStr">
@@ -15414,7 +15414,7 @@
     <row r="368">
       <c r="A368" s="6" t="inlineStr">
         <is>
-          <t>OUR-50</t>
+          <t>OUR-49</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -15422,24 +15422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C368" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C368" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D368" s="9" t="inlineStr">
         <is>
-          <t>A finished copy can be brought over again</t>
+          <t>A settled copy carries a completion DATE, not just a done flag</t>
         </is>
       </c>
       <c r="E368" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, hold that row in Ours.</t>
+          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
         </is>
       </c>
       <c r="F368" s="9" t="inlineStr">
         <is>
-          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
+          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
         </is>
       </c>
       <c r="G368" s="7" t="inlineStr">
@@ -15454,7 +15454,7 @@
     <row r="369">
       <c r="A369" s="6" t="inlineStr">
         <is>
-          <t>OUR-51</t>
+          <t>OUR-50</t>
         </is>
       </c>
       <c r="B369" s="7" t="inlineStr">
@@ -15462,24 +15462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C369" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C369" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D369" s="9" t="inlineStr">
         <is>
-          <t>Your own edit never highlights; their later edit always does</t>
+          <t>A finished copy can be brought over again</t>
         </is>
       </c>
       <c r="E369" s="9" t="inlineStr">
         <is>
-          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
+          <t>After OUR-48, hold that row in Ours.</t>
         </is>
       </c>
       <c r="F369" s="9" t="inlineStr">
         <is>
-          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
+          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
         </is>
       </c>
       <c r="G369" s="7" t="inlineStr">
@@ -15494,7 +15494,7 @@
     <row r="370">
       <c r="A370" s="6" t="inlineStr">
         <is>
-          <t>OUR-52</t>
+          <t>OUR-51</t>
         </is>
       </c>
       <c r="B370" s="7" t="inlineStr">
@@ -15502,24 +15502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C370" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C370" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D370" s="9" t="inlineStr">
         <is>
-          <t>The highlight arrives at once and fades away</t>
+          <t>Your own edit never highlights; their later edit always does</t>
         </is>
       </c>
       <c r="E370" s="9" t="inlineStr">
         <is>
-          <t>Have B change a row while A is on the list.</t>
+          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
         </is>
       </c>
       <c r="F370" s="9" t="inlineStr">
         <is>
-          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
+          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
         </is>
       </c>
       <c r="G370" s="7" t="inlineStr">
@@ -15534,7 +15534,7 @@
     <row r="371">
       <c r="A371" s="6" t="inlineStr">
         <is>
-          <t>OUR-53</t>
+          <t>OUR-52</t>
         </is>
       </c>
       <c r="B371" s="7" t="inlineStr">
@@ -15549,17 +15549,17 @@
       </c>
       <c r="D371" s="9" t="inlineStr">
         <is>
-          <t>Two devices share ONE clock</t>
+          <t>The highlight arrives at once and fades away</t>
         </is>
       </c>
       <c r="E371" s="9" t="inlineStr">
         <is>
-          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
+          <t>Have B change a row while A is on the list.</t>
         </is>
       </c>
       <c r="F371" s="9" t="inlineStr">
         <is>
-          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
+          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
         </is>
       </c>
       <c r="G371" s="7" t="inlineStr">
@@ -15574,7 +15574,7 @@
     <row r="372">
       <c r="A372" s="6" t="inlineStr">
         <is>
-          <t>OUR-54</t>
+          <t>OUR-53</t>
         </is>
       </c>
       <c r="B372" s="7" t="inlineStr">
@@ -15582,24 +15582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C372" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C372" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D372" s="9" t="inlineStr">
         <is>
-          <t>The debug panel is opt-in and carries no task text</t>
+          <t>Two devices share ONE clock</t>
         </is>
       </c>
       <c r="E372" s="9" t="inlineStr">
         <is>
-          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
+          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
         </is>
       </c>
       <c r="F372" s="9" t="inlineStr">
         <is>
-          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
+          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
         </is>
       </c>
       <c r="G372" s="7" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="373">
       <c r="A373" s="6" t="inlineStr">
         <is>
-          <t>OUR-55</t>
+          <t>OUR-54</t>
         </is>
       </c>
       <c r="B373" s="7" t="inlineStr">
@@ -15622,24 +15622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C373" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C373" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D373" s="9" t="inlineStr">
         <is>
-          <t>Capture on Ours IS Today's capture</t>
+          <t>The debug panel is opt-in and carries no task text</t>
         </is>
       </c>
       <c r="E373" s="9" t="inlineStr">
         <is>
-          <t>Open a shared list and tap the + pill at the foot of the screen.</t>
+          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
         </is>
       </c>
       <c r="F373" s="9" t="inlineStr">
         <is>
-          <t>The same pill and the same panel Today has, headed 'Add to {name}': the same box, the same Speak button (web), the same When chip and door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
+          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
         </is>
       </c>
       <c r="G373" s="7" t="inlineStr">
@@ -15654,7 +15654,7 @@
     <row r="374">
       <c r="A374" s="6" t="inlineStr">
         <is>
-          <t>OUR-56</t>
+          <t>OUR-55</t>
         </is>
       </c>
       <c r="B374" s="7" t="inlineStr">
@@ -15669,17 +15669,17 @@
       </c>
       <c r="D374" s="9" t="inlineStr">
         <is>
-          <t>Repeating can be set AT capture, without knowing a gesture</t>
+          <t>Capture on Ours IS Today's capture</t>
         </is>
       </c>
       <c r="E374" s="9" t="inlineStr">
         <is>
-          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
+          <t>Open a shared list and tap the + pill at the foot of the screen.</t>
         </is>
       </c>
       <c r="F374" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
+          <t>The same pill and the same panel Today has, headed 'Add to {name}': the same box, the same Speak button (web), the same When chip and door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
         </is>
       </c>
       <c r="G374" s="7" t="inlineStr">
@@ -15694,7 +15694,7 @@
     <row r="375">
       <c r="A375" s="6" t="inlineStr">
         <is>
-          <t>OUR-57</t>
+          <t>OUR-56</t>
         </is>
       </c>
       <c r="B375" s="7" t="inlineStr">
@@ -15702,24 +15702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C375" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C375" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D375" s="9" t="inlineStr">
         <is>
-          <t>A dump becomes several shared rows, in the order typed</t>
+          <t>Repeating can be set AT capture, without knowing a gesture</t>
         </is>
       </c>
       <c r="E375" s="9" t="inlineStr">
         <is>
-          <t>Type three lines into the Ours capture and Add.</t>
+          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
         </is>
       </c>
       <c r="F375" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
+          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
         </is>
       </c>
       <c r="G375" s="7" t="inlineStr">
@@ -15734,7 +15734,7 @@
     <row r="376">
       <c r="A376" s="6" t="inlineStr">
         <is>
-          <t>OUR-58</t>
+          <t>OUR-57</t>
         </is>
       </c>
       <c r="B376" s="7" t="inlineStr">
@@ -15742,24 +15742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C376" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C376" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D376" s="9" t="inlineStr">
         <is>
-          <t>The shared door offers When and Repeating, never Steps</t>
+          <t>A dump becomes several shared rows, in the order typed</t>
         </is>
       </c>
       <c r="E376" s="9" t="inlineStr">
         <is>
-          <t>Open the door on Ours and compare it with the door on Today.</t>
+          <t>Type three lines into the Ours capture and Add.</t>
         </is>
       </c>
       <c r="F376" s="9" t="inlineStr">
         <is>
-          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
+          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
         </is>
       </c>
       <c r="G376" s="7" t="inlineStr">
@@ -15774,7 +15774,7 @@
     <row r="377">
       <c r="A377" s="6" t="inlineStr">
         <is>
-          <t>OUR-59</t>
+          <t>OUR-58</t>
         </is>
       </c>
       <c r="B377" s="7" t="inlineStr">
@@ -15782,24 +15782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C377" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C377" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D377" s="9" t="inlineStr">
         <is>
-          <t>Typed text survives the panel going</t>
+          <t>The shared door offers When and Repeating, never Steps</t>
         </is>
       </c>
       <c r="E377" s="9" t="inlineStr">
         <is>
-          <t>Type half a sentence into the Ours panel, Close it, tick something, then tap the pill again.</t>
+          <t>Open the door on Ours and compare it with the door on Today.</t>
         </is>
       </c>
       <c r="F377" s="9" t="inlineStr">
         <is>
-          <t>The pill shows '+' and three dots while words wait, and the half sentence is still there. The panel is always mounted, never unmounted. Only an Add resets the door; the words never reset on their own.</t>
+          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
         </is>
       </c>
       <c r="G377" s="7" t="inlineStr">
@@ -15814,7 +15814,7 @@
     <row r="378">
       <c r="A378" s="6" t="inlineStr">
         <is>
-          <t>OUR-60</t>
+          <t>OUR-59</t>
         </is>
       </c>
       <c r="B378" s="7" t="inlineStr">
@@ -15829,22 +15829,22 @@
       </c>
       <c r="D378" s="9" t="inlineStr">
         <is>
-          <t>The Ours panel rides above the keyboard</t>
+          <t>Typed text survives the panel going</t>
         </is>
       </c>
       <c r="E378" s="9" t="inlineStr">
         <is>
-          <t>On a real Android device, tap the + pill on the Ours list, tap the box and start typing.</t>
+          <t>Type half a sentence into the Ours panel, Close it, tick something, then tap the pill again.</t>
         </is>
       </c>
       <c r="F378" s="9" t="inlineStr">
         <is>
-          <t>The panel and its Add button stay visible above the keyboard while you type. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
+          <t>The pill shows '+' and three dots while words wait, and the half sentence is still there. The panel is always mounted, never unmounted. Only an Add resets the door; the words never reset on their own.</t>
         </is>
       </c>
       <c r="G378" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H378" s="7" t="inlineStr"/>
@@ -15854,7 +15854,7 @@
     <row r="379">
       <c r="A379" s="6" t="inlineStr">
         <is>
-          <t>OUR-61</t>
+          <t>OUR-60</t>
         </is>
       </c>
       <c r="B379" s="7" t="inlineStr">
@@ -15862,29 +15862,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C379" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C379" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D379" s="9" t="inlineStr">
         <is>
-          <t>No AI on the shared capture</t>
+          <t>The Ours panel rides above the keyboard</t>
         </is>
       </c>
       <c r="E379" s="9" t="inlineStr">
         <is>
-          <t>Open the Ours capture panel with AI enabled in Settings, and type a long run-on line.</t>
+          <t>On a real Android device, tap the + pill on the Ours list, tap the box and start typing.</t>
         </is>
       </c>
       <c r="F379" s="9" t="inlineStr">
         <is>
-          <t>No 'Break it down', no 'Sort for me', and no 'Tidy this into tasks': steps or rewrites a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
+          <t>The panel and its Add button stay visible above the keyboard while you type. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
         </is>
       </c>
       <c r="G379" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H379" s="7" t="inlineStr"/>
@@ -15894,7 +15894,7 @@
     <row r="380">
       <c r="A380" s="6" t="inlineStr">
         <is>
-          <t>OUR-62</t>
+          <t>OUR-61</t>
         </is>
       </c>
       <c r="B380" s="7" t="inlineStr">
@@ -15902,29 +15902,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C380" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C380" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D380" s="9" t="inlineStr">
         <is>
-          <t>Scan (premium) reaches the shared capture</t>
+          <t>No AI on the shared capture</t>
         </is>
       </c>
       <c r="E380" s="9" t="inlineStr">
         <is>
-          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
+          <t>Open the Ours capture panel with AI enabled in Settings, and type a long run-on line.</t>
         </is>
       </c>
       <c r="F380" s="9" t="inlineStr">
         <is>
-          <t>The panel rises with the words IN its box (keyboard down), not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
+          <t>No 'Break it down', no 'Sort for me', and no 'Tidy this into tasks': steps or rewrites a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
         </is>
       </c>
       <c r="G380" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H380" s="7" t="inlineStr"/>
@@ -15934,7 +15934,7 @@
     <row r="381">
       <c r="A381" s="6" t="inlineStr">
         <is>
-          <t>OUR-63</t>
+          <t>OUR-62</t>
         </is>
       </c>
       <c r="B381" s="7" t="inlineStr">
@@ -15949,22 +15949,22 @@
       </c>
       <c r="D381" s="9" t="inlineStr">
         <is>
-          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
+          <t>Scan (premium) reaches the shared capture</t>
         </is>
       </c>
       <c r="E381" s="9" t="inlineStr">
         <is>
-          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
+          <t>Premium, AI enabled in Settings. Open the Ours capture on a phone. Tap Scan and photograph a handwritten shopping list.</t>
         </is>
       </c>
       <c r="F381" s="9" t="inlineStr">
         <is>
-          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
+          <t>The panel rises with the words IN its box (keyboard down), not on the list. You read them, edit them, and Add them yourself. This is the surface Scan most belongs on: the most photographed list anybody owns is the one on the fridge, and that list is shared by definition.</t>
         </is>
       </c>
       <c r="G381" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H381" s="7" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
     <row r="382">
       <c r="A382" s="6" t="inlineStr">
         <is>
-          <t>OUR-64</t>
+          <t>OUR-63</t>
         </is>
       </c>
       <c r="B382" s="7" t="inlineStr">
@@ -15982,24 +15982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C382" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C382" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D382" s="9" t="inlineStr">
         <is>
-          <t>The photo never reaches the shared list</t>
+          <t>Scan on Ours meets the paywall, tagged apart from Today's</t>
         </is>
       </c>
       <c r="E382" s="9" t="inlineStr">
         <is>
-          <t>Scan something into Ours and Add it. Check the other device.</t>
+          <t>Sign in as a NON-premium user, open the Ours capture, tap Scan.</t>
         </is>
       </c>
       <c r="F382" s="9" t="inlineStr">
         <is>
-          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
+          <t>The premium screen opens, the same one Today's Scan opens. Nothing is scanned and nothing is charged. The gate logs reason 'ocr_ours', not 'ocr': a paywall met on a surface a second person can see is a different moment from one met alone.</t>
         </is>
       </c>
       <c r="G382" s="7" t="inlineStr">
@@ -16014,7 +16014,7 @@
     <row r="383">
       <c r="A383" s="6" t="inlineStr">
         <is>
-          <t>OUR-65</t>
+          <t>OUR-64</t>
         </is>
       </c>
       <c r="B383" s="7" t="inlineStr">
@@ -16022,24 +16022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C383" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C383" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D383" s="9" t="inlineStr">
         <is>
-          <t>Scan is absent when AI is off</t>
+          <t>The photo never reaches the shared list</t>
         </is>
       </c>
       <c r="E383" s="9" t="inlineStr">
         <is>
-          <t>Turn AI off in Settings, then open the Ours capture.</t>
+          <t>Scan something into Ours and Add it. Check the other device.</t>
         </is>
       </c>
       <c r="F383" s="9" t="inlineStr">
         <is>
-          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
+          <t>Your person sees the rows you added and nothing else, exactly as if you had typed them. No image is stored anywhere, shared or otherwise: it is sent to be read, then discarded.</t>
         </is>
       </c>
       <c r="G383" s="7" t="inlineStr">
@@ -16054,7 +16054,7 @@
     <row r="384">
       <c r="A384" s="6" t="inlineStr">
         <is>
-          <t>OUR-66</t>
+          <t>OUR-65</t>
         </is>
       </c>
       <c r="B384" s="7" t="inlineStr">
@@ -16062,24 +16062,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C384" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C384" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D384" s="9" t="inlineStr">
         <is>
-          <t>A repeating shared row appears on BOTH Todays on its day</t>
+          <t>Scan is absent when AI is off</t>
         </is>
       </c>
       <c r="E384" s="9" t="inlineStr">
         <is>
-          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
+          <t>Turn AI off in Settings, then open the Ours capture.</t>
         </is>
       </c>
       <c r="F384" s="9" t="inlineStr">
         <is>
-          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
+          <t>No Scan button, on either screen. Speak stays: it is on-device dictation, not a server call.</t>
         </is>
       </c>
       <c r="G384" s="7" t="inlineStr">
@@ -16094,7 +16094,7 @@
     <row r="385">
       <c r="A385" s="6" t="inlineStr">
         <is>
-          <t>OUR-67</t>
+          <t>OUR-66</t>
         </is>
       </c>
       <c r="B385" s="7" t="inlineStr">
@@ -16109,17 +16109,17 @@
       </c>
       <c r="D385" s="9" t="inlineStr">
         <is>
-          <t>An UNDATED shared row never reaches Today</t>
+          <t>A repeating shared row appears on BOTH Todays on its day</t>
         </is>
       </c>
       <c r="E385" s="9" t="inlineStr">
         <is>
-          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
+          <t>Make a shared task repeat weekly on today's weekday. Open Today on both devices.</t>
         </is>
       </c>
       <c r="F385" s="9" t="inlineStr">
         <is>
-          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
+          <t>It appears on each Today under a 'From Ours' heading, below the day's own tasks. Neither person had to fetch it. This is the answer to 'I do not want to manually decide what gets added to my list for today'.</t>
         </is>
       </c>
       <c r="G385" s="7" t="inlineStr">
@@ -16134,7 +16134,7 @@
     <row r="386">
       <c r="A386" s="6" t="inlineStr">
         <is>
-          <t>OUR-68</t>
+          <t>OUR-67</t>
         </is>
       </c>
       <c r="B386" s="7" t="inlineStr">
@@ -16149,17 +16149,17 @@
       </c>
       <c r="D386" s="9" t="inlineStr">
         <is>
-          <t>Shared rows never make the day look heavier</t>
+          <t>An UNDATED shared row never reaches Today</t>
         </is>
       </c>
       <c r="E386" s="9" t="inlineStr">
         <is>
-          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
+          <t>Add an ordinary shared task with the door left on Anytime. Check Today on both devices.</t>
         </is>
       </c>
       <c r="F386" s="9" t="inlineStr">
         <is>
-          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
+          <t>It is in the room and NOWHERE on Today. This is the load-bearing rule: without it, your person adding eight things to the shopping list makes your morning eight heavier without you agreeing to any of it.</t>
         </is>
       </c>
       <c r="G386" s="7" t="inlineStr">
@@ -16174,7 +16174,7 @@
     <row r="387">
       <c r="A387" s="6" t="inlineStr">
         <is>
-          <t>OUR-69</t>
+          <t>OUR-68</t>
         </is>
       </c>
       <c r="B387" s="7" t="inlineStr">
@@ -16189,17 +16189,17 @@
       </c>
       <c r="D387" s="9" t="inlineStr">
         <is>
-          <t>Ticking a shared row from Today closes it for both</t>
+          <t>Shared rows never make the day look heavier</t>
         </is>
       </c>
       <c r="E387" s="9" t="inlineStr">
         <is>
-          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
+          <t>With several shared rows showing on Today, check the weight gauge, Plan my day, Lighten, and the close-the-day count.</t>
         </is>
       </c>
       <c r="F387" s="9" t="inlineStr">
         <is>
-          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
+          <t>All of them ignore the shared rows entirely. They are not in `tasks`, so they cannot reach any of it by construction. The day the app promises is finite stays finite.</t>
         </is>
       </c>
       <c r="G387" s="7" t="inlineStr">
@@ -16214,7 +16214,7 @@
     <row r="388">
       <c r="A388" s="6" t="inlineStr">
         <is>
-          <t>OUR-70</t>
+          <t>OUR-69</t>
         </is>
       </c>
       <c r="B388" s="7" t="inlineStr">
@@ -16222,24 +16222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C388" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C388" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D388" s="9" t="inlineStr">
         <is>
-          <t>A dated shared row shows from its day onward, never before</t>
+          <t>Ticking a shared row from Today closes it for both</t>
         </is>
       </c>
       <c r="E388" s="9" t="inlineStr">
         <is>
-          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
+          <t>Tick a row in the From Ours strip on device A. Look at device B's Ours list and Today.</t>
         </is>
       </c>
       <c r="F388" s="9" t="inlineStr">
         <is>
-          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
+          <t>Done on both, within a poll. Nothing anywhere says who did it, and neither room tints it as a stranger's change on the device that did it (noteOursMine).</t>
         </is>
       </c>
       <c r="G388" s="7" t="inlineStr">
@@ -16254,7 +16254,7 @@
     <row r="389">
       <c r="A389" s="6" t="inlineStr">
         <is>
-          <t>OUR-71</t>
+          <t>OUR-70</t>
         </is>
       </c>
       <c r="B389" s="7" t="inlineStr">
@@ -16262,24 +16262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C389" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C389" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D389" s="9" t="inlineStr">
         <is>
-          <t>The shared capture rests on Anytime, and says what a day means</t>
+          <t>A dated shared row shows from its day onward, never before</t>
         </is>
       </c>
       <c r="E389" s="9" t="inlineStr">
         <is>
-          <t>Tap the + pill on Ours and read the line beside the When chip. Open the door. Pick Today, then Tomorrow, then Daily, reading that line each time.</t>
+          <t>Add a shared task with the door set to a date two days out. Check Today now, then on the day.</t>
         </is>
       </c>
       <c r="F389" s="9" t="inlineStr">
         <is>
-          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected, and the Add button says just 'Add'. Choosing Today makes it read 'Add · Today', because that is the notable case: it will appear on both your days. The line beside the chip says, in plain words, what the current choice means on a shared list (no day lives here; a day reaches both Todays; a rhythm repeats for both of you), before you add.</t>
+          <t>Absent today, present on the day and on any day after (a shared thing nobody did does not stop being one). The room shows its date on the row all along, so it is never a surprise.</t>
         </is>
       </c>
       <c r="G389" s="7" t="inlineStr">
@@ -16294,7 +16294,7 @@
     <row r="390">
       <c r="A390" s="6" t="inlineStr">
         <is>
-          <t>OUR-112</t>
+          <t>OUR-71</t>
         </is>
       </c>
       <c r="B390" s="7" t="inlineStr">
@@ -16309,17 +16309,17 @@
       </c>
       <c r="D390" s="9" t="inlineStr">
         <is>
-          <t>A shared row's WHEN can be changed, and cleared</t>
+          <t>The shared capture rests on Anytime, and says what a day means</t>
         </is>
       </c>
       <c r="E390" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
+          <t>Tap the + pill on Ours and read the line beside the When chip. Open the door. Pick Today, then Tomorrow, then Daily, reading that line each time.</t>
         </is>
       </c>
       <c r="F390" s="9" t="inlineStr">
         <is>
-          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
+          <t>The When row reads Anytime / Today / Tomorrow / Pick a date, with Anytime selected, and the Add button says just 'Add'. Choosing Today makes it read 'Add · Today', because that is the notable case: it will appear on both your days. The line beside the chip says, in plain words, what the current choice means on a shared list (no day lives here; a day reaches both Todays; a rhythm repeats for both of you), before you add.</t>
         </is>
       </c>
       <c r="G390" s="7" t="inlineStr">
@@ -16334,7 +16334,7 @@
     <row r="391">
       <c r="A391" s="6" t="inlineStr">
         <is>
-          <t>OUR-113</t>
+          <t>OUR-112</t>
         </is>
       </c>
       <c r="B391" s="7" t="inlineStr">
@@ -16349,17 +16349,17 @@
       </c>
       <c r="D391" s="9" t="inlineStr">
         <is>
-          <t>Ending a rhythm does NOT mark the row done for both people</t>
+          <t>A shared row's WHEN can be changed, and cleared</t>
         </is>
       </c>
       <c r="E391" s="9" t="inlineStr">
         <is>
-          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
+          <t>In the room, hold a row. The door reads 'When…' with the row's current answer beside it. Open it. Set a date, Set. Reopen, pick a different date, Set. Reopen, tap Anytime, Set.</t>
         </is>
       </c>
       <c r="F391" s="9" t="inlineStr">
         <is>
-          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
+          <t>All three land: date set, date CHANGED, and back to plain. Changing a date and getting back to a plain row were both impossible before this; remove-and-recreate was the only way out, and on a repeat that ends the series for both people. The button always names the outcome ('Set . Thu 20 Aug', 'Set . Anytime'), never 'Save'.</t>
         </is>
       </c>
       <c r="G391" s="7" t="inlineStr">
@@ -16374,7 +16374,7 @@
     <row r="392">
       <c r="A392" s="6" t="inlineStr">
         <is>
-          <t>OUR-114</t>
+          <t>OUR-113</t>
         </is>
       </c>
       <c r="B392" s="7" t="inlineStr">
@@ -16382,24 +16382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C392" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C392" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D392" s="9" t="inlineStr">
         <is>
-          <t>The day zone changes its question when a rhythm is alive</t>
+          <t>Ending a rhythm does NOT mark the row done for both people</t>
         </is>
       </c>
       <c r="E392" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
+          <t>Make a shared row repeat weekly and tick it on one of its days, on either device. Then hold it, open When…, tap the selected rhythm chip to release it, choose Anytime, and Set. Watch BOTH devices.</t>
         </is>
       </c>
       <c r="F392" s="9" t="inlineStr">
         <is>
-          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
+          <t>The row goes plain and stays UN-ticked on both. It must not come back done. A repeat's ticks live per-date in a completion log and the row's own done flag stays false; the moment the recurrence goes, the merge would read that same log as a one-off's tick and mark the row finished, for both people, with a doneAt from whenever it was last ticked. Try it for a DATED ending too (release the rhythm, pick a day): that path feels least like an ending and is the easiest to get wrong.</t>
         </is>
       </c>
       <c r="G392" s="7" t="inlineStr">
@@ -16414,7 +16414,7 @@
     <row r="393">
       <c r="A393" s="6" t="inlineStr">
         <is>
-          <t>OUR-115</t>
+          <t>OUR-114</t>
         </is>
       </c>
       <c r="B393" s="7" t="inlineStr">
@@ -16429,17 +16429,17 @@
       </c>
       <c r="D393" s="9" t="inlineStr">
         <is>
-          <t>Setting a shared row to Today actually reaches both Todays</t>
+          <t>The day zone changes its question when a rhythm is alive</t>
         </is>
       </c>
       <c r="E393" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
+          <t>In the room, hold a row and open When…. With no rhythm selected, read the label above the day chips. Now tap Daily. Read it again. Then tap Anytime.</t>
         </is>
       </c>
       <c r="F393" s="9" t="inlineStr">
         <is>
-          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
+          <t>It reads 'A day' with no rhythm, and relabels to 'Starting' the moment one is selected, in the accent colour. The same chips now mean 'from when' rather than 'which day'. Anytime stays available throughout, and ONE tap on it ends the rhythm: the label goes back to 'A day' and the summary says 'The rhythm ends.' before anything commits. Tapping the selected rhythm chip releases it too, for anyone who finds that natural, and both routes land in exactly the same place.</t>
         </is>
       </c>
       <c r="G393" s="7" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="394">
       <c r="A394" s="6" t="inlineStr">
         <is>
-          <t>OUR-116</t>
+          <t>OUR-115</t>
         </is>
       </c>
       <c r="B394" s="7" t="inlineStr">
@@ -16462,24 +16462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C394" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C394" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D394" s="9" t="inlineStr">
         <is>
-          <t>An idle Set does not wash the row on the other device</t>
+          <t>Setting a shared row to Today actually reaches both Todays</t>
         </is>
       </c>
       <c r="E394" s="9" t="inlineStr">
         <is>
-          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
+          <t>In the room, hold a plain row, open When…, tap Today, and Set. Check BOTH Todays (look away and back on each).</t>
         </is>
       </c>
       <c r="F394" s="9" t="inlineStr">
         <is>
-          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
+          <t>It appears under DUE TODAY on both. The line in the sheet reads 'Today . &lt;the date&gt;' on purpose: a shared row with no date reaches nobody, so Today has to write a real date rather than 'no date', which is the same bug that once shipped on the shared capture bar above this sheet.</t>
         </is>
       </c>
       <c r="G394" s="7" t="inlineStr">
@@ -16494,7 +16494,7 @@
     <row r="395">
       <c r="A395" s="6" t="inlineStr">
         <is>
-          <t>OUR-118</t>
+          <t>OUR-116</t>
         </is>
       </c>
       <c r="B395" s="7" t="inlineStr">
@@ -16502,24 +16502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C395" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C395" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D395" s="9" t="inlineStr">
         <is>
-          <t>A repeat you have already done today keeps its held card</t>
+          <t>An idle Set does not wash the row on the other device</t>
         </is>
       </c>
       <c r="E395" s="9" t="inlineStr">
         <is>
-          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
+          <t>On A, hold a row, open When…, change nothing, and tap Set. On B, leave the room and come back.</t>
         </is>
       </c>
       <c r="F395" s="9" t="inlineStr">
         <is>
-          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
+          <t>No 'changed since you looked' mark on B. Every write stamps the row, and a fresh stamp is exactly what the other person's screen reads as a change, so a Set that altered nothing would send them hunting for something nobody did.</t>
         </is>
       </c>
       <c r="G395" s="7" t="inlineStr">
@@ -16534,7 +16534,7 @@
     <row r="396">
       <c r="A396" s="6" t="inlineStr">
         <is>
-          <t>OUR-117</t>
+          <t>OUR-118</t>
         </is>
       </c>
       <c r="B396" s="7" t="inlineStr">
@@ -16542,24 +16542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C396" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C396" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D396" s="9" t="inlineStr">
         <is>
-          <t>The Repeating room's Edit sheet is untouched by the When editor</t>
+          <t>A repeat you have already done today keeps its held card</t>
         </is>
       </c>
       <c r="E396" s="9" t="inlineStr">
         <is>
-          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
+          <t>In the room, make a row repeat on TODAY's weekday, then tick it. Now hold it.</t>
         </is>
       </c>
       <c r="F396" s="9" t="inlineStr">
         <is>
-          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the Repeating room.</t>
+          <t>The card still offers When… with its rhythm beside it, and it does NOT say 'Done is done.' A repeat is not a finished thing: it comes back, so the day you did it is exactly a day you might want to move it. Before this, ticking a repeat took its whole held card away until the next day, which put the When editor out of reach on the rows most likely to need it. A finished ONE-OFF still gets the minimal card, which is correct.</t>
         </is>
       </c>
       <c r="G396" s="7" t="inlineStr">
@@ -16574,7 +16574,7 @@
     <row r="397">
       <c r="A397" s="6" t="inlineStr">
         <is>
-          <t>OUR-119</t>
+          <t>OUR-117</t>
         </is>
       </c>
       <c r="B397" s="7" t="inlineStr">
@@ -16589,17 +16589,17 @@
       </c>
       <c r="D397" s="9" t="inlineStr">
         <is>
-          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
+          <t>The Repeating room's Edit sheet is untouched by the When editor</t>
         </is>
       </c>
       <c r="E397" s="9" t="inlineStr">
         <is>
-          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
+          <t>Menu -&gt; Repeating -&gt; Edit on any series. Compare with before.</t>
         </is>
       </c>
       <c r="F397" s="9" t="inlineStr">
         <is>
-          <t>Monthly is the fourth rhythm chip here too, from the same sheet the Repeating room uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
+          <t>Same sheet as always: title, the four cadence chips (Daily / Weekly / Every few days / Monthly), weekday toggles or the stepper or the 1-31 grid, 'Starting from' with its date, and a commit button naming the cadence. NO Anytime chip, NO day zone, and tapping the selected cadence chip does NOT release it. 'No rhythm' there would mean the entry should not exist, which is removal, and removal stays in the Repeating room.</t>
         </is>
       </c>
       <c r="G397" s="7" t="inlineStr">
@@ -16614,7 +16614,7 @@
     <row r="398">
       <c r="A398" s="6" t="inlineStr">
         <is>
-          <t>OUR-111</t>
+          <t>OUR-119</t>
         </is>
       </c>
       <c r="B398" s="7" t="inlineStr">
@@ -16622,24 +16622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C398" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C398" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D398" s="9" t="inlineStr">
         <is>
-          <t>A finished dated shared row leaves both Todays the next day</t>
+          <t>Monthly works on a shared row, and an out-of-date partner still sees the rhythm</t>
         </is>
       </c>
       <c r="E398" s="9" t="inlineStr">
         <is>
-          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
+          <t>On Ours, hold a row and tap 'Repeat…'. Choose Monthly and a day. Read the summary, commit, then look at the row and at both Todays on that day. If a partner is on an older build (1.3.1 or earlier), have them look at the same row.</t>
         </is>
       </c>
       <c r="F398" s="9" t="inlineStr">
         <is>
-          <t>Today: still there on BOTH, ticked, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
+          <t>Monthly is the fourth rhythm chip here too, from the same sheet the Repeating room uses, so a shared monthly row and a personal one are identical in shape. The summary reads 'Every month on the 15th · from {start}' and the commit button names it. The row lands on BOTH Todays on that day. A partner whose build predates monthly cannot compute the days, so their app shows the row with the plain-English line the writing client left alongside the rhythm rather than showing a repeating row with no rhythm at all. What it must never do is HIDE the row: one person seeing a task the other does not is the invisible disagreement this whole feature exists to prevent.</t>
         </is>
       </c>
       <c r="G398" s="7" t="inlineStr">
@@ -16654,7 +16654,7 @@
     <row r="399">
       <c r="A399" s="6" t="inlineStr">
         <is>
-          <t>OUR-72</t>
+          <t>OUR-111</t>
         </is>
       </c>
       <c r="B399" s="7" t="inlineStr">
@@ -16662,24 +16662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C399" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C399" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D399" s="9" t="inlineStr">
         <is>
-          <t>A repeat supersedes the day rather than joining it</t>
+          <t>A finished dated shared row leaves both Todays the next day</t>
         </is>
       </c>
       <c r="E399" s="9" t="inlineStr">
         <is>
-          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
+          <t>Give a shared row today's date so it appears under DUE TODAY on both phones. Tick it on either phone. Look at both Todays now, then again tomorrow (or move a device's clock forward a day and reopen).</t>
         </is>
       </c>
       <c r="F399" s="9" t="inlineStr">
         <is>
-          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
+          <t>Today: still there on BOTH, ticked, and un-tickable again, because ticking is the reversible act on this list. Tomorrow: gone from both. It must not accumulate. Before this rule the strip kept every dated row either of you had ever ticked, for good, on a screen excluded from the weight gauge and the close-the-day count, whose whole premise is that a day is finite. Check the other half too: an UNFINISHED row with a past date is still there tomorrow, which is correct and is not shaming.</t>
         </is>
       </c>
       <c r="G399" s="7" t="inlineStr">
@@ -16694,7 +16694,7 @@
     <row r="400">
       <c r="A400" s="6" t="inlineStr">
         <is>
-          <t>OUR-73</t>
+          <t>OUR-72</t>
         </is>
       </c>
       <c r="B400" s="7" t="inlineStr">
@@ -16702,24 +16702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C400" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C400" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D400" s="9" t="inlineStr">
         <is>
-          <t>An unreadable cadence is never placed on a day</t>
+          <t>A repeat supersedes the day rather than joining it</t>
         </is>
       </c>
       <c r="E400" s="9" t="inlineStr">
         <is>
-          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
+          <t>On the Ours capture, set a Daily repeat with When left on Anytime.</t>
         </is>
       </c>
       <c r="F400" s="9" t="inlineStr">
         <is>
-          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
+          <t>The door summary reads 'Daily', not 'Anytime . Daily'. On Today's own capture it still reads 'Today . Daily', where the when genuinely IS the repeat's start.</t>
         </is>
       </c>
       <c r="G400" s="7" t="inlineStr">
@@ -16734,7 +16734,7 @@
     <row r="401">
       <c r="A401" s="6" t="inlineStr">
         <is>
-          <t>OUR-74</t>
+          <t>OUR-73</t>
         </is>
       </c>
       <c r="B401" s="7" t="inlineStr">
@@ -16742,24 +16742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C401" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C401" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D401" s="9" t="inlineStr">
         <is>
-          <t>The heading's '!' says something changed since you looked, and clears when you look</t>
+          <t>An unreadable cadence is never placed on a day</t>
         </is>
       </c>
       <c r="E401" s="9" t="inlineStr">
         <is>
-          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap the list's name in the heading and come back. Also have device B delete a row and check again.</t>
+          <t>Have a newer build write a cadence this build cannot parse, then open Today.</t>
         </is>
       </c>
       <c r="F401" s="9" t="inlineStr">
         <is>
-          <t>A small tinted '!' sits beside the list's name in Today's heading, and a screen reader hears '{name}. 1 since you looked'. After visiting, it is gone. A deleted row never raises it. The mark is bounded by your own attention, not by the list's length, and it never shows a climbing number.</t>
+          <t>It shows in the room (never invisible to the person who set it) and appears on NO Today. This build cannot know which days it means, and a wrong day on a shared surface is a thing the other person has to puzzle over.</t>
         </is>
       </c>
       <c r="G401" s="7" t="inlineStr">
@@ -16774,7 +16774,7 @@
     <row r="402">
       <c r="A402" s="6" t="inlineStr">
         <is>
-          <t>OUR-75</t>
+          <t>OUR-74</t>
         </is>
       </c>
       <c r="B402" s="7" t="inlineStr">
@@ -16782,24 +16782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C402" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C402" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D402" s="9" t="inlineStr">
         <is>
-          <t>Your OWN changes never raise the '!'</t>
+          <t>The heading's '!' says something changed since you looked, and clears when you look</t>
         </is>
       </c>
       <c r="E402" s="9" t="inlineStr">
         <is>
-          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
+          <t>Device B changes something on the shared list. On device A, open Today WITHOUT visiting Ours. Then tap the list's name in the heading and come back. Also have device B delete a row and check again.</t>
         </is>
       </c>
       <c r="F402" s="9" t="inlineStr">
         <is>
-          <t>No '!' in the heading. It uses the room's own wash arithmetic, so the heading and the room always agree about whose change it was.</t>
+          <t>A small tinted '!' sits beside the list's name in Today's heading, and a screen reader hears '{name}. 1 since you looked'. After visiting, it is gone. A deleted row never raises it. The mark is bounded by your own attention, not by the list's length, and it never shows a climbing number.</t>
         </is>
       </c>
       <c r="G402" s="7" t="inlineStr">
@@ -16814,7 +16814,7 @@
     <row r="403">
       <c r="A403" s="6" t="inlineStr">
         <is>
-          <t>OUR-76</t>
+          <t>OUR-75</t>
         </is>
       </c>
       <c r="B403" s="7" t="inlineStr">
@@ -16829,17 +16829,17 @@
       </c>
       <c r="D403" s="9" t="inlineStr">
         <is>
-          <t>A first-ever visit raises nothing</t>
+          <t>Your OWN changes never raise the '!'</t>
         </is>
       </c>
       <c r="E403" s="9" t="inlineStr">
         <is>
-          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
+          <t>On device A, add or tick several shared rows. Go to Today on the SAME device.</t>
         </is>
       </c>
       <c r="F403" s="9" t="inlineStr">
         <is>
-          <t>No '!'. There is no 'last looked' to measure against, and inventing one would open the app with a mark already on it.</t>
+          <t>No '!' in the heading. It uses the room's own wash arithmetic, so the heading and the room always agree about whose change it was.</t>
         </is>
       </c>
       <c r="G403" s="7" t="inlineStr">
@@ -16854,7 +16854,7 @@
     <row r="404">
       <c r="A404" s="6" t="inlineStr">
         <is>
-          <t>OUR-77</t>
+          <t>OUR-76</t>
         </is>
       </c>
       <c r="B404" s="7" t="inlineStr">
@@ -16862,24 +16862,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C404" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C404" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D404" s="9" t="inlineStr">
         <is>
-          <t>The capture's AI note names only what that surface HAS</t>
+          <t>A first-ever visit raises nothing</t>
         </is>
       </c>
       <c r="E404" s="9" t="inlineStr">
         <is>
-          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
+          <t>Pair two accounts, put rows on the list from device B, and open Today on a device A that has never opened the room.</t>
         </is>
       </c>
       <c r="F404" s="9" t="inlineStr">
         <is>
-          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
+          <t>No '!'. There is no 'last looked' to measure against, and inventing one would open the app with a mark already on it.</t>
         </is>
       </c>
       <c r="G404" s="7" t="inlineStr">
@@ -16894,7 +16894,7 @@
     <row r="405">
       <c r="A405" s="6" t="inlineStr">
         <is>
-          <t>OUR-78</t>
+          <t>OUR-77</t>
         </is>
       </c>
       <c r="B405" s="7" t="inlineStr">
@@ -16909,17 +16909,17 @@
       </c>
       <c r="D405" s="9" t="inlineStr">
         <is>
-          <t>Scan discloses on every path that can reach a camera</t>
+          <t>The capture's AI note names only what that surface HAS</t>
         </is>
       </c>
       <c r="E405" s="9" t="inlineStr">
         <is>
-          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
+          <t>Type into the Ours capture, then into Today's, and read the line under the buttons.</t>
         </is>
       </c>
       <c r="F405" s="9" t="inlineStr">
         <is>
-          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
+          <t>Ours says Scan sends your photo. Today says Sort for me, Break it down and Scan send what you type or photograph. Ours must NEVER name Sort for me or Break it down: neither button is there, and a false claim about where your data goes teaches people the disclosure is decorative.</t>
         </is>
       </c>
       <c r="G405" s="7" t="inlineStr">
@@ -16934,7 +16934,7 @@
     <row r="406">
       <c r="A406" s="6" t="inlineStr">
         <is>
-          <t>OUR-79</t>
+          <t>OUR-78</t>
         </is>
       </c>
       <c r="B406" s="7" t="inlineStr">
@@ -16949,17 +16949,17 @@
       </c>
       <c r="D406" s="9" t="inlineStr">
         <is>
-          <t>Press and hold a From Ours row on Today</t>
+          <t>Scan discloses on every path that can reach a camera</t>
         </is>
       </c>
       <c r="E406" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Ours strip.</t>
+          <t>Open Scan on web (gallery picker) and on Android with the camera already allowed.</t>
         </is>
       </c>
       <c r="F406" s="9" t="inlineStr">
         <is>
-          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
+          <t>Both show the egress line. It used to appear only on the Android permission screen, so the two paths a person can reach WITHOUT a prompt sent a photograph having said nothing.</t>
         </is>
       </c>
       <c r="G406" s="7" t="inlineStr">
@@ -16974,7 +16974,7 @@
     <row r="407">
       <c r="A407" s="6" t="inlineStr">
         <is>
-          <t>OUR-80</t>
+          <t>OUR-79</t>
         </is>
       </c>
       <c r="B407" s="7" t="inlineStr">
@@ -16989,17 +16989,17 @@
       </c>
       <c r="D407" s="9" t="inlineStr">
         <is>
-          <t>Pin and Move-to never rearrange the other person's day</t>
+          <t>Press and hold a From Ours row on Today</t>
         </is>
       </c>
       <c r="E407" s="9" t="inlineStr">
         <is>
-          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
+          <t>Hold a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F407" s="9" t="inlineStr">
         <is>
-          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
+          <t>The held card opens with Pin and, on a non-repeating row, Move to. Choosing either TAKES THE ROW ON as your own copy: it leaves the strip and joins your day, where the ordinary reorder and the rest of the held card already work.</t>
         </is>
       </c>
       <c r="G407" s="7" t="inlineStr">
@@ -17014,7 +17014,7 @@
     <row r="408">
       <c r="A408" s="6" t="inlineStr">
         <is>
-          <t>OUR-81</t>
+          <t>OUR-80</t>
         </is>
       </c>
       <c r="B408" s="7" t="inlineStr">
@@ -17022,24 +17022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C408" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C408" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D408" s="9" t="inlineStr">
         <is>
-          <t>A taken-on row is never on screen twice</t>
+          <t>Pin and Move-to never rearrange the other person's day</t>
         </is>
       </c>
       <c r="E408" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
+          <t>Move a shared row to tomorrow from your Today. Check the other device.</t>
         </is>
       </c>
       <c r="F408" s="9" t="inlineStr">
         <is>
-          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
+          <t>YOUR copy moves to tomorrow. The shared row is untouched and still on her day. Applied to the shared row itself this would silently take it off her Wednesday too, on a thing she may have planned around.</t>
         </is>
       </c>
       <c r="G408" s="7" t="inlineStr">
@@ -17054,7 +17054,7 @@
     <row r="409">
       <c r="A409" s="6" t="inlineStr">
         <is>
-          <t>OUR-82</t>
+          <t>OUR-81</t>
         </is>
       </c>
       <c r="B409" s="7" t="inlineStr">
@@ -17069,17 +17069,17 @@
       </c>
       <c r="D409" s="9" t="inlineStr">
         <is>
-          <t>Move-to is not offered on a repeating shared row</t>
+          <t>A taken-on row is never on screen twice</t>
         </is>
       </c>
       <c r="E409" s="9" t="inlineStr">
         <is>
-          <t>Hold a repeating row in the From Ours strip.</t>
+          <t>Take a shared row on (Pin it, or Bring it from the room). Look at Today.</t>
         </is>
       </c>
       <c r="F409" s="9" t="inlineStr">
         <is>
-          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
+          <t>It appears once, as your task, and NOT also in the From Ours strip. Still true once it is ticked: a finished copy and its finished origin must not both render.</t>
         </is>
       </c>
       <c r="G409" s="7" t="inlineStr">
@@ -17094,7 +17094,7 @@
     <row r="410">
       <c r="A410" s="6" t="inlineStr">
         <is>
-          <t>OUR-83</t>
+          <t>OUR-82</t>
         </is>
       </c>
       <c r="B410" s="7" t="inlineStr">
@@ -17102,24 +17102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C410" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C410" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D410" s="9" t="inlineStr">
         <is>
-          <t>One shared row, one route onto your day</t>
+          <t>Move-to is not offered on a repeating shared row</t>
         </is>
       </c>
       <c r="E410" s="9" t="inlineStr">
         <is>
-          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
+          <t>Hold a repeating row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F410" s="9" t="inlineStr">
         <is>
-          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
+          <t>Pin is there, Move to is not. A date and a rhythm are alternatives, and rescheduling a series is a question for the room's cadence sheet, not a one-tap action on a day.</t>
         </is>
       </c>
       <c r="G410" s="7" t="inlineStr">
@@ -17134,7 +17134,7 @@
     <row r="411">
       <c r="A411" s="6" t="inlineStr">
         <is>
-          <t>OUR-84</t>
+          <t>OUR-83</t>
         </is>
       </c>
       <c r="B411" s="7" t="inlineStr">
@@ -17149,17 +17149,17 @@
       </c>
       <c r="D411" s="9" t="inlineStr">
         <is>
-          <t>Take a From Ours row on, and it becomes an ordinary task</t>
+          <t>One shared row, one route onto your day</t>
         </is>
       </c>
       <c r="E411" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
+          <t>In the room, hold an UNDATED row, then hold a repeating or dated one.</t>
         </is>
       </c>
       <c r="F411" s="9" t="inlineStr">
         <is>
-          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
+          <t>The undated row offers 'Bring to my Today'. The dated or repeating one does NOT: it already arrives by itself. Two routes landing in two different places (a copy in your list, or the strip) was the confusion Melroy hit twice.</t>
         </is>
       </c>
       <c r="G411" s="7" t="inlineStr">
@@ -17174,7 +17174,7 @@
     <row r="412">
       <c r="A412" s="6" t="inlineStr">
         <is>
-          <t>OUR-85</t>
+          <t>OUR-84</t>
         </is>
       </c>
       <c r="B412" s="7" t="inlineStr">
@@ -17182,24 +17182,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C412" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C412" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D412" s="9" t="inlineStr">
         <is>
-          <t>Break it down works once taken on, and never touches the shared list</t>
+          <t>Take a From Ours row on, and it becomes an ordinary task</t>
         </is>
       </c>
       <c r="E412" s="9" t="inlineStr">
         <is>
-          <t>Take a shared row on, then Break it down.</t>
+          <t>Hold a row in the From Just Us strip and choose 'Take this on today'.</t>
         </is>
       </c>
       <c r="F412" s="9" t="inlineStr">
         <is>
-          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
+          <t>It leaves the strip and joins your list tagged '. Ours'. Holding it now gives the FULL held card: Break it down, Make tiny, Steps, Nudge, reorder, everything. That visible move IS the message: you have taken it on.</t>
         </is>
       </c>
       <c r="G412" s="7" t="inlineStr">
@@ -17214,7 +17214,7 @@
     <row r="413">
       <c r="A413" s="6" t="inlineStr">
         <is>
-          <t>OUR-86</t>
+          <t>OUR-85</t>
         </is>
       </c>
       <c r="B413" s="7" t="inlineStr">
@@ -17222,24 +17222,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C413" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C413" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D413" s="9" t="inlineStr">
         <is>
-          <t>Select several rows in the room and tick them together</t>
+          <t>Break it down works once taken on, and never touches the shared list</t>
         </is>
       </c>
       <c r="E413" s="9" t="inlineStr">
         <is>
-          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
+          <t>Take a shared row on, then Break it down.</t>
         </is>
       </c>
       <c r="F413" s="9" t="inlineStr">
         <is>
-          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
+          <t>The steps land on YOUR copy, on your day. The shared list is unchanged and your person sees nothing new. Breaking down was blocked on the shared row because a model authoring steps onto a list another person reads is a decision about them; on your own copy that objection is gone.</t>
         </is>
       </c>
       <c r="G413" s="7" t="inlineStr">
@@ -17254,7 +17254,7 @@
     <row r="414">
       <c r="A414" s="6" t="inlineStr">
         <is>
-          <t>OUR-87</t>
+          <t>OUR-86</t>
         </is>
       </c>
       <c r="B414" s="7" t="inlineStr">
@@ -17269,17 +17269,17 @@
       </c>
       <c r="D414" s="9" t="inlineStr">
         <is>
-          <t>Bulk tick never UN-ticks</t>
+          <t>Select several rows in the room and tick them together</t>
         </is>
       </c>
       <c r="E414" s="9" t="inlineStr">
         <is>
-          <t>Select a mix of done and not-done rows and tap Done.</t>
+          <t>Hold a row, choose Select more, tap a few more, then Done.</t>
         </is>
       </c>
       <c r="F414" s="9" t="inlineStr">
         <is>
-          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
+          <t>All of them tick at once and reach the other device. This is the trip-to-the-shops case: six things bought, six taps was a tax that stops people keeping the list.</t>
         </is>
       </c>
       <c r="G414" s="7" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="415">
       <c r="A415" s="6" t="inlineStr">
         <is>
-          <t>OUR-88</t>
+          <t>OUR-87</t>
         </is>
       </c>
       <c r="B415" s="7" t="inlineStr">
@@ -17309,17 +17309,17 @@
       </c>
       <c r="D415" s="9" t="inlineStr">
         <is>
-          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
+          <t>Bulk tick never UN-ticks</t>
         </is>
       </c>
       <c r="E415" s="9" t="inlineStr">
         <is>
-          <t>Select a repeating row along with others. Read the shelf.</t>
+          <t>Select a mix of done and not-done rows and tap Done.</t>
         </is>
       </c>
       <c r="F415" s="9" t="inlineStr">
         <is>
-          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
+          <t>The not-done ones tick. The already-done ones are untouched. A bulk toggle would silently undo somebody's finished work on a mixed selection.</t>
         </is>
       </c>
       <c r="G415" s="7" t="inlineStr">
@@ -17334,7 +17334,7 @@
     <row r="416">
       <c r="A416" s="6" t="inlineStr">
         <is>
-          <t>OUR-89</t>
+          <t>OUR-88</t>
         </is>
       </c>
       <c r="B416" s="7" t="inlineStr">
@@ -17342,24 +17342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C416" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C416" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D416" s="9" t="inlineStr">
         <is>
-          <t>The pill steps aside for the select shelf</t>
+          <t>Bulk remove warns BEFORE the tap when a repeat is selected</t>
         </is>
       </c>
       <c r="E416" s="9" t="inlineStr">
         <is>
-          <t>Enter select mode in the room with a few words waiting in the capture panel.</t>
+          <t>Select a repeating row along with others. Read the shelf.</t>
         </is>
       </c>
       <c r="F416" s="9" t="inlineStr">
         <is>
-          <t>The pill is gone while selecting (the select shelf docks at the foot), and back when you cancel, still showing its waiting words. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
+          <t>A line says removing a repeat here ends it for both of you. A shared list has no per-day skip, so this is not a thing to learn from the consequence.</t>
         </is>
       </c>
       <c r="G416" s="7" t="inlineStr">
@@ -17374,7 +17374,7 @@
     <row r="417">
       <c r="A417" s="6" t="inlineStr">
         <is>
-          <t>OUR-90</t>
+          <t>OUR-89</t>
         </is>
       </c>
       <c r="B417" s="7" t="inlineStr">
@@ -17382,24 +17382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C417" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C417" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D417" s="9" t="inlineStr">
         <is>
-          <t>No select mode on a closed list</t>
+          <t>The pill steps aside for the select shelf</t>
         </is>
       </c>
       <c r="E417" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list and hold a row.</t>
+          <t>Enter select mode in the room with a few words waiting in the capture panel.</t>
         </is>
       </c>
       <c r="F417" s="9" t="inlineStr">
         <is>
-          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
+          <t>The pill is gone while selecting (the select shelf docks at the foot), and back when you cancel, still showing its waiting words. Two bottom-anchored surfaces competing for the thumb is how a calm screen stops being one, and you are not adding things while you are clearing things.</t>
         </is>
       </c>
       <c r="G417" s="7" t="inlineStr">
@@ -17414,7 +17414,7 @@
     <row r="418">
       <c r="A418" s="6" t="inlineStr">
         <is>
-          <t>OUR-91</t>
+          <t>OUR-90</t>
         </is>
       </c>
       <c r="B418" s="7" t="inlineStr">
@@ -17422,24 +17422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C418" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C418" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D418" s="9" t="inlineStr">
         <is>
-          <t>A copy says when its shared row was taken off the list</t>
+          <t>No select mode on a closed list</t>
         </is>
       </c>
       <c r="E418" s="9" t="inlineStr">
         <is>
-          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
+          <t>Open an archived list and hold a row.</t>
         </is>
       </c>
       <c r="F418" s="9" t="inlineStr">
         <is>
-          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
+          <t>No Select more. A closed list is readable and nothing else, and the server would refuse the write anyway.</t>
         </is>
       </c>
       <c r="G418" s="7" t="inlineStr">
@@ -17454,7 +17454,7 @@
     <row r="419">
       <c r="A419" s="6" t="inlineStr">
         <is>
-          <t>OUR-92</t>
+          <t>OUR-91</t>
         </is>
       </c>
       <c r="B419" s="7" t="inlineStr">
@@ -17469,17 +17469,17 @@
       </c>
       <c r="D419" s="9" t="inlineStr">
         <is>
-          <t>That line never says who, and never says why</t>
+          <t>A copy says when its shared row was taken off the list</t>
         </is>
       </c>
       <c r="E419" s="9" t="inlineStr">
         <is>
-          <t>Read the line closely.</t>
+          <t>Device B removes a row from Ours. On device A, look at the brought copy on Today.</t>
         </is>
       </c>
       <c r="F419" s="9" t="inlineStr">
         <is>
-          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
+          <t>The copy STAYS (it is your task now) and carries a faint line: 'no longer on &lt;list name&gt;'. The deciding case is wasted effort: she removed milk because she already bought it, and a silent copy sends you to the shop.</t>
         </is>
       </c>
       <c r="G419" s="7" t="inlineStr">
@@ -17494,7 +17494,7 @@
     <row r="420">
       <c r="A420" s="6" t="inlineStr">
         <is>
-          <t>OUR-93</t>
+          <t>OUR-92</t>
         </is>
       </c>
       <c r="B420" s="7" t="inlineStr">
@@ -17502,24 +17502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C420" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C420" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D420" s="9" t="inlineStr">
         <is>
-          <t>No line on a copy you already finished or removed</t>
+          <t>That line never says who, and never says why</t>
         </is>
       </c>
       <c r="E420" s="9" t="inlineStr">
         <is>
-          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
+          <t>Read the line closely.</t>
         </is>
       </c>
       <c r="F420" s="9" t="inlineStr">
         <is>
-          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
+          <t>It states the fact only. Not who removed it (no such data exists anywhere in this feature, and a bridge is where that temptation returns) and not why (removal could be done, not-needed or tidying, and the app cannot tell them apart).</t>
         </is>
       </c>
       <c r="G420" s="7" t="inlineStr">
@@ -17534,7 +17534,7 @@
     <row r="421">
       <c r="A421" s="6" t="inlineStr">
         <is>
-          <t>OUR-94</t>
+          <t>OUR-93</t>
         </is>
       </c>
       <c r="B421" s="7" t="inlineStr">
@@ -17542,24 +17542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C421" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C421" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D421" s="9" t="inlineStr">
         <is>
-          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
+          <t>No line on a copy you already finished or removed</t>
         </is>
       </c>
       <c r="E421" s="9" t="inlineStr">
         <is>
-          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
+          <t>Finish your copy, then have B remove the shared row. Then try it with a copy you removed yourself.</t>
         </is>
       </c>
       <c r="F421" s="9" t="inlineStr">
         <is>
-          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
+          <t>No line in either case. You did the thing, so its origin's fate is not news, and a note there would read as a correction.</t>
         </is>
       </c>
       <c r="G421" s="7" t="inlineStr">
@@ -17574,7 +17574,7 @@
     <row r="422">
       <c r="A422" s="6" t="inlineStr">
         <is>
-          <t>OUR-95</t>
+          <t>OUR-94</t>
         </is>
       </c>
       <c r="B422" s="7" t="inlineStr">
@@ -17582,24 +17582,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C422" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C422" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D422" s="9" t="inlineStr">
         <is>
-          <t>A row's note is VISIBLE, not only spoken</t>
+          <t>The line goes quiet after the tombstone sweep, rather than guessing</t>
         </is>
       </c>
       <c r="E422" s="9" t="inlineStr">
         <is>
-          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
+          <t>More than seven days after a removal (or with the tombstone swept), check the copy.</t>
         </is>
       </c>
       <c r="F422" s="9" t="inlineStr">
         <is>
-          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
+          <t>No line. A swept origin is indistinguishable from one never pulled, and keeping a permanent record of a deletion so the app can keep mentioning it is its own kind of creepy. Accepted limit, not a bug.</t>
         </is>
       </c>
       <c r="G422" s="7" t="inlineStr">
@@ -17614,7 +17614,7 @@
     <row r="423">
       <c r="A423" s="6" t="inlineStr">
         <is>
-          <t>OUR-96</t>
+          <t>OUR-95</t>
         </is>
       </c>
       <c r="B423" s="7" t="inlineStr">
@@ -17622,24 +17622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C423" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C423" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D423" s="9" t="inlineStr">
         <is>
-          <t>Rows WITHOUT a note are unchanged</t>
+          <t>A row's note is VISIBLE, not only spoken</t>
         </is>
       </c>
       <c r="E423" s="9" t="inlineStr">
         <is>
-          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
+          <t>Trigger any row note: have B change a row (the room's wash) or remove a shared row you hold a copy of (Today).</t>
         </is>
       </c>
       <c r="F423" s="9" t="inlineStr">
         <is>
-          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
+          <t>The words appear as a quiet second line under the title. Before 2026-08-12 the note prop reached only the accessibility label, so every one of these lines was spoken to screen readers and shown to nobody, for as long as the prop had existed.</t>
         </is>
       </c>
       <c r="G423" s="7" t="inlineStr">
@@ -17654,7 +17654,7 @@
     <row r="424">
       <c r="A424" s="6" t="inlineStr">
         <is>
-          <t>OUR-97</t>
+          <t>OUR-96</t>
         </is>
       </c>
       <c r="B424" s="7" t="inlineStr">
@@ -17662,24 +17662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C424" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C424" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D424" s="9" t="inlineStr">
         <is>
-          <t>A tick after midnight lands on the RIGHT day</t>
+          <t>Rows WITHOUT a note are unchanged</t>
         </is>
       </c>
       <c r="E424" s="9" t="inlineStr">
         <is>
-          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
+          <t>Compare a plain row, a 'big' row and a repeating row against a build before the note landed.</t>
         </is>
       </c>
       <c r="F424" s="9" t="inlineStr">
         <is>
-          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
+          <t>Same height to within a pixel. The note gave TaskRow a second line, and a row that has no note must not gain one, shift, or reflow.</t>
         </is>
       </c>
       <c r="G424" s="7" t="inlineStr">
@@ -17694,7 +17694,7 @@
     <row r="425">
       <c r="A425" s="6" t="inlineStr">
         <is>
-          <t>OUR-98</t>
+          <t>OUR-97</t>
         </is>
       </c>
       <c r="B425" s="7" t="inlineStr">
@@ -17709,17 +17709,17 @@
       </c>
       <c r="D425" s="9" t="inlineStr">
         <is>
-          <t>A tick made during a background sync is not undone</t>
+          <t>A tick after midnight lands on the RIGHT day</t>
         </is>
       </c>
       <c r="E425" s="9" t="inlineStr">
         <is>
-          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
+          <t>Open the room at 23:58 and leave it open. Tick a row at 00:02. Check the partner's device.</t>
         </is>
       </c>
       <c r="F425" s="9" t="inlineStr">
         <is>
-          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
+          <t>Done on both, dated today. The room's date used to freeze at mount, so the completion log took yesterday's key and the partner's phone, asking about today, got false. Permanently: the merge is per-date.</t>
         </is>
       </c>
       <c r="G425" s="7" t="inlineStr">
@@ -17734,7 +17734,7 @@
     <row r="426">
       <c r="A426" s="6" t="inlineStr">
         <is>
-          <t>OUR-99</t>
+          <t>OUR-98</t>
         </is>
       </c>
       <c r="B426" s="7" t="inlineStr">
@@ -17749,17 +17749,17 @@
       </c>
       <c r="D426" s="9" t="inlineStr">
         <is>
-          <t>A tick survives a device that has never opened the room</t>
+          <t>A tick made during a background sync is not undone</t>
         </is>
       </c>
       <c r="E426" s="9" t="inlineStr">
         <is>
-          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
+          <t>Background and reopen the app (which triggers a settle), then immediately tick a row in the From Ours strip.</t>
         </is>
       </c>
       <c r="F426" s="9" t="inlineStr">
         <is>
-          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
+          <t>It stays ticked. The settle now refuses to save a merge that predates any local write made while it was on the wire.</t>
         </is>
       </c>
       <c r="G426" s="7" t="inlineStr">
@@ -17774,7 +17774,7 @@
     <row r="427">
       <c r="A427" s="6" t="inlineStr">
         <is>
-          <t>OUR-100</t>
+          <t>OUR-99</t>
         </is>
       </c>
       <c r="B427" s="7" t="inlineStr">
@@ -17789,17 +17789,17 @@
       </c>
       <c r="D427" s="9" t="inlineStr">
         <is>
-          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
+          <t>A tick survives a device that has never opened the room</t>
         </is>
       </c>
       <c r="E427" s="9" t="inlineStr">
         <is>
-          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
+          <t>On a device with no Ours cache, go offline, tick a brought copy, come back online, reopen the app.</t>
         </is>
       </c>
       <c r="F427" s="9" t="inlineStr">
         <is>
-          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
+          <t>The tick reaches the shared list. It used to be lost forever: the only carrier pulled before writing, and nothing retried. The settle now carries it, with the copy's OWN completion time, so a deliberate un-tick on the other side still wins.</t>
         </is>
       </c>
       <c r="G427" s="7" t="inlineStr">
@@ -17814,7 +17814,7 @@
     <row r="428">
       <c r="A428" s="6" t="inlineStr">
         <is>
-          <t>OUR-101</t>
+          <t>OUR-100</t>
         </is>
       </c>
       <c r="B428" s="7" t="inlineStr">
@@ -17822,24 +17822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C428" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C428" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D428" s="9" t="inlineStr">
         <is>
-          <t>A closed list stops promising it keeps trying</t>
+          <t>A repeat is visible in the room EVERY day, tickable only on its own</t>
         </is>
       </c>
       <c r="E428" s="9" t="inlineStr">
         <is>
-          <t>Open an archived list that has unpushed local changes.</t>
+          <t>Make a weekly shared repeat. Open the room on a day it is not due.</t>
         </is>
       </c>
       <c r="F428" s="9" t="inlineStr">
         <is>
-          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
+          <t>The row is there, with its rhythm in words, and its checkbox is inert with 'you can tick this on its day'. It used to vanish six days a week: unreachable to edit or remove, and a list of only repeats said 'Nothing here yet'.</t>
         </is>
       </c>
       <c r="G428" s="7" t="inlineStr">
@@ -17854,7 +17854,7 @@
     <row r="429">
       <c r="A429" s="6" t="inlineStr">
         <is>
-          <t>OUR-102</t>
+          <t>OUR-101</t>
         </is>
       </c>
       <c r="B429" s="7" t="inlineStr">
@@ -17869,17 +17869,17 @@
       </c>
       <c r="D429" s="9" t="inlineStr">
         <is>
-          <t>Setting a rhythm clears any date the row was carrying</t>
+          <t>A closed list stops promising it keeps trying</t>
         </is>
       </c>
       <c r="E429" s="9" t="inlineStr">
         <is>
-          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
+          <t>Open an archived list that has unpushed local changes.</t>
         </is>
       </c>
       <c r="F429" s="9" t="inlineStr">
         <is>
-          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
+          <t>It says the list is closed, not 'Saved here, not there'. On a list where the write can never succeed, the second is a false hope on a screen a separated or bereaved person may keep for years.</t>
         </is>
       </c>
       <c r="G429" s="7" t="inlineStr">
@@ -17894,7 +17894,7 @@
     <row r="430">
       <c r="A430" s="6" t="inlineStr">
         <is>
-          <t>OUR-103</t>
+          <t>OUR-102</t>
         </is>
       </c>
       <c r="B430" s="7" t="inlineStr">
@@ -17909,17 +17909,17 @@
       </c>
       <c r="D430" s="9" t="inlineStr">
         <is>
-          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
+          <t>Setting a rhythm clears any date the row was carrying</t>
         </is>
       </c>
       <c r="E430" s="9" t="inlineStr">
         <is>
-          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
+          <t>Give a DATED shared row a weekly rhythm, then read the row.</t>
         </is>
       </c>
       <c r="F430" s="9" t="inlineStr">
         <is>
-          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
+          <t>One schedule, not two. The date is gone. Leaving it made the row answer differently depending on which code asked.</t>
         </is>
       </c>
       <c r="G430" s="7" t="inlineStr">
@@ -17934,7 +17934,7 @@
     <row r="431">
       <c r="A431" s="6" t="inlineStr">
         <is>
-          <t>OUR-104</t>
+          <t>OUR-103</t>
         </is>
       </c>
       <c r="B431" s="7" t="inlineStr">
@@ -17942,24 +17942,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C431" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C431" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D431" s="9" t="inlineStr">
         <is>
-          <t>No dead reorder rail on shared rows</t>
+          <t>Renaming inside the cadence sheet warns about the 500-character cap</t>
         </is>
       </c>
       <c r="E431" s="9" t="inlineStr">
         <is>
-          <t>Hold a row in the room and in the From Ours strip.</t>
+          <t>Open a row's rhythm sheet, paste a title over 500 characters, save.</t>
         </is>
       </c>
       <c r="F431" s="9" t="inlineStr">
         <is>
-          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
+          <t>The trim notice appears BEFORE the save, the same as renaming on the row. It used to save silently and the server clamped it, so the words vanished a second later.</t>
         </is>
       </c>
       <c r="G431" s="7" t="inlineStr">
@@ -17974,7 +17974,7 @@
     <row r="432">
       <c r="A432" s="6" t="inlineStr">
         <is>
-          <t>OUR-105</t>
+          <t>OUR-104</t>
         </is>
       </c>
       <c r="B432" s="7" t="inlineStr">
@@ -17982,24 +17982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C432" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C432" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D432" s="9" t="inlineStr">
         <is>
-          <t>First run introduces the shared list</t>
+          <t>No dead reorder rail on shared rows</t>
         </is>
       </c>
       <c r="E432" s="9" t="inlineStr">
         <is>
-          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
+          <t>Hold a row in the room and in the From Ours strip.</t>
         </is>
       </c>
       <c r="F432" s="9" t="inlineStr">
         <is>
-          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
+          <t>No up/down rail. Neither surface supplies those handlers, so it was two permanently inert controls on the screen briefed to be plainer than Today. Dim-in-place is for a control that is sometimes live.</t>
         </is>
       </c>
       <c r="G432" s="7" t="inlineStr">
@@ -18014,7 +18014,7 @@
     <row r="433">
       <c r="A433" s="6" t="inlineStr">
         <is>
-          <t>OUR-106</t>
+          <t>OUR-105</t>
         </is>
       </c>
       <c r="B433" s="7" t="inlineStr">
@@ -18029,17 +18029,17 @@
       </c>
       <c r="D433" s="9" t="inlineStr">
         <is>
-          <t>Anyone can start a shared list, not just an allowlisted address</t>
+          <t>First run introduces the shared list</t>
         </is>
       </c>
       <c r="E433" s="9" t="inlineStr">
         <is>
-          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
+          <t>Reset onboarding (Settings, replay the first run) and step through it.</t>
         </is>
       </c>
       <c r="F433" s="9" t="inlineStr">
         <is>
-          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
+          <t>An eighth step sits between 'keep' and 'premium', headed 'A list the two of you keep.' It says what arrives by itself, what deliberately does NOT, and that nothing keeps score. Its position matters: a FREE feature read immediately before the premium screen would be mistaken for part of the paid list.</t>
         </is>
       </c>
       <c r="G433" s="7" t="inlineStr">
@@ -18054,7 +18054,7 @@
     <row r="434">
       <c r="A434" s="6" t="inlineStr">
         <is>
-          <t>OUR-107</t>
+          <t>OUR-106</t>
         </is>
       </c>
       <c r="B434" s="7" t="inlineStr">
@@ -18069,17 +18069,17 @@
       </c>
       <c r="D434" s="9" t="inlineStr">
         <is>
-          <t>The shared-list onboarding step can actually be REACHED</t>
+          <t>Anyone can start a shared list, not just an allowlisted address</t>
         </is>
       </c>
       <c r="E434" s="9" t="inlineStr">
         <is>
-          <t>Replay the first run and press the primary button through every step without skipping.</t>
+          <t>With supabase/ours-open.sql applied, sign in as an account that was never in ours_allowlist and create an invite.</t>
         </is>
       </c>
       <c r="F434" s="9" t="inlineStr">
         <is>
-          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
+          <t>It works. Before that migration only JOINING was open; STARTING was gated, so the refusal hit exactly the person a store listing brings you.</t>
         </is>
       </c>
       <c r="G434" s="7" t="inlineStr">
@@ -18094,7 +18094,7 @@
     <row r="435">
       <c r="A435" s="6" t="inlineStr">
         <is>
-          <t>OUR-108</t>
+          <t>OUR-107</t>
         </is>
       </c>
       <c r="B435" s="7" t="inlineStr">
@@ -18102,24 +18102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C435" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C435" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D435" s="9" t="inlineStr">
         <is>
-          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
+          <t>The shared-list onboarding step can actually be REACHED</t>
         </is>
       </c>
       <c r="E435" s="9" t="inlineStr">
         <is>
-          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
+          <t>Replay the first run and press the primary button through every step without skipping.</t>
         </is>
       </c>
       <c r="F435" s="9" t="inlineStr">
         <is>
-          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
+          <t>The shared-list screen appears as the sixth of eight, between 'What you finish, you keep' and the premium screen. It shipped once as a step that existed, was translated into five languages, and could not be arrived at: the flow advanced by a hand-written map that still went keep -&gt; premium.</t>
         </is>
       </c>
       <c r="G435" s="7" t="inlineStr">
@@ -18134,7 +18134,7 @@
     <row r="436">
       <c r="A436" s="6" t="inlineStr">
         <is>
-          <t>OUR-109</t>
+          <t>OUR-108</t>
         </is>
       </c>
       <c r="B436" s="7" t="inlineStr">
@@ -18142,24 +18142,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C436" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C436" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D436" s="9" t="inlineStr">
         <is>
-          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
+          <t>ONE person, TWO devices: does your own edit wash on your other phone?</t>
         </is>
       </c>
       <c r="E436" s="9" t="inlineStr">
         <is>
-          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
+          <t>Sign in to the same account on two devices (an iPhone and an Android, say). Change a row in Ours on the FIRST. Open Ours on the SECOND.</t>
         </is>
       </c>
       <c r="F436" s="9" t="inlineStr">
         <is>
-          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
+          <t>OPEN QUESTION, not a known-good expectation. The 'this edit was mine' record is stored PER DEVICE (noteOursMine writes to local storage), so the second device has no idea the first one did it and will most likely tint the row as changed-since-you-looked. It breaks none of the three laws, since the wording never names a person, but it may still read wrong: your own edit wearing the mark that means 'your person did something'. Only reachable when one person holds two phones, which nobody did until 2026-08-13. If it tints, the fix is to key `mine` on the account rather than the device.</t>
         </is>
       </c>
       <c r="G436" s="7" t="inlineStr">
@@ -18174,7 +18174,7 @@
     <row r="437">
       <c r="A437" s="6" t="inlineStr">
         <is>
-          <t>OUR-110</t>
+          <t>OUR-109</t>
         </is>
       </c>
       <c r="B437" s="7" t="inlineStr">
@@ -18189,17 +18189,17 @@
       </c>
       <c r="D437" s="9" t="inlineStr">
         <is>
-          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
+          <t>A repeat's rhythm sits INSIDE its own card and reads as a rhythm</t>
         </is>
       </c>
       <c r="E437" s="9" t="inlineStr">
         <is>
-          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
+          <t>Give a shared task a weekly repeat on a weekday that is not today. Look at it in the room.</t>
         </is>
       </c>
       <c r="F437" s="9" t="inlineStr">
         <is>
-          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
+          <t>The line is indented under that row's title, inside the card, and reads 'Every Thu' rather than a bare 'Thu'. It used to be drawn BELOW the card, so it floated between two rows belonging to neither, and said only the weekday.</t>
         </is>
       </c>
       <c r="G437" s="7" t="inlineStr">
@@ -18214,12 +18214,12 @@
     <row r="438">
       <c r="A438" s="6" t="inlineStr">
         <is>
-          <t>UPD-01</t>
+          <t>OUR-110</t>
         </is>
       </c>
       <c r="B438" s="7" t="inlineStr">
         <is>
-          <t>Updates</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C438" s="8" t="inlineStr">
@@ -18229,17 +18229,17 @@
       </c>
       <c r="D438" s="9" t="inlineStr">
         <is>
-          <t>Settings states the version, and up-to-date is a fact</t>
+          <t>A circle you cannot tick LOOKS like one you cannot tick</t>
         </is>
       </c>
       <c r="E438" s="9" t="inlineStr">
         <is>
-          <t>Open Settings and scroll to the foot.</t>
+          <t>Find that same repeat on a day it is not due, or open any row on a closed list.</t>
         </is>
       </c>
       <c r="F438" s="9" t="inlineStr">
         <is>
-          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
+          <t>The circle is visibly faded. It used to render identically to a live one, so the row offered a control that looked tappable and did nothing, which is the exact failure the 'quiet-unavailable' rule was written to prevent.</t>
         </is>
       </c>
       <c r="G438" s="7" t="inlineStr">
@@ -18254,7 +18254,7 @@
     <row r="439">
       <c r="A439" s="6" t="inlineStr">
         <is>
-          <t>UPD-02</t>
+          <t>UPD-01</t>
         </is>
       </c>
       <c r="B439" s="7" t="inlineStr">
@@ -18269,22 +18269,22 @@
       </c>
       <c r="D439" s="9" t="inlineStr">
         <is>
-          <t>Web offers a reload, and says drafts are kept</t>
+          <t>Settings states the version, and up-to-date is a fact</t>
         </is>
       </c>
       <c r="E439" s="9" t="inlineStr">
         <is>
-          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
+          <t>Open Settings and scroll to the foot.</t>
         </is>
       </c>
       <c r="F439" s="9" t="inlineStr">
         <is>
-          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
+          <t>One line: 'v1.2.0 (11)  ·  Up to date'. It is a sage FACT, not a control. Nothing is offered when there is nothing to offer.</t>
         </is>
       </c>
       <c r="G439" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H439" s="7" t="inlineStr"/>
@@ -18294,7 +18294,7 @@
     <row r="440">
       <c r="A440" s="6" t="inlineStr">
         <is>
-          <t>UPD-03</t>
+          <t>UPD-02</t>
         </is>
       </c>
       <c r="B440" s="7" t="inlineStr">
@@ -18309,22 +18309,22 @@
       </c>
       <c r="D440" s="9" t="inlineStr">
         <is>
-          <t>Native points at the store, and says lists are untouched</t>
+          <t>Web offers a reload, and says drafts are kept</t>
         </is>
       </c>
       <c r="E440" s="9" t="inlineStr">
         <is>
-          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
+          <t>With doubledone.app/version.json's "web" set ahead of the running build, open Settings on the web.</t>
         </is>
       </c>
       <c r="F440" s="9" t="inlineStr">
         <is>
-          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
+          <t>'A newer version is ready.' + 'Reload to get it' + 'Anything you were typing is kept.' Type something into the capture box first and confirm it survives the reload.</t>
         </is>
       </c>
       <c r="G440" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H440" s="7" t="inlineStr"/>
@@ -18334,7 +18334,7 @@
     <row r="441">
       <c r="A441" s="6" t="inlineStr">
         <is>
-          <t>UPD-04</t>
+          <t>UPD-03</t>
         </is>
       </c>
       <c r="B441" s="7" t="inlineStr">
@@ -18342,29 +18342,29 @@
           <t>Updates</t>
         </is>
       </c>
-      <c r="C441" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C441" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D441" s="9" t="inlineStr">
         <is>
-          <t>Unreachable server says NOTHING, never 'up to date'</t>
+          <t>Native points at the store, and says lists are untouched</t>
         </is>
       </c>
       <c r="E441" s="9" t="inlineStr">
         <is>
-          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
+          <t>With version.json's "ios" / "android" set ahead of the installed build, open Settings on a device.</t>
         </is>
       </c>
       <c r="F441" s="9" t="inlineStr">
         <is>
-          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
+          <t>'This build is getting old.' + 'Open the store' + 'Your lists stay exactly as they are.' The button opens the correct store listing.</t>
         </is>
       </c>
       <c r="G441" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H441" s="7" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
     <row r="442">
       <c r="A442" s="6" t="inlineStr">
         <is>
-          <t>UPD-05</t>
+          <t>UPD-04</t>
         </is>
       </c>
       <c r="B442" s="7" t="inlineStr">
@@ -18389,17 +18389,17 @@
       </c>
       <c r="D442" s="9" t="inlineStr">
         <is>
-          <t>The goodnight mention is rare, and framed for the other person</t>
+          <t>Unreachable server says NOTHING, never 'up to date'</t>
         </is>
       </c>
       <c r="E442" s="9" t="inlineStr">
         <is>
-          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
+          <t>Put the device in aeroplane mode and open Settings. Then, online, confirm doubledone.app/version.json returns JSON rather than the app's HTML (the SPA fallback would break it silently).</t>
         </is>
       </c>
       <c r="F442" s="9" t="inlineStr">
         <is>
-          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
+          <t>No update line at all, and no 'Up to date' either: it cannot tell, so it says nothing. No spinner and no error.</t>
         </is>
       </c>
       <c r="G442" s="7" t="inlineStr">
@@ -18414,32 +18414,32 @@
     <row r="443">
       <c r="A443" s="6" t="inlineStr">
         <is>
-          <t>OUR-12</t>
+          <t>UPD-05</t>
         </is>
       </c>
       <c r="B443" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C443" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Updates</t>
+        </is>
+      </c>
+      <c r="C443" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D443" s="9" t="inlineStr">
         <is>
-          <t>Unnamed lists read in each person's language</t>
+          <t>The goodnight mention is rare, and framed for the other person</t>
         </is>
       </c>
       <c r="E443" s="9" t="inlineStr">
         <is>
-          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+          <t>Clear the day with a build two minor versions behind, and reach the rested screen.</t>
         </is>
       </c>
       <c r="F443" s="9" t="inlineStr">
         <is>
-          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+          <t>At most ONE offer shows. If it is the update one it reads 'The newer one can read everything your person sets, rhythms included.' 'Not now' dismisses it and it does not return for a fortnight. It never displaces the reminder, widget or scrapbook offer.</t>
         </is>
       </c>
       <c r="G443" s="7" t="inlineStr">
@@ -18451,9 +18451,49 @@
       <c r="I443" s="9" t="inlineStr"/>
       <c r="J443" s="7" t="inlineStr"/>
     </row>
+    <row r="444">
+      <c r="A444" s="6" t="inlineStr">
+        <is>
+          <t>OUR-12</t>
+        </is>
+      </c>
+      <c r="B444" s="7" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="C444" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D444" s="9" t="inlineStr">
+        <is>
+          <t>Unnamed lists read in each person's language</t>
+        </is>
+      </c>
+      <c r="E444" s="9" t="inlineStr">
+        <is>
+          <t>Create a list WITHOUT naming it. Set the two accounts' devices to different languages (e.g. English and Italian).</t>
+        </is>
+      </c>
+      <c r="F444" s="9" t="inlineStr">
+        <is>
+          <t>Each person sees the app's own word for a shared list in their own language, not the other person's.</t>
+        </is>
+      </c>
+      <c r="G444" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H444" s="7" t="inlineStr"/>
+      <c r="I444" s="9" t="inlineStr"/>
+      <c r="J444" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J443"/>
-  <conditionalFormatting sqref="H2:H443">
+  <autoFilter ref="A1:J444"/>
+  <conditionalFormatting sqref="H2:H444">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -18465,7 +18505,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H443" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
+    <dataValidation sqref="H2:H444" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick Pass, Fail, Blocked or Not run." prompt="Pass / Fail / Blocked / Not run" type="list">
       <formula1>"Pass,Fail,Blocked,Not run"</formula1>
     </dataValidation>
   </dataValidations>
@@ -18501,7 +18541,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>443</t>
         </is>
       </c>
     </row>
@@ -18512,7 +18552,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF('Test Suite'!$H$2:$H$443,"Pass")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$444,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -18523,7 +18563,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF('Test Suite'!$H$2:$H$443,"Fail")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$444,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -18534,7 +18574,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF('Test Suite'!$H$2:$H$443,"Blocked")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$444,"Blocked")</f>
         <v/>
       </c>
     </row>
@@ -18545,7 +18585,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF('Test Suite'!$H$2:$H$443,"Not run")</f>
+        <f>COUNTIF('Test Suite'!$H$2:$H$444,"Not run")</f>
         <v/>
       </c>
     </row>
@@ -18556,7 +18596,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>442-COUNTA('Test Suite'!$H$2:$H$443)</f>
+        <f>443-COUNTA('Test Suite'!$H$2:$H$444)</f>
         <v/>
       </c>
     </row>
@@ -18567,7 +18607,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF('Test Suite'!$C$2:$C$443,"P1")</f>
+        <f>COUNTIF('Test Suite'!$C$2:$C$444,"P1")</f>
         <v/>
       </c>
     </row>
@@ -18578,7 +18618,7 @@
         </is>
       </c>
       <c r="B10">
-        <f>COUNTIFS('Test Suite'!$C$2:$C$443,"P1",'Test Suite'!$H$2:$H$443,"Pass")</f>
+        <f>COUNTIFS('Test Suite'!$C$2:$C$444,"P1",'Test Suite'!$H$2:$H$444,"Pass")</f>
         <v/>
       </c>
     </row>

--- a/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
+++ b/docs/qa/DoubleDone-E2E-Test-Suite.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$444</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Suite'!$A$1:$J$445</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J444"/>
+  <dimension ref="A1:J445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11258,7 +11258,7 @@
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>PREM-29</t>
+          <t>PREM-51</t>
         </is>
       </c>
       <c r="B264" s="7" t="inlineStr">
@@ -11273,22 +11273,22 @@
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>The Android AAB does NOT contain Google Play Billing</t>
+          <t>A Google Play subscriber on the web is told where their subscription lives</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>Build the Android AAB, unzip it, and grep for com.android.billingclient. Also confirm the app still builds and installs, and that Premium is NOT sold on Android (PREM-42).</t>
+          <t>PREREQUISITE: an account with a live Google Play subscription (PREM-50, or a D1 row with source 'google' on a test account). Sign in with it on the web (and, once the next iOS build ships, on an iPhone). Open Premium and tap Manage subscription.</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>react-native-purchases (and Play Billing) is absent from the AAB: the expo.autolinking.android.exclude in client/package.json drops it. Android sells nothing (Path C, 2026-09-27): no price, no Go Premium, no Stripe. This is the regression guard on adding the native module.</t>
+          <t>Premium shows as active. Manage does NOT open Stripe's portal and never says 'Your Premium is on us'. It says the subscription was bought through Google Play and names the Play Store path (profile picture, Payments and subscriptions, Subscriptions), with no link. In all five languages.</t>
         </is>
       </c>
       <c r="G264" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H264" s="7" t="inlineStr"/>
@@ -11298,7 +11298,7 @@
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>PREM-30</t>
+          <t>PREM-29</t>
         </is>
       </c>
       <c r="B265" s="7" t="inlineStr">
@@ -11313,22 +11313,22 @@
       </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
-          <t>The web build is unchanged and still sells via Stripe</t>
+          <t>The Android AAB does NOT contain Google Play Billing</t>
         </is>
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>Build the production web export (expo export --platform web). Open /premium on web.</t>
+          <t>Build the Android AAB, unzip it, and grep for com.android.billingclient. Also confirm the app still builds and installs, and that Premium is NOT sold on Android (PREM-42).</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>The export succeeds (the native purchases module never enters the web bundle, proving the purchases.ts / purchases.ios.ts split). The web paywall shows the catalog price, the 'Billed securely via Stripe' line, NO Restore control, and the Stripe checkout path is unchanged. The regression guard on the paywall rewrite.</t>
+          <t>react-native-purchases (and Play Billing) is absent from the AAB: the expo.autolinking.android.exclude in client/package.json drops it. Android sells nothing (Path C, 2026-09-27): no price, no Go Premium, no Stripe. This is the regression guard on adding the native module.</t>
         </is>
       </c>
       <c r="G265" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H265" s="7" t="inlineStr"/>
@@ -11338,7 +11338,7 @@
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>PREM-32</t>
+          <t>PREM-30</t>
         </is>
       </c>
       <c r="B266" s="7" t="inlineStr">
@@ -11353,22 +11353,22 @@
       </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
-          <t>PRODUCTION paywall price matches App Store Connect</t>
+          <t>The web build is unchanged and still sells via Stripe</t>
         </is>
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>After the app is RELEASED, install it from the App Store (not TestFlight) on an Australian account and open Premium. Read the monthly and annual prices.</t>
+          <t>Build the production web export (expo export --platform web). Open /premium on web.</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>The paywall reads A$5.00 / month and A$50.00 / year, matching the App Store Connect price schedule for Australia, and matching what Apple's purchase sheet charges. CRITICAL: TestFlight and sandbox CANNOT verify this. They are known to answer product queries for the US storefront regardless of the account's real region, so a TestFlight paywall showing US dollars is expected and is NOT the bug. Only a production App Store install proves it. If production still disagrees with the sheet, that is a misleading pre-purchase price (an Australian Consumer Law problem, not just a display bug): pull the release via Pricing and Availability, Remove from sale. Prerequisite: app released. Gate the RELEASE on this, never the submission.</t>
+          <t>The export succeeds (the native purchases module never enters the web bundle, proving the purchases.ts / purchases.ios.ts split). The web paywall shows the catalog price, the 'Billed securely via Stripe' line, NO Restore control, and the Stripe checkout path is unchanged. The regression guard on the paywall rewrite.</t>
         </is>
       </c>
       <c r="G266" s="7" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H266" s="7" t="inlineStr"/>
@@ -11378,7 +11378,7 @@
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>PREM-33</t>
+          <t>PREM-32</t>
         </is>
       </c>
       <c r="B267" s="7" t="inlineStr">
@@ -11393,22 +11393,22 @@
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>A dunning subscriber is never sold a second subscription</t>
+          <t>PRODUCTION paywall price matches App Store Connect</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>Put a test Stripe subscription into past_due (in Stripe test mode: attach a failing card, or use the test clock to fail a renewal). Open /premium signed in as that user. Read the panel, then try to buy.</t>
+          <t>After the app is RELEASED, install it from the App Store (not TestFlight) on an Australian account and open Premium. Read the monthly and annual prices.</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>Access has lapsed so the UPSELL panel shows, but with a calm notice at the top: 'Your Premium is paused while a payment retries. Updating your card brings it back. There is no need to buy again.' with an 'Update payment details' link that opens the Stripe portal (the customer id exists in this state). If the user taps Go Premium anyway, the server refuses with 409 billing_issue and the app explains the card is the fix, NEVER 'You're already on Premium' (false: they are not) and NEVER a second Checkout. REGRESSION GUARDS on the same server change (locked by stripe.test.ts): a LAPSED subscriber (status canceled, customer id kept) can still re-subscribe via a fresh Checkout, an abandoned checkout (incomplete) can still buy, and a trial still converts. The old guard keyed on premium &amp;&amp; customerId, so a past_due user could mint a SECOND subscription whose webhook overwrote stripe_customer_id and orphaned the first: paying twice with one visible.</t>
+          <t>The paywall reads A$5.00 / month and A$50.00 / year, matching the App Store Connect price schedule for Australia, and matching what Apple's purchase sheet charges. CRITICAL: TestFlight and sandbox CANNOT verify this. They are known to answer product queries for the US storefront regardless of the account's real region, so a TestFlight paywall showing US dollars is expected and is NOT the bug. Only a production App Store install proves it. If production still disagrees with the sheet, that is a misleading pre-purchase price (an Australian Consumer Law problem, not just a display bug): pull the release via Pricing and Availability, Remove from sale. Prerequisite: app released. Gate the RELEASE on this, never the submission.</t>
         </is>
       </c>
       <c r="G267" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="H267" s="7" t="inlineStr"/>
@@ -11418,7 +11418,7 @@
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>PREM-34</t>
+          <t>PREM-33</t>
         </is>
       </c>
       <c r="B268" s="7" t="inlineStr">
@@ -11433,22 +11433,22 @@
       </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
-          <t>An ANNUAL subscriber is warned a week before the charge, once</t>
+          <t>A dunning subscriber is never sold a second subscription</t>
         </is>
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>Needs a Stripe test clock, because the whole feature is about a year passing. Put a test user on the ANNUAL price. Open the app once while the renewal is far away (this is what teaches the device the period is a year: it is only ever judged annual when first seen more than 40 days out). Advance the test clock to ~10 days before renewal and open Today again. Then open it several more times. Separately, repeat the whole thing with a MONTHLY subscriber, and again with an annual one that has been CANCELLED (cancel_at_period_end).</t>
+          <t>Put a test Stripe subscription into past_due (in Stripe test mode: attach a failing card, or use the test clock to fail a renewal). Open /premium signed in as that user. Read the panel, then try to buy.</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>The annual subscriber gets ONE new task, dated SEVEN days before the charge (not on the day of it, which would be a receipt rather than a warning), reading 'Your DoubleDone year renews on &lt;date&gt;. Nothing to do.' Re-opening the app does NOT add a second: it is remembered against that period, and the next one is only noticed after the period rolls. The MONTHLY subscriber never gets one, however many times the app is opened (twelve notices a year is nagging). The CANCELLED subscriber never gets one either, because nothing is renewing and saying otherwise to someone who has decided to leave is both false and unkind. A device that first opens the app INSIDE the last 40 days gets no notice that year, by design, and self-corrects the next. This is the only place the app writes a task nobody typed, so a false positive here is a spine violation, not a cosmetic bug.</t>
+          <t>Access has lapsed so the UPSELL panel shows, but with a calm notice at the top: 'Your Premium is paused while a payment retries. Updating your card brings it back. There is no need to buy again.' with an 'Update payment details' link that opens the Stripe portal (the customer id exists in this state). If the user taps Go Premium anyway, the server refuses with 409 billing_issue and the app explains the card is the fix, NEVER 'You're already on Premium' (false: they are not) and NEVER a second Checkout. REGRESSION GUARDS on the same server change (locked by stripe.test.ts): a LAPSED subscriber (status canceled, customer id kept) can still re-subscribe via a fresh Checkout, an abandoned checkout (incomplete) can still buy, and a trial still converts. The old guard keyed on premium &amp;&amp; customerId, so a past_due user could mint a SECOND subscription whose webhook overwrote stripe_customer_id and orphaned the first: paying twice with one visible.</t>
         </is>
       </c>
       <c r="G268" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H268" s="7" t="inlineStr"/>
@@ -11458,7 +11458,7 @@
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>PREM-31</t>
+          <t>PREM-34</t>
         </is>
       </c>
       <c r="B269" s="7" t="inlineStr">
@@ -11466,25 +11466,29 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="C269" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C269" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
-          <t>Sandbox tester + Restore Behavior confirmed in the RevenueCat dashboard</t>
-        </is>
-      </c>
-      <c r="E269" s="9" t="inlineStr"/>
+          <t>An ANNUAL subscriber is warned a week before the charge, once</t>
+        </is>
+      </c>
+      <c r="E269" s="9" t="inlineStr">
+        <is>
+          <t>Needs a Stripe test clock, because the whole feature is about a year passing. Put a test user on the ANNUAL price. Open the app once while the renewal is far away (this is what teaches the device the period is a year: it is only ever judged annual when first seen more than 40 days out). Advance the test clock to ~10 days before renewal and open Today again. Then open it several more times. Separately, repeat the whole thing with a MONTHLY subscriber, and again with an annual one that has been CANCELLED (cancel_at_period_end).</t>
+        </is>
+      </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>In the RevenueCat dashboard: Restore Behavior is set to keep-with-original (so TRANSFER never fires), the App Store Connect API key + In-App-Purchase key are uploaded, both products read 'Ready to Submit', and the IAPs are attached to the SAME App Store submission as the first binary (a first-time subscription submitted separately is not reviewed). A Sandbox Apple ID exists for testing.</t>
+          <t>The annual subscriber gets ONE new task, dated SEVEN days before the charge (not on the day of it, which would be a receipt rather than a warning), reading 'Your DoubleDone year renews on &lt;date&gt;. Nothing to do.' Re-opening the app does NOT add a second: it is remembered against that period, and the next one is only noticed after the period rolls. The MONTHLY subscriber never gets one, however many times the app is opened (twelve notices a year is nagging). The CANCELLED subscriber never gets one either, because nothing is renewing and saying otherwise to someone who has decided to leave is both false and unkind. A device that first opens the app INSIDE the last 40 days gets no notice that year, by design, and self-corrects the next. This is the only place the app writes a task nobody typed, so a false positive here is a spine violation, not a cosmetic bug.</t>
         </is>
       </c>
       <c r="G269" s="7" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H269" s="7" t="inlineStr"/>
@@ -11494,37 +11498,33 @@
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>QUI-01</t>
+          <t>PREM-31</t>
         </is>
       </c>
       <c r="B270" s="7" t="inlineStr">
         <is>
-          <t>Interface</t>
-        </is>
-      </c>
-      <c r="C270" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="C270" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>The Quiet interface is free, both ways</t>
-        </is>
-      </c>
-      <c r="E270" s="9" t="inlineStr">
-        <is>
-          <t>As a FREE or signed-out user, open Settings -&gt; Look -&gt; 'Interface' and tap 'Quiet', then reload. Then tap 'Standard'. Then, as an account whose Premium or trial ended while it was on Quiet, open Settings -&gt; Look -&gt; 'Interface' and tap 'Standard'.</t>
-        </is>
-      </c>
+          <t>Sandbox tester + Restore Behavior confirmed in the RevenueCat dashboard</t>
+        </is>
+      </c>
+      <c r="E270" s="9" t="inlineStr"/>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>The Interface row carries no '✦ Premium' tag and shows one hint ('Quiet strips the interface back to calm text. Standard keeps the cards and buttons.'). The change applies live in both directions, the paywall never opens, and 'appearance.locked' is never logged. In Quiet the whole Today surface goes borderless. Card outlines drop, and every action that looked like a button or a link renders as plain text with no outline or fill: the header Menu pill (which keeps just the word 'Menu', no dots), 'Focus on one thing', 'Lighten today', 'Close the day', and 'Plan my day' (which in Standard is the filled premium gradient) all become plain text (accent for the AI / premium ones, soft ink for the calm structural ones). The energy / weight-of-today gauge is KEPT, not removed: it shrinks to a 3px hairline bar so the day's load still reads at a glance. The choice survives reload with 'Quiet' ringed. 'Standard' is the default and looks identical to the app today (gradient button, 6px gauge, outlined actions all return). The account whose Premium or trial ended can leave Quiet with one tap: before 2026-09-27 every tap, Standard included, bounced to the paywall, so it was stuck in Quiet with no way out (and none at all on Android, whose Premium page sells nothing).</t>
+          <t>In the RevenueCat dashboard: Restore Behavior is set to keep-with-original (so TRANSFER never fires), the App Store Connect API key + In-App-Purchase key are uploaded, both products read 'Ready to Submit', and the IAPs are attached to the SAME App Store submission as the first binary (a first-time subscription submitted separately is not reviewed). A Sandbox Apple ID exists for testing.</t>
         </is>
       </c>
       <c r="G270" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="H270" s="7" t="inlineStr"/>
@@ -11534,7 +11534,7 @@
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>QUI-02</t>
+          <t>QUI-01</t>
         </is>
       </c>
       <c r="B271" s="7" t="inlineStr">
@@ -11542,24 +11542,24 @@
           <t>Interface</t>
         </is>
       </c>
-      <c r="C271" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C271" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>Switching Standard &lt;-&gt; Quiet never moves the layout</t>
+          <t>The Quiet interface is free, both ways</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>With a handful of tasks on Today (some open, one or two done), toggle Interface between Standard and Quiet a few times, watching the task rows and the capture line. On ANDROID, specifically do the full round trip (Standard -&gt; Quiet -&gt; Standard) from the Settings screen and then return to Today.</t>
+          <t>As a FREE or signed-out user, open Settings -&gt; Look -&gt; 'Interface' and tap 'Quiet', then reload. Then tap 'Standard'. Then, as an account whose Premium or trial ended while it was on Quiet, open Settings -&gt; Look -&gt; 'Interface' and tap 'Standard'.</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>Content stays put: no visible jump in row height or position as you toggle. Quiet removes chrome (row borders, fills, the per-task progress bar, the capture underline weight) but preserves spacing, so nothing shifts under the finger. On Android the round trip must leave rows pixel-perfect, in particular the row BOTTOMS never look clipped/'eaten' (regression: toggling while Today sat detached behind Settings in the native stack left rows at Quiet's slightly shorter measured height under Standard's styles; Today now remounts on an appearance change so native lays it out fresh).</t>
+          <t>The Interface row carries no '✦ Premium' tag and shows one hint ('Quiet strips the interface back to calm text. Standard keeps the cards and buttons.'). The change applies live in both directions, the paywall never opens, and 'appearance.locked' is never logged. In Quiet the whole Today surface goes borderless. Card outlines drop, and every action that looked like a button or a link renders as plain text with no outline or fill: the header Menu pill (which keeps just the word 'Menu', no dots), 'Focus on one thing', 'Lighten today', 'Close the day', and 'Plan my day' (which in Standard is the filled premium gradient) all become plain text (accent for the AI / premium ones, soft ink for the calm structural ones). The energy / weight-of-today gauge is KEPT, not removed: it shrinks to a 3px hairline bar so the day's load still reads at a glance. The choice survives reload with 'Quiet' ringed. 'Standard' is the default and looks identical to the app today (gradient button, 6px gauge, outlined actions all return). The account whose Premium or trial ended can leave Quiet with one tap: before 2026-09-27 every tap, Standard included, bounced to the paywall, so it was stuck in Quiet with no way out (and none at all on Android, whose Premium page sells nothing).</t>
         </is>
       </c>
       <c r="G271" s="7" t="inlineStr">
@@ -11574,7 +11574,7 @@
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>QUI-06</t>
+          <t>QUI-02</t>
         </is>
       </c>
       <c r="B272" s="7" t="inlineStr">
@@ -11589,17 +11589,17 @@
       </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
-          <t>Quiet draws Energy as three words</t>
+          <t>Switching Standard &lt;-&gt; Quiet never moves the layout</t>
         </is>
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>Settings -&gt; Look -&gt; Interface -&gt; Quiet. Open Today and change Energy between Low, Normal and High.</t>
+          <t>With a handful of tasks on Today (some open, one or two done), toggle Interface between Standard and Quiet a few times, watching the task rows and the capture line. On ANDROID, specifically do the full round trip (Standard -&gt; Quiet -&gt; Standard) from the Settings screen and then return to Today.</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>No pills: Low, Normal and High are plain words, the chosen one in bold ink, the others in soft ink. Each still has a full 44pt tap area and nothing shifts when the choice changes. Standard keeps the soft pill.</t>
+          <t>Content stays put: no visible jump in row height or position as you toggle. Quiet removes chrome (row borders, fills, the per-task progress bar, the capture underline weight) but preserves spacing, so nothing shifts under the finger. On Android the round trip must leave rows pixel-perfect, in particular the row BOTTOMS never look clipped/'eaten' (regression: toggling while Today sat detached behind Settings in the native stack left rows at Quiet's slightly shorter measured height under Standard's styles; Today now remounts on an appearance change so native lays it out fresh).</t>
         </is>
       </c>
       <c r="G272" s="7" t="inlineStr">
@@ -11614,7 +11614,7 @@
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>QUI-03</t>
+          <t>QUI-06</t>
         </is>
       </c>
       <c r="B273" s="7" t="inlineStr">
@@ -11629,17 +11629,17 @@
       </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
-          <t>The held card is identical in Quiet and Standard (only the tint differs)</t>
+          <t>Quiet draws Energy as three words</t>
         </is>
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>Hold the SAME one-off task on Today in Quiet, then switch appearance and hold it again in Standard. Compare them side by side. Then in Quiet also hold a 'Later' task and (if you have one) a recurring task.</t>
+          <t>Settings -&gt; Look -&gt; Interface -&gt; Quiet. Open Today and change Energy between Low, Normal and High.</t>
         </is>
       </c>
       <c r="F273" s="9" t="inlineStr">
         <is>
-          <t>BOTH appearances now give the same in-place card with the same actions in the same order (see TOD-07): there is no longer a Quiet model and a Standard model. Only the treatment differs: Quiet gets a soft wash with a rounded bleed, Standard the accent tint. Mark-as-a-lot and Pin act-and-dismiss (the row updates, the card closes). Pin shows only on Today one-off rows (not Later, not recurring), matching PIN-05; a free user on Quiet who taps Pin is routed to the paywall, never wrongly pinned. 'Select more' closes the card and drops into multi-select with THIS task pre-selected ('1 selected'); Combine appears once a second task is selected. The one-time 'hold a task for more' coachmark in Quiet is a faint line with a small accent dot, not a filled pill.</t>
+          <t>No pills: Low, Normal and High are plain words, the chosen one in bold ink, the others in soft ink. Each still has a full 44pt tap area and nothing shifts when the choice changes. Standard keeps the soft pill.</t>
         </is>
       </c>
       <c r="G273" s="7" t="inlineStr">
@@ -11654,7 +11654,7 @@
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>QUI-04</t>
+          <t>QUI-03</t>
         </is>
       </c>
       <c r="B274" s="7" t="inlineStr">
@@ -11669,17 +11669,17 @@
       </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
-          <t>Quiet close-the-day reads as page text and stays reachable when full</t>
+          <t>The held card is identical in Quiet and Standard (only the tint differs)</t>
         </is>
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>In Quiet, finish several tasks, then also test a very full day (roughly 16+ finished), and tap 'Close the day'.</t>
+          <t>Hold the SAME one-off task on Today in Quiet, then switch appearance and hold it again in Standard. Compare them side by side. Then in Quiet also hold a 'Later' task and (if you have one) a recurring task.</t>
         </is>
       </c>
       <c r="F274" s="9" t="inlineStr">
         <is>
-          <t>The wrap shows on the plain page colour with no dim scrim and no card outline, and 'Goodnight' is a plain accent text link, not a filled button. On a very full day the finished list still scrolls inside a bounded area and 'Goodnight' stays on screen and reachable, so the TOD-04d regression holds in Quiet too. Reopen / rested behaviour is unchanged.</t>
+          <t>BOTH appearances now give the same in-place card with the same actions in the same order (see TOD-07): there is no longer a Quiet model and a Standard model. Only the treatment differs: Quiet gets a soft wash with a rounded bleed, Standard the accent tint. Mark-as-a-lot and Pin act-and-dismiss (the row updates, the card closes). Pin shows only on Today one-off rows (not Later, not recurring), matching PIN-05; a free user on Quiet who taps Pin is routed to the paywall, never wrongly pinned. 'Select more' closes the card and drops into multi-select with THIS task pre-selected ('1 selected'); Combine appears once a second task is selected. The one-time 'hold a task for more' coachmark in Quiet is a faint line with a small accent dot, not a filled pill.</t>
         </is>
       </c>
       <c r="G274" s="7" t="inlineStr">
@@ -11694,7 +11694,7 @@
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>QUI-05</t>
+          <t>QUI-04</t>
         </is>
       </c>
       <c r="B275" s="7" t="inlineStr">
@@ -11702,24 +11702,24 @@
           <t>Interface</t>
         </is>
       </c>
-      <c r="C275" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C275" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
-          <t>Quiet honours reduce-motion and every colour theme</t>
+          <t>Quiet close-the-day reads as page text and stays reachable when full</t>
         </is>
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>In Quiet, set Settings -&gt; Motion -&gt; Reduce (or the OS reduce-motion), then complete a task, open the held-state, and close the day. Separately, view Quiet across a couple of colour themes (e.g. Dusk and Sage) in BOTH light and dark.</t>
+          <t>In Quiet, finish several tasks, then also test a very full day (roughly 16+ finished), and tap 'Close the day'.</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
         <is>
-          <t>Nothing animates beyond the app's reduce-motion baseline: the held-state and the wrap appear without motion. Quiet derives its hairlines and washes from the ACTIVE palette, so it looks right on every colour theme in light and dark (not only Dusk), with no washed-out or invisible text.</t>
+          <t>The wrap shows on the plain page colour with no dim scrim and no card outline, and 'Goodnight' is a plain accent text link, not a filled button. On a very full day the finished list still scrolls inside a bounded area and 'Goodnight' stays on screen and reachable, so the TOD-04d regression holds in Quiet too. Reopen / rested behaviour is unchanged.</t>
         </is>
       </c>
       <c r="G275" s="7" t="inlineStr">
@@ -11734,7 +11734,7 @@
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>QUI-07</t>
+          <t>QUI-05</t>
         </is>
       </c>
       <c r="B276" s="7" t="inlineStr">
@@ -11742,24 +11742,24 @@
           <t>Interface</t>
         </is>
       </c>
-      <c r="C276" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C276" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
-          <t>A free account turns Quiet on in Settings, and nothing mentions Premium</t>
+          <t>Quiet honours reduce-motion and every colour theme</t>
         </is>
       </c>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>Signed in as a FREE account (no trial, no dev override), open Settings -&gt; Look -&gt; 'Interface'. Read the row, then tap 'Quiet'. Open Premium from the Settings card and read the feature list. Replay the welcome from Settings to its Premium screen, once with AI on and once with AI off. Then, still in Quiet, look at every Premium mark that remains: Plan my day in Right now and in the tools panel, the dimmed Pin in the More fold of a held task, the Colour theme row and the Premium card in Settings, and the energy allowance line (use 'What fits right now?' until it reads '10 of your 15 free picks left this month.').</t>
+          <t>In Quiet, set Settings -&gt; Motion -&gt; Reduce (or the OS reduce-motion), then complete a task, open the held-state, and close the day. Separately, view Quiet across a couple of colour themes (e.g. Dusk and Sage) in BOTH light and dark.</t>
         </is>
       </c>
       <c r="F276" s="9" t="inlineStr">
         <is>
-          <t>The Interface row has no '✦ Premium' tag and its hint never says Premium. Tapping 'Quiet' applies at once, with no paywall and nothing in the row naming Premium. The Premium page does not list Quiet, and the welcome's Premium screen does not list 'Quiet interface' (with AI off it shows just Your colour and Pin). In Quiet every remaining Premium mark still reads: Plan my day keeps its honey ✦ in Right now and in the tools panel, Pin stays dimmed with its ✦ in the More fold, the Colour theme row keeps its soft-ink '✦ Premium', the Premium card keeps its gradient with a clear white label, and the energy allowance line is legible. Until 2026-09-27 only subscribers ever saw Quiet, so these had never been looked at by a free user.</t>
+          <t>Nothing animates beyond the app's reduce-motion baseline: the held-state and the wrap appear without motion. Quiet derives its hairlines and washes from the ACTIVE palette, so it looks right on every colour theme in light and dark (not only Dusk), with no washed-out or invisible text.</t>
         </is>
       </c>
       <c r="G276" s="7" t="inlineStr">
@@ -11774,12 +11774,12 @@
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>PIN-01</t>
+          <t>QUI-07</t>
         </is>
       </c>
       <c r="B277" s="7" t="inlineStr">
         <is>
-          <t>Pin</t>
+          <t>Interface</t>
         </is>
       </c>
       <c r="C277" s="8" t="inlineStr">
@@ -11789,17 +11789,17 @@
       </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
-          <t>Premium: pin a task as the day's one thing</t>
+          <t>A free account turns Quiet on in Settings, and nothing mentions Premium</t>
         </is>
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>As premium (or with the dev Premium override on), tap-and-hold a one-off task to select it, then tap 'Pin' in the held row's actions.</t>
+          <t>Signed in as a FREE account (no trial, no dev override), open Settings -&gt; Look -&gt; 'Interface'. Read the row, then tap 'Quiet'. Open Premium from the Settings card and read the feature list. Replay the welcome from Settings to its Premium screen, once with AI on and once with AI off. Then, still in Quiet, look at every Premium mark that remains: Plan my day in Right now and in the tools panel, the dimmed Pin in the More fold of a held task, the Colour theme row and the Premium card in Settings, and the energy allowance line (use 'What fits right now?' until it reads '10 of your 15 free picks left this month.').</t>
         </is>
       </c>
       <c r="F277" s="9" t="inlineStr">
         <is>
-          <t>The task gets a calm mauve PIN MARK (a drawn pushpin; the star it replaced read as favourite, not pin, per Melroy 2026-08-30, and a drawn SVG cannot hit the iOS missing-glyph failure the round-one flag did) and the thick accent border, and floats to the top of Today. 'Focus on one thing' then opens straight to it.</t>
+          <t>The Interface row has no '✦ Premium' tag and its hint never says Premium. Tapping 'Quiet' applies at once, with no paywall and nothing in the row naming Premium. The Premium page does not list Quiet, and the welcome's Premium screen does not list 'Quiet interface' (with AI off it shows just Your colour and Pin). In Quiet every remaining Premium mark still reads: Plan my day keeps its honey ✦ in Right now and in the tools panel, Pin stays dimmed with its ✦ in the More fold, the Colour theme row keeps its soft-ink '✦ Premium', the Premium card keeps its gradient with a clear white label, and the energy allowance line is legible. Until 2026-09-27 only subscribers ever saw Quiet, so these had never been looked at by a free user.</t>
         </is>
       </c>
       <c r="G277" s="7" t="inlineStr">
@@ -11814,7 +11814,7 @@
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>PIN-02</t>
+          <t>PIN-01</t>
         </is>
       </c>
       <c r="B278" s="7" t="inlineStr">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
-          <t>Free: Pin routes to the upsell, never pins</t>
+          <t>Premium: pin a task as the day's one thing</t>
         </is>
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>As a free user, select a single one-off task and tap the dimmed 'Pin' action.</t>
+          <t>As premium (or with the dev Premium override on), tap-and-hold a one-off task to select it, then tap 'Pin' in the held row's actions.</t>
         </is>
       </c>
       <c r="F278" s="9" t="inlineStr">
         <is>
-          <t>No task is pinned, and the Premium screen opens calmly (never a shaming wall). A 'premium.gate_hit' with reason 'pin' is logged.</t>
+          <t>The task gets a calm mauve PIN MARK (a drawn pushpin; the star it replaced read as favourite, not pin, per Melroy 2026-08-30, and a drawn SVG cannot hit the iOS missing-glyph failure the round-one flag did) and the thick accent border, and floats to the top of Today. 'Focus on one thing' then opens straight to it.</t>
         </is>
       </c>
       <c r="G278" s="7" t="inlineStr">
@@ -11854,7 +11854,7 @@
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>PIN-03</t>
+          <t>PIN-02</t>
         </is>
       </c>
       <c r="B279" s="7" t="inlineStr">
@@ -11862,24 +11862,24 @@
           <t>Pin</t>
         </is>
       </c>
-      <c r="C279" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C279" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
-          <t>Only one task is pinned at a time</t>
+          <t>Free: Pin routes to the upsell, never pins</t>
         </is>
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>As premium, pin task A, then hold task B and pin it.</t>
+          <t>As a free user, select a single one-off task and tap the dimmed 'Pin' action.</t>
         </is>
       </c>
       <c r="F279" s="9" t="inlineStr">
         <is>
-          <t>Task B is now pinned (pin-marked, floated to the top), and task A is no longer pinned. At most one pin ever exists.</t>
+          <t>No task is pinned, and the Premium screen opens calmly (never a shaming wall). A 'premium.gate_hit' with reason 'pin' is logged.</t>
         </is>
       </c>
       <c r="G279" s="7" t="inlineStr">
@@ -11894,7 +11894,7 @@
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>PIN-04</t>
+          <t>PIN-03</t>
         </is>
       </c>
       <c r="B280" s="7" t="inlineStr">
@@ -11909,17 +11909,17 @@
       </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
-          <t>A pin syncs across devices</t>
+          <t>Only one task is pinned at a time</t>
         </is>
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>As premium and signed in, pin a task, then sign out and back in (or open a second device).</t>
+          <t>As premium, pin task A, then hold task B and pin it.</t>
         </is>
       </c>
       <c r="F280" s="9" t="inlineStr">
         <is>
-          <t>The task is still pinned after the sync round-trip (the pin mark and float persist). Needs the pinned_at column applied in Supabase.</t>
+          <t>Task B is now pinned (pin-marked, floated to the top), and task A is no longer pinned. At most one pin ever exists.</t>
         </is>
       </c>
       <c r="G280" s="7" t="inlineStr">
@@ -11934,7 +11934,7 @@
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>PIN-05</t>
+          <t>PIN-04</t>
         </is>
       </c>
       <c r="B281" s="7" t="inlineStr">
@@ -11942,24 +11942,24 @@
           <t>Pin</t>
         </is>
       </c>
-      <c r="C281" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C281" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
-          <t>Pin is offered only on one-off Today rows</t>
+          <t>A pin syncs across devices</t>
         </is>
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>Hold a recurring task, then hold a task in the 'Later' list.</t>
+          <t>As premium and signed in, pin a task, then sign out and back in (or open a second device).</t>
         </is>
       </c>
       <c r="F281" s="9" t="inlineStr">
         <is>
-          <t>No 'Pin' action appears on a recurring task's held card, and a Later task's card carries no Pin either (pinning is Today-only and one-offs only).</t>
+          <t>The task is still pinned after the sync round-trip (the pin mark and float persist). Needs the pinned_at column applied in Supabase.</t>
         </is>
       </c>
       <c r="G281" s="7" t="inlineStr">
@@ -11974,32 +11974,32 @@
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>NRG-01</t>
+          <t>PIN-05</t>
         </is>
       </c>
       <c r="B282" s="7" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C282" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Pin</t>
+        </is>
+      </c>
+      <c r="C282" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
-          <t>What fits right now: one question, one pick, propose-only</t>
+          <t>Pin is offered only on one-off Today rows</t>
         </is>
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>With AI on and 2+ open one-off tasks, tap 'Focus on one thing'; in the 'Which one?' picker, 'What fits right now?' sits above the task choices in a soft hairline pill (its border makes it read as tappable; it lives INSIDE Focus, not as a standalone Today button). Tap it, pick an energy level (Running low / Somewhere in between / Feeling good). Then tap 'Start with this'; separately try 'Not now'.</t>
+          <t>Hold a recurring task, then hold a task in the 'Later' list.</t>
         </is>
       </c>
       <c r="F282" s="9" t="inlineStr">
         <is>
-          <t>A calm one-question card with the privacy line ('Your open tasks go to Claude to pick one. Nothing is added or changed.'). Choosing a level shows ONE task from today's list with a short warm line on why it fits (never shaming, never about what's undone). 'Start with this' opens Focus mode on exactly that task; 'Not now' just closes, nothing changed. A failed call shows a calm 'Couldn't find a pick just now.' line and does NOT spend a free pick. The entry hides when AI is off or fewer than 2 tasks are open. Needs the Worker deployed with /energy.</t>
+          <t>No 'Pin' action appears on a recurring task's held card, and a Later task's card carries no Pin either (pinning is Today-only and one-offs only).</t>
         </is>
       </c>
       <c r="G282" s="7" t="inlineStr">
@@ -12014,7 +12014,7 @@
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>NRG-02</t>
+          <t>NRG-01</t>
         </is>
       </c>
       <c r="B283" s="7" t="inlineStr">
@@ -12029,17 +12029,17 @@
       </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
-          <t>The freemium meter: 15 a month, reminders at 10 and 5, then the paywall</t>
+          <t>What fits right now: one question, one pick, propose-only</t>
         </is>
       </c>
       <c r="E283" s="9" t="inlineStr">
         <is>
-          <t>As a FREE user, use energy matching repeatedly in one calendar month (seed doubledone.energyUses.v1 to fast-forward). Watch the 10-left and 5-left moments, then the 16th tap. Then as premium, use it well past 15.</t>
+          <t>With AI on and 2+ open one-off tasks, tap 'Focus on one thing'; in the 'Which one?' picker, 'What fits right now?' sits above the task choices in a soft hairline pill (its border makes it read as tappable; it lives INSIDE Focus, not as a standalone Today button). Tap it, pick an energy level (Running low / Somewhere in between / Feeling good). Then tap 'Start with this'; separately try 'Not now'.</t>
         </is>
       </c>
       <c r="F283" s="9" t="inlineStr">
         <is>
-          <t>Each successful pick spends one of 15 free picks a calendar month (counted locally, like the scrapbook gate). Exactly at 10 left and at 5 left, the result shows one calm line: '10 of your 15 free picks left this month.' (then 5). Past 15, tapping the entry routes to the paywall (which lists 'Energy matching without limits'), never a shaming wall, and no AI call is made ('premium.gate_hit' reason 'energy' logs). The counter resets on the 1st of the month with no carry-over. Premium is unlimited and never sees a counter line.</t>
+          <t>A calm one-question card with the privacy line ('Your open tasks go to Claude to pick one. Nothing is added or changed.'). Choosing a level shows ONE task from today's list with a short warm line on why it fits (never shaming, never about what's undone). 'Start with this' opens Focus mode on exactly that task; 'Not now' just closes, nothing changed. A failed call shows a calm 'Couldn't find a pick just now.' line and does NOT spend a free pick. The entry hides when AI is off or fewer than 2 tasks are open. Needs the Worker deployed with /energy.</t>
         </is>
       </c>
       <c r="G283" s="7" t="inlineStr">
@@ -12054,12 +12054,12 @@
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>OCR-01</t>
+          <t>NRG-02</t>
         </is>
       </c>
       <c r="B284" s="7" t="inlineStr">
         <is>
-          <t>Scan</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C284" s="8" t="inlineStr">
@@ -12069,17 +12069,17 @@
       </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
-          <t>Premium: the Scan button opens the camera</t>
+          <t>The freemium meter: 15 a month, reminders at 10 and 5, then the paywall</t>
         </is>
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>As premium, tap the + pill and then Scan (camera) beside Speak in the panel.</t>
+          <t>As a FREE user, use energy matching repeatedly in one calendar month (seed doubledone.energyUses.v1 to fast-forward). Watch the 10-left and 5-left moments, then the 16th tap. Then as premium, use it well past 15.</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>The camera screen opens: a live viewfinder with a shutter and a Photos shortcut on a device, or a 'Choose a photo' prompt on web. No paywall.</t>
+          <t>Each successful pick spends one of 15 free picks a calendar month (counted locally, like the scrapbook gate). Exactly at 10 left and at 5 left, the result shows one calm line: '10 of your 15 free picks left this month.' (then 5). Past 15, tapping the entry routes to the paywall (which lists 'Energy matching without limits'), never a shaming wall, and no AI call is made ('premium.gate_hit' reason 'energy' logs). The counter resets on the 1st of the month with no carry-over. Premium is unlimited and never sees a counter line.</t>
         </is>
       </c>
       <c r="G284" s="7" t="inlineStr">
@@ -12094,7 +12094,7 @@
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>OCR-02</t>
+          <t>OCR-01</t>
         </is>
       </c>
       <c r="B285" s="7" t="inlineStr">
@@ -12109,17 +12109,17 @@
       </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
-          <t>Free: Scan routes to the upsell, never opens the camera</t>
+          <t>Premium: the Scan button opens the camera</t>
         </is>
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>As a free user, tap the + pill and then Scan in the panel.</t>
+          <t>As premium, tap the + pill and then Scan (camera) beside Speak in the panel.</t>
         </is>
       </c>
       <c r="F285" s="9" t="inlineStr">
         <is>
-          <t>Routed to the Premium screen calmly (never a wall). A 'premium.gate_hit' with reason 'ocr' is logged. No camera opens.</t>
+          <t>The camera screen opens: a live viewfinder with a shutter and a Photos shortcut on a device, or a 'Choose a photo' prompt on web. No paywall.</t>
         </is>
       </c>
       <c r="G285" s="7" t="inlineStr">
@@ -12134,7 +12134,7 @@
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>OCR-03</t>
+          <t>OCR-02</t>
         </is>
       </c>
       <c r="B286" s="7" t="inlineStr">
@@ -12149,22 +12149,22 @@
       </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
-          <t>Photograph a list and the tasks land in the box</t>
+          <t>Free: Scan routes to the upsell, never opens the camera</t>
         </is>
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>As premium on a device, tap Scan, photograph a short printed or handwritten list (fill the frame), wait for 'Reading your list...'.</t>
+          <t>As a free user, tap the + pill and then Scan in the panel.</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>The tasks it reads appear in the brain-dump box, one per line, editable. Nothing is auto-added to Today, and tapping Add commits them. An 'ocr.captured' event is logged.</t>
+          <t>Routed to the Premium screen calmly (never a wall). A 'premium.gate_hit' with reason 'ocr' is logged. No camera opens.</t>
         </is>
       </c>
       <c r="G286" s="7" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H286" s="7" t="inlineStr"/>
@@ -12174,7 +12174,7 @@
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>OCR-04</t>
+          <t>OCR-03</t>
         </is>
       </c>
       <c r="B287" s="7" t="inlineStr">
@@ -12182,29 +12182,29 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="C287" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C287" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D287" s="9" t="inlineStr">
         <is>
-          <t>Gallery fallback reads an existing photo</t>
+          <t>Photograph a list and the tasks land in the box</t>
         </is>
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>Tap Scan, then 'Photos' (device) or 'Choose a photo' (web), and pick a photo of a list, a note, or a whiteboard.</t>
+          <t>As premium on a device, tap Scan, photograph a short printed or handwritten list (fill the frame), wait for 'Reading your list...'.</t>
         </is>
       </c>
       <c r="F287" s="9" t="inlineStr">
         <is>
-          <t>Same result: the read tasks land in the box for review. Covers a screenshot of a texted list, or a photo taken earlier.</t>
+          <t>The tasks it reads appear in the brain-dump box, one per line, editable. Nothing is auto-added to Today, and tapping Add commits them. An 'ocr.captured' event is logged.</t>
         </is>
       </c>
       <c r="G287" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="H287" s="7" t="inlineStr"/>
@@ -12214,7 +12214,7 @@
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>OCR-05</t>
+          <t>OCR-04</t>
         </is>
       </c>
       <c r="B288" s="7" t="inlineStr">
@@ -12229,17 +12229,17 @@
       </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
-          <t>An unreadable photo fails calmly</t>
+          <t>Gallery fallback reads an existing photo</t>
         </is>
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>Scan a blank, blurry, or list-free image.</t>
+          <t>Tap Scan, then 'Photos' (device) or 'Choose a photo' (web), and pick a photo of a list, a note, or a whiteboard.</t>
         </is>
       </c>
       <c r="F288" s="9" t="inlineStr">
         <is>
-          <t>A calm line ('I couldn't read any tasks from that. Try again...'), the camera stays open, never a crash and never a shaming message.</t>
+          <t>Same result: the read tasks land in the box for review. Covers a screenshot of a texted list, or a photo taken earlier.</t>
         </is>
       </c>
       <c r="G288" s="7" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>OCR-06</t>
+          <t>OCR-05</t>
         </is>
       </c>
       <c r="B289" s="7" t="inlineStr">
@@ -12269,22 +12269,22 @@
       </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
-          <t>Camera denial is never a dead end</t>
+          <t>An unreadable photo fails calmly</t>
         </is>
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>On a device, deny the camera permission when prompted.</t>
+          <t>Scan a blank, blurry, or list-free image.</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
         <is>
-          <t>A calm screen offers 'Allow camera' and 'Choose from photos instead', and the gallery path still reads a list.</t>
+          <t>A calm line ('I couldn't read any tasks from that. Try again...'), the camera stays open, never a crash and never a shaming message.</t>
         </is>
       </c>
       <c r="G289" s="7" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H289" s="7" t="inlineStr"/>
@@ -12294,7 +12294,7 @@
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>OCR-07</t>
+          <t>OCR-06</t>
         </is>
       </c>
       <c r="B290" s="7" t="inlineStr">
@@ -12302,29 +12302,29 @@
           <t>Scan</t>
         </is>
       </c>
-      <c r="C290" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C290" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>AI egress is disclosed at the point of use</t>
+          <t>Camera denial is never a dead end</t>
         </is>
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>Open the Scan screen (device or web).</t>
+          <t>On a device, deny the camera permission when prompted.</t>
         </is>
       </c>
       <c r="F290" s="9" t="inlineStr">
         <is>
-          <t>The note 'Your photo is sent to the AI to read your list, then discarded. It is never stored.' is visible. The D1 'ocr' telemetry row holds only the image size and task count, never the image or the titles.</t>
+          <t>A calm screen offers 'Allow camera' and 'Choose from photos instead', and the gallery path still reads a list.</t>
         </is>
       </c>
       <c r="G290" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="H290" s="7" t="inlineStr"/>
@@ -12334,32 +12334,32 @@
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>CHART-01</t>
+          <t>OCR-07</t>
         </is>
       </c>
       <c r="B291" s="7" t="inlineStr">
         <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C291" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Scan</t>
+        </is>
+      </c>
+      <c r="C291" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
-          <t>Premium: chart a course toward a goal</t>
+          <t>AI egress is disclosed at the point of use</t>
         </is>
       </c>
       <c r="E291" s="9" t="inlineStr">
         <is>
-          <t>As premium (or dev Premium override on), open Rooms, tap 'Chart a course', type a goal like 'get fit for a 10k', tap 'Suggest steps'.</t>
+          <t>Open the Scan screen (device or web).</t>
         </is>
       </c>
       <c r="F291" s="9" t="inlineStr">
         <is>
-          <t>A calm one-line heading plus 3-7 ticked next steps appear, and nothing is added yet. Tapping 'Add N tasks' lands them on Today (the first undated, later ones spread forward), each an ordinary task, and returns to Today. The 'chart.requested' then 'chart.added' events are logged.</t>
+          <t>The note 'Your photo is sent to the AI to read your list, then discarded. It is never stored.' is visible. The D1 'ocr' telemetry row holds only the image size and task count, never the image or the titles.</t>
         </is>
       </c>
       <c r="G291" s="7" t="inlineStr">
@@ -12374,7 +12374,7 @@
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>CHART-02</t>
+          <t>CHART-01</t>
         </is>
       </c>
       <c r="B292" s="7" t="inlineStr">
@@ -12389,17 +12389,17 @@
       </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
-          <t>Free: charting routes to the upsell, never plans</t>
+          <t>Premium: chart a course toward a goal</t>
         </is>
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>As a free user, open the Menu, tap 'Chart a course', type a goal, pick a timeframe, tap 'Suggest steps', then come back.</t>
+          <t>As premium (or dev Premium override on), open Rooms, tap 'Chart a course', type a goal like 'get fit for a 10k', tap 'Suggest steps'.</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>Before the tap the room already says '✦ Suggesting steps is part of Premium.' under the button, once and static. The tap routes to the Premium screen calmly (never a wall), and a 'premium.gate_hit' with reason 'chart' is logged. No plan is generated and nothing is added. Coming back, the goal and the chosen timeframe are still there, including after a purchase: on the phone the Premium panel's way out reads '‹ Chart a course', and on web a checkout round-trip brings the goal back the next time the room opens. Nothing is locked, blurred or priced.</t>
+          <t>A calm one-line heading plus 3-7 ticked next steps appear, and nothing is added yet. Tapping 'Add N tasks' lands them on Today (the first undated, later ones spread forward), each an ordinary task, and returns to Today. The 'chart.requested' then 'chart.added' events are logged.</t>
         </is>
       </c>
       <c r="G292" s="7" t="inlineStr">
@@ -12414,7 +12414,7 @@
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>CHART-03</t>
+          <t>CHART-02</t>
         </is>
       </c>
       <c r="B293" s="7" t="inlineStr">
@@ -12422,24 +12422,24 @@
           <t>Chart</t>
         </is>
       </c>
-      <c r="C293" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C293" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>Propose-then-accept: nothing auto-adds</t>
+          <t>Free: charting routes to the upsell, never plans</t>
         </is>
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>As premium, generate a plan, untick two steps, then tap 'Add'. Separately, generate a plan and back out with 'Not these, start over' or Back.</t>
+          <t>As a free user, open the Menu, tap 'Chart a course', type a goal, pick a timeframe, tap 'Suggest steps', then come back.</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>Only the ticked steps are added as plain tasks, and backing out adds nothing. Today was unchanged before accepting.</t>
+          <t>Before the tap the room already says '✦ Suggesting steps is part of Premium.' under the button, once and static. The tap routes to the Premium screen calmly (never a wall), and a 'premium.gate_hit' with reason 'chart' is logged. No plan is generated and nothing is added. Coming back, the goal and the chosen timeframe are still there, including after a purchase: on the phone the Premium panel's way out reads '‹ Chart a course', and on web a checkout round-trip brings the goal back the next time the room opens. Nothing is locked, blurred or priced.</t>
         </is>
       </c>
       <c r="G293" s="7" t="inlineStr">
@@ -12454,7 +12454,7 @@
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>CHART-04</t>
+          <t>CHART-03</t>
         </is>
       </c>
       <c r="B294" s="7" t="inlineStr">
@@ -12469,17 +12469,17 @@
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>A goal that cannot be mapped fails calmly</t>
+          <t>Propose-then-accept: nothing auto-adds</t>
         </is>
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>Enter an empty goal (the button is disabled), then a nonsensical goal and submit.</t>
+          <t>As premium, generate a plan, untick two steps, then tap 'Add'. Separately, generate a plan and back out with 'Not these, start over' or Back.</t>
         </is>
       </c>
       <c r="F294" s="9" t="inlineStr">
         <is>
-          <t>The empty case cannot submit. A nonsensical goal shows one calm line ('I couldn't map that out just now'), the goal stays editable, never a crash or a shaming message.</t>
+          <t>Only the ticked steps are added as plain tasks, and backing out adds nothing. Today was unchanged before accepting.</t>
         </is>
       </c>
       <c r="G294" s="7" t="inlineStr">
@@ -12494,7 +12494,7 @@
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>CHART-05</t>
+          <t>CHART-04</t>
         </is>
       </c>
       <c r="B295" s="7" t="inlineStr">
@@ -12509,17 +12509,17 @@
       </c>
       <c r="D295" s="9" t="inlineStr">
         <is>
-          <t>A deadline spreads the steps across the timeframe</t>
+          <t>A goal that cannot be mapped fails calmly</t>
         </is>
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>As premium, type a goal, tap a 'By when?' chip (e.g. 'In 2 months'), then Suggest steps and Add.</t>
+          <t>Enter an empty goal (the button is disabled), then a nonsensical goal and submit.</t>
         </is>
       </c>
       <c r="F295" s="9" t="inlineStr">
         <is>
-          <t>The steps are paced for that timeframe, and the accepted tasks spread from Today out to the chosen date (not crammed into the next few days). 'No deadline' keeps the gentle one-per-day default.</t>
+          <t>The empty case cannot submit. A nonsensical goal shows one calm line ('I couldn't map that out just now'), the goal stays editable, never a crash or a shaming message.</t>
         </is>
       </c>
       <c r="G295" s="7" t="inlineStr">
@@ -12534,7 +12534,7 @@
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>CHART-06</t>
+          <t>CHART-05</t>
         </is>
       </c>
       <c r="B296" s="7" t="inlineStr">
@@ -12549,17 +12549,17 @@
       </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
-          <t>The timeframe stays named once the steps arrive</t>
+          <t>A deadline spreads the steps across the timeframe</t>
         </is>
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>Premium. Type a goal, pick 'In 2 months', Suggest steps. Then 'Not these, start over', pick no deadline, and suggest again.</t>
+          <t>As premium, type a goal, tap a 'By when?' chip (e.g. 'In 2 months'), then Suggest steps and Add.</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
         <is>
-          <t>Once the steps arrive the chips step aside, and one quiet line above the heading keeps the choice named: 'By when · In 2 months' (then 'By when · No deadline'). The AI's heading is in italic serif; every step starts ticked, each with its minutes and a ✕. The button counts only what will be added.</t>
+          <t>The steps are paced for that timeframe, and the accepted tasks spread from Today out to the chosen date (not crammed into the next few days). 'No deadline' keeps the gentle one-per-day default.</t>
         </is>
       </c>
       <c r="G296" s="7" t="inlineStr">
@@ -12574,7 +12574,7 @@
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>CHART-07</t>
+          <t>CHART-06</t>
         </is>
       </c>
       <c r="B297" s="7" t="inlineStr">
@@ -12589,17 +12589,17 @@
       </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
-          <t>The steps show where they landed on Today</t>
+          <t>The timeframe stays named once the steps arrive</t>
         </is>
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>Premium. Chart a course, accept the steps with 'Add N tasks'.</t>
+          <t>Premium. Type a goal, pick 'In 2 months', Suggest steps. Then 'Not these, start over', pick no deadline, and suggest again.</t>
         </is>
       </c>
       <c r="F297" s="9" t="inlineStr">
         <is>
-          <t>You land on Today (never back on the spent proposal; back from Today does not return to it). The first step is on Today carrying the soft 'just added' tint, which fades away after a couple of seconds. The rest wait on their days.</t>
+          <t>Once the steps arrive the chips step aside, and one quiet line above the heading keeps the choice named: 'By when · In 2 months' (then 'By when · No deadline'). The AI's heading is in italic serif; every step starts ticked, each with its minutes and a ✕. The button counts only what will be added.</t>
         </is>
       </c>
       <c r="G297" s="7" t="inlineStr">
@@ -12614,7 +12614,7 @@
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>CHART-08</t>
+          <t>CHART-07</t>
         </is>
       </c>
       <c r="B298" s="7" t="inlineStr">
@@ -12622,24 +12622,24 @@
           <t>Chart</t>
         </is>
       </c>
-      <c r="C298" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C298" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
-          <t>The small marks read on paper</t>
+          <t>The steps show where they landed on Today</t>
         </is>
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>In light mode, open Chart a course, get a proposal, and look at an unticked box, a step's minutes, the ✕, the spread note and the note at the foot. Then look at a selected timeframe chip.</t>
+          <t>Premium. Chart a course, accept the steps with 'Add N tasks'.</t>
         </is>
       </c>
       <c r="F298" s="9" t="inlineStr">
         <is>
-          <t>All of them read clearly (they moved from the faintest ink to the soft ink). The instruction under the title is in full ink. A selected chip keeps its tinted fill and border, and its label is ink rather than the accent, which was too faint on the tint. In dark mode the selected label stays the accent.</t>
+          <t>You land on Today (never back on the spent proposal; back from Today does not return to it). The first step is on Today carrying the soft 'just added' tint, which fades away after a couple of seconds. The rest wait on their days.</t>
         </is>
       </c>
       <c r="G298" s="7" t="inlineStr">
@@ -12654,32 +12654,32 @@
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>SEQ-01</t>
+          <t>CHART-08</t>
         </is>
       </c>
       <c r="B299" s="7" t="inlineStr">
         <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="C299" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C299" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>Premium: Plan my day suggests a calm sequence</t>
+          <t>The small marks read on paper</t>
         </is>
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>As premium with 3+ open one-off tasks on Today, tap 'Plan my day'. Answer the questions it asks first (or skip them).</t>
+          <t>In light mode, open Chart a course, get a proposal, and look at an unticked box, a step's minutes, the ✕, the spread note and the note at the foot. Then look at a selected timeframe chip.</t>
         </is>
       </c>
       <c r="F299" s="9" t="inlineStr">
         <is>
-          <t>A proposal card lists today's tasks in a suggested order, each with a short calm reason. Nothing reorders until 'Use this order' is tapped, then the list re-sequences in place (no dates change, no task moves to another day). A 'sequence.accepted' event is logged.</t>
+          <t>All of them read clearly (they moved from the faintest ink to the soft ink). The instruction under the title is in full ink. A selected chip keeps its tinted fill and border, and its label is ink rather than the accent, which was too faint on the tint. In dark mode the selected label stays the accent.</t>
         </is>
       </c>
       <c r="G299" s="7" t="inlineStr">
@@ -12694,12 +12694,12 @@
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>TOD-27</t>
+          <t>SEQ-01</t>
         </is>
       </c>
       <c r="B300" s="7" t="inlineStr">
         <is>
-          <t>Today</t>
+          <t>Sequence</t>
         </is>
       </c>
       <c r="C300" s="8" t="inlineStr">
@@ -12709,17 +12709,17 @@
       </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
-          <t>Right now: one card near the top, a clock-set slot, the tools open downward, Energy pills</t>
+          <t>Premium: Plan my day suggests a calm sequence</t>
         </is>
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>Open Today in the MORNING (before 11), around MIDDAY (11-17), and in the EVENING (17+), reading the 'RIGHT NOW' card under Energy each time. Tap the caret at its right. Add and complete tasks and watch whether ANY control moves. Tap an unavailable (faded) tool. Set the Energy pills to High on a 7-task day and re-open the caret; set Low and read the gauge. Reload the app and check the pill. Turn AI off in Settings and re-open the caret. Also check with 0 tasks, in select mode, while typing in the composer, and after closing the day.</t>
+          <t>As premium with 3+ open one-off tasks on Today, tap 'Plan my day'. Answer the questions it asks first (or skip them).</t>
         </is>
       </c>
       <c r="F300" s="9" t="inlineStr">
         <is>
-          <t>ONE card sits under the Energy pills, near the top: an overline 'RIGHT NOW' + the tool that suits the HOUR (morning: Plan my day; midday: Focus on one thing; evening: Close the day), plus a caret ('All day tools'). The occupant is set by the CLOCK at open and never changes mid-session; it NEVER shows Lighten today. The caret opens the tools DOWNWARD inside the same card, in the same day order every time: Plan my day, Focus on one thing, Lighten today, Settle, Close the day, the current occupant tagged 'now', Plan my day wearing the honey ✦ when you are not Premium. The list moves down to make room and nothing covers it (no dim, no scrim). NOTHING in the card appears, vanishes or slides as tasks are added or completed: an unavailable tool stays in place at lowered contrast and tapping it explains in one plain line what the TOOL needs ('Plan my day needs two or more tasks.' / 'Lighten today is for a full day.'), never what the person lacks. The Energy pills (Low/Normal/High) sit under a small 'ENERGY' overline with the gauge above, on EVERY open day, including an empty one ('A clear day.'). A fresh day defaults to Normal. High re-scales what 'full' means, Low IS the low-capacity day, and the choice survives a reload but RESETS to Normal next morning. With AI OFF the card holds only the non-AI tools (AI tools are gone, not faded). In select mode the card RESTS (dimmed, does not respond) rather than vanishing, so the list does not jump. While the composer is open the card steps aside with the rest of the heading. On a closed day it is gone.</t>
+          <t>A proposal card lists today's tasks in a suggested order, each with a short calm reason. Nothing reorders until 'Use this order' is tapped, then the list re-sequences in place (no dates change, no task moves to another day). A 'sequence.accepted' event is logged.</t>
         </is>
       </c>
       <c r="G300" s="7" t="inlineStr">
@@ -12734,7 +12734,7 @@
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>TOD-28</t>
+          <t>TOD-27</t>
         </is>
       </c>
       <c r="B301" s="7" t="inlineStr">
@@ -12742,24 +12742,24 @@
           <t>Today</t>
         </is>
       </c>
-      <c r="C301" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C301" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
-          <t>The rested screen mentions the scrapbook once, at the earned moment (the ladder's last rung)</t>
+          <t>Right now: one card near the top, a clock-set slot, the tools open downward, Energy pills</t>
         </is>
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>With AI on, the reminder and widget asks already spent (or reminder on, widget placed), NO scrapbook ever made, and at least 3 finishes this week, close the day and read the rested screen. Tap 'See your Calendar'. Then close a day again on another evening. Separately: repeat with AI off, and repeat with only 1-2 finishes.</t>
+          <t>Open Today in the MORNING (before 11), around MIDDAY (11-17), and in the EVENING (17+), reading the 'RIGHT NOW' card under Energy each time. Tap the caret at its right. Add and complete tasks and watch whether ANY control moves. Tap an unavailable (faded) tool. Set the Energy pills to High on a 7-task day and re-open the caret; set Low and read the gauge. Reload the app and check the pill. Turn AI off in Settings and re-open the caret. Also check with 0 tasks, in select mode, while typing in the composer, and after closing the day.</t>
         </is>
       </c>
       <c r="F301" s="9" t="inlineStr">
         <is>
-          <t>One calm mention appears under the goodnight text: 'You've finished enough this week to make a keepsake of it. It's waiting in your Calendar.' with 'See your Calendar' and 'Not now'. Either answer spends the mention FOREVER (it is the third and LAST rung of the one-ask-at-a-time ladder; reminder and widget always win the evening if pending). 'See your Calendar' opens the Calendar where the scrapbook lives. It never shows with AI off, never with fewer than 3 finishes this week, never to someone who has already made a scrapbook, and never twice.</t>
+          <t>ONE card sits under the Energy pills, near the top: an overline 'RIGHT NOW' + the tool that suits the HOUR (morning: Plan my day; midday: Focus on one thing; evening: Close the day), plus a caret ('All day tools'). The occupant is set by the CLOCK at open and never changes mid-session; it NEVER shows Lighten today. The caret opens the tools DOWNWARD inside the same card, in the same day order every time: Plan my day, Focus on one thing, Lighten today, Settle, Close the day, the current occupant tagged 'now', Plan my day wearing the honey ✦ when you are not Premium. The list moves down to make room and nothing covers it (no dim, no scrim). NOTHING in the card appears, vanishes or slides as tasks are added or completed: an unavailable tool stays in place at lowered contrast and tapping it explains in one plain line what the TOOL needs ('Plan my day needs two or more tasks.' / 'Lighten today is for a full day.'), never what the person lacks. The Energy pills (Low/Normal/High) sit under a small 'ENERGY' overline with the gauge above, on EVERY open day, including an empty one ('A clear day.'). A fresh day defaults to Normal. High re-scales what 'full' means, Low IS the low-capacity day, and the choice survives a reload but RESETS to Normal next morning. With AI OFF the card holds only the non-AI tools (AI tools are gone, not faded). In select mode the card RESTS (dimmed, does not respond) rather than vanishing, so the list does not jump. While the composer is open the card steps aside with the rest of the heading. On a closed day it is gone.</t>
         </is>
       </c>
       <c r="G301" s="7" t="inlineStr">
@@ -12774,32 +12774,32 @@
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
         <is>
-          <t>SEQ-07</t>
+          <t>TOD-28</t>
         </is>
       </c>
       <c r="B302" s="7" t="inlineStr">
         <is>
-          <t>Sequence</t>
-        </is>
-      </c>
-      <c r="C302" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="C302" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
-          <t>Plan my day asks about the day BEFORE it sorts</t>
+          <t>The rested screen mentions the scrapbook once, at the earned moment (the ladder's last rung)</t>
         </is>
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>As premium, tap 'Plan my day'. Read the sheet that opens. Tap an answer, then tap the SAME answer again. Try sorting with all three answered, with only one answered, and with none answered ('Sort today' straight away). Also tap 'Not now'. Separately, as a FREE user, tap 'Plan my day'.</t>
+          <t>With AI on, the reminder and widget asks already spent (or reminder on, widget placed), NO scrapbook ever made, and at least 3 finishes this week, close the day and read the rested screen. Tap 'See your Calendar'. Then close a day again on another evening. Separately: repeat with AI off, and repeat with only 1-2 finishes.</t>
         </is>
       </c>
       <c r="F302" s="9" t="inlineStr">
         <is>
-          <t>Before any sorting, a calm sheet asks three OPTIONAL questions: 'How's your energy?' (Running low / Somewhere in between / Feeling good), 'What kind of day?' (Work day / Day off) and 'Where are you?' (Indoors / Out and about / Either), under 'Answer what you like. Skip what you don't.'. A chosen answer tints (accent border, fill and bold accent text); tapping it AGAIN clears it, so a mis-tap is undone the way it was made. Skipping a question sends nothing for it, so it never becomes an assumption, and skipping all three sorts exactly as it always did. The order that comes back reflects what was said (a low-energy day starts small; a day off does not front-load work; 'out and about' clusters the errands), but the app NEVER comments on how you feel. 'Not now' closes with nothing sent and the day untouched. A FREE user hits the Premium screen BEFORE the questions, never after answering them. NEW (the constant frame): when the Energy PILLS at the top of Today were touched today, the sheet's energy question DOES NOT APPEAR at all, and the pill's answer rides the request instead (Low-&gt;low, Normal-&gt;medium, High-&gt;good): energy is read, never asked twice. Only when the pills are untouched does the sheet ask. NOTE: there is deliberately no weather question. A model has no live weather data, and a forecast would need an API plus a location permission; 'Where are you?' is what the sort actually needs.</t>
+          <t>One calm mention appears under the goodnight text: 'You've finished enough this week to make a keepsake of it. It's waiting in your Calendar.' with 'See your Calendar' and 'Not now'. Either answer spends the mention FOREVER (it is the third and LAST rung of the one-ask-at-a-time ladder; reminder and widget always win the evening if pending). 'See your Calendar' opens the Calendar where the scrapbook lives. It never shows with AI off, never with fewer than 3 finishes this week, never to someone who has already made a scrapbook, and never twice.</t>
         </is>
       </c>
       <c r="G302" s="7" t="inlineStr">
@@ -12814,7 +12814,7 @@
     <row r="303">
       <c r="A303" s="6" t="inlineStr">
         <is>
-          <t>SEQ-08</t>
+          <t>SEQ-07</t>
         </is>
       </c>
       <c r="B303" s="7" t="inlineStr">
@@ -12829,17 +12829,17 @@
       </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
-          <t>The suggested order can be edited before it is used</t>
+          <t>Plan my day asks about the day BEFORE it sorts</t>
         </is>
       </c>
       <c r="E303" s="9" t="inlineStr">
         <is>
-          <t>Get a proposal from 'Plan my day'. Use the up and down arrows on a row. Try the up arrow on the FIRST row and the down arrow on the LAST. Remove a row with x. Remove every row. Then tap 'Use this order'.</t>
+          <t>As premium, tap 'Plan my day'. Read the sheet that opens. Tap an answer, then tap the SAME answer again. Try sorting with all three answered, with only one answered, and with none answered ('Sort today' straight away). Also tap 'Not now'. Separately, as a FREE user, tap 'Plan my day'.</t>
         </is>
       </c>
       <c r="F303" s="9" t="inlineStr">
         <is>
-          <t>Each row carries up / down / x. Up and down swap the row with its neighbour immediately, renumbering as they go; the first row's up and the last row's down are visibly dimmed and do nothing (they are disabled, not hidden, so rows never change shape as things move). 'x' takes that task OUT OF THIS PLAN ONLY: the task stays on Today untouched, is not deleted, and is not moved to another day. Removing everything is allowed and says 'Nothing left in the plan. That's allowed.' with the accept button gone (an empty plan cannot be applied). Nothing at all changes on Today until 'Use this order' is tapped; 'Not now' or closing discards every edit. Editing is by buttons, never drag: dragging is unusable with a screen reader and hard with shaky hands.</t>
+          <t>Before any sorting, a calm sheet asks three OPTIONAL questions: 'How's your energy?' (Running low / Somewhere in between / Feeling good), 'What kind of day?' (Work day / Day off) and 'Where are you?' (Indoors / Out and about / Either), under 'Answer what you like. Skip what you don't.'. A chosen answer tints (accent border, fill and bold accent text); tapping it AGAIN clears it, so a mis-tap is undone the way it was made. Skipping a question sends nothing for it, so it never becomes an assumption, and skipping all three sorts exactly as it always did. The order that comes back reflects what was said (a low-energy day starts small; a day off does not front-load work; 'out and about' clusters the errands), but the app NEVER comments on how you feel. 'Not now' closes with nothing sent and the day untouched. A FREE user hits the Premium screen BEFORE the questions, never after answering them. NEW (the constant frame): when the Energy PILLS at the top of Today were touched today, the sheet's energy question DOES NOT APPEAR at all, and the pill's answer rides the request instead (Low-&gt;low, Normal-&gt;medium, High-&gt;good): energy is read, never asked twice. Only when the pills are untouched does the sheet ask. NOTE: there is deliberately no weather question. A model has no live weather data, and a forecast would need an API plus a location permission; 'Where are you?' is what the sort actually needs.</t>
         </is>
       </c>
       <c r="G303" s="7" t="inlineStr">
@@ -12854,7 +12854,7 @@
     <row r="304">
       <c r="A304" s="6" t="inlineStr">
         <is>
-          <t>SEQ-02</t>
+          <t>SEQ-08</t>
         </is>
       </c>
       <c r="B304" s="7" t="inlineStr">
@@ -12869,17 +12869,17 @@
       </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
-          <t>Free: Plan my day routes to the upsell, never reorders</t>
+          <t>The suggested order can be edited before it is used</t>
         </is>
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>As a free user with 2+ tasks on Today, tap 'Plan my day'.</t>
+          <t>Get a proposal from 'Plan my day'. Use the up and down arrows on a row. Try the up arrow on the FIRST row and the down arrow on the LAST. Remove a row with x. Remove every row. Then tap 'Use this order'.</t>
         </is>
       </c>
       <c r="F304" s="9" t="inlineStr">
         <is>
-          <t>The Premium screen opens calmly (never a wall), a 'premium.gate_hit' with reason 'sequence' is logged, and the day's order is unchanged.</t>
+          <t>Each row carries up / down / x. Up and down swap the row with its neighbour immediately, renumbering as they go; the first row's up and the last row's down are visibly dimmed and do nothing (they are disabled, not hidden, so rows never change shape as things move). 'x' takes that task OUT OF THIS PLAN ONLY: the task stays on Today untouched, is not deleted, and is not moved to another day. Removing everything is allowed and says 'Nothing left in the plan. That's allowed.' with the accept button gone (an empty plan cannot be applied). Nothing at all changes on Today until 'Use this order' is tapped; 'Not now' or closing discards every edit. Editing is by buttons, never drag: dragging is unusable with a screen reader and hard with shaky hands.</t>
         </is>
       </c>
       <c r="G304" s="7" t="inlineStr">
@@ -12894,7 +12894,7 @@
     <row r="305">
       <c r="A305" s="6" t="inlineStr">
         <is>
-          <t>SEQ-03</t>
+          <t>SEQ-02</t>
         </is>
       </c>
       <c r="B305" s="7" t="inlineStr">
@@ -12902,24 +12902,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C305" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C305" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
-          <t>'Not now' leaves the day untouched</t>
+          <t>Free: Plan my day routes to the upsell, never reorders</t>
         </is>
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>As premium, open the proposal, then tap 'Not now' or the backdrop.</t>
+          <t>As a free user with 2+ tasks on Today, tap 'Plan my day'.</t>
         </is>
       </c>
       <c r="F305" s="9" t="inlineStr">
         <is>
-          <t>The order is exactly as before, nothing reordered, and no manualOrder is written.</t>
+          <t>The Premium screen opens calmly (never a wall), a 'premium.gate_hit' with reason 'sequence' is logged, and the day's order is unchanged.</t>
         </is>
       </c>
       <c r="G305" s="7" t="inlineStr">
@@ -12934,7 +12934,7 @@
     <row r="306">
       <c r="A306" s="6" t="inlineStr">
         <is>
-          <t>SEQ-04</t>
+          <t>SEQ-03</t>
         </is>
       </c>
       <c r="B306" s="7" t="inlineStr">
@@ -12949,17 +12949,17 @@
       </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
-          <t>An accepted order survives a reload (local-first)</t>
+          <t>'Not now' leaves the day untouched</t>
         </is>
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>As premium, accept an order, then fully reload the app.</t>
+          <t>As premium, open the proposal, then tap 'Not now' or the backdrop.</t>
         </is>
       </c>
       <c r="F306" s="9" t="inlineStr">
         <is>
-          <t>Today still shows the accepted order after reload (manualOrder persists on-device). Note: the order does not yet sync across devices, which is a documented follow-up.</t>
+          <t>The order is exactly as before, nothing reordered, and no manualOrder is written.</t>
         </is>
       </c>
       <c r="G306" s="7" t="inlineStr">
@@ -12974,7 +12974,7 @@
     <row r="307">
       <c r="A307" s="6" t="inlineStr">
         <is>
-          <t>SEQ-05</t>
+          <t>SEQ-04</t>
         </is>
       </c>
       <c r="B307" s="7" t="inlineStr">
@@ -12982,24 +12982,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C307" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C307" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
-          <t>A pinned task still wins the very top</t>
+          <t>An accepted order survives a reload (local-first)</t>
         </is>
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>As premium, pin a task, then accept a 'Plan my day' sequence that puts a different task first.</t>
+          <t>As premium, accept an order, then fully reload the app.</t>
         </is>
       </c>
       <c r="F307" s="9" t="inlineStr">
         <is>
-          <t>The pinned task stays at the very top, and the accepted order applies to everything below it.</t>
+          <t>Today still shows the accepted order after reload (manualOrder persists on-device). Note: the order does not yet sync across devices, which is a documented follow-up.</t>
         </is>
       </c>
       <c r="G307" s="7" t="inlineStr">
@@ -13014,7 +13014,7 @@
     <row r="308">
       <c r="A308" s="6" t="inlineStr">
         <is>
-          <t>SEQ-06</t>
+          <t>SEQ-05</t>
         </is>
       </c>
       <c r="B308" s="7" t="inlineStr">
@@ -13022,24 +13022,24 @@
           <t>Sequence</t>
         </is>
       </c>
-      <c r="C308" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C308" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
-          <t>Plan my day offers to lighten a heavy day</t>
+          <t>A pinned task still wins the very top</t>
         </is>
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>As premium on a heavy day (6+ tasks), tap 'Plan my day', accept the order.</t>
+          <t>As premium, pin a task, then accept a 'Plan my day' sequence that puts a different task first.</t>
         </is>
       </c>
       <c r="F308" s="9" t="inlineStr">
         <is>
-          <t>After the order applies, a 'Still a full day?' card offers to push a few tasks out to later days. Yes runs the re-spread (propose-then-accept), No leaves it ordered. On a calm day the offer never appears.</t>
+          <t>The pinned task stays at the very top, and the accepted order applies to everything below it.</t>
         </is>
       </c>
       <c r="G308" s="7" t="inlineStr">
@@ -13054,32 +13054,32 @@
     <row r="309">
       <c r="A309" s="6" t="inlineStr">
         <is>
-          <t>BIG-01</t>
+          <t>SEQ-06</t>
         </is>
       </c>
       <c r="B309" s="7" t="inlineStr">
         <is>
-          <t>Big task</t>
-        </is>
-      </c>
-      <c r="C309" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Sequence</t>
+        </is>
+      </c>
+      <c r="C309" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
-          <t>Mark a task big: the tag, and the weight it adds</t>
+          <t>Plan my day offers to lighten a heavy day</t>
         </is>
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>On Today with a few one-off tasks, tap and hold one, then tap 'Mark as a lot' in the held row's actions. ALSO hold a RECURRING task and confirm 'Mark as a lot' is offered there too (a chore can be a lot; this used to be offered only via the bulk bar).</t>
+          <t>As premium on a heavy day (6+ tasks), tap 'Plan my day', accept the order.</t>
         </is>
       </c>
       <c r="F309" s="9" t="inlineStr">
         <is>
-          <t>The card closes and the task shows a calm accent 'Big' tag beside its title (never red, never a warning), with a brief validating note ('Marked as a lot...'). The weight gauge fills further and reads heavier (one big task floors the bar to at least 'A full day, but doable.'). Free for everyone, no upsell.</t>
+          <t>After the order applies, a 'Still a full day?' card offers to push a few tasks out to later days. Yes runs the re-spread (propose-then-accept), No leaves it ordered. On a calm day the offer never appears.</t>
         </is>
       </c>
       <c r="G309" s="7" t="inlineStr">
@@ -13094,7 +13094,7 @@
     <row r="310">
       <c r="A310" s="6" t="inlineStr">
         <is>
-          <t>BIG-02</t>
+          <t>BIG-01</t>
         </is>
       </c>
       <c r="B310" s="7" t="inlineStr">
@@ -13102,24 +13102,24 @@
           <t>Big task</t>
         </is>
       </c>
-      <c r="C310" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C310" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
-          <t>Big is a multi-select toggle</t>
+          <t>Mark a task big: the tag, and the weight it adds</t>
         </is>
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>Hold a task, 'Select more', tick another, then tap 'Mark as a lot'; then re-select tasks that are all big and tap the action again (it now reads 'Not big').</t>
+          <t>On Today with a few one-off tasks, tap and hold one, then tap 'Mark as a lot' in the held row's actions. ALSO hold a RECURRING task and confirm 'Mark as a lot' is offered there too (a chore can be a lot; this used to be offered only via the bulk bar).</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
         <is>
-          <t>The first tap marks every selected task big at once. When all selected tasks are already big the action reads 'Not big' and clears the mark off all of them. A mixed selection marks all big (the additive default).</t>
+          <t>The card closes and the task shows a calm accent 'Big' tag beside its title (never red, never a warning), with a brief validating note ('Marked as a lot...'). The weight gauge fills further and reads heavier (one big task floors the bar to at least 'A full day, but doable.'). Free for everyone, no upsell.</t>
         </is>
       </c>
       <c r="G310" s="7" t="inlineStr">
@@ -13134,7 +13134,7 @@
     <row r="311">
       <c r="A311" s="6" t="inlineStr">
         <is>
-          <t>BIG-03</t>
+          <t>BIG-02</t>
         </is>
       </c>
       <c r="B311" s="7" t="inlineStr">
@@ -13149,17 +13149,17 @@
       </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
-          <t>A lone big task lifts the bar but is not a re-spread problem</t>
+          <t>Big is a multi-select toggle</t>
         </is>
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>Have just one or two tasks on Today, one marked big.</t>
+          <t>Hold a task, 'Select more', tick another, then tap 'Mark as a lot'; then re-select tasks that are all big and tap the action again (it now reads 'Not big').</t>
         </is>
       </c>
       <c r="F311" s="9" t="inlineStr">
         <is>
-          <t>The weight gauge reads at least 'A full day, but doable.' (the big task is felt), but 'Today's looking full' and 'Lighten today' do NOT appear for a lone big task (re-spreading cannot dissolve one big rock; Break it down is the tool). A big task plus a real pile (weighted load 6+) does surface Lighten today.</t>
+          <t>The first tap marks every selected task big at once. When all selected tasks are already big the action reads 'Not big' and clears the mark off all of them. A mixed selection marks all big (the additive default).</t>
         </is>
       </c>
       <c r="G311" s="7" t="inlineStr">
@@ -13174,7 +13174,7 @@
     <row r="312">
       <c r="A312" s="6" t="inlineStr">
         <is>
-          <t>BIG-04</t>
+          <t>BIG-03</t>
         </is>
       </c>
       <c r="B312" s="7" t="inlineStr">
@@ -13189,17 +13189,17 @@
       </c>
       <c r="D312" s="9" t="inlineStr">
         <is>
-          <t>Finishing a big task is a big-win in the Calendar</t>
+          <t>A lone big task lifts the bar but is not a re-spread problem</t>
         </is>
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>Mark a task big, complete it, then open the Calendar to its day.</t>
+          <t>Have just one or two tasks on Today, one marked big.</t>
         </is>
       </c>
       <c r="F312" s="9" t="inlineStr">
         <is>
-          <t>The completed task carries the warmer 'a big one' treatment on its day, the same payoff a long-dreaded or chunky task earns. The big flag never adds disappointment if the task is left unfinished.</t>
+          <t>The weight gauge reads at least 'A full day, but doable.' (the big task is felt), but 'Today's looking full' and 'Lighten today' do NOT appear for a lone big task (re-spreading cannot dissolve one big rock; Break it down is the tool). A big task plus a real pile (weighted load 6+) does surface Lighten today.</t>
         </is>
       </c>
       <c r="G312" s="7" t="inlineStr">
@@ -13214,7 +13214,7 @@
     <row r="313">
       <c r="A313" s="6" t="inlineStr">
         <is>
-          <t>BIG-05</t>
+          <t>BIG-04</t>
         </is>
       </c>
       <c r="B313" s="7" t="inlineStr">
@@ -13229,17 +13229,17 @@
       </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
-          <t>Big syncs across devices (and old marks survive the upgrade)</t>
+          <t>Finishing a big task is a big-win in the Calendar</t>
         </is>
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>Signed in on two devices (e.g. web + Android). Mark a task big on device 1, wait for or trigger a sync, then open device 2. Then unmark it on device 2 and check device 1. Prerequisite: an account with the same task on both.</t>
+          <t>Mark a task big, complete it, then open the Calendar to its day.</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>The Big tag appears on device 2 (with its weight-gauge effect), and the unmark travels back: no resurrection, the newest change wins. Marks made BEFORE this build (when big was device-only) are seeded up to the account on that device's first sync rather than erased. One known transition quirk: a device still on a PRE-sync build can re-surface a cleared big once when it upgrades; clearing it again sticks everywhere. Manual order (Plan my order) remains per-device by design.</t>
+          <t>The completed task carries the warmer 'a big one' treatment on its day, the same payoff a long-dreaded or chunky task earns. The big flag never adds disappointment if the task is left unfinished.</t>
         </is>
       </c>
       <c r="G313" s="7" t="inlineStr">
@@ -13254,37 +13254,37 @@
     <row r="314">
       <c r="A314" s="6" t="inlineStr">
         <is>
-          <t>NAV-01</t>
+          <t>BIG-05</t>
         </is>
       </c>
       <c r="B314" s="7" t="inlineStr">
         <is>
-          <t>Rooms</t>
-        </is>
-      </c>
-      <c r="C314" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>Big task</t>
+        </is>
+      </c>
+      <c r="C314" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
-          <t>Rooms sheet caps its width on wide web</t>
+          <t>Big syncs across devices (and old marks survive the upgrade)</t>
         </is>
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>On a wide desktop browser, open Rooms (the header pill).</t>
+          <t>Signed in on two devices (e.g. web + Android). Mark a task big on device 1, wait for or trigger a sync, then open device 2. Then unmark it on device 2 and check device 1. Prerequisite: an account with the same task on both.</t>
         </is>
       </c>
       <c r="F314" s="9" t="inlineStr">
         <is>
-          <t>The sheet is a centred column (about 560px, matching the page content), not full-bleed, so the 'Premium' gradient pill on 'Chart a course' sits beside its label rather than at the far screen edge. On a phone the sheet stays full-width with the pill at the row's edge.</t>
+          <t>The Big tag appears on device 2 (with its weight-gauge effect), and the unmark travels back: no resurrection, the newest change wins. Marks made BEFORE this build (when big was device-only) are seeded up to the account on that device's first sync rather than erased. One known transition quirk: a device still on a PRE-sync build can re-surface a cleared big once when it upgrades; clearing it again sticks everywhere. Manual order (Plan my order) remains per-device by design.</t>
         </is>
       </c>
       <c r="G314" s="7" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H314" s="7" t="inlineStr"/>
@@ -13294,37 +13294,37 @@
     <row r="315">
       <c r="A315" s="6" t="inlineStr">
         <is>
-          <t>OUR-01</t>
+          <t>NAV-01</t>
         </is>
       </c>
       <c r="B315" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C315" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="C315" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
-          <t>The door only exists for an allowed account</t>
+          <t>Rooms sheet caps its width on wide web</t>
         </is>
       </c>
       <c r="E315" s="9" t="inlineStr">
         <is>
-          <t>Sign in as an account that is NOT on the ours_allowlist and open Settings. Then sign in as one that is.</t>
+          <t>On a wide desktop browser, open Rooms (the header pill).</t>
         </is>
       </c>
       <c r="F315" s="9" t="inlineStr">
         <is>
-          <t>The 'Ours' row is absent for the first account and present for the second. Nobody is ever offered a door that answers 'shared lists aren't open yet'.</t>
+          <t>The sheet is a centred column (about 560px, matching the page content), not full-bleed, so the 'Premium' gradient pill on 'Chart a course' sits beside its label rather than at the far screen edge. On a phone the sheet stays full-width with the pill at the row's edge.</t>
         </is>
       </c>
       <c r="G315" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H315" s="7" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
     <row r="316">
       <c r="A316" s="6" t="inlineStr">
         <is>
-          <t>OUR-02</t>
+          <t>OUR-01</t>
         </is>
       </c>
       <c r="B316" s="7" t="inlineStr">
@@ -13349,17 +13349,17 @@
       </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
-          <t>Signed out: the explanation, never a nag</t>
+          <t>The door only exists for an allowed account</t>
         </is>
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>Sign out, then open /ours directly.</t>
+          <t>Sign in as an account that is NOT on the ours_allowlist and open Settings. Then sign in as one that is.</t>
         </is>
       </c>
       <c r="F316" s="9" t="inlineStr">
         <is>
-          <t>A calm one-screen explanation of why sharing needs an account, and a way to sign in. No pressure, no count of what you are missing.</t>
+          <t>The 'Ours' row is absent for the first account and present for the second. Nobody is ever offered a door that answers 'shared lists aren't open yet'.</t>
         </is>
       </c>
       <c r="G316" s="7" t="inlineStr">
@@ -13374,7 +13374,7 @@
     <row r="317">
       <c r="A317" s="6" t="inlineStr">
         <is>
-          <t>OUR-03</t>
+          <t>OUR-02</t>
         </is>
       </c>
       <c r="B317" s="7" t="inlineStr">
@@ -13389,17 +13389,17 @@
       </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
-          <t>Name the list and mint a code</t>
+          <t>Signed out: the explanation, never a nag</t>
         </is>
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>Ours &gt; Start a shared list. Pick 'The house'. Type your own name. Type the OTHER account's email exactly. Get a code.</t>
+          <t>Sign out, then open /ours directly.</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
         <is>
-          <t>A six-character code appears grouped as XXX-XXX, containing no 0, 1, I, L or O. The screen says it works once, for the next day, and only for the address you gave.</t>
+          <t>A calm one-screen explanation of why sharing needs an account, and a way to sign in. No pressure, no count of what you are missing.</t>
         </is>
       </c>
       <c r="G317" s="7" t="inlineStr">
@@ -13414,7 +13414,7 @@
     <row r="318">
       <c r="A318" s="6" t="inlineStr">
         <is>
-          <t>OUR-04</t>
+          <t>OUR-03</t>
         </is>
       </c>
       <c r="B318" s="7" t="inlineStr">
@@ -13429,17 +13429,17 @@
       </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
-          <t>Join from the second account</t>
+          <t>Name the list and mint a code</t>
         </is>
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>On the second account, Ours &gt; Join with a code. Type the code (try it lower-case and with the dash). Type your own name. Join.</t>
+          <t>Ours &gt; Start a shared list. Pick 'The house'. Type your own name. Type the OTHER account's email exactly. Get a code.</t>
         </is>
       </c>
       <c r="F318" s="9" t="inlineStr">
         <is>
-          <t>You land on the shared list showing the FIRST person's chosen name and the list's name ('The house'). No email address is shown anywhere, to either person.</t>
+          <t>A six-character code appears grouped as XXX-XXX, containing no 0, 1, I, L or O. The screen says it works once, for the next day, and only for the address you gave.</t>
         </is>
       </c>
       <c r="G318" s="7" t="inlineStr">
@@ -13454,7 +13454,7 @@
     <row r="319">
       <c r="A319" s="6" t="inlineStr">
         <is>
-          <t>OUR-05</t>
+          <t>OUR-04</t>
         </is>
       </c>
       <c r="B319" s="7" t="inlineStr">
@@ -13469,17 +13469,17 @@
       </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
-          <t>The first person sees the arrival without refreshing</t>
+          <t>Join from the second account</t>
         </is>
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>Leave the first account sitting on the Ours screen while the second joins.</t>
+          <t>On the second account, Ours &gt; Join with a code. Type the code (try it lower-case and with the dash). Type your own name. Join.</t>
         </is>
       </c>
       <c r="F319" s="9" t="inlineStr">
         <is>
-          <t>Within about ten seconds it announces that they joined, with a way out for someone who meant a different person. It never says how long they took.</t>
+          <t>You land on the shared list showing the FIRST person's chosen name and the list's name ('The house'). No email address is shown anywhere, to either person.</t>
         </is>
       </c>
       <c r="G319" s="7" t="inlineStr">
@@ -13494,7 +13494,7 @@
     <row r="320">
       <c r="A320" s="6" t="inlineStr">
         <is>
-          <t>OUR-06</t>
+          <t>OUR-05</t>
         </is>
       </c>
       <c r="B320" s="7" t="inlineStr">
@@ -13502,24 +13502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C320" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C320" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
-          <t>A wrong code says one calm thing</t>
+          <t>The first person sees the arrival without refreshing</t>
         </is>
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>Try a made-up code, then a code meant for a different address, then the same code twice.</t>
+          <t>Leave the first account sitting on the Ours screen while the second joins.</t>
         </is>
       </c>
       <c r="F320" s="9" t="inlineStr">
         <is>
-          <t>Every one gives the SAME single line ('That code isn't valid.'). Nothing hints at which reason, so a guesser learns nothing. Repeated wrong tries eventually ask you to have a break.</t>
+          <t>Within about ten seconds it announces that they joined, with a way out for someone who meant a different person. It never says how long they took.</t>
         </is>
       </c>
       <c r="G320" s="7" t="inlineStr">
@@ -13534,7 +13534,7 @@
     <row r="321">
       <c r="A321" s="6" t="inlineStr">
         <is>
-          <t>OUR-07</t>
+          <t>OUR-06</t>
         </is>
       </c>
       <c r="B321" s="7" t="inlineStr">
@@ -13549,17 +13549,17 @@
       </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
-          <t>Mistyped invitee address is recoverable</t>
+          <t>A wrong code says one calm thing</t>
         </is>
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>Mint a code with a deliberately wrong email, then use 'Wrong address? Start again' and mint a fresh one with the right address.</t>
+          <t>Try a made-up code, then a code meant for a different address, then the same code twice.</t>
         </is>
       </c>
       <c r="F321" s="9" t="inlineStr">
         <is>
-          <t>The new code works and the old one does not. Nothing had to be deleted to recover, and no address is ever displayed back to you.</t>
+          <t>Every one gives the SAME single line ('That code isn't valid.'). Nothing hints at which reason, so a guesser learns nothing. Repeated wrong tries eventually ask you to have a break.</t>
         </is>
       </c>
       <c r="G321" s="7" t="inlineStr">
@@ -13574,7 +13574,7 @@
     <row r="322">
       <c r="A322" s="6" t="inlineStr">
         <is>
-          <t>OUR-08</t>
+          <t>OUR-07</t>
         </is>
       </c>
       <c r="B322" s="7" t="inlineStr">
@@ -13589,17 +13589,17 @@
       </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
-          <t>Rename the list, and both sides see it</t>
+          <t>Mistyped invitee address is recoverable</t>
         </is>
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>On the shared list, tap the list's name, type a new one, and confirm. Reopen Ours on the other account.</t>
+          <t>Mint a code with a deliberately wrong email, then use 'Wrong address? Start again' and mint a fresh one with the right address.</t>
         </is>
       </c>
       <c r="F322" s="9" t="inlineStr">
         <is>
-          <t>Both people see the new name. An emptied name falls back to the app's own word, in each person's own language.</t>
+          <t>The new code works and the old one does not. Nothing had to be deleted to recover, and no address is ever displayed back to you.</t>
         </is>
       </c>
       <c r="G322" s="7" t="inlineStr">
@@ -13614,7 +13614,7 @@
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
         <is>
-          <t>OUR-09</t>
+          <t>OUR-08</t>
         </is>
       </c>
       <c r="B323" s="7" t="inlineStr">
@@ -13622,24 +13622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C323" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C323" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
-          <t>Leaving freezes and takes nothing</t>
+          <t>Rename the list, and both sides see it</t>
         </is>
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>On one account, Leave this list. Then open Ours on BOTH accounts.</t>
+          <t>On the shared list, tap the list's name, type a new one, and confirm. Reopen Ours on the other account.</t>
         </is>
       </c>
       <c r="F323" s="9" t="inlineStr">
         <is>
-          <t>Both see 'This list is closed' and can still read everything. Nothing was deleted from either side. Neither person is told off, and neither is told what the other did.</t>
+          <t>Both people see the new name. An emptied name falls back to the app's own word, in each person's own language.</t>
         </is>
       </c>
       <c r="G323" s="7" t="inlineStr">
@@ -13654,7 +13654,7 @@
     <row r="324">
       <c r="A324" s="6" t="inlineStr">
         <is>
-          <t>OUR-10</t>
+          <t>OUR-09</t>
         </is>
       </c>
       <c r="B324" s="7" t="inlineStr">
@@ -13662,24 +13662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C324" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C324" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
-          <t>Remove a closed list from your side only</t>
+          <t>Leaving freezes and takes nothing</t>
         </is>
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Remove this list'. Then check the other account.</t>
+          <t>On one account, Leave this list. Then open Ours on BOTH accounts.</t>
         </is>
       </c>
       <c r="F324" s="9" t="inlineStr">
         <is>
-          <t>It disappears for you. The other person still has their copy and is not notified.</t>
+          <t>Both see 'This list is closed' and can still read everything. Nothing was deleted from either side. Neither person is told off, and neither is told what the other did.</t>
         </is>
       </c>
       <c r="G324" s="7" t="inlineStr">
@@ -13694,7 +13694,7 @@
     <row r="325">
       <c r="A325" s="6" t="inlineStr">
         <is>
-          <t>OUR-11</t>
+          <t>OUR-10</t>
         </is>
       </c>
       <c r="B325" s="7" t="inlineStr">
@@ -13702,24 +13702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C325" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C325" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
-          <t>Nothing anywhere attributes a task to a person</t>
+          <t>Remove a closed list from your side only</t>
         </is>
       </c>
       <c r="E325" s="9" t="inlineStr">
         <is>
-          <t>With a shared list live, look at Ours, Today, the Lookback and Settings on both accounts.</t>
+          <t>On a closed list, tap 'Remove this list'. Then check the other account.</t>
         </is>
       </c>
       <c r="F325" s="9" t="inlineStr">
         <is>
-          <t>No initials, no 'done by', no counts of who did what, no progress bar across two people, no activity feed. The data to build one does not exist.</t>
+          <t>It disappears for you. The other person still has their copy and is not notified.</t>
         </is>
       </c>
       <c r="G325" s="7" t="inlineStr">
@@ -13734,7 +13734,7 @@
     <row r="326">
       <c r="A326" s="6" t="inlineStr">
         <is>
-          <t>OUR-13</t>
+          <t>OUR-11</t>
         </is>
       </c>
       <c r="B326" s="7" t="inlineStr">
@@ -13749,17 +13749,17 @@
       </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
-          <t>The code stays on screen from the moment it is minted</t>
+          <t>Nothing anywhere attributes a task to a person</t>
         </is>
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>On a throttled connection (devtools, slow 3G), fill the create form and tap the code button.</t>
+          <t>With a shared list live, look at Ours, Today, the Lookback and Settings on both accounts.</t>
         </is>
       </c>
       <c r="F326" s="9" t="inlineStr">
         <is>
-          <t>The six characters appear as soon as the button stops spinning and are NEVER replaced by the intro screen. The server returns that code exactly once, so a flash back to 'Start a shared list' loses it for good.</t>
+          <t>No initials, no 'done by', no counts of who did what, no progress bar across two people, no activity feed. The data to build one does not exist.</t>
         </is>
       </c>
       <c r="G326" s="7" t="inlineStr">
@@ -13774,7 +13774,7 @@
     <row r="327">
       <c r="A327" s="6" t="inlineStr">
         <is>
-          <t>OUR-14</t>
+          <t>OUR-13</t>
         </is>
       </c>
       <c r="B327" s="7" t="inlineStr">
@@ -13789,17 +13789,17 @@
       </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
-          <t>'Get a new code' reaches the form and mints a different code</t>
+          <t>The code stays on screen from the moment it is minted</t>
         </is>
       </c>
       <c r="E327" s="9" t="inlineStr">
         <is>
-          <t>From the waiting screen, tap the get-a-new-code action. Change the email. Submit.</t>
+          <t>On a throttled connection (devtools, slow 3G), fill the create form and tap the code button.</t>
         </is>
       </c>
       <c r="F327" s="9" t="inlineStr">
         <is>
-          <t>The create form appears with your name and list name already filled. Submitting shows a DIFFERENT six characters, and the old one no longer works. Your chosen name is unchanged afterwards.</t>
+          <t>The six characters appear as soon as the button stops spinning and are NEVER replaced by the intro screen. The server returns that code exactly once, so a flash back to 'Start a shared list' loses it for good.</t>
         </is>
       </c>
       <c r="G327" s="7" t="inlineStr">
@@ -13814,7 +13814,7 @@
     <row r="328">
       <c r="A328" s="6" t="inlineStr">
         <is>
-          <t>OUR-120</t>
+          <t>OUR-14</t>
         </is>
       </c>
       <c r="B328" s="7" t="inlineStr">
@@ -13829,17 +13829,17 @@
       </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>Waiting-with-no-code is reachable, says so, and the re-mint is a real button</t>
+          <t>'Get a new code' reaches the form and mints a different code</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>Mint a code, leave Ours entirely (back to Today), then come back via the MENU's Ours row before anyone joins.</t>
+          <t>From the waiting screen, tap the get-a-new-code action. Change the email. Submit.</t>
         </is>
       </c>
       <c r="F328" s="9" t="inlineStr">
         <is>
-          <t>The Menu lands on the shared LIST (usable solo while waiting), and the list's header line reads 'Waiting for your person - Get a new code' where 'Kept with {name}' will later sit; tapping it opens the pairing screen (both Melroy's C6 check and the field report hit this as a dead end before 2026-09-20). That screen is titled 'Waiting for your person', NOT 'Read this to your person' over an empty space (the code renders exactly once; the server keeps only a hash, so it can never be re-shown), and 'Get a new code' is a full primary button there, not a quiet text link. While the code IS still on screen, the old title and quiet link stay as they were.</t>
+          <t>The create form appears with your name and list name already filled. Submitting shows a DIFFERENT six characters, and the old one no longer works. Your chosen name is unchanged afterwards.</t>
         </is>
       </c>
       <c r="G328" s="7" t="inlineStr">
@@ -13854,7 +13854,7 @@
     <row r="329">
       <c r="A329" s="6" t="inlineStr">
         <is>
-          <t>OUR-121</t>
+          <t>OUR-120</t>
         </is>
       </c>
       <c r="B329" s="7" t="inlineStr">
@@ -13869,17 +13869,17 @@
       </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>Whose email, and which code goes where</t>
+          <t>Waiting-with-no-code is reachable, says so, and the re-mint is a real button</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>Signed out: read the Menu's Ours line, open Ours, read the signed-out screen, tap Sign in and read the field. Then, on the sign-in code step, paste an Ours-style code (letters in it). Separately, signed in, open Ours 'I have a code' and type a 6-digit emailed sign-in code.</t>
+          <t>Mint a code, leave Ours entirely (back to Today), then come back via the MENU's Ours row before anyone joins.</t>
         </is>
       </c>
       <c r="F329" s="9" t="inlineStr">
         <is>
-          <t>The Menu's Ours line reads 'A list kept with one person. Sign in first.' (the old 'Needs your email, no password' invited typing the PARTNER'S email; a real user did exactly that on 2026-09-13 and it became their account). The Ours signed-out screen opens with the plain fact 'You're not signed in on this phone.' The sign-in email field is labelled 'Your own email', and the subtitle says sharing happens later, in Ours, with a code, never by typing the partner's email here. Letters in the 6-digit code field draw the calm hint that it will be an Ours invite code (a hint, never an auto-redirect or a cleared field). Six bare digits failing in the Ours join field add one line naming the emailed sign-in code as the likely mix-up, alongside the unchanged honest failure.</t>
+          <t>The Menu lands on the shared LIST (usable solo while waiting), and the list's header line reads 'Waiting for your person - Get a new code' where 'Kept with {name}' will later sit; tapping it opens the pairing screen (both Melroy's C6 check and the field report hit this as a dead end before 2026-09-20). That screen is titled 'Waiting for your person', NOT 'Read this to your person' over an empty space (the code renders exactly once; the server keeps only a hash, so it can never be re-shown), and 'Get a new code' is a full primary button there, not a quiet text link. While the code IS still on screen, the old title and quiet link stay as they were.</t>
         </is>
       </c>
       <c r="G329" s="7" t="inlineStr">
@@ -13894,7 +13894,7 @@
     <row r="330">
       <c r="A330" s="6" t="inlineStr">
         <is>
-          <t>OUR-15</t>
+          <t>OUR-121</t>
         </is>
       </c>
       <c r="B330" s="7" t="inlineStr">
@@ -13909,17 +13909,17 @@
       </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
-          <t>Leave a list, then start a new one WITHOUT deleting the old</t>
+          <t>Whose email, and which code goes where</t>
         </is>
       </c>
       <c r="E330" s="9" t="inlineStr">
         <is>
-          <t>Leave a shared list. On the closed screen, start a new shared list with someone else.</t>
+          <t>Signed out: read the Menu's Ours line, open Ours, read the signed-out screen, tap Sign in and read the field. Then, on the sign-in code step, paste an Ours-style code (letters in it). Separately, signed in, open Ours 'I have a code' and type a 6-digit emailed sign-in code.</t>
         </is>
       </c>
       <c r="F330" s="9" t="inlineStr">
         <is>
-          <t>Starting a new list is offered on the closed screen itself and works. The old list is NOT deleted and is still readable. At no point is destroying it the only way forward.</t>
+          <t>The Menu's Ours line reads 'A list kept with one person. Sign in first.' (the old 'Needs your email, no password' invited typing the PARTNER'S email; a real user did exactly that on 2026-09-13 and it became their account). The Ours signed-out screen opens with the plain fact 'You're not signed in on this phone.' The sign-in email field is labelled 'Your own email', and the subtitle says sharing happens later, in Ours, with a code, never by typing the partner's email here. Letters in the 6-digit code field draw the calm hint that it will be an Ours invite code (a hint, never an auto-redirect or a cleared field). Six bare digits failing in the Ours join field add one line naming the emailed sign-in code as the likely mix-up, alongside the unchanged honest failure.</t>
         </is>
       </c>
       <c r="G330" s="7" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="331">
       <c r="A331" s="6" t="inlineStr">
         <is>
-          <t>OUR-16</t>
+          <t>OUR-15</t>
         </is>
       </c>
       <c r="B331" s="7" t="inlineStr">
@@ -13949,17 +13949,17 @@
       </c>
       <c r="D331" s="9" t="inlineStr">
         <is>
-          <t>A failed read never offers to start a list you already have</t>
+          <t>Leave a list, then start a new one WITHOUT deleting the old</t>
         </is>
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, turn the network off and open Ours.</t>
+          <t>Leave a shared list. On the closed screen, start a new shared list with someone else.</t>
         </is>
       </c>
       <c r="F331" s="9" t="inlineStr">
         <is>
-          <t>A calm connection line. The screen never says you have no shared list and never offers to start one. Turning the network back on recovers without a restart.</t>
+          <t>Starting a new list is offered on the closed screen itself and works. The old list is NOT deleted and is still readable. At no point is destroying it the only way forward.</t>
         </is>
       </c>
       <c r="G331" s="7" t="inlineStr">
@@ -13974,7 +13974,7 @@
     <row r="332">
       <c r="A332" s="6" t="inlineStr">
         <is>
-          <t>OUR-17</t>
+          <t>OUR-16</t>
         </is>
       </c>
       <c r="B332" s="7" t="inlineStr">
@@ -13982,24 +13982,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C332" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C332" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D332" s="9" t="inlineStr">
         <is>
-          <t>A list nobody joined can be left</t>
+          <t>A failed read never offers to start a list you already have</t>
         </is>
       </c>
       <c r="E332" s="9" t="inlineStr">
         <is>
-          <t>Create a list, get a code, give it to nobody. Return to Ours.</t>
+          <t>With a live shared list, turn the network off and open Ours.</t>
         </is>
       </c>
       <c r="F332" s="9" t="inlineStr">
         <is>
-          <t>There is a way out on the waiting screen, and its wording does not claim it closes for two people. After leaving, you can start or join a list again.</t>
+          <t>A calm connection line. The screen never says you have no shared list and never offers to start one. Turning the network back on recovers without a restart.</t>
         </is>
       </c>
       <c r="G332" s="7" t="inlineStr">
@@ -14014,7 +14014,7 @@
     <row r="333">
       <c r="A333" s="6" t="inlineStr">
         <is>
-          <t>OUR-18</t>
+          <t>OUR-17</t>
         </is>
       </c>
       <c r="B333" s="7" t="inlineStr">
@@ -14029,17 +14029,17 @@
       </c>
       <c r="D333" s="9" t="inlineStr">
         <is>
-          <t>The arrival announces once and stays announced</t>
+          <t>A list nobody joined can be left</t>
         </is>
       </c>
       <c r="E333" s="9" t="inlineStr">
         <is>
-          <t>Sit on the waiting screen while the other account joins. Background the app and return.</t>
+          <t>Create a list, get a code, give it to nobody. Return to Ours.</t>
         </is>
       </c>
       <c r="F333" s="9" t="inlineStr">
         <is>
-          <t>The name appears once and does not flicker back to waiting and re-announce. The way out beside it ('that wasn't who I meant') never appears on a list you did not just gain a person on.</t>
+          <t>There is a way out on the waiting screen, and its wording does not claim it closes for two people. After leaving, you can start or join a list again.</t>
         </is>
       </c>
       <c r="G333" s="7" t="inlineStr">
@@ -14054,7 +14054,7 @@
     <row r="334">
       <c r="A334" s="6" t="inlineStr">
         <is>
-          <t>OUR-19</t>
+          <t>OUR-18</t>
         </is>
       </c>
       <c r="B334" s="7" t="inlineStr">
@@ -14069,17 +14069,17 @@
       </c>
       <c r="D334" s="9" t="inlineStr">
         <is>
-          <t>A repeat the app cannot read is SHOWN, never hidden</t>
+          <t>The arrival announces once and stays announced</t>
         </is>
       </c>
       <c r="E334" s="9" t="inlineStr">
         <is>
-          <t>Requires two app versions. On the newer one, set a shared task to a cadence the older build does not have. Open the list on the older build.</t>
+          <t>Sit on the waiting screen while the other account joins. Background the app and return.</t>
         </is>
       </c>
       <c r="F334" s="9" t="inlineStr">
         <is>
-          <t>The task is visible on both, with whatever cadence line the newer app left. It is never silently absent from one person's list, and the older app does not erase the schedule when it syncs.</t>
+          <t>The name appears once and does not flicker back to waiting and re-announce. The way out beside it ('that wasn't who I meant') never appears on a list you did not just gain a person on.</t>
         </is>
       </c>
       <c r="G334" s="7" t="inlineStr">
@@ -14094,7 +14094,7 @@
     <row r="335">
       <c r="A335" s="6" t="inlineStr">
         <is>
-          <t>OUR-20</t>
+          <t>OUR-19</t>
         </is>
       </c>
       <c r="B335" s="7" t="inlineStr">
@@ -14102,24 +14102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C335" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C335" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D335" s="9" t="inlineStr">
         <is>
-          <t>The room opens from Today's heading and from the Menu</t>
+          <t>A repeat the app cannot read is SHOWN, never hidden</t>
         </is>
       </c>
       <c r="E335" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, tap the list's name beside 'Today' in Today's heading. Then go back and reach it through Menu › Ours.</t>
+          <t>Requires two app versions. On the newer one, set a shared task to a cadence the older build does not have. Open the list on the older build.</t>
         </is>
       </c>
       <c r="F335" s="9" t="inlineStr">
         <is>
-          <t>Both land on the shared list itself, not the pairing screen, with a fade (a tab changing), not a sideways slide. The room's heading reads 'Today' and the list's name side by side, the name underlined as the current one, then the line 'Shared. Anything with a day reaches both your Todays on that day.' The date and the same Menu pill sit above it. 'Kept with {their name} ›' still goes to the pairing/management screen. Tapping 'Today' in the room's heading goes back to Today.</t>
+          <t>The task is visible on both, with whatever cadence line the newer app left. It is never silently absent from one person's list, and the older app does not erase the schedule when it syncs.</t>
         </is>
       </c>
       <c r="G335" s="7" t="inlineStr">
@@ -14134,7 +14134,7 @@
     <row r="336">
       <c r="A336" s="6" t="inlineStr">
         <is>
-          <t>OUR-21</t>
+          <t>OUR-20</t>
         </is>
       </c>
       <c r="B336" s="7" t="inlineStr">
@@ -14149,17 +14149,17 @@
       </c>
       <c r="D336" s="9" t="inlineStr">
         <is>
-          <t>Add, tick and UN-tick on the shared list</t>
+          <t>The room opens from Today's heading and from the Menu</t>
         </is>
       </c>
       <c r="E336" s="9" t="inlineStr">
         <is>
-          <t>Add a task in the room. Tick it. Un-tick it. Watch the other account (reload or wait ~15s).</t>
+          <t>With a live shared list, tap the list's name beside 'Today' in Today's heading. Then go back and reach it through Menu › Ours.</t>
         </is>
       </c>
       <c r="F336" s="9" t="inlineStr">
         <is>
-          <t>Every step appears on both. Un-ticking works as easily as ticking, on both sides. No affirmation or celebration fires on Ours.</t>
+          <t>Both land on the shared list itself, not the pairing screen, with a fade (a tab changing), not a sideways slide. The room's heading reads 'Today' and the list's name side by side, the name underlined as the current one, then the line 'Shared. Anything with a day reaches both your Todays on that day.' The date and the same Menu pill sit above it. 'Kept with {their name} ›' still goes to the pairing/management screen. Tapping 'Today' in the room's heading goes back to Today.</t>
         </is>
       </c>
       <c r="G336" s="7" t="inlineStr">
@@ -14174,7 +14174,7 @@
     <row r="337">
       <c r="A337" s="6" t="inlineStr">
         <is>
-          <t>OUR-22</t>
+          <t>OUR-21</t>
         </is>
       </c>
       <c r="B337" s="7" t="inlineStr">
@@ -14189,17 +14189,17 @@
       </c>
       <c r="D337" s="9" t="inlineStr">
         <is>
-          <t>Un-tick a one-off the DAY AFTER it was ticked</t>
+          <t>Add, tick and UN-tick on the shared list</t>
         </is>
       </c>
       <c r="E337" s="9" t="inlineStr">
         <is>
-          <t>Tick a shared one-off. Change the device date to tomorrow (or wait a day), reopen the room, tap it again.</t>
+          <t>Add a task in the room. Tick it. Un-tick it. Watch the other account (reload or wait ~15s).</t>
         </is>
       </c>
       <c r="F337" s="9" t="inlineStr">
         <is>
-          <t>It un-ticks. (The pre-fix build could never un-tick it again, on any device, forever.)</t>
+          <t>Every step appears on both. Un-ticking works as easily as ticking, on both sides. No affirmation or celebration fires on Ours.</t>
         </is>
       </c>
       <c r="G337" s="7" t="inlineStr">
@@ -14214,7 +14214,7 @@
     <row r="338">
       <c r="A338" s="6" t="inlineStr">
         <is>
-          <t>OUR-23</t>
+          <t>OUR-22</t>
         </is>
       </c>
       <c r="B338" s="7" t="inlineStr">
@@ -14229,17 +14229,17 @@
       </c>
       <c r="D338" s="9" t="inlineStr">
         <is>
-          <t>Bring to my Today makes a COPY, and marks only yours</t>
+          <t>Un-tick a one-off the DAY AFTER it was ticked</t>
         </is>
       </c>
       <c r="E338" s="9" t="inlineStr">
         <is>
-          <t>Hold a shared row, tap 'Bring to my Today'. Look at your Today, then at the shared list on BOTH accounts.</t>
+          <t>Tick a shared one-off. Change the device date to tomorrow (or wait a day), reopen the room, tap it again.</t>
         </is>
       </c>
       <c r="F338" s="9" t="inlineStr">
         <is>
-          <t>Your Today shows the task with a faint '· Ours'. The shared row is completely unchanged on both sides, with no marker of any kind. The held card now reads 'Already on your Today' and cannot make a second copy.</t>
+          <t>It un-ticks. (The pre-fix build could never un-tick it again, on any device, forever.)</t>
         </is>
       </c>
       <c r="G338" s="7" t="inlineStr">
@@ -14254,7 +14254,7 @@
     <row r="339">
       <c r="A339" s="6" t="inlineStr">
         <is>
-          <t>OUR-24</t>
+          <t>OUR-23</t>
         </is>
       </c>
       <c r="B339" s="7" t="inlineStr">
@@ -14269,17 +14269,17 @@
       </c>
       <c r="D339" s="9" t="inlineStr">
         <is>
-          <t>Your tick on the copy closes both</t>
+          <t>Bring to my Today makes a COPY, and marks only yours</t>
         </is>
       </c>
       <c r="E339" s="9" t="inlineStr">
         <is>
-          <t>Tick the brought copy on your Today. Check the shared list on the other account.</t>
+          <t>Hold a shared row, tap 'Bring to my Today'. Look at your Today, then at the shared list on BOTH accounts.</t>
         </is>
       </c>
       <c r="F339" s="9" t="inlineStr">
         <is>
-          <t>The shared row is done. It enters YOUR Lookback. Nothing on the other side says who did it.</t>
+          <t>Your Today shows the task with a faint '· Ours'. The shared row is completely unchanged on both sides, with no marker of any kind. The held card now reads 'Already on your Today' and cannot make a second copy.</t>
         </is>
       </c>
       <c r="G339" s="7" t="inlineStr">
@@ -14294,7 +14294,7 @@
     <row r="340">
       <c r="A340" s="6" t="inlineStr">
         <is>
-          <t>OUR-25</t>
+          <t>OUR-24</t>
         </is>
       </c>
       <c r="B340" s="7" t="inlineStr">
@@ -14309,17 +14309,17 @@
       </c>
       <c r="D340" s="9" t="inlineStr">
         <is>
-          <t>Ticking a brought copy on a device that has NEVER opened the room</t>
+          <t>Your tick on the copy closes both</t>
         </is>
       </c>
       <c r="E340" s="9" t="inlineStr">
         <is>
-          <t>Bring a task over on phone A. Sign in on a second device (or clear its local data) and go straight to Today WITHOUT opening Ours. Tick the copy there.</t>
+          <t>Tick the brought copy on your Today. Check the shared list on the other account.</t>
         </is>
       </c>
       <c r="F340" s="9" t="inlineStr">
         <is>
-          <t>The shared row closes. (The pre-fix build silently discarded the tick with no error.)</t>
+          <t>The shared row is done. It enters YOUR Lookback. Nothing on the other side says who did it.</t>
         </is>
       </c>
       <c r="G340" s="7" t="inlineStr">
@@ -14334,7 +14334,7 @@
     <row r="341">
       <c r="A341" s="6" t="inlineStr">
         <is>
-          <t>OUR-26</t>
+          <t>OUR-25</t>
         </is>
       </c>
       <c r="B341" s="7" t="inlineStr">
@@ -14349,17 +14349,17 @@
       </c>
       <c r="D341" s="9" t="inlineStr">
         <is>
-          <t>Their tick leaves a rest-note, never a strike-through</t>
+          <t>Ticking a brought copy on a device that has NEVER opened the room</t>
         </is>
       </c>
       <c r="E341" s="9" t="inlineStr">
         <is>
-          <t>Bring a task over. On the OTHER account, tick the shared row. Return to your Today.</t>
+          <t>Bring a task over on phone A. Sign in on a second device (or clear its local data) and go straight to Today WITHOUT opening Ours. Tick the copy there.</t>
         </is>
       </c>
       <c r="F341" s="9" t="inlineStr">
         <is>
-          <t>Your copy is gone from the day, replaced by a dashed sage line: 'Handled on Ours. It's off your day.' It is NOT struck through and does NOT appear in your Lookback. Leaving Today and coming back clears the note.</t>
+          <t>The shared row closes. (The pre-fix build silently discarded the tick with no error.)</t>
         </is>
       </c>
       <c r="G341" s="7" t="inlineStr">
@@ -14374,7 +14374,7 @@
     <row r="342">
       <c r="A342" s="6" t="inlineStr">
         <is>
-          <t>OUR-27</t>
+          <t>OUR-26</t>
         </is>
       </c>
       <c r="B342" s="7" t="inlineStr">
@@ -14382,24 +14382,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C342" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C342" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>Share to Ours warns about the length BEFORE it copies</t>
+          <t>Their tick leaves a rest-note, never a strike-through</t>
         </is>
       </c>
       <c r="E342" s="9" t="inlineStr">
         <is>
-          <t>Hold one of your own Today tasks with a very long title (500+ chars), open More, tap 'Share to Ours'.</t>
+          <t>Bring a task over. On the OTHER account, tick the shared row. Return to your Today.</t>
         </is>
       </c>
       <c r="F342" s="9" t="inlineStr">
         <is>
-          <t>A line says Ours keeps titles shorter and this one will be trimmed, BEFORE the copy is made. The copy appears on the shared list. 'Share to Ours' is absent entirely when there is no live list.</t>
+          <t>Your copy is gone from the day, replaced by a dashed sage line: 'Handled on Ours. It's off your day.' It is NOT struck through and does NOT appear in your Lookback. Leaving Today and coming back clears the note.</t>
         </is>
       </c>
       <c r="G342" s="7" t="inlineStr">
@@ -14414,7 +14414,7 @@
     <row r="343">
       <c r="A343" s="6" t="inlineStr">
         <is>
-          <t>OUR-28</t>
+          <t>OUR-27</t>
         </is>
       </c>
       <c r="B343" s="7" t="inlineStr">
@@ -14422,24 +14422,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C343" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C343" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D343" s="9" t="inlineStr">
         <is>
-          <t>A repeat set on Ours uses the SAME cadence sheet as home</t>
+          <t>Share to Ours warns about the length BEFORE it copies</t>
         </is>
       </c>
       <c r="E343" s="9" t="inlineStr">
         <is>
-          <t>Hold a shared row, tap 'Repeat…'. Compare with Menu › Repeating › Edit on a personal task.</t>
+          <t>Hold one of your own Today tasks with a very long title (500+ chars), open More, tap 'Share to Ours'.</t>
         </is>
       </c>
       <c r="F343" s="9" t="inlineStr">
         <is>
-          <t>Identical controls. The commit button NAMES the cadence ('Every day', 'Every 2 days'), on both. The Ours sheet adds one line: 'You'll both see it on its day.' It appears on its days for both people.</t>
+          <t>A line says Ours keeps titles shorter and this one will be trimmed, BEFORE the copy is made. The copy appears on the shared list. 'Share to Ours' is absent entirely when there is no live list.</t>
         </is>
       </c>
       <c r="G343" s="7" t="inlineStr">
@@ -14454,7 +14454,7 @@
     <row r="344">
       <c r="A344" s="6" t="inlineStr">
         <is>
-          <t>OUR-29</t>
+          <t>OUR-28</t>
         </is>
       </c>
       <c r="B344" s="7" t="inlineStr">
@@ -14469,17 +14469,17 @@
       </c>
       <c r="D344" s="9" t="inlineStr">
         <is>
-          <t>A cadence this build cannot read is inert, and says why</t>
+          <t>A repeat set on Ours uses the SAME cadence sheet as home</t>
         </is>
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>Get a shared row carrying a recurrence this build does not understand (a newer build, or hand-write one via the API).</t>
+          <t>Hold a shared row, tap 'Repeat…'. Compare with Menu › Repeating › Edit on a personal task.</t>
         </is>
       </c>
       <c r="F344" s="9" t="inlineStr">
         <is>
-          <t>The row is SHOWN, never hidden. Tapping it does nothing and a line explains it is safe and will appear on its days after an update. 'Repeat…' is withheld. It never marks itself done.</t>
+          <t>Identical controls. The commit button NAMES the cadence ('Every day', 'Every 2 days'), on both. The Ours sheet adds one line: 'You'll both see it on its day.' It appears on its days for both people.</t>
         </is>
       </c>
       <c r="G344" s="7" t="inlineStr">
@@ -14494,7 +14494,7 @@
     <row r="345">
       <c r="A345" s="6" t="inlineStr">
         <is>
-          <t>OUR-30</t>
+          <t>OUR-29</t>
         </is>
       </c>
       <c r="B345" s="7" t="inlineStr">
@@ -14502,24 +14502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C345" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C345" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D345" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash marks what changed, and never your own edits</t>
+          <t>A cadence this build cannot read is inert, and says why</t>
         </is>
       </c>
       <c r="E345" s="9" t="inlineStr">
         <is>
-          <t>Have the other account add and change a few rows. Open the room. Then tick something yourself and reopen.</t>
+          <t>Get a shared row carrying a recurrence this build does not understand (a newer build, or hand-write one via the API).</t>
         </is>
       </c>
       <c r="F345" s="9" t="inlineStr">
         <is>
-          <t>Their changed rows carry a tint and a firmer border on arrival; a screen reader says 'changed since you last looked'. Your OWN edits are never washed. Leaving and returning clears it.</t>
+          <t>The row is SHOWN, never hidden. Tapping it does nothing and a line explains it is safe and will appear on its days after an update. 'Repeat…' is withheld. It never marks itself done.</t>
         </is>
       </c>
       <c r="G345" s="7" t="inlineStr">
@@ -14534,7 +14534,7 @@
     <row r="346">
       <c r="A346" s="6" t="inlineStr">
         <is>
-          <t>OUR-31</t>
+          <t>OUR-30</t>
         </is>
       </c>
       <c r="B346" s="7" t="inlineStr">
@@ -14549,17 +14549,17 @@
       </c>
       <c r="D346" s="9" t="inlineStr">
         <is>
-          <t>Recently removed puts a task back</t>
+          <t>The quiet wash marks what changed, and never your own edits</t>
         </is>
       </c>
       <c r="E346" s="9" t="inlineStr">
         <is>
-          <t>Remove a shared row. Scroll to the foot of the list.</t>
+          <t>Have the other account add and change a few rows. Open the room. Then tick something yourself and reopen.</t>
         </is>
       </c>
       <c r="F346" s="9" t="inlineStr">
         <is>
-          <t>It sits under 'Recently removed', dimmed, with 'Put it back'. Restoring returns it for both people. Nothing anywhere says which of you removed it.</t>
+          <t>Their changed rows carry a tint and a firmer border on arrival; a screen reader says 'changed since you last looked'. Your OWN edits are never washed. Leaving and returning clears it.</t>
         </is>
       </c>
       <c r="G346" s="7" t="inlineStr">
@@ -14574,7 +14574,7 @@
     <row r="347">
       <c r="A347" s="6" t="inlineStr">
         <is>
-          <t>OUR-32</t>
+          <t>OUR-31</t>
         </is>
       </c>
       <c r="B347" s="7" t="inlineStr">
@@ -14589,17 +14589,17 @@
       </c>
       <c r="D347" s="9" t="inlineStr">
         <is>
-          <t>Removing a shared REPEAT does not pretend to be 'Skip today'</t>
+          <t>Recently removed puts a task back</t>
         </is>
       </c>
       <c r="E347" s="9" t="inlineStr">
         <is>
-          <t>Hold a repeating shared row and look at the shelf.</t>
+          <t>Remove a shared row. Scroll to the foot of the list.</t>
         </is>
       </c>
       <c r="F347" s="9" t="inlineStr">
         <is>
-          <t>It reads 'Remove', not 'Skip today', and the spoken label names removing the repeat. (The shared list has no per-day skip; the pre-fix build promised one and deleted the series for both people.)</t>
+          <t>It sits under 'Recently removed', dimmed, with 'Put it back'. Restoring returns it for both people. Nothing anywhere says which of you removed it.</t>
         </is>
       </c>
       <c r="G347" s="7" t="inlineStr">
@@ -14614,7 +14614,7 @@
     <row r="348">
       <c r="A348" s="6" t="inlineStr">
         <is>
-          <t>OUR-33</t>
+          <t>OUR-32</t>
         </is>
       </c>
       <c r="B348" s="7" t="inlineStr">
@@ -14622,24 +14622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C348" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C348" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D348" s="9" t="inlineStr">
         <is>
-          <t>A closed list is still readable, and read-only</t>
+          <t>Removing a shared REPEAT does not pretend to be 'Skip today'</t>
         </is>
       </c>
       <c r="E348" s="9" t="inlineStr">
         <is>
-          <t>Leave a list. Open it from the archive on the pairing screen.</t>
+          <t>Hold a repeating shared row and look at the shelf.</t>
         </is>
       </c>
       <c r="F348" s="9" t="inlineStr">
         <is>
-          <t>Every row is readable. There is no + pill at all. Ticking, renaming, removing and re-cadencing all do nothing, and each row says why. Each row still offers taking a copy for yourself.</t>
+          <t>It reads 'Remove', not 'Skip today', and the spoken label names removing the repeat. (The shared list has no per-day skip; the pre-fix build promised one and deleted the series for both people.)</t>
         </is>
       </c>
       <c r="G348" s="7" t="inlineStr">
@@ -14654,7 +14654,7 @@
     <row r="349">
       <c r="A349" s="6" t="inlineStr">
         <is>
-          <t>OUR-34</t>
+          <t>OUR-33</t>
         </is>
       </c>
       <c r="B349" s="7" t="inlineStr">
@@ -14662,24 +14662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C349" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C349" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D349" s="9" t="inlineStr">
         <is>
-          <t>The archive lists closed lists, and puts them away</t>
+          <t>A closed list is still readable, and read-only</t>
         </is>
       </c>
       <c r="E349" s="9" t="inlineStr">
         <is>
-          <t>With at least one closed list, look under 'Lists you have kept' on the pairing screen.</t>
+          <t>Leave a list. Open it from the archive on the pairing screen.</t>
         </is>
       </c>
       <c r="F349" s="9" t="inlineStr">
         <is>
-          <t>Purpose and closed MONTH only, no counts of any kind. 'Put it away' hides it from the default view; 'Show the ones put away' brings it back. Nothing is deleted.</t>
+          <t>Every row is readable. There is no + pill at all. Ticking, renaming, removing and re-cadencing all do nothing, and each row says why. Each row still offers taking a copy for yourself.</t>
         </is>
       </c>
       <c r="G349" s="7" t="inlineStr">
@@ -14694,7 +14694,7 @@
     <row r="350">
       <c r="A350" s="6" t="inlineStr">
         <is>
-          <t>OUR-35</t>
+          <t>OUR-34</t>
         </is>
       </c>
       <c r="B350" s="7" t="inlineStr">
@@ -14702,24 +14702,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C350" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C350" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D350" s="9" t="inlineStr">
         <is>
-          <t>Reopening together is a handshake, never unilateral</t>
+          <t>The archive lists closed lists, and puts them away</t>
         </is>
       </c>
       <c r="E350" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Reopen together…' on ONE side only and STAY on that screen, hands off. Read the code to the second account. On that side, tap 'Got a code from them? Enter it to reopen.' (under the reopen hint on the closed-list screen) and enter it. Repeat with the closed list being the ONLY closed list on both accounts.</t>
+          <t>With at least one closed list, look under 'Lists you have kept' on the pairing screen.</t>
         </is>
       </c>
       <c r="F350" s="9" t="inlineStr">
         <is>
-          <t>The offering side gets a code and nothing reopens yet. The other side has a named door to the join field and entering the code there reopens the list for both, with everything as it was. It is never asked which kind of code it is, and it works when the closed list on screen is the only one (the D2 'handshake purgatory', 2026-09-22). Within about ten seconds, with nothing touched, the offering side's screen changes on its own: the code is gone and the live list shows 'They used the code. The list is open again…'.</t>
+          <t>Purpose and closed MONTH only, no counts of any kind. 'Put it away' hides it from the default view; 'Show the ones put away' brings it back. Nothing is deleted.</t>
         </is>
       </c>
       <c r="G350" s="7" t="inlineStr">
@@ -14734,7 +14734,7 @@
     <row r="351">
       <c r="A351" s="6" t="inlineStr">
         <is>
-          <t>OUR-122</t>
+          <t>OUR-35</t>
         </is>
       </c>
       <c r="B351" s="7" t="inlineStr">
@@ -14742,24 +14742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C351" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C351" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D351" s="9" t="inlineStr">
         <is>
-          <t>Waiting screens look on their own, and 'Check now' is there for the impatient</t>
+          <t>Reopening together is a handshake, never unilateral</t>
         </is>
       </c>
       <c r="E351" s="9" t="inlineStr">
         <is>
-          <t>A: mint a pairing code and stay on that screen, hands off. B: join. Watch A. Then, on a closed list: A taps 'Reopen together…' and stays; B redeems. Watch A. Then, on either waiting screen, tap 'Check now'.</t>
+          <t>On a closed list, tap 'Reopen together…' on ONE side only and STAY on that screen, hands off. Read the code to the second account. On that side, tap 'Got a code from them? Enter it to reopen.' (under the reopen hint on the closed-list screen) and enter it. Repeat with the closed list being the ONLY closed list on both accounts.</t>
         </is>
       </c>
       <c r="F351" s="9" t="inlineStr">
         <is>
-          <t>Both times A's screen changes on its own within about ten seconds: the pairing wait becomes '{name} joined.', and the closed list becomes the live list with the 'They used the code' line and the spent code gone. 'Check now' sits under the waiting text and under a minted reopen code, and does the same immediately. Once A has opened the list, the pairing screen underneath stops looking (nothing to see by eye; the rule is focus AND foreground AND under 30 minutes).</t>
+          <t>The offering side gets a code and nothing reopens yet. The other side has a named door to the join field and entering the code there reopens the list for both, with everything as it was. It is never asked which kind of code it is, and it works when the closed list on screen is the only one (the D2 'handshake purgatory', 2026-09-22). Within about ten seconds, with nothing touched, the offering side's screen changes on its own: the code is gone and the live list shows 'They used the code. The list is open again…'.</t>
         </is>
       </c>
       <c r="G351" s="7" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="352">
       <c r="A352" s="6" t="inlineStr">
         <is>
-          <t>OUR-123</t>
+          <t>OUR-122</t>
         </is>
       </c>
       <c r="B352" s="7" t="inlineStr">
@@ -14782,24 +14782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C352" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C352" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D352" s="9" t="inlineStr">
         <is>
-          <t>The Ours card goes home rather than into a room</t>
+          <t>Waiting screens look on their own, and 'Check now' is there for the impatient</t>
         </is>
       </c>
       <c r="E352" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, open the Menu and tap Ours. Then open the Menu from the Ours tab and tap Ours again. Then, with no shared list yet (signed in), tap Ours from the Menu.</t>
+          <t>A: mint a pairing code and stay on that screen, hands off. B: join. Watch A. Then, on a closed list: A taps 'Reopen together…' and stays; B redeems. Watch A. Then, on either waiting screen, tap 'Check now'.</t>
         </is>
       </c>
       <c r="F352" s="9" t="inlineStr">
         <is>
-          <t>With a live list the contents page closes and you land on Today's Ours tab (the list's name underlined) in one short fade; back from there does not return to the contents page. From the Ours tab's own Menu, the Ours card simply goes back to it. With no list yet it opens the invite screen as a room: '‹ Menu' and the two-mugs picture as a band, then the invite screen as it was.</t>
+          <t>Both times A's screen changes on its own within about ten seconds: the pairing wait becomes '{name} joined.', and the closed list becomes the live list with the 'They used the code' line and the spent code gone. 'Check now' sits under the waiting text and under a minted reopen code, and does the same immediately. Once A has opened the list, the pairing screen underneath stops looking (nothing to see by eye; the rule is focus AND foreground AND under 30 minutes).</t>
         </is>
       </c>
       <c r="G352" s="7" t="inlineStr">
@@ -14814,7 +14814,7 @@
     <row r="353">
       <c r="A353" s="6" t="inlineStr">
         <is>
-          <t>OUR-124</t>
+          <t>OUR-123</t>
         </is>
       </c>
       <c r="B353" s="7" t="inlineStr">
@@ -14822,24 +14822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C353" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C353" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D353" s="9" t="inlineStr">
         <is>
-          <t>The room opens with your list's own name, in any language</t>
+          <t>The Ours card goes home rather than into a room</t>
         </is>
       </c>
       <c r="E353" s="9" t="inlineStr">
         <is>
-          <t>With a named shared list (e.g. 'Just us') and the app set to Italian (or German, Spanish, French), tap the list's name in Today's heading.</t>
+          <t>With a live shared list, open the Menu and tap Ours. Then open the Menu from the Ours tab and tap Ours again. Then, with no shared list yet (signed in), tap Ours from the Menu.</t>
         </is>
       </c>
       <c r="F353" s="9" t="inlineStr">
         <is>
-          <t>The room's heading shows your list's own name from the first frame, and the capture panel's heading reads 'Aggiungi a Just us'. It never shows the default ('La nostra lista') for a beat and then flips, which read as the app changing language. A list with no name shows the default in the app's language. The list's own name is shown as you typed it, in whatever language that was.</t>
+          <t>With a live list the contents page closes and you land on Today's Ours tab (the list's name underlined) in one short fade; back from there does not return to the contents page. From the Ours tab's own Menu, the Ours card simply goes back to it. With no list yet it opens the invite screen as a room: '‹ Menu' and the two-mugs picture as a band, then the invite screen as it was.</t>
         </is>
       </c>
       <c r="G353" s="7" t="inlineStr">
@@ -14854,7 +14854,7 @@
     <row r="354">
       <c r="A354" s="6" t="inlineStr">
         <is>
-          <t>OUR-125</t>
+          <t>OUR-124</t>
         </is>
       </c>
       <c r="B354" s="7" t="inlineStr">
@@ -14869,17 +14869,17 @@
       </c>
       <c r="D354" s="9" t="inlineStr">
         <is>
-          <t>Today and the Ours tab look like one page</t>
+          <t>The room opens with your list's own name, in any language</t>
         </is>
       </c>
       <c r="E354" s="9" t="inlineStr">
         <is>
-          <t>With a live shared list, on a phone, tap the list's name in Today's heading, then 'Today', a few times. Do it in light and dark, at dawn or dusk if you can, and on an iPhone as well as Android.</t>
+          <t>With a named shared list (e.g. 'Just us') and the app set to Italian (or German, Spanish, French), tap the list's name in Today's heading.</t>
         </is>
       </c>
       <c r="F354" s="9" t="inlineStr">
         <is>
-          <t>The date, the Menu pill and the two heading words sit at exactly the same height on both, so nothing jumps as you flip. The Ours tab has Today's own background (the warm time-of-day gradient, and on iPhone and web the soft drifting glow), and the glow does not jump or restart during the fade: it is in the same place on both. A closed list opened from the archive keeps the plain room background and its '‹ Back'.</t>
+          <t>The room's heading shows your list's own name from the first frame, and the capture panel's heading reads 'Aggiungi a Just us'. It never shows the default ('La nostra lista') for a beat and then flips, which read as the app changing language. A list with no name shows the default in the app's language. The list's own name is shown as you typed it, in whatever language that was.</t>
         </is>
       </c>
       <c r="G354" s="7" t="inlineStr">
@@ -14894,7 +14894,7 @@
     <row r="355">
       <c r="A355" s="6" t="inlineStr">
         <is>
-          <t>OUR-36</t>
+          <t>OUR-125</t>
         </is>
       </c>
       <c r="B355" s="7" t="inlineStr">
@@ -14902,24 +14902,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C355" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C355" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D355" s="9" t="inlineStr">
         <is>
-          <t>Delete for good commits when the screen closes, not on a timer</t>
+          <t>Today and the Ours tab look like one page</t>
         </is>
       </c>
       <c r="E355" s="9" t="inlineStr">
         <is>
-          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
+          <t>With a live shared list, on a phone, tap the list's name in Today's heading, then 'Today', a few times. Do it in light and dark, at dawn or dusk if you can, and on an iPhone as well as Android.</t>
         </is>
       </c>
       <c r="F355" s="9" t="inlineStr">
         <is>
-          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
+          <t>The date, the Menu pill and the two heading words sit at exactly the same height on both, so nothing jumps as you flip. The Ours tab has Today's own background (the warm time-of-day gradient, and on iPhone and web the soft drifting glow), and the glow does not jump or restart during the fade: it is in the same place on both. A closed list opened from the archive keeps the plain room background and its '‹ Back'.</t>
         </is>
       </c>
       <c r="G355" s="7" t="inlineStr">
@@ -14934,7 +14934,7 @@
     <row r="356">
       <c r="A356" s="6" t="inlineStr">
         <is>
-          <t>OUR-37</t>
+          <t>OUR-36</t>
         </is>
       </c>
       <c r="B356" s="7" t="inlineStr">
@@ -14942,24 +14942,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C356" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C356" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D356" s="9" t="inlineStr">
         <is>
-          <t>Rename yourself, and only yourself</t>
+          <t>Delete for good commits when the screen closes, not on a timer</t>
         </is>
       </c>
       <c r="E356" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
+          <t>On a closed list, tap 'Delete this list for good'. Read what appears. Tap 'Keep it'. Then do it again and navigate away instead.</t>
         </is>
       </c>
       <c r="F356" s="9" t="inlineStr">
         <is>
-          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
+          <t>The line says nothing has been told to anyone yet and that it deletes when you leave this screen. There is NO countdown anywhere. 'Keep it' cancels it entirely. Leaving the screen with it standing actually deletes it.</t>
         </is>
       </c>
       <c r="G356" s="7" t="inlineStr">
@@ -14974,7 +14974,7 @@
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
         <is>
-          <t>OUR-38</t>
+          <t>OUR-37</t>
         </is>
       </c>
       <c r="B357" s="7" t="inlineStr">
@@ -14989,17 +14989,17 @@
       </c>
       <c r="D357" s="9" t="inlineStr">
         <is>
-          <t>A dropped signal never throws you out of the room</t>
+          <t>Rename yourself, and only yourself</t>
         </is>
       </c>
       <c r="E357" s="9" t="inlineStr">
         <is>
-          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
+          <t>On a live list, tap the line reading 'They see you as {name}' and type a new name.</t>
         </is>
       </c>
       <c r="F357" s="9" t="inlineStr">
         <is>
-          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
+          <t>Your name changes for both of you. There is no affordance anywhere to edit the OTHER person's name.</t>
         </is>
       </c>
       <c r="G357" s="7" t="inlineStr">
@@ -15014,7 +15014,7 @@
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
         <is>
-          <t>OUR-39</t>
+          <t>OUR-38</t>
         </is>
       </c>
       <c r="B358" s="7" t="inlineStr">
@@ -15022,24 +15022,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C358" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C358" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D358" s="9" t="inlineStr">
         <is>
-          <t>Report this list reaches us and tells nobody else</t>
+          <t>A dropped signal never throws you out of the room</t>
         </is>
       </c>
       <c r="E358" s="9" t="inlineStr">
         <is>
-          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
+          <t>Open the room, then turn off the network and wait for a poll (~15s).</t>
         </is>
       </c>
       <c r="F358" s="9" t="inlineStr">
         <is>
-          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
+          <t>The list stays on screen with a quiet 'no connection' line. You are NOT redirected to the pairing screen, and nothing looks deleted.</t>
         </is>
       </c>
       <c r="G358" s="7" t="inlineStr">
@@ -15054,7 +15054,7 @@
     <row r="359">
       <c r="A359" s="6" t="inlineStr">
         <is>
-          <t>OUR-40</t>
+          <t>OUR-39</t>
         </is>
       </c>
       <c r="B359" s="7" t="inlineStr">
@@ -15069,17 +15069,17 @@
       </c>
       <c r="D359" s="9" t="inlineStr">
         <is>
-          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
+          <t>Report this list reaches us and tells nobody else</t>
         </is>
       </c>
       <c r="E359" s="9" t="inlineStr">
         <is>
-          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
+          <t>On a live shared list, scroll to the foot of the pairing screen and tap 'Report this list'. Then check the other account.</t>
         </is>
       </c>
       <c r="F359" s="9" t="inlineStr">
         <is>
-          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
+          <t>The row is quiet, never a red button, and says plainly that only we are told. After tapping it thanks you and says your person has not been told. NOTHING changes on the other account's screen, anywhere. The report email arrives carrying the pair id and no task text.</t>
         </is>
       </c>
       <c r="G359" s="7" t="inlineStr">
@@ -15094,7 +15094,7 @@
     <row r="360">
       <c r="A360" s="6" t="inlineStr">
         <is>
-          <t>OUR-41</t>
+          <t>OUR-40</t>
         </is>
       </c>
       <c r="B360" s="7" t="inlineStr">
@@ -15102,24 +15102,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C360" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C360" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D360" s="9" t="inlineStr">
         <is>
-          <t>Leaving is the block, and needs no reason</t>
+          <t>A disabled list reads EXACTLY like an ordinary closed one</t>
         </is>
       </c>
       <c r="E360" s="9" t="inlineStr">
         <is>
-          <t>On a live list, tap 'Leave this list'.</t>
+          <t>Set pairs.disabled_at by hand in Supabase for a test pair, then open it on both accounts.</t>
         </is>
       </c>
       <c r="F360" s="9" t="inlineStr">
         <is>
-          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
+          <t>Both see the ordinary 'This list is closed' state, read-only, with the archive row. There is NO mark, word, colour or ordering anywhere that distinguishes it from a list somebody simply left. (Any difference would tell a reported person they were reported.)</t>
         </is>
       </c>
       <c r="G360" s="7" t="inlineStr">
@@ -15134,12 +15134,12 @@
     <row r="361">
       <c r="A361" s="6" t="inlineStr">
         <is>
-          <t>LEG-05</t>
+          <t>OUR-41</t>
         </is>
       </c>
       <c r="B361" s="7" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Ours</t>
         </is>
       </c>
       <c r="C361" s="10" t="inlineStr">
@@ -15149,17 +15149,17 @@
       </c>
       <c r="D361" s="9" t="inlineStr">
         <is>
-          <t>The shared-list clauses are in both copies of both documents</t>
+          <t>Leaving is the block, and needs no reason</t>
         </is>
       </c>
       <c r="E361" s="9" t="inlineStr">
         <is>
-          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
+          <t>On a live list, tap 'Leave this list'.</t>
         </is>
       </c>
       <c r="F361" s="9" t="inlineStr">
         <is>
-          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
+          <t>It closes immediately for both people, with no confirmation gauntlet, no reason asked, and no way for the other person to reopen it alone. Both can still read everything.</t>
         </is>
       </c>
       <c r="G361" s="7" t="inlineStr">
@@ -15174,32 +15174,32 @@
     <row r="362">
       <c r="A362" s="6" t="inlineStr">
         <is>
-          <t>OUR-42</t>
+          <t>LEG-05</t>
         </is>
       </c>
       <c r="B362" s="7" t="inlineStr">
         <is>
-          <t>Ours</t>
-        </is>
-      </c>
-      <c r="C362" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="C362" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D362" s="9" t="inlineStr">
         <is>
-          <t>A change on one phone appears on the other WITHOUT touching it</t>
+          <t>The shared-list clauses are in both copies of both documents</t>
         </is>
       </c>
       <c r="E362" s="9" t="inlineStr">
         <is>
-          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
+          <t>Read Settings &gt; Privacy and Settings &gt; Terms in-app, then doubledone.app/privacy.html and /terms.html.</t>
         </is>
       </c>
       <c r="F362" s="9" t="inlineStr">
         <is>
-          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
+          <t>Privacy carries the shared-lists sections (what the other person sees, that authorship is not stored, freezing, the 30-day window). Terms carry 'Shared lists, and what is not allowed on them' plus 'Reporting, and what we will do' with the 24-hour aim. In-app and web wording match.</t>
         </is>
       </c>
       <c r="G362" s="7" t="inlineStr">
@@ -15214,7 +15214,7 @@
     <row r="363">
       <c r="A363" s="6" t="inlineStr">
         <is>
-          <t>OUR-43</t>
+          <t>OUR-42</t>
         </is>
       </c>
       <c r="B363" s="7" t="inlineStr">
@@ -15229,17 +15229,17 @@
       </c>
       <c r="D363" s="9" t="inlineStr">
         <is>
-          <t>Opening your own list does not bounce you back</t>
+          <t>A change on one phone appears on the other WITHOUT touching it</t>
         </is>
       </c>
       <c r="E363" s="9" t="inlineStr">
         <is>
-          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
+          <t>Both sit on the shared list. One adds a task. Do not touch the other device.</t>
         </is>
       </c>
       <c r="F363" s="9" t="inlineStr">
         <is>
-          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
+          <t>It appears within about 15 seconds. (The poll never fired once before 2026-08-09: setPair rebuilt the pair object every sync, which restarted the interval before it could tick.)</t>
         </is>
       </c>
       <c r="G363" s="7" t="inlineStr">
@@ -15254,7 +15254,7 @@
     <row r="364">
       <c r="A364" s="6" t="inlineStr">
         <is>
-          <t>OUR-44</t>
+          <t>OUR-43</t>
         </is>
       </c>
       <c r="B364" s="7" t="inlineStr">
@@ -15262,24 +15262,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C364" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C364" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D364" s="9" t="inlineStr">
         <is>
-          <t>The pairing screen offers a way INTO the list</t>
+          <t>Opening your own list does not bounce you back</t>
         </is>
       </c>
       <c r="E364" s="9" t="inlineStr">
         <is>
-          <t>Finish pairing, then look at the pairing screen.</t>
+          <t>With a live list, tap Ours then 'Open the list'. Also try /ours-list directly in a cold tab.</t>
         </is>
       </c>
       <c r="F364" s="9" t="inlineStr">
         <is>
-          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
+          <t>You land on the list and stay. (useSession returns null while hydrating; the room used to read that as signed-out and redirect, making the button an endless loop.)</t>
         </is>
       </c>
       <c r="G364" s="7" t="inlineStr">
@@ -15294,7 +15294,7 @@
     <row r="365">
       <c r="A365" s="6" t="inlineStr">
         <is>
-          <t>OUR-45</t>
+          <t>OUR-44</t>
         </is>
       </c>
       <c r="B365" s="7" t="inlineStr">
@@ -15309,17 +15309,17 @@
       </c>
       <c r="D365" s="9" t="inlineStr">
         <is>
-          <t>The quiet wash appears and then takes itself away</t>
+          <t>The pairing screen offers a way INTO the list</t>
         </is>
       </c>
       <c r="E365" s="9" t="inlineStr">
         <is>
-          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
+          <t>Finish pairing, then look at the pairing screen.</t>
         </is>
       </c>
       <c r="F365" s="9" t="inlineStr">
         <is>
-          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
+          <t>There is an 'Open the list' button. (It used to dead-end: the only route to the room was Today's door or the Menu, which a new pair has no reason to know about.)</t>
         </is>
       </c>
       <c r="G365" s="7" t="inlineStr">
@@ -15334,7 +15334,7 @@
     <row r="366">
       <c r="A366" s="6" t="inlineStr">
         <is>
-          <t>OUR-47</t>
+          <t>OUR-45</t>
         </is>
       </c>
       <c r="B366" s="7" t="inlineStr">
@@ -15342,24 +15342,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C366" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C366" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D366" s="9" t="inlineStr">
         <is>
-          <t>Ours lives in Today's heading (Today v3)</t>
+          <t>The quiet wash appears and then takes itself away</t>
         </is>
       </c>
       <c r="E366" s="9" t="inlineStr">
         <is>
-          <t>With a live list, look at the top of Today. Then leave the list (or sign out) and look again. With a screen reader, move through the heading.</t>
+          <t>Have the other account change a row while you are elsewhere, then open the list.</t>
         </is>
       </c>
       <c r="F366" s="9" t="inlineStr">
         <is>
-          <t>With a live list the heading reads 'Today' and the list's name side by side (its own name when it has one, else 'Ours'), 'Today' underlined as the current tab. With no live list there is only 'Today', and no empty space where Ours would be. A screen reader hears them as tabs, 'Today, selected' and '{name}'. The old Ours door card under the list is gone.</t>
+          <t>The changed row carries ONE warmed border, on the card itself, never a second ring around it. It clears itself after about 8 seconds without animating. It does not return on the next visit, even if the other phone's clock runs ahead.</t>
         </is>
       </c>
       <c r="G366" s="7" t="inlineStr">
@@ -15374,7 +15374,7 @@
     <row r="367">
       <c r="A367" s="6" t="inlineStr">
         <is>
-          <t>OUR-48</t>
+          <t>OUR-47</t>
         </is>
       </c>
       <c r="B367" s="7" t="inlineStr">
@@ -15389,17 +15389,17 @@
       </c>
       <c r="D367" s="9" t="inlineStr">
         <is>
-          <t>Their tick marks your copy DONE and leaves it on your day</t>
+          <t>Ours lives in Today's heading (Today v3)</t>
         </is>
       </c>
       <c r="E367" s="9" t="inlineStr">
         <is>
-          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
+          <t>With a live list, look at the top of Today. Then leave the list (or sign out) and look again. With a screen reader, move through the heading.</t>
         </is>
       </c>
       <c r="F367" s="9" t="inlineStr">
         <is>
-          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
+          <t>With a live list the heading reads 'Today' and the list's name side by side (its own name when it has one, else 'Ours'), 'Today' underlined as the current tab. With no live list there is only 'Today', and no empty space where Ours would be. A screen reader hears them as tabs, 'Today, selected' and '{name}'. The old Ours door card under the list is gone.</t>
         </is>
       </c>
       <c r="G367" s="7" t="inlineStr">
@@ -15414,7 +15414,7 @@
     <row r="368">
       <c r="A368" s="6" t="inlineStr">
         <is>
-          <t>OUR-49</t>
+          <t>OUR-48</t>
         </is>
       </c>
       <c r="B368" s="7" t="inlineStr">
@@ -15429,17 +15429,17 @@
       </c>
       <c r="D368" s="9" t="inlineStr">
         <is>
-          <t>A settled copy carries a completion DATE, not just a done flag</t>
+          <t>Their tick marks your copy DONE and leaves it on your day</t>
         </is>
       </c>
       <c r="E368" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
+          <t>A has an open brought copy on Today. B ticks that row in Ours. A backgrounds the app and returns to Today WITHOUT navigating.</t>
         </is>
       </c>
       <c r="F368" s="9" t="inlineStr">
         <is>
-          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
+          <t>The copy is still there, ticked, NOT gone. It appears in A's Lookback. Nothing anywhere says which of them did it. (Before 2026-08-11 it was tombstoned and replaced by a note, and for three rounds it vanished outright because it was marked done with no completion date.)</t>
         </is>
       </c>
       <c r="G368" s="7" t="inlineStr">
@@ -15454,7 +15454,7 @@
     <row r="369">
       <c r="A369" s="6" t="inlineStr">
         <is>
-          <t>OUR-50</t>
+          <t>OUR-49</t>
         </is>
       </c>
       <c r="B369" s="7" t="inlineStr">
@@ -15462,24 +15462,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C369" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C369" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D369" s="9" t="inlineStr">
         <is>
-          <t>A finished copy can be brought over again</t>
+          <t>A settled copy carries a completion DATE, not just a done flag</t>
         </is>
       </c>
       <c r="E369" s="9" t="inlineStr">
         <is>
-          <t>After OUR-48, hold that row in Ours.</t>
+          <t>After OUR-48, open Today with ?debug=1 and read the `copy` line for that task.</t>
         </is>
       </c>
       <c r="F369" s="9" t="inlineStr">
         <is>
-          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
+          <t>done=true, doneDay = today's date, showsToday=true. A done task with doneDay=none is invisible on Today AND absent from Lookback: tasksForToday places a finished task by its completion day.</t>
         </is>
       </c>
       <c r="G369" s="7" t="inlineStr">
@@ -15494,7 +15494,7 @@
     <row r="370">
       <c r="A370" s="6" t="inlineStr">
         <is>
-          <t>OUR-51</t>
+          <t>OUR-50</t>
         </is>
       </c>
       <c r="B370" s="7" t="inlineStr">
@@ -15502,24 +15502,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C370" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C370" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D370" s="9" t="inlineStr">
         <is>
-          <t>Your own edit never highlights; their later edit always does</t>
+          <t>A finished copy can be brought over again</t>
         </is>
       </c>
       <c r="E370" s="9" t="inlineStr">
         <is>
-          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
+          <t>After OUR-48, hold that row in Ours.</t>
         </is>
       </c>
       <c r="F370" s="9" t="inlineStr">
         <is>
-          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
+          <t>'Bring to my Today' is offered again, not 'Already on your Today'. (A done copy is not on your plate; while only tombstones were skipped you had a task you could neither see nor re-add.)</t>
         </is>
       </c>
       <c r="G370" s="7" t="inlineStr">
@@ -15534,7 +15534,7 @@
     <row r="371">
       <c r="A371" s="6" t="inlineStr">
         <is>
-          <t>OUR-52</t>
+          <t>OUR-51</t>
         </is>
       </c>
       <c r="B371" s="7" t="inlineStr">
@@ -15542,24 +15542,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C371" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C371" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D371" s="9" t="inlineStr">
         <is>
-          <t>The highlight arrives at once and fades away</t>
+          <t>Your own edit never highlights; their later edit always does</t>
         </is>
       </c>
       <c r="E371" s="9" t="inlineStr">
         <is>
-          <t>Have B change a row while A is on the list.</t>
+          <t>B ticks a row (A highlights). A un-ticks it. B ticks it again. Watch both screens throughout.</t>
         </is>
       </c>
       <c r="F371" s="9" t="inlineStr">
         <is>
-          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
+          <t>Each side lights up for the OTHER's change every time, including repeatedly on the same row, and never for its own. (`mine` records WHEN you wrote a row, not merely that you did; as a plain id set, one touch made that row permanently dark on that device.)</t>
         </is>
       </c>
       <c r="G371" s="7" t="inlineStr">
@@ -15574,7 +15574,7 @@
     <row r="372">
       <c r="A372" s="6" t="inlineStr">
         <is>
-          <t>OUR-53</t>
+          <t>OUR-52</t>
         </is>
       </c>
       <c r="B372" s="7" t="inlineStr">
@@ -15589,17 +15589,17 @@
       </c>
       <c r="D372" s="9" t="inlineStr">
         <is>
-          <t>Two devices share ONE clock</t>
+          <t>The highlight arrives at once and fades away</t>
         </is>
       </c>
       <c r="E372" s="9" t="inlineStr">
         <is>
-          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
+          <t>Have B change a row while A is on the list.</t>
         </is>
       </c>
       <c r="F372" s="9" t="inlineStr">
         <is>
-          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
+          <t>A's row warms immediately, holds about 8 seconds, then fades over roughly 700ms. It does not snap off, does not strobe, and does not return on the next poll for the same change. Reduce-motion gets an instant disappearance instead of a fade.</t>
         </is>
       </c>
       <c r="G372" s="7" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="373">
       <c r="A373" s="6" t="inlineStr">
         <is>
-          <t>OUR-54</t>
+          <t>OUR-53</t>
         </is>
       </c>
       <c r="B373" s="7" t="inlineStr">
@@ -15622,24 +15622,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C373" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C373" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D373" s="9" t="inlineStr">
         <is>
-          <t>The debug panel is opt-in and carries no task text</t>
+          <t>Two devices share ONE clock</t>
         </is>
       </c>
       <c r="E373" s="9" t="inlineStr">
         <is>
-          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
+          <t>Open the list on both devices with ?debug=1 and read `skew` on the wash line.</t>
         </is>
       </c>
       <c r="F373" s="9" t="inlineStr">
         <is>
-          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
+          <t>A small value in seconds, not minutes, on both. Every stamp (completion log, last-look, last-write-wins) is compared against server time via server_now(). A device whose clock ran ahead used to stamp its own last-look into the future and could never highlight anything again.</t>
         </is>
       </c>
       <c r="G373" s="7" t="inlineStr">
@@ -15654,7 +15654,7 @@
     <row r="374">
       <c r="A374" s="6" t="inlineStr">
         <is>
-          <t>OUR-55</t>
+          <t>OUR-54</t>
         </is>
       </c>
       <c r="B374" s="7" t="inlineStr">
@@ -15662,24 +15662,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C374" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C374" s="11" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D374" s="9" t="inlineStr">
         <is>
-          <t>Capture on Ours IS Today's capture</t>
+          <t>The debug panel is opt-in and carries no task text</t>
         </is>
       </c>
       <c r="E374" s="9" t="inlineStr">
         <is>
-          <t>Open a shared list and tap the + pill at the foot of the screen.</t>
+          <t>Open /ours-list?debug=1 and /today?debug=1, then the same URLs without the flag.</t>
         </is>
       </c>
       <c r="F374" s="9" t="inlineStr">
         <is>
-          <t>The same pill and the same panel Today has, headed 'Add to {name}': the same box, the same Speak button (web), the same When chip and door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
+          <t>A small log appears only with the flag, at the top of Today and the foot of the list. Every line is counts, ids and flags. NO task title ever appears in it: these get screenshotted and pasted, and a shared list is two people's words.</t>
         </is>
       </c>
       <c r="G374" s="7" t="inlineStr">
@@ -15694,7 +15694,7 @@
     <row r="375">
       <c r="A375" s="6" t="inlineStr">
         <is>
-          <t>OUR-56</t>
+          <t>OUR-55</t>
         </is>
       </c>
       <c r="B375" s="7" t="inlineStr">
@@ -15709,17 +15709,17 @@
       </c>
       <c r="D375" s="9" t="inlineStr">
         <is>
-          <t>Repeating can be set AT capture, without knowing a gesture</t>
+          <t>Capture on Ours IS Today's capture</t>
         </is>
       </c>
       <c r="E375" s="9" t="inlineStr">
         <is>
-          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
+          <t>Open a shared list and tap the + pill at the foot of the screen.</t>
         </is>
       </c>
       <c r="F375" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
+          <t>The same pill and the same panel Today has, headed 'Add to {name}': the same box, the same Speak button (web), the same When chip and door, the same Add button naming its own consequence. Not a lookalike, the same component, so the two can never drift apart.</t>
         </is>
       </c>
       <c r="G375" s="7" t="inlineStr">
@@ -15734,7 +15734,7 @@
     <row r="376">
       <c r="A376" s="6" t="inlineStr">
         <is>
-          <t>OUR-57</t>
+          <t>OUR-56</t>
         </is>
       </c>
       <c r="B376" s="7" t="inlineStr">
@@ -15742,24 +15742,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C376" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C376" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D376" s="9" t="inlineStr">
         <is>
-          <t>A dump becomes several shared rows, in the order typed</t>
+          <t>Repeating can be set AT capture, without knowing a gesture</t>
         </is>
       </c>
       <c r="E376" s="9" t="inlineStr">
         <is>
-          <t>Type three lines into the Ours capture and Add.</t>
+          <t>In that panel, open the door and choose Daily (or Weekly, or Every N days), then Add.</t>
         </is>
       </c>
       <c r="F376" s="9" t="inlineStr">
         <is>
-          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
+          <t>The button reads 'Add · Daily' before the tap, and the row lands already repeating, visible to both of you. (Before this, the only way to make a repeating shared task was to add it and then somehow know to long-press it. Melroy: 'there is no way to add Repeating Tasks.')</t>
         </is>
       </c>
       <c r="G376" s="7" t="inlineStr">
@@ -15774,7 +15774,7 @@
     <row r="377">
       <c r="A377" s="6" t="inlineStr">
         <is>
-          <t>OUR-58</t>
+          <t>OUR-57</t>
         </is>
       </c>
       <c r="B377" s="7" t="inlineStr">
@@ -15782,24 +15782,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C377" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C377" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D377" s="9" t="inlineStr">
         <is>
-          <t>The shared door offers When and Repeating, never Steps</t>
+          <t>A dump becomes several shared rows, in the order typed</t>
         </is>
       </c>
       <c r="E377" s="9" t="inlineStr">
         <is>
-          <t>Open the door on Ours and compare it with the door on Today.</t>
+          <t>Type three lines into the Ours capture and Add.</t>
         </is>
       </c>
       <c r="F377" s="9" t="inlineStr">
         <is>
-          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
+          <t>The button reads 'Add 3' and three rows land, in the typed order, on both devices. With a cadence set, all three carry it.</t>
         </is>
       </c>
       <c r="G377" s="7" t="inlineStr">
@@ -15814,7 +15814,7 @@
     <row r="378">
       <c r="A378" s="6" t="inlineStr">
         <is>
-          <t>OUR-59</t>
+          <t>OUR-58</t>
         </is>
       </c>
       <c r="B378" s="7" t="inlineStr">
@@ -15822,24 +15822,24 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C378" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C378" s="8" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D378" s="9" t="inlineStr">
         <is>
-          <t>Typed text survives the panel going</t>
+          <t>The shared door offers When and Repeating, never Steps</t>
         </is>
       </c>
       <c r="E378" s="9" t="inlineStr">
         <is>
-          <t>Type half a sentence into the Ours panel, Close it, tick something, then tap the pill again.</t>
+          <t>Open the door on Ours and compare it with the door on Today.</t>
         </is>
       </c>
       <c r="F378" s="9" t="inlineStr">
         <is>
-          <t>The pill shows '+' and three dots while words wait, and the half sentence is still there. The panel is always mounted, never unmounted. Only an Add resets the door; the words never reset on their own.</t>
+          <t>Ours shows a When row and a Repeating row, and NO Steps row (a shared row has no slices field, and breaking a thing down is personal). The When row is deliberate: a dated or repeating shared row now reaches BOTH Todays, so a day here is a real act rather than a word that means nothing. See OUR-71 for what the When row rests on.</t>
         </is>
       </c>
       <c r="G378" s="7" t="inlineStr">
@@ -15854,7 +15854,7 @@
     <row r="379">
       <c r="A379" s="6" t="inlineStr">
         <is>
-          <t>OUR-60</t>
+          <t>OUR-59</t>
         </is>
       </c>
       <c r="B379" s="7" t="inlineStr">
@@ -15869,22 +15869,22 @@
       </c>
       <c r="D379" s="9" t="inlineStr">
         <is>
-          <t>The Ours panel rides above the keyboard</t>
+          <t>Typed text survives the panel going</t>
         </is>
       </c>
       <c r="E379" s="9" t="inlineStr">
         <is>
-          <t>On a real Android device, tap the + pill on the Ours list, tap the box and start typing.</t>
+          <t>Type half a sentence into the Ours panel, Close it, tick something, then tap the pill again.</t>
         </is>
       </c>
       <c r="F379" s="9" t="inlineStr">
         <is>
-          <t>The panel and its Add button stay visible above the keyboard while you type. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
+          <t>The pill shows '+' and three dots while words wait, and the half sentence is still there. The panel is always mounted, never unmounted. Only an Add resets the door; the words never reset on their own.</t>
         </is>
       </c>
       <c r="G379" s="7" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H379" s="7" t="inlineStr"/>
@@ -15894,7 +15894,7 @@
     <row r="380">
       <c r="A380" s="6" t="inlineStr">
         <is>
-          <t>OUR-61</t>
+          <t>OUR-60</t>
         </is>
       </c>
       <c r="B380" s="7" t="inlineStr">
@@ -15902,29 +15902,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C380" s="11" t="inlineStr">
-        <is>
-          <t>P3</t>
+      <c r="C380" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D380" s="9" t="inlineStr">
         <is>
-          <t>No AI on the shared capture</t>
+          <t>The Ours panel rides above the keyboard</t>
         </is>
       </c>
       <c r="E380" s="9" t="inlineStr">
         <is>
-          <t>Open the Ours capture panel with AI enabled in Settings, and type a long run-on line.</t>
+          <t>On a real Android device, tap the + pill on the Ours list, tap the box and start typing.</t>
         </is>
       </c>
       <c r="F380" s="9" t="inlineStr">
         <is>
-          <t>No 'Break it down', no 'Sort for me', and no 'Tidy this into tasks': steps or rewrites a model proposes would land on a list another person reads, and pointing a model at somebody else's screen is a decision about them. Speak stays (on-device dictation, not a server call) and so does Scan, which reads a photo INTO the box for you to edit rather than authoring anything, and is the one AI action that belongs here. See OUR-62.</t>
+          <t>The panel and its Add button stay visible above the keyboard while you type. Nothing on this stack does this by itself (edge-to-edge Android ignores softwareKeyboardLayoutMode), so it is done by hand and must be re-checked on a device, never only in a browser.</t>
         </is>
       </c>
       <c r="G380" s="7" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="H380" s="7" t="inlineStr"/>
@@ -15934,7 +15934,7 @@
     <row r="381">
       <c r="A381" s="6" t="inlineStr">
         <is>
-          <t>OUR-62</t>
+          <t>OUR-61</t>
         </is>
       </c>
       <c r="B381" s="7" t="inlineStr">
@@ -15942,29 +15942,29 @@
           <t>Ours</t>
         </is>
       </c>
-      <c r="C381" s="8" t="inlineS